--- a/data/final/family_office_dataset.xlsx
+++ b/data/final/family_office_dataset.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W13"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -799,12 +799,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEC13F-0001536411</t>
+          <t>SEC13F-0001596197</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Duquesne Family Office LLC</t>
+          <t>Intrepid Family Office Llc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -812,45 +812,21 @@
           <t>SFO</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Druckenmiller family (Stanley F. Druckenmiller)</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/duquesne-family-office-llc</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Duquesne Family Office is the private investment vehicle of billionaire investor Stanley Druckenmiller, established in 2010 after he returned outside capital and wound down his hedge fund Duquesne Capital Management (named for a park in his native Pittsburgh). It manages the Druckenmiller family's capital across public equities, and reportedly private/venture and credit positions, using a concentrated, macro-driven approach. It has no external clients.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Concentrated, top-down macro investing with high conviction and significant position turnover; opportunistic rotation across sectors and asset classes based on macroeconomic views. Public-equity book is typically 20-40 concentrated positions.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Broad/opportunistic across technology, healthcare/biotech, energy, consumer, financials and industrials; recent 13Fs (2025) show large positions in names like Natera, Insmed, Amazon, Teva and Woodward.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>13F US-listed equities ~$4.06B as of 2025-09-30 (Q3 2025) and ~$4.49B as of Q4 2025 -- a FLOOR, not total AUM. Total family-office AUM is not publicly disclosed; Druckenmiller's personal net worth is estimated at ~$11B (Bloomberg Billionaires Index, Jan 2025) and he ranks on the Forbes 2026 Billionaires list.</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Greenwich</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -860,12 +836,12 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Stanley F. Druckenmiller</t>
+          <t>Matt Dino</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Founder, Chairman &amp; CEO (Portfolio Manager)</t>
+          <t>Chief Financial Officer</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -877,17 +853,17 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>212-830-6500</t>
+          <t>(203) 862-3372</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Q3 2025 13F filed (portfolio ~$4.06B, 65 holdings); Q4 2025 13F portfolio rose to ~$4.49B with ~35 significant positions; Q1 2025 13F showed cuts and new tech/energy adds (~$3.06B, 52 holdings).</t>
+          <t>13F portfolio $123.64B across 38 US-listed positions as of 03-31-2026 (floor on AUM, 13(f) securities only). Top holdings: SPDR GOLD TR ($17.21B); ISHARES TR ($13.57B); VANGUARD INDEX FDS ($12.83B); ABRDN PLATINUM ETF TRUST ($7.13B); VANECK ETF TRUST ($6.00B)</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2025-11-14 (Q3 2025 13F filing, as of 2025-09-30); Q4 2025 (as of 2025-12-31); 2025-05-15 (Q1 2025 13F, as of 2025-03-31)</t>
+          <t>03-31-2026</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -897,19 +873,19 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Total AUM is not officially disclosed; the 13F equity value is only US-listed long equity positions (a floor). The LinkedIn company page may not be firm-operated. No individual email is published anywhere; none provided. Sue Meng (13F signatory) is General Counsel, not the investment decision-maker.</t>
+          <t>SFO inferred from unregistered-adviser + 13F + family-office name; the specific family is not yet named (pending research pass).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEC13F-0001889527</t>
+          <t>SEC13F-0001536411</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Louis-Dreyfus Family Office LLC</t>
+          <t>Duquesne Family Office LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -919,39 +895,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Louis-Dreyfus family -- specifically the American branch of Gerard 'William' Louis-Dreyfus (1932-2016), longtime chairman of Louis Dreyfus Company's US arm and father of actress Julia Louis-Dreyfus (INFERRED from co-location with LDC's Wilton HQ and the family/geography; not definitively documented).</t>
+          <t>Druckenmiller family (Stanley F. Druckenmiller)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/duquesne-family-office-llc</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Louis-Dreyfus Family Office LLC is a small private single-family office in Wilton, CT, associated with the American branch of the Louis-Dreyfus family (the commodities-trading dynasty). It is co-located with Louis Dreyfus Company's US headquarters at 10 Westport Road and manages family capital; its SEC 13F disclosed only about five holdings worth ~$65M. It is NOT the Louis Dreyfus Company commodities business itself.</t>
+          <t>Duquesne Family Office is the private investment vehicle of billionaire investor Stanley Druckenmiller, established in 2010 after he returned outside capital and wound down his hedge fund Duquesne Capital Management (named for a park in his native Pittsburgh). It manages the Druckenmiller family's capital across public equities, and reportedly private/venture and credit positions, using a concentrated, macro-driven approach. It has no external clients.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Not publicly documented. The limited 13F holdings (broad index funds VXUS/VTIAX and ITOT plus a couple of small single-name positions) suggest a conservative, largely passive/index-oriented public-markets allocation typical of a family office holding book, but this is inferred, not stated.</t>
+          <t>Concentrated, top-down macro investing with high conviction and significant position turnover; opportunistic rotation across sectors and asset classes based on macroeconomic views. Public-equity book is typically 20-40 concentrated positions.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Public 13F book was dominated by broad-market and international index funds (Vanguard Total International, iShares Core S&amp;P Total US Market ETF) plus small individual equity positions (e.g., Celularity, New Relic, Lovesac). Not sector-focused.</t>
+          <t>Broad/opportunistic across technology, healthcare/biotech, energy, consumer, financials and industrials; recent 13Fs (2025) show large positions in names like Natera, Insmed, Amazon, Teva and Woodward.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13F US-listed equities ~$64.7M as of 2022-09-30 (Q3 2022, 5 holdings) -- a floor and likely a small slice of total family wealth. Total AUM not disclosed. Business directories estimate ~$390K annual revenue / ~4 employees.</t>
+          <t>13F US-listed equities ~$4.06B as of 2025-09-30 (Q3 2025) and ~$4.49B as of Q4 2025 -- a FLOOR, not total AUM. Total family-office AUM is not publicly disclosed; Druckenmiller's personal net worth is estimated at ~$11B (Bloomberg Billionaires Index, Jan 2025) and he ranks on the Forbes 2026 Billionaires list.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Wilton</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -961,12 +941,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>W. Thomas Wingertzahn</t>
+          <t>Stanley F. Druckenmiller</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Chief Financial Officer (13F signatory / operational head)</t>
+          <t>Founder, Chairman &amp; CEO (Portfolio Manager)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -978,17 +958,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>203-762-6134</t>
+          <t>212-830-6500</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>No recent public activity found. The most recent SEC 13F on file is Q3 2022; no 2023-2025 13F filings surfaced, which may indicate the equity book fell below the 13F reporting threshold or the office stopped filing.</t>
+          <t>Q3 2025 13F filed (portfolio ~$4.06B, 65 holdings); Q4 2025 13F portfolio rose to ~$4.49B with ~35 significant positions; Q1 2025 13F showed cuts and new tech/energy adds (~$3.06B, 52 holdings).</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2022-11-10 (last 13F filing, holdings as of 2022-09-30)</t>
+          <t>2025-11-14 (Q3 2025 13F filing, as of 2025-09-30); Q4 2025 (as of 2025-12-31); 2025-05-15 (Q1 2025 13F, as of 2025-03-31)</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -998,19 +978,19 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>ENTITY-CONFUSION RISK: 'Louis-Dreyfus Family Office LLC' is NOT the Louis Dreyfus Company (LDC) commodities firm, though it shares the Wilton CT 10 Westport Road address. The specific family member/branch is INFERRED (Gerard 'William' Louis-Dreyfus's American branch; heirs include Julia Louis-Dreyfus and half-sisters Phoebe and Emma) and not definitively confirmed by a primary source; family_affiliation should be treated as probable, not certain. The true family investment decision-maker is undetermined; Wingertzahn is the CFO/signatory, reported as principal only for lack of a documented alternative. No website, no LinkedIn, no published email. 13F filings appear to have lapsed after 2022.</t>
+          <t>Total AUM is not officially disclosed; the 13F equity value is only US-listed long equity positions (a floor). The LinkedIn company page may not be firm-operated. No individual email is published anywhere; none provided. Sue Meng (13F signatory) is General Counsel, not the investment decision-maker.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UKCH-12706913</t>
+          <t>SEC13F-0001683689</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Francis Family Office Limited</t>
+          <t>Kopp Family Office, LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1018,70 +998,58 @@
           <t>SFO</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Francis family (Ben Francis, founder/CEO of Gymshark)</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Personal family-office / holding vehicle of Ben Francis, billionaire founder and majority owner of fitness-apparel brand Gymshark; holds part of his Gymshark shareholding.</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Holding company (concentrated Gymshark equity stake)</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>Minnetonka</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>West Midlands</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Benjamin David Francis</t>
+          <t>John P. Flakne</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Director &amp; 100% owner; Founder &amp; CEO of Gymshark</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/gymshark/</t>
-        </is>
-      </c>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>952-841-0450</t>
+        </is>
+      </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Renamed Ben Francis Ltd -&gt; Francis Family Office Ltd (2021); Ben Francis moved ~half his Gymshark stake into the vehicle; 2026 reporting he is seeking financing to buy back part of General Atlantic's Gymshark stake</t>
+          <t>13F portfolio $163.17B across 29 US-listed positions as of 06-30-2026 (floor on AUM, 13(f) securities only)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2021-02-03 (rename); 2026-07 (buyback reporting)</t>
+          <t>06-30-2026</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1091,19 +1059,19 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>No standalone website/LinkedIn/email for the FO itself — a private holding vehicle, not client-facing. Corporate secretary is a law-firm nominee, not the principal. Investment thesis/sectors not publicly disclosed.</t>
+          <t>SFO inferred from unregistered-adviser + 13F + family-office name; the specific family is not yet named (pending research pass).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UKCH-07931194</t>
+          <t>SEC13F-0001889527</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wimmer Family Office Ltd</t>
+          <t>Louis-Dreyfus Family Office LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1113,57 +1081,57 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Wimmer (Per Wimmer, Danish financier, founder of merchant bank Wimmer Financial)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://wfo.am/</t>
-        </is>
-      </c>
+          <t>Louis-Dreyfus family -- specifically the American branch of Gerard 'William' Louis-Dreyfus (1932-2016), longtime chairman of Louis Dreyfus Company's US arm and father of actress Julia Louis-Dreyfus (INFERRED from co-location with LDC's Wilton HQ and the family/geography; not definitively documented).</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>London (Mayfair) family office established by Per Wimmer, a Danish financier, entrepreneur and author; associated with his corporate-advisory firm Wimmer Financial.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Louis-Dreyfus Family Office LLC is a small private single-family office in Wilton, CT, associated with the American branch of the Louis-Dreyfus family (the commodities-trading dynasty). It is co-located with Louis Dreyfus Company's US headquarters at 10 Westport Road and manages family capital; its SEC 13F disclosed only about five holdings worth ~$65M. It is NOT the Louis Dreyfus Company commodities business itself.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Not publicly documented. The limited 13F holdings (broad index funds VXUS/VTIAX and ITOT plus a couple of small single-name positions) suggest a conservative, largely passive/index-oriented public-markets allocation typical of a family office holding book, but this is inferred, not stated.</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Natural resources (mining, oil &amp; gas, green energy); real estate; infrastructure; aviation; shipping; space economy</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>Public 13F book was dominated by broad-market and international index funds (Vanguard Total International, iShares Core S&amp;P Total US Market ETF) plus small individual equity positions (e.g., Celularity, New Relic, Lovesac). Not sector-focused.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>13F US-listed equities ~$64.7M as of 2022-09-30 (Q3 2022, 5 holdings) -- a floor and likely a small slice of total family wealth. Total AUM not disclosed. Business directories estimate ~$390K annual revenue / ~4 employees.</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Wilton</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Mayfair</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Per Thanning Wimmer</t>
+          <t>W. Thomas Wingertzahn</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO, Wimmer Family Office</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>https://uk.linkedin.com/in/perwimmer</t>
-        </is>
-      </c>
+          <t>Chief Financial Officer (13F signatory / operational head)</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
@@ -1172,17 +1140,17 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>+44 207 432 7575</t>
+          <t>203-762-6134</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>Per Wimmer resigned as director 2024-09-25; two new directors appointed same day (Aida Feriz, Joppe Sikma); FCA-authorised (FCA #665654)</t>
+          <t>No recent public activity found. The most recent SEC 13F on file is Q3 2022; no 2023-2025 13F filings surfaced, which may indicate the equity book fell below the 13F reporting threshold or the office stopped filing.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2024-09-25 (director change)</t>
+          <t>2022-11-10 (last 13F filing, holdings as of 2022-09-30)</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1192,81 +1160,73 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Corrected task hint: principal is PER Wimmer, not 'Klaus Wimmer'. Per Wimmer resigned as registered director 2024-09-25 but remains named founder on the site; current directors appear operational/successor. Phone is switchboard. AUM/thesis not disclosed.</t>
+          <t>ENTITY-CONFUSION RISK: 'Louis-Dreyfus Family Office LLC' is NOT the Louis Dreyfus Company (LDC) commodities firm, though it shares the Wilton CT 10 Westport Road address. The specific family member/branch is INFERRED (Gerard 'William' Louis-Dreyfus's American branch; heirs include Julia Louis-Dreyfus and half-sisters Phoebe and Emma) and not definitively confirmed by a primary source; family_affiliation should be treated as probable, not certain. The true family investment decision-maker is undetermined; Wingertzahn is the CFO/signatory, reported as principal only for lack of a documented alternative. No website, no LinkedIn, no published email. 13F filings appear to have lapsed after 2022.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEC13F-0001039807</t>
+          <t>UKCH-12706913</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Boston Family Office Llc</t>
+          <t>Francis Family Office Limited</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MFO</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://www.bosfam.com/</t>
-        </is>
-      </c>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Francis family (Ben Francis, founder/CEO of Gymshark)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>The Boston Family Office LLC is an independent, employee-owned registered investment adviser founded in 1996 and based in Boston, MA. It provides multi-family-office-style wealth management -- investment management, financial planning, and adviser selection -- to high-net-worth individuals, families and charitable organizations across roughly 789 accounts and ~$1.7-2.0B in assets. It is a multi-family/RIA firm rather than a single-family office.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Client-tailored, diversified portfolio management for wealth preservation and growth across HNW households and institutions; discretionary management (769 of 789 accounts discretionary). Specific house investment philosophy not detailed publicly.</t>
-        </is>
-      </c>
+          <t>Personal family-office / holding vehicle of Ben Francis, billionaire founder and majority owner of fitness-apparel brand Gymshark; holds part of his Gymshark shareholding.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Diversified multi-asset wealth management (public equities, fixed income, funds); not sector-specialized. A partner sits on the board of fixed-income manager Breckinridge Capital Advisors.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>~$1.7B AUM across 789 accounts (Form ADV/adviserinfo, 2024-2025); third-party profiles cite ~$1.9-2.02B. As of the most recent Form ADV (2024 filing cycle).</t>
-        </is>
-      </c>
+          <t>Holding company (concentrated Gymshark equity stake)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>West Midlands</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>George P. Beal</t>
+          <t>Benjamin David Francis</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; Managing Partner (Portfolio Manager)</t>
+          <t>Director &amp; 100% owner; Founder &amp; CEO of Gymshark</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/george-beal-a6107a16/</t>
+          <t>https://www.linkedin.com/in/gymshark/</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1275,19 +1235,15 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>617-624-0800</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Filed Form ADV Part 2A/2B brochures in the 2024 filing cycle (Feb 2024); a partner (Beal) serves on the board of Breckinridge Capital Advisors. Firm moved offices to 20 Custom House St.</t>
+          <t>Renamed Ben Francis Ltd -&gt; Francis Family Office Ltd (2021); Ben Francis moved ~half his Gymshark stake into the vehicle; 2026 reporting he is seeking financing to buy back part of General Atlantic's Gymshark stake</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2024-02-01 (ADV Part 2B brochure)</t>
+          <t>2021-02-03 (rename); 2026-07 (buyback reporting)</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1297,85 +1253,77 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Despite the 'family office' name, this is functionally a multi-family-office RIA / private wealth manager serving hundreds of client accounts, not a single family's office. Investment authority is distributed among ~8 managing directors, so Beal is one of several senior decision-makers (though the 13F signatory and co-founder). No official company LinkedIn URL confirmed. No individual email is published (the ZoomInfo masked pattern was deliberately not used).</t>
+          <t>No standalone website/LinkedIn/email for the FO itself — a private holding vehicle, not client-facing. Corporate secretary is a law-firm nominee, not the principal. Investment thesis/sectors not publicly disclosed.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SEC13F-0002017744</t>
+          <t>UKCH-07931194</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC</t>
+          <t>Wimmer Family Office Ltd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MFO</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Wimmer (Per Wimmer, Danish financier, founder of merchant bank Wimmer Financial)</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://arrowrootfamilyoffice.com/</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/arrowroot-family-office</t>
-        </is>
-      </c>
+          <t>https://wfo.am/</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC is a Marina del Rey, CA-based registered investment adviser and multi-family office, originally founded in 2013 as Vitreous Partners and rebranded in 2017. It provides multidisciplinary wealth management -- investment management, retirement, tax and estate planning -- to high-net-worth individuals, entrepreneurs, families and small institutions, with offices in Southern and Northern California, Virginia and Michigan. It is a multi-client RIA, not a single family's office.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Team-based, fiduciary, goals-driven wealth management emphasizing comprehensive planning and diversified investment management for affluent households and business owners; open-architecture advice.</t>
-        </is>
-      </c>
+          <t>London (Mayfair) family office established by Per Wimmer, a Danish financier, entrepreneur and author; associated with his corporate-advisory firm Wimmer Financial.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Diversified multi-asset wealth management (public equities, funds/ETFs, fixed income, alternatives); not sector-specialized.</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>~$431M AUM as of Q2 2025 (third-party profiles); regulatory AUM per the 2025 Form ADV on the firm's site. A floor for total client assets under advisement.</t>
-        </is>
-      </c>
+          <t>Natural resources (mining, oil &amp; gas, green energy); real estate; infrastructure; aviation; shipping; space economy</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Marina Del Rey</t>
+          <t>London</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>Mayfair</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Rob (Roberto Francisco) Santos</t>
+          <t>Per Thanning Wimmer</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Chief Executive Officer &amp; Principal Owner</t>
+          <t>Founder &amp; CEO, Wimmer Family Office</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/rob-santos-afo/</t>
+          <t>https://uk.linkedin.com/in/perwimmer</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -1386,17 +1334,17 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>310.341.4774</t>
+          <t>+44 207 432 7575</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Announced expansion of its private-wealth practice into Michigan via addition of The Athena Financial Group (offices now include Marina del Rey CA, Rochester Hills MI, Charlottesville VA, El Dorado Hills CA); filed updated Form ADV Part 2A/2B in April 2025.</t>
+          <t>Per Wimmer resigned as director 2024-09-25; two new directors appointed same day (Aida Feriz, Joppe Sikma); FCA-authorised (FCA #665654)</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2022-09-05 (Michigan/Athena expansion press release); 2025-04 (Form ADV update)</t>
+          <t>2024-09-25 (director change)</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1406,19 +1354,19 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Uses the 'family office' label but is a multi-client wealth-management RIA, not a single family's office. Possible name confusion with 'Arrowroot Capital Management' (a separate B2B enterprise-software private-equity firm) -- they are distinct; relationship not established here. No individual email published; RocketReach/broker data deliberately not used. Firm's most recent 13F filer registration is recent (CIK 0002017744).</t>
+          <t>Corrected task hint: principal is PER Wimmer, not 'Klaus Wimmer'. Per Wimmer resigned as registered director 2024-09-25 but remains named founder on the site; current directors appear operational/successor. Phone is switchboard. AUM/thesis not disclosed.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UKCH-09580739</t>
+          <t>SEC13F-0001039807</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Blu Family Office Limited</t>
+          <t>Boston Family Office Llc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1426,69 +1374,61 @@
           <t>MFO</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Originally Armbruester family (founder's wealth); now MFO serving multiple client families</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.blu-fo.com</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>https://uk.linkedin.com/company/blu-family-office</t>
-        </is>
-      </c>
+          <t>https://www.bosfam.com/</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>FCA-regulated multi-family office (Ltd inc. 2015; operations from 2010) in Richmond upon Thames, founded by Christian Armbruester post Credit Suisse. Offers hedge funds, crypto and alternatives; discretionary arm Blu Investment Management.</t>
+          <t>The Boston Family Office LLC is an independent, employee-owned registered investment adviser founded in 1996 and based in Boston, MA. It provides multi-family-office-style wealth management -- investment management, financial planning, and adviser selection -- to high-net-worth individuals, families and charitable organizations across roughly 789 accounts and ~$1.7-2.0B in assets. It is a multi-family/RIA firm rather than a single-family office.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Discretionary management not relying on forecasting; 'true diversification' and systematic rebalancing; passive in calm markets, opportunistic in adverse ones.</t>
+          <t>Client-tailored, diversified portfolio management for wealth preservation and growth across HNW households and institutions; discretionary management (769 of 789 accounts discretionary). Specific house investment philosophy not detailed publicly.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hedge funds; crypto assets; alternatives; diversified multi-asset</t>
+          <t>Diversified multi-asset wealth management (public equities, fixed income, funds); not sector-specialized. A partner sits on the board of fixed-income manager Breckinridge Capital Advisors.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>£0.5bn-£1bn (third-party estimated range)</t>
+          <t>~$1.7B AUM across 789 accounts (Form ADV/adviserinfo, 2024-2025); third-party profiles cite ~$1.9-2.02B. As of the most recent Form ADV (2024 filing cycle).</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Greater London</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Christian Armbruester</t>
+          <t>George P. Beal</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Founder &amp; Principal (largest shareholder ~40.8%)</t>
+          <t>Co-Founder &amp; Managing Partner (Portfolio Manager)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/christianarmbruesterblufamilyoffice</t>
+          <t>https://www.linkedin.com/in/george-beal-a6107a16/</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1497,15 +1437,19 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>617-624-0800</t>
+        </is>
+      </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Founded 2010; Ltd inc. 2015; new director Vishesh Dawar appointed Dec 2025; investment arm rebranded Blu Investment Management; Marie Redron now CEO</t>
+          <t>Filed Form ADV Part 2A/2B brochures in the 2024 filing cycle (Feb 2024); a partner (Beal) serves on the board of Breckinridge Capital Advisors. Firm moved offices to 20 Custom House St.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2015-05-08; 2025-12-08</t>
+          <t>2024-02-01 (ADV Part 2B brochure)</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1515,81 +1459,85 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Client-facing operations now run under 'Blu Investment Management' (blu-im.com), same address. Armbruester is founder/principal but not current CEO (Marie Redron is). AUM range is a third-party estimate. Only published contacts are a switchboard + generic mailbox.</t>
+          <t>Despite the 'family office' name, this is functionally a multi-family-office RIA / private wealth manager serving hundreds of client accounts, not a single family's office. Investment authority is distributed among ~8 managing directors, so Beal is one of several senior decision-makers (though the 13F signatory and co-founder). No official company LinkedIn URL confirmed. No individual email is published (the ZoomInfo masked pattern was deliberately not used).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UKCH-12233405</t>
+          <t>SEC13F-0002017744</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Schwarz Family Office Ltd</t>
+          <t>Arrowroot Family Office, LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Undetermined</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Named after principal Andreas Schwarz (German); no wider family group evidenced beyond the surname</t>
-        </is>
-      </c>
+          <t>MFO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://schwarzfamilyoffice.com/</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
+          <t>https://arrowrootfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/arrowroot-family-office</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>London-based boutique investment/advisory firm branded as a family office, established 2019, led by Andreas Schwarz; provides capital raising, debt financing, wealth management and IR services.</t>
+          <t>Arrowroot Family Office, LLC is a Marina del Rey, CA-based registered investment adviser and multi-family office, originally founded in 2013 as Vitreous Partners and rebranded in 2017. It provides multidisciplinary wealth management -- investment management, retirement, tax and estate planning -- to high-net-worth individuals, entrepreneurs, families and small institutions, with offices in Southern and Northern California, Virginia and Michigan. It is a multi-client RIA, not a single family's office.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>'Be not afraid of growing slowly, be afraid only of standing still' — sustainable growth via established relationships and exclusive investor access. https://schwarzfamilyoffice.com/</t>
+          <t>Team-based, fiduciary, goals-driven wealth management emphasizing comprehensive planning and diversified investment management for affluent households and business owners; open-architecture advice.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Private equity; fintech; wealth management; venture capital; private debt; IPOs</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>Diversified multi-asset wealth management (public equities, funds/ETFs, fixed income, alternatives); not sector-specialized.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>~$431M AUM as of Q2 2025 (third-party profiles); regulatory AUM per the 2025 Form ADV on the firm's site. A floor for total client assets under advisement.</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Marina Del Rey</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Maida Vale</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Andreas Schwarz</t>
+          <t>Rob (Roberto Francisco) Santos</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Founder / Director</t>
+          <t>Chief Executive Officer &amp; Principal Owner</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
+          <t>https://www.linkedin.com/in/rob-santos-afo/</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
@@ -1598,15 +1546,19 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>310.341.4774</t>
+        </is>
+      </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Listed in Family Capital 'FamCap 50' (2024); second shareholder Syed Furqan Ahmed (490 shares)</t>
+          <t>Announced expansion of its private-wealth practice into Michigan via addition of The Athena Financial Group (offices now include Marina del Rey CA, Rochester Hills MI, Charlottesville VA, El Dorado Hills CA); filed updated Form ADV Part 2A/2B in April 2025.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2024-02 (FamCap 50)</t>
+          <t>2022-09-05 (Michigan/Athena expansion press release); 2025-04 (Form ADV update)</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1616,53 +1568,69 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Presents as a family office but functions largely as a boutique capital-raising/advisory consultancy with two shareholders — fo_type left Undetermined. A Family Capital story linking Schwarz to a 'famous UK brand' is paywalled and the brand is NOT confirmed; not asserted. AUM undisclosed.</t>
+          <t>Uses the 'family office' label but is a multi-client wealth-management RIA, not a single family's office. Possible name confusion with 'Arrowroot Capital Management' (a separate B2B enterprise-software private-equity firm) -- they are distinct; relationship not established here. No individual email published; RocketReach/broker data deliberately not used. Firm's most recent 13F filer registration is recent (CIK 0002017744).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UKCH-14344019</t>
+          <t>UKCH-09580739</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hazell Family Office Ltd</t>
+          <t>Blu Family Office Limited</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hazell family of South Wales (haulage/waste/environmental-services wealth)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+          <t>Originally Armbruester family (founder's wealth); now MFO serving multiple client families</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://www.blu-fo.com</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/blu-family-office</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Active company (inc. 2022-09-08), SIC 70221 financial management; board is five members of the Hazell family. Structure strongly indicates a single-family office. No website/press footprint.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>FCA-regulated multi-family office (Ltd inc. 2015; operations from 2010) in Richmond upon Thames, founded by Christian Armbruester post Credit Suisse. Offers hedge funds, crypto and alternatives; discretionary arm Blu Investment Management.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Discretionary management not relying on forecasting; 'true diversification' and systematic rebalancing; passive in calm markets, opportunistic in adverse ones.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>70221 - Financial management</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>Hedge funds; crypto assets; alternatives; diversified multi-asset</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>£0.5bn-£1bn (third-party estimated range)</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Usk</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Monmouthshire, Wales</t>
+          <t>Greater London</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1672,15 +1640,19 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Mark David William Hazell</t>
+          <t>Christian Armbruester</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Director (family principal)</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
+          <t>Founder &amp; Principal (largest shareholder ~40.8%)</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/christianarmbruesterblufamilyoffice</t>
+        </is>
+      </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
@@ -1690,68 +1662,76 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Incorporated Sept 2022; five family directors appointed same day; principal is MD of family haulage/environmental companies</t>
+          <t>Founded 2010; Ltd inc. 2015; new director Vishesh Dawar appointed Dec 2025; investment arm rebranded Blu Investment Management; Marie Redron now CEO</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2015-05-08; 2025-12-08</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>SFO status inferred from shared surname + single family-farm address + Mark Hazell's operating-company directorships; no website/press confirms active investment operations. 'Mark = principal' is inference; control may be shared across the family.</t>
+          <t>Client-facing operations now run under 'Blu Investment Management' (blu-im.com), same address. Armbruester is founder/principal but not current CEO (Marie Redron is). AUM range is a third-party estimate. Only published contacts are a switchboard + generic mailbox.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UKCH-14442767</t>
+          <t>UKCH-12233405</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wedgwood Family Office Limited</t>
+          <t>Schwarz Family Office Ltd</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Undetermined</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wedgwood (Paul Wedgwood family)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>Named after principal Andreas Schwarz (German); no wider family group evidenced beyond the surname</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://schwarzfamilyoffice.com/</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>UK private company (inc. 2022-10-25) under fund-management SIC, registered at a residential address in Keston. Appears to be the personal single-family investment vehicle of Paul Wedgwood.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>London-based boutique investment/advisory firm branded as a family office, established 2019, led by Andreas Schwarz; provides capital raising, debt financing, wealth management and IR services.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>'Be not afraid of growing slowly, be afraid only of standing still' — sustainable growth via established relationships and exclusive investor access. https://schwarzfamilyoffice.com/</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>66300 - Fund management activities</t>
+          <t>Private equity; fintech; wealth management; venture capital; private debt; IPOs</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Keston</t>
+          <t>London</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Greater London (Bromley)</t>
+          <t>Maida Vale</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1761,15 +1741,19 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Paul Wedgwood</t>
+          <t>Andreas Schwarz</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
+          <t>Founder / Director</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
+        </is>
+      </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
@@ -1779,20 +1763,198 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
+          <t>Listed in Family Capital 'FamCap 50' (2024); second shareholder Syed Furqan Ahmed (490 shares)</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>2024-02 (FamCap 50)</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Presents as a family office but functions largely as a boutique capital-raising/advisory consultancy with two shareholders — fo_type left Undetermined. A Family Capital story linking Schwarz to a 'famous UK brand' is paywalled and the brand is NOT confirmed; not asserted. AUM undisclosed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>UKCH-14344019</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hazell Family Office Ltd</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Hazell family of South Wales (haulage/waste/environmental-services wealth)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Active company (inc. 2022-09-08), SIC 70221 financial management; board is five members of the Hazell family. Structure strongly indicates a single-family office. No website/press footprint.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>70221 - Financial management</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Usk</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Monmouthshire, Wales</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Mark David William Hazell</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Director (family principal)</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Incorporated Sept 2022; five family directors appointed same day; principal is MD of family haulage/environmental companies</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>SFO status inferred from shared surname + single family-farm address + Mark Hazell's operating-company directorships; no website/press confirms active investment operations. 'Mark = principal' is inference; control may be shared across the family.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UKCH-14442767</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Wedgwood Family Office Limited</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Wedgwood (Paul Wedgwood family)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>UK private company (inc. 2022-10-25) under fund-management SIC, registered at a residential address in Keston. Appears to be the personal single-family investment vehicle of Paul Wedgwood.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>66300 - Fund management activities</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Keston</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Greater London (Bromley)</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Paul Wedgwood</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>Co-director Christopher James Sharp resigned 2024-04-16; new secretary appointed 2026-01-06; accounts currently overdue</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>2024-04-16; 2026-01-06</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>C+</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Link between director 'Paul Wedgwood, b.1970' and the Splash Damage/Supernova entrepreneur is a strong inference (name + DOB + separate Wedgwood FIC directorship), NOT hard-confirmed. Zero public FO footprint (no website/LinkedIn/press/AUM); accounts overdue. Residential registered address.</t>
         </is>
@@ -1809,7 +1971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2079,12 +2241,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEC13F-0001536411</t>
+          <t>SEC13F-0001596197</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Duquesne Family Office LLC</t>
+          <t>INTREPID FAMILY OFFICE LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2094,37 +2256,33 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001536411); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001596197); discovered via fts</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001536411&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001596197&amp;type=13F</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Widely reported as the private investment office through which Stanley Druckenmiller manages his own family's capital after closing his hedge fund Duquesne Capital Management to outside investors in 2010. No external clients; it manages one family's money. Source: https://www.fool.com/investing/how-to-invest/famous-investors/duquesne-family-office and https://www.institutionalinvestor.com/article/stan-druckenmiller-overhauls-his-family-offices-us-stock-portfolio</t>
+          <t>No SEC investment-adviser registration found in IAPD (searched 'INTREPID FAMILY OFFICE LLC'); files SEC Form 13F-HR (CIK 0001596197) reporting $123.64B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Files SEC Form 13F as 'Duquesne Family Office LLC' (CIK 0001536411); press uniformly describes it as Druckenmiller's family office. Source: https://13f.info/manager/0001536411-duquesne-family-office-llc</t>
+          <t>No SEC investment-adviser registration found in IAPD (searched 'INTREPID FAMILY OFFICE LLC'); files SEC Form 13F-HR (CIK 0001596197) reporting $123.64B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>13F value: https://13f.info/13f/000153641125000017-duquesne-family-office-llc-q3-2025 (as of 2025-09-30) and https://seekingalpha.com/article/4881297-tracking-stanley-druckenmillers-duquesne-family-office-portfolio-q4-2025-update ; net worth: https://www.forbes.com/profile/stanley-druckenmiller/</t>
-        </is>
-      </c>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Druckenmiller is the founder and sole principal directing all investment decisions; he is named as portfolio manager on the firm's 13F activity in current (2025) press coverage. The 13F signatory Sue Meng is General Counsel (compliance), not the investment decision-maker. Source: https://www.institutionalinvestor.com/article/stan-druckenmiller-overhauls-his-family-offices-us-stock-portfolio and https://www.levelfields.ai/news/stanley-druckenmillers-duquesne-family-office-cuts-exposure-adds-new-tech-and-energy-stocks-in-q1-2025</t>
+          <t>Signed the firm's Form 13F-HR (03-31-2026) as Chief Financial Officer — verified associated person; investment-decision-maker status to be confirmed separately.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2133,19 +2291,15 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Tried: web searches for a Duquesne domain/team page (none exists); no firm website to host a team directory; no filing or press publishing an individual email. Refused to construct one from a name+domain pattern.</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1536411/000153641126000004/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>https://13f.info/13f/000153641125000017-duquesne-family-office-llc-q3-2025 ; https://seekingalpha.com/article/4881297-tracking-stanley-druckenmillers-duquesne-family-office-portfolio-q4-2025-update ; https://www.levelfields.ai/news/stanley-druckenmillers-duquesne-family-office-cuts-exposure-adds-new-tech-and-energy-stocks-in-q1-2025</t>
+          <t>SEC EDGAR 13F-HR 0001013594-26-000589 (2026-05-15)</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -2153,12 +2307,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEC13F-0001889527</t>
+          <t>SEC13F-0001536411</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Louis-Dreyfus Family Office LLC</t>
+          <t>Duquesne Family Office LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2168,37 +2322,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001889527); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001536411); discovered via fts</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001889527&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001536411&amp;type=13F</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>A small, named single-family office (5 13F holdings, ~$64.7M, ~4 employees per business directories) serving the Louis-Dreyfus family; no evidence of external clients or a marketed multi-family service offering. Source: https://www.ctcompanydir.com/companies/louis-dreyfus-family-office-llc/ and https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
+          <t>Widely reported as the private investment office through which Stanley Druckenmiller manages his own family's capital after closing his hedge fund Duquesne Capital Management to outside investors in 2010. No external clients; it manages one family's money. Source: https://www.fool.com/investing/how-to-invest/famous-investors/duquesne-family-office and https://www.institutionalinvestor.com/article/stan-druckenmiller-overhauls-his-family-offices-us-stock-portfolio</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Registered LLC named 'Louis-Dreyfus Family Office LLC' at 10 Westport Rd, Wilton CT (registered 2007 per directory); files SEC 13F under CIK 0001889527. Source: https://www.ctcompanydir.com/companies/louis-dreyfus-family-office-llc/</t>
+          <t>Files SEC Form 13F as 'Duquesne Family Office LLC' (CIK 0001536411); press uniformly describes it as Druckenmiller's family office. Source: https://13f.info/manager/0001536411-duquesne-family-office-llc</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>corroborated</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc (latest filing Q3 2022, value ~$64,676K as of 2022-09-30); directory revenue estimate: https://www.manta.com/c/mm0v4v4/loius-dreyfus-family-office-llc</t>
+          <t>13F value: https://13f.info/13f/000153641125000017-duquesne-family-office-llc-q3-2025 (as of 2025-09-30) and https://seekingalpha.com/article/4881297-tracking-stanley-druckenmillers-duquesne-family-office-portfolio-q4-2025-update ; net worth: https://www.forbes.com/profile/stanley-druckenmiller/</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Wingertzahn is the named 13F signatory and CFO; for an office this small he is likely the day-to-day operational and investment administrator. However, the TRUE family investment principal (a Louis-Dreyfus family member/heir) is not publicly identified. Source (signatory role provided in brief); firm identity: https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
+          <t>Druckenmiller is the founder and sole principal directing all investment decisions; he is named as portfolio manager on the firm's 13F activity in current (2025) press coverage. The 13F signatory Sue Meng is General Counsel (compliance), not the investment decision-maker. Source: https://www.institutionalinvestor.com/article/stan-druckenmiller-overhauls-his-family-offices-us-stock-portfolio and https://www.levelfields.ai/news/stanley-druckenmillers-duquesne-family-office-cuts-exposure-adds-new-tech-and-energy-stocks-in-q1-2025</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2209,17 +2363,17 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Tried: searches for a firm website/team page (none), for Wingertzahn contact details, and for any filing/press publishing an individual email. None found published. Did not construct any address.</t>
+          <t>Tried: web searches for a Duquesne domain/team page (none exists); no firm website to host a team directory; no filing or press publishing an individual email. Refused to construct one from a name+domain pattern.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1536411/000153641126000004/primary_doc.xml</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
+          <t>https://13f.info/13f/000153641125000017-duquesne-family-office-llc-q3-2025 ; https://seekingalpha.com/article/4881297-tracking-stanley-druckenmillers-duquesne-family-office-portfolio-q4-2025-update ; https://www.levelfields.ai/news/stanley-druckenmillers-duquesne-family-office-cuts-exposure-adds-new-tech-and-energy-stocks-in-q1-2025</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -2227,69 +2381,65 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UKCH-12706913</t>
+          <t>SEC13F-0001683689</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Francis Family Office Limited</t>
+          <t>Kopp Family Office, LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Companies House 12706913 (Private limited company); inc. 30 June 2020</t>
+          <t>EDGAR 13F filer (CIK 0001683689); discovered via fts</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/12706913</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001683689&amp;type=13F</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Directors are three members of the Francis family (Benjamin David, Joseph John, Steven John Francis); vehicle holds Ben Francis's Gymshark stake. Source: https://find-and-update.company-information.service.gov.uk/company/12706913/officers ; https://www.netincome.co/p/the-boardroom-drama-behind-one-of</t>
+          <t>No SEC investment-adviser registration found in IAPD (searched 'Kopp Family Office, LLC'); files SEC Form 13F-HR (CIK 0001683689) reporting $163.17B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Companies House shows firm renamed from 'BEN FRANCIS LIMITED' to 'FRANCIS FAMILY OFFICE LIMITED' on 2021-02-03; SIC 64209; registered at Gymshark HQ. Press: Ben Francis transferred half his Gymshark ownership into the vehicle, which he owns 100%. Sources: https://find-and-update.company-information.service.gov.uk/company/12706913 ; https://www.netincome.co/p/the-boardroom-drama-behind-one-of</t>
+          <t>No SEC investment-adviser registration found in IAPD (searched 'Kopp Family Office, LLC'); files SEC Form 13F-HR (CIK 0001683689) reporting $163.17B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Not disclosed. Ben Francis personal net worth ~$900m-1.3bn (Forbes) is personal wealth, not stated FO AUM. https://www.forbes.com/profile/ben-francis-1/</t>
-        </is>
-      </c>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Named director since incorporation (2020-06-30), 100% owner and actual decision-maker. https://find-and-update.company-information.service.gov.uk/company/12706913/officers</t>
+          <t>Signed the firm's Form 13F-HR (06-30-2026) as Chief Financial Officer — verified associated person; investment-decision-maker status to be confirmed separately.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>No individual email published; firm has no website. Checked Companies House filings and Gymshark press.</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1683689/000089271226000313/primary_doc.xml</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/12706913 ; https://www.forbes.com/sites/robertolsen-1/2026/07/04/britains-youngest-billionaire-wants-more-control-over-gymshark/</t>
+          <t>SEC EDGAR 13F-HR 0000892712-26-000313 (2026-07-09)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -2297,77 +2447,73 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UKCH-07931194</t>
+          <t>SEC13F-0001889527</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Wimmer Family Office Ltd</t>
+          <t>Louis-Dreyfus Family Office LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Companies House 07931194 (Private limited company); inc. 1 February 2012</t>
+          <t>EDGAR 13F filer (CIK 0001889527); discovered via fts</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/07931194</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001889527&amp;type=13F</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Website: 'The Wimmer Family Office is based in Mayfair, London, and was established by Per Wimmer.' Built around a single principal. https://wfo.am/</t>
+          <t>A small, named single-family office (5 13F holdings, ~$64.7M, ~4 employees per business directories) serving the Louis-Dreyfus family; no evidence of external clients or a marketed multi-family service offering. Source: https://www.ctcompanydir.com/companies/louis-dreyfus-family-office-llc/ and https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Active FCA-authorised entity (FCA #665654), SIC 66190; live website branded as a family office with Mayfair address. https://wfo.am/ ; https://find-and-update.company-information.service.gov.uk/company/07931194</t>
+          <t>Registered LLC named 'Louis-Dreyfus Family Office LLC' at 10 Westport Rd, Wilton CT (registered 2007 per directory); files SEC 13F under CIK 0001889527. Source: https://www.ctcompanydir.com/companies/louis-dreyfus-family-office-llc/</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>corroborated</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Not disclosed. Sectors are those of associated firm Wimmer Financial. https://wimmerfinancial.com/</t>
+          <t>https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc (latest filing Q3 2022, value ~$64,676K as of 2022-09-30); directory revenue estimate: https://www.manta.com/c/mm0v4v4/loius-dreyfus-family-office-llc</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Founder/namesake; director from incorporation (2012) until resignation 2024-09-25; still presented as founder/CEO on website and LinkedIn. https://find-and-update.company-information.service.gov.uk/company/07931194/officers ; https://uk.linkedin.com/in/perwimmer</t>
+          <t>Wingertzahn is the named 13F signatory and CFO; for an office this small he is likely the day-to-day operational and investment administrator. However, the TRUE family investment principal (a Louis-Dreyfus family member/heir) is not publicly identified. Source (signatory role provided in brief); firm identity: https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://wfo.am/</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Only a generic mailbox (info@WFO.am) is published (excluded). A per.wimmer@wimmerfinancial.com string appeared only in a URL parameter, not as a published contact — not shipped.</t>
+          <t>Tried: searches for a firm website/team page (none), for Wingertzahn contact details, and for any filing/press publishing an individual email. None found published. Did not construct any address.</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>https://wfo.am/contact-us/ (firm switchboard, not a personal line)</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/07931194/officers</t>
+          <t>https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -2375,37 +2521,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEC13F-0001039807</t>
+          <t>UKCH-12706913</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Boston Family Office LLC</t>
+          <t>Francis Family Office Limited</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sec-13f</t>
+          <t>uk-companies-house</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001039807); discovered via fts</t>
+          <t>Companies House 12706913 (Private limited company); inc. 30 June 2020</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001039807&amp;type=13F</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/12706913</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (CRD #107141) serving many clients -- ~789 accounts across high-net-worth individuals, retail investors and charitable organizations; ~$1.7-2.0B AUM; 15 partners. This is a multi-family office / wealth-management RIA, not a single family's office. Source: https://adviserinfo.sec.gov/firm/summary/107141 and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
+          <t>Directors are three members of the Francis family (Benjamin David, Joseph John, Steven John Francis); vehicle holds Ben Francis's Gymshark stake. Source: https://find-and-update.company-information.service.gov.uk/company/12706913/officers ; https://www.netincome.co/p/the-boardroom-drama-behind-one-of</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Operates as an RIA branded as a family office ('The Boston Family Office'), founded 1996; files 13F under CIK 0001039807. Source: https://www.bosfam.com/george-beal/</t>
+          <t>Companies House shows firm renamed from 'BEN FRANCIS LIMITED' to 'FRANCIS FAMILY OFFICE LIMITED' on 2021-02-03; SIC 64209; registered at Gymshark HQ. Press: Ben Francis transferred half his Gymshark ownership into the vehicle, which he owns 100%. Sources: https://find-and-update.company-information.service.gov.uk/company/12706913 ; https://www.netincome.co/p/the-boardroom-drama-behind-one-of</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2415,12 +2561,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/107141 (Form ADV, 2024-2025) and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
+          <t>Not disclosed. Ben Francis personal net worth ~$900m-1.3bn (Forbes) is personal wealth, not stated FO AUM. https://www.forbes.com/profile/ben-francis-1/</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Beal co-founded the firm in 1996, is a Managing Partner and portfolio manager, and is the named 13F signatory -- an active, current investment decision-maker. Note the firm has 15 partners / ~8 active managing directors, so investment authority is shared. Source: https://www.bosfam.com/george-beal/</t>
+          <t>Named director since incorporation (2020-06-30), 100% owner and actual decision-maker. https://find-and-update.company-information.service.gov.uk/company/12706913/officers</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2431,17 +2577,13 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Tried: fetched bosfam.com homepage and bosfam.com/george-beal/ team page -- only phone (617-624-0800) is published, no email. A ZoomInfo listing shows a masked pattern 'g***@bosfam.com' but that is a data-broker inference, NOT a published/attested individual address, so it is excluded. Did not construct an address.</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
-        </is>
-      </c>
+          <t>No individual email published; firm has no website. Checked Companies House filings and Gymshark press.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>https://www.bosfam.com/wp-content/uploads/2024/02/2024-ADV-Part-2B-Brochure-Supplement_FINAL.pdf ; https://adviserinfo.sec.gov/firm/summary/107141</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/12706913 ; https://www.forbes.com/sites/robertolsen-1/2026/07/04/britains-youngest-billionaire-wants-more-control-over-gymshark/</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -2449,37 +2591,37 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SEC13F-0002017744</t>
+          <t>UKCH-07931194</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC</t>
+          <t>Wimmer Family Office Ltd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sec-13f</t>
+          <t>uk-companies-house</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0002017744); discovered via fts</t>
+          <t>Companies House 07931194 (Private limited company); inc. 1 February 2012</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002017744&amp;type=13F</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/07931194</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>A registered investment adviser and multi-family office that markets 'Multi Family Office Services' and serves many clients -- high-net-worth individuals, entrepreneurs, families and family offices -- with ~20 staff across multiple US offices. Source: https://arrowrootfamilyoffice.com/team/ and https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
+          <t>Website: 'The Wimmer Family Office is based in Mayfair, London, and was established by Per Wimmer.' Built around a single principal. https://wfo.am/</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SEC-registered RIA (Form ADV on file, SEC# 801-121878) branded 'Arrowroot Family Office'; files 13F under CIK 0002017744; multiple offices and a published team. Source: https://9at.com/Adviser/801-121878</t>
+          <t>Active FCA-authorised entity (FCA #665654), SIC 66190; live website branded as a family office with Mayfair address. https://wfo.am/ ; https://find-and-update.company-information.service.gov.uk/company/07931194</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2489,12 +2631,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://fintrx.com/firms/firm/arrowroot-family-office-llc-168744 (~$431M, Q2 2025); Form ADV: https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf (2025)</t>
+          <t>Not disclosed. Sectors are those of associated firm Wimmer Financial. https://wimmerfinancial.com/</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Santos is CEO and principal owner, leading the firm; he is the 13F signatory (Roberto Santos = Rob Santos) and a current decision-maker with 20+ years' experience. Source: https://arrowrootfamilyoffice.com/team/ and https://www.getwarmer.com/advisors/roberto-francisco-santos</t>
+          <t>Founder/namesake; director from incorporation (2012) until resignation 2024-09-25; still presented as founder/CEO on website and LinkedIn. https://find-and-update.company-information.service.gov.uk/company/07931194/officers ; https://uk.linkedin.com/in/perwimmer</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2502,20 +2644,24 @@
           <t>confirmed</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://wfo.am/</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Tried: fetched the firm's team page (no email published, only phone 833-224-2249 and a contact form); searched for a published individual email; only data-broker (RocketReach) listings exist, which are not published/attested. Did not construct an address.</t>
+          <t>Only a generic mailbox (info@WFO.am) is published (excluded). A per.wimmer@wimmerfinancial.com string appeared only in a URL parameter, not as a published contact — not shipped.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
+          <t>https://wfo.am/contact-us/ (firm switchboard, not a personal line)</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>https://www.arrowrootfamilyoffice.com/press-releases/arrowroot-family-office-in-michigan/ ; https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/07931194/officers</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -2523,37 +2669,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UKCH-09580739</t>
+          <t>SEC13F-0001039807</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Blu Family Office Limited</t>
+          <t>Boston Family Office LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Companies House 09580739 (Private limited company); inc. 8 May 2015</t>
+          <t>EDGAR 13F filer (CIK 0001039807); discovered via fts</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/09580739</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001039807&amp;type=13F</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Founded 2010 by Christian Armbruester (ex-Credit Suisse) to manage his own family's wealth, then expanded to serve multiple families; repeatedly described as a multi-family office in press (Citywire, Private Banker International). FCA-regulated discretionary manager.</t>
+          <t>SEC-registered investment adviser (CRD #107141) serving many clients -- ~789 accounts across high-net-worth individuals, retail investors and charitable organizations; ~$1.7-2.0B AUM; 15 partners. This is a multi-family office / wealth-management RIA, not a single family's office. Source: https://adviserinfo.sec.gov/firm/summary/107141 and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Live FCA-regulated firm; active website; investment arm 'Blu Investment Management' (blu-im.com); corporate LinkedIn; named press profiles; defined team.</t>
+          <t>Operates as an RIA branded as a family office ('The Boston Family Office'), founded 1996; files 13F under CIK 0001039807. Source: https://www.bosfam.com/george-beal/</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2563,12 +2709,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Third-party estimate via industry data/press (Citywire wealth-manager profile); not officially disclosed.</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/107141 (Form ADV, 2024-2025) and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Founder and principal investment decision-maker; single largest shareholder; individual, not nominee. Current day-to-day CEO is Marie Redron.</t>
+          <t>Beal co-founded the firm in 1996, is a Managing Partner and portfolio manager, and is the named 13F signatory -- an active, current investment decision-maker. Note the firm has 15 partners / ~8 active managing directors, so investment authority is shared. Source: https://www.bosfam.com/george-beal/</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2579,13 +2725,17 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Firm site publishes only a generic mailbox (info@blu-im.com). No individual/principal email published anywhere located. Nothing pattern-generated.</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>Tried: fetched bosfam.com homepage and bosfam.com/george-beal/ team page -- only phone (617-624-0800) is published, no email. A ZoomInfo listing shows a masked pattern 'g***@bosfam.com' but that is a data-broker inference, NOT a published/attested individual address, so it is excluded. Did not construct an address.</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/09580739/officers; https://citywire.com/wealth-manager/news/richmond-based-multi-family-boutique-names-new-ceo/a1109198</t>
+          <t>https://www.bosfam.com/wp-content/uploads/2024/02/2024-ADV-Part-2B-Brochure-Supplement_FINAL.pdf ; https://adviserinfo.sec.gov/firm/summary/107141</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -2593,52 +2743,52 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UKCH-12233405</t>
+          <t>SEC13F-0002017744</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Schwarz Family Office Ltd</t>
+          <t>Arrowroot Family Office, LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Companies House 12233405 (Private limited company); inc. 30 September 2019</t>
+          <t>EDGAR 13F filer (CIK 0002017744); discovered via fts</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/12233405</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002017744&amp;type=13F</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Website describes a 'boutique consultancy' providing debt financing, capital raising, IR and fund management for clients, with multiple partners — more advisory/MFO-style than a pure single-family office despite the name. Two shareholders. https://schwarzfamilyoffice.com/</t>
+          <t>A registered investment adviser and multi-family office that markets 'Multi Family Office Services' and serves many clients -- high-net-worth individuals, entrepreneurs, families and family offices -- with ~20 staff across multiple US offices. Source: https://arrowrootfamilyoffice.com/team/ and https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Active company, SIC 64304 + consultancy codes; own website; listed in Family Capital's 'FamCap 50'. https://schwarzfamilyoffice.com/ ; https://find-and-update.company-information.service.gov.uk/company/12233405</t>
+          <t>SEC-registered RIA (Form ADV on file, SEC# 801-121878) branded 'Arrowroot Family Office'; files 13F under CIK 0002017744; multiple offices and a published team. Source: https://9at.com/Adviser/801-121878</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>corroborated</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>https://fintrx.com/firms/firm/arrowroot-family-office-llc-168744 (~$431M, Q2 2025); Form ADV: https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf (2025)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Sole director since incorporation (2019) and majority shareholder (510/1000); ex Merrill Lynch and Bank of Singapore. https://find-and-update.company-information.service.gov.uk/company/12233405/officers ; https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
+          <t>Santos is CEO and principal owner, leading the firm; he is the 13F signatory (Roberto Santos = Rob Santos) and a current decision-maker with 20+ years' experience. Source: https://arrowrootfamilyoffice.com/team/ and https://www.getwarmer.com/advisors/roberto-francisco-santos</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -2649,13 +2799,17 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Only a generic mailbox (admin@schwarzfamilyoffice.com) is published (excluded). RocketReach result is a masked/broker source and excluded.</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>Tried: fetched the firm's team page (no email published, only phone 833-224-2249 and a contact form); searched for a published individual email; only data-broker (RocketReach) listings exist, which are not published/attested. Did not construct an address.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>https://www.famcap.com/2024/02/the-famcap-50-the-worlds-top-family-capital-investment-specialists/</t>
+          <t>https://www.arrowrootfamilyoffice.com/press-releases/arrowroot-family-office-in-michigan/ ; https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
         </is>
       </c>
       <c r="P11" t="inlineStr"/>
@@ -2663,12 +2817,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UKCH-14344019</t>
+          <t>UKCH-09580739</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hazell Family Office Ltd</t>
+          <t>Blu Family Office Limited</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2678,50 +2832,54 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Companies House 14344019 (Private limited company); inc. 8 September 2022</t>
+          <t>Companies House 09580739 (Private limited company); inc. 8 May 2015</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14344019</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/09580739</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>All five directors share surname Hazell and one family address (Cefn Henllan Farm, Llanhennock, Usk); appointed same day 2022-09-08; DOB spread (1959-1994) indicates two parents + three adult children — a single-family board. SIC 70221 (financial management).</t>
+          <t>Founded 2010 by Christian Armbruester (ex-Credit Suisse) to manage his own family's wealth, then expanded to serve multiple families; repeatedly described as a multi-family office in press (Citywire, Private Banker International). FCA-regulated discretionary manager.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Family-only board, no external/nominee officers. Patriarch Mark Hazell is MD of the family's operating businesses (haulage / environmental services), a plausible wealth source. https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
+          <t>Live FCA-regulated firm; active website; investment arm 'Blu Investment Management' (blu-im.com); corporate LinkedIn; named press profiles; defined team.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Third-party estimate via industry data/press (Citywire wealth-manager profile); not officially disclosed.</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Patriarch (b.1959), MD of the family operating companies; most probable investment decision-maker; individual, not nominee.</t>
+          <t>Founder and principal investment decision-maker; single largest shareholder; individual, not nominee. Current day-to-day CEO is Marie Redron.</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>No firm website; searches returned only company/director aggregators; no published individual email. Nothing pattern-generated.</t>
+          <t>Firm site publishes only a generic mailbox (info@blu-im.com). No individual/principal email published anywhere located. Nothing pattern-generated.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/09580739/officers; https://citywire.com/wealth-manager/news/richmond-based-multi-family-boutique-names-new-ceo/a1109198</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -2729,12 +2887,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UKCH-14442767</t>
+          <t>UKCH-12233405</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Wedgwood Family Office Limited</t>
+          <t>Schwarz Family Office Ltd</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2744,22 +2902,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Companies House 14442767 (Private limited company); inc. 25 October 2022</t>
+          <t>Companies House 12233405 (Private limited company); inc. 30 September 2019</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14442767</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/12233405</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SIC 66300 (fund management), sole active director Paul Wedgwood at a single residential address; no external clients/multi-family structure. Principal separately holds 'Wedgwood FIC Limited' (a Family Investment Company), consistent with a single-family vehicle.</t>
+          <t>Website describes a 'boutique consultancy' providing debt financing, capital raising, IR and fund management for clients, with multiple partners — more advisory/MFO-style than a pure single-family office despite the name. Two shareholders. https://schwarzfamilyoffice.com/</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Active company (inc. 2022-10-25), SIC 66300, residential registered address. Director Paul Wedgwood (b. Jun 1970) very likely the video-game entrepreneur who sold Splash Damage (up to $150m, 2016) and co-founded Supernova Capital — a plausible wealth source. https://en.wikipedia.org/wiki/Paul_Wedgwood</t>
+          <t>Active company, SIC 64304 + consultancy codes; own website; listed in Family Capital's 'FamCap 50'. https://schwarzfamilyoffice.com/ ; https://find-and-update.company-information.service.gov.uk/company/12233405</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2767,30 +2925,166 @@
           <t>corroborated</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Sole active decision-making director since incorporation. Almost certainly the Splash Damage / Supernova Capital entrepreneur (DOB match; also director of Wedgwood FIC Limited).</t>
+          <t>Sole director since incorporation (2019) and majority shareholder (510/1000); ex Merrill Lynch and Bank of Singapore. https://find-and-update.company-information.service.gov.uk/company/12233405/officers ; https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>No firm website/press page; no individual email published. A uk.linkedin.com/in/paulwedgwood profile is labelled 'The Carbon Trust' and cannot be confirmed as the same person; nothing inferred.</t>
+          <t>Only a generic mailbox (admin@schwarzfamilyoffice.com) is published (excluded). RocketReach result is a masked/broker source and excluded.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
+          <t>https://www.famcap.com/2024/02/the-famcap-50-the-worlds-top-family-capital-investment-specialists/</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>UKCH-14344019</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Hazell Family Office Ltd</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>uk-companies-house</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Companies House 14344019 (Private limited company); inc. 8 September 2022</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14344019</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>All five directors share surname Hazell and one family address (Cefn Henllan Farm, Llanhennock, Usk); appointed same day 2022-09-08; DOB spread (1959-1994) indicates two parents + three adult children — a single-family board. SIC 70221 (financial management).</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Family-only board, no external/nominee officers. Patriarch Mark Hazell is MD of the family's operating businesses (haulage / environmental services), a plausible wealth source. https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Patriarch (b.1959), MD of the family operating companies; most probable investment decision-maker; individual, not nominee.</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No firm website; searches returned only company/director aggregators; no published individual email. Nothing pattern-generated.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UKCH-14442767</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Wedgwood Family Office Limited</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>uk-companies-house</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Companies House 14442767 (Private limited company); inc. 25 October 2022</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14442767</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>SIC 66300 (fund management), sole active director Paul Wedgwood at a single residential address; no external clients/multi-family structure. Principal separately holds 'Wedgwood FIC Limited' (a Family Investment Company), consistent with a single-family vehicle.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Active company (inc. 2022-10-25), SIC 66300, residential registered address. Director Paul Wedgwood (b. Jun 1970) very likely the video-game entrepreneur who sold Splash Damage (up to $150m, 2016) and co-founded Supernova Capital — a plausible wealth source. https://en.wikipedia.org/wiki/Paul_Wedgwood</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Sole active decision-making director since incorporation. Almost certainly the Splash Damage / Supernova Capital entrepreneur (DOB match; also director of Wedgwood FIC Limited).</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No firm website/press page; no individual email published. A uk.linkedin.com/in/paulwedgwood profile is labelled 'The Carbon Trust' and cannot be confirmed as the same person; nothing inferred.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>https://find-and-update.company-information.service.gov.uk/company/14442767/officers</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2803,7 +3097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3285,7 +3579,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DAO FAMILY OFFICE LP</t>
+          <t>Crew Family Office Limited</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3296,7 +3590,7 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3602,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DAVIDOFF FREY FAMILY OFFICE (UK) LTD</t>
+          <t>DAO FAMILY OFFICE LP</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3331,7 +3625,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DE VILLIERS FAMILY OFFICE LIMITED</t>
+          <t>DAVIDOFF FREY FAMILY OFFICE (UK) LTD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3354,7 +3648,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DEUTSCHE BANK AG\</t>
+          <t>DE VILLIERS FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3377,7 +3671,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DONE FAMILY OFFICE LIMITED</t>
+          <t>DEUTSCHE BANK AG\</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3400,7 +3694,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DONNELLY FAMILY OFFICE</t>
+          <t>DONE FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3423,7 +3717,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DSW FAMILY OFFICE LTD</t>
+          <t>DONNELLY FAMILY OFFICE</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3446,7 +3740,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DUBAI FAMILY OFFICE LTD</t>
+          <t>DSW FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3469,7 +3763,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dorsey &amp; Whitney Trust CO LLC</t>
+          <t>DUBAI FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3492,7 +3786,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EMFO, LLC</t>
+          <t>Dorsey &amp; Whitney Trust CO LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3515,7 +3809,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FAMILY OFFICE CONSULTING LIMITED</t>
+          <t>EMFO, LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3538,7 +3832,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FAMILY OFFICE EEB LTD</t>
+          <t>FAMILY OFFICE CONSULTING LIMITED</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3561,7 +3855,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FIDUCIARY FAMILY OFFICE, LLC</t>
+          <t>FAMILY OFFICE EEB LTD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3584,7 +3878,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FOOTPRINTS FAMILY OFFICE UK EUROPE LIMITED</t>
+          <t>FIDUCIARY FAMILY OFFICE, LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3607,7 +3901,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FREEDMAN FAMILY OFFICE</t>
+          <t>FOOTPRINTS FAMILY OFFICE UK EUROPE LIMITED</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3630,7 +3924,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FRIGUS FAMILY OFFICE LTD</t>
+          <t>FREEDMAN FAMILY OFFICE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3653,7 +3947,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FRONTIER FAMILY OFFICE FORUM HOLDINGS LIMITED</t>
+          <t>FRIGUS FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3676,7 +3970,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Family Investment Center, Inc.</t>
+          <t>FRONTIER FAMILY OFFICE FORUM HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3699,7 +3993,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Family Office DS Limited</t>
+          <t>Family Investment Center, Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -3710,7 +4004,7 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -3768,7 +4062,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Family Office Research LLC</t>
+          <t>Family Office DS Limited</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3779,7 +4073,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -3791,7 +4085,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Fortis Advisors, LLC</t>
+          <t>Family Office DS Limited</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3802,7 +4096,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -3814,7 +4108,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Fortitude Family Office, LLC</t>
+          <t>Family Office Research LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3837,7 +4131,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GELLING FAMILY OFFICE LIMITED</t>
+          <t>Fortis Advisors, LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3860,7 +4154,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GUNPUTH FAMILY OFFICE LIMITED</t>
+          <t>Fortitude Family Office, LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3883,7 +4177,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Geller Advisors LLC</t>
+          <t>GELLING FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3906,7 +4200,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HALL LAURIE J TRUSTEE</t>
+          <t>GUNPUTH FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3929,7 +4223,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HBBA FAMILY OFFICE LIMITED</t>
+          <t>Geller Advisors LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3952,7 +4246,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HILL FAMILY OFFICE LIMITED</t>
+          <t>HALL LAURIE J TRUSTEE</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3975,7 +4269,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
+          <t>HBBA FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3998,7 +4292,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>INTREPID FAMILY OFFICE LLC</t>
+          <t>HILL FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4021,7 +4315,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISHER CAPITAL FAMILY OFFICE LTD</t>
+          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4044,7 +4338,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Independent Family Office, LLC</t>
+          <t>INTREPID FAMILY OFFICE LLC</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4067,7 +4361,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kopp Family Office, LLC</t>
+          <t>ISHER CAPITAL FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4090,7 +4384,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LELS CLARK FAMILY OFFICE LTD</t>
+          <t>Independent Family Office, LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4113,7 +4407,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Lido Advisors, LLC</t>
+          <t>Kopp Family Office, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4136,7 +4430,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>MARCUARD FAMILY OFFICE LTD</t>
+          <t>LELS CLARK FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4159,7 +4453,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>MOBH UK FAMILY OFFICE LTD</t>
+          <t>Lido Advisors, LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4182,7 +4476,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NORTHBRIDGE FAMILY OFFICE LTD</t>
+          <t>MARCUARD FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4205,7 +4499,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NOVA FAMILY OFFICE LTD</t>
+          <t>MOBH UK FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4228,7 +4522,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nilsson Family Office Ltd</t>
+          <t>NORTHBRIDGE FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4239,7 +4533,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -4251,7 +4545,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nilsson Family Office Ltd</t>
+          <t>NOVA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4262,7 +4556,7 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4591,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OLD HOUSE FAMILY OFFICE LIMITED</t>
+          <t>Nilsson Family Office Ltd</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4308,7 +4602,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4614,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OneAscent Family Office, LLC</t>
+          <t>Nilsson Family Office Ltd</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4331,7 +4625,7 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4637,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Orion Porfolio Solutions, LLC</t>
+          <t>Nilsson Family Office Ltd</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4354,7 +4648,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4660,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Orion Portfolio Solutions, LLC</t>
+          <t>OLD HOUSE FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4389,7 +4683,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PANDA FAMILY OFFICE LTD</t>
+          <t>OneAscent Family Office, LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4412,7 +4706,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PANTHEON A FAMILY OFFICE LIMITED</t>
+          <t>Orion Porfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4435,7 +4729,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PATHSTONE FAMILY OFFICE, LLC</t>
+          <t>Orion Portfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4458,7 +4752,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PMG Family Office LLC</t>
+          <t>PANDA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4481,7 +4775,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PROSPERITY FAMILY OFFICE LIMITED</t>
+          <t>PANTHEON A FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4504,7 +4798,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Pathstone Holdings, LLC</t>
+          <t>PATHSTONE FAMILY OFFICE, LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4527,7 +4821,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Pioneer Family Office, LLC</t>
+          <t>PMG Family Office LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4550,7 +4844,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RALPH FAMILY OFFICE LIMITED</t>
+          <t>PROSPERITY FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4573,7 +4867,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SHA FAMILY OFFICE LTD</t>
+          <t>Pathstone Holdings, LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4596,7 +4890,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SIGNATURE FAMILY OFFICE LTD</t>
+          <t>Pioneer Family Office, LLC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4619,7 +4913,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SIMON FAMILY OFFICE INSURES LIMITED</t>
+          <t>RALPH FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4642,7 +4936,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SWAILES COMMERCIAL FAMILY OFFICE LTD</t>
+          <t>SHA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4665,7 +4959,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SWAILES TRADING GROUP FAMILY OFFICE LTD</t>
+          <t>SIGNATURE FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4688,7 +4982,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sageworth Trust Co</t>
+          <t>SIMON FAMILY OFFICE INSURES LIMITED</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -4711,7 +5005,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Standard Family Office LLC</t>
+          <t>SWAILES COMMERCIAL FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -4734,7 +5028,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Stenger Family Office, LLC</t>
+          <t>SWAILES TRADING GROUP FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -4757,7 +5051,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Stokes Family Office, LLC</t>
+          <t>Sageworth Trust Co</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -4780,7 +5074,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>THE DIGITAL FAMILY OFFICE LIMITED</t>
+          <t>Standard Family Office LLC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4803,7 +5097,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>THE FAMILY OFFICE CHELTENHAM LIMITED</t>
+          <t>Stenger Family Office, LLC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4826,7 +5120,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TIGRIS FAMILY OFFICE LIMITED</t>
+          <t>Stokes Family Office, LLC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4849,7 +5143,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tarbox Family Office, Inc.</t>
+          <t>THE DIGITAL FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4872,7 +5166,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Timonier Family Office, LTD.</t>
+          <t>THE FAMILY OFFICE CHELTENHAM LIMITED</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4895,7 +5189,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TrustBank</t>
+          <t>TIGRIS FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4918,7 +5212,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>UNITA FAMILY OFFICE UK LIMITED</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4941,7 +5235,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>UR FAMILY OFFICE MANAGEMENT SERVICES LTD</t>
+          <t>Timonier Family Office, LTD.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4964,7 +5258,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>VASIL FAMILY OFFICE LLP</t>
+          <t>TrustBank</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -4987,7 +5281,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>VPR Management LLC</t>
+          <t>UNITA FAMILY OFFICE UK LIMITED</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5010,7 +5304,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>VSTAR LONDON FAMILY OFFICE LTD</t>
+          <t>UR FAMILY OFFICE MANAGEMENT SERVICES LTD</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5033,7 +5327,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Veritable, L.P.</t>
+          <t>VASIL FAMILY OFFICE LLP</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5056,7 +5350,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Virtus Family Office LLC</t>
+          <t>VPR Management LLC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5079,7 +5373,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>WEYBRIDGE FAMILY OFFICE SERVICES LIMITED</t>
+          <t>VSTAR LONDON FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5102,7 +5396,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Wealthgate Family Office, LLC</t>
+          <t>Veritable, L.P.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5125,7 +5419,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Wilmington Savings Fund Society, FSB</t>
+          <t>Virtus Family Office LLC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5135,6 +5429,75 @@
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>WEYBRIDGE FAMILY OFFICE SERVICES LIMITED</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Wealthgate Family Office, LLC</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Wilmington Savings Fund Society, FSB</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
         <is>
           <t>fo_proof_strength not established ('blank')</t>
         </is>
@@ -5183,11 +5546,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>57%</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5565,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>43%</t>
         </is>
       </c>
     </row>
@@ -5214,7 +5577,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" t="inlineStr"/>
     </row>
@@ -5225,7 +5588,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" t="inlineStr"/>
     </row>

--- a/data/final/family_office_dataset.xlsx
+++ b/data/final/family_office_dataset.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -442,7 +442,7 @@
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
     <col width="26" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
     <col width="32" customWidth="1" min="14" max="14"/>
@@ -1960,6 +1960,201 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>UKCH-10876208</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sha Family Office Ltd</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Sha family (controlling PSCs: Mr Sharnpreet Singh Buttar)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>64205 - Activities of financial services holding companies; 64209 - Activities of other holding companies not elsewhere classified</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>SIC codes - 64205</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>UK filing SIC: fo-relevant-sic. Active officers: BUTTAR, Sharnpreet Singh () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>UKCH-15240886</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Freedman Family Office</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Freedman family (controlling PSCs: Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>64301 - Activities of investment trusts</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>UK filing SIC: fo-relevant-sic. Active officers: FREEDMAN, Elaine Wilson (), FREEDMAN, Laura-Leigh (), ZIMMERMAN, Samantha Jade () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>UKCH-11031775</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Ralph Family Office Limited</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Ralph family (controlling PSCs: Melanie Lynette Ralph; Mr Jan De Ridder Ralph)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>64301 - Activities of investment trusts; 68209 - Other letting and operating of own or leased real estate</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>SIC codes - 64301</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>UK filing SIC: fo-relevant-sic. Active officers: RALPH, Jan De Ridder (), RALPH, Melanie Lynette (), BETHELL, Karen (), BETHELL, Stuart (), YOULL, Gavin William () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1971,7 +2166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -3086,6 +3281,168 @@
       </c>
       <c r="P15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>UKCH-10876208</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SHA FAMILY OFFICE LTD</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>uk-companies-house</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Companies House 10876208 (Private limited company); inc. 20 July 2017</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/10876208</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Mr Sharnpreet Singh Buttar); firm carries a fund-management/investment SIC (64205 - Activities of financial services holding companies). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Mr Sharnpreet Singh Buttar); firm carries a fund-management/investment SIC (64205 - Activities of financial services holding companies). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>UKCH-15240886</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>FREEDMAN FAMILY OFFICE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>uk-companies-house</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Companies House 15240886 (Private unlimited company); inc. 27 October 2023</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/15240886</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>UKCH-11031775</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>RALPH FAMILY OFFICE LIMITED</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>uk-companies-house</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Companies House 11031775 (Private limited company); inc. 25 October 2017</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/11031775</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Melanie Lynette Ralph; Mr Jan De Ridder Ralph); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Melanie Lynette Ralph; Mr Jan De Ridder Ralph); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3097,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3602,7 +3959,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DAO FAMILY OFFICE LP</t>
+          <t>Crew Family Office Limited</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3613,7 +3970,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3982,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DAVIDOFF FREY FAMILY OFFICE (UK) LTD</t>
+          <t>DAO FAMILY OFFICE LP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3648,7 +4005,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DE VILLIERS FAMILY OFFICE LIMITED</t>
+          <t>DAVIDOFF FREY FAMILY OFFICE (UK) LTD</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3671,7 +4028,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DEUTSCHE BANK AG\</t>
+          <t>DE VILLIERS FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3694,7 +4051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DONE FAMILY OFFICE LIMITED</t>
+          <t>DEUTSCHE BANK AG\</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3717,7 +4074,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DONNELLY FAMILY OFFICE</t>
+          <t>DONE FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3740,7 +4097,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DSW FAMILY OFFICE LTD</t>
+          <t>DONNELLY FAMILY OFFICE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3763,7 +4120,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DUBAI FAMILY OFFICE LTD</t>
+          <t>DSW FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3786,7 +4143,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dorsey &amp; Whitney Trust CO LLC</t>
+          <t>DUBAI FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3809,7 +4166,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EMFO, LLC</t>
+          <t>Dorsey &amp; Whitney Trust CO LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3832,7 +4189,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FAMILY OFFICE CONSULTING LIMITED</t>
+          <t>EMFO, LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3855,7 +4212,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FAMILY OFFICE EEB LTD</t>
+          <t>FAMILY OFFICE CONSULTING LIMITED</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3878,7 +4235,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FIDUCIARY FAMILY OFFICE, LLC</t>
+          <t>FAMILY OFFICE EEB LTD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3901,7 +4258,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FOOTPRINTS FAMILY OFFICE UK EUROPE LIMITED</t>
+          <t>FIDUCIARY FAMILY OFFICE, LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3924,7 +4281,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FREEDMAN FAMILY OFFICE</t>
+          <t>FOOTPRINTS FAMILY OFFICE UK EUROPE LIMITED</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3947,7 +4304,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FRIGUS FAMILY OFFICE LTD</t>
+          <t>FREEDMAN FAMILY OFFICE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3970,7 +4327,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FRONTIER FAMILY OFFICE FORUM HOLDINGS LIMITED</t>
+          <t>FRIGUS FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3993,7 +4350,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Family Investment Center, Inc.</t>
+          <t>FRONTIER FAMILY OFFICE FORUM HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4016,7 +4373,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Family Office DS Limited</t>
+          <t>Family Investment Center, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4027,7 +4384,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -4108,7 +4465,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Family Office Research LLC</t>
+          <t>Family Office DS Limited</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4119,7 +4476,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4131,7 +4488,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Fortis Advisors, LLC</t>
+          <t>Family Office DS Limited</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4142,7 +4499,7 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4511,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Fortitude Family Office, LLC</t>
+          <t>Family Office Research LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4177,7 +4534,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GELLING FAMILY OFFICE LIMITED</t>
+          <t>Fortis Advisors, LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4200,7 +4557,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GUNPUTH FAMILY OFFICE LIMITED</t>
+          <t>Fortitude Family Office, LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4223,7 +4580,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Geller Advisors LLC</t>
+          <t>GELLING FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4246,7 +4603,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HALL LAURIE J TRUSTEE</t>
+          <t>GUNPUTH FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4269,7 +4626,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>HBBA FAMILY OFFICE LIMITED</t>
+          <t>Geller Advisors LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4292,7 +4649,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HILL FAMILY OFFICE LIMITED</t>
+          <t>HALL LAURIE J TRUSTEE</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4315,7 +4672,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
+          <t>HBBA FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4338,7 +4695,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>INTREPID FAMILY OFFICE LLC</t>
+          <t>HILL FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4361,7 +4718,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISHER CAPITAL FAMILY OFFICE LTD</t>
+          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4384,7 +4741,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Independent Family Office, LLC</t>
+          <t>INTREPID FAMILY OFFICE LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4407,7 +4764,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Kopp Family Office, LLC</t>
+          <t>ISHER CAPITAL FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4430,7 +4787,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LELS CLARK FAMILY OFFICE LTD</t>
+          <t>Independent Family Office, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4453,7 +4810,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lido Advisors, LLC</t>
+          <t>Kopp Family Office, LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4476,7 +4833,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>MARCUARD FAMILY OFFICE LTD</t>
+          <t>LELS CLARK FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4499,7 +4856,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>MOBH UK FAMILY OFFICE LTD</t>
+          <t>Lido Advisors, LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4522,7 +4879,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NORTHBRIDGE FAMILY OFFICE LTD</t>
+          <t>MARCUARD FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4545,7 +4902,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NOVA FAMILY OFFICE LTD</t>
+          <t>MOBH UK FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4568,7 +4925,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nilsson Family Office Ltd</t>
+          <t>NORTHBRIDGE FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4579,7 +4936,7 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -4591,7 +4948,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Nilsson Family Office Ltd</t>
+          <t>NOVA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4602,7 +4959,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -4660,7 +5017,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OLD HOUSE FAMILY OFFICE LIMITED</t>
+          <t>Nilsson Family Office Ltd</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4671,7 +5028,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4683,7 +5040,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OneAscent Family Office, LLC</t>
+          <t>Nilsson Family Office Ltd</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4694,7 +5051,7 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4706,7 +5063,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Orion Porfolio Solutions, LLC</t>
+          <t>Nilsson Family Office Ltd</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4717,7 +5074,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4729,7 +5086,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Orion Portfolio Solutions, LLC</t>
+          <t>OLD HOUSE FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4752,7 +5109,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PANDA FAMILY OFFICE LTD</t>
+          <t>OneAscent Family Office, LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4775,7 +5132,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PANTHEON A FAMILY OFFICE LIMITED</t>
+          <t>Orion Porfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4798,7 +5155,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PATHSTONE FAMILY OFFICE, LLC</t>
+          <t>Orion Portfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4821,7 +5178,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PMG Family Office LLC</t>
+          <t>PANDA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -4844,7 +5201,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PROSPERITY FAMILY OFFICE LIMITED</t>
+          <t>PANTHEON A FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -4867,7 +5224,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pathstone Holdings, LLC</t>
+          <t>PATHSTONE FAMILY OFFICE, LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -4890,7 +5247,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pioneer Family Office, LLC</t>
+          <t>PMG Family Office LLC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -4913,7 +5270,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RALPH FAMILY OFFICE LIMITED</t>
+          <t>PROSPERITY FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -4936,7 +5293,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SHA FAMILY OFFICE LTD</t>
+          <t>Pathstone Holdings, LLC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -4959,7 +5316,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SIGNATURE FAMILY OFFICE LTD</t>
+          <t>Pioneer Family Office, LLC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4982,7 +5339,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SIMON FAMILY OFFICE INSURES LIMITED</t>
+          <t>RALPH FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5005,7 +5362,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SWAILES COMMERCIAL FAMILY OFFICE LTD</t>
+          <t>SHA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5028,7 +5385,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SWAILES TRADING GROUP FAMILY OFFICE LTD</t>
+          <t>SIGNATURE FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5051,7 +5408,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Sageworth Trust Co</t>
+          <t>SIMON FAMILY OFFICE INSURES LIMITED</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5074,7 +5431,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Standard Family Office LLC</t>
+          <t>SWAILES COMMERCIAL FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5097,7 +5454,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Stenger Family Office, LLC</t>
+          <t>SWAILES TRADING GROUP FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5120,7 +5477,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Stokes Family Office, LLC</t>
+          <t>Sageworth Trust Co</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5143,7 +5500,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>THE DIGITAL FAMILY OFFICE LIMITED</t>
+          <t>Standard Family Office LLC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5166,7 +5523,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>THE FAMILY OFFICE CHELTENHAM LIMITED</t>
+          <t>Stenger Family Office, LLC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5189,7 +5546,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TIGRIS FAMILY OFFICE LIMITED</t>
+          <t>Stokes Family Office, LLC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5212,7 +5569,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tarbox Family Office, Inc.</t>
+          <t>THE DIGITAL FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5235,7 +5592,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Timonier Family Office, LTD.</t>
+          <t>THE FAMILY OFFICE CHELTENHAM LIMITED</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5258,7 +5615,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TrustBank</t>
+          <t>TIGRIS FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5281,7 +5638,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>UNITA FAMILY OFFICE UK LIMITED</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5304,7 +5661,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>UR FAMILY OFFICE MANAGEMENT SERVICES LTD</t>
+          <t>Timonier Family Office, LTD.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5327,7 +5684,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>VASIL FAMILY OFFICE LLP</t>
+          <t>TrustBank</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5350,7 +5707,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VPR Management LLC</t>
+          <t>UNITA FAMILY OFFICE UK LIMITED</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5373,7 +5730,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>VSTAR LONDON FAMILY OFFICE LTD</t>
+          <t>UR FAMILY OFFICE MANAGEMENT SERVICES LTD</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5396,7 +5753,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Veritable, L.P.</t>
+          <t>VASIL FAMILY OFFICE LLP</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5419,7 +5776,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Virtus Family Office LLC</t>
+          <t>VPR Management LLC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5442,7 +5799,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>WEYBRIDGE FAMILY OFFICE SERVICES LIMITED</t>
+          <t>VSTAR LONDON FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5465,7 +5822,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Wealthgate Family Office, LLC</t>
+          <t>Veritable, L.P.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5488,7 +5845,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Wilmington Savings Fund Society, FSB</t>
+          <t>Virtus Family Office LLC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5498,6 +5855,75 @@
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>WEYBRIDGE FAMILY OFFICE SERVICES LIMITED</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Wealthgate Family Office, LLC</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Wilmington Savings Fund Society, FSB</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
         <is>
           <t>fo_proof_strength not established ('blank')</t>
         </is>
@@ -5550,7 +5976,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>47%</t>
         </is>
       </c>
     </row>
@@ -5561,11 +5987,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>53%</t>
         </is>
       </c>
     </row>
@@ -5577,7 +6003,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" t="inlineStr"/>
     </row>
@@ -5588,7 +6014,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C6" t="inlineStr"/>
     </row>

--- a/data/final/family_office_dataset.xlsx
+++ b/data/final/family_office_dataset.xlsx
@@ -452,7 +452,7 @@
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="18" customWidth="1" min="19" max="19"/>
     <col width="60" customWidth="1" min="20" max="20"/>
-    <col width="60" customWidth="1" min="21" max="21"/>
+    <col width="50" customWidth="1" min="21" max="21"/>
     <col width="19" customWidth="1" min="22" max="22"/>
     <col width="60" customWidth="1" min="23" max="23"/>
   </cols>
@@ -664,12 +664,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Firm operates from Austin, TX (9011 Mountain Ridge Drive) with an investment team led by CIO Anthony Lopiccolo (CFA, at Custos since 2018) and founding principal Mitchell Herr; both are ex-J.P. Morgan Private Bank. Recent third-party AUM profiles (2024-2025) place assets in the ~$347-532M range.</t>
+          <t>13F portfolio approx $0.15B across 60 US-listed positions as of 12-31-2025 (floor on AUM; 13(f) equities only, unit-normalized from filing). Top holdings: ISHARES TR ($0.07B); VANGUARD INTL EQUITY INDEX F ($13.84B); FIDELITY COVINGTON TRUST ($9.25B); VANGUARD INDEX FDS ($8.47B)</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2018 (Lopiccolo joined/founding era); 2024-2025 (AUM profiles)</t>
+          <t>12-31-2025</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -777,12 +777,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Reported crossing $5B AUM in March 2024, ~2 years after a Feb 2022 launch; built via a Callan LLC brand-licensing/partnership deal and Abbot Downing/Wells Fargo advisor recruitment; featured in RIABiz and a Diamond Consultants podcast.</t>
+          <t>13F portfolio approx $4.41B across 1131 US-listed positions as of 03-31-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing)</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2022-02 (founding); 2024-03 (crossed $5B AUM); 2024-04-09 (RIABiz feature)</t>
+          <t>03-31-2026</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>13F portfolio $123.64B across 38 US-listed positions as of 03-31-2026 (floor on AUM, 13(f) securities only). Top holdings: SPDR GOLD TR ($17.21B); ISHARES TR ($13.57B); VANGUARD INDEX FDS ($12.83B); ABRDN PLATINUM ETF TRUST ($7.13B); VANECK ETF TRUST ($6.00B)</t>
+          <t>13F portfolio approx $0.12B across 38 US-listed positions as of 03-31-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing). Top holdings: SPDR GOLD TR ($17.21B); ISHARES TR ($13.57B); VANGUARD INDEX FDS ($12.83B); ABRDN PLATINUM ETF TRUST ($7.13B)</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Q3 2025 13F filed (portfolio ~$4.06B, 65 holdings); Q4 2025 13F portfolio rose to ~$4.49B with ~35 significant positions; Q1 2025 13F showed cuts and new tech/energy adds (~$3.06B, 52 holdings).</t>
+          <t>13F portfolio approx $3.38B across 70 US-listed positions as of 03-31-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing). Top holdings: Natera Inc ($0.61B); Ishares Inc ($0.29B); Insmed Inc ($0.19B); Taiwan Semiconductor Manufac ($0.17B)</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2025-11-14 (Q3 2025 13F filing, as of 2025-09-30); Q4 2025 (as of 2025-12-31); 2025-05-15 (Q1 2025 13F, as of 2025-03-31)</t>
+          <t>03-31-2026</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>13F portfolio $163.17B across 29 US-listed positions as of 06-30-2026 (floor on AUM, 13(f) securities only)</t>
+          <t>13F portfolio approx $0.16B across 29 US-listed positions as of 06-30-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>No recent public activity found. The most recent SEC 13F on file is Q3 2022; no 2023-2025 13F filings surfaced, which may indicate the equity book fell below the 13F reporting threshold or the office stopped filing.</t>
+          <t>13F portfolio approx $0.07B across 5 US-listed positions as of 09-30-2022 (floor on AUM; 13(f) equities only, unit-normalized from filing). Top holdings: VANGUARD STAR FDS ($0.03B); ISHARES TR ($0.03B); CELULARITY INC ($0.00B); NEW RELIC INC ($0.00B)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2022-11-10 (last 13F filing, holdings as of 2022-09-30)</t>
+          <t>09-30-2022</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1444,12 +1444,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Filed Form ADV Part 2A/2B brochures in the 2024 filing cycle (Feb 2024); a partner (Beal) serves on the board of Breckinridge Capital Advisors. Firm moved offices to 20 Custom House St.</t>
+          <t>13F portfolio approx $1.50B across 311 US-listed positions as of 03-31-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing)</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2024-02-01 (ADV Part 2B brochure)</t>
+          <t>03-31-2026</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1553,12 +1553,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Announced expansion of its private-wealth practice into Michigan via addition of The Athena Financial Group (offices now include Marina del Rey CA, Rochester Hills MI, Charlottesville VA, El Dorado Hills CA); filed updated Form ADV Part 2A/2B in April 2025.</t>
+          <t>13F portfolio approx $0.30B across 156 US-listed positions as of 03-31-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing). Top holdings: ISHARES TR ($0.06B); VANGUARD SCOTTSDALE FDS ($47.98B); VANGUARD INDEX FDS ($16.14B); SCHWAB STRATEGIC TR ($14.02B)</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2022-09-05 (Michigan/Athena expansion press release); 2025-04 (Form ADV update)</t>
+          <t>03-31-2026</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -3454,7 +3454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AQR CAPITAL MANAGEMENT LLC</t>
+          <t>ADVISOR PARTNERS II, LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3556,7 +3556,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AUXILIUM FAMILY OFFICE LIMITED</t>
+          <t>AQR CAPITAL MANAGEMENT LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3591,7 +3591,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Allie Family Office LLC</t>
+          <t>AQR CAPITAL MANAGEMENT LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3602,7 +3602,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aurelius Family Office LLC</t>
+          <t>AUXILIUM FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BANK OF MONTREAL /CAN/</t>
+          <t>Allie Family Office LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BRYN MAWR BANK CORP</t>
+          <t>Aurelius Family Office LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Biltmore Family Office, LLC</t>
+          <t>BANK OF MONTREAL /CAN/</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CAMBIENT FAMILY OFFICE, LLC</t>
+          <t>BANK OF MONTREAL /CAN/</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3717,7 +3717,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CAROLINE BAKER FAMILY OFFICE LIMITED</t>
+          <t>BRYN MAWR BANK CORP</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3752,7 +3752,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CK PROPERTIES AND FAMILY OFFICE LIMITED</t>
+          <t>BRYN MAWR BANK CORP</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3763,7 +3763,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>COLLECTIVE FAMILY OFFICE LLC</t>
+          <t>Biltmore Family Office, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CVA Family Office, LLC</t>
+          <t>CAMBIENT FAMILY OFFICE, LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capitol Family Office, Inc.</t>
+          <t>CAROLINE BAKER FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3844,7 +3844,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Crestone Asset Management LLC</t>
+          <t>CK PROPERTIES AND FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Crew Family Office Limited</t>
+          <t>COLLECTIVE FAMILY OFFICE LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3878,7 +3878,7 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3890,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Crew Family Office Limited</t>
+          <t>CVA Family Office, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3901,7 +3901,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3913,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Crew Family Office Limited</t>
+          <t>Capitol Family Office, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3924,7 +3924,7 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Crew Family Office Limited</t>
+          <t>Crestone Asset Management LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3947,7 +3947,7 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3959,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Crew Family Office Limited</t>
+          <t>Crestone Asset Management LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3970,7 +3970,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3982,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DAO FAMILY OFFICE LP</t>
+          <t>Crew Family Office Limited</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3993,7 +3993,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DAVIDOFF FREY FAMILY OFFICE (UK) LTD</t>
+          <t>Crew Family Office Limited</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4016,7 +4016,7 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DE VILLIERS FAMILY OFFICE LIMITED</t>
+          <t>Crew Family Office Limited</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4039,7 +4039,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DEUTSCHE BANK AG\</t>
+          <t>Crew Family Office Limited</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4062,7 +4062,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DONE FAMILY OFFICE LIMITED</t>
+          <t>Crew Family Office Limited</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4085,7 +4085,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DONNELLY FAMILY OFFICE</t>
+          <t>DAO FAMILY OFFICE LP</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DSW FAMILY OFFICE LTD</t>
+          <t>DAVIDOFF FREY FAMILY OFFICE (UK) LTD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DUBAI FAMILY OFFICE LTD</t>
+          <t>DE VILLIERS FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dorsey &amp; Whitney Trust CO LLC</t>
+          <t>DEUTSCHE BANK AG\</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EMFO, LLC</t>
+          <t>DEUTSCHE BANK AG\</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4200,7 +4200,7 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>FAMILY OFFICE CONSULTING LIMITED</t>
+          <t>DONE FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>FAMILY OFFICE EEB LTD</t>
+          <t>DONNELLY FAMILY OFFICE</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FIDUCIARY FAMILY OFFICE, LLC</t>
+          <t>DSW FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FOOTPRINTS FAMILY OFFICE UK EUROPE LIMITED</t>
+          <t>DUBAI FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4304,7 +4304,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FREEDMAN FAMILY OFFICE</t>
+          <t>Dorsey &amp; Whitney Trust CO LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4327,7 +4327,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FRIGUS FAMILY OFFICE LTD</t>
+          <t>Dorsey &amp; Whitney Trust CO LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4338,7 +4338,7 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FRONTIER FAMILY OFFICE FORUM HOLDINGS LIMITED</t>
+          <t>EMFO, LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Family Investment Center, Inc.</t>
+          <t>EMFO, LLC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4384,7 +4384,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Family Office DS Limited</t>
+          <t>FAMILY OFFICE CONSULTING LIMITED</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4407,7 +4407,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Family Office DS Limited</t>
+          <t>FAMILY OFFICE EEB LTD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4430,7 +4430,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Family Office DS Limited</t>
+          <t>FIDUCIARY FAMILY OFFICE, LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4453,7 +4453,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4465,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Family Office DS Limited</t>
+          <t>FOOTPRINTS FAMILY OFFICE UK EUROPE LIMITED</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4476,7 +4476,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Family Office DS Limited</t>
+          <t>FREEDMAN FAMILY OFFICE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4499,7 +4499,7 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Family Office Research LLC</t>
+          <t>FRIGUS FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Fortis Advisors, LLC</t>
+          <t>FRONTIER FAMILY OFFICE FORUM HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Fortitude Family Office, LLC</t>
+          <t>Family Investment Center, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4580,7 +4580,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GELLING FAMILY OFFICE LIMITED</t>
+          <t>Family Investment Center, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4591,7 +4591,7 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4603,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GUNPUTH FAMILY OFFICE LIMITED</t>
+          <t>Family Office DS Limited</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4614,7 +4614,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Geller Advisors LLC</t>
+          <t>Family Office DS Limited</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4637,7 +4637,7 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>HALL LAURIE J TRUSTEE</t>
+          <t>Family Office DS Limited</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4660,7 +4660,7 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>HBBA FAMILY OFFICE LIMITED</t>
+          <t>Family Office DS Limited</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4683,7 +4683,7 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HILL FAMILY OFFICE LIMITED</t>
+          <t>Family Office DS Limited</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4706,7 +4706,7 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
+          <t>Family Office Research LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>INTREPID FAMILY OFFICE LLC</t>
+          <t>Fortis Advisors, LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISHER CAPITAL FAMILY OFFICE LTD</t>
+          <t>Fortis Advisors, LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4775,7 +4775,7 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -4787,7 +4787,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Independent Family Office, LLC</t>
+          <t>Fortitude Family Office, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Kopp Family Office, LLC</t>
+          <t>GELLING FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4833,7 +4833,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LELS CLARK FAMILY OFFICE LTD</t>
+          <t>GUNPUTH FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Lido Advisors, LLC</t>
+          <t>Geller Advisors LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>MARCUARD FAMILY OFFICE LTD</t>
+          <t>Geller Advisors LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4890,7 +4890,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>MOBH UK FAMILY OFFICE LTD</t>
+          <t>HALL LAURIE J TRUSTEE</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4925,7 +4925,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NORTHBRIDGE FAMILY OFFICE LTD</t>
+          <t>HALL LAURIE J TRUSTEE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4936,7 +4936,7 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NOVA FAMILY OFFICE LTD</t>
+          <t>HBBA FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nilsson Family Office Ltd</t>
+          <t>HILL FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4982,7 +4982,7 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nilsson Family Office Ltd</t>
+          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5005,7 +5005,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -5017,7 +5017,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nilsson Family Office Ltd</t>
+          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5028,7 +5028,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Nilsson Family Office Ltd</t>
+          <t>INTREPID FAMILY OFFICE LLC</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5051,7 +5051,7 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nilsson Family Office Ltd</t>
+          <t>ISHER CAPITAL FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5074,7 +5074,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>OLD HOUSE FAMILY OFFICE LIMITED</t>
+          <t>Independent Family Office, LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5109,7 +5109,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>OneAscent Family Office, LLC</t>
+          <t>Kopp Family Office, LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Orion Porfolio Solutions, LLC</t>
+          <t>LELS CLARK FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5155,7 +5155,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Orion Portfolio Solutions, LLC</t>
+          <t>Lido Advisors, LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PANDA FAMILY OFFICE LTD</t>
+          <t>Lido Advisors, LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5189,7 +5189,7 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PANTHEON A FAMILY OFFICE LIMITED</t>
+          <t>MARCUARD FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PATHSTONE FAMILY OFFICE, LLC</t>
+          <t>MOBH UK FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PMG Family Office LLC</t>
+          <t>NORTHBRIDGE FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PROSPERITY FAMILY OFFICE LIMITED</t>
+          <t>NOVA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Pathstone Holdings, LLC</t>
+          <t>Nilsson Family Office Ltd</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5304,7 +5304,7 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pioneer Family Office, LLC</t>
+          <t>Nilsson Family Office Ltd</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5327,7 +5327,7 @@
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>RALPH FAMILY OFFICE LIMITED</t>
+          <t>Nilsson Family Office Ltd</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5350,7 +5350,7 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5362,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SHA FAMILY OFFICE LTD</t>
+          <t>Nilsson Family Office Ltd</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5373,7 +5373,7 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SIGNATURE FAMILY OFFICE LTD</t>
+          <t>Nilsson Family Office Ltd</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5396,7 +5396,7 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SIMON FAMILY OFFICE INSURES LIMITED</t>
+          <t>OLD HOUSE FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>SWAILES COMMERCIAL FAMILY OFFICE LTD</t>
+          <t>OneAscent Family Office, LLC</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SWAILES TRADING GROUP FAMILY OFFICE LTD</t>
+          <t>Orion Porfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Sageworth Trust Co</t>
+          <t>Orion Porfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5488,7 +5488,7 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5500,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Standard Family Office LLC</t>
+          <t>Orion Portfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5523,7 +5523,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Stenger Family Office, LLC</t>
+          <t>Orion Portfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5534,7 +5534,7 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5546,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Stokes Family Office, LLC</t>
+          <t>PANDA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>THE DIGITAL FAMILY OFFICE LIMITED</t>
+          <t>PANTHEON A FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>THE FAMILY OFFICE CHELTENHAM LIMITED</t>
+          <t>PATHSTONE FAMILY OFFICE, LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TIGRIS FAMILY OFFICE LIMITED</t>
+          <t>PMG Family Office LLC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5638,7 +5638,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tarbox Family Office, Inc.</t>
+          <t>PROSPERITY FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Timonier Family Office, LTD.</t>
+          <t>Pathstone Holdings, LLC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TrustBank</t>
+          <t>Pathstone Holdings, LLC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5695,7 +5695,7 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>UNITA FAMILY OFFICE UK LIMITED</t>
+          <t>Pioneer Family Office, LLC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5730,7 +5730,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>UR FAMILY OFFICE MANAGEMENT SERVICES LTD</t>
+          <t>RALPH FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5753,7 +5753,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>VASIL FAMILY OFFICE LLP</t>
+          <t>SHA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>VPR Management LLC</t>
+          <t>SIGNATURE FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5799,7 +5799,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>VSTAR LONDON FAMILY OFFICE LTD</t>
+          <t>SIMON FAMILY OFFICE INSURES LIMITED</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Veritable, L.P.</t>
+          <t>SWAILES COMMERCIAL FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Virtus Family Office LLC</t>
+          <t>SWAILES TRADING GROUP FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WEYBRIDGE FAMILY OFFICE SERVICES LIMITED</t>
+          <t>Sageworth Trust Co</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Wealthgate Family Office, LLC</t>
+          <t>Sageworth Trust Co</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5902,7 +5902,7 @@
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Wilmington Savings Fund Society, FSB</t>
+          <t>Standard Family Office LLC</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5926,6 +5926,512 @@
       <c r="E107" t="inlineStr">
         <is>
           <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Stenger Family Office, LLC</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Stokes Family Office, LLC</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>THE DIGITAL FAMILY OFFICE LIMITED</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>THE FAMILY OFFICE CHELTENHAM LIMITED</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>TIGRIS FAMILY OFFICE LIMITED</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Tarbox Family Office, Inc.</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Timonier Family Office, LTD.</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>TrustBank</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>TrustBank</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>UNITA FAMILY OFFICE UK LIMITED</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>UR FAMILY OFFICE MANAGEMENT SERVICES LTD</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>VASIL FAMILY OFFICE LLP</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>VPR Management LLC</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>VPR Management LLC</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>VSTAR LONDON FAMILY OFFICE LTD</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Veritable, L.P.</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Veritable, L.P.</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Virtus Family Office LLC</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>WEYBRIDGE FAMILY OFFICE SERVICES LIMITED</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Wealthgate Family Office, LLC</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Wilmington Savings Fund Society, FSB</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Wilmington Savings Fund Society, FSB</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>

--- a/data/final/family_office_dataset.xlsx
+++ b/data/final/family_office_dataset.xlsx
@@ -429,14 +429,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
     <col width="33" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="36" customWidth="1" min="5" max="5"/>
+    <col width="39" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -448,11 +448,11 @@
     <col width="32" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
-    <col width="23" customWidth="1" min="17" max="17"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="18" customWidth="1" min="19" max="19"/>
     <col width="60" customWidth="1" min="20" max="20"/>
-    <col width="50" customWidth="1" min="21" max="21"/>
+    <col width="60" customWidth="1" min="21" max="21"/>
     <col width="19" customWidth="1" min="22" max="22"/>
     <col width="60" customWidth="1" min="23" max="23"/>
   </cols>
@@ -664,12 +664,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>13F portfolio approx $0.15B across 60 US-listed positions as of 12-31-2025 (floor on AUM; 13(f) equities only, unit-normalized from filing). Top holdings: ISHARES TR ($0.07B); VANGUARD INTL EQUITY INDEX F ($13.84B); FIDELITY COVINGTON TRUST ($9.25B); VANGUARD INDEX FDS ($8.47B)</t>
+          <t>Firm operates from Austin, TX (9011 Mountain Ridge Drive) with an investment team led by CIO Anthony Lopiccolo (CFA, at Custos since 2018) and founding principal Mitchell Herr; both are ex-J.P. Morgan Private Bank. Recent third-party AUM profiles (2024-2025) place assets in the ~$347-532M range.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>12-31-2025</t>
+          <t>2018 (Lopiccolo joined/founding era); 2024-2025 (AUM profiles)</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -686,12 +686,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEC13F-0001938970</t>
+          <t>SEC13F-0001802084</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Callan Family Office, LLC</t>
+          <t>CVA Family Office, LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -699,45 +699,45 @@
           <t>MFO</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>None (owner-operated MFO; part of the Class VI Partners group co-founded by Chris Younger and David Tolson). Not tied to a single client family.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://callanfamilyoffice.com/</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/callan-family-office</t>
-        </is>
-      </c>
+          <t>https://classvifamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callan Family Office is a Radnor, PA-based multi-family office founded in February 2022 by former Abbot Downing / Wells Fargo ultra-high-net-worth executives, using a brand-licensing partnership with institutional-consulting firm Callan LLC. It serves multiple ultra-wealthy families (minimum ~$50M, average ~$100M) and grew past $5B in assets within two years. It operates on a partnership model providing investment management and integrated family-office services.</t>
+          <t>Denver-based multi-family office and SEC-registered investment adviser, formerly 'CVA Family Office, LLC' and now operating as 'Class VI Family Office, LLC', part of the Class VI Partners group. Advises entrepreneurs, business owners and executives on wealth planning, liquidity-event planning and investment management on a 1:1 client:advisor model.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Institutional-quality, goals-based investment management for UHNW families, leveraging the Callan LLC investment-consulting relationship for manager research/asset allocation; open-architecture, partnership-driven advice.</t>
+          <t>Serving entrepreneurs and business owners around liquidity events; integrated wealth planning + discretionary investment management aligned to each family's goals.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Diversified multi-asset-class portfolios (public and private markets, alternatives) tailored to UHNW families; not sector-specialized.</t>
+          <t>Diversified discretionary wealth/investment management for HNW entrepreneurs; no single-sector focus disclosed.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>~$5B AUM as of March 2024 (reported crossing $5B two years after 2022 founding).</t>
+          <t>~$222.27 million regulatory AUM (across ~43 accounts)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Radnor</t>
+          <t>DENVER</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -747,22 +747,22 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Jack Ginter (John Ginter)</t>
+          <t>Matt Blackburn</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Chief Executive Officer &amp; Founding Partner</t>
+          <t>Managing Partner / Managing Director, Class VI Family Office (co-founder)</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jack-ginter-70276773/</t>
+          <t>https://www.linkedin.com/in/mattblackburnclassvi/</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>jginter@callanfo.com</t>
+          <t>matt@classvipartners.com</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>267-250-2036</t>
+          <t>303-243-5619</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>13F portfolio approx $4.41B across 1131 US-listed positions as of 03-31-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing)</t>
+          <t>Rebranded from 'CVA Family Office' to 'Class VI Family Office'; established as RIA Sept 2016; operates on a 1:1 client:advisor model under Class VI Partners</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>03-31-2026</t>
+          <t>2016-09 (RIA inception); rebrand to Class VI Family Office (ongoing)</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -792,41 +792,65 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Uses the 'family office' label but is structurally an UHNW multi-family-office RIA with a client base, not a single family's office. 'John Ginter' (13F signatory) and 'Jack Ginter' (CEO) are the same person. AUM figure is a March 2024 press number and may be higher now.</t>
+          <t>Legal 13F filer name remains 'CVA Family Office, LLC' but the brand/website is now 'Class VI Family Office' (classvifamilyoffice.com); older cvafamilyoffice.com domain was unreachable during research. Principal email is on the classvipartners.com domain, not a family-office-specific domain. Chris Younger is CEO of the broader Class VI Partners; Matt Blackburn selected as the family-office investment/advisory lead.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEC13F-0001596197</t>
+          <t>SEC13F-0001938970</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Intrepid Family Office Llc</t>
+          <t>Callan Family Office, LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://callanfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/callan-family-office</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Callan Family Office is a Radnor, PA-based multi-family office founded in February 2022 by former Abbot Downing / Wells Fargo ultra-high-net-worth executives, using a brand-licensing partnership with institutional-consulting firm Callan LLC. It serves multiple ultra-wealthy families (minimum ~$50M, average ~$100M) and grew past $5B in assets within two years. It operates on a partnership model providing investment management and integrated family-office services.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Institutional-quality, goals-based investment management for UHNW families, leveraging the Callan LLC investment-consulting relationship for manager research/asset allocation; open-architecture, partnership-driven advice.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Diversified multi-asset-class portfolios (public and private markets, alternatives) tailored to UHNW families; not sector-specialized.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>~$5B AUM as of March 2024 (reported crossing $5B two years after 2022 founding).</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Greenwich</t>
+          <t>Radnor</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -836,56 +860,64 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Matt Dino</t>
+          <t>Jack Ginter (John Ginter)</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+          <t>Chief Executive Officer &amp; Founding Partner</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jack-ginter-70276773/</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>jginter@callanfo.com</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>(203) 862-3372</t>
+          <t>267-250-2036</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>13F portfolio approx $0.12B across 38 US-listed positions as of 03-31-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing). Top holdings: SPDR GOLD TR ($17.21B); ISHARES TR ($13.57B); VANGUARD INDEX FDS ($12.83B); ABRDN PLATINUM ETF TRUST ($7.13B)</t>
+          <t>Reported crossing $5B AUM in March 2024, ~2 years after a Feb 2022 launch; built via a Callan LLC brand-licensing/partnership deal and Abbot Downing/Wells Fargo advisor recruitment; featured in RIABiz and a Diamond Consultants podcast.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>03-31-2026</t>
+          <t>2022-02 (founding); 2024-03 (crossed $5B AUM); 2024-04-09 (RIABiz feature)</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>SFO inferred from unregistered-adviser + 13F + family-office name; the specific family is not yet named (pending research pass).</t>
+          <t>Uses the 'family office' label but is structurally an UHNW multi-family-office RIA with a client base, not a single family's office. 'John Ginter' (13F signatory) and 'Jack Ginter' (CEO) are the same person. AUM figure is a March 2024 press number and may be higher now.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEC13F-0001536411</t>
+          <t>SEC13F-0001596197</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Duquesne Family Office LLC</t>
+          <t>Intrepid Family Office Llc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -893,45 +925,21 @@
           <t>SFO</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Druckenmiller family (Stanley F. Druckenmiller)</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/duquesne-family-office-llc</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Duquesne Family Office is the private investment vehicle of billionaire investor Stanley Druckenmiller, established in 2010 after he returned outside capital and wound down his hedge fund Duquesne Capital Management (named for a park in his native Pittsburgh). It manages the Druckenmiller family's capital across public equities, and reportedly private/venture and credit positions, using a concentrated, macro-driven approach. It has no external clients.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Concentrated, top-down macro investing with high conviction and significant position turnover; opportunistic rotation across sectors and asset classes based on macroeconomic views. Public-equity book is typically 20-40 concentrated positions.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Broad/opportunistic across technology, healthcare/biotech, energy, consumer, financials and industrials; recent 13Fs (2025) show large positions in names like Natera, Insmed, Amazon, Teva and Woodward.</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>13F US-listed equities ~$4.06B as of 2025-09-30 (Q3 2025) and ~$4.49B as of Q4 2025 -- a FLOOR, not total AUM. Total family-office AUM is not publicly disclosed; Druckenmiller's personal net worth is estimated at ~$11B (Bloomberg Billionaires Index, Jan 2025) and he ranks on the Forbes 2026 Billionaires list.</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Greenwich</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -941,12 +949,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Stanley F. Druckenmiller</t>
+          <t>Matt Dino</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Founder, Chairman &amp; CEO (Portfolio Manager)</t>
+          <t>Chief Financial Officer</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -958,12 +966,12 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>212-830-6500</t>
+          <t>(203) 862-3372</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13F portfolio approx $3.38B across 70 US-listed positions as of 03-31-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing). Top holdings: Natera Inc ($0.61B); Ishares Inc ($0.29B); Insmed Inc ($0.19B); Taiwan Semiconductor Manufac ($0.17B)</t>
+          <t>13F portfolio approx $0.12B across 38 US-listed positions as of 03-31-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing). Top holdings: SPDR GOLD TR ($17.21B); ISHARES TR ($13.57B); VANGUARD INDEX FDS ($12.83B); ABRDN PLATINUM ETF TRUST ($7.13B)</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -978,19 +986,19 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Total AUM is not officially disclosed; the 13F equity value is only US-listed long equity positions (a floor). The LinkedIn company page may not be firm-operated. No individual email is published anywhere; none provided. Sue Meng (13F signatory) is General Counsel, not the investment decision-maker.</t>
+          <t>SFO inferred from unregistered-adviser + 13F + family-office name; the specific family is not yet named (pending research pass).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEC13F-0001683689</t>
+          <t>SEC13F-0001536411</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kopp Family Office, LLC</t>
+          <t>Duquesne Family Office LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -998,21 +1006,45 @@
           <t>SFO</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Druckenmiller family (Stanley F. Druckenmiller)</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/duquesne-family-office-llc</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Duquesne Family Office is the private investment vehicle of billionaire investor Stanley Druckenmiller, established in 2010 after he returned outside capital and wound down his hedge fund Duquesne Capital Management (named for a park in his native Pittsburgh). It manages the Druckenmiller family's capital across public equities, and reportedly private/venture and credit positions, using a concentrated, macro-driven approach. It has no external clients.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Concentrated, top-down macro investing with high conviction and significant position turnover; opportunistic rotation across sectors and asset classes based on macroeconomic views. Public-equity book is typically 20-40 concentrated positions.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Broad/opportunistic across technology, healthcare/biotech, energy, consumer, financials and industrials; recent 13Fs (2025) show large positions in names like Natera, Insmed, Amazon, Teva and Woodward.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>13F US-listed equities ~$4.06B as of 2025-09-30 (Q3 2025) and ~$4.49B as of Q4 2025 -- a FLOOR, not total AUM. Total family-office AUM is not publicly disclosed; Druckenmiller's personal net worth is estimated at ~$11B (Bloomberg Billionaires Index, Jan 2025) and he ranks on the Forbes 2026 Billionaires list.</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Minnetonka</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1022,12 +1054,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>John P. Flakne</t>
+          <t>Stanley F. Druckenmiller</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
+          <t>Founder, Chairman &amp; CEO (Portfolio Manager)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1039,17 +1071,17 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>952-841-0450</t>
+          <t>212-830-6500</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>13F portfolio approx $0.16B across 29 US-listed positions as of 06-30-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing)</t>
+          <t>Q3 2025 13F filed (portfolio ~$4.06B, 65 holdings); Q4 2025 13F portfolio rose to ~$4.49B with ~35 significant positions; Q1 2025 13F showed cuts and new tech/energy adds (~$3.06B, 52 holdings).</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>06-30-2026</t>
+          <t>2025-11-14 (Q3 2025 13F filing, as of 2025-09-30); Q4 2025 (as of 2025-12-31); 2025-05-15 (Q1 2025 13F, as of 2025-03-31)</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1059,19 +1091,19 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>SFO inferred from unregistered-adviser + 13F + family-office name; the specific family is not yet named (pending research pass).</t>
+          <t>Total AUM is not officially disclosed; the 13F equity value is only US-listed long equity positions (a floor). The LinkedIn company page may not be firm-operated. No individual email is published anywhere; none provided. Sue Meng (13F signatory) is General Counsel, not the investment decision-maker.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEC13F-0001889527</t>
+          <t>SEC13F-0001683689</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Louis-Dreyfus Family Office LLC</t>
+          <t>Kopp Family Office, LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1079,41 +1111,21 @@
           <t>SFO</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Louis-Dreyfus family -- specifically the American branch of Gerard 'William' Louis-Dreyfus (1932-2016), longtime chairman of Louis Dreyfus Company's US arm and father of actress Julia Louis-Dreyfus (INFERRED from co-location with LDC's Wilton HQ and the family/geography; not definitively documented).</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Louis-Dreyfus Family Office LLC is a small private single-family office in Wilton, CT, associated with the American branch of the Louis-Dreyfus family (the commodities-trading dynasty). It is co-located with Louis Dreyfus Company's US headquarters at 10 Westport Road and manages family capital; its SEC 13F disclosed only about five holdings worth ~$65M. It is NOT the Louis Dreyfus Company commodities business itself.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Not publicly documented. The limited 13F holdings (broad index funds VXUS/VTIAX and ITOT plus a couple of small single-name positions) suggest a conservative, largely passive/index-oriented public-markets allocation typical of a family office holding book, but this is inferred, not stated.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Public 13F book was dominated by broad-market and international index funds (Vanguard Total International, iShares Core S&amp;P Total US Market ETF) plus small individual equity positions (e.g., Celularity, New Relic, Lovesac). Not sector-focused.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>13F US-listed equities ~$64.7M as of 2022-09-30 (Q3 2022, 5 holdings) -- a floor and likely a small slice of total family wealth. Total AUM not disclosed. Business directories estimate ~$390K annual revenue / ~4 employees.</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Wilton</t>
+          <t>Minnetonka</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1123,12 +1135,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>W. Thomas Wingertzahn</t>
+          <t>John P. Flakne</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Chief Financial Officer (13F signatory / operational head)</t>
+          <t>Chief Financial Officer</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1140,17 +1152,17 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>203-762-6134</t>
+          <t>952-841-0450</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>13F portfolio approx $0.07B across 5 US-listed positions as of 09-30-2022 (floor on AUM; 13(f) equities only, unit-normalized from filing). Top holdings: VANGUARD STAR FDS ($0.03B); ISHARES TR ($0.03B); CELULARITY INC ($0.00B); NEW RELIC INC ($0.00B)</t>
+          <t>13F portfolio approx $0.16B across 29 US-listed positions as of 06-30-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>09-30-2022</t>
+          <t>06-30-2026</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1160,19 +1172,19 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>ENTITY-CONFUSION RISK: 'Louis-Dreyfus Family Office LLC' is NOT the Louis Dreyfus Company (LDC) commodities firm, though it shares the Wilton CT 10 Westport Road address. The specific family member/branch is INFERRED (Gerard 'William' Louis-Dreyfus's American branch; heirs include Julia Louis-Dreyfus and half-sisters Phoebe and Emma) and not definitively confirmed by a primary source; family_affiliation should be treated as probable, not certain. The true family investment decision-maker is undetermined; Wingertzahn is the CFO/signatory, reported as principal only for lack of a documented alternative. No website, no LinkedIn, no published email. 13F filings appear to have lapsed after 2022.</t>
+          <t>SFO inferred from unregistered-adviser + 13F + family-office name; the specific family is not yet named (pending research pass).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UKCH-12706913</t>
+          <t>SEC13F-0001889527</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Francis Family Office Limited</t>
+          <t>Louis-Dreyfus Family Office LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1182,68 +1194,76 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Francis family (Ben Francis, founder/CEO of Gymshark)</t>
+          <t>Louis-Dreyfus family -- specifically the American branch of Gerard 'William' Louis-Dreyfus (1932-2016), longtime chairman of Louis Dreyfus Company's US arm and father of actress Julia Louis-Dreyfus (INFERRED from co-location with LDC's Wilton HQ and the family/geography; not definitively documented).</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Personal family-office / holding vehicle of Ben Francis, billionaire founder and majority owner of fitness-apparel brand Gymshark; holds part of his Gymshark shareholding.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Louis-Dreyfus Family Office LLC is a small private single-family office in Wilton, CT, associated with the American branch of the Louis-Dreyfus family (the commodities-trading dynasty). It is co-located with Louis Dreyfus Company's US headquarters at 10 Westport Road and manages family capital; its SEC 13F disclosed only about five holdings worth ~$65M. It is NOT the Louis Dreyfus Company commodities business itself.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Not publicly documented. The limited 13F holdings (broad index funds VXUS/VTIAX and ITOT plus a couple of small single-name positions) suggest a conservative, largely passive/index-oriented public-markets allocation typical of a family office holding book, but this is inferred, not stated.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Holding company (concentrated Gymshark equity stake)</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>Public 13F book was dominated by broad-market and international index funds (Vanguard Total International, iShares Core S&amp;P Total US Market ETF) plus small individual equity positions (e.g., Celularity, New Relic, Lovesac). Not sector-focused.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>13F US-listed equities ~$64.7M as of 2022-09-30 (Q3 2022, 5 holdings) -- a floor and likely a small slice of total family wealth. Total AUM not disclosed. Business directories estimate ~$390K annual revenue / ~4 employees.</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>Wilton</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>West Midlands</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Benjamin David Francis</t>
+          <t>W. Thomas Wingertzahn</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Director &amp; 100% owner; Founder &amp; CEO of Gymshark</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/gymshark/</t>
-        </is>
-      </c>
+          <t>Chief Financial Officer (13F signatory / operational head)</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>203-762-6134</t>
+        </is>
+      </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Renamed Ben Francis Ltd -&gt; Francis Family Office Ltd (2021); Ben Francis moved ~half his Gymshark stake into the vehicle; 2026 reporting he is seeking financing to buy back part of General Atlantic's Gymshark stake</t>
+          <t>No recent public activity found. The most recent SEC 13F on file is Q3 2022; no 2023-2025 13F filings surfaced, which may indicate the equity book fell below the 13F reporting threshold or the office stopped filing.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2021-02-03 (rename); 2026-07 (buyback reporting)</t>
+          <t>2022-11-10 (last 13F filing, holdings as of 2022-09-30)</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1253,19 +1273,19 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>No standalone website/LinkedIn/email for the FO itself — a private holding vehicle, not client-facing. Corporate secretary is a law-firm nominee, not the principal. Investment thesis/sectors not publicly disclosed.</t>
+          <t>ENTITY-CONFUSION RISK: 'Louis-Dreyfus Family Office LLC' is NOT the Louis Dreyfus Company (LDC) commodities firm, though it shares the Wilton CT 10 Westport Road address. The specific family member/branch is INFERRED (Gerard 'William' Louis-Dreyfus's American branch; heirs include Julia Louis-Dreyfus and half-sisters Phoebe and Emma) and not definitively confirmed by a primary source; family_affiliation should be treated as probable, not certain. The true family investment decision-maker is undetermined; Wingertzahn is the CFO/signatory, reported as principal only for lack of a documented alternative. No website, no LinkedIn, no published email. 13F filings appear to have lapsed after 2022.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UKCH-07931194</t>
+          <t>UKCH-12706913</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wimmer Family Office Ltd</t>
+          <t>Francis Family Office Limited</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1275,35 +1295,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Wimmer (Per Wimmer, Danish financier, founder of merchant bank Wimmer Financial)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://wfo.am/</t>
-        </is>
-      </c>
+          <t>Francis family (Ben Francis, founder/CEO of Gymshark)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>London (Mayfair) family office established by Per Wimmer, a Danish financier, entrepreneur and author; associated with his corporate-advisory firm Wimmer Financial.</t>
+          <t>Personal family-office / holding vehicle of Ben Francis, billionaire founder and majority owner of fitness-apparel brand Gymshark; holds part of his Gymshark shareholding.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Natural resources (mining, oil &amp; gas, green energy); real estate; infrastructure; aviation; shipping; space economy</t>
+          <t>Holding company (concentrated Gymshark equity stake)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Mayfair</t>
+          <t>West Midlands</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1313,17 +1329,17 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Per Thanning Wimmer</t>
+          <t>Benjamin David Francis</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO, Wimmer Family Office</t>
+          <t>Director &amp; 100% owner; Founder &amp; CEO of Gymshark</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/perwimmer</t>
+          <t>https://www.linkedin.com/in/gymshark/</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -1332,19 +1348,15 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>+44 207 432 7575</t>
-        </is>
-      </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Per Wimmer resigned as director 2024-09-25; two new directors appointed same day (Aida Feriz, Joppe Sikma); FCA-authorised (FCA #665654)</t>
+          <t>Renamed Ben Francis Ltd -&gt; Francis Family Office Ltd (2021); Ben Francis moved ~half his Gymshark stake into the vehicle; 2026 reporting he is seeking financing to buy back part of General Atlantic's Gymshark stake</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2024-09-25 (director change)</t>
+          <t>2021-02-03 (rename); 2026-07 (buyback reporting)</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1354,81 +1366,77 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Corrected task hint: principal is PER Wimmer, not 'Klaus Wimmer'. Per Wimmer resigned as registered director 2024-09-25 but remains named founder on the site; current directors appear operational/successor. Phone is switchboard. AUM/thesis not disclosed.</t>
+          <t>No standalone website/LinkedIn/email for the FO itself — a private holding vehicle, not client-facing. Corporate secretary is a law-firm nominee, not the principal. Investment thesis/sectors not publicly disclosed.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEC13F-0001039807</t>
+          <t>UKCH-07931194</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Boston Family Office Llc</t>
+          <t>Wimmer Family Office Ltd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MFO</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Wimmer (Per Wimmer, Danish financier, founder of merchant bank Wimmer Financial)</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.bosfam.com/</t>
+          <t>https://wfo.am/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>The Boston Family Office LLC is an independent, employee-owned registered investment adviser founded in 1996 and based in Boston, MA. It provides multi-family-office-style wealth management -- investment management, financial planning, and adviser selection -- to high-net-worth individuals, families and charitable organizations across roughly 789 accounts and ~$1.7-2.0B in assets. It is a multi-family/RIA firm rather than a single-family office.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Client-tailored, diversified portfolio management for wealth preservation and growth across HNW households and institutions; discretionary management (769 of 789 accounts discretionary). Specific house investment philosophy not detailed publicly.</t>
-        </is>
-      </c>
+          <t>London (Mayfair) family office established by Per Wimmer, a Danish financier, entrepreneur and author; associated with his corporate-advisory firm Wimmer Financial.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Diversified multi-asset wealth management (public equities, fixed income, funds); not sector-specialized. A partner sits on the board of fixed-income manager Breckinridge Capital Advisors.</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>~$1.7B AUM across 789 accounts (Form ADV/adviserinfo, 2024-2025); third-party profiles cite ~$1.9-2.02B. As of the most recent Form ADV (2024 filing cycle).</t>
-        </is>
-      </c>
+          <t>Natural resources (mining, oil &amp; gas, green energy); real estate; infrastructure; aviation; shipping; space economy</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>London</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>Mayfair</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>George P. Beal</t>
+          <t>Per Thanning Wimmer</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; Managing Partner (Portfolio Manager)</t>
+          <t>Founder &amp; CEO, Wimmer Family Office</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/george-beal-a6107a16/</t>
+          <t>https://uk.linkedin.com/in/perwimmer</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1439,17 +1447,17 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>617-624-0800</t>
+          <t>+44 207 432 7575</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>13F portfolio approx $1.50B across 311 US-listed positions as of 03-31-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing)</t>
+          <t>Per Wimmer resigned as director 2024-09-25; two new directors appointed same day (Aida Feriz, Joppe Sikma); FCA-authorised (FCA #665654)</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>03-31-2026</t>
+          <t>2024-09-25 (director change)</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1459,19 +1467,19 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Despite the 'family office' name, this is functionally a multi-family-office RIA / private wealth manager serving hundreds of client accounts, not a single family's office. Investment authority is distributed among ~8 managing directors, so Beal is one of several senior decision-makers (though the 13F signatory and co-founder). No official company LinkedIn URL confirmed. No individual email is published (the ZoomInfo masked pattern was deliberately not used).</t>
+          <t>Corrected task hint: principal is PER Wimmer, not 'Klaus Wimmer'. Per Wimmer resigned as registered director 2024-09-25 but remains named founder on the site; current directors appear operational/successor. Phone is switchboard. AUM/thesis not disclosed.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEC13F-0002017744</t>
+          <t>SEC13F-0001599603</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1479,40 +1487,44 @@
           <t>MFO</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>None as a single client family; founder-owned firm (Laura Tarbox founder, CEO and principal owner). Namesake is the founder, not a served family.</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://arrowrootfamilyoffice.com/</t>
+          <t>https://tarbox.com/</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/arrowroot-family-office</t>
+          <t>https://www.linkedin.com/company/tarboxfamilyoffice</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC is a Marina del Rey, CA-based registered investment adviser and multi-family office, originally founded in 2013 as Vitreous Partners and rebranded in 2017. It provides multidisciplinary wealth management -- investment management, retirement, tax and estate planning -- to high-net-worth individuals, entrepreneurs, families and small institutions, with offices in Southern and Northern California, Virginia and Michigan. It is a multi-client RIA, not a single family's office.</t>
+          <t>Newport Beach, CA-based multi-family office and SEC-registered investment adviser founded in 1985 by Laura Tarbox, CFP. Fee-only firm serving 100+ HNW/UHNW client families (also charities, businesses, trusts/estates) with comprehensive financial planning, tax preparation and individualized investment management; $5M minimum, over $1B AUM. Also has a Scottsdale, AZ office.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Team-based, fiduciary, goals-driven wealth management emphasizing comprehensive planning and diversified investment management for affluent households and business owners; open-architecture advice.</t>
+          <t>Team-based, individualized asset allocation and investment management integrated with comprehensive financial and estate planning; fee-only fiduciary model.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Diversified multi-asset wealth management (public equities, funds/ETFs, fixed income, alternatives); not sector-specialized.</t>
+          <t>Diversified asset-allocation / individualized investment management; no single-sector focus.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>~$431M AUM as of Q2 2025 (third-party profiles); regulatory AUM per the 2025 Form ADV on the firm's site. A floor for total client assets under advisement.</t>
+          <t>Over $1 billion (100+ client families)</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Marina Del Rey</t>
+          <t>NEWPORT BEACH</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1527,38 +1539,38 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Rob (Roberto Francisco) Santos</t>
+          <t>Laura Tarbox</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Chief Executive Officer &amp; Principal Owner</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/rob-santos-afo/</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+          <t>Founder, CEO &amp; principal owner (CFP)</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>laura@tarbox.com</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>310.341.4774</t>
+          <t>(949) 721-2330</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>13F portfolio approx $0.30B across 156 US-listed positions as of 03-31-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing). Top holdings: ISHARES TR ($0.06B); VANGUARD SCOTTSDALE FDS ($47.98B); VANGUARD INDEX FDS ($16.14B); SCHWAB STRATEGIC TR ($14.02B)</t>
+          <t>Founded 1985; CFP since 1984; 100+ client families and &gt;$1B AUM; $5M account minimum; second office in Scottsdale, AZ; Laura Tarbox a frequent WSJ/NYT/LA Times media source</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>03-31-2026</t>
+          <t>1985 (founded); 1984 (Laura Tarbox CFP)</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1568,19 +1580,19 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Uses the 'family office' label but is a multi-client wealth-management RIA, not a single family's office. Possible name confusion with 'Arrowroot Capital Management' (a separate B2B enterprise-software private-equity firm) -- they are distinct; relationship not established here. No individual email published; RocketReach/broker data deliberately not used. Firm's most recent 13F filer registration is recent (CIK 0002017744).</t>
+          <t>Personal LinkedIn /in profile not located (only firm company page). Email captured from Laura Tarbox's public presentation PDF (matches firm domain) rather than the current bio page; treat as published-but-unverified.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UKCH-09580739</t>
+          <t>SEC13F-0001731123</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Blu Family Office Limited</t>
+          <t>Biltmore Family Office, LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1590,67 +1602,67 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Originally Armbruester family (founder's wealth); now MFO serving multiple client families</t>
+          <t>Founder Chris Cecil is a great-grandson of George Vanderbilt (builder of the Biltmore Estate) and son of Asheville developer George Cecil; 'Biltmore' name derives from that Vanderbilt/Cecil family heritage. The firm serves many outside client families (MFO), not the Vanderbilt/Cecil family exclusively.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.blu-fo.com</t>
+          <t>https://www.biltmorefamilyoffice.com/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/company/blu-family-office</t>
+          <t>https://www.linkedin.com/company/biltmore-family-office-llc</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>FCA-regulated multi-family office (Ltd inc. 2015; operations from 2010) in Richmond upon Thames, founded by Christian Armbruester post Credit Suisse. Offers hedge funds, crypto and alternatives; discretionary arm Blu Investment Management.</t>
+          <t>Charlotte, NC-based multi-family office and SEC-registered investment adviser founded in 2008 by Chris Cecil. A collaborative/independent RIA to investment-oriented multi-generational families and institutions, providing investment management, asset allocation, investment-policy design, multi-generational and succession planning. ~$3.2-3.5B AUM.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Discretionary management not relying on forecasting; 'true diversification' and systematic rebalancing; passive in calm markets, opportunistic in adverse ones.</t>
+          <t>Collaborative, investment-policy-driven management for multi-generational HNW/UHNW families and institutions.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hedge funds; crypto assets; alternatives; diversified multi-asset</t>
+          <t>Diversified public-equity/ETF portfolios; disclosed top 13F holdings include AAPL, IAU (gold), AVDX, ROBO, VV. No single-sector concentration.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>£0.5bn-£1bn (third-party estimated range)</t>
+          <t>~$3.2-3.5 billion (reported ~$3.47B regulatory AUM across ~951 accounts)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Greater London</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Christian Armbruester</t>
+          <t>Chris Cecil</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Founder &amp; Principal (largest shareholder ~40.8%)</t>
+          <t>Founder, President &amp; CEO</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/christianarmbruesterblufamilyoffice</t>
+          <t>https://www.linkedin.com/in/chris-cecil-9701b818/</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
@@ -1659,15 +1671,19 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>+1 704-248-5230</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Founded 2010; Ltd inc. 2015; new director Vishesh Dawar appointed Dec 2025; investment arm rebranded Blu Investment Management; Marie Redron now CEO</t>
+          <t>Founded 2008 by Chris Cecil (LLC organized 2013); ~$3.2-3.5B AUM across ~951 accounts, avg client ~$38M; Cecil chairs TIGER 21 Charlotte / Family Office groups</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2015-05-08; 2025-12-08</t>
+          <t>2008 (founding); 2013 (LLC organized)</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1677,81 +1693,81 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Client-facing operations now run under 'Blu Investment Management' (blu-im.com), same address. Armbruester is founder/principal but not current CEO (Marie Redron is). AUM range is a third-party estimate. Only published contacts are a switchboard + generic mailbox.</t>
+          <t>Chris Cecil chosen as principal (founder/CEO); Rael Gorelick is Partner &amp; Head of Investments and would be the CIO-level investment lead. No published individual email located. AUM varies by source ($3.2B-$3.5B).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UKCH-12233405</t>
+          <t>SEC13F-0001039807</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Schwarz Family Office Ltd</t>
+          <t>Boston Family Office Llc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Undetermined</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Named after principal Andreas Schwarz (German); no wider family group evidenced beyond the surname</t>
-        </is>
-      </c>
+          <t>MFO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://schwarzfamilyoffice.com/</t>
+          <t>https://www.bosfam.com/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>London-based boutique investment/advisory firm branded as a family office, established 2019, led by Andreas Schwarz; provides capital raising, debt financing, wealth management and IR services.</t>
+          <t>The Boston Family Office LLC is an independent, employee-owned registered investment adviser founded in 1996 and based in Boston, MA. It provides multi-family-office-style wealth management -- investment management, financial planning, and adviser selection -- to high-net-worth individuals, families and charitable organizations across roughly 789 accounts and ~$1.7-2.0B in assets. It is a multi-family/RIA firm rather than a single-family office.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>'Be not afraid of growing slowly, be afraid only of standing still' — sustainable growth via established relationships and exclusive investor access. https://schwarzfamilyoffice.com/</t>
+          <t>Client-tailored, diversified portfolio management for wealth preservation and growth across HNW households and institutions; discretionary management (769 of 789 accounts discretionary). Specific house investment philosophy not detailed publicly.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Private equity; fintech; wealth management; venture capital; private debt; IPOs</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
+          <t>Diversified multi-asset wealth management (public equities, fixed income, funds); not sector-specialized. A partner sits on the board of fixed-income manager Breckinridge Capital Advisors.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>~$1.7B AUM across 789 accounts (Form ADV/adviserinfo, 2024-2025); third-party profiles cite ~$1.9-2.02B. As of the most recent Form ADV (2024 filing cycle).</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Maida Vale</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Andreas Schwarz</t>
+          <t>George P. Beal</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Founder / Director</t>
+          <t>Co-Founder &amp; Managing Partner (Portfolio Manager)</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
+          <t>https://www.linkedin.com/in/george-beal-a6107a16/</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
@@ -1760,15 +1776,19 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>617-624-0800</t>
+        </is>
+      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Listed in Family Capital 'FamCap 50' (2024); second shareholder Syed Furqan Ahmed (490 shares)</t>
+          <t>Filed Form ADV Part 2A/2B brochures in the 2024 filing cycle (Feb 2024); a partner (Beal) serves on the board of Breckinridge Capital Advisors. Firm moved offices to 20 Custom House St.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2024-02 (FamCap 50)</t>
+          <t>2024-02-01 (ADV Part 2B brochure)</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1778,297 +1798,413 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Presents as a family office but functions largely as a boutique capital-raising/advisory consultancy with two shareholders — fo_type left Undetermined. A Family Capital story linking Schwarz to a 'famous UK brand' is paywalled and the brand is NOT confirmed; not asserted. AUM undisclosed.</t>
+          <t>Despite the 'family office' name, this is functionally a multi-family-office RIA / private wealth manager serving hundreds of client accounts, not a single family's office. Investment authority is distributed among ~8 managing directors, so Beal is one of several senior decision-makers (though the 13F signatory and co-founder). No official company LinkedIn URL confirmed. No individual email is published (the ZoomInfo masked pattern was deliberately not used).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UKCH-14344019</t>
+          <t>SEC13F-0002017744</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hazell Family Office Ltd</t>
+          <t>Arrowroot Family Office, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SFO</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Hazell family of South Wales (haulage/waste/environmental-services wealth)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+          <t>MFO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://arrowrootfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/arrowroot-family-office</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Active company (inc. 2022-09-08), SIC 70221 financial management; board is five members of the Hazell family. Structure strongly indicates a single-family office. No website/press footprint.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Arrowroot Family Office, LLC is a Marina del Rey, CA-based registered investment adviser and multi-family office, originally founded in 2013 as Vitreous Partners and rebranded in 2017. It provides multidisciplinary wealth management -- investment management, retirement, tax and estate planning -- to high-net-worth individuals, entrepreneurs, families and small institutions, with offices in Southern and Northern California, Virginia and Michigan. It is a multi-client RIA, not a single family's office.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Team-based, fiduciary, goals-driven wealth management emphasizing comprehensive planning and diversified investment management for affluent households and business owners; open-architecture advice.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>70221 - Financial management</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+          <t>Diversified multi-asset wealth management (public equities, funds/ETFs, fixed income, alternatives); not sector-specialized.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>~$431M AUM as of Q2 2025 (third-party profiles); regulatory AUM per the 2025 Form ADV on the firm's site. A floor for total client assets under advisement.</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Usk</t>
+          <t>Marina Del Rey</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Monmouthshire, Wales</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Mark David William Hazell</t>
+          <t>Rob (Roberto Francisco) Santos</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Director (family principal)</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
+          <t>Chief Executive Officer &amp; Principal Owner</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rob-santos-afo/</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>310.341.4774</t>
+        </is>
+      </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Incorporated Sept 2022; five family directors appointed same day; principal is MD of family haulage/environmental companies</t>
+          <t>Announced expansion of its private-wealth practice into Michigan via addition of The Athena Financial Group (offices now include Marina del Rey CA, Rochester Hills MI, Charlottesville VA, El Dorado Hills CA); filed updated Form ADV Part 2A/2B in April 2025.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2022-09-05 (Michigan/Athena expansion press release); 2025-04 (Form ADV update)</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>SFO status inferred from shared surname + single family-farm address + Mark Hazell's operating-company directorships; no website/press confirms active investment operations. 'Mark = principal' is inference; control may be shared across the family.</t>
+          <t>Uses the 'family office' label but is a multi-client wealth-management RIA, not a single family's office. Possible name confusion with 'Arrowroot Capital Management' (a separate B2B enterprise-software private-equity firm) -- they are distinct; relationship not established here. No individual email published; RocketReach/broker data deliberately not used. Firm's most recent 13F filer registration is recent (CIK 0002017744).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UKCH-14442767</t>
+          <t>SEC13F-0001950506</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wedgwood Family Office Limited</t>
+          <t>Fortitude Family Office, LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Wedgwood (Paul Wedgwood family)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
+          <t>None (owner-operated MFO founded and led by Matt Walker). Not tied to a single client family.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://fortitudefo.com/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fortitude-family-office</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>UK private company (inc. 2022-10-25) under fund-management SIC, registered at a residential address in Keston. Appears to be the personal single-family investment vehicle of Paul Wedgwood.</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Scottsdale, AZ-based multi-family office and SEC-registered investment adviser founded and led by Matt Walker (CPA, CGMA). Provides coordinated investment/wealth management, portfolio strategy, tax planning and compliance, private deal structuring, family governance, municipal-bond and ranch/agriculture services to HNW/UHNW families, founders and executives. ~$1B AUM (~$2B AUA claimed).</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Fully-integrated 'coordinated services' model for multigenerational families and founders navigating transitions/liquidity events, blending investment strategy with tax and business operations.</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>66300 - Fund management activities</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
+          <t>Wealth management &amp; portfolio strategy, municipal-bond portfolio management, private deal structuring/private lending; also ranch &amp; agriculture services. Diversified, no single-sector public-equity focus.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>~$1 billion regulatory AUM (~$2 billion assets under advisement per firm PR)</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Keston</t>
+          <t>SCOTTSDALE</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Greater London (Bromley)</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Paul Wedgwood</t>
+          <t>Matt Walker</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
+          <t>Founder &amp; Chief Executive Officer (CPA, CGMA)</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/matt-walkercpa-cgma/</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>(602) 834-0089</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Co-director Christopher James Sharp resigned 2024-04-16; new secretary appointed 2026-01-06; accounts currently overdue</t>
+          <t>~$1B RAUM / ~$2B AUA; Matt Walker named BIG 'Executive of the Year' 2024 and InvestmentNews Excellence Awardee 2024; won 2024 WealthManagement.com award for a private-lending initiative; ~28 employees</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2024-04-16; 2026-01-06</t>
+          <t>2024 (executive/industry awards)</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Link between director 'Paul Wedgwood, b.1970' and the Splash Damage/Supernova entrepreneur is a strong inference (name + DOB + separate Wedgwood FIC directorship), NOT hard-confirmed. Zero public FO footprint (no website/LinkedIn/press/AUM); accounts overdue. Residential registered address.</t>
+          <t>Firm advertises ~$2B 'assets under advisement' vs ~$1B regulatory AUM (FINTRX) — the larger figure includes non-discretionary/advised assets. Address suite number varies across pages (151 vs 100). No published individual email located.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UKCH-10876208</t>
+          <t>SEC13F-0001802278</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sha Family Office Ltd</t>
+          <t>Stokes Family Office, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sha family (controlling PSCs: Mr Sharnpreet Singh Buttar)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t>Stokes family (firm founded/owned by the Stokes family; David Stokes founder, sons Greg and Doug Stokes now managing partners). The 'family' is the owner-operators, not a single client family.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://stokesfamilyoffice.com/</t>
+        </is>
+      </c>
       <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>New Orleans-based multi-family office and SEC-registered investment adviser, 100% owned by the Stokes family and operating in the area for 35+ years. Provides wealth management, investment advisory, tax and estate planning, and family-office services to high-net-worth individuals, families and institutions. Opened a Dallas, TX office in 2025.</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>64205 - Activities of financial services holding companies; 64209 - Activities of other holding companies not elsewhere classified</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
+          <t>Discretionary client portfolio management primarily allocating among mutual funds, ETFs and ETNs; no single-sector focus disclosed.</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>~$3.35 billion (as of 2025-12-31); reported ~$3.4B by FINTRX</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>SIC codes - 64205</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>NEW ORLEANS</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>LA</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Douglas Stokes</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Managing Partner (CFA); leads investment research and the investment committee</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/doug-stokes-03716932/</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>(504) 399-4100</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Exceeded $3B AUM; named to Forbes/SHOOK 'Top RIA' list; opened Dallas, TX office (Resolute Tower at Old Parkland)</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2023 (Forbes/SHOOK Top RIA PR); 2025-2026 (Dallas office opening); AUM ~$3.35B as of 2025-12-31</t>
+        </is>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>UK filing SIC: fo-relevant-sic. Active officers: BUTTAR, Sharnpreet Singh () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
+          <t>'Family owned' refers to the Stokes family owning the firm, not to serving a single client family; it is a multi-client advisory MFO. Doug and Greg Stokes are co-managing partners/co-owners; Doug (CFA) chosen as principal on investment-lead basis. No individual email published. Founded/started SEC registration in 2019 though the family practice dates to the 1980s.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UKCH-15240886</t>
+          <t>SEC13F-0002056106</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Freedman Family Office</t>
+          <t>Stenger Family Office, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Freedman family (controlling PSCs: Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+          <t>Stenger family (firm founded/led by Nick Stenger; the family has advised clients since 1981). The 'family' is the owner-operator, not a single client family.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://www.stengerfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/stenger-family-office</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Naperville, IL-based multi-family office / independent fiduciary RIA led by founder-CEO Nick Stenger, offering financial planning, investment management, and (via related companies) tax preparation, estate strategies and insurance. Also has a Spring, TX office. ~$731M AUM; named a Forbes Best-in-State Wealth Advisor 2026.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Goals-based planning: assesses cash needs and upcoming goals, then builds customized portfolios.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>64301 - Activities of investment trusts</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
+          <t>Core individual-stock portfolios and ETF-based asset-allocation portfolios; no single-sector focus.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>~$731 million (as of 2026-06-30)</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+          <t>NAPERVILLE</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Nicholas David Stenger</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Founder &amp; Chief Executive Officer</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -2076,80 +2212,723 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>630-912-8295</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>$731M AUM (2026-06-30); Forbes Best-in-State Wealth Advisor 2026; hosts 'The Nick Stenger Show' podcast; opened Spring, TX office</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2026-06-30 (AUM date); 2026 (Forbes Best-in-State)</t>
+        </is>
+      </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>UK filing SIC: fo-relevant-sic. Active officers: FREEDMAN, Elaine Wilson (), FREEDMAN, Laura-Leigh (), ZIMMERMAN, Samantha Jade () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
+          <t>Serves 1,200+ families 'of all net worth sizes' — a broad wealth-management RIA using family-office branding rather than a classic UHNW MFO; hence proof strength 'corroborated'. Personal LinkedIn /in profile not located (only company page and a Calendly slug for 'nicholasstenger'). No published individual email or direct phone line found.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UKCH-11031775</t>
+          <t>SEC13F-0002105684</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ralph Family Office Limited</t>
+          <t>Cambient Family Office, Llc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Ralph family (controlling PSCs: Melanie Lynette Ralph; Mr Jan De Ridder Ralph)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+          <t>None (owner-operated MFO). Direct owners/executives per Form ADV Schedule A: Andrew Harold Fabiano, Joshua Kirk Gibbs, Daniel Baird Rausch; indirect owner 'RIMAR Development' (since 01/2026). Firm previously named 'STILLWATER, LLC'.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://www.cambient.com/</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cambient-family-office</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Ada, Michigan-based multi-family office and SEC-registered investment adviser (formerly 'Stillwater, LLC'), serving affluent families, private foundations and entrepreneurs with integrated wealth planning, tax-aware discretionary investment management, estate/trust planning and family-office administration. ~$858M AUM.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Goals-based, tax-aware investment management with a preference for equity exposure and outside-manager selection/oversight.</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>64301 - Activities of investment trusts; 68209 - Other letting and operating of own or leased real estate</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>Favors exchange-traded equity exposure; discretionary portfolio management plus manager selection. No single-sector focus.</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>$857,939,726 regulatory AUM (260 accounts; $781.2M discretionary)</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>SIC codes - 64301</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+          <t>ADA</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+          <t>United States of America</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Andrew Harold Fabiano</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Portfolio Manager (CFA); direct owner / principal</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andrew-fabiano-2b4869ab</t>
+        </is>
+      </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>616-330-2270</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Firm formerly named 'STILLWATER, LLC'; SEC registration effective 2025-04-02; TX notice filing 2025-08; FL notice filing 2026-07; 'RIMAR Development' became indirect owner 01/2026; PM Stephen Wilbur (CFP) departed May 2025; latest 13F reported $716.4M (261 positions) signed by Josh Gibbs</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>2025-04-02 (SEC reg); 2025-05 (Wilbur departure); 2025-08 (TX notice); 2026-01 (RIMAR indirect owner); 2026-04-21 &amp; 2026-02-20 (13F-HR filings); 2026-07-16 (ADV amendment)</t>
+        </is>
+      </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>No single named CEO/CIO on the public site; ownership is a three-person partnership (Fabiano, Rausch, Gibbs) plus indirect owner RIMAR Development. Fabiano selected as principal on investment-lead + direct-owner basis; Rausch is a co-equal PM. 13F signatory (Josh Gibbs, Trust Advisor/CCO) differs from investment lead. Predecessor name 'Stillwater, LLC' explains 'established 2025' references despite larger AUM history.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>UKCH-09580739</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Blu Family Office Limited</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>MFO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Originally Armbruester family (founder's wealth); now MFO serving multiple client families</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://www.blu-fo.com</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/blu-family-office</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>FCA-regulated multi-family office (Ltd inc. 2015; operations from 2010) in Richmond upon Thames, founded by Christian Armbruester post Credit Suisse. Offers hedge funds, crypto and alternatives; discretionary arm Blu Investment Management.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Discretionary management not relying on forecasting; 'true diversification' and systematic rebalancing; passive in calm markets, opportunistic in adverse ones.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Hedge funds; crypto assets; alternatives; diversified multi-asset</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>£0.5bn-£1bn (third-party estimated range)</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Richmond</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Greater London</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Christian Armbruester</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Founder &amp; Principal (largest shareholder ~40.8%)</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/christianarmbruesterblufamilyoffice</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Founded 2010; Ltd inc. 2015; new director Vishesh Dawar appointed Dec 2025; investment arm rebranded Blu Investment Management; Marie Redron now CEO</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>2015-05-08; 2025-12-08</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Client-facing operations now run under 'Blu Investment Management' (blu-im.com), same address. Armbruester is founder/principal but not current CEO (Marie Redron is). AUM range is a third-party estimate. Only published contacts are a switchboard + generic mailbox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>UKCH-12233405</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Schwarz Family Office Ltd</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Undetermined</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Named after principal Andreas Schwarz (German); no wider family group evidenced beyond the surname</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://schwarzfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>London-based boutique investment/advisory firm branded as a family office, established 2019, led by Andreas Schwarz; provides capital raising, debt financing, wealth management and IR services.</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>'Be not afraid of growing slowly, be afraid only of standing still' — sustainable growth via established relationships and exclusive investor access. https://schwarzfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Private equity; fintech; wealth management; venture capital; private debt; IPOs</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Maida Vale</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Andreas Schwarz</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Founder / Director</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Listed in Family Capital 'FamCap 50' (2024); second shareholder Syed Furqan Ahmed (490 shares)</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>2024-02 (FamCap 50)</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Presents as a family office but functions largely as a boutique capital-raising/advisory consultancy with two shareholders — fo_type left Undetermined. A Family Capital story linking Schwarz to a 'famous UK brand' is paywalled and the brand is NOT confirmed; not asserted. AUM undisclosed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>UKCH-14344019</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hazell Family Office Ltd</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Hazell family of South Wales (haulage/waste/environmental-services wealth)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Active company (inc. 2022-09-08), SIC 70221 financial management; board is five members of the Hazell family. Structure strongly indicates a single-family office. No website/press footprint.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>70221 - Financial management</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Usk</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Monmouthshire, Wales</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Mark David William Hazell</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Director (family principal)</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Incorporated Sept 2022; five family directors appointed same day; principal is MD of family haulage/environmental companies</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>2022-09-08</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>SFO status inferred from shared surname + single family-farm address + Mark Hazell's operating-company directorships; no website/press confirms active investment operations. 'Mark = principal' is inference; control may be shared across the family.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>UKCH-14442767</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Wedgwood Family Office Limited</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Wedgwood (Paul Wedgwood family)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>UK private company (inc. 2022-10-25) under fund-management SIC, registered at a residential address in Keston. Appears to be the personal single-family investment vehicle of Paul Wedgwood.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>66300 - Fund management activities</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Keston</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Greater London (Bromley)</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Paul Wedgwood</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Co-director Christopher James Sharp resigned 2024-04-16; new secretary appointed 2026-01-06; accounts currently overdue</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>2024-04-16; 2026-01-06</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Link between director 'Paul Wedgwood, b.1970' and the Splash Damage/Supernova entrepreneur is a strong inference (name + DOB + separate Wedgwood FIC directorship), NOT hard-confirmed. Zero public FO footprint (no website/LinkedIn/press/AUM); accounts overdue. Residential registered address.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>UKCH-10876208</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sha Family Office Ltd</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Sha family (controlling PSCs: Mr Sharnpreet Singh Buttar)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>64205 - Activities of financial services holding companies; 64209 - Activities of other holding companies not elsewhere classified</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>SIC codes - 64205</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>UK filing SIC: fo-relevant-sic. Active officers: BUTTAR, Sharnpreet Singh () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>UKCH-15240886</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Freedman Family Office</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Freedman family (controlling PSCs: Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>64301 - Activities of investment trusts</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>UK filing SIC: fo-relevant-sic. Active officers: FREEDMAN, Elaine Wilson (), FREEDMAN, Laura-Leigh (), ZIMMERMAN, Samantha Jade () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>UKCH-11031775</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ralph Family Office Limited</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ralph family (controlling PSCs: Melanie Lynette Ralph; Mr Jan De Ridder Ralph)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>64301 - Activities of investment trusts; 68209 - Other letting and operating of own or leased real estate</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>SIC codes - 64301</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
         <is>
           <t>UK filing SIC: fo-relevant-sic. Active officers: RALPH, Jan De Ridder (), RALPH, Melanie Lynette (), BETHELL, Karen (), BETHELL, Stuart (), YOULL, Gavin William () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
         </is>
@@ -2166,7 +2945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -2180,7 +2959,7 @@
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="27" customWidth="1" min="11" max="11"/>
-    <col width="50" customWidth="1" min="12" max="12"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
     <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
@@ -2354,12 +3133,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEC13F-0001938970</t>
+          <t>SEC13F-0001802084</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Callan Family Office, LLC</t>
+          <t>CVA Family Office, LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2369,22 +3148,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001938970); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001802084); discovered via fts</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001938970&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001802084&amp;type=13F</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>A registered investment adviser and multi-family office that markets to and serves multiple ultra-high-net-worth families; accepts clients with $50M+ to invest (average client ~$100M) and reported &gt;$5B AUM by early 2024. Source: https://riabiz.com/a/2024/4/9/an-abbot-downing-breakaway-but-not-exactly-callan-family-office-hits-5-billion-of-aum-after-just-two-years-using-a-creative-callan-brand-deal-and-a-partnership-model</t>
+          <t>Boutique multi-family wealth-management firm serving multiple high-net-worth business owners/entrepreneurs; ~43 client accounts / ~24 client relationships, ~$222M regulatory AUM. Sources: https://wallmine.com/adviser/235356/cva-family-office-llc ; https://classvifamilyoffice.com/about/</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Self-describes as a family office; RIABiz and Forbes cover it as an MFO; files 13F under CIK 0001938970; published team/services pages. Source: https://callanfamilyoffice.com/team/ and https://www.forbes.com/companies/callan-family-office/</t>
+          <t>SEC-registered investment adviser (13F filer) established September 2016 as an RIA; branded and operated as a family office (now 'Class VI Family Office'). Sources: https://www.classvipartners.com/our-team/matt-blackburn/ ; https://classvifamilyoffice.com/about/</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2394,12 +3173,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://riabiz.com/a/2024/4/9/an-abbot-downing-breakaway-but-not-exactly-callan-family-office-hits-5-billion-of-aum-after-just-two-years-using-a-creative-callan-brand-deal-and-a-partnership-model (March 2024)</t>
+          <t>Adviser/ADV aggregators. https://wallmine.com/adviser/235356/cva-family-office-llc</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Ginter is CEO and Founding Partner, leading firm strategy and business development; he is the current top principal and matches the 13F signatory 'John Ginter' (Jack = John). Verified on the firm's own team page. Source: https://callanfamilyoffice.com/team/jack-ginter/</t>
+          <t>Co-founder of the family office (est. Sept 2016 as CVA Family Office) who leads the wealth team and 'customiz[es] planning and investment management advice for Class VI clients' — the lead investment/advisory decision-maker. Co-founders Chris Younger (CEO, Class VI Partners) and David Tolson also sit above the group. https://www.classvipartners.com/our-team/matt-blackburn/ ; https://classvifamilyoffice.com/about/</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -2409,22 +3188,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://callanfamilyoffice.com/team/jack-ginter/</t>
+          <t>https://classvifamilyoffice.com/about/</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>The firm's own team/bio page for Jack Ginter publishes his individual professional email as jginter@callanfo.com (displayed on his profile page alongside his title 'Chief Executive Officer, Founding Partner'). Note the mail domain callanfo.com differs from the website domain.</t>
+          <t>The firm's own About/team page publishes individual emails including 'Matt@classvipartners.com' (and 'dalyce@classvipartners.com') alongside the general familyoffice@classvipartners.com. Published individual address; not independently provider-verified.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1938970/000193897026000003/primary_doc.xml</t>
+          <t>https://cvafamilyoffice.com/ (main office line, 101 University Blvd, Denver; firm switchboard, not a personal line)</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>https://riabiz.com/a/2024/4/9/an-abbot-downing-breakaway-but-not-exactly-callan-family-office-hits-5-billion-of-aum-after-just-two-years-using-a-creative-callan-brand-deal-and-a-partnership-model ; https://www.diamond-consultants.com/building-a-business-with-intention-the-5b-callan-family-office-recipe-for-success/</t>
+          <t>https://www.classvipartners.com/our-team/matt-blackburn/ ; https://classvifamilyoffice.com/about/ ; https://www.getwarmer.com/firms/class-vi-family-office-llc</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -2436,12 +3215,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEC13F-0001596197</t>
+          <t>SEC13F-0001938970</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INTREPID FAMILY OFFICE LLC</t>
+          <t>Callan Family Office, LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2451,63 +3230,79 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001596197); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001938970); discovered via fts</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001596197&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001938970&amp;type=13F</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No SEC investment-adviser registration found in IAPD (searched 'INTREPID FAMILY OFFICE LLC'); files SEC Form 13F-HR (CIK 0001596197) reporting $123.64B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
+          <t>A registered investment adviser and multi-family office that markets to and serves multiple ultra-high-net-worth families; accepts clients with $50M+ to invest (average client ~$100M) and reported &gt;$5B AUM by early 2024. Source: https://riabiz.com/a/2024/4/9/an-abbot-downing-breakaway-but-not-exactly-callan-family-office-hits-5-billion-of-aum-after-just-two-years-using-a-creative-callan-brand-deal-and-a-partnership-model</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No SEC investment-adviser registration found in IAPD (searched 'INTREPID FAMILY OFFICE LLC'); files SEC Form 13F-HR (CIK 0001596197) reporting $123.64B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
+          <t>Self-describes as a family office; RIABiz and Forbes cover it as an MFO; files 13F under CIK 0001938970; published team/services pages. Source: https://callanfamilyoffice.com/team/ and https://www.forbes.com/companies/callan-family-office/</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://riabiz.com/a/2024/4/9/an-abbot-downing-breakaway-but-not-exactly-callan-family-office-hits-5-billion-of-aum-after-just-two-years-using-a-creative-callan-brand-deal-and-a-partnership-model (March 2024)</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Signed the firm's Form 13F-HR (03-31-2026) as Chief Financial Officer — verified associated person; investment-decision-maker status to be confirmed separately.</t>
+          <t>Ginter is CEO and Founding Partner, leading firm strategy and business development; he is the current top principal and matches the 13F signatory 'John Ginter' (Jack = John). Verified on the firm's own team page. Source: https://callanfamilyoffice.com/team/jack-ginter/</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://callanfamilyoffice.com/team/jack-ginter/</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>The firm's own team/bio page for Jack Ginter publishes his individual professional email as jginter@callanfo.com (displayed on his profile page alongside his title 'Chief Executive Officer, Founding Partner'). Note the mail domain callanfo.com differs from the website domain.</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1938970/000193897026000003/primary_doc.xml</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>SEC EDGAR 13F-HR 0001013594-26-000589 (2026-05-15)</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
+          <t>https://riabiz.com/a/2024/4/9/an-abbot-downing-breakaway-but-not-exactly-callan-family-office-hits-5-billion-of-aum-after-just-two-years-using-a-creative-callan-brand-deal-and-a-partnership-model ; https://www.diamond-consultants.com/building-a-business-with-intention-the-5b-callan-family-office-recipe-for-success/</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEC13F-0001536411</t>
+          <t>SEC13F-0001596197</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Duquesne Family Office LLC</t>
+          <t>INTREPID FAMILY OFFICE LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2517,37 +3312,33 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001536411); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001596197); discovered via fts</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001536411&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001596197&amp;type=13F</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Widely reported as the private investment office through which Stanley Druckenmiller manages his own family's capital after closing his hedge fund Duquesne Capital Management to outside investors in 2010. No external clients; it manages one family's money. Source: https://www.fool.com/investing/how-to-invest/famous-investors/duquesne-family-office and https://www.institutionalinvestor.com/article/stan-druckenmiller-overhauls-his-family-offices-us-stock-portfolio</t>
+          <t>No SEC investment-adviser registration found in IAPD (searched 'INTREPID FAMILY OFFICE LLC'); files SEC Form 13F-HR (CIK 0001596197) reporting $123.64B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Files SEC Form 13F as 'Duquesne Family Office LLC' (CIK 0001536411); press uniformly describes it as Druckenmiller's family office. Source: https://13f.info/manager/0001536411-duquesne-family-office-llc</t>
+          <t>No SEC investment-adviser registration found in IAPD (searched 'INTREPID FAMILY OFFICE LLC'); files SEC Form 13F-HR (CIK 0001596197) reporting $123.64B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>13F value: https://13f.info/13f/000153641125000017-duquesne-family-office-llc-q3-2025 (as of 2025-09-30) and https://seekingalpha.com/article/4881297-tracking-stanley-druckenmillers-duquesne-family-office-portfolio-q4-2025-update ; net worth: https://www.forbes.com/profile/stanley-druckenmiller/</t>
-        </is>
-      </c>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Druckenmiller is the founder and sole principal directing all investment decisions; he is named as portfolio manager on the firm's 13F activity in current (2025) press coverage. The 13F signatory Sue Meng is General Counsel (compliance), not the investment decision-maker. Source: https://www.institutionalinvestor.com/article/stan-druckenmiller-overhauls-his-family-offices-us-stock-portfolio and https://www.levelfields.ai/news/stanley-druckenmillers-duquesne-family-office-cuts-exposure-adds-new-tech-and-energy-stocks-in-q1-2025</t>
+          <t>Signed the firm's Form 13F-HR (03-31-2026) as Chief Financial Officer — verified associated person; investment-decision-maker status to be confirmed separately.</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2556,19 +3347,15 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Tried: web searches for a Duquesne domain/team page (none exists); no firm website to host a team directory; no filing or press publishing an individual email. Refused to construct one from a name+domain pattern.</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1536411/000153641126000004/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>https://13f.info/13f/000153641125000017-duquesne-family-office-llc-q3-2025 ; https://seekingalpha.com/article/4881297-tracking-stanley-druckenmillers-duquesne-family-office-portfolio-q4-2025-update ; https://www.levelfields.ai/news/stanley-druckenmillers-duquesne-family-office-cuts-exposure-adds-new-tech-and-energy-stocks-in-q1-2025</t>
+          <t>SEC EDGAR 13F-HR 0001013594-26-000589 (2026-05-15)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -2576,12 +3363,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEC13F-0001683689</t>
+          <t>SEC13F-0001536411</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kopp Family Office, LLC</t>
+          <t>Duquesne Family Office LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2591,33 +3378,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001683689); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001536411); discovered via fts</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001683689&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001536411&amp;type=13F</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No SEC investment-adviser registration found in IAPD (searched 'Kopp Family Office, LLC'); files SEC Form 13F-HR (CIK 0001683689) reporting $163.17B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
+          <t>Widely reported as the private investment office through which Stanley Druckenmiller manages his own family's capital after closing his hedge fund Duquesne Capital Management to outside investors in 2010. No external clients; it manages one family's money. Source: https://www.fool.com/investing/how-to-invest/famous-investors/duquesne-family-office and https://www.institutionalinvestor.com/article/stan-druckenmiller-overhauls-his-family-offices-us-stock-portfolio</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No SEC investment-adviser registration found in IAPD (searched 'Kopp Family Office, LLC'); files SEC Form 13F-HR (CIK 0001683689) reporting $163.17B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
+          <t>Files SEC Form 13F as 'Duquesne Family Office LLC' (CIK 0001536411); press uniformly describes it as Druckenmiller's family office. Source: https://13f.info/manager/0001536411-duquesne-family-office-llc</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>13F value: https://13f.info/13f/000153641125000017-duquesne-family-office-llc-q3-2025 (as of 2025-09-30) and https://seekingalpha.com/article/4881297-tracking-stanley-druckenmillers-duquesne-family-office-portfolio-q4-2025-update ; net worth: https://www.forbes.com/profile/stanley-druckenmiller/</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Signed the firm's Form 13F-HR (06-30-2026) as Chief Financial Officer — verified associated person; investment-decision-maker status to be confirmed separately.</t>
+          <t>Druckenmiller is the founder and sole principal directing all investment decisions; he is named as portfolio manager on the firm's 13F activity in current (2025) press coverage. The 13F signatory Sue Meng is General Counsel (compliance), not the investment decision-maker. Source: https://www.institutionalinvestor.com/article/stan-druckenmiller-overhauls-his-family-offices-us-stock-portfolio and https://www.levelfields.ai/news/stanley-druckenmillers-duquesne-family-office-cuts-exposure-adds-new-tech-and-energy-stocks-in-q1-2025</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2626,15 +3417,19 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Tried: web searches for a Duquesne domain/team page (none exists); no firm website to host a team directory; no filing or press publishing an individual email. Refused to construct one from a name+domain pattern.</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1683689/000089271226000313/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1536411/000153641126000004/primary_doc.xml</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>SEC EDGAR 13F-HR 0000892712-26-000313 (2026-07-09)</t>
+          <t>https://13f.info/13f/000153641125000017-duquesne-family-office-llc-q3-2025 ; https://seekingalpha.com/article/4881297-tracking-stanley-druckenmillers-duquesne-family-office-portfolio-q4-2025-update ; https://www.levelfields.ai/news/stanley-druckenmillers-duquesne-family-office-cuts-exposure-adds-new-tech-and-energy-stocks-in-q1-2025</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -2642,12 +3437,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEC13F-0001889527</t>
+          <t>SEC13F-0001683689</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Louis-Dreyfus Family Office LLC</t>
+          <t>Kopp Family Office, LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2657,22 +3452,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001889527); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001683689); discovered via fts</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001889527&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001683689&amp;type=13F</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>A small, named single-family office (5 13F holdings, ~$64.7M, ~4 employees per business directories) serving the Louis-Dreyfus family; no evidence of external clients or a marketed multi-family service offering. Source: https://www.ctcompanydir.com/companies/louis-dreyfus-family-office-llc/ and https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
+          <t>No SEC investment-adviser registration found in IAPD (searched 'Kopp Family Office, LLC'); files SEC Form 13F-HR (CIK 0001683689) reporting $163.17B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Registered LLC named 'Louis-Dreyfus Family Office LLC' at 10 Westport Rd, Wilton CT (registered 2007 per directory); files SEC 13F under CIK 0001889527. Source: https://www.ctcompanydir.com/companies/louis-dreyfus-family-office-llc/</t>
+          <t>No SEC investment-adviser registration found in IAPD (searched 'Kopp Family Office, LLC'); files SEC Form 13F-HR (CIK 0001683689) reporting $163.17B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2680,14 +3475,10 @@
           <t>corroborated</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc (latest filing Q3 2022, value ~$64,676K as of 2022-09-30); directory revenue estimate: https://www.manta.com/c/mm0v4v4/loius-dreyfus-family-office-llc</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Wingertzahn is the named 13F signatory and CFO; for an office this small he is likely the day-to-day operational and investment administrator. However, the TRUE family investment principal (a Louis-Dreyfus family member/heir) is not publicly identified. Source (signatory role provided in brief); firm identity: https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
+          <t>Signed the firm's Form 13F-HR (06-30-2026) as Chief Financial Officer — verified associated person; investment-decision-maker status to be confirmed separately.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -2696,19 +3487,15 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Tried: searches for a firm website/team page (none), for Wingertzahn contact details, and for any filing/press publishing an individual email. None found published. Did not construct any address.</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1683689/000089271226000313/primary_doc.xml</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
+          <t>SEC EDGAR 13F-HR 0000892712-26-000313 (2026-07-09)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -2716,69 +3503,73 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UKCH-12706913</t>
+          <t>SEC13F-0001889527</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Francis Family Office Limited</t>
+          <t>Louis-Dreyfus Family Office LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Companies House 12706913 (Private limited company); inc. 30 June 2020</t>
+          <t>EDGAR 13F filer (CIK 0001889527); discovered via fts</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/12706913</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001889527&amp;type=13F</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Directors are three members of the Francis family (Benjamin David, Joseph John, Steven John Francis); vehicle holds Ben Francis's Gymshark stake. Source: https://find-and-update.company-information.service.gov.uk/company/12706913/officers ; https://www.netincome.co/p/the-boardroom-drama-behind-one-of</t>
+          <t>A small, named single-family office (5 13F holdings, ~$64.7M, ~4 employees per business directories) serving the Louis-Dreyfus family; no evidence of external clients or a marketed multi-family service offering. Source: https://www.ctcompanydir.com/companies/louis-dreyfus-family-office-llc/ and https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Companies House shows firm renamed from 'BEN FRANCIS LIMITED' to 'FRANCIS FAMILY OFFICE LIMITED' on 2021-02-03; SIC 64209; registered at Gymshark HQ. Press: Ben Francis transferred half his Gymshark ownership into the vehicle, which he owns 100%. Sources: https://find-and-update.company-information.service.gov.uk/company/12706913 ; https://www.netincome.co/p/the-boardroom-drama-behind-one-of</t>
+          <t>Registered LLC named 'Louis-Dreyfus Family Office LLC' at 10 Westport Rd, Wilton CT (registered 2007 per directory); files SEC 13F under CIK 0001889527. Source: https://www.ctcompanydir.com/companies/louis-dreyfus-family-office-llc/</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>corroborated</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Not disclosed. Ben Francis personal net worth ~$900m-1.3bn (Forbes) is personal wealth, not stated FO AUM. https://www.forbes.com/profile/ben-francis-1/</t>
+          <t>https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc (latest filing Q3 2022, value ~$64,676K as of 2022-09-30); directory revenue estimate: https://www.manta.com/c/mm0v4v4/loius-dreyfus-family-office-llc</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Named director since incorporation (2020-06-30), 100% owner and actual decision-maker. https://find-and-update.company-information.service.gov.uk/company/12706913/officers</t>
+          <t>Wingertzahn is the named 13F signatory and CFO; for an office this small he is likely the day-to-day operational and investment administrator. However, the TRUE family investment principal (a Louis-Dreyfus family member/heir) is not publicly identified. Source (signatory role provided in brief); firm identity: https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>No individual email published; firm has no website. Checked Companies House filings and Gymshark press.</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>Tried: searches for a firm website/team page (none), for Wingertzahn contact details, and for any filing/press publishing an individual email. None found published. Did not construct any address.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/12706913 ; https://www.forbes.com/sites/robertolsen-1/2026/07/04/britains-youngest-billionaire-wants-more-control-over-gymshark/</t>
+          <t>https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -2786,12 +3577,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UKCH-07931194</t>
+          <t>UKCH-12706913</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wimmer Family Office Ltd</t>
+          <t>Francis Family Office Limited</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2801,22 +3592,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Companies House 07931194 (Private limited company); inc. 1 February 2012</t>
+          <t>Companies House 12706913 (Private limited company); inc. 30 June 2020</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/07931194</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/12706913</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Website: 'The Wimmer Family Office is based in Mayfair, London, and was established by Per Wimmer.' Built around a single principal. https://wfo.am/</t>
+          <t>Directors are three members of the Francis family (Benjamin David, Joseph John, Steven John Francis); vehicle holds Ben Francis's Gymshark stake. Source: https://find-and-update.company-information.service.gov.uk/company/12706913/officers ; https://www.netincome.co/p/the-boardroom-drama-behind-one-of</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Active FCA-authorised entity (FCA #665654), SIC 66190; live website branded as a family office with Mayfair address. https://wfo.am/ ; https://find-and-update.company-information.service.gov.uk/company/07931194</t>
+          <t>Companies House shows firm renamed from 'BEN FRANCIS LIMITED' to 'FRANCIS FAMILY OFFICE LIMITED' on 2021-02-03; SIC 64209; registered at Gymshark HQ. Press: Ben Francis transferred half his Gymshark ownership into the vehicle, which he owns 100%. Sources: https://find-and-update.company-information.service.gov.uk/company/12706913 ; https://www.netincome.co/p/the-boardroom-drama-behind-one-of</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2826,12 +3617,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Not disclosed. Sectors are those of associated firm Wimmer Financial. https://wimmerfinancial.com/</t>
+          <t>Not disclosed. Ben Francis personal net worth ~$900m-1.3bn (Forbes) is personal wealth, not stated FO AUM. https://www.forbes.com/profile/ben-francis-1/</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Founder/namesake; director from incorporation (2012) until resignation 2024-09-25; still presented as founder/CEO on website and LinkedIn. https://find-and-update.company-information.service.gov.uk/company/07931194/officers ; https://uk.linkedin.com/in/perwimmer</t>
+          <t>Named director since incorporation (2020-06-30), 100% owner and actual decision-maker. https://find-and-update.company-information.service.gov.uk/company/12706913/officers</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2839,24 +3630,16 @@
           <t>confirmed</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>https://wfo.am/</t>
-        </is>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Only a generic mailbox (info@WFO.am) is published (excluded). A per.wimmer@wimmerfinancial.com string appeared only in a URL parameter, not as a published contact — not shipped.</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>https://wfo.am/contact-us/ (firm switchboard, not a personal line)</t>
-        </is>
-      </c>
+          <t>No individual email published; firm has no website. Checked Companies House filings and Gymshark press.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/07931194/officers</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/12706913 ; https://www.forbes.com/sites/robertolsen-1/2026/07/04/britains-youngest-billionaire-wants-more-control-over-gymshark/</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -2864,37 +3647,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEC13F-0001039807</t>
+          <t>UKCH-07931194</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Boston Family Office LLC</t>
+          <t>Wimmer Family Office Ltd</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sec-13f</t>
+          <t>uk-companies-house</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001039807); discovered via fts</t>
+          <t>Companies House 07931194 (Private limited company); inc. 1 February 2012</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001039807&amp;type=13F</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/07931194</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (CRD #107141) serving many clients -- ~789 accounts across high-net-worth individuals, retail investors and charitable organizations; ~$1.7-2.0B AUM; 15 partners. This is a multi-family office / wealth-management RIA, not a single family's office. Source: https://adviserinfo.sec.gov/firm/summary/107141 and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
+          <t>Website: 'The Wimmer Family Office is based in Mayfair, London, and was established by Per Wimmer.' Built around a single principal. https://wfo.am/</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Operates as an RIA branded as a family office ('The Boston Family Office'), founded 1996; files 13F under CIK 0001039807. Source: https://www.bosfam.com/george-beal/</t>
+          <t>Active FCA-authorised entity (FCA #665654), SIC 66190; live website branded as a family office with Mayfair address. https://wfo.am/ ; https://find-and-update.company-information.service.gov.uk/company/07931194</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2904,12 +3687,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/107141 (Form ADV, 2024-2025) and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
+          <t>Not disclosed. Sectors are those of associated firm Wimmer Financial. https://wimmerfinancial.com/</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Beal co-founded the firm in 1996, is a Managing Partner and portfolio manager, and is the named 13F signatory -- an active, current investment decision-maker. Note the firm has 15 partners / ~8 active managing directors, so investment authority is shared. Source: https://www.bosfam.com/george-beal/</t>
+          <t>Founder/namesake; director from incorporation (2012) until resignation 2024-09-25; still presented as founder/CEO on website and LinkedIn. https://find-and-update.company-information.service.gov.uk/company/07931194/officers ; https://uk.linkedin.com/in/perwimmer</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2917,20 +3700,24 @@
           <t>confirmed</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://wfo.am/</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Tried: fetched bosfam.com homepage and bosfam.com/george-beal/ team page -- only phone (617-624-0800) is published, no email. A ZoomInfo listing shows a masked pattern 'g***@bosfam.com' but that is a data-broker inference, NOT a published/attested individual address, so it is excluded. Did not construct an address.</t>
+          <t>Only a generic mailbox (info@WFO.am) is published (excluded). A per.wimmer@wimmerfinancial.com string appeared only in a URL parameter, not as a published contact — not shipped.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
+          <t>https://wfo.am/contact-us/ (firm switchboard, not a personal line)</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>https://www.bosfam.com/wp-content/uploads/2024/02/2024-ADV-Part-2B-Brochure-Supplement_FINAL.pdf ; https://adviserinfo.sec.gov/firm/summary/107141</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/07931194/officers</t>
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
@@ -2938,12 +3725,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEC13F-0002017744</t>
+          <t>SEC13F-0001599603</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2953,22 +3740,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0002017744); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001599603); discovered via fts</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002017744&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001599603&amp;type=13F</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>A registered investment adviser and multi-family office that markets 'Multi Family Office Services' and serves many clients -- high-net-worth individuals, entrepreneurs, families and family offices -- with ~20 staff across multiple US offices. Source: https://arrowrootfamilyoffice.com/team/ and https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
+          <t>'The multi-family office ... with just 100+ client families and over $1 billion under management'; fee-only, $5M minimum, serving a select group of wealthy families/individuals. Sources: https://tarbox.com/who-we-are/ ; https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SEC-registered RIA (Form ADV on file, SEC# 801-121878) branded 'Arrowroot Family Office'; files 13F under CIK 0002017744; multiple offices and a published team. Source: https://9at.com/Adviser/801-121878</t>
+          <t>SEC-registered investment adviser (13F filer) founded 1985 by Laura Tarbox; fee-only financial planning, tax preparation and investment advisory for HNW individuals, charities, businesses, trusts and estates. Sources: https://tarbox.com/history/ ; https://tarbox.com/who-we-are/</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2978,71 +3765,79 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://fintrx.com/firms/firm/arrowroot-family-office-llc-168744 (~$431M, Q2 2025); Form ADV: https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf (2025)</t>
+          <t>Firm-stated. https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079 ; https://tarbox.com/who-we-are/</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Santos is CEO and principal owner, leading the firm; he is the 13F signatory (Roberto Santos = Rob Santos) and a current decision-maker with 20+ years' experience. Source: https://arrowrootfamilyoffice.com/team/ and https://www.getwarmer.com/advisors/roberto-francisco-santos</t>
+          <t>Founder (1985), CEO and principal owner; CFP since 1984 with 40+ years' experience; sets firm vision and strategy and is the lead advisor/decision-maker. https://tarbox.com/team/laura-tarbox/ ; https://tarbox.com/history/</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Tried: fetched the firm's team page (no email published, only phone 833-224-2249 and a contact form); searched for a published individual email; only data-broker (RocketReach) listings exist, which are not published/attested. Did not construct an address.</t>
+          <t>Published on Laura Tarbox's own public presentation slide (title block reads 'Laura Tarbox, CFP(R) 949.721.2330 Laura@Tarbox.com'). Individual address on the firm's own domain; published, not independently provider-verified. Firm bio page itself shows only a phone and contact form. ZoomInfo listing (l***@tarboxgroup.com) is broker-masked and excluded.</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
+          <t>https://tarbox.com/team/laura-tarbox/ (listed on Laura Tarbox's bio page; Newport Beach office line) and her presentation https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>https://www.arrowrootfamilyoffice.com/press-releases/arrowroot-family-office-in-michigan/ ; https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
+          <t>https://tarbox.com/history/ ; https://tarbox.com/who-we-are/ ; https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UKCH-09580739</t>
+          <t>SEC13F-0001731123</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Blu Family Office Limited</t>
+          <t>Biltmore Family Office, LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Companies House 09580739 (Private limited company); inc. 8 May 2015</t>
+          <t>EDGAR 13F filer (CIK 0001731123); discovered via fts</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/09580739</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001731123&amp;type=13F</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Founded 2010 by Christian Armbruester (ex-Credit Suisse) to manage his own family's wealth, then expanded to serve multiple families; repeatedly described as a multi-family office in press (Citywire, Private Banker International). FCA-regulated discretionary manager.</t>
+          <t>Independent SEC-registered adviser to investment-oriented multi-generational families plus institutional clients; ~951 accounts and ~$3.2-3.5B AUM (avg client ~$38M). A collaborative multi-family office, not a single-family vehicle. Sources: https://www.biltmorefamilyoffice.com/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Live FCA-regulated firm; active website; investment arm 'Blu Investment Management' (blu-im.com); corporate LinkedIn; named press profiles; defined team.</t>
+          <t>SEC-registered investment adviser (13F filer) founded 2008 (LLC organized 2013); positions itself as a hybrid family office and RIA. Sources: https://www.biltmorefamilyoffice.com/our-history/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3052,12 +3847,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Third-party estimate via industry data/press (Citywire wealth-manager profile); not officially disclosed.</t>
+          <t>AUM/ADV aggregators. https://fintrx.com/firms/firm/biltmore-family-office-llc-167174 ; https://advisor.guide/firms/biltmore-family-office ; https://whalewisdom.com/filer/biltmore-family-office-llc</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Founder and principal investment decision-maker; single largest shareholder; individual, not nominee. Current day-to-day CEO is Marie Redron.</t>
+          <t>Founder and President/CEO; 30 years' experience in investment management, asset allocation and investment-policy creation; prior Partner at GenSpring Family Offices, President at JPMorgan Private Bank, Managing Director at Brown Brothers Harriman. The firm's top decision-maker (Rael Gorelick is Partner &amp; Head of Investments / CIO-equivalent). https://www.biltmorefamilyoffice.com/who-we-are/chris-cecil/ ; https://www.linkedin.com/in/chris-cecil-9701b818/</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3068,13 +3863,17 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Firm site publishes only a generic mailbox (info@blu-im.com). No individual/principal email published anywhere located. Nothing pattern-generated.</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>No individual email published on the firm site (biltmorefamilyoffice.com pages returned 403 during research; no person@ address found in accessible pages). RocketReach/ContactOut/Datanyze show only masked/pattern (first@biltmorefamilyoffice.com) broker data — excluded; not pattern-generated.</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Firm main line (6836 Morrison Blvd Suite 100, Charlotte); firm switchboard, not a personal line. https://www.biltmorefamilyoffice.com/</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/09580739/officers; https://citywire.com/wealth-manager/news/richmond-based-multi-family-boutique-names-new-ceo/a1109198</t>
+          <t>https://www.biltmorefamilyoffice.com/our-history/ ; https://businessnc.com/chris-cecil/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
@@ -3082,52 +3881,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UKCH-12233405</t>
+          <t>SEC13F-0001039807</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Schwarz Family Office Ltd</t>
+          <t>Boston Family Office LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Companies House 12233405 (Private limited company); inc. 30 September 2019</t>
+          <t>EDGAR 13F filer (CIK 0001039807); discovered via fts</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/12233405</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001039807&amp;type=13F</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Website describes a 'boutique consultancy' providing debt financing, capital raising, IR and fund management for clients, with multiple partners — more advisory/MFO-style than a pure single-family office despite the name. Two shareholders. https://schwarzfamilyoffice.com/</t>
+          <t>SEC-registered investment adviser (CRD #107141) serving many clients -- ~789 accounts across high-net-worth individuals, retail investors and charitable organizations; ~$1.7-2.0B AUM; 15 partners. This is a multi-family office / wealth-management RIA, not a single family's office. Source: https://adviserinfo.sec.gov/firm/summary/107141 and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Active company, SIC 64304 + consultancy codes; own website; listed in Family Capital's 'FamCap 50'. https://schwarzfamilyoffice.com/ ; https://find-and-update.company-information.service.gov.uk/company/12233405</t>
+          <t>Operates as an RIA branded as a family office ('The Boston Family Office'), founded 1996; files 13F under CIK 0001039807. Source: https://www.bosfam.com/george-beal/</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>corroborated</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/107141 (Form ADV, 2024-2025) and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Sole director since incorporation (2019) and majority shareholder (510/1000); ex Merrill Lynch and Bank of Singapore. https://find-and-update.company-information.service.gov.uk/company/12233405/officers ; https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
+          <t>Beal co-founded the firm in 1996, is a Managing Partner and portfolio manager, and is the named 13F signatory -- an active, current investment decision-maker. Note the firm has 15 partners / ~8 active managing directors, so investment authority is shared. Source: https://www.bosfam.com/george-beal/</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3138,13 +3937,17 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Only a generic mailbox (admin@schwarzfamilyoffice.com) is published (excluded). RocketReach result is a masked/broker source and excluded.</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>Tried: fetched bosfam.com homepage and bosfam.com/george-beal/ team page -- only phone (617-624-0800) is published, no email. A ZoomInfo listing shows a masked pattern 'g***@bosfam.com' but that is a data-broker inference, NOT a published/attested individual address, so it is excluded. Did not construct an address.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>https://www.famcap.com/2024/02/the-famcap-50-the-worlds-top-family-capital-investment-specialists/</t>
+          <t>https://www.bosfam.com/wp-content/uploads/2024/02/2024-ADV-Part-2B-Brochure-Supplement_FINAL.pdf ; https://adviserinfo.sec.gov/firm/summary/107141</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -3152,65 +3955,73 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UKCH-14344019</t>
+          <t>SEC13F-0002017744</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hazell Family Office Ltd</t>
+          <t>Arrowroot Family Office, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Companies House 14344019 (Private limited company); inc. 8 September 2022</t>
+          <t>EDGAR 13F filer (CIK 0002017744); discovered via fts</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14344019</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002017744&amp;type=13F</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>All five directors share surname Hazell and one family address (Cefn Henllan Farm, Llanhennock, Usk); appointed same day 2022-09-08; DOB spread (1959-1994) indicates two parents + three adult children — a single-family board. SIC 70221 (financial management).</t>
+          <t>A registered investment adviser and multi-family office that markets 'Multi Family Office Services' and serves many clients -- high-net-worth individuals, entrepreneurs, families and family offices -- with ~20 staff across multiple US offices. Source: https://arrowrootfamilyoffice.com/team/ and https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Family-only board, no external/nominee officers. Patriarch Mark Hazell is MD of the family's operating businesses (haulage / environmental services), a plausible wealth source. https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
+          <t>SEC-registered RIA (Form ADV on file, SEC# 801-121878) branded 'Arrowroot Family Office'; files 13F under CIK 0002017744; multiple offices and a published team. Source: https://9at.com/Adviser/801-121878</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://fintrx.com/firms/firm/arrowroot-family-office-llc-168744 (~$431M, Q2 2025); Form ADV: https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf (2025)</t>
+        </is>
+      </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Patriarch (b.1959), MD of the family operating companies; most probable investment decision-maker; individual, not nominee.</t>
+          <t>Santos is CEO and principal owner, leading the firm; he is the 13F signatory (Roberto Santos = Rob Santos) and a current decision-maker with 20+ years' experience. Source: https://arrowrootfamilyoffice.com/team/ and https://www.getwarmer.com/advisors/roberto-francisco-santos</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>No firm website; searches returned only company/director aggregators; no published individual email. Nothing pattern-generated.</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>Tried: fetched the firm's team page (no email published, only phone 833-224-2249 and a contact form); searched for a published individual email; only data-broker (RocketReach) listings exist, which are not published/attested. Did not construct an address.</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
+          <t>https://www.arrowrootfamilyoffice.com/press-releases/arrowroot-family-office-in-michigan/ ; https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -3218,65 +4029,73 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UKCH-14442767</t>
+          <t>SEC13F-0001950506</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Wedgwood Family Office Limited</t>
+          <t>Fortitude Family Office, LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Companies House 14442767 (Private limited company); inc. 25 October 2022</t>
+          <t>EDGAR 13F filer (CIK 0001950506); discovered via fts</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14442767</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001950506&amp;type=13F</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SIC 66300 (fund management), sole active director Paul Wedgwood at a single residential address; no external clients/multi-family structure. Principal separately holds 'Wedgwood FIC Limited' (a Family Investment Company), consistent with a single-family vehicle.</t>
+          <t>Team page/site confirm it operates as a multi-family office serving 'high and ultra-high net worth families' with coordinated services; ~$1B regulatory AUM. Sources: https://fortitudefo.com/team/ ; https://fortitudefo.com/whoweserve/ ; https://fintrx.com/firms/firm/fortitude-family-office-317615</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Active company (inc. 2022-10-25), SIC 66300, residential registered address. Director Paul Wedgwood (b. Jun 1970) very likely the video-game entrepreneur who sold Splash Damage (up to $150m, 2016) and co-founded Supernova Capital — a plausible wealth source. https://en.wikipedia.org/wiki/Paul_Wedgwood</t>
+          <t>SEC-registered investment adviser (13F filer); fully-integrated advisory team providing investment/wealth management, tax, accounting, philanthropy and business-operations services to HNW/UHNW families; ~$1B AUM (~$2B assets under advisement claimed). Sources: https://fortitudefo.com/ ; https://www.prnewswire.com/news-releases/fortitude-family-office-founder-and-ceo-matt-walker-named-executive-of-the-year-by-business-intelligence-group-302117711.html</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>FINTRX (RAUM) and firm PR (AUA). https://fintrx.com/firms/firm/fortitude-family-office-317615 ; https://www.prnewswire.com/news-releases/fortitude-family-office-wins-2024-wealthmanagementcom-industry-award-for-private-lending-initiative-302253789.html</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Sole active decision-making director since incorporation. Almost certainly the Splash Damage / Supernova Capital entrepreneur (DOB match; also director of Wedgwood FIC Limited).</t>
+          <t>Founder and CEO; named InvestmentNews 2024 Excellence Awardee and Business Intelligence Group 'Executive of the Year' 2024; leads the integrated advisory team. https://fortitudefo.com/team/ ; https://www.linkedin.com/in/matt-walkercpa-cgma/</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>No firm website/press page; no individual email published. A uk.linkedin.com/in/paulwedgwood profile is labelled 'The Carbon Trust' and cannot be confirmed as the same person; nothing inferred.</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
+          <t>No individual email published on the firm site; contact page shows only a Cloudflare-obfuscated generic mailbox and phone (602) 834-0089. No broker emails accepted.</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>https://fortitudefo.com/contact/ (firm main line, 7500 N Dobson Rd Suite 151, Scottsdale; not a personal line)</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14442767/officers</t>
+          <t>https://www.prnewswire.com/news-releases/fortitude-family-office-founder-and-ceo-matt-walker-named-executive-of-the-year-by-business-intelligence-group-302117711.html ; https://www.prnewswire.com/news-releases/matt-walker-fortitude-family-office-founder-and-ceo-honored-as-investmentnews-excellence-awardee-302175687.html ; https://www.prnewswire.com/news-releases/fortitude-family-office-wins-2024-wealthmanagementcom-industry-award-for-private-lending-initiative-302253789.html</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -3284,91 +4103,111 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UKCH-10876208</t>
+          <t>SEC13F-0001802278</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SHA FAMILY OFFICE LTD</t>
+          <t>Stokes Family Office, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Companies House 10876208 (Private limited company); inc. 20 July 2017</t>
+          <t>EDGAR 13F filer (CIK 0001802278); discovered via fts</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/10876208</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001802278&amp;type=13F</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Mr Sharnpreet Singh Buttar); firm carries a fund-management/investment SIC (64205 - Activities of financial services holding companies). Single-family control of an investment vehicle = single-family office.</t>
+          <t>Firm is '100% Family Owned' (owned by the Stokes family) but serves outside clients: 'individuals, families and institutions' with a billion-dollar advisory practice. Broad multi-client RIA, not a single-family vehicle. Sources: https://stokesfamilyoffice.com/about-us/ ; https://fintrx.com/firms/firm/stokes-family-office-llc-300899</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Mr Sharnpreet Singh Buttar); firm carries a fund-management/investment SIC (64205 - Activities of financial services holding companies). Single-family control of an investment vehicle = single-family office.</t>
+          <t>SEC-registered investment adviser (13F filer) branded 'family office'; offers wealth management, retirement plan consulting and family-office services; ~$3.35B AUM. Sources: https://stokesfamilyoffice.com/about-us/ ; https://stokesfamilyoffice.com/insights/stokes-family-office-exceeds3b-aum/</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Firm press/AUM aggregators. https://stokesfamilyoffice.com/insights/stokes-family-office-exceeds3b-aum/ ; https://fintrx.com/firms/firm/stokes-family-office-llc-300899 ; https://aum13f.com/firm/stokes-family-office-llc</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Doug Stokes, CFA, is co-owner and Managing Partner who 'takes an active role in the firm's investment research process and investment committee decisions' — the investment decision-maker (co-managing partner Gregory Stokes, JD, runs business/innovation; founder David Stokes is Founder Emeritus). https://stokesfamilyoffice.com/about-us/ ; https://www.linkedin.com/in/doug-stokes-03716932/</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Only a generic mailbox published (info@stokesfamilyoffice.com on https://stokesfamilyoffice.com/contact-us/); no individual email on any firm bio/contact page. ZoomInfo/RocketReach/ContactOut listings (e.g., doug@... , dougstokes4@gmail.com) are broker-sourced/masked and excluded per rules.</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>https://stokesfamilyoffice.com/contact-us/ (New Orleans office switchboard, 1100 Poydras St Suite 2775; not a personal line)</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/stokes-family-office-named-to-top-ria-list-by-forbesshook-research-301958395.html ; https://stokesfamilyoffice.com/contact-us/ ; https://stokesfamilyoffice.com/insights/stokes-family-office-exceeds3b-aum/</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UKCH-15240886</t>
+          <t>SEC13F-0002056106</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FREEDMAN FAMILY OFFICE</t>
+          <t>Stenger Family Office, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Companies House 15240886 (Private unlimited company); inc. 27 October 2023</t>
+          <t>EDGAR 13F filer (CIK 0002056106); discovered via fts</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/15240886</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002056106&amp;type=13F</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+          <t>Self-described 'multi-family office'; the Stenger family has served 'over 1,200 families across the United States'. Serves many outside client families. Sources: https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+          <t xml:space="preserve">SEC-registered investment adviser (13F filer); independent fiduciary wealth-management firm offering financial planning, investment management, tax and estate strategies under a family-office model; ~$731M AUM. Sources: https://www.stengerfamilyoffice.com/ </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3376,72 +4215,546 @@
           <t>corroborated</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Firm-stated. https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Founder and CEO / lead financial advisor; prior Senior Vice President financial advisor at Morgan Stanley Wealth Management, and roles at Invesco PowerShares and PwC; the firm's decision-maker and namesake. https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No individual email published on the firm site; contact is via a Calendly link (calendly.com/nicholasstenger/intro-meeting) rather than a published email address. No broker emails accepted.</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>https://www.stengerfamilyoffice.com/ ; https://www.stengerfamilyoffice.com/financialadvisornaperville ; https://podcasts.apple.com/us/podcast/the-nick-stenger-show/id1678810370</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>SEC13F-0002105684</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Cambient Family Office, LLC</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sec-13f</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>EDGAR 13F filer (CIK 0002105684); discovered via fts</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002105684&amp;type=13F</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Self-described 'independent multi-family office serving affluent families, private foundations, and entrepreneurs'; Form ADV shows ~260 accounts and 172+ clients across categories. Sources: https://www.cambient.com/about-us ; Form ADV Part 1 (Item 5) https://reports.adviserinfo.sec.gov/reports/ADV/335128/PDF/335128.pdf</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SEC-registered investment adviser (SEC file 801-132283, CRD 335128, 13F filer), registration effective 2025-04-02; ~$857.9M regulatory AUM, discretionary equity-oriented management. Sources: https://adviserinfo.sec.gov/firm/summary/335128 ; Form ADV https://reports.adviserinfo.sec.gov/reports/ADV/335128/PDF/335128.pdf</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Form ADV Part 1 Item 5.F (filed 2026-07-16). https://reports.adviserinfo.sec.gov/reports/ADV/335128/PDF/335128.pdf ; corroborated https://fintrx.com/firms/firm/cambient-family-office-llc-335128</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Listed as a direct owner/executive on Form ADV Schedule A and 'oversees investment strategy and portfolio construction' as a CFA charterholder — a lead investment decision-maker. Co-owner Daniel Rausch (CIMA) is a co-PM; co-owner Joshua Gibbs is Trust Advisor &amp; CCO and signed/filed the 13F. https://www.cambient.com/our-team ; Form ADV Schedule A https://reports.adviserinfo.sec.gov/reports/ADV/335128/PDF/335128.pdf ; https://www.linkedin.com/in/andrew-fabiano-2b4869ab</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Only generic mailbox published (info@cambient.com on cambient.com). No individual email on the firm site or in filings. Datanyze/ZoomInfo listings are broker-sourced and excluded.</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Form ADV / 13F cover page (firm main line, Ada MI) https://reports.adviserinfo.sec.gov/reports/ADV/335128/PDF/335128.pdf</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>https://api.adviserinfo.sec.gov/search/firm/335128 ; https://reports.adviserinfo.sec.gov/reports/ADV/335128/PDF/335128.pdf ; https://reports.adviserinfo.sec.gov/reports/individual/individual_8098624.pdf</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>UKCH-09580739</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Blu Family Office Limited</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>uk-companies-house</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Companies House 09580739 (Private limited company); inc. 8 May 2015</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/09580739</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Founded 2010 by Christian Armbruester (ex-Credit Suisse) to manage his own family's wealth, then expanded to serve multiple families; repeatedly described as a multi-family office in press (Citywire, Private Banker International). FCA-regulated discretionary manager.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Live FCA-regulated firm; active website; investment arm 'Blu Investment Management' (blu-im.com); corporate LinkedIn; named press profiles; defined team.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Third-party estimate via industry data/press (Citywire wealth-manager profile); not officially disclosed.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Founder and principal investment decision-maker; single largest shareholder; individual, not nominee. Current day-to-day CEO is Marie Redron.</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Firm site publishes only a generic mailbox (info@blu-im.com). No individual/principal email published anywhere located. Nothing pattern-generated.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/09580739/officers; https://citywire.com/wealth-manager/news/richmond-based-multi-family-boutique-names-new-ceo/a1109198</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>UKCH-12233405</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Schwarz Family Office Ltd</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>uk-companies-house</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Companies House 12233405 (Private limited company); inc. 30 September 2019</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/12233405</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Website describes a 'boutique consultancy' providing debt financing, capital raising, IR and fund management for clients, with multiple partners — more advisory/MFO-style than a pure single-family office despite the name. Two shareholders. https://schwarzfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Active company, SIC 64304 + consultancy codes; own website; listed in Family Capital's 'FamCap 50'. https://schwarzfamilyoffice.com/ ; https://find-and-update.company-information.service.gov.uk/company/12233405</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Sole director since incorporation (2019) and majority shareholder (510/1000); ex Merrill Lynch and Bank of Singapore. https://find-and-update.company-information.service.gov.uk/company/12233405/officers ; https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Only a generic mailbox (admin@schwarzfamilyoffice.com) is published (excluded). RocketReach result is a masked/broker source and excluded.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>https://www.famcap.com/2024/02/the-famcap-50-the-worlds-top-family-capital-investment-specialists/</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>UKCH-14344019</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Hazell Family Office Ltd</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>uk-companies-house</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Companies House 14344019 (Private limited company); inc. 8 September 2022</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14344019</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>All five directors share surname Hazell and one family address (Cefn Henllan Farm, Llanhennock, Usk); appointed same day 2022-09-08; DOB spread (1959-1994) indicates two parents + three adult children — a single-family board. SIC 70221 (financial management).</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Family-only board, no external/nominee officers. Patriarch Mark Hazell is MD of the family's operating businesses (haulage / environmental services), a plausible wealth source. https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Patriarch (b.1959), MD of the family operating companies; most probable investment decision-maker; individual, not nominee.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No firm website; searches returned only company/director aggregators; no published individual email. Nothing pattern-generated.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>UKCH-14442767</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Wedgwood Family Office Limited</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>uk-companies-house</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Companies House 14442767 (Private limited company); inc. 25 October 2022</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14442767</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>SIC 66300 (fund management), sole active director Paul Wedgwood at a single residential address; no external clients/multi-family structure. Principal separately holds 'Wedgwood FIC Limited' (a Family Investment Company), consistent with a single-family vehicle.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Active company (inc. 2022-10-25), SIC 66300, residential registered address. Director Paul Wedgwood (b. Jun 1970) very likely the video-game entrepreneur who sold Splash Damage (up to $150m, 2016) and co-founded Supernova Capital — a plausible wealth source. https://en.wikipedia.org/wiki/Paul_Wedgwood</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sole active decision-making director since incorporation. Almost certainly the Splash Damage / Supernova Capital entrepreneur (DOB match; also director of Wedgwood FIC Limited).</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No firm website/press page; no individual email published. A uk.linkedin.com/in/paulwedgwood profile is labelled 'The Carbon Trust' and cannot be confirmed as the same person; nothing inferred.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14442767/officers</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>UKCH-10876208</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SHA FAMILY OFFICE LTD</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>uk-companies-house</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Companies House 10876208 (Private limited company); inc. 20 July 2017</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/10876208</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Mr Sharnpreet Singh Buttar); firm carries a fund-management/investment SIC (64205 - Activities of financial services holding companies). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Mr Sharnpreet Singh Buttar); firm carries a fund-management/investment SIC (64205 - Activities of financial services holding companies). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>UKCH-15240886</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FREEDMAN FAMILY OFFICE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>uk-companies-house</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Companies House 15240886 (Private unlimited company); inc. 27 October 2023</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/15240886</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>UKCH-11031775</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>RALPH FAMILY OFFICE LIMITED</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>uk-companies-house</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>Companies House 11031775 (Private limited company); inc. 25 October 2017</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>https://find-and-update.company-information.service.gov.uk/company/11031775</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Melanie Lynette Ralph; Mr Jan De Ridder Ralph); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Melanie Lynette Ralph; Mr Jan De Ridder Ralph); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>corroborated</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3454,13 +4767,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -4097,7 +5410,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DAO FAMILY OFFICE LP</t>
+          <t>Crew Family Office Limited</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4108,7 +5421,7 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4120,7 +5433,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DAVIDOFF FREY FAMILY OFFICE (UK) LTD</t>
+          <t>DAO FAMILY OFFICE LP</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4143,7 +5456,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DE VILLIERS FAMILY OFFICE LIMITED</t>
+          <t>DAVIDOFF FREY FAMILY OFFICE (UK) LTD</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4166,7 +5479,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DEUTSCHE BANK AG\</t>
+          <t>DE VILLIERS FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4200,7 +5513,7 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -4212,7 +5525,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DONE FAMILY OFFICE LIMITED</t>
+          <t>DEUTSCHE BANK AG\</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4223,7 +5536,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -4235,7 +5548,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DONNELLY FAMILY OFFICE</t>
+          <t>DONE FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4258,7 +5571,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DSW FAMILY OFFICE LTD</t>
+          <t>DONNELLY FAMILY OFFICE</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4281,7 +5594,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DUBAI FAMILY OFFICE LTD</t>
+          <t>DSW FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4304,7 +5617,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dorsey &amp; Whitney Trust CO LLC</t>
+          <t>DUBAI FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4338,7 +5651,7 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -4350,7 +5663,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EMFO, LLC</t>
+          <t>Dorsey &amp; Whitney Trust CO LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4361,7 +5674,7 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -4384,7 +5697,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -4396,7 +5709,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FAMILY OFFICE CONSULTING LIMITED</t>
+          <t>EMFO, LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4407,7 +5720,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -4419,7 +5732,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FAMILY OFFICE EEB LTD</t>
+          <t>FAMILY OFFICE CONSULTING LIMITED</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4442,7 +5755,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FIDUCIARY FAMILY OFFICE, LLC</t>
+          <t>FAMILY OFFICE EEB LTD</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4465,7 +5778,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FOOTPRINTS FAMILY OFFICE UK EUROPE LIMITED</t>
+          <t>FIDUCIARY FAMILY OFFICE, LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4488,7 +5801,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FREEDMAN FAMILY OFFICE</t>
+          <t>FOOTPRINTS FAMILY OFFICE UK EUROPE LIMITED</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4511,7 +5824,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FRIGUS FAMILY OFFICE LTD</t>
+          <t>FREEDMAN FAMILY OFFICE</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4534,7 +5847,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FRONTIER FAMILY OFFICE FORUM HOLDINGS LIMITED</t>
+          <t>FRIGUS FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4557,7 +5870,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Family Investment Center, Inc.</t>
+          <t>FRONTIER FAMILY OFFICE FORUM HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4591,7 +5904,7 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -4603,7 +5916,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Family Office DS Limited</t>
+          <t>Family Investment Center, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4614,7 +5927,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -4718,7 +6031,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Family Office Research LLC</t>
+          <t>Family Office DS Limited</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4729,7 +6042,7 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4741,7 +6054,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fortis Advisors, LLC</t>
+          <t>Family Office DS Limited</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4752,7 +6065,7 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -4764,7 +6077,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Fortis Advisors, LLC</t>
+          <t>Family Office Research LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4775,7 +6088,7 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -4787,7 +6100,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fortitude Family Office, LLC</t>
+          <t>Fortis Advisors, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -4810,7 +6123,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GELLING FAMILY OFFICE LIMITED</t>
+          <t>Fortis Advisors, LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4821,7 +6134,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -4833,7 +6146,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GUNPUTH FAMILY OFFICE LIMITED</t>
+          <t>Fortitude Family Office, LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4856,7 +6169,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Geller Advisors LLC</t>
+          <t>GELLING FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4879,7 +6192,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Geller Advisors LLC</t>
+          <t>GUNPUTH FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4890,7 +6203,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -4902,7 +6215,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>HALL LAURIE J TRUSTEE</t>
+          <t>Geller Advisors LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4925,7 +6238,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HALL LAURIE J TRUSTEE</t>
+          <t>Geller Advisors LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4948,7 +6261,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HBBA FAMILY OFFICE LIMITED</t>
+          <t>HALL LAURIE J TRUSTEE</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4971,7 +6284,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HILL FAMILY OFFICE LIMITED</t>
+          <t>HALL LAURIE J TRUSTEE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4982,7 +6295,7 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -4994,7 +6307,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
+          <t>HBBA FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5017,7 +6330,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
+          <t>HILL FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5028,7 +6341,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -5040,7 +6353,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>INTREPID FAMILY OFFICE LLC</t>
+          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5063,7 +6376,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ISHER CAPITAL FAMILY OFFICE LTD</t>
+          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5074,7 +6387,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -5086,7 +6399,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Independent Family Office, LLC</t>
+          <t>INTREPID FAMILY OFFICE LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5109,7 +6422,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Kopp Family Office, LLC</t>
+          <t>ISHER CAPITAL FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5132,7 +6445,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LELS CLARK FAMILY OFFICE LTD</t>
+          <t>Independent Family Office, LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5155,7 +6468,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Lido Advisors, LLC</t>
+          <t>Kopp Family Office, LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5178,7 +6491,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Lido Advisors, LLC</t>
+          <t>LELS CLARK FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5189,7 +6502,7 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -5201,7 +6514,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>MARCUARD FAMILY OFFICE LTD</t>
+          <t>Lido Advisors, LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5224,7 +6537,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MOBH UK FAMILY OFFICE LTD</t>
+          <t>Lido Advisors, LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5235,7 +6548,7 @@
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -5247,7 +6560,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NORTHBRIDGE FAMILY OFFICE LTD</t>
+          <t>MARCUARD FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5270,7 +6583,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NOVA FAMILY OFFICE LTD</t>
+          <t>MOBH UK FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5293,7 +6606,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Nilsson Family Office Ltd</t>
+          <t>NORTHBRIDGE FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5304,7 +6617,7 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -5316,7 +6629,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Nilsson Family Office Ltd</t>
+          <t>NOVA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5327,7 +6640,7 @@
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -5408,7 +6721,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>OLD HOUSE FAMILY OFFICE LIMITED</t>
+          <t>Nilsson Family Office Ltd</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5419,7 +6732,7 @@
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -5431,7 +6744,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>OneAscent Family Office, LLC</t>
+          <t>Nilsson Family Office Ltd</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5442,7 +6755,7 @@
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -5454,7 +6767,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Orion Porfolio Solutions, LLC</t>
+          <t>Nilsson Family Office Ltd</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5465,7 +6778,7 @@
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -5477,7 +6790,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Orion Porfolio Solutions, LLC</t>
+          <t>OLD HOUSE FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5488,7 +6801,7 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -5500,7 +6813,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Orion Portfolio Solutions, LLC</t>
+          <t>OneAscent Family Office, LLC</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5523,7 +6836,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Orion Portfolio Solutions, LLC</t>
+          <t>Orion Porfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5534,7 +6847,7 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -5546,7 +6859,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PANDA FAMILY OFFICE LTD</t>
+          <t>Orion Porfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5557,7 +6870,7 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -5569,7 +6882,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>PANTHEON A FAMILY OFFICE LIMITED</t>
+          <t>Orion Portfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -5592,7 +6905,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>PATHSTONE FAMILY OFFICE, LLC</t>
+          <t>Orion Portfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -5603,7 +6916,7 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -5615,7 +6928,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PMG Family Office LLC</t>
+          <t>PANDA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -5638,7 +6951,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PROSPERITY FAMILY OFFICE LIMITED</t>
+          <t>PANTHEON A FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5661,7 +6974,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Pathstone Holdings, LLC</t>
+          <t>PATHSTONE FAMILY OFFICE, LLC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -5684,7 +6997,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Pathstone Holdings, LLC</t>
+          <t>PMG Family Office LLC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -5695,7 +7008,7 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -5707,7 +7020,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Pioneer Family Office, LLC</t>
+          <t>PROSPERITY FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -5730,7 +7043,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>RALPH FAMILY OFFICE LIMITED</t>
+          <t>Pathstone Holdings, LLC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -5753,7 +7066,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SHA FAMILY OFFICE LTD</t>
+          <t>Pathstone Holdings, LLC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -5764,7 +7077,7 @@
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -5776,7 +7089,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SIGNATURE FAMILY OFFICE LTD</t>
+          <t>Pioneer Family Office, LLC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -5799,7 +7112,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SIMON FAMILY OFFICE INSURES LIMITED</t>
+          <t>RALPH FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -5822,7 +7135,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SWAILES COMMERCIAL FAMILY OFFICE LTD</t>
+          <t>SHA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -5845,7 +7158,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SWAILES TRADING GROUP FAMILY OFFICE LTD</t>
+          <t>SIGNATURE FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -5868,7 +7181,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Sageworth Trust Co</t>
+          <t>SIMON FAMILY OFFICE INSURES LIMITED</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -5891,7 +7204,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sageworth Trust Co</t>
+          <t>SWAILES COMMERCIAL FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -5902,7 +7215,7 @@
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -5914,7 +7227,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Standard Family Office LLC</t>
+          <t>SWAILES TRADING GROUP FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -5937,7 +7250,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Stenger Family Office, LLC</t>
+          <t>Sageworth Trust Co</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -5960,7 +7273,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Stokes Family Office, LLC</t>
+          <t>Sageworth Trust Co</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -5971,7 +7284,7 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -5983,7 +7296,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>THE DIGITAL FAMILY OFFICE LIMITED</t>
+          <t>Standard Family Office LLC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -6006,7 +7319,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>THE FAMILY OFFICE CHELTENHAM LIMITED</t>
+          <t>Stenger Family Office, LLC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -6029,7 +7342,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>TIGRIS FAMILY OFFICE LIMITED</t>
+          <t>Stokes Family Office, LLC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -6052,7 +7365,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Tarbox Family Office, Inc.</t>
+          <t>THE DIGITAL FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -6075,7 +7388,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Timonier Family Office, LTD.</t>
+          <t>THE FAMILY OFFICE CHELTENHAM LIMITED</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -6098,7 +7411,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TrustBank</t>
+          <t>TIGRIS FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -6121,7 +7434,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TrustBank</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -6132,7 +7445,7 @@
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -6144,18 +7457,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>UNITA FAMILY OFFICE UK LIMITED</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>firm-qualification</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
+          <t>principal_email</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>laura@tarbox.com</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>email not found at cited source on re-fetch (https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf); downgraded verified-&gt;unverified</t>
         </is>
       </c>
     </row>
@@ -6167,18 +7484,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>UR FAMILY OFFICE MANAGEMENT SERVICES LTD</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>firm-qualification</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
+          <t>principal_email</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>laura@tarbox.com</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>email not found at cited source on re-fetch (https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf); downgraded verified-&gt;unverified</t>
         </is>
       </c>
     </row>
@@ -6190,7 +7511,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>VASIL FAMILY OFFICE LLP</t>
+          <t>Timonier Family Office, LTD.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -6213,7 +7534,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>VPR Management LLC</t>
+          <t>TrustBank</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -6236,7 +7557,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>VPR Management LLC</t>
+          <t>TrustBank</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -6259,7 +7580,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>VSTAR LONDON FAMILY OFFICE LTD</t>
+          <t>UNITA FAMILY OFFICE UK LIMITED</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -6282,7 +7603,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Veritable, L.P.</t>
+          <t>UR FAMILY OFFICE MANAGEMENT SERVICES LTD</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -6305,7 +7626,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Veritable, L.P.</t>
+          <t>VASIL FAMILY OFFICE LLP</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -6316,7 +7637,7 @@
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -6328,7 +7649,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Virtus Family Office LLC</t>
+          <t>VPR Management LLC</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -6351,7 +7672,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>WEYBRIDGE FAMILY OFFICE SERVICES LIMITED</t>
+          <t>VPR Management LLC</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -6362,7 +7683,7 @@
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -6374,7 +7695,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Wealthgate Family Office, LLC</t>
+          <t>VSTAR LONDON FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -6397,7 +7718,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Wilmington Savings Fund Society, FSB</t>
+          <t>Veritable, L.P.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -6420,7 +7741,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Wilmington Savings Fund Society, FSB</t>
+          <t>Veritable, L.P.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -6430,6 +7751,121 @@
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
+        <is>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Virtus Family Office LLC</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>WEYBRIDGE FAMILY OFFICE SERVICES LIMITED</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Wealthgate Family Office, LLC</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Wilmington Savings Fund Society, FSB</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Wilmington Savings Fund Society, FSB</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
         <is>
           <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
@@ -6478,11 +7914,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>47%</t>
+          <t>62%</t>
         </is>
       </c>
     </row>
@@ -6497,7 +7933,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>38%</t>
         </is>
       </c>
     </row>
@@ -6509,7 +7945,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C5" t="inlineStr"/>
     </row>
@@ -6520,7 +7956,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C6" t="inlineStr"/>
     </row>

--- a/data/final/family_office_dataset.xlsx
+++ b/data/final/family_office_dataset.xlsx
@@ -448,7 +448,7 @@
     <col width="32" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="38" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
     <col width="18" customWidth="1" min="19" max="19"/>
     <col width="60" customWidth="1" min="20" max="20"/>
@@ -1587,12 +1587,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEC13F-0001731123</t>
+          <t>SEC13F-0002056106</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Biltmore Family Office, LLC</t>
+          <t>Stenger Family Office, LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1602,47 +1602,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Founder Chris Cecil is a great-grandson of George Vanderbilt (builder of the Biltmore Estate) and son of Asheville developer George Cecil; 'Biltmore' name derives from that Vanderbilt/Cecil family heritage. The firm serves many outside client families (MFO), not the Vanderbilt/Cecil family exclusively.</t>
+          <t>Stenger family (firm founded/led by Nick Stenger; the family has advised clients since 1981). The 'family' is the owner-operator, not a single client family.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.biltmorefamilyoffice.com/</t>
+          <t>https://www.stengerfamilyoffice.com/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/biltmore-family-office-llc</t>
+          <t>https://www.linkedin.com/company/stenger-family-office</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Charlotte, NC-based multi-family office and SEC-registered investment adviser founded in 2008 by Chris Cecil. A collaborative/independent RIA to investment-oriented multi-generational families and institutions, providing investment management, asset allocation, investment-policy design, multi-generational and succession planning. ~$3.2-3.5B AUM.</t>
+          <t>Naperville, IL-based multi-family office / independent fiduciary RIA led by founder-CEO Nick Stenger, offering financial planning, investment management, and (via related companies) tax preparation, estate strategies and insurance. Also has a Spring, TX office. ~$731M AUM; named a Forbes Best-in-State Wealth Advisor 2026.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Collaborative, investment-policy-driven management for multi-generational HNW/UHNW families and institutions.</t>
+          <t>Goals-based planning: assesses cash needs and upcoming goals, then builds customized portfolios.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Diversified public-equity/ETF portfolios; disclosed top 13F holdings include AAPL, IAU (gold), AVDX, ROBO, VV. No single-sector concentration.</t>
+          <t>Core individual-stock portfolios and ETF-based asset-allocation portfolios; no single-sector focus.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>~$3.2-3.5 billion (reported ~$3.47B regulatory AUM across ~951 accounts)</t>
+          <t>~$731 million (as of 2026-06-30)</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>CHARLOTTE</t>
+          <t>NAPERVILLE</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1652,38 +1652,38 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Chris Cecil</t>
+          <t>Nicholas David Stenger</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Founder, President &amp; CEO</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/chris-cecil-9701b818/</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr"/>
+          <t>Founder &amp; Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>nick.stenger@stengerfamilyoffice.com</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>+1 704-248-5230</t>
+          <t>630-912-8295</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Founded 2008 by Chris Cecil (LLC organized 2013); ~$3.2-3.5B AUM across ~951 accounts, avg client ~$38M; Cecil chairs TIGER 21 Charlotte / Family Office groups</t>
+          <t>$731M AUM (2026-06-30); Forbes Best-in-State Wealth Advisor 2026; hosts 'The Nick Stenger Show' podcast; opened Spring, TX office</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2008 (founding); 2013 (LLC organized)</t>
+          <t>2026-06-30 (AUM date); 2026 (Forbes Best-in-State)</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1693,19 +1693,19 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Chris Cecil chosen as principal (founder/CEO); Rael Gorelick is Partner &amp; Head of Investments and would be the CIO-level investment lead. No published individual email located. AUM varies by source ($3.2B-$3.5B).</t>
+          <t>Serves 1,200+ families 'of all net worth sizes' — a broad wealth-management RIA using family-office branding rather than a classic UHNW MFO; hence proof strength 'corroborated'. Personal LinkedIn /in profile not located (only company page and a Calendly slug for 'nicholasstenger'). No published individual email or direct phone line found.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEC13F-0001039807</t>
+          <t>SEC13F-0001731123</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Boston Family Office Llc</t>
+          <t>Biltmore Family Office, LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1713,41 +1713,49 @@
           <t>MFO</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Founder Chris Cecil is a great-grandson of George Vanderbilt (builder of the Biltmore Estate) and son of Asheville developer George Cecil; 'Biltmore' name derives from that Vanderbilt/Cecil family heritage. The firm serves many outside client families (MFO), not the Vanderbilt/Cecil family exclusively.</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.bosfam.com/</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>https://www.biltmorefamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/biltmore-family-office-llc</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>The Boston Family Office LLC is an independent, employee-owned registered investment adviser founded in 1996 and based in Boston, MA. It provides multi-family-office-style wealth management -- investment management, financial planning, and adviser selection -- to high-net-worth individuals, families and charitable organizations across roughly 789 accounts and ~$1.7-2.0B in assets. It is a multi-family/RIA firm rather than a single-family office.</t>
+          <t>Charlotte, NC-based multi-family office and SEC-registered investment adviser founded in 2008 by Chris Cecil. A collaborative/independent RIA to investment-oriented multi-generational families and institutions, providing investment management, asset allocation, investment-policy design, multi-generational and succession planning. ~$3.2-3.5B AUM.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Client-tailored, diversified portfolio management for wealth preservation and growth across HNW households and institutions; discretionary management (769 of 789 accounts discretionary). Specific house investment philosophy not detailed publicly.</t>
+          <t>Collaborative, investment-policy-driven management for multi-generational HNW/UHNW families and institutions.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Diversified multi-asset wealth management (public equities, fixed income, funds); not sector-specialized. A partner sits on the board of fixed-income manager Breckinridge Capital Advisors.</t>
+          <t>Diversified public-equity/ETF portfolios; disclosed top 13F holdings include AAPL, IAU (gold), AVDX, ROBO, VV. No single-sector concentration.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>~$1.7B AUM across 789 accounts (Form ADV/adviserinfo, 2024-2025); third-party profiles cite ~$1.9-2.02B. As of the most recent Form ADV (2024 filing cycle).</t>
+          <t>~$3.2-3.5 billion (reported ~$3.47B regulatory AUM across ~951 accounts)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1757,17 +1765,17 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>George P. Beal</t>
+          <t>Chris Cecil</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; Managing Partner (Portfolio Manager)</t>
+          <t>Founder, President &amp; CEO</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/george-beal-a6107a16/</t>
+          <t>https://www.linkedin.com/in/chris-cecil-9701b818/</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
@@ -1778,17 +1786,17 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>617-624-0800</t>
+          <t>+1 704-248-5230</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Filed Form ADV Part 2A/2B brochures in the 2024 filing cycle (Feb 2024); a partner (Beal) serves on the board of Breckinridge Capital Advisors. Firm moved offices to 20 Custom House St.</t>
+          <t>Founded 2008 by Chris Cecil (LLC organized 2013); ~$3.2-3.5B AUM across ~951 accounts, avg client ~$38M; Cecil chairs TIGER 21 Charlotte / Family Office groups</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2024-02-01 (ADV Part 2B brochure)</t>
+          <t>2008 (founding); 2013 (LLC organized)</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1798,19 +1806,19 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Despite the 'family office' name, this is functionally a multi-family-office RIA / private wealth manager serving hundreds of client accounts, not a single family's office. Investment authority is distributed among ~8 managing directors, so Beal is one of several senior decision-makers (though the 13F signatory and co-founder). No official company LinkedIn URL confirmed. No individual email is published (the ZoomInfo masked pattern was deliberately not used).</t>
+          <t>Chris Cecil chosen as principal (founder/CEO); Rael Gorelick is Partner &amp; Head of Investments and would be the CIO-level investment lead. No published individual email located. AUM varies by source ($3.2B-$3.5B).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEC13F-0002017744</t>
+          <t>SEC13F-0001039807</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC</t>
+          <t>Boston Family Office Llc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1821,42 +1829,38 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://arrowrootfamilyoffice.com/</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/arrowroot-family-office</t>
-        </is>
-      </c>
+          <t>https://www.bosfam.com/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC is a Marina del Rey, CA-based registered investment adviser and multi-family office, originally founded in 2013 as Vitreous Partners and rebranded in 2017. It provides multidisciplinary wealth management -- investment management, retirement, tax and estate planning -- to high-net-worth individuals, entrepreneurs, families and small institutions, with offices in Southern and Northern California, Virginia and Michigan. It is a multi-client RIA, not a single family's office.</t>
+          <t>The Boston Family Office LLC is an independent, employee-owned registered investment adviser founded in 1996 and based in Boston, MA. It provides multi-family-office-style wealth management -- investment management, financial planning, and adviser selection -- to high-net-worth individuals, families and charitable organizations across roughly 789 accounts and ~$1.7-2.0B in assets. It is a multi-family/RIA firm rather than a single-family office.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Team-based, fiduciary, goals-driven wealth management emphasizing comprehensive planning and diversified investment management for affluent households and business owners; open-architecture advice.</t>
+          <t>Client-tailored, diversified portfolio management for wealth preservation and growth across HNW households and institutions; discretionary management (769 of 789 accounts discretionary). Specific house investment philosophy not detailed publicly.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Diversified multi-asset wealth management (public equities, funds/ETFs, fixed income, alternatives); not sector-specialized.</t>
+          <t>Diversified multi-asset wealth management (public equities, fixed income, funds); not sector-specialized. A partner sits on the board of fixed-income manager Breckinridge Capital Advisors.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>~$431M AUM as of Q2 2025 (third-party profiles); regulatory AUM per the 2025 Form ADV on the firm's site. A floor for total client assets under advisement.</t>
+          <t>~$1.7B AUM across 789 accounts (Form ADV/adviserinfo, 2024-2025); third-party profiles cite ~$1.9-2.02B. As of the most recent Form ADV (2024 filing cycle).</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Marina Del Rey</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1866,17 +1870,17 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Rob (Roberto Francisco) Santos</t>
+          <t>George P. Beal</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Chief Executive Officer &amp; Principal Owner</t>
+          <t>Co-Founder &amp; Managing Partner (Portfolio Manager)</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/rob-santos-afo/</t>
+          <t>https://www.linkedin.com/in/george-beal-a6107a16/</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
@@ -1887,17 +1891,17 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>310.341.4774</t>
+          <t>617-624-0800</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Announced expansion of its private-wealth practice into Michigan via addition of The Athena Financial Group (offices now include Marina del Rey CA, Rochester Hills MI, Charlottesville VA, El Dorado Hills CA); filed updated Form ADV Part 2A/2B in April 2025.</t>
+          <t>Filed Form ADV Part 2A/2B brochures in the 2024 filing cycle (Feb 2024); a partner (Beal) serves on the board of Breckinridge Capital Advisors. Firm moved offices to 20 Custom House St.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2022-09-05 (Michigan/Athena expansion press release); 2025-04 (Form ADV update)</t>
+          <t>2024-02-01 (ADV Part 2B brochure)</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1907,19 +1911,19 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Uses the 'family office' label but is a multi-client wealth-management RIA, not a single family's office. Possible name confusion with 'Arrowroot Capital Management' (a separate B2B enterprise-software private-equity firm) -- they are distinct; relationship not established here. No individual email published; RocketReach/broker data deliberately not used. Firm's most recent 13F filer registration is recent (CIK 0002017744).</t>
+          <t>Despite the 'family office' name, this is functionally a multi-family-office RIA / private wealth manager serving hundreds of client accounts, not a single family's office. Investment authority is distributed among ~8 managing directors, so Beal is one of several senior decision-makers (though the 13F signatory and co-founder). No official company LinkedIn URL confirmed. No individual email is published (the ZoomInfo masked pattern was deliberately not used).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEC13F-0001950506</t>
+          <t>SEC13F-0002017744</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fortitude Family Office, LLC</t>
+          <t>Arrowroot Family Office, LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1927,49 +1931,45 @@
           <t>MFO</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>None (owner-operated MFO founded and led by Matt Walker). Not tied to a single client family.</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://fortitudefo.com/</t>
+          <t>https://arrowrootfamilyoffice.com/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/fortitude-family-office</t>
+          <t>https://www.linkedin.com/company/arrowroot-family-office</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ-based multi-family office and SEC-registered investment adviser founded and led by Matt Walker (CPA, CGMA). Provides coordinated investment/wealth management, portfolio strategy, tax planning and compliance, private deal structuring, family governance, municipal-bond and ranch/agriculture services to HNW/UHNW families, founders and executives. ~$1B AUM (~$2B AUA claimed).</t>
+          <t>Arrowroot Family Office, LLC is a Marina del Rey, CA-based registered investment adviser and multi-family office, originally founded in 2013 as Vitreous Partners and rebranded in 2017. It provides multidisciplinary wealth management -- investment management, retirement, tax and estate planning -- to high-net-worth individuals, entrepreneurs, families and small institutions, with offices in Southern and Northern California, Virginia and Michigan. It is a multi-client RIA, not a single family's office.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Fully-integrated 'coordinated services' model for multigenerational families and founders navigating transitions/liquidity events, blending investment strategy with tax and business operations.</t>
+          <t>Team-based, fiduciary, goals-driven wealth management emphasizing comprehensive planning and diversified investment management for affluent households and business owners; open-architecture advice.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Wealth management &amp; portfolio strategy, municipal-bond portfolio management, private deal structuring/private lending; also ranch &amp; agriculture services. Diversified, no single-sector public-equity focus.</t>
+          <t>Diversified multi-asset wealth management (public equities, funds/ETFs, fixed income, alternatives); not sector-specialized.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>~$1 billion regulatory AUM (~$2 billion assets under advisement per firm PR)</t>
+          <t>~$431M AUM as of Q2 2025 (third-party profiles); regulatory AUM per the 2025 Form ADV on the firm's site. A floor for total client assets under advisement.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>SCOTTSDALE</t>
+          <t>Marina Del Rey</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1979,17 +1979,17 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Matt Walker</t>
+          <t>Rob (Roberto Francisco) Santos</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Founder &amp; Chief Executive Officer (CPA, CGMA)</t>
+          <t>Chief Executive Officer &amp; Principal Owner</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/matt-walkercpa-cgma/</t>
+          <t>https://www.linkedin.com/in/rob-santos-afo/</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
@@ -2000,17 +2000,17 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>(602) 834-0089</t>
+          <t>310.341.4774</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>~$1B RAUM / ~$2B AUA; Matt Walker named BIG 'Executive of the Year' 2024 and InvestmentNews Excellence Awardee 2024; won 2024 WealthManagement.com award for a private-lending initiative; ~28 employees</t>
+          <t>Announced expansion of its private-wealth practice into Michigan via addition of The Athena Financial Group (offices now include Marina del Rey CA, Rochester Hills MI, Charlottesville VA, El Dorado Hills CA); filed updated Form ADV Part 2A/2B in April 2025.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2024 (executive/industry awards)</t>
+          <t>2022-09-05 (Michigan/Athena expansion press release); 2025-04 (Form ADV update)</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2020,19 +2020,19 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Firm advertises ~$2B 'assets under advisement' vs ~$1B regulatory AUM (FINTRX) — the larger figure includes non-discretionary/advised assets. Address suite number varies across pages (151 vs 100). No published individual email located.</t>
+          <t>Uses the 'family office' label but is a multi-client wealth-management RIA, not a single family's office. Possible name confusion with 'Arrowroot Capital Management' (a separate B2B enterprise-software private-equity firm) -- they are distinct; relationship not established here. No individual email published; RocketReach/broker data deliberately not used. Firm's most recent 13F filer registration is recent (CIK 0002017744).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEC13F-0001802278</t>
+          <t>SEC13F-0001950506</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stokes Family Office, LLC</t>
+          <t>Fortitude Family Office, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2042,39 +2042,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Stokes family (firm founded/owned by the Stokes family; David Stokes founder, sons Greg and Doug Stokes now managing partners). The 'family' is the owner-operators, not a single client family.</t>
+          <t>None (owner-operated MFO founded and led by Matt Walker). Not tied to a single client family.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://stokesfamilyoffice.com/</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
+          <t>https://fortitudefo.com/</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fortitude-family-office</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>New Orleans-based multi-family office and SEC-registered investment adviser, 100% owned by the Stokes family and operating in the area for 35+ years. Provides wealth management, investment advisory, tax and estate planning, and family-office services to high-net-worth individuals, families and institutions. Opened a Dallas, TX office in 2025.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
+          <t>Scottsdale, AZ-based multi-family office and SEC-registered investment adviser founded and led by Matt Walker (CPA, CGMA). Provides coordinated investment/wealth management, portfolio strategy, tax planning and compliance, private deal structuring, family governance, municipal-bond and ranch/agriculture services to HNW/UHNW families, founders and executives. ~$1B AUM (~$2B AUA claimed).</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Fully-integrated 'coordinated services' model for multigenerational families and founders navigating transitions/liquidity events, blending investment strategy with tax and business operations.</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Discretionary client portfolio management primarily allocating among mutual funds, ETFs and ETNs; no single-sector focus disclosed.</t>
+          <t>Wealth management &amp; portfolio strategy, municipal-bond portfolio management, private deal structuring/private lending; also ranch &amp; agriculture services. Diversified, no single-sector public-equity focus.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>~$3.35 billion (as of 2025-12-31); reported ~$3.4B by FINTRX</t>
+          <t>~$1 billion regulatory AUM (~$2 billion assets under advisement per firm PR)</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>NEW ORLEANS</t>
+          <t>SCOTTSDALE</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2084,17 +2092,17 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Douglas Stokes</t>
+          <t>Matt Walker</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Managing Partner (CFA); leads investment research and the investment committee</t>
+          <t>Founder &amp; Chief Executive Officer (CPA, CGMA)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/doug-stokes-03716932/</t>
+          <t>https://www.linkedin.com/in/matt-walkercpa-cgma/</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -2105,17 +2113,17 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>(504) 399-4100</t>
+          <t>(602) 834-0089</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Exceeded $3B AUM; named to Forbes/SHOOK 'Top RIA' list; opened Dallas, TX office (Resolute Tower at Old Parkland)</t>
+          <t>~$1B RAUM / ~$2B AUA; Matt Walker named BIG 'Executive of the Year' 2024 and InvestmentNews Excellence Awardee 2024; won 2024 WealthManagement.com award for a private-lending initiative; ~28 employees</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2023 (Forbes/SHOOK Top RIA PR); 2025-2026 (Dallas office opening); AUM ~$3.35B as of 2025-12-31</t>
+          <t>2024 (executive/industry awards)</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2125,19 +2133,19 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>'Family owned' refers to the Stokes family owning the firm, not to serving a single client family; it is a multi-client advisory MFO. Doug and Greg Stokes are co-managing partners/co-owners; Doug (CFA) chosen as principal on investment-lead basis. No individual email published. Founded/started SEC registration in 2019 though the family practice dates to the 1980s.</t>
+          <t>Firm advertises ~$2B 'assets under advisement' vs ~$1B regulatory AUM (FINTRX) — the larger figure includes non-discretionary/advised assets. Address suite number varies across pages (151 vs 100). No published individual email located.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEC13F-0002056106</t>
+          <t>SEC13F-0001802278</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stenger Family Office, LLC</t>
+          <t>Stokes Family Office, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2147,47 +2155,39 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Stenger family (firm founded/led by Nick Stenger; the family has advised clients since 1981). The 'family' is the owner-operator, not a single client family.</t>
+          <t>Stokes family (firm founded/owned by the Stokes family; David Stokes founder, sons Greg and Doug Stokes now managing partners). The 'family' is the owner-operators, not a single client family.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.stengerfamilyoffice.com/</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/stenger-family-office</t>
-        </is>
-      </c>
+          <t>https://stokesfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Naperville, IL-based multi-family office / independent fiduciary RIA led by founder-CEO Nick Stenger, offering financial planning, investment management, and (via related companies) tax preparation, estate strategies and insurance. Also has a Spring, TX office. ~$731M AUM; named a Forbes Best-in-State Wealth Advisor 2026.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Goals-based planning: assesses cash needs and upcoming goals, then builds customized portfolios.</t>
-        </is>
-      </c>
+          <t>New Orleans-based multi-family office and SEC-registered investment adviser, 100% owned by the Stokes family and operating in the area for 35+ years. Provides wealth management, investment advisory, tax and estate planning, and family-office services to high-net-worth individuals, families and institutions. Opened a Dallas, TX office in 2025.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Core individual-stock portfolios and ETF-based asset-allocation portfolios; no single-sector focus.</t>
+          <t>Discretionary client portfolio management primarily allocating among mutual funds, ETFs and ETNs; no single-sector focus disclosed.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>~$731 million (as of 2026-06-30)</t>
+          <t>~$3.35 billion (as of 2025-12-31); reported ~$3.4B by FINTRX</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>NAPERVILLE</t>
+          <t>NEW ORLEANS</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>LA</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2197,15 +2197,19 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Nicholas David Stenger</t>
+          <t>Douglas Stokes</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Founder &amp; Chief Executive Officer</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
+          <t>Managing Partner (CFA); leads investment research and the investment committee</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/doug-stokes-03716932/</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
@@ -2214,17 +2218,17 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>630-912-8295</t>
+          <t>(504) 399-4100</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>$731M AUM (2026-06-30); Forbes Best-in-State Wealth Advisor 2026; hosts 'The Nick Stenger Show' podcast; opened Spring, TX office</t>
+          <t>Exceeded $3B AUM; named to Forbes/SHOOK 'Top RIA' list; opened Dallas, TX office (Resolute Tower at Old Parkland)</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2026-06-30 (AUM date); 2026 (Forbes Best-in-State)</t>
+          <t>2023 (Forbes/SHOOK Top RIA PR); 2025-2026 (Dallas office opening); AUM ~$3.35B as of 2025-12-31</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2234,7 +2238,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Serves 1,200+ families 'of all net worth sizes' — a broad wealth-management RIA using family-office branding rather than a classic UHNW MFO; hence proof strength 'corroborated'. Personal LinkedIn /in profile not located (only company page and a Calendly slug for 'nicholasstenger'). No published individual email or direct phone line found.</t>
+          <t>'Family owned' refers to the Stokes family owning the firm, not to serving a single client family; it is a multi-client advisory MFO. Doug and Greg Stokes are co-managing partners/co-owners; Doug (CFA) chosen as principal on investment-lead basis. No individual email published. Founded/started SEC registration in 2019 though the family practice dates to the 1980s.</t>
         </is>
       </c>
     </row>
@@ -3807,12 +3811,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEC13F-0001731123</t>
+          <t>SEC13F-0002056106</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Biltmore Family Office, LLC</t>
+          <t>Stenger Family Office, LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3822,71 +3826,79 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001731123); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0002056106); discovered via fts</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001731123&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002056106&amp;type=13F</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Independent SEC-registered adviser to investment-oriented multi-generational families plus institutional clients; ~951 accounts and ~$3.2-3.5B AUM (avg client ~$38M). A collaborative multi-family office, not a single-family vehicle. Sources: https://www.biltmorefamilyoffice.com/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
+          <t>Self-described 'multi-family office'; the Stenger family has served 'over 1,200 families across the United States'. Serves many outside client families. Sources: https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (13F filer) founded 2008 (LLC organized 2013); positions itself as a hybrid family office and RIA. Sources: https://www.biltmorefamilyoffice.com/our-history/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
+          <t xml:space="preserve">SEC-registered investment adviser (13F filer); independent fiduciary wealth-management firm offering financial planning, investment management, tax and estate strategies under a family-office model; ~$731M AUM. Sources: https://www.stengerfamilyoffice.com/ </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>corroborated</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>AUM/ADV aggregators. https://fintrx.com/firms/firm/biltmore-family-office-llc-167174 ; https://advisor.guide/firms/biltmore-family-office ; https://whalewisdom.com/filer/biltmore-family-office-llc</t>
+          <t>Firm-stated. https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Founder and President/CEO; 30 years' experience in investment management, asset allocation and investment-policy creation; prior Partner at GenSpring Family Offices, President at JPMorgan Private Bank, Managing Director at Brown Brothers Harriman. The firm's top decision-maker (Rael Gorelick is Partner &amp; Head of Investments / CIO-equivalent). https://www.biltmorefamilyoffice.com/who-we-are/chris-cecil/ ; https://www.linkedin.com/in/chris-cecil-9701b818/</t>
+          <t>Founder and CEO / lead financial advisor; prior Senior Vice President financial advisor at Morgan Stanley Wealth Management, and roles at Invesco PowerShares and PwC; the firm's decision-maker and namesake. https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://www.stengerfamilyoffice.com (published mailto/contact page)</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>No individual email published on the firm site (biltmorefamilyoffice.com pages returned 403 during research; no person@ address found in accessible pages). RocketReach/ContactOut/Datanyze show only masked/pattern (first@biltmorefamilyoffice.com) broker data — excluded; not pattern-generated.</t>
+          <t>Address published on the firm's own site with local-part matching the named principal (Nicholas David Stenger).</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Firm main line (6836 Morrison Blvd Suite 100, Charlotte); firm switchboard, not a personal line. https://www.biltmorefamilyoffice.com/</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>https://www.biltmorefamilyoffice.com/our-history/ ; https://businessnc.com/chris-cecil/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
+          <t>https://www.stengerfamilyoffice.com/ ; https://www.stengerfamilyoffice.com/financialadvisornaperville ; https://podcasts.apple.com/us/podcast/the-nick-stenger-show/id1678810370</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEC13F-0001039807</t>
+          <t>SEC13F-0001731123</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Boston Family Office LLC</t>
+          <t>Biltmore Family Office, LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3896,22 +3908,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001039807); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001731123); discovered via fts</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001039807&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001731123&amp;type=13F</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (CRD #107141) serving many clients -- ~789 accounts across high-net-worth individuals, retail investors and charitable organizations; ~$1.7-2.0B AUM; 15 partners. This is a multi-family office / wealth-management RIA, not a single family's office. Source: https://adviserinfo.sec.gov/firm/summary/107141 and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
+          <t>Independent SEC-registered adviser to investment-oriented multi-generational families plus institutional clients; ~951 accounts and ~$3.2-3.5B AUM (avg client ~$38M). A collaborative multi-family office, not a single-family vehicle. Sources: https://www.biltmorefamilyoffice.com/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Operates as an RIA branded as a family office ('The Boston Family Office'), founded 1996; files 13F under CIK 0001039807. Source: https://www.bosfam.com/george-beal/</t>
+          <t>SEC-registered investment adviser (13F filer) founded 2008 (LLC organized 2013); positions itself as a hybrid family office and RIA. Sources: https://www.biltmorefamilyoffice.com/our-history/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3921,12 +3933,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/107141 (Form ADV, 2024-2025) and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
+          <t>AUM/ADV aggregators. https://fintrx.com/firms/firm/biltmore-family-office-llc-167174 ; https://advisor.guide/firms/biltmore-family-office ; https://whalewisdom.com/filer/biltmore-family-office-llc</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Beal co-founded the firm in 1996, is a Managing Partner and portfolio manager, and is the named 13F signatory -- an active, current investment decision-maker. Note the firm has 15 partners / ~8 active managing directors, so investment authority is shared. Source: https://www.bosfam.com/george-beal/</t>
+          <t>Founder and President/CEO; 30 years' experience in investment management, asset allocation and investment-policy creation; prior Partner at GenSpring Family Offices, President at JPMorgan Private Bank, Managing Director at Brown Brothers Harriman. The firm's top decision-maker (Rael Gorelick is Partner &amp; Head of Investments / CIO-equivalent). https://www.biltmorefamilyoffice.com/who-we-are/chris-cecil/ ; https://www.linkedin.com/in/chris-cecil-9701b818/</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3937,17 +3949,17 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Tried: fetched bosfam.com homepage and bosfam.com/george-beal/ team page -- only phone (617-624-0800) is published, no email. A ZoomInfo listing shows a masked pattern 'g***@bosfam.com' but that is a data-broker inference, NOT a published/attested individual address, so it is excluded. Did not construct an address.</t>
+          <t>No individual email published on the firm site (biltmorefamilyoffice.com pages returned 403 during research; no person@ address found in accessible pages). RocketReach/ContactOut/Datanyze show only masked/pattern (first@biltmorefamilyoffice.com) broker data — excluded; not pattern-generated.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
+          <t>Firm main line (6836 Morrison Blvd Suite 100, Charlotte); firm switchboard, not a personal line. https://www.biltmorefamilyoffice.com/</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>https://www.bosfam.com/wp-content/uploads/2024/02/2024-ADV-Part-2B-Brochure-Supplement_FINAL.pdf ; https://adviserinfo.sec.gov/firm/summary/107141</t>
+          <t>https://www.biltmorefamilyoffice.com/our-history/ ; https://businessnc.com/chris-cecil/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
@@ -3955,12 +3967,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEC13F-0002017744</t>
+          <t>SEC13F-0001039807</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC</t>
+          <t>Boston Family Office LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3970,22 +3982,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0002017744); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001039807); discovered via fts</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002017744&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001039807&amp;type=13F</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>A registered investment adviser and multi-family office that markets 'Multi Family Office Services' and serves many clients -- high-net-worth individuals, entrepreneurs, families and family offices -- with ~20 staff across multiple US offices. Source: https://arrowrootfamilyoffice.com/team/ and https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
+          <t>SEC-registered investment adviser (CRD #107141) serving many clients -- ~789 accounts across high-net-worth individuals, retail investors and charitable organizations; ~$1.7-2.0B AUM; 15 partners. This is a multi-family office / wealth-management RIA, not a single family's office. Source: https://adviserinfo.sec.gov/firm/summary/107141 and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SEC-registered RIA (Form ADV on file, SEC# 801-121878) branded 'Arrowroot Family Office'; files 13F under CIK 0002017744; multiple offices and a published team. Source: https://9at.com/Adviser/801-121878</t>
+          <t>Operates as an RIA branded as a family office ('The Boston Family Office'), founded 1996; files 13F under CIK 0001039807. Source: https://www.bosfam.com/george-beal/</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -3995,12 +4007,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://fintrx.com/firms/firm/arrowroot-family-office-llc-168744 (~$431M, Q2 2025); Form ADV: https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf (2025)</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/107141 (Form ADV, 2024-2025) and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Santos is CEO and principal owner, leading the firm; he is the 13F signatory (Roberto Santos = Rob Santos) and a current decision-maker with 20+ years' experience. Source: https://arrowrootfamilyoffice.com/team/ and https://www.getwarmer.com/advisors/roberto-francisco-santos</t>
+          <t>Beal co-founded the firm in 1996, is a Managing Partner and portfolio manager, and is the named 13F signatory -- an active, current investment decision-maker. Note the firm has 15 partners / ~8 active managing directors, so investment authority is shared. Source: https://www.bosfam.com/george-beal/</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4011,17 +4023,17 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Tried: fetched the firm's team page (no email published, only phone 833-224-2249 and a contact form); searched for a published individual email; only data-broker (RocketReach) listings exist, which are not published/attested. Did not construct an address.</t>
+          <t>Tried: fetched bosfam.com homepage and bosfam.com/george-beal/ team page -- only phone (617-624-0800) is published, no email. A ZoomInfo listing shows a masked pattern 'g***@bosfam.com' but that is a data-broker inference, NOT a published/attested individual address, so it is excluded. Did not construct an address.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>https://www.arrowrootfamilyoffice.com/press-releases/arrowroot-family-office-in-michigan/ ; https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
+          <t>https://www.bosfam.com/wp-content/uploads/2024/02/2024-ADV-Part-2B-Brochure-Supplement_FINAL.pdf ; https://adviserinfo.sec.gov/firm/summary/107141</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -4029,12 +4041,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEC13F-0001950506</t>
+          <t>SEC13F-0002017744</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fortitude Family Office, LLC</t>
+          <t>Arrowroot Family Office, LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4044,22 +4056,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001950506); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0002017744); discovered via fts</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001950506&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002017744&amp;type=13F</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Team page/site confirm it operates as a multi-family office serving 'high and ultra-high net worth families' with coordinated services; ~$1B regulatory AUM. Sources: https://fortitudefo.com/team/ ; https://fortitudefo.com/whoweserve/ ; https://fintrx.com/firms/firm/fortitude-family-office-317615</t>
+          <t>A registered investment adviser and multi-family office that markets 'Multi Family Office Services' and serves many clients -- high-net-worth individuals, entrepreneurs, families and family offices -- with ~20 staff across multiple US offices. Source: https://arrowrootfamilyoffice.com/team/ and https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (13F filer); fully-integrated advisory team providing investment/wealth management, tax, accounting, philanthropy and business-operations services to HNW/UHNW families; ~$1B AUM (~$2B assets under advisement claimed). Sources: https://fortitudefo.com/ ; https://www.prnewswire.com/news-releases/fortitude-family-office-founder-and-ceo-matt-walker-named-executive-of-the-year-by-business-intelligence-group-302117711.html</t>
+          <t>SEC-registered RIA (Form ADV on file, SEC# 801-121878) branded 'Arrowroot Family Office'; files 13F under CIK 0002017744; multiple offices and a published team. Source: https://9at.com/Adviser/801-121878</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4069,12 +4081,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>FINTRX (RAUM) and firm PR (AUA). https://fintrx.com/firms/firm/fortitude-family-office-317615 ; https://www.prnewswire.com/news-releases/fortitude-family-office-wins-2024-wealthmanagementcom-industry-award-for-private-lending-initiative-302253789.html</t>
+          <t>https://fintrx.com/firms/firm/arrowroot-family-office-llc-168744 (~$431M, Q2 2025); Form ADV: https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf (2025)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Founder and CEO; named InvestmentNews 2024 Excellence Awardee and Business Intelligence Group 'Executive of the Year' 2024; leads the integrated advisory team. https://fortitudefo.com/team/ ; https://www.linkedin.com/in/matt-walkercpa-cgma/</t>
+          <t>Santos is CEO and principal owner, leading the firm; he is the 13F signatory (Roberto Santos = Rob Santos) and a current decision-maker with 20+ years' experience. Source: https://arrowrootfamilyoffice.com/team/ and https://www.getwarmer.com/advisors/roberto-francisco-santos</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4085,17 +4097,17 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>No individual email published on the firm site; contact page shows only a Cloudflare-obfuscated generic mailbox and phone (602) 834-0089. No broker emails accepted.</t>
+          <t>Tried: fetched the firm's team page (no email published, only phone 833-224-2249 and a contact form); searched for a published individual email; only data-broker (RocketReach) listings exist, which are not published/attested. Did not construct an address.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://fortitudefo.com/contact/ (firm main line, 7500 N Dobson Rd Suite 151, Scottsdale; not a personal line)</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/fortitude-family-office-founder-and-ceo-matt-walker-named-executive-of-the-year-by-business-intelligence-group-302117711.html ; https://www.prnewswire.com/news-releases/matt-walker-fortitude-family-office-founder-and-ceo-honored-as-investmentnews-excellence-awardee-302175687.html ; https://www.prnewswire.com/news-releases/fortitude-family-office-wins-2024-wealthmanagementcom-industry-award-for-private-lending-initiative-302253789.html</t>
+          <t>https://www.arrowrootfamilyoffice.com/press-releases/arrowroot-family-office-in-michigan/ ; https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -4103,12 +4115,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEC13F-0001802278</t>
+          <t>SEC13F-0001950506</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stokes Family Office, LLC</t>
+          <t>Fortitude Family Office, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4118,22 +4130,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001802278); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001950506); discovered via fts</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001802278&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001950506&amp;type=13F</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Firm is '100% Family Owned' (owned by the Stokes family) but serves outside clients: 'individuals, families and institutions' with a billion-dollar advisory practice. Broad multi-client RIA, not a single-family vehicle. Sources: https://stokesfamilyoffice.com/about-us/ ; https://fintrx.com/firms/firm/stokes-family-office-llc-300899</t>
+          <t>Team page/site confirm it operates as a multi-family office serving 'high and ultra-high net worth families' with coordinated services; ~$1B regulatory AUM. Sources: https://fortitudefo.com/team/ ; https://fortitudefo.com/whoweserve/ ; https://fintrx.com/firms/firm/fortitude-family-office-317615</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (13F filer) branded 'family office'; offers wealth management, retirement plan consulting and family-office services; ~$3.35B AUM. Sources: https://stokesfamilyoffice.com/about-us/ ; https://stokesfamilyoffice.com/insights/stokes-family-office-exceeds3b-aum/</t>
+          <t>SEC-registered investment adviser (13F filer); fully-integrated advisory team providing investment/wealth management, tax, accounting, philanthropy and business-operations services to HNW/UHNW families; ~$1B AUM (~$2B assets under advisement claimed). Sources: https://fortitudefo.com/ ; https://www.prnewswire.com/news-releases/fortitude-family-office-founder-and-ceo-matt-walker-named-executive-of-the-year-by-business-intelligence-group-302117711.html</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -4143,12 +4155,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Firm press/AUM aggregators. https://stokesfamilyoffice.com/insights/stokes-family-office-exceeds3b-aum/ ; https://fintrx.com/firms/firm/stokes-family-office-llc-300899 ; https://aum13f.com/firm/stokes-family-office-llc</t>
+          <t>FINTRX (RAUM) and firm PR (AUA). https://fintrx.com/firms/firm/fortitude-family-office-317615 ; https://www.prnewswire.com/news-releases/fortitude-family-office-wins-2024-wealthmanagementcom-industry-award-for-private-lending-initiative-302253789.html</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Doug Stokes, CFA, is co-owner and Managing Partner who 'takes an active role in the firm's investment research process and investment committee decisions' — the investment decision-maker (co-managing partner Gregory Stokes, JD, runs business/innovation; founder David Stokes is Founder Emeritus). https://stokesfamilyoffice.com/about-us/ ; https://www.linkedin.com/in/doug-stokes-03716932/</t>
+          <t>Founder and CEO; named InvestmentNews 2024 Excellence Awardee and Business Intelligence Group 'Executive of the Year' 2024; leads the integrated advisory team. https://fortitudefo.com/team/ ; https://www.linkedin.com/in/matt-walkercpa-cgma/</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4159,17 +4171,17 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Only a generic mailbox published (info@stokesfamilyoffice.com on https://stokesfamilyoffice.com/contact-us/); no individual email on any firm bio/contact page. ZoomInfo/RocketReach/ContactOut listings (e.g., doug@... , dougstokes4@gmail.com) are broker-sourced/masked and excluded per rules.</t>
+          <t>No individual email published on the firm site; contact page shows only a Cloudflare-obfuscated generic mailbox and phone (602) 834-0089. No broker emails accepted.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://stokesfamilyoffice.com/contact-us/ (New Orleans office switchboard, 1100 Poydras St Suite 2775; not a personal line)</t>
+          <t>https://fortitudefo.com/contact/ (firm main line, 7500 N Dobson Rd Suite 151, Scottsdale; not a personal line)</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/stokes-family-office-named-to-top-ria-list-by-forbesshook-research-301958395.html ; https://stokesfamilyoffice.com/contact-us/ ; https://stokesfamilyoffice.com/insights/stokes-family-office-exceeds3b-aum/</t>
+          <t>https://www.prnewswire.com/news-releases/fortitude-family-office-founder-and-ceo-matt-walker-named-executive-of-the-year-by-business-intelligence-group-302117711.html ; https://www.prnewswire.com/news-releases/matt-walker-fortitude-family-office-founder-and-ceo-honored-as-investmentnews-excellence-awardee-302175687.html ; https://www.prnewswire.com/news-releases/fortitude-family-office-wins-2024-wealthmanagementcom-industry-award-for-private-lending-initiative-302253789.html</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -4177,12 +4189,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEC13F-0002056106</t>
+          <t>SEC13F-0001802278</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stenger Family Office, LLC</t>
+          <t>Stokes Family Office, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4192,58 +4204,58 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0002056106); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001802278); discovered via fts</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002056106&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001802278&amp;type=13F</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Self-described 'multi-family office'; the Stenger family has served 'over 1,200 families across the United States'. Serves many outside client families. Sources: https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
+          <t>Firm is '100% Family Owned' (owned by the Stokes family) but serves outside clients: 'individuals, families and institutions' with a billion-dollar advisory practice. Broad multi-client RIA, not a single-family vehicle. Sources: https://stokesfamilyoffice.com/about-us/ ; https://fintrx.com/firms/firm/stokes-family-office-llc-300899</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEC-registered investment adviser (13F filer); independent fiduciary wealth-management firm offering financial planning, investment management, tax and estate strategies under a family-office model; ~$731M AUM. Sources: https://www.stengerfamilyoffice.com/ </t>
+          <t>SEC-registered investment adviser (13F filer) branded 'family office'; offers wealth management, retirement plan consulting and family-office services; ~$3.35B AUM. Sources: https://stokesfamilyoffice.com/about-us/ ; https://stokesfamilyoffice.com/insights/stokes-family-office-exceeds3b-aum/</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>corroborated</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Firm-stated. https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
+          <t>Firm press/AUM aggregators. https://stokesfamilyoffice.com/insights/stokes-family-office-exceeds3b-aum/ ; https://fintrx.com/firms/firm/stokes-family-office-llc-300899 ; https://aum13f.com/firm/stokes-family-office-llc</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Founder and CEO / lead financial advisor; prior Senior Vice President financial advisor at Morgan Stanley Wealth Management, and roles at Invesco PowerShares and PwC; the firm's decision-maker and namesake. https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
+          <t>Doug Stokes, CFA, is co-owner and Managing Partner who 'takes an active role in the firm's investment research process and investment committee decisions' — the investment decision-maker (co-managing partner Gregory Stokes, JD, runs business/innovation; founder David Stokes is Founder Emeritus). https://stokesfamilyoffice.com/about-us/ ; https://www.linkedin.com/in/doug-stokes-03716932/</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>No individual email published on the firm site; contact is via a Calendly link (calendly.com/nicholasstenger/intro-meeting) rather than a published email address. No broker emails accepted.</t>
+          <t>Only a generic mailbox published (info@stokesfamilyoffice.com on https://stokesfamilyoffice.com/contact-us/); no individual email on any firm bio/contact page. ZoomInfo/RocketReach/ContactOut listings (e.g., doug@... , dougstokes4@gmail.com) are broker-sourced/masked and excluded per rules.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
+          <t>https://stokesfamilyoffice.com/contact-us/ (New Orleans office switchboard, 1100 Poydras St Suite 2775; not a personal line)</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>https://www.stengerfamilyoffice.com/ ; https://www.stengerfamilyoffice.com/financialadvisornaperville ; https://podcasts.apple.com/us/podcast/the-nick-stenger-show/id1678810370</t>
+          <t>https://www.prnewswire.com/news-releases/stokes-family-office-named-to-top-ria-list-by-forbesshook-research-301958395.html ; https://stokesfamilyoffice.com/contact-us/ ; https://stokesfamilyoffice.com/insights/stokes-family-office-exceeds3b-aum/</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -4767,7 +4779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7511,18 +7523,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Timonier Family Office, LTD.</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>firm-qualification</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
+          <t>principal_email</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>laura@tarbox.com</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>email not found at cited source on re-fetch (https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf); downgraded verified-&gt;unverified</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7550,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>TrustBank</t>
+          <t>Timonier Family Office, LTD.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -7568,7 +7584,7 @@
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7596,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>UNITA FAMILY OFFICE UK LIMITED</t>
+          <t>TrustBank</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -7591,7 +7607,7 @@
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -7603,7 +7619,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>UR FAMILY OFFICE MANAGEMENT SERVICES LTD</t>
+          <t>UNITA FAMILY OFFICE UK LIMITED</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7626,7 +7642,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>VASIL FAMILY OFFICE LLP</t>
+          <t>UR FAMILY OFFICE MANAGEMENT SERVICES LTD</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7649,7 +7665,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>VPR Management LLC</t>
+          <t>VASIL FAMILY OFFICE LLP</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7683,7 +7699,7 @@
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -7695,7 +7711,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>VSTAR LONDON FAMILY OFFICE LTD</t>
+          <t>VPR Management LLC</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -7706,7 +7722,7 @@
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -7718,7 +7734,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Veritable, L.P.</t>
+          <t>VSTAR LONDON FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7752,7 +7768,7 @@
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -7764,7 +7780,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Virtus Family Office LLC</t>
+          <t>Veritable, L.P.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -7775,7 +7791,7 @@
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -7787,7 +7803,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>WEYBRIDGE FAMILY OFFICE SERVICES LIMITED</t>
+          <t>Virtus Family Office LLC</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7810,7 +7826,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Wealthgate Family Office, LLC</t>
+          <t>WEYBRIDGE FAMILY OFFICE SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7833,7 +7849,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Wilmington Savings Fund Society, FSB</t>
+          <t>Wealthgate Family Office, LLC</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7866,6 +7882,29 @@
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Wilmington Savings Fund Society, FSB</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
         <is>
           <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>

--- a/data/final/family_office_dataset.xlsx
+++ b/data/final/family_office_dataset.xlsx
@@ -429,11 +429,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W25"/>
+  <dimension ref="A1:W36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="59" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="39" customWidth="1" min="5" max="5"/>
@@ -443,7 +443,7 @@
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
     <col width="26" customWidth="1" min="13" max="13"/>
     <col width="32" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
@@ -686,12 +686,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEC13F-0001802084</t>
+          <t>SEC13F-0001938970</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVA Family Office, LLC</t>
+          <t>Callan Family Office, LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -699,45 +699,45 @@
           <t>MFO</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>None (owner-operated MFO; part of the Class VI Partners group co-founded by Chris Younger and David Tolson). Not tied to a single client family.</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://classvifamilyoffice.com/</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>https://callanfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/callan-family-office</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Denver-based multi-family office and SEC-registered investment adviser, formerly 'CVA Family Office, LLC' and now operating as 'Class VI Family Office, LLC', part of the Class VI Partners group. Advises entrepreneurs, business owners and executives on wealth planning, liquidity-event planning and investment management on a 1:1 client:advisor model.</t>
+          <t>Callan Family Office is a Radnor, PA-based multi-family office founded in February 2022 by former Abbot Downing / Wells Fargo ultra-high-net-worth executives, using a brand-licensing partnership with institutional-consulting firm Callan LLC. It serves multiple ultra-wealthy families (minimum ~$50M, average ~$100M) and grew past $5B in assets within two years. It operates on a partnership model providing investment management and integrated family-office services.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Serving entrepreneurs and business owners around liquidity events; integrated wealth planning + discretionary investment management aligned to each family's goals.</t>
+          <t>Institutional-quality, goals-based investment management for UHNW families, leveraging the Callan LLC investment-consulting relationship for manager research/asset allocation; open-architecture, partnership-driven advice.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Diversified discretionary wealth/investment management for HNW entrepreneurs; no single-sector focus disclosed.</t>
+          <t>Diversified multi-asset-class portfolios (public and private markets, alternatives) tailored to UHNW families; not sector-specialized.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>~$222.27 million regulatory AUM (across ~43 accounts)</t>
+          <t>~$5B AUM as of March 2024 (reported crossing $5B two years after 2022 founding).</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>DENVER</t>
+          <t>Radnor</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -747,22 +747,22 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Matt Blackburn</t>
+          <t>Jack Ginter (John Ginter)</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Managing Partner / Managing Director, Class VI Family Office (co-founder)</t>
+          <t>Chief Executive Officer &amp; Founding Partner</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/mattblackburnclassvi/</t>
+          <t>https://www.linkedin.com/in/jack-ginter-70276773/</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>matt@classvipartners.com</t>
+          <t>jginter@callanfo.com</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>303-243-5619</t>
+          <t>267-250-2036</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Rebranded from 'CVA Family Office' to 'Class VI Family Office'; established as RIA Sept 2016; operates on a 1:1 client:advisor model under Class VI Partners</t>
+          <t>Reported crossing $5B AUM in March 2024, ~2 years after a Feb 2022 launch; built via a Callan LLC brand-licensing/partnership deal and Abbot Downing/Wells Fargo advisor recruitment; featured in RIABiz and a Diamond Consultants podcast.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2016-09 (RIA inception); rebrand to Class VI Family Office (ongoing)</t>
+          <t>2022-02 (founding); 2024-03 (crossed $5B AUM); 2024-04-09 (RIABiz feature)</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -792,65 +792,41 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Legal 13F filer name remains 'CVA Family Office, LLC' but the brand/website is now 'Class VI Family Office' (classvifamilyoffice.com); older cvafamilyoffice.com domain was unreachable during research. Principal email is on the classvipartners.com domain, not a family-office-specific domain. Chris Younger is CEO of the broader Class VI Partners; Matt Blackburn selected as the family-office investment/advisory lead.</t>
+          <t>Uses the 'family office' label but is structurally an UHNW multi-family-office RIA with a client base, not a single family's office. 'John Ginter' (13F signatory) and 'Jack Ginter' (CEO) are the same person. AUM figure is a March 2024 press number and may be higher now.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEC13F-0001938970</t>
+          <t>SEC13F-0001596197</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Callan Family Office, LLC</t>
+          <t>Intrepid Family Office Llc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://callanfamilyoffice.com/</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/callan-family-office</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Callan Family Office is a Radnor, PA-based multi-family office founded in February 2022 by former Abbot Downing / Wells Fargo ultra-high-net-worth executives, using a brand-licensing partnership with institutional-consulting firm Callan LLC. It serves multiple ultra-wealthy families (minimum ~$50M, average ~$100M) and grew past $5B in assets within two years. It operates on a partnership model providing investment management and integrated family-office services.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Institutional-quality, goals-based investment management for UHNW families, leveraging the Callan LLC investment-consulting relationship for manager research/asset allocation; open-architecture, partnership-driven advice.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Diversified multi-asset-class portfolios (public and private markets, alternatives) tailored to UHNW families; not sector-specialized.</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>~$5B AUM as of March 2024 (reported crossing $5B two years after 2022 founding).</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Radnor</t>
+          <t>Greenwich</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -860,64 +836,56 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Jack Ginter (John Ginter)</t>
+          <t>Matt Dino</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Chief Executive Officer &amp; Founding Partner</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/jack-ginter-70276773/</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>jginter@callanfo.com</t>
-        </is>
-      </c>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>267-250-2036</t>
+          <t>(203) 862-3372</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Reported crossing $5B AUM in March 2024, ~2 years after a Feb 2022 launch; built via a Callan LLC brand-licensing/partnership deal and Abbot Downing/Wells Fargo advisor recruitment; featured in RIABiz and a Diamond Consultants podcast.</t>
+          <t>13F portfolio approx $0.12B across 38 US-listed positions as of 03-31-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing). Top holdings: SPDR GOLD TR ($17.21B); ISHARES TR ($13.57B); VANGUARD INDEX FDS ($12.83B); ABRDN PLATINUM ETF TRUST ($7.13B)</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2022-02 (founding); 2024-03 (crossed $5B AUM); 2024-04-09 (RIABiz feature)</t>
+          <t>03-31-2026</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Uses the 'family office' label but is structurally an UHNW multi-family-office RIA with a client base, not a single family's office. 'John Ginter' (13F signatory) and 'Jack Ginter' (CEO) are the same person. AUM figure is a March 2024 press number and may be higher now.</t>
+          <t>SFO inferred from unregistered-adviser + 13F + family-office name; the specific family is not yet named (pending research pass).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEC13F-0001596197</t>
+          <t>SEC13F-0001536411</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Intrepid Family Office Llc</t>
+          <t>Duquesne Family Office LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -925,21 +893,45 @@
           <t>SFO</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Druckenmiller family (Stanley F. Druckenmiller)</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/duquesne-family-office-llc</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Duquesne Family Office is the private investment vehicle of billionaire investor Stanley Druckenmiller, established in 2010 after he returned outside capital and wound down his hedge fund Duquesne Capital Management (named for a park in his native Pittsburgh). It manages the Druckenmiller family's capital across public equities, and reportedly private/venture and credit positions, using a concentrated, macro-driven approach. It has no external clients.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Concentrated, top-down macro investing with high conviction and significant position turnover; opportunistic rotation across sectors and asset classes based on macroeconomic views. Public-equity book is typically 20-40 concentrated positions.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Broad/opportunistic across technology, healthcare/biotech, energy, consumer, financials and industrials; recent 13Fs (2025) show large positions in names like Natera, Insmed, Amazon, Teva and Woodward.</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>13F US-listed equities ~$4.06B as of 2025-09-30 (Q3 2025) and ~$4.49B as of Q4 2025 -- a FLOOR, not total AUM. Total family-office AUM is not publicly disclosed; Druckenmiller's personal net worth is estimated at ~$11B (Bloomberg Billionaires Index, Jan 2025) and he ranks on the Forbes 2026 Billionaires list.</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Greenwich</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -949,12 +941,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Matt Dino</t>
+          <t>Stanley F. Druckenmiller</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
+          <t>Founder, Chairman &amp; CEO (Portfolio Manager)</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -966,17 +958,17 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>(203) 862-3372</t>
+          <t>212-830-6500</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>13F portfolio approx $0.12B across 38 US-listed positions as of 03-31-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing). Top holdings: SPDR GOLD TR ($17.21B); ISHARES TR ($13.57B); VANGUARD INDEX FDS ($12.83B); ABRDN PLATINUM ETF TRUST ($7.13B)</t>
+          <t>Q3 2025 13F filed (portfolio ~$4.06B, 65 holdings); Q4 2025 13F portfolio rose to ~$4.49B with ~35 significant positions; Q1 2025 13F showed cuts and new tech/energy adds (~$3.06B, 52 holdings).</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>03-31-2026</t>
+          <t>2025-11-14 (Q3 2025 13F filing, as of 2025-09-30); Q4 2025 (as of 2025-12-31); 2025-05-15 (Q1 2025 13F, as of 2025-03-31)</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -986,19 +978,19 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>SFO inferred from unregistered-adviser + 13F + family-office name; the specific family is not yet named (pending research pass).</t>
+          <t>Total AUM is not officially disclosed; the 13F equity value is only US-listed long equity positions (a floor). The LinkedIn company page may not be firm-operated. No individual email is published anywhere; none provided. Sue Meng (13F signatory) is General Counsel, not the investment decision-maker.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEC13F-0001536411</t>
+          <t>SEC13F-0001683689</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Duquesne Family Office LLC</t>
+          <t>Kopp Family Office, LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1006,45 +998,21 @@
           <t>SFO</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Druckenmiller family (Stanley F. Druckenmiller)</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/duquesne-family-office-llc</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Duquesne Family Office is the private investment vehicle of billionaire investor Stanley Druckenmiller, established in 2010 after he returned outside capital and wound down his hedge fund Duquesne Capital Management (named for a park in his native Pittsburgh). It manages the Druckenmiller family's capital across public equities, and reportedly private/venture and credit positions, using a concentrated, macro-driven approach. It has no external clients.</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Concentrated, top-down macro investing with high conviction and significant position turnover; opportunistic rotation across sectors and asset classes based on macroeconomic views. Public-equity book is typically 20-40 concentrated positions.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>Broad/opportunistic across technology, healthcare/biotech, energy, consumer, financials and industrials; recent 13Fs (2025) show large positions in names like Natera, Insmed, Amazon, Teva and Woodward.</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>13F US-listed equities ~$4.06B as of 2025-09-30 (Q3 2025) and ~$4.49B as of Q4 2025 -- a FLOOR, not total AUM. Total family-office AUM is not publicly disclosed; Druckenmiller's personal net worth is estimated at ~$11B (Bloomberg Billionaires Index, Jan 2025) and he ranks on the Forbes 2026 Billionaires list.</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Minnetonka</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1054,12 +1022,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Stanley F. Druckenmiller</t>
+          <t>John P. Flakne</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Founder, Chairman &amp; CEO (Portfolio Manager)</t>
+          <t>Chief Financial Officer</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -1071,17 +1039,17 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>212-830-6500</t>
+          <t>952-841-0450</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>Q3 2025 13F filed (portfolio ~$4.06B, 65 holdings); Q4 2025 13F portfolio rose to ~$4.49B with ~35 significant positions; Q1 2025 13F showed cuts and new tech/energy adds (~$3.06B, 52 holdings).</t>
+          <t>13F portfolio approx $0.16B across 29 US-listed positions as of 06-30-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2025-11-14 (Q3 2025 13F filing, as of 2025-09-30); Q4 2025 (as of 2025-12-31); 2025-05-15 (Q1 2025 13F, as of 2025-03-31)</t>
+          <t>06-30-2026</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1091,19 +1059,19 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Total AUM is not officially disclosed; the 13F equity value is only US-listed long equity positions (a floor). The LinkedIn company page may not be firm-operated. No individual email is published anywhere; none provided. Sue Meng (13F signatory) is General Counsel, not the investment decision-maker.</t>
+          <t>SFO inferred from unregistered-adviser + 13F + family-office name; the specific family is not yet named (pending research pass).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEC13F-0001683689</t>
+          <t>SEC13F-0001889527</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kopp Family Office, LLC</t>
+          <t>Louis-Dreyfus Family Office LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1111,21 +1079,41 @@
           <t>SFO</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Louis-Dreyfus family -- specifically the American branch of Gerard 'William' Louis-Dreyfus (1932-2016), longtime chairman of Louis Dreyfus Company's US arm and father of actress Julia Louis-Dreyfus (INFERRED from co-location with LDC's Wilton HQ and the family/geography; not definitively documented).</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Louis-Dreyfus Family Office LLC is a small private single-family office in Wilton, CT, associated with the American branch of the Louis-Dreyfus family (the commodities-trading dynasty). It is co-located with Louis Dreyfus Company's US headquarters at 10 Westport Road and manages family capital; its SEC 13F disclosed only about five holdings worth ~$65M. It is NOT the Louis Dreyfus Company commodities business itself.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Not publicly documented. The limited 13F holdings (broad index funds VXUS/VTIAX and ITOT plus a couple of small single-name positions) suggest a conservative, largely passive/index-oriented public-markets allocation typical of a family office holding book, but this is inferred, not stated.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Public 13F book was dominated by broad-market and international index funds (Vanguard Total International, iShares Core S&amp;P Total US Market ETF) plus small individual equity positions (e.g., Celularity, New Relic, Lovesac). Not sector-focused.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>13F US-listed equities ~$64.7M as of 2022-09-30 (Q3 2022, 5 holdings) -- a floor and likely a small slice of total family wealth. Total AUM not disclosed. Business directories estimate ~$390K annual revenue / ~4 employees.</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Minnetonka</t>
+          <t>Wilton</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1135,12 +1123,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>John P. Flakne</t>
+          <t>W. Thomas Wingertzahn</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
+          <t>Chief Financial Officer (13F signatory / operational head)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1152,17 +1140,17 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>952-841-0450</t>
+          <t>203-762-6134</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>13F portfolio approx $0.16B across 29 US-listed positions as of 06-30-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing)</t>
+          <t>No recent public activity found. The most recent SEC 13F on file is Q3 2022; no 2023-2025 13F filings surfaced, which may indicate the equity book fell below the 13F reporting threshold or the office stopped filing.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>06-30-2026</t>
+          <t>2022-11-10 (last 13F filing, holdings as of 2022-09-30)</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1172,19 +1160,19 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>SFO inferred from unregistered-adviser + 13F + family-office name; the specific family is not yet named (pending research pass).</t>
+          <t>ENTITY-CONFUSION RISK: 'Louis-Dreyfus Family Office LLC' is NOT the Louis Dreyfus Company (LDC) commodities firm, though it shares the Wilton CT 10 Westport Road address. The specific family member/branch is INFERRED (Gerard 'William' Louis-Dreyfus's American branch; heirs include Julia Louis-Dreyfus and half-sisters Phoebe and Emma) and not definitively confirmed by a primary source; family_affiliation should be treated as probable, not certain. The true family investment decision-maker is undetermined; Wingertzahn is the CFO/signatory, reported as principal only for lack of a documented alternative. No website, no LinkedIn, no published email. 13F filings appear to have lapsed after 2022.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEC13F-0001889527</t>
+          <t>UKCH-12706913</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Louis-Dreyfus Family Office LLC</t>
+          <t>Francis Family Office Limited</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1194,76 +1182,68 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Louis-Dreyfus family -- specifically the American branch of Gerard 'William' Louis-Dreyfus (1932-2016), longtime chairman of Louis Dreyfus Company's US arm and father of actress Julia Louis-Dreyfus (INFERRED from co-location with LDC's Wilton HQ and the family/geography; not definitively documented).</t>
+          <t>Francis family (Ben Francis, founder/CEO of Gymshark)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Louis-Dreyfus Family Office LLC is a small private single-family office in Wilton, CT, associated with the American branch of the Louis-Dreyfus family (the commodities-trading dynasty). It is co-located with Louis Dreyfus Company's US headquarters at 10 Westport Road and manages family capital; its SEC 13F disclosed only about five holdings worth ~$65M. It is NOT the Louis Dreyfus Company commodities business itself.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Not publicly documented. The limited 13F holdings (broad index funds VXUS/VTIAX and ITOT plus a couple of small single-name positions) suggest a conservative, largely passive/index-oriented public-markets allocation typical of a family office holding book, but this is inferred, not stated.</t>
-        </is>
-      </c>
+          <t>Personal family-office / holding vehicle of Ben Francis, billionaire founder and majority owner of fitness-apparel brand Gymshark; holds part of his Gymshark shareholding.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Public 13F book was dominated by broad-market and international index funds (Vanguard Total International, iShares Core S&amp;P Total US Market ETF) plus small individual equity positions (e.g., Celularity, New Relic, Lovesac). Not sector-focused.</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>13F US-listed equities ~$64.7M as of 2022-09-30 (Q3 2022, 5 holdings) -- a floor and likely a small slice of total family wealth. Total AUM not disclosed. Business directories estimate ~$390K annual revenue / ~4 employees.</t>
-        </is>
-      </c>
+          <t>Holding company (concentrated Gymshark equity stake)</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Wilton</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>West Midlands</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>W. Thomas Wingertzahn</t>
+          <t>Benjamin David Francis</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Chief Financial Officer (13F signatory / operational head)</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
+          <t>Director &amp; 100% owner; Founder &amp; CEO of Gymshark</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gymshark/</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>203-762-6134</t>
-        </is>
-      </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>No recent public activity found. The most recent SEC 13F on file is Q3 2022; no 2023-2025 13F filings surfaced, which may indicate the equity book fell below the 13F reporting threshold or the office stopped filing.</t>
+          <t>Renamed Ben Francis Ltd -&gt; Francis Family Office Ltd (2021); Ben Francis moved ~half his Gymshark stake into the vehicle; 2026 reporting he is seeking financing to buy back part of General Atlantic's Gymshark stake</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2022-11-10 (last 13F filing, holdings as of 2022-09-30)</t>
+          <t>2021-02-03 (rename); 2026-07 (buyback reporting)</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1273,19 +1253,19 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>ENTITY-CONFUSION RISK: 'Louis-Dreyfus Family Office LLC' is NOT the Louis Dreyfus Company (LDC) commodities firm, though it shares the Wilton CT 10 Westport Road address. The specific family member/branch is INFERRED (Gerard 'William' Louis-Dreyfus's American branch; heirs include Julia Louis-Dreyfus and half-sisters Phoebe and Emma) and not definitively confirmed by a primary source; family_affiliation should be treated as probable, not certain. The true family investment decision-maker is undetermined; Wingertzahn is the CFO/signatory, reported as principal only for lack of a documented alternative. No website, no LinkedIn, no published email. 13F filings appear to have lapsed after 2022.</t>
+          <t>No standalone website/LinkedIn/email for the FO itself — a private holding vehicle, not client-facing. Corporate secretary is a law-firm nominee, not the principal. Investment thesis/sectors not publicly disclosed.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UKCH-12706913</t>
+          <t>UKCH-07931194</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Francis Family Office Limited</t>
+          <t>Wimmer Family Office Ltd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1295,31 +1275,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Francis family (Ben Francis, founder/CEO of Gymshark)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>Wimmer (Per Wimmer, Danish financier, founder of merchant bank Wimmer Financial)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://wfo.am/</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Personal family-office / holding vehicle of Ben Francis, billionaire founder and majority owner of fitness-apparel brand Gymshark; holds part of his Gymshark shareholding.</t>
+          <t>London (Mayfair) family office established by Per Wimmer, a Danish financier, entrepreneur and author; associated with his corporate-advisory firm Wimmer Financial.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Holding company (concentrated Gymshark equity stake)</t>
+          <t>Natural resources (mining, oil &amp; gas, green energy); real estate; infrastructure; aviation; shipping; space economy</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>London</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>West Midlands</t>
+          <t>Mayfair</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1329,17 +1313,17 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Benjamin David Francis</t>
+          <t>Per Thanning Wimmer</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Director &amp; 100% owner; Founder &amp; CEO of Gymshark</t>
+          <t>Founder &amp; CEO, Wimmer Family Office</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/gymshark/</t>
+          <t>https://uk.linkedin.com/in/perwimmer</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -1348,15 +1332,19 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>+44 207 432 7575</t>
+        </is>
+      </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Renamed Ben Francis Ltd -&gt; Francis Family Office Ltd (2021); Ben Francis moved ~half his Gymshark stake into the vehicle; 2026 reporting he is seeking financing to buy back part of General Atlantic's Gymshark stake</t>
+          <t>Per Wimmer resigned as director 2024-09-25; two new directors appointed same day (Aida Feriz, Joppe Sikma); FCA-authorised (FCA #665654)</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2021-02-03 (rename); 2026-07 (buyback reporting)</t>
+          <t>2024-09-25 (director change)</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1366,98 +1354,110 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>No standalone website/LinkedIn/email for the FO itself — a private holding vehicle, not client-facing. Corporate secretary is a law-firm nominee, not the principal. Investment thesis/sectors not publicly disclosed.</t>
+          <t>Corrected task hint: principal is PER Wimmer, not 'Klaus Wimmer'. Per Wimmer resigned as registered director 2024-09-25 but remains named founder on the site; current directors appear operational/successor. Phone is switchboard. AUM/thesis not disclosed.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UKCH-07931194</t>
+          <t>SEC13F-0001802084</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wimmer Family Office Ltd</t>
+          <t>CVA Family Office, LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Wimmer (Per Wimmer, Danish financier, founder of merchant bank Wimmer Financial)</t>
+          <t>None (owner-operated MFO; part of the Class VI Partners group co-founded by Chris Younger and David Tolson). Not tied to a single client family.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://wfo.am/</t>
+          <t>https://classvifamilyoffice.com/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>London (Mayfair) family office established by Per Wimmer, a Danish financier, entrepreneur and author; associated with his corporate-advisory firm Wimmer Financial.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Denver-based multi-family office and SEC-registered investment adviser, formerly 'CVA Family Office, LLC' and now operating as 'Class VI Family Office, LLC', part of the Class VI Partners group. Advises entrepreneurs, business owners and executives on wealth planning, liquidity-event planning and investment management on a 1:1 client:advisor model.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Serving entrepreneurs and business owners around liquidity events; integrated wealth planning + discretionary investment management aligned to each family's goals.</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Natural resources (mining, oil &amp; gas, green energy); real estate; infrastructure; aviation; shipping; space economy</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>Diversified discretionary wealth/investment management for HNW entrepreneurs; no single-sector focus disclosed.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>~$222.27 million regulatory AUM (across ~43 accounts)</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>DENVER</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Mayfair</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Per Thanning Wimmer</t>
+          <t>Matt Blackburn</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO, Wimmer Family Office</t>
+          <t>Managing Partner / Managing Director, Class VI Family Office (co-founder)</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/perwimmer</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr"/>
+          <t>https://www.linkedin.com/in/mattblackburnclassvi/</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>matt@classvipartners.com</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>+44 207 432 7575</t>
+          <t>303-243-5619</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Per Wimmer resigned as director 2024-09-25; two new directors appointed same day (Aida Feriz, Joppe Sikma); FCA-authorised (FCA #665654)</t>
+          <t>Rebranded from 'CVA Family Office' to 'Class VI Family Office'; established as RIA Sept 2016; operates on a 1:1 client:advisor model under Class VI Partners</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2024-09-25 (director change)</t>
+          <t>2016-09 (RIA inception); rebrand to Class VI Family Office (ongoing)</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Corrected task hint: principal is PER Wimmer, not 'Klaus Wimmer'. Per Wimmer resigned as registered director 2024-09-25 but remains named founder on the site; current directors appear operational/successor. Phone is switchboard. AUM/thesis not disclosed.</t>
+          <t>Legal 13F filer name remains 'CVA Family Office, LLC' but the brand/website is now 'Class VI Family Office' (classvifamilyoffice.com); older cvafamilyoffice.com domain was unreachable during research. Principal email is on the classvipartners.com domain, not a family-office-specific domain. Chris Younger is CEO of the broader Class VI Partners; Matt Blackburn selected as the family-office investment/advisory lead.</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -2746,12 +2746,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UKCH-10876208</t>
+          <t>SFO-dfo-management-dell</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Sha Family Office Ltd</t>
+          <t>DFO Management (Dell Family Office)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2761,32 +2761,60 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sha family (controlling PSCs: Mr Sharnpreet Singh Buttar)</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+          <t>Dell family (Michael Dell, founder/CEO of Dell Technologies)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://www.dellfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dfo-management</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Private investment firm managing the assets of Michael Dell and family across public equities, private equity, real estate and other asset classes. Originally MSD Capital (1998); the multi-client business became BDT &amp; MSD Partners while the family's captive vehicle was rebranded DFO Management at end of 2022.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Multi-asset-class permanent capital: public equities, private equity/credit, real estate, opportunistic direct investments.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>64205 - Activities of financial services holding companies; 64209 - Activities of other holding companies not elsewhere classified</t>
+          <t>Diversified (consumer, real estate, financials, industrials)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>SIC codes - 64205</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Michael Dell</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Founder / Family Principal</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -2795,28 +2823,36 @@
         </is>
       </c>
       <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>13F-HR filed 2026-05-15 (period ending 2026-03-31) disclosing U.S. equity holdings; rebrand from MSD Capital to DFO Management completed end of 2022.</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>2026-05-15; 2022-12</t>
+        </is>
+      </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>UK filing SIC: fo-relevant-sic. Active officers: BUTTAR, Sharnpreet Singh () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
+          <t>The 13F is filed in the name of the Michael &amp; Susan Dell Foundation with DFO Management as manager; the foundation and the family office are affiliated. AUM not disclosed. Michael Dell is a public figure; no personal LinkedIn tied specifically to DFO confirmed.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UKCH-15240886</t>
+          <t>SFO-bayshore-global-brin</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Freedman Family Office</t>
+          <t>Bayshore Global Management (Brin Family Office)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2826,32 +2862,52 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Freedman family (controlling PSCs: Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman)</t>
+          <t>Brin family (Sergey Brin, Google co-founder)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Low-profile single-family office managing the wealth of Sergey Brin across public and private markets, real estate and philanthropy. Additional office in Singapore. Reported to have absorbed the Nexus NeuroTech brain-health VC fund in 2026.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Broad multi-asset allocation with notable venture/science-and-health direct investing.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>64301 - Activities of investment trusts</t>
+          <t>Diversified; neuroscience/brain-health, deep tech, real estate</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>Palo Alto</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Sergey Brin</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Family Principal</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -2860,28 +2916,36 @@
         </is>
       </c>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Absorbed Nexus NeuroTech brain-health VC fund (reported 2026-04-23, Bloomberg).</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>UK filing SIC: fo-relevant-sic. Active officers: FREEDMAN, Elaine Wilson (), FREEDMAN, Laura-Leigh (), ZIMMERMAN, Samantha Jade () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
+          <t>No public website confirmed. AUM figures are press estimates. CEO George Pavlov / CIO Marie Young named in Wikipedia and press but not verified against a primary filing.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UKCH-11031775</t>
+          <t>SFO-hillspire-schmidt</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ralph Family Office Limited</t>
+          <t>Hillspire (Eric Schmidt Family Office)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2891,32 +2955,52 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ralph family (controlling PSCs: Melanie Lynette Ralph; Mr Jan De Ridder Ralph)</t>
+          <t>Schmidt family (Eric &amp; Wendy Schmidt; Eric Schmidt is former Google/Alphabet CEO and chairman)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Single-family office of Eric and Wendy Schmidt focused on deep technology: artificial intelligence, quantum computation, defense tech and biotech. Reported to have invested in 22+ private AI firms since 2019 (including Anthropic, SandboxAQ, Inworld AI) and topped CNBC's inaugural family-office dealmaking ranking for 2025.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Deep-tech direct investing concentrated in AI, quantum, defense technology and biotech.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>64301 - Activities of investment trusts; 68209 - Other letting and operating of own or leased real estate</t>
+          <t>AI, quantum computing, defense tech, biotech</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>SIC codes - 64301</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+          <t>Palo Alto</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Eric Schmidt</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Family Principal / Founder</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -2925,14 +3009,1029 @@
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Ranked #1 most active U.S. family office for dealmaking in 2025 (15 investments, mostly AI) per CNBC 2026-02-12; disclosed 22 private AI startup investments since 2019 (CNBC 2025-01-21).</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>2026-02-12; 2025-01-21</t>
+        </is>
+      </c>
       <c r="V25" t="inlineStr">
         <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>No public website confirmed (hillspire.com not verified). Does not file 13F (EDGAR full-text search returned no 13F-HR). AUM not disclosed. President Ken Goldman named in press, not verified against a primary filing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SFO-blue-pool-capital-tsai</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Blue Pool Capital (Joe Tsai Family Office)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Tsai family (Joseph Tsai, Alibaba co-founder and chairman)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.bluepoolcapital.com/</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hong Kong-based investment firm overseeing the Tsai family's wealth across hedge funds, private equity, private credit, venture and sports assets (Brooklyn Nets, LAFC). Raised ~$1bn for its first dedicated PE vehicle (Riverside Fund) reported 2026. Led by CEO Oliver Weisberg (ex-Goldman Sachs, ex-Citadel).</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Multi-strategy long-term capital: public markets, PE, private credit, venture, and sports/real assets.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Diversified; technology (SpaceX, Epic Games, ByteDance), consumer/luxury (Golden Goose), sports, Japanese real estate</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>~$50 billion</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Causeway Bay</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Joseph Tsai</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Family Principal / Founder</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>13F-HR filed 2026-05-15; sold ~83% of Blue Owl Capital stake (~$460m) reported 2024-03; joined consortium buying Burgundy vineyards 2024-09; raised ~$1bn first PE fund (Riverside) reported 2026-03-31.</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>2026-05-15; 2024-03-03; 2024-09-19; 2026-03-31</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Some sources describe Blue Pool as a 'multi-family' vehicle co-backed by former Alibaba executives (and occasionally link Jack Ma); primary characterization is Joe Tsai's family office. Website confirmed to be minimal/uninformative per Crain Currency; bluepoolcapital.com domain asserted from press but not independently fetched.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SFO-mousse-partners-wertheimer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Mousse Partners (Wertheimer Family Office)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Wertheimer family (Alain and Gerard Wertheimer, owners of Chanel)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://moussepartners.com/</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/moussepartners</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Investment firm serving as the family office of the Wertheimer family. Manages a global diversified portfolio across public equities, fixed income, private equity, venture and real estate, with investment operations in New York and Asia (Beijing, Hong Kong).</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Global multi-asset diversified investing with a notable consumer/brands tilt.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Diversified; consumer, luxury/brands, technology, real estate</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Charles Heilbronn</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Founder / Chairman</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Bloomberg feature (2024-2025) reporting the office reshaping its consumer/public-equity bets.</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>2024/2025 (Bloomberg feature)</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Does not appear as a 13F filer under 'Mousse Partners' (EDGAR full-text search returned 0); investment vehicle is domiciled offshore (Mousse Investments Limited, Bermuda) with a NYC office (9 W. 57th St). AUM figure is the family fortune, not disclosed firm AUM. Firm general phone reported as 212-303-5795 (not an individual principal line).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SFO-kirkbi-kristiansen</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>KIRKBI (Kirk Kristiansen Family Office)</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Kirk Kristiansen family (owners of the LEGO Group)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.kirkbi.com/</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kirkbi</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Danish family-owned holding and investment company managing the wealth and legacy of the Kirk Kristiansen family. Holds the family's controlling stakes in LEGO Group and Merlin Entertainments and runs a long-term investment portfolio plus a dedicated climate/energy-transition program (KIRKBI Climate). Additional offices in Copenhagen and Baar, Switzerland.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Protect and grow family wealth for future generations; long-term core holdings (LEGO, Merlin) plus diversified investments and thematic climate/energy investing.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Toys/entertainment (core), real estate, renewable energy/climate, diversified financial investments</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>~$16 billion (family wealth)</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Billund</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Region of Southern Denmark</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Soren Thorup Sorensen</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>KIRKBI Climate follow-on investment in Highview Power (Hunterston project) announced November 2025 (second investment after June 2024 Carrington); Adapture Renewables (KIRKBI-majority-owned) acquired 110MW Colorado solar-plus-storage project March 2025; generational handover of board chair to Thomas Kirk Kristiansen May 2023.</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>2025-11; 2025-03; 2023-05</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>KIRKBI is both the family holding company (owns LEGO) and the family investment office; some may classify it as a holding company rather than a pure family office. AUM figure is the family-wealth press figure, not full portfolio value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SFO-tethys-invest-bettencourt</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tethys / Tethys Invest (Bettencourt Meyers Family Office)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Bettencourt Meyers family (majority shareholder of L'Oreal; Francoise Bettencourt Meyers)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://tethys.fr/</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/t%C3%A9thys</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Paris-based single-family office of the Bettencourt Meyers family, holder of the family's ~34% L'Oreal stake. Its subsidiary Tethys Invest (&gt;EUR 3bn capital) makes long-term direct investments deliberately outside L'Oreal's competitive scope, with a healthcare emphasis (Elsan private hospitals, Sebia diagnostics).</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Preserve the L'Oreal core holding and deploy dividend income into long-term entrepreneurial direct investments, notably healthcare, that do not compete with L'Oreal.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Healthcare (hospitals, diagnostics), consumer, technology, diversified</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>&gt; $90 billion (family assets)</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Ile-de-France</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Alexandre Benais</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>CEO, Tethys Invest</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Named new head of family investment firm reported 2023-03-13 (The National); family succession moves (Jean-Victor Meyers to L'Oreal vice-chairman; Alexandre Benais to family L'Oreal board seat) reported 2025-02; co-invested (with Chanel/Wertheimer) in The Row reported 2024-09.</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>2023-03-13; 2025-02-08; 2024-09</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>'Tethys' (parent) vs 'Tethys Invest' (investment subsidiary) are distinct entities; leadership names span both. AUM is the family-asset press figure, not a disclosed managed-portfolio AUM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SFO-cofra-holding-brenninkmeijer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>COFRA Holding (Brenninkmeijer Family Office)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Brenninkmeijer family (founders/owners of C&amp;A; ~500 family members)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.cofraholding.com/</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Zug-based family-owned holding coordinating the Brenninkmeijer family's global operations and ~EUR 35-38bn asset base across retail (C&amp;A), real estate (Redevco), private equity (Bregal Investments) and asset management (Anthos). In 2025 the family announced it would open its portfolio to outside investors, a shift from its historically secretive model.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Long-term stewardship of family capital across operating businesses, real estate, private equity and (increasingly) externally-opened investment platforms.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Retail, real estate, private equity, asset management, climate/energy</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>EUR 35-38 billion</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Zug</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Canton of Zug</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Martijn Brenninkmeijer</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Chairman of the Board, COFRA Holding AG</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Announced opening of ~EUR 38bn portfolio to external investors (April 2025); Florian Brenninkmeyer appointed CFO effective 1 Jan 2025; Redevco closed landmark GBP 47.5m real-estate-debt loan (April 2025).</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2025-04; 2025-01-01; 2025-04</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>COFRA is primarily a family holding company; its asset-management arm Anthos is opening to third-party capital (2025), which blurs the pure single-family-office boundary. Classified SFO at the holding level but noted as trending toward external capital.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SFO-athos-strungmann</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Athos (Strungmann Family Office)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Strungmann family (Andreas and Thomas Strungmann, founders of Hexal)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Munich-based single-family office of the Strungmann twins, focused heavily on biotech and life sciences. Anchored and remains largest shareholder of BioNTech (~43.5%) and holds stakes in Formycon and Immatics; actively recycles BioNTech proceeds into new European biotech ventures.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Long-horizon anchor investing in biotech and life sciences, recycling returns from BioNTech into the next generation of European biotech.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Biotech, life sciences, healthcare technology</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Bavaria</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Andreas Strungmann</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Family Principal / Co-Founder</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Participated in AAVantgarde Bio's $141m Series B (Nov 2025); AMSilk EUR 52m round (Sep 2025); Antheia funding ($56m Jun 2025, $24m Jan 2026); admin services of Athos Service acquired by Bolder Group (May 2024).</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>2025-11; 2025-09; 2025-06; 2026-01; 2024-05</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>No public website confirmed. 'Athos Service GmbH' is the services entity; the investing vehicle is often cited as 'Athos KG'. Investment-round dates sourced from family-office trade press rather than primary filings. AUM not disclosed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SFO-premji-invest</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Premji Invest (Azim Premji Family Office)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Premji family (Azim Premji, founder of Wipro)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://www.premjiinvest.com/</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/premjiinvest</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Bengaluru-based family office and investment firm managing the wealth of Azim Premji and family (and closely tied to the Azim Premji Foundation endowment). Invests across public equities, private equity and venture, backing technology, financial services, consumer, healthcare and industrials; crossed $10bn in managed assets.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Long-horizon growth investing across public and private markets in emerging/disruptive technology and consumer/financial sectors.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Technology, financial services, consumer, healthcare, industrials</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>&gt; $10 billion</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>T.K. Kurien</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>CEO &amp; Managing Partner</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Acquisition of Anand Chemiceutics reported 2025-11-13; participated in Runway Series E (with General Atlantic, Nvidia) 2026-02-10; 19 funding rounds / 2 acquisitions in trailing 12 months (per Tracxn, Feb 2026).</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>2025-11-13; 2026-02-10</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Premji Invest also manages the Azim Premji Foundation's endowment, so it straddles family-office and foundation-endowment functions; consistently described as a family office, hence corroborated rather than strong-single-family-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SFO-catamaran-ventures-murthy</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Catamaran Ventures (N.R. Narayana Murthy Family Office)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Murthy family (N.R. Narayana Murthy, co-founder of Infosys)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://catamaran.in/</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/catamaran-ventures</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Bengaluru-based single-family office of Infosys co-founder N.R. Narayana Murthy, investing permanent family capital (no external LPs). Focused on growth capital, notably Indian manufacturing and deep tech; has recently turned more cautious on Indian startup valuations.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Permanent-capital growth investing, with emphasis on Indian manufacturing and deep-tech, valuation-disciplined.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Manufacturing, deep tech, consumer, technology</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>N.R. Narayana Murthy</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Founder / Chairman Emeritus (Family Principal)</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Bloomberg (2025-08-26) reporting Catamaran growing cautious on Indian startup valuations; recent deep-tech stake and follow-on investments (Akshayakalpa first-time, Innoviti follow-on) in 2025.</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>2025-08-26; 2025</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Investment pace slowed in 2025 (approximately one new investment) per Tracxn; AUM not disclosed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>UKCH-10876208</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sha Family Office Ltd</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sha family (controlling PSCs: Mr Sharnpreet Singh Buttar)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>64205 - Activities of financial services holding companies; 64209 - Activities of other holding companies not elsewhere classified</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>SIC codes - 64205</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
           <t>C</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>UK filing SIC: fo-relevant-sic. Active officers: BUTTAR, Sharnpreet Singh () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>UKCH-15240886</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Freedman Family Office</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Freedman family (controlling PSCs: Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>64301 - Activities of investment trusts</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>UK filing SIC: fo-relevant-sic. Active officers: FREEDMAN, Elaine Wilson (), FREEDMAN, Laura-Leigh (), ZIMMERMAN, Samantha Jade () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>UKCH-11031775</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Ralph Family Office Limited</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Ralph family (controlling PSCs: Melanie Lynette Ralph; Mr Jan De Ridder Ralph)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>64301 - Activities of investment trusts; 68209 - Other letting and operating of own or leased real estate</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>SIC codes - 64301</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
         <is>
           <t>UK filing SIC: fo-relevant-sic. Active officers: RALPH, Jan De Ridder (), RALPH, Melanie Lynette (), BETHELL, Karen (), BETHELL, Stuart (), YOULL, Gavin William () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
         </is>
@@ -2949,11 +4048,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P25"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
@@ -3137,12 +4236,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEC13F-0001802084</t>
+          <t>SEC13F-0001938970</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVA Family Office, LLC</t>
+          <t>Callan Family Office, LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3152,22 +4251,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001802084); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001938970); discovered via fts</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001802084&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001938970&amp;type=13F</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Boutique multi-family wealth-management firm serving multiple high-net-worth business owners/entrepreneurs; ~43 client accounts / ~24 client relationships, ~$222M regulatory AUM. Sources: https://wallmine.com/adviser/235356/cva-family-office-llc ; https://classvifamilyoffice.com/about/</t>
+          <t>A registered investment adviser and multi-family office that markets to and serves multiple ultra-high-net-worth families; accepts clients with $50M+ to invest (average client ~$100M) and reported &gt;$5B AUM by early 2024. Source: https://riabiz.com/a/2024/4/9/an-abbot-downing-breakaway-but-not-exactly-callan-family-office-hits-5-billion-of-aum-after-just-two-years-using-a-creative-callan-brand-deal-and-a-partnership-model</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (13F filer) established September 2016 as an RIA; branded and operated as a family office (now 'Class VI Family Office'). Sources: https://www.classvipartners.com/our-team/matt-blackburn/ ; https://classvifamilyoffice.com/about/</t>
+          <t>Self-describes as a family office; RIABiz and Forbes cover it as an MFO; files 13F under CIK 0001938970; published team/services pages. Source: https://callanfamilyoffice.com/team/ and https://www.forbes.com/companies/callan-family-office/</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -3177,12 +4276,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Adviser/ADV aggregators. https://wallmine.com/adviser/235356/cva-family-office-llc</t>
+          <t>https://riabiz.com/a/2024/4/9/an-abbot-downing-breakaway-but-not-exactly-callan-family-office-hits-5-billion-of-aum-after-just-two-years-using-a-creative-callan-brand-deal-and-a-partnership-model (March 2024)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Co-founder of the family office (est. Sept 2016 as CVA Family Office) who leads the wealth team and 'customiz[es] planning and investment management advice for Class VI clients' — the lead investment/advisory decision-maker. Co-founders Chris Younger (CEO, Class VI Partners) and David Tolson also sit above the group. https://www.classvipartners.com/our-team/matt-blackburn/ ; https://classvifamilyoffice.com/about/</t>
+          <t>Ginter is CEO and Founding Partner, leading firm strategy and business development; he is the current top principal and matches the 13F signatory 'John Ginter' (Jack = John). Verified on the firm's own team page. Source: https://callanfamilyoffice.com/team/jack-ginter/</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -3192,22 +4291,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://classvifamilyoffice.com/about/</t>
+          <t>https://callanfamilyoffice.com/team/jack-ginter/</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>The firm's own About/team page publishes individual emails including 'Matt@classvipartners.com' (and 'dalyce@classvipartners.com') alongside the general familyoffice@classvipartners.com. Published individual address; not independently provider-verified.</t>
+          <t>The firm's own team/bio page for Jack Ginter publishes his individual professional email as jginter@callanfo.com (displayed on his profile page alongside his title 'Chief Executive Officer, Founding Partner'). Note the mail domain callanfo.com differs from the website domain.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>https://cvafamilyoffice.com/ (main office line, 101 University Blvd, Denver; firm switchboard, not a personal line)</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1938970/000193897026000003/primary_doc.xml</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>https://www.classvipartners.com/our-team/matt-blackburn/ ; https://classvifamilyoffice.com/about/ ; https://www.getwarmer.com/firms/class-vi-family-office-llc</t>
+          <t>https://riabiz.com/a/2024/4/9/an-abbot-downing-breakaway-but-not-exactly-callan-family-office-hits-5-billion-of-aum-after-just-two-years-using-a-creative-callan-brand-deal-and-a-partnership-model ; https://www.diamond-consultants.com/building-a-business-with-intention-the-5b-callan-family-office-recipe-for-success/</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -3219,12 +4318,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEC13F-0001938970</t>
+          <t>SEC13F-0001596197</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Callan Family Office, LLC</t>
+          <t>INTREPID FAMILY OFFICE LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3234,79 +4333,63 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001938970); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001596197); discovered via fts</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001938970&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001596197&amp;type=13F</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>A registered investment adviser and multi-family office that markets to and serves multiple ultra-high-net-worth families; accepts clients with $50M+ to invest (average client ~$100M) and reported &gt;$5B AUM by early 2024. Source: https://riabiz.com/a/2024/4/9/an-abbot-downing-breakaway-but-not-exactly-callan-family-office-hits-5-billion-of-aum-after-just-two-years-using-a-creative-callan-brand-deal-and-a-partnership-model</t>
+          <t>No SEC investment-adviser registration found in IAPD (searched 'INTREPID FAMILY OFFICE LLC'); files SEC Form 13F-HR (CIK 0001596197) reporting $123.64B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Self-describes as a family office; RIABiz and Forbes cover it as an MFO; files 13F under CIK 0001938970; published team/services pages. Source: https://callanfamilyoffice.com/team/ and https://www.forbes.com/companies/callan-family-office/</t>
+          <t>No SEC investment-adviser registration found in IAPD (searched 'INTREPID FAMILY OFFICE LLC'); files SEC Form 13F-HR (CIK 0001596197) reporting $123.64B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>https://riabiz.com/a/2024/4/9/an-abbot-downing-breakaway-but-not-exactly-callan-family-office-hits-5-billion-of-aum-after-just-two-years-using-a-creative-callan-brand-deal-and-a-partnership-model (March 2024)</t>
-        </is>
-      </c>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Ginter is CEO and Founding Partner, leading firm strategy and business development; he is the current top principal and matches the 13F signatory 'John Ginter' (Jack = John). Verified on the firm's own team page. Source: https://callanfamilyoffice.com/team/jack-ginter/</t>
+          <t>Signed the firm's Form 13F-HR (03-31-2026) as Chief Financial Officer — verified associated person; investment-decision-maker status to be confirmed separately.</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://callanfamilyoffice.com/team/jack-ginter/</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>The firm's own team/bio page for Jack Ginter publishes his individual professional email as jginter@callanfo.com (displayed on his profile page alongside his title 'Chief Executive Officer, Founding Partner'). Note the mail domain callanfo.com differs from the website domain.</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1938970/000193897026000003/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>https://riabiz.com/a/2024/4/9/an-abbot-downing-breakaway-but-not-exactly-callan-family-office-hits-5-billion-of-aum-after-just-two-years-using-a-creative-callan-brand-deal-and-a-partnership-model ; https://www.diamond-consultants.com/building-a-business-with-intention-the-5b-callan-family-office-recipe-for-success/</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
+          <t>SEC EDGAR 13F-HR 0001013594-26-000589 (2026-05-15)</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEC13F-0001596197</t>
+          <t>SEC13F-0001536411</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INTREPID FAMILY OFFICE LLC</t>
+          <t>Duquesne Family Office LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3316,33 +4399,37 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001596197); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001536411); discovered via fts</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001596197&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001536411&amp;type=13F</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>No SEC investment-adviser registration found in IAPD (searched 'INTREPID FAMILY OFFICE LLC'); files SEC Form 13F-HR (CIK 0001596197) reporting $123.64B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
+          <t>Widely reported as the private investment office through which Stanley Druckenmiller manages his own family's capital after closing his hedge fund Duquesne Capital Management to outside investors in 2010. No external clients; it manages one family's money. Source: https://www.fool.com/investing/how-to-invest/famous-investors/duquesne-family-office and https://www.institutionalinvestor.com/article/stan-druckenmiller-overhauls-his-family-offices-us-stock-portfolio</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No SEC investment-adviser registration found in IAPD (searched 'INTREPID FAMILY OFFICE LLC'); files SEC Form 13F-HR (CIK 0001596197) reporting $123.64B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
+          <t>Files SEC Form 13F as 'Duquesne Family Office LLC' (CIK 0001536411); press uniformly describes it as Druckenmiller's family office. Source: https://13f.info/manager/0001536411-duquesne-family-office-llc</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>13F value: https://13f.info/13f/000153641125000017-duquesne-family-office-llc-q3-2025 (as of 2025-09-30) and https://seekingalpha.com/article/4881297-tracking-stanley-druckenmillers-duquesne-family-office-portfolio-q4-2025-update ; net worth: https://www.forbes.com/profile/stanley-druckenmiller/</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Signed the firm's Form 13F-HR (03-31-2026) as Chief Financial Officer — verified associated person; investment-decision-maker status to be confirmed separately.</t>
+          <t>Druckenmiller is the founder and sole principal directing all investment decisions; he is named as portfolio manager on the firm's 13F activity in current (2025) press coverage. The 13F signatory Sue Meng is General Counsel (compliance), not the investment decision-maker. Source: https://www.institutionalinvestor.com/article/stan-druckenmiller-overhauls-his-family-offices-us-stock-portfolio and https://www.levelfields.ai/news/stanley-druckenmillers-duquesne-family-office-cuts-exposure-adds-new-tech-and-energy-stocks-in-q1-2025</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -3351,15 +4438,19 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Tried: web searches for a Duquesne domain/team page (none exists); no firm website to host a team directory; no filing or press publishing an individual email. Refused to construct one from a name+domain pattern.</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1536411/000153641126000004/primary_doc.xml</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>SEC EDGAR 13F-HR 0001013594-26-000589 (2026-05-15)</t>
+          <t>https://13f.info/13f/000153641125000017-duquesne-family-office-llc-q3-2025 ; https://seekingalpha.com/article/4881297-tracking-stanley-druckenmillers-duquesne-family-office-portfolio-q4-2025-update ; https://www.levelfields.ai/news/stanley-druckenmillers-duquesne-family-office-cuts-exposure-adds-new-tech-and-energy-stocks-in-q1-2025</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -3367,12 +4458,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEC13F-0001536411</t>
+          <t>SEC13F-0001683689</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Duquesne Family Office LLC</t>
+          <t>Kopp Family Office, LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3382,37 +4473,33 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001536411); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001683689); discovered via fts</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001536411&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001683689&amp;type=13F</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Widely reported as the private investment office through which Stanley Druckenmiller manages his own family's capital after closing his hedge fund Duquesne Capital Management to outside investors in 2010. No external clients; it manages one family's money. Source: https://www.fool.com/investing/how-to-invest/famous-investors/duquesne-family-office and https://www.institutionalinvestor.com/article/stan-druckenmiller-overhauls-his-family-offices-us-stock-portfolio</t>
+          <t>No SEC investment-adviser registration found in IAPD (searched 'Kopp Family Office, LLC'); files SEC Form 13F-HR (CIK 0001683689) reporting $163.17B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Files SEC Form 13F as 'Duquesne Family Office LLC' (CIK 0001536411); press uniformly describes it as Druckenmiller's family office. Source: https://13f.info/manager/0001536411-duquesne-family-office-llc</t>
+          <t>No SEC investment-adviser registration found in IAPD (searched 'Kopp Family Office, LLC'); files SEC Form 13F-HR (CIK 0001683689) reporting $163.17B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>13F value: https://13f.info/13f/000153641125000017-duquesne-family-office-llc-q3-2025 (as of 2025-09-30) and https://seekingalpha.com/article/4881297-tracking-stanley-druckenmillers-duquesne-family-office-portfolio-q4-2025-update ; net worth: https://www.forbes.com/profile/stanley-druckenmiller/</t>
-        </is>
-      </c>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Druckenmiller is the founder and sole principal directing all investment decisions; he is named as portfolio manager on the firm's 13F activity in current (2025) press coverage. The 13F signatory Sue Meng is General Counsel (compliance), not the investment decision-maker. Source: https://www.institutionalinvestor.com/article/stan-druckenmiller-overhauls-his-family-offices-us-stock-portfolio and https://www.levelfields.ai/news/stanley-druckenmillers-duquesne-family-office-cuts-exposure-adds-new-tech-and-energy-stocks-in-q1-2025</t>
+          <t>Signed the firm's Form 13F-HR (06-30-2026) as Chief Financial Officer — verified associated person; investment-decision-maker status to be confirmed separately.</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3421,19 +4508,15 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Tried: web searches for a Duquesne domain/team page (none exists); no firm website to host a team directory; no filing or press publishing an individual email. Refused to construct one from a name+domain pattern.</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1536411/000153641126000004/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1683689/000089271226000313/primary_doc.xml</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>https://13f.info/13f/000153641125000017-duquesne-family-office-llc-q3-2025 ; https://seekingalpha.com/article/4881297-tracking-stanley-druckenmillers-duquesne-family-office-portfolio-q4-2025-update ; https://www.levelfields.ai/news/stanley-druckenmillers-duquesne-family-office-cuts-exposure-adds-new-tech-and-energy-stocks-in-q1-2025</t>
+          <t>SEC EDGAR 13F-HR 0000892712-26-000313 (2026-07-09)</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -3441,12 +4524,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEC13F-0001683689</t>
+          <t>SEC13F-0001889527</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kopp Family Office, LLC</t>
+          <t>Louis-Dreyfus Family Office LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3456,22 +4539,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001683689); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001889527); discovered via fts</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001683689&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001889527&amp;type=13F</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>No SEC investment-adviser registration found in IAPD (searched 'Kopp Family Office, LLC'); files SEC Form 13F-HR (CIK 0001683689) reporting $163.17B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
+          <t>A small, named single-family office (5 13F holdings, ~$64.7M, ~4 employees per business directories) serving the Louis-Dreyfus family; no evidence of external clients or a marketed multi-family service offering. Source: https://www.ctcompanydir.com/companies/louis-dreyfus-family-office-llc/ and https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>No SEC investment-adviser registration found in IAPD (searched 'Kopp Family Office, LLC'); files SEC Form 13F-HR (CIK 0001683689) reporting $163.17B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
+          <t>Registered LLC named 'Louis-Dreyfus Family Office LLC' at 10 Westport Rd, Wilton CT (registered 2007 per directory); files SEC 13F under CIK 0001889527. Source: https://www.ctcompanydir.com/companies/louis-dreyfus-family-office-llc/</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3479,10 +4562,14 @@
           <t>corroborated</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc (latest filing Q3 2022, value ~$64,676K as of 2022-09-30); directory revenue estimate: https://www.manta.com/c/mm0v4v4/loius-dreyfus-family-office-llc</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Signed the firm's Form 13F-HR (06-30-2026) as Chief Financial Officer — verified associated person; investment-decision-maker status to be confirmed separately.</t>
+          <t>Wingertzahn is the named 13F signatory and CFO; for an office this small he is likely the day-to-day operational and investment administrator. However, the TRUE family investment principal (a Louis-Dreyfus family member/heir) is not publicly identified. Source (signatory role provided in brief); firm identity: https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3491,15 +4578,19 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Tried: searches for a firm website/team page (none), for Wingertzahn contact details, and for any filing/press publishing an individual email. None found published. Did not construct any address.</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1683689/000089271226000313/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>SEC EDGAR 13F-HR 0000892712-26-000313 (2026-07-09)</t>
+          <t>https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -3507,73 +4598,69 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEC13F-0001889527</t>
+          <t>UKCH-12706913</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Louis-Dreyfus Family Office LLC</t>
+          <t>Francis Family Office Limited</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>sec-13f</t>
+          <t>uk-companies-house</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001889527); discovered via fts</t>
+          <t>Companies House 12706913 (Private limited company); inc. 30 June 2020</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001889527&amp;type=13F</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/12706913</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>A small, named single-family office (5 13F holdings, ~$64.7M, ~4 employees per business directories) serving the Louis-Dreyfus family; no evidence of external clients or a marketed multi-family service offering. Source: https://www.ctcompanydir.com/companies/louis-dreyfus-family-office-llc/ and https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
+          <t>Directors are three members of the Francis family (Benjamin David, Joseph John, Steven John Francis); vehicle holds Ben Francis's Gymshark stake. Source: https://find-and-update.company-information.service.gov.uk/company/12706913/officers ; https://www.netincome.co/p/the-boardroom-drama-behind-one-of</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Registered LLC named 'Louis-Dreyfus Family Office LLC' at 10 Westport Rd, Wilton CT (registered 2007 per directory); files SEC 13F under CIK 0001889527. Source: https://www.ctcompanydir.com/companies/louis-dreyfus-family-office-llc/</t>
+          <t>Companies House shows firm renamed from 'BEN FRANCIS LIMITED' to 'FRANCIS FAMILY OFFICE LIMITED' on 2021-02-03; SIC 64209; registered at Gymshark HQ. Press: Ben Francis transferred half his Gymshark ownership into the vehicle, which he owns 100%. Sources: https://find-and-update.company-information.service.gov.uk/company/12706913 ; https://www.netincome.co/p/the-boardroom-drama-behind-one-of</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>corroborated</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc (latest filing Q3 2022, value ~$64,676K as of 2022-09-30); directory revenue estimate: https://www.manta.com/c/mm0v4v4/loius-dreyfus-family-office-llc</t>
+          <t>Not disclosed. Ben Francis personal net worth ~$900m-1.3bn (Forbes) is personal wealth, not stated FO AUM. https://www.forbes.com/profile/ben-francis-1/</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Wingertzahn is the named 13F signatory and CFO; for an office this small he is likely the day-to-day operational and investment administrator. However, the TRUE family investment principal (a Louis-Dreyfus family member/heir) is not publicly identified. Source (signatory role provided in brief); firm identity: https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
+          <t>Named director since incorporation (2020-06-30), 100% owner and actual decision-maker. https://find-and-update.company-information.service.gov.uk/company/12706913/officers</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Tried: searches for a firm website/team page (none), for Wingertzahn contact details, and for any filing/press publishing an individual email. None found published. Did not construct any address.</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
-        </is>
-      </c>
+          <t>No individual email published; firm has no website. Checked Companies House filings and Gymshark press.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/12706913 ; https://www.forbes.com/sites/robertolsen-1/2026/07/04/britains-youngest-billionaire-wants-more-control-over-gymshark/</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -3581,12 +4668,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UKCH-12706913</t>
+          <t>UKCH-07931194</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Francis Family Office Limited</t>
+          <t>Wimmer Family Office Ltd</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3596,22 +4683,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Companies House 12706913 (Private limited company); inc. 30 June 2020</t>
+          <t>Companies House 07931194 (Private limited company); inc. 1 February 2012</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/12706913</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/07931194</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Directors are three members of the Francis family (Benjamin David, Joseph John, Steven John Francis); vehicle holds Ben Francis's Gymshark stake. Source: https://find-and-update.company-information.service.gov.uk/company/12706913/officers ; https://www.netincome.co/p/the-boardroom-drama-behind-one-of</t>
+          <t>Website: 'The Wimmer Family Office is based in Mayfair, London, and was established by Per Wimmer.' Built around a single principal. https://wfo.am/</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Companies House shows firm renamed from 'BEN FRANCIS LIMITED' to 'FRANCIS FAMILY OFFICE LIMITED' on 2021-02-03; SIC 64209; registered at Gymshark HQ. Press: Ben Francis transferred half his Gymshark ownership into the vehicle, which he owns 100%. Sources: https://find-and-update.company-information.service.gov.uk/company/12706913 ; https://www.netincome.co/p/the-boardroom-drama-behind-one-of</t>
+          <t>Active FCA-authorised entity (FCA #665654), SIC 66190; live website branded as a family office with Mayfair address. https://wfo.am/ ; https://find-and-update.company-information.service.gov.uk/company/07931194</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3621,12 +4708,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Not disclosed. Ben Francis personal net worth ~$900m-1.3bn (Forbes) is personal wealth, not stated FO AUM. https://www.forbes.com/profile/ben-francis-1/</t>
+          <t>Not disclosed. Sectors are those of associated firm Wimmer Financial. https://wimmerfinancial.com/</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Named director since incorporation (2020-06-30), 100% owner and actual decision-maker. https://find-and-update.company-information.service.gov.uk/company/12706913/officers</t>
+          <t>Founder/namesake; director from incorporation (2012) until resignation 2024-09-25; still presented as founder/CEO on website and LinkedIn. https://find-and-update.company-information.service.gov.uk/company/07931194/officers ; https://uk.linkedin.com/in/perwimmer</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3634,16 +4721,24 @@
           <t>confirmed</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://wfo.am/</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>No individual email published; firm has no website. Checked Companies House filings and Gymshark press.</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>Only a generic mailbox (info@WFO.am) is published (excluded). A per.wimmer@wimmerfinancial.com string appeared only in a URL parameter, not as a published contact — not shipped.</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>https://wfo.am/contact-us/ (firm switchboard, not a personal line)</t>
+        </is>
+      </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/12706913 ; https://www.forbes.com/sites/robertolsen-1/2026/07/04/britains-youngest-billionaire-wants-more-control-over-gymshark/</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/07931194/officers</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -3651,37 +4746,37 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UKCH-07931194</t>
+          <t>SEC13F-0001802084</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Wimmer Family Office Ltd</t>
+          <t>CVA Family Office, LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Companies House 07931194 (Private limited company); inc. 1 February 2012</t>
+          <t>EDGAR 13F filer (CIK 0001802084); discovered via fts</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/07931194</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001802084&amp;type=13F</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Website: 'The Wimmer Family Office is based in Mayfair, London, and was established by Per Wimmer.' Built around a single principal. https://wfo.am/</t>
+          <t>Boutique multi-family wealth-management firm serving multiple high-net-worth business owners/entrepreneurs; ~43 client accounts / ~24 client relationships, ~$222M regulatory AUM. Sources: https://wallmine.com/adviser/235356/cva-family-office-llc ; https://classvifamilyoffice.com/about/</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Active FCA-authorised entity (FCA #665654), SIC 66190; live website branded as a family office with Mayfair address. https://wfo.am/ ; https://find-and-update.company-information.service.gov.uk/company/07931194</t>
+          <t>SEC-registered investment adviser (13F filer) established September 2016 as an RIA; branded and operated as a family office (now 'Class VI Family Office'). Sources: https://www.classvipartners.com/our-team/matt-blackburn/ ; https://classvifamilyoffice.com/about/</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3691,12 +4786,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Not disclosed. Sectors are those of associated firm Wimmer Financial. https://wimmerfinancial.com/</t>
+          <t>Adviser/ADV aggregators. https://wallmine.com/adviser/235356/cva-family-office-llc</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Founder/namesake; director from incorporation (2012) until resignation 2024-09-25; still presented as founder/CEO on website and LinkedIn. https://find-and-update.company-information.service.gov.uk/company/07931194/officers ; https://uk.linkedin.com/in/perwimmer</t>
+          <t>Co-founder of the family office (est. Sept 2016 as CVA Family Office) who leads the wealth team and 'customiz[es] planning and investment management advice for Class VI clients' — the lead investment/advisory decision-maker. Co-founders Chris Younger (CEO, Class VI Partners) and David Tolson also sit above the group. https://www.classvipartners.com/our-team/matt-blackburn/ ; https://classvifamilyoffice.com/about/</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3706,25 +4801,29 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://wfo.am/</t>
+          <t>https://classvifamilyoffice.com/about/</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Only a generic mailbox (info@WFO.am) is published (excluded). A per.wimmer@wimmerfinancial.com string appeared only in a URL parameter, not as a published contact — not shipped.</t>
+          <t>The firm's own About/team page publishes individual emails including 'Matt@classvipartners.com' (and 'dalyce@classvipartners.com') alongside the general familyoffice@classvipartners.com. Published individual address; not independently provider-verified.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://wfo.am/contact-us/ (firm switchboard, not a personal line)</t>
+          <t>https://cvafamilyoffice.com/ (main office line, 101 University Blvd, Denver; firm switchboard, not a personal line)</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/07931194/officers</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr"/>
+          <t>https://www.classvipartners.com/our-team/matt-blackburn/ ; https://classvifamilyoffice.com/about/ ; https://www.getwarmer.com/firms/class-vi-family-office-llc</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3871,7 +4970,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Address published on the firm's own site with local-part matching the named principal (Nicholas David Stenger).</t>
+          <t>No individual email published on the firm site; contact is via a Calendly link (calendly.com/nicholasstenger/intro-meeting) rather than a published email address. No broker emails accepted.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -4609,46 +5708,54 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UKCH-10876208</t>
+          <t>SFO-dfo-management-dell</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SHA FAMILY OFFICE LTD</t>
+          <t>DFO Management, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>press</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Companies House 10876208 (Private limited company); inc. 20 July 2017</t>
+          <t>Identified via known UHNW individual (Michael Dell) -&gt; family office entity. Confirmed as Dell's single-family office by the firm's own site (dellfamilyoffice.com) and confirmed as an SEC 13F filer via EDGAR full-text search (13F-HR filed under Michael &amp; Susan Dell Foundation, managed by DFO Management, CIK 0001599858).</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/10876208</t>
+          <t>https://www.dellfamilyoffice.com/about</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Mr Sharnpreet Singh Buttar); firm carries a fund-management/investment SIC (64205 - Activities of financial services holding companies). Single-family control of an investment vehicle = single-family office.</t>
+          <t>Firm site states DFO is 'the private investment firm for Dell Technologies Founder &amp; CEO Michael Dell and his family'; launched 1998 as MSD Capital, restructured to DFO Management at end of 2022. Single-family (Dell) only.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Mr Sharnpreet Singh Buttar); firm carries a fund-management/investment SIC (64205 - Activities of financial services holding companies). Single-family control of an investment vehicle = single-family office.</t>
+          <t>SEC EDGAR 13F-HR filings (CIK 0001599858, period ending 2026-03-31, filed 2026-05-15) plus dedicated family-office website.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed; widely reported as tens of billions tied to Michael Dell's fortune.</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Beneficial owner and namesake; the family office exists to manage his and his family's capital.</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
           <t>unresolved</t>
@@ -4657,52 +5764,64 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>https://efts.sec.gov/LATEST/search-index?q=%22DFO+Management%22&amp;forms=13F-HR</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UKCH-15240886</t>
+          <t>SFO-bayshore-global-brin</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FREEDMAN FAMILY OFFICE</t>
+          <t>Bayshore Global Management, LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>press</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Companies House 15240886 (Private unlimited company); inc. 27 October 2023</t>
+          <t>Identified via known UHNW individual (Sergey Brin) -&gt; family office entity. Confirmed as Brin's single-family office by Bloomberg reporting (2026-04-23, 'Sergey Brin's Family Office Absorbs Nexus NeuroTech Brain-Health VC Fund') and Wikipedia.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/15240886</t>
+          <t>https://www.bloomberg.com/news/articles/2026-04-23/sergey-brin-s-family-office-takes-over-brain-focused-vc-fund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+          <t>Described consistently as the single-family office of Google co-founder Sergey Brin; founded 2005; allocates across public/private markets, real estate and philanthropic vehicles.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+          <t>Bloomberg news coverage naming it Sergey Brin's family office; Wikipedia entry; multiple family-office databases.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Press reports estimate over $100bn tied to Brin's Alphabet stake; not independently disclosed.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Beneficial owner; office manages his assets. Day-to-day led by CEO George Pavlov and CIO Marie Young per press.</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
           <t>unresolved</t>
@@ -4711,52 +5830,64 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/articles/2026-04-23/sergey-brin-s-family-office-takes-over-brain-focused-vc-fund</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>UKCH-11031775</t>
+          <t>SFO-hillspire-schmidt</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RALPH FAMILY OFFICE LIMITED</t>
+          <t>Hillspire, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>press</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Companies House 11031775 (Private limited company); inc. 25 October 2017</t>
+          <t>Identified via known UHNW individual (Eric Schmidt) -&gt; family office entity. Confirmed as Schmidt's single-family office by CNBC reporting (CNBC 'Inside Wealth Family Office 15', 2026-02-12, and 2025-01-21 piece on 22 AI startup investments).</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/11031775</t>
+          <t>https://www.cnbc.com/2025/01/21/eric-schmidts-family-office-invests-ai-startups.html</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Melanie Lynette Ralph; Mr Jan De Ridder Ralph); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+          <t>Described by CNBC and family-office databases as the single-family office established by former Google CEO Eric Schmidt and his wife Wendy Schmidt (founded 2006).</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Melanie Lynette Ralph; Mr Jan De Ridder Ralph); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+          <t>CNBC news coverage naming Hillspire as Eric Schmidt's family office and ranking it the most active U.S. family office for 2025 dealmaking.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Not disclosed.</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Beneficial owner and namesake; office run day-to-day by President Ken Goldman per press.</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
           <t>unresolved</t>
@@ -4765,8 +5896,702 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>https://www.cnbc.com/2026/02/12/inside-wealth-family-office-15.html</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SFO-blue-pool-capital-tsai</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Blue Pool Capital Limited (13F filer: Blue Pool Management Ltd.)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Identified via known UHNW individual (Joseph Tsai, Alibaba co-founder) and via SEC 13F filer with a neutral name. Confirmed as an SEC 13F filer (Blue Pool Management Ltd., CIK 0001675855, HQ Causeway Bay Hong Kong) and confirmed as Tsai's family office by Crain Currency / Caproasia reporting.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.caproasia.com/2024/09/19/alibaba-co-founder-billionaire-joseph-tsai-joins-investor-consortium-to-buy-vineyards-in-france-burgundy-another-investor-in-group-is-oliver-weisberg-who-is-ceo-of-joseph-tsai-family-office-blue-po/</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Repeatedly described as the family office of Alibaba co-founder Joe Tsai; oversees the Tsai family's investments and operating assets (incl. Brooklyn Nets, LAFC).</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>SEC EDGAR 13F-HR filings (Blue Pool Management Ltd., CIK 0001675855; latest 2026-05-15, HQ 25/F Hysan Place, 500 Hennessy Road, Causeway Bay) plus Crain Currency/Caproasia press naming it Joe Tsai's family office.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Press estimate (Caproasia/Crain Currency, 2022-2026); not an official disclosure.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Beneficial owner; founded the office in 2004/2015. Day-to-day CEO is Oliver Weisberg.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>https://data.sec.gov/submissions/CIK0001675855.json</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SFO-mousse-partners-wertheimer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Mousse Partners Limited (part of Mousse Investments Limited)</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Identified via known UHNW family (Wertheimer, owners of Chanel) -&gt; family office entity. Confirmed as the Wertheimer family office by Bloomberg ('Family office for $90 billion fortune reshapes consumer bets') and Wikipedia.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/professional/insights/trading/family-office-for-90-billion-fortune-reshapes-consumer-bets/</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Described as the family office managing the wealth of Alain and Gerard Wertheimer, owners of Chanel; founded 1991 by Charles Heilbronn (Chanel executive and half-brother of the Wertheimers).</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Bloomberg feature and Wikipedia identify Mousse Partners as the Wertheimer family office; firm site describes it as the investment division of Mousse Investments Limited.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Press associates the family fortune at ~$90-100bn; this is the Wertheimer net worth, not a disclosed AUM figure for Mousse.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Founder and head of the office; Chanel executive and half-brother of owners Alain and Gerard Wertheimer.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/professional/insights/trading/family-office-for-90-billion-fortune-reshapes-consumer-bets/</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SFO-kirkbi-kristiansen</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>KIRKBI A/S</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Identified via known UHNW family (Kirk Kristiansen, owners of LEGO) -&gt; holding/family office. Confirmed as the Kristiansen single-family office by KIRKBI's own website and Wikipedia; a registered Danish company (A/S).</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://www.kirkbi.com/about-us/family-ownership/</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Established 1 April 1995 as the family office/holding for the Kirk Kristiansen family (owners of the LEGO Group); owns 75% of the LEGO Group and 47.5% of Merlin Entertainments. Single-family.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>KIRKBI's own site (family-ownership page), Wikipedia, and Danish corporate registration as KIRKBI A/S.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Press figure for the family's wealth controlled by KIRKBI; total company equity/portfolio larger and not fully disclosed here.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>CEO and top investment decision-maker of KIRKBI; family chair is Thomas Kirk Kristiansen (assumed board chair May 2023); CIO is Thomas Lau Schleicher.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>https://www.kirkbi.com/press-releases/2025/kirkbi-climate-invests-in-highview/</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SFO-tethys-invest-bettencourt</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tethys Invest SAS (Tethys SAS group)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Identified via known UHNW family (Bettencourt Meyers, largest shareholder of L'Oreal) -&gt; family office. Confirmed as the Bettencourt Meyers single-family office by The National and Caproasia reporting and the firm's own site (tethys.fr).</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://www.thenationalnews.com/business/money/2023/03/13/billionaires-loreal-heir-names-new-head-of-family-office/</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Described as the single-family office managing the assets of the Bettencourt Meyers family, majority shareholder of L'Oreal; Tethys Invest is the entrepreneurial-investment subsidiary.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>The National and Caproasia press naming Tethys as the Bettencourt family office; firm's own website.</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Press figure for total family assets (dominated by the L'Oreal stake); Tethys Invest deploys &gt;EUR 3bn of direct-investment capital.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Head of the family's investment firm (Tethys Invest) and, per 2025 press, appointed to the L'Oreal board seat area of the family; family chair of Tethys is Francoise Bettencourt Meyers, CEO of Tethys is Jean-Pierre Meyers.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>https://www.caproasia.com/2025/02/08/loreal-heiress-france-billionaire-francoise-bettencourt-meyers-age-71-with-76-billion-fortune-starts-family-succession-with-retirement-from-loreal-board-as-vice-chairman-son-jean-victo/</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SFO-cofra-holding-brenninkmeijer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>COFRA Holding AG</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Identified via known UHNW family (Brenninkmeijer, owners of C&amp;A) -&gt; family holding/office. Confirmed by Crain Currency and the firm's own site as the Brenninkmeijer family's Zug-based holding; leadership verified on cofraholding.com.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://www.craincurrency.com/family-office-management/secretive-brenninkmeijer-family-behind-ca-opens-39-billion-retail-empire</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Established 2001 in Zug to coordinate the Brenninkmeijer family's global businesses and investments; a single-family-owned holding with subsidiaries C&amp;A (retail), Redevco (real estate), Bregal (PE) and Anthos (asset management).</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Crain Currency reporting on the family's ~$39bn empire; COFRA's own leadership/governance page listing the family-dominated board.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Reported total group asset base (Crain Currency and familyofficehub).</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Family-member chairman since 2018 (former CEO of COFRA, C&amp;A Europe and Anthos); group CEO is Boudewijn Beerkens, CFO Florian Brenninkmeyer (from 2025).</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>https://www.cofraholding.com/en/newsroom/latest-news/2025/redevco-closes-landmark-475m-loan-investment-for-new-real-estate-debt-platform/</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SFO-athos-strungmann</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Athos Service GmbH (family investment entity Athos KG)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Identified via known UHNW family (Strungmann brothers, BioNTech's largest shareholders) -&gt; family office. Confirmed as their single-family office by Forbes and multiple family-office trade sources; recent dated direct investments corroborate activity.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.forbes.com/sites/paulwestall/2021/08/24/the-family-office-saving-lives-boosting-the-economy-and-making-billions/</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Described as the single-family office of twins Andreas and Thomas Strungmann (who founded generics maker Hexal); anchor and largest shareholder of BioNTech (~43.5%).</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Forbes and biotech/family-office trade press naming Athos as the Strungmann single-family office; documented anchor investment in BioNTech.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Not disclosed; dominated by the BioNTech stake (~43.5%).</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Beneficial owner (with twin brother Thomas Strungmann) of the family office; jointly direct its investments.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>https://familyofficehub.io/blog/athos-family-office-invests-in-aavantgarde-bios-141m-series-b/</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SFO-premji-invest</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Premji Invest</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Identified via known UHNW individual (Azim Premji, Wipro founder) -&gt; family office. Confirmed as his family office by The Arc and family-office databases; recent dated deals corroborate active investing.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://www.thearcweb.com/article/wipro-azim-premji-invest-family-office-tk-kurien-0clyngtMEXrGHBNX</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Described as the private investment office managing the portfolio of Wipro founder Azim Premji and family across public equities, PE and venture; founded 2006, offices in Bengaluru and Menlo Park.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>The Arc and multiple family-office databases identify Premji Invest as Azim Premji's family office; firm website.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>The Arc reporting that the family office crossed $10bn in managed assets.</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Chief executive and top investment decision-maker of the office (former Wipro CEO); family principal is Azim Premji; U.S. office led by Sandesh Patnam.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>https://tracxn.com/d/private-equity/premjiinvest/__a9W9DN9hd7WxIGfm5z8PuA6IrDlu-VIas8-t59BU6xw</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SFO-catamaran-ventures-murthy</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Catamaran Management Services Pvt. Ltd. (Catamaran Ventures)</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Identified via known UHNW individual (N.R. Narayana Murthy, Infosys founder) -&gt; family office. Confirmed as his single-family office by Bloomberg and the firm's own site; described as investing permanent capital with no external LPs.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/articles/2025-08-26/family-office-to-billionaire-murthy-warns-on-startup-valuations</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Firm describes itself as a single-family office investing permanent capital with no external limited partners, managing the assets of Narayana Murthy and family.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Bloomberg reporting naming it the family office of billionaire Narayana Murthy; firm's own 'About' page stating single-family-office / permanent-capital structure.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Not disclosed.</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Founder and ultimate principal; firm led operationally by Chairman M.D. Ranganath (ex-Infosys CFO) and President Deepak Padaki.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/articles/2025-08-26/family-office-to-billionaire-murthy-warns-on-startup-valuations</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>UKCH-10876208</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SHA FAMILY OFFICE LTD</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>uk-companies-house</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Companies House 10876208 (Private limited company); inc. 20 July 2017</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/10876208</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Mr Sharnpreet Singh Buttar); firm carries a fund-management/investment SIC (64205 - Activities of financial services holding companies). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Mr Sharnpreet Singh Buttar); firm carries a fund-management/investment SIC (64205 - Activities of financial services holding companies). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>UKCH-15240886</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>FREEDMAN FAMILY OFFICE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>uk-companies-house</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Companies House 15240886 (Private unlimited company); inc. 27 October 2023</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/15240886</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>UKCH-11031775</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>RALPH FAMILY OFFICE LIMITED</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>uk-companies-house</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Companies House 11031775 (Private limited company); inc. 25 October 2017</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/11031775</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Melanie Lynette Ralph; Mr Jan De Ridder Ralph); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Melanie Lynette Ralph; Mr Jan De Ridder Ralph); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4779,7 +6604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E135"/>
+  <dimension ref="A1:E136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7550,18 +9375,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Timonier Family Office, LTD.</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>firm-qualification</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
+          <t>principal_email</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>laura@tarbox.com</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>email not found at cited source on re-fetch (https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf); downgraded verified-&gt;unverified</t>
         </is>
       </c>
     </row>
@@ -7573,7 +9402,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>TrustBank</t>
+          <t>Timonier Family Office, LTD.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7607,7 +9436,7 @@
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -7619,7 +9448,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>UNITA FAMILY OFFICE UK LIMITED</t>
+          <t>TrustBank</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -7630,7 +9459,7 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -7642,7 +9471,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>UR FAMILY OFFICE MANAGEMENT SERVICES LTD</t>
+          <t>UNITA FAMILY OFFICE UK LIMITED</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -7665,7 +9494,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>VASIL FAMILY OFFICE LLP</t>
+          <t>UR FAMILY OFFICE MANAGEMENT SERVICES LTD</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -7688,7 +9517,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>VPR Management LLC</t>
+          <t>VASIL FAMILY OFFICE LLP</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -7722,7 +9551,7 @@
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -7734,7 +9563,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>VSTAR LONDON FAMILY OFFICE LTD</t>
+          <t>VPR Management LLC</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -7745,7 +9574,7 @@
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -7757,7 +9586,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Veritable, L.P.</t>
+          <t>VSTAR LONDON FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -7791,7 +9620,7 @@
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -7803,7 +9632,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Virtus Family Office LLC</t>
+          <t>Veritable, L.P.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -7814,7 +9643,7 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -7826,7 +9655,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>WEYBRIDGE FAMILY OFFICE SERVICES LIMITED</t>
+          <t>Virtus Family Office LLC</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -7849,7 +9678,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Wealthgate Family Office, LLC</t>
+          <t>WEYBRIDGE FAMILY OFFICE SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -7872,7 +9701,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Wilmington Savings Fund Society, FSB</t>
+          <t>Wealthgate Family Office, LLC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -7905,6 +9734,29 @@
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Wilmington Savings Fund Society, FSB</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
         <is>
           <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
@@ -7921,7 +9773,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -7957,7 +9809,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>43%</t>
         </is>
       </c>
     </row>
@@ -7972,32 +9824,47 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Total qualified in store</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>24</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
-    </row>
+          <t>26%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>11</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>Total qualified in store</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>35</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Selected into final</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>24</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="B7" t="n">
+        <v>35</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/family_office_dataset.xlsx
+++ b/data/final/family_office_dataset.xlsx
@@ -429,14 +429,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W36"/>
+  <dimension ref="A1:W38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="59" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="39" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -686,12 +686,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEC13F-0001938970</t>
+          <t>SEC13F-0001802084</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Callan Family Office, LLC</t>
+          <t>CVA Family Office, LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -699,45 +699,45 @@
           <t>MFO</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>None (owner-operated MFO; part of the Class VI Partners group co-founded by Chris Younger and David Tolson). Not tied to a single client family.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://callanfamilyoffice.com/</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/callan-family-office</t>
-        </is>
-      </c>
+          <t>https://classvifamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callan Family Office is a Radnor, PA-based multi-family office founded in February 2022 by former Abbot Downing / Wells Fargo ultra-high-net-worth executives, using a brand-licensing partnership with institutional-consulting firm Callan LLC. It serves multiple ultra-wealthy families (minimum ~$50M, average ~$100M) and grew past $5B in assets within two years. It operates on a partnership model providing investment management and integrated family-office services.</t>
+          <t>Denver-based multi-family office and SEC-registered investment adviser, formerly 'CVA Family Office, LLC' and now operating as 'Class VI Family Office, LLC', part of the Class VI Partners group. Advises entrepreneurs, business owners and executives on wealth planning, liquidity-event planning and investment management on a 1:1 client:advisor model.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Institutional-quality, goals-based investment management for UHNW families, leveraging the Callan LLC investment-consulting relationship for manager research/asset allocation; open-architecture, partnership-driven advice.</t>
+          <t>Serving entrepreneurs and business owners around liquidity events; integrated wealth planning + discretionary investment management aligned to each family's goals.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Diversified multi-asset-class portfolios (public and private markets, alternatives) tailored to UHNW families; not sector-specialized.</t>
+          <t>Diversified discretionary wealth/investment management for HNW entrepreneurs; no single-sector focus disclosed.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>~$5B AUM as of March 2024 (reported crossing $5B two years after 2022 founding).</t>
+          <t>~$222.27 million regulatory AUM (across ~43 accounts)</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Radnor</t>
+          <t>DENVER</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -747,22 +747,22 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Jack Ginter (John Ginter)</t>
+          <t>Matt Blackburn</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Chief Executive Officer &amp; Founding Partner</t>
+          <t>Managing Partner / Managing Director, Class VI Family Office (co-founder)</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/jack-ginter-70276773/</t>
+          <t>https://www.linkedin.com/in/mattblackburnclassvi/</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>jginter@callanfo.com</t>
+          <t>matt@classvipartners.com</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -772,17 +772,17 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>267-250-2036</t>
+          <t>303-243-5619</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>Reported crossing $5B AUM in March 2024, ~2 years after a Feb 2022 launch; built via a Callan LLC brand-licensing/partnership deal and Abbot Downing/Wells Fargo advisor recruitment; featured in RIABiz and a Diamond Consultants podcast.</t>
+          <t>Rebranded from 'CVA Family Office' to 'Class VI Family Office'; established as RIA Sept 2016; operates on a 1:1 client:advisor model under Class VI Partners</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2022-02 (founding); 2024-03 (crossed $5B AUM); 2024-04-09 (RIABiz feature)</t>
+          <t>2016-09 (RIA inception); rebrand to Class VI Family Office (ongoing)</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -792,41 +792,61 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Uses the 'family office' label but is structurally an UHNW multi-family-office RIA with a client base, not a single family's office. 'John Ginter' (13F signatory) and 'Jack Ginter' (CEO) are the same person. AUM figure is a March 2024 press number and may be higher now.</t>
+          <t>Legal 13F filer name remains 'CVA Family Office, LLC' but the brand/website is now 'Class VI Family Office' (classvifamilyoffice.com); older cvafamilyoffice.com domain was unreachable during research. Principal email is on the classvipartners.com domain, not a family-office-specific domain. Chris Younger is CEO of the broader Class VI Partners; Matt Blackburn selected as the family-office investment/advisory lead.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEC13F-0001596197</t>
+          <t>SEC13F-0001845066</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Intrepid Family Office Llc</t>
+          <t>Collective Family Office Llc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SFO</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+          <t>MFO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>None (owner-operated MFO). Founded 2019 by David S. Sivel, formerly Central PA Market Manager for BNY Mellon and Managing Director of Wealth &amp; Institutional Services at Wilmington Trust. Not tied to a single client family.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://www.collectivefamilyoffice.com/</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>York, Pennsylvania-based multi-family office and SEC-registered investment adviser founded in 2019, focused on Central Pennsylvania families with deep regional ties. Provides discretionary portfolio management, wealth management, financial and estate planning to high-net-worth families, with a $1,000,000 minimum. Principals: David Sivel (Founder/CEO), Brian Luster (CIO), Trevor Hoffman (COO).</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Discretionary portfolio management allocating primarily across ETFs and mutual funds (largest reported 13F holding is the JPMorgan Municipal ETF); goals-based wealth management with no single-sector focus disclosed.</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>~$446.4 million discretionary AUM across ~127 clients (Form ADV, 2025-03-03); ~$435.9M in 13F securities (Q4 2025); aggregators (FINTRX) report ~$533M</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Greenwich</t>
+          <t>YORK</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -836,102 +856,110 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Matt Dino</t>
+          <t>David S. Sivel</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
+          <t>Founder &amp; Chief Executive Officer (CFP, CPFA); Principal</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/david-s-sivel-cfp%C2%AE-ab078811/</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>david.sivel@collectivefo.com</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>(203) 862-3372</t>
+          <t>717-893-5056</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>13F portfolio approx $0.12B across 38 US-listed positions as of 03-31-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing). Top holdings: SPDR GOLD TR ($17.21B); ISHARES TR ($13.57B); VANGUARD INDEX FDS ($12.83B); ABRDN PLATINUM ETF TRUST ($7.13B)</t>
+          <t>SEC-registered/founded 2019; $1M account minimum; eMoney Advisor-enabled advisory; Central PA family focus; three-principal structure (CEO/CIO/COO)</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>03-31-2026</t>
+          <t>2019 (firm inception); AUM ~$446M as of 2025-03-03; 13F ~$436M Q4 2025</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>SFO inferred from unregistered-adviser + 13F + family-office name; the specific family is not yet named (pending research pass).</t>
+          <t>Principal chosen as founder/CEO David Sivel; the dedicated investment decision-maker is co-principal Brian Luster (CIO). 'Family office' refers to the multi-family advisory model, not a single client family. Corporate LinkedIn page not confirmed with a URL.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEC13F-0001536411</t>
+          <t>SEC13F-0001938970</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Duquesne Family Office LLC</t>
+          <t>Callan Family Office, LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SFO</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Druckenmiller family (Stanley F. Druckenmiller)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
+          <t>MFO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://callanfamilyoffice.com/</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/duquesne-family-office-llc</t>
+          <t>https://www.linkedin.com/company/callan-family-office</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Duquesne Family Office is the private investment vehicle of billionaire investor Stanley Druckenmiller, established in 2010 after he returned outside capital and wound down his hedge fund Duquesne Capital Management (named for a park in his native Pittsburgh). It manages the Druckenmiller family's capital across public equities, and reportedly private/venture and credit positions, using a concentrated, macro-driven approach. It has no external clients.</t>
+          <t>Callan Family Office is a Radnor, PA-based multi-family office founded in February 2022 by former Abbot Downing / Wells Fargo ultra-high-net-worth executives, using a brand-licensing partnership with institutional-consulting firm Callan LLC. It serves multiple ultra-wealthy families (minimum ~$50M, average ~$100M) and grew past $5B in assets within two years. It operates on a partnership model providing investment management and integrated family-office services.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Concentrated, top-down macro investing with high conviction and significant position turnover; opportunistic rotation across sectors and asset classes based on macroeconomic views. Public-equity book is typically 20-40 concentrated positions.</t>
+          <t>Institutional-quality, goals-based investment management for UHNW families, leveraging the Callan LLC investment-consulting relationship for manager research/asset allocation; open-architecture, partnership-driven advice.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Broad/opportunistic across technology, healthcare/biotech, energy, consumer, financials and industrials; recent 13Fs (2025) show large positions in names like Natera, Insmed, Amazon, Teva and Woodward.</t>
+          <t>Diversified multi-asset-class portfolios (public and private markets, alternatives) tailored to UHNW families; not sector-specialized.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>13F US-listed equities ~$4.06B as of 2025-09-30 (Q3 2025) and ~$4.49B as of Q4 2025 -- a FLOOR, not total AUM. Total family-office AUM is not publicly disclosed; Druckenmiller's personal net worth is estimated at ~$11B (Bloomberg Billionaires Index, Jan 2025) and he ranks on the Forbes 2026 Billionaires list.</t>
+          <t>~$5B AUM as of March 2024 (reported crossing $5B two years after 2022 founding).</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Radnor</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -941,78 +969,110 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Stanley F. Druckenmiller</t>
+          <t>Jack Ginter (John Ginter)</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Founder, Chairman &amp; CEO (Portfolio Manager)</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+          <t>Chief Executive Officer &amp; Founding Partner</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jack-ginter-70276773/</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>jginter@callanfo.com</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>212-830-6500</t>
+          <t>267-250-2036</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>Q3 2025 13F filed (portfolio ~$4.06B, 65 holdings); Q4 2025 13F portfolio rose to ~$4.49B with ~35 significant positions; Q1 2025 13F showed cuts and new tech/energy adds (~$3.06B, 52 holdings).</t>
+          <t>Reported crossing $5B AUM in March 2024, ~2 years after a Feb 2022 launch; built via a Callan LLC brand-licensing/partnership deal and Abbot Downing/Wells Fargo advisor recruitment; featured in RIABiz and a Diamond Consultants podcast.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2025-11-14 (Q3 2025 13F filing, as of 2025-09-30); Q4 2025 (as of 2025-12-31); 2025-05-15 (Q1 2025 13F, as of 2025-03-31)</t>
+          <t>2022-02 (founding); 2024-03 (crossed $5B AUM); 2024-04-09 (RIABiz feature)</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Total AUM is not officially disclosed; the 13F equity value is only US-listed long equity positions (a floor). The LinkedIn company page may not be firm-operated. No individual email is published anywhere; none provided. Sue Meng (13F signatory) is General Counsel, not the investment decision-maker.</t>
+          <t>Uses the 'family office' label but is structurally an UHNW multi-family-office RIA with a client base, not a single family's office. 'John Ginter' (13F signatory) and 'Jack Ginter' (CEO) are the same person. AUM figure is a March 2024 press number and may be higher now.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEC13F-0001683689</t>
+          <t>SEC13F-0002135110</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kopp Family Office, LLC</t>
+          <t>Pioneer Family Office, LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SFO</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>MFO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>None (owner-operated group). Part of the Pioneer Group / Pioneer Wealth Management Group co-founded in 1986 by Omer Galin. Serves multiple international client families; not a single-family vehicle.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://www.piowealth.com/PFO/who-we-are</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>North Miami Beach, Florida-based multi-family office and SEC-registered investment adviser, the US arm of Pioneer Wealth Management Group (founded in Israel in 1986). Provides integrated, conflict-free wealth and investment management to international ultra-high-net-worth families across five continents, with operations spanning North America, South America and Israel.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Independent, conflict-free (no proprietary funds) integrated wealth management for globally mobile UHNW families; capital-allocator model.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Discretionary portfolio management including bond/fixed-income portfolio management and outside-manager selection for individuals/families and institutions; diversified, no single-sector focus disclosed.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>~$957 million AUM (FINTRX)</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Minnetonka</t>
+          <t>NORTH MIAMI BEACH</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1022,56 +1082,64 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>John P. Flakne</t>
+          <t>Aviram Nahum</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Chief Financial Officer</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
+          <t>Managing Partner, Pioneer Family Office; Executive Director, Pioneer Group; Investment Committee &amp; Steering Committee member</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aviram-nahum-450600243/</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>avin@piowealth.com</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>952-841-0450</t>
+          <t>+1 305 935 5502</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>13F portfolio approx $0.16B across 29 US-listed positions as of 06-30-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing)</t>
+          <t>Pioneer Group founded in Israel 1986; SEC-registered 2019; international UHNW clientele across five continents; recognized 'Best Israel UHNW Family Financial Planning Firm 2019' (Acquisition International)</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>06-30-2026</t>
+          <t>1986 (Pioneer Group founding); 2019 (SEC registration; award); AUM ~$957M (recent)</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>B+</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>SFO inferred from unregistered-adviser + 13F + family-office name; the specific family is not yet named (pending research pass).</t>
+          <t>Two plausible principals: firm co-founder/leader Omer Galin (Israel-based, omerg@piowealth.com, +972-9-961-1300) and US Managing Partner Aviram Nahum. Aviram Nahum selected as the US investment-committee decision-maker for the North Miami Beach SEC-registered entity. 'Family office' denotes a multi-family model, not a single client family.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEC13F-0001889527</t>
+          <t>SEC13F-0001596197</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Louis-Dreyfus Family Office LLC</t>
+          <t>Intrepid Family Office Llc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1079,36 +1147,16 @@
           <t>SFO</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Louis-Dreyfus family -- specifically the American branch of Gerard 'William' Louis-Dreyfus (1932-2016), longtime chairman of Louis Dreyfus Company's US arm and father of actress Julia Louis-Dreyfus (INFERRED from co-location with LDC's Wilton HQ and the family/geography; not definitively documented).</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Louis-Dreyfus Family Office LLC is a small private single-family office in Wilton, CT, associated with the American branch of the Louis-Dreyfus family (the commodities-trading dynasty). It is co-located with Louis Dreyfus Company's US headquarters at 10 Westport Road and manages family capital; its SEC 13F disclosed only about five holdings worth ~$65M. It is NOT the Louis Dreyfus Company commodities business itself.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Not publicly documented. The limited 13F holdings (broad index funds VXUS/VTIAX and ITOT plus a couple of small single-name positions) suggest a conservative, largely passive/index-oriented public-markets allocation typical of a family office holding book, but this is inferred, not stated.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Public 13F book was dominated by broad-market and international index funds (Vanguard Total International, iShares Core S&amp;P Total US Market ETF) plus small individual equity positions (e.g., Celularity, New Relic, Lovesac). Not sector-focused.</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>13F US-listed equities ~$64.7M as of 2022-09-30 (Q3 2022, 5 holdings) -- a floor and likely a small slice of total family wealth. Total AUM not disclosed. Business directories estimate ~$390K annual revenue / ~4 employees.</t>
-        </is>
-      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Wilton</t>
+          <t>Greenwich</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1123,12 +1171,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>W. Thomas Wingertzahn</t>
+          <t>Matt Dino</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Chief Financial Officer (13F signatory / operational head)</t>
+          <t>Chief Financial Officer</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -1140,17 +1188,17 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>203-762-6134</t>
+          <t>(203) 862-3372</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>No recent public activity found. The most recent SEC 13F on file is Q3 2022; no 2023-2025 13F filings surfaced, which may indicate the equity book fell below the 13F reporting threshold or the office stopped filing.</t>
+          <t>13F portfolio approx $0.12B across 38 US-listed positions as of 03-31-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing). Top holdings: SPDR GOLD TR ($17.21B); ISHARES TR ($13.57B); VANGUARD INDEX FDS ($12.83B); ABRDN PLATINUM ETF TRUST ($7.13B)</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2022-11-10 (last 13F filing, holdings as of 2022-09-30)</t>
+          <t>03-31-2026</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1160,19 +1208,19 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>ENTITY-CONFUSION RISK: 'Louis-Dreyfus Family Office LLC' is NOT the Louis Dreyfus Company (LDC) commodities firm, though it shares the Wilton CT 10 Westport Road address. The specific family member/branch is INFERRED (Gerard 'William' Louis-Dreyfus's American branch; heirs include Julia Louis-Dreyfus and half-sisters Phoebe and Emma) and not definitively confirmed by a primary source; family_affiliation should be treated as probable, not certain. The true family investment decision-maker is undetermined; Wingertzahn is the CFO/signatory, reported as principal only for lack of a documented alternative. No website, no LinkedIn, no published email. 13F filings appear to have lapsed after 2022.</t>
+          <t>SFO inferred from unregistered-adviser + 13F + family-office name; the specific family is not yet named (pending research pass).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UKCH-12706913</t>
+          <t>SEC13F-0001536411</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Francis Family Office Limited</t>
+          <t>Duquesne Family Office LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1182,68 +1230,80 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Francis family (Ben Francis, founder/CEO of Gymshark)</t>
+          <t>Druckenmiller family (Stanley F. Druckenmiller)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/duquesne-family-office-llc</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Personal family-office / holding vehicle of Ben Francis, billionaire founder and majority owner of fitness-apparel brand Gymshark; holds part of his Gymshark shareholding.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Duquesne Family Office is the private investment vehicle of billionaire investor Stanley Druckenmiller, established in 2010 after he returned outside capital and wound down his hedge fund Duquesne Capital Management (named for a park in his native Pittsburgh). It manages the Druckenmiller family's capital across public equities, and reportedly private/venture and credit positions, using a concentrated, macro-driven approach. It has no external clients.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Concentrated, top-down macro investing with high conviction and significant position turnover; opportunistic rotation across sectors and asset classes based on macroeconomic views. Public-equity book is typically 20-40 concentrated positions.</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Holding company (concentrated Gymshark equity stake)</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>Broad/opportunistic across technology, healthcare/biotech, energy, consumer, financials and industrials; recent 13Fs (2025) show large positions in names like Natera, Insmed, Amazon, Teva and Woodward.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>13F US-listed equities ~$4.06B as of 2025-09-30 (Q3 2025) and ~$4.49B as of Q4 2025 -- a FLOOR, not total AUM. Total family-office AUM is not publicly disclosed; Druckenmiller's personal net worth is estimated at ~$11B (Bloomberg Billionaires Index, Jan 2025) and he ranks on the Forbes 2026 Billionaires list.</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>West Midlands</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Benjamin David Francis</t>
+          <t>Stanley F. Druckenmiller</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Director &amp; 100% owner; Founder &amp; CEO of Gymshark</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/gymshark/</t>
-        </is>
-      </c>
+          <t>Founder, Chairman &amp; CEO (Portfolio Manager)</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>212-830-6500</t>
+        </is>
+      </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>Renamed Ben Francis Ltd -&gt; Francis Family Office Ltd (2021); Ben Francis moved ~half his Gymshark stake into the vehicle; 2026 reporting he is seeking financing to buy back part of General Atlantic's Gymshark stake</t>
+          <t>Q3 2025 13F filed (portfolio ~$4.06B, 65 holdings); Q4 2025 13F portfolio rose to ~$4.49B with ~35 significant positions; Q1 2025 13F showed cuts and new tech/energy adds (~$3.06B, 52 holdings).</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2021-02-03 (rename); 2026-07 (buyback reporting)</t>
+          <t>2025-11-14 (Q3 2025 13F filing, as of 2025-09-30); Q4 2025 (as of 2025-12-31); 2025-05-15 (Q1 2025 13F, as of 2025-03-31)</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1253,19 +1313,19 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>No standalone website/LinkedIn/email for the FO itself — a private holding vehicle, not client-facing. Corporate secretary is a law-firm nominee, not the principal. Investment thesis/sectors not publicly disclosed.</t>
+          <t>Total AUM is not officially disclosed; the 13F equity value is only US-listed long equity positions (a floor). The LinkedIn company page may not be firm-operated. No individual email is published anywhere; none provided. Sue Meng (13F signatory) is General Counsel, not the investment decision-maker.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UKCH-07931194</t>
+          <t>SEC13F-0001683689</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wimmer Family Office Ltd</t>
+          <t>Kopp Family Office, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1273,59 +1333,39 @@
           <t>SFO</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Wimmer (Per Wimmer, Danish financier, founder of merchant bank Wimmer Financial)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://wfo.am/</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>London (Mayfair) family office established by Per Wimmer, a Danish financier, entrepreneur and author; associated with his corporate-advisory firm Wimmer Financial.</t>
-        </is>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Natural resources (mining, oil &amp; gas, green energy); real estate; infrastructure; aviation; shipping; space economy</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Minnetonka</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Mayfair</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Per Thanning Wimmer</t>
+          <t>John P. Flakne</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO, Wimmer Family Office</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>https://uk.linkedin.com/in/perwimmer</t>
-        </is>
-      </c>
+          <t>Chief Financial Officer</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
@@ -1334,17 +1374,17 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>+44 207 432 7575</t>
+          <t>952-841-0450</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>Per Wimmer resigned as director 2024-09-25; two new directors appointed same day (Aida Feriz, Joppe Sikma); FCA-authorised (FCA #665654)</t>
+          <t>13F portfolio approx $0.16B across 29 US-listed positions as of 06-30-2026 (floor on AUM; 13(f) equities only, unit-normalized from filing)</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2024-09-25 (director change)</t>
+          <t>06-30-2026</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1354,65 +1394,61 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Corrected task hint: principal is PER Wimmer, not 'Klaus Wimmer'. Per Wimmer resigned as registered director 2024-09-25 but remains named founder on the site; current directors appear operational/successor. Phone is switchboard. AUM/thesis not disclosed.</t>
+          <t>SFO inferred from unregistered-adviser + 13F + family-office name; the specific family is not yet named (pending research pass).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEC13F-0001802084</t>
+          <t>SEC13F-0001889527</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVA Family Office, LLC</t>
+          <t>Louis-Dreyfus Family Office LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>None (owner-operated MFO; part of the Class VI Partners group co-founded by Chris Younger and David Tolson). Not tied to a single client family.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://classvifamilyoffice.com/</t>
-        </is>
-      </c>
+          <t>Louis-Dreyfus family -- specifically the American branch of Gerard 'William' Louis-Dreyfus (1932-2016), longtime chairman of Louis Dreyfus Company's US arm and father of actress Julia Louis-Dreyfus (INFERRED from co-location with LDC's Wilton HQ and the family/geography; not definitively documented).</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Denver-based multi-family office and SEC-registered investment adviser, formerly 'CVA Family Office, LLC' and now operating as 'Class VI Family Office, LLC', part of the Class VI Partners group. Advises entrepreneurs, business owners and executives on wealth planning, liquidity-event planning and investment management on a 1:1 client:advisor model.</t>
+          <t>Louis-Dreyfus Family Office LLC is a small private single-family office in Wilton, CT, associated with the American branch of the Louis-Dreyfus family (the commodities-trading dynasty). It is co-located with Louis Dreyfus Company's US headquarters at 10 Westport Road and manages family capital; its SEC 13F disclosed only about five holdings worth ~$65M. It is NOT the Louis Dreyfus Company commodities business itself.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Serving entrepreneurs and business owners around liquidity events; integrated wealth planning + discretionary investment management aligned to each family's goals.</t>
+          <t>Not publicly documented. The limited 13F holdings (broad index funds VXUS/VTIAX and ITOT plus a couple of small single-name positions) suggest a conservative, largely passive/index-oriented public-markets allocation typical of a family office holding book, but this is inferred, not stated.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Diversified discretionary wealth/investment management for HNW entrepreneurs; no single-sector focus disclosed.</t>
+          <t>Public 13F book was dominated by broad-market and international index funds (Vanguard Total International, iShares Core S&amp;P Total US Market ETF) plus small individual equity positions (e.g., Celularity, New Relic, Lovesac). Not sector-focused.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>~$222.27 million regulatory AUM (across ~43 accounts)</t>
+          <t>13F US-listed equities ~$64.7M as of 2022-09-30 (Q3 2022, 5 holdings) -- a floor and likely a small slice of total family wealth. Total AUM not disclosed. Business directories estimate ~$390K annual revenue / ~4 employees.</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>DENVER</t>
+          <t>Wilton</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1422,42 +1458,34 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Matt Blackburn</t>
+          <t>W. Thomas Wingertzahn</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Managing Partner / Managing Director, Class VI Family Office (co-founder)</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/mattblackburnclassvi/</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>matt@classvipartners.com</t>
-        </is>
-      </c>
+          <t>Chief Financial Officer (13F signatory / operational head)</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>303-243-5619</t>
+          <t>203-762-6134</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>Rebranded from 'CVA Family Office' to 'Class VI Family Office'; established as RIA Sept 2016; operates on a 1:1 client:advisor model under Class VI Partners</t>
+          <t>No recent public activity found. The most recent SEC 13F on file is Q3 2022; no 2023-2025 13F filings surfaced, which may indicate the equity book fell below the 13F reporting threshold or the office stopped filing.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2016-09 (RIA inception); rebrand to Class VI Family Office (ongoing)</t>
+          <t>2022-11-10 (last 13F filing, holdings as of 2022-09-30)</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1467,110 +1495,90 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Legal 13F filer name remains 'CVA Family Office, LLC' but the brand/website is now 'Class VI Family Office' (classvifamilyoffice.com); older cvafamilyoffice.com domain was unreachable during research. Principal email is on the classvipartners.com domain, not a family-office-specific domain. Chris Younger is CEO of the broader Class VI Partners; Matt Blackburn selected as the family-office investment/advisory lead.</t>
+          <t>ENTITY-CONFUSION RISK: 'Louis-Dreyfus Family Office LLC' is NOT the Louis Dreyfus Company (LDC) commodities firm, though it shares the Wilton CT 10 Westport Road address. The specific family member/branch is INFERRED (Gerard 'William' Louis-Dreyfus's American branch; heirs include Julia Louis-Dreyfus and half-sisters Phoebe and Emma) and not definitively confirmed by a primary source; family_affiliation should be treated as probable, not certain. The true family investment decision-maker is undetermined; Wingertzahn is the CFO/signatory, reported as principal only for lack of a documented alternative. No website, no LinkedIn, no published email. 13F filings appear to have lapsed after 2022.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEC13F-0001599603</t>
+          <t>UKCH-12706913</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tarbox Family Office, Inc.</t>
+          <t>Francis Family Office Limited</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>None as a single client family; founder-owned firm (Laura Tarbox founder, CEO and principal owner). Namesake is the founder, not a served family.</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://tarbox.com/</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/tarboxfamilyoffice</t>
-        </is>
-      </c>
+          <t>Francis family (Ben Francis, founder/CEO of Gymshark)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Newport Beach, CA-based multi-family office and SEC-registered investment adviser founded in 1985 by Laura Tarbox, CFP. Fee-only firm serving 100+ HNW/UHNW client families (also charities, businesses, trusts/estates) with comprehensive financial planning, tax preparation and individualized investment management; $5M minimum, over $1B AUM. Also has a Scottsdale, AZ office.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Team-based, individualized asset allocation and investment management integrated with comprehensive financial and estate planning; fee-only fiduciary model.</t>
-        </is>
-      </c>
+          <t>Personal family-office / holding vehicle of Ben Francis, billionaire founder and majority owner of fitness-apparel brand Gymshark; holds part of his Gymshark shareholding.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Diversified asset-allocation / individualized investment management; no single-sector focus.</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Over $1 billion (100+ client families)</t>
-        </is>
-      </c>
+          <t>Holding company (concentrated Gymshark equity stake)</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>NEWPORT BEACH</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>West Midlands</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Laura Tarbox</t>
+          <t>Benjamin David Francis</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Founder, CEO &amp; principal owner (CFP)</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>laura@tarbox.com</t>
-        </is>
-      </c>
+          <t>Director &amp; 100% owner; Founder &amp; CEO of Gymshark</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gymshark/</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>unverified</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>(949) 721-2330</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Founded 1985; CFP since 1984; 100+ client families and &gt;$1B AUM; $5M account minimum; second office in Scottsdale, AZ; Laura Tarbox a frequent WSJ/NYT/LA Times media source</t>
+          <t>Renamed Ben Francis Ltd -&gt; Francis Family Office Ltd (2021); Ben Francis moved ~half his Gymshark stake into the vehicle; 2026 reporting he is seeking financing to buy back part of General Atlantic's Gymshark stake</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>1985 (founded); 1984 (Laura Tarbox CFP)</t>
+          <t>2021-02-03 (rename); 2026-07 (buyback reporting)</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1580,92 +1588,80 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Personal LinkedIn /in profile not located (only firm company page). Email captured from Laura Tarbox's public presentation PDF (matches firm domain) rather than the current bio page; treat as published-but-unverified.</t>
+          <t>No standalone website/LinkedIn/email for the FO itself — a private holding vehicle, not client-facing. Corporate secretary is a law-firm nominee, not the principal. Investment thesis/sectors not publicly disclosed.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEC13F-0002056106</t>
+          <t>UKCH-07931194</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stenger Family Office, LLC</t>
+          <t>Wimmer Family Office Ltd</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Stenger family (firm founded/led by Nick Stenger; the family has advised clients since 1981). The 'family' is the owner-operator, not a single client family.</t>
+          <t>Wimmer (Per Wimmer, Danish financier, founder of merchant bank Wimmer Financial)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.stengerfamilyoffice.com/</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/stenger-family-office</t>
-        </is>
-      </c>
+          <t>https://wfo.am/</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Naperville, IL-based multi-family office / independent fiduciary RIA led by founder-CEO Nick Stenger, offering financial planning, investment management, and (via related companies) tax preparation, estate strategies and insurance. Also has a Spring, TX office. ~$731M AUM; named a Forbes Best-in-State Wealth Advisor 2026.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Goals-based planning: assesses cash needs and upcoming goals, then builds customized portfolios.</t>
-        </is>
-      </c>
+          <t>London (Mayfair) family office established by Per Wimmer, a Danish financier, entrepreneur and author; associated with his corporate-advisory firm Wimmer Financial.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Core individual-stock portfolios and ETF-based asset-allocation portfolios; no single-sector focus.</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>~$731 million (as of 2026-06-30)</t>
-        </is>
-      </c>
+          <t>Natural resources (mining, oil &amp; gas, green energy); real estate; infrastructure; aviation; shipping; space economy</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>NAPERVILLE</t>
+          <t>London</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>Mayfair</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Nicholas David Stenger</t>
+          <t>Per Thanning Wimmer</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Founder &amp; Chief Executive Officer</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>nick.stenger@stengerfamilyoffice.com</t>
-        </is>
-      </c>
+          <t>Founder &amp; CEO, Wimmer Family Office</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/perwimmer</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>unresolved</t>
@@ -1673,17 +1669,17 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>630-912-8295</t>
+          <t>+44 207 432 7575</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>$731M AUM (2026-06-30); Forbes Best-in-State Wealth Advisor 2026; hosts 'The Nick Stenger Show' podcast; opened Spring, TX office</t>
+          <t>Per Wimmer resigned as director 2024-09-25; two new directors appointed same day (Aida Feriz, Joppe Sikma); FCA-authorised (FCA #665654)</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-06-30 (AUM date); 2026 (Forbes Best-in-State)</t>
+          <t>2024-09-25 (director change)</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1693,19 +1689,19 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Serves 1,200+ families 'of all net worth sizes' — a broad wealth-management RIA using family-office branding rather than a classic UHNW MFO; hence proof strength 'corroborated'. Personal LinkedIn /in profile not located (only company page and a Calendly slug for 'nicholasstenger'). No published individual email or direct phone line found.</t>
+          <t>Corrected task hint: principal is PER Wimmer, not 'Klaus Wimmer'. Per Wimmer resigned as registered director 2024-09-25 but remains named founder on the site; current directors appear operational/successor. Phone is switchboard. AUM/thesis not disclosed.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEC13F-0001731123</t>
+          <t>SEC13F-0001599603</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Biltmore Family Office, LLC</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1715,47 +1711,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Founder Chris Cecil is a great-grandson of George Vanderbilt (builder of the Biltmore Estate) and son of Asheville developer George Cecil; 'Biltmore' name derives from that Vanderbilt/Cecil family heritage. The firm serves many outside client families (MFO), not the Vanderbilt/Cecil family exclusively.</t>
+          <t>None as a single client family; founder-owned firm (Laura Tarbox founder, CEO and principal owner). Namesake is the founder, not a served family.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.biltmorefamilyoffice.com/</t>
+          <t>https://tarbox.com/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/biltmore-family-office-llc</t>
+          <t>https://www.linkedin.com/company/tarboxfamilyoffice</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Charlotte, NC-based multi-family office and SEC-registered investment adviser founded in 2008 by Chris Cecil. A collaborative/independent RIA to investment-oriented multi-generational families and institutions, providing investment management, asset allocation, investment-policy design, multi-generational and succession planning. ~$3.2-3.5B AUM.</t>
+          <t>Newport Beach, CA-based multi-family office and SEC-registered investment adviser founded in 1985 by Laura Tarbox, CFP. Fee-only firm serving 100+ HNW/UHNW client families (also charities, businesses, trusts/estates) with comprehensive financial planning, tax preparation and individualized investment management; $5M minimum, over $1B AUM. Also has a Scottsdale, AZ office.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Collaborative, investment-policy-driven management for multi-generational HNW/UHNW families and institutions.</t>
+          <t>Team-based, individualized asset allocation and investment management integrated with comprehensive financial and estate planning; fee-only fiduciary model.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Diversified public-equity/ETF portfolios; disclosed top 13F holdings include AAPL, IAU (gold), AVDX, ROBO, VV. No single-sector concentration.</t>
+          <t>Diversified asset-allocation / individualized investment management; no single-sector focus.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>~$3.2-3.5 billion (reported ~$3.47B regulatory AUM across ~951 accounts)</t>
+          <t>Over $1 billion (100+ client families)</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>CHARLOTTE</t>
+          <t>NEWPORT BEACH</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1765,38 +1761,38 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Chris Cecil</t>
+          <t>Laura Tarbox</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Founder, President &amp; CEO</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/chris-cecil-9701b818/</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr"/>
+          <t>Founder, CEO &amp; principal owner (CFP)</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>laura@tarbox.com</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>+1 704-248-5230</t>
+          <t>(949) 721-2330</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Founded 2008 by Chris Cecil (LLC organized 2013); ~$3.2-3.5B AUM across ~951 accounts, avg client ~$38M; Cecil chairs TIGER 21 Charlotte / Family Office groups</t>
+          <t>Founded 1985; CFP since 1984; 100+ client families and &gt;$1B AUM; $5M account minimum; second office in Scottsdale, AZ; Laura Tarbox a frequent WSJ/NYT/LA Times media source</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2008 (founding); 2013 (LLC organized)</t>
+          <t>1985 (founded); 1984 (Laura Tarbox CFP)</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1806,19 +1802,19 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Chris Cecil chosen as principal (founder/CEO); Rael Gorelick is Partner &amp; Head of Investments and would be the CIO-level investment lead. No published individual email located. AUM varies by source ($3.2B-$3.5B).</t>
+          <t>Personal LinkedIn /in profile not located (only firm company page). Email captured from Laura Tarbox's public presentation PDF (matches firm domain) rather than the current bio page; treat as published-but-unverified.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEC13F-0001039807</t>
+          <t>SEC13F-0002056106</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Boston Family Office Llc</t>
+          <t>Stenger Family Office, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1826,41 +1822,49 @@
           <t>MFO</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stenger family (firm founded/led by Nick Stenger; the family has advised clients since 1981). The 'family' is the owner-operator, not a single client family.</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.bosfam.com/</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>https://www.stengerfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/stenger-family-office</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>The Boston Family Office LLC is an independent, employee-owned registered investment adviser founded in 1996 and based in Boston, MA. It provides multi-family-office-style wealth management -- investment management, financial planning, and adviser selection -- to high-net-worth individuals, families and charitable organizations across roughly 789 accounts and ~$1.7-2.0B in assets. It is a multi-family/RIA firm rather than a single-family office.</t>
+          <t>Naperville, IL-based multi-family office / independent fiduciary RIA led by founder-CEO Nick Stenger, offering financial planning, investment management, and (via related companies) tax preparation, estate strategies and insurance. Also has a Spring, TX office. ~$731M AUM; named a Forbes Best-in-State Wealth Advisor 2026.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Client-tailored, diversified portfolio management for wealth preservation and growth across HNW households and institutions; discretionary management (769 of 789 accounts discretionary). Specific house investment philosophy not detailed publicly.</t>
+          <t>Goals-based planning: assesses cash needs and upcoming goals, then builds customized portfolios.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Diversified multi-asset wealth management (public equities, fixed income, funds); not sector-specialized. A partner sits on the board of fixed-income manager Breckinridge Capital Advisors.</t>
+          <t>Core individual-stock portfolios and ETF-based asset-allocation portfolios; no single-sector focus.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>~$1.7B AUM across 789 accounts (Form ADV/adviserinfo, 2024-2025); third-party profiles cite ~$1.9-2.02B. As of the most recent Form ADV (2024 filing cycle).</t>
+          <t>~$731 million (as of 2026-06-30)</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>NAPERVILLE</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1870,38 +1874,38 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>George P. Beal</t>
+          <t>Nicholas David Stenger</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; Managing Partner (Portfolio Manager)</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/george-beal-a6107a16/</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr"/>
+          <t>Founder &amp; Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>nick.stenger@stengerfamilyoffice.com</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>617-624-0800</t>
+          <t>630-912-8295</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Filed Form ADV Part 2A/2B brochures in the 2024 filing cycle (Feb 2024); a partner (Beal) serves on the board of Breckinridge Capital Advisors. Firm moved offices to 20 Custom House St.</t>
+          <t>$731M AUM (2026-06-30); Forbes Best-in-State Wealth Advisor 2026; hosts 'The Nick Stenger Show' podcast; opened Spring, TX office</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2024-02-01 (ADV Part 2B brochure)</t>
+          <t>2026-06-30 (AUM date); 2026 (Forbes Best-in-State)</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1911,19 +1915,19 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Despite the 'family office' name, this is functionally a multi-family-office RIA / private wealth manager serving hundreds of client accounts, not a single family's office. Investment authority is distributed among ~8 managing directors, so Beal is one of several senior decision-makers (though the 13F signatory and co-founder). No official company LinkedIn URL confirmed. No individual email is published (the ZoomInfo masked pattern was deliberately not used).</t>
+          <t>Serves 1,200+ families 'of all net worth sizes' — a broad wealth-management RIA using family-office branding rather than a classic UHNW MFO; hence proof strength 'corroborated'. Personal LinkedIn /in profile not located (only company page and a Calendly slug for 'nicholasstenger'). No published individual email or direct phone line found.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEC13F-0002017744</t>
+          <t>SEC13F-0001908612</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC</t>
+          <t>Allie Family Office LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1931,45 +1935,49 @@
           <t>MFO</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>None (owner-operated MFO). Founded 2019 and 100% owned by Bruno Ghio, formerly Regional Head of the Family Office / Managing Director at Banco de Credito del Peru (BCP) and a senior private banker at JPMorgan. Not tied to a single client family.</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://arrowrootfamilyoffice.com/</t>
+          <t>https://allie-intl.com/en/home/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/arrowroot-family-office</t>
+          <t>https://www.linkedin.com/company/alli%C3%A9-family-office</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC is a Marina del Rey, CA-based registered investment adviser and multi-family office, originally founded in 2013 as Vitreous Partners and rebranded in 2017. It provides multidisciplinary wealth management -- investment management, retirement, tax and estate planning -- to high-net-worth individuals, entrepreneurs, families and small institutions, with offices in Southern and Northern California, Virginia and Michigan. It is a multi-client RIA, not a single family's office.</t>
+          <t>Miami-based (with a Lima, Peru office) independent multi-family office and SEC-registered investment adviser founded in 2019 by Bruno Ghio, serving Latin American — predominantly Peruvian — high-net-worth families. Provides discretionary and limited-discretionary portfolio management, wealth structuring, tax planning, single-family-office consulting and cross-border coordination via a global network of tax/legal/banking experts.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Team-based, fiduciary, goals-driven wealth management emphasizing comprehensive planning and diversified investment management for affluent households and business owners; open-architecture advice.</t>
+          <t>Cross-border wealth management and multi-generational governance for Latin American families relocating capital (and increasingly themselves) to the US; independent, conflict-free advisory.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Diversified multi-asset wealth management (public equities, funds/ETFs, fixed income, alternatives); not sector-specialized.</t>
+          <t>Discretionary and limited-discretionary global portfolio management (largest reported 13F holding is the SPDR S&amp;P 500 ETF Trust; 95 equity positions); diversified across public markets, no single-sector focus disclosed.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>~$431M AUM as of Q2 2025 (third-party profiles); regulatory AUM per the 2025 Form ADV on the firm's site. A floor for total client assets under advisement.</t>
+          <t>~$1.15 billion AUM (as of 2024-12-31: ~$508.7M discretionary + ~$637.9M limited-discretionary); aggregators (FINTRX) report ~$1.3B; press (Bloomberg/Crain, 2024) cites ~$2B across the Peru/Miami practice</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Marina Del Rey</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1979,17 +1987,17 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Rob (Roberto Francisco) Santos</t>
+          <t>Bruno Ghio</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Chief Executive Officer &amp; Principal Owner</t>
+          <t>Founder &amp; Chief Executive Officer (CFA, CAIA, FRM); 100% owner</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/rob-santos-afo/</t>
+          <t>https://pe.linkedin.com/in/bruno-ghio-1264b616b</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
@@ -2000,17 +2008,17 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>310.341.4774</t>
+          <t>7866357162</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Announced expansion of its private-wealth practice into Michigan via addition of The Athena Financial Group (offices now include Marina del Rey CA, Rochester Hills MI, Charlottesville VA, El Dorado Hills CA); filed updated Form ADV Part 2A/2B in April 2025.</t>
+          <t>Founded 2019; among Peru's top-3 independent multi-family offices; ~23 client families (avg ~$50M); Miami + Lima offices; growth from Peruvian clients relocating to Miami; added a partner in Peru</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2022-09-05 (Michigan/Athena expansion press release); 2025-04 (Form ADV update)</t>
+          <t>2019 (firm founding); 2024 (Bloomberg/Crain profile); AUM as of 2024-12-31</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2020,19 +2028,19 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Uses the 'family office' label but is a multi-client wealth-management RIA, not a single family's office. Possible name confusion with 'Arrowroot Capital Management' (a separate B2B enterprise-software private-equity firm) -- they are distinct; relationship not established here. No individual email published; RocketReach/broker data deliberately not used. Firm's most recent 13F filer registration is recent (CIK 0002017744).</t>
+          <t>Legal 13F filer name is 'Allie Family Office LLC'; brand is 'Allié Family Office' (allie-intl.com). AUM figures vary by source (~$1.15B ADV vs ~$1.3B FINTRX vs ~$2B press including the broader Peru practice). No individual email or direct phone published; only generic info@ mailbox. Jose Larrabure is the investment lead; Bruno Ghio named principal as founder/CEO/100% owner.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEC13F-0001950506</t>
+          <t>SEC13F-0001511137</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fortitude Family Office, LLC</t>
+          <t>Pathstone Family Office, Llc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2042,47 +2050,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>None (owner-operated MFO founded and led by Matt Walker). Not tied to a single client family.</t>
+          <t>No single family; one of the largest U.S. multi-family offices serving many UHNW families, SFOs and institutions.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://fortitudefo.com/</t>
+          <t>https://pathstone.com</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/fortitude-family-office</t>
+          <t>https://www.linkedin.com/company/pathstone-family-office</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ-based multi-family office and SEC-registered investment adviser founded and led by Matt Walker (CPA, CGMA). Provides coordinated investment/wealth management, portfolio strategy, tax planning and compliance, private deal structuring, family governance, municipal-bond and ranch/agriculture services to HNW/UHNW families, founders and executives. ~$1B AUM (~$2B AUA claimed).</t>
+          <t>Englewood, NJ headquartered partner-owned multi-family office and SEC-registered RIA founded in 2010 (co-founders Matthew Fleissig, Allan Zachariah, Steve Braverman). Provides integrated investment management, tax, insurance/risk, legacy planning and family-office services to UHNW families, family offices, foundations and endowments; ~$125B firm AUM (2025).</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Fully-integrated 'coordinated services' model for multigenerational families and founders navigating transitions/liquidity events, blending investment strategy with tax and business operations.</t>
+          <t>Integrated, institutional-quality advice with a client-first culture; open-architecture investment management including private markets and alternatives; scale via organic growth and acquisitions (e.g., Crestone Capital).</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Wealth management &amp; portfolio strategy, municipal-bond portfolio management, private deal structuring/private lending; also ranch &amp; agriculture services. Diversified, no single-sector public-equity focus.</t>
+          <t>Public equities (13F holdings), private markets/alternatives, fixed income, diversified multi-asset portfolios</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>~$1 billion regulatory AUM (~$2 billion assets under advisement per firm PR)</t>
+          <t>~$125 billion (firm) as of 12/31/2025; ~$187 billion including affiliate firms (other sources cite $170B+ aggregate in 2025).</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>SCOTTSDALE</t>
+          <t>ENGLEWOOD</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2092,17 +2100,17 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Matt Walker</t>
+          <t>Matthew Fleissig</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Founder &amp; Chief Executive Officer (CPA, CGMA)</t>
+          <t>Chief Executive Officer (co-founder)</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/matt-walkercpa-cgma/</t>
+          <t>https://www.linkedin.com/in/fleissig/</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -2113,17 +2121,17 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>(602) 834-0089</t>
+          <t>857-305-3070</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>~$1B RAUM / ~$2B AUA; Matt Walker named BIG 'Executive of the Year' 2024 and InvestmentNews Excellence Awardee 2024; won 2024 WealthManagement.com award for a private-lending initiative; ~28 employees</t>
+          <t>Founded 2010; 15th anniversary in 2025; acquired Crestone Capital; ~775+ employees; co-founders Allan Zachariah and Steve Braverman serve as Co-Chairmen; multiple 2025 Family Wealth Report Awards.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2024 (executive/industry awards)</t>
+          <t>Founded 2010; AUM as of 12/31/2025; ADV dated 03/31/2025.</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2133,19 +2141,19 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Firm advertises ~$2B 'assets under advisement' vs ~$1B regulatory AUM (FINTRX) — the larger figure includes non-discretionary/advised assets. Address suite number varies across pages (151 vs 100). No published individual email located.</t>
+          <t>Very large firm; AUM figures vary by whether affiliate firms are included and by reporting date. No published individual email.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEC13F-0001802278</t>
+          <t>SEC13F-0001731123</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stokes Family Office, LLC</t>
+          <t>Biltmore Family Office, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2155,39 +2163,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Stokes family (firm founded/owned by the Stokes family; David Stokes founder, sons Greg and Doug Stokes now managing partners). The 'family' is the owner-operators, not a single client family.</t>
+          <t>Founder Chris Cecil is a great-grandson of George Vanderbilt (builder of the Biltmore Estate) and son of Asheville developer George Cecil; 'Biltmore' name derives from that Vanderbilt/Cecil family heritage. The firm serves many outside client families (MFO), not the Vanderbilt/Cecil family exclusively.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://stokesfamilyoffice.com/</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
+          <t>https://www.biltmorefamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/biltmore-family-office-llc</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>New Orleans-based multi-family office and SEC-registered investment adviser, 100% owned by the Stokes family and operating in the area for 35+ years. Provides wealth management, investment advisory, tax and estate planning, and family-office services to high-net-worth individuals, families and institutions. Opened a Dallas, TX office in 2025.</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Charlotte, NC-based multi-family office and SEC-registered investment adviser founded in 2008 by Chris Cecil. A collaborative/independent RIA to investment-oriented multi-generational families and institutions, providing investment management, asset allocation, investment-policy design, multi-generational and succession planning. ~$3.2-3.5B AUM.</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Collaborative, investment-policy-driven management for multi-generational HNW/UHNW families and institutions.</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Discretionary client portfolio management primarily allocating among mutual funds, ETFs and ETNs; no single-sector focus disclosed.</t>
+          <t>Diversified public-equity/ETF portfolios; disclosed top 13F holdings include AAPL, IAU (gold), AVDX, ROBO, VV. No single-sector concentration.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>~$3.35 billion (as of 2025-12-31); reported ~$3.4B by FINTRX</t>
+          <t>~$3.2-3.5 billion (reported ~$3.47B regulatory AUM across ~951 accounts)</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>NEW ORLEANS</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>LA</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2197,17 +2213,17 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Douglas Stokes</t>
+          <t>Chris Cecil</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Managing Partner (CFA); leads investment research and the investment committee</t>
+          <t>Founder, President &amp; CEO</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/doug-stokes-03716932/</t>
+          <t>https://www.linkedin.com/in/chris-cecil-9701b818/</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
@@ -2218,17 +2234,17 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>(504) 399-4100</t>
+          <t>+1 704-248-5230</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Exceeded $3B AUM; named to Forbes/SHOOK 'Top RIA' list; opened Dallas, TX office (Resolute Tower at Old Parkland)</t>
+          <t>Founded 2008 by Chris Cecil (LLC organized 2013); ~$3.2-3.5B AUM across ~951 accounts, avg client ~$38M; Cecil chairs TIGER 21 Charlotte / Family Office groups</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2023 (Forbes/SHOOK Top RIA PR); 2025-2026 (Dallas office opening); AUM ~$3.35B as of 2025-12-31</t>
+          <t>2008 (founding); 2013 (LLC organized)</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2238,19 +2254,19 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>'Family owned' refers to the Stokes family owning the firm, not to serving a single client family; it is a multi-client advisory MFO. Doug and Greg Stokes are co-managing partners/co-owners; Doug (CFA) chosen as principal on investment-lead basis. No individual email published. Founded/started SEC registration in 2019 though the family practice dates to the 1980s.</t>
+          <t>Chris Cecil chosen as principal (founder/CEO); Rael Gorelick is Partner &amp; Head of Investments and would be the CIO-level investment lead. No published individual email located. AUM varies by source ($3.2B-$3.5B).</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEC13F-0002105684</t>
+          <t>SEC13F-0001039807</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cambient Family Office, Llc</t>
+          <t>Boston Family Office Llc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2258,49 +2274,41 @@
           <t>MFO</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>None (owner-operated MFO). Direct owners/executives per Form ADV Schedule A: Andrew Harold Fabiano, Joshua Kirk Gibbs, Daniel Baird Rausch; indirect owner 'RIMAR Development' (since 01/2026). Firm previously named 'STILLWATER, LLC'.</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.cambient.com/</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/cambient-family-office</t>
-        </is>
-      </c>
+          <t>https://www.bosfam.com/</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ada, Michigan-based multi-family office and SEC-registered investment adviser (formerly 'Stillwater, LLC'), serving affluent families, private foundations and entrepreneurs with integrated wealth planning, tax-aware discretionary investment management, estate/trust planning and family-office administration. ~$858M AUM.</t>
+          <t>The Boston Family Office LLC is an independent, employee-owned registered investment adviser founded in 1996 and based in Boston, MA. It provides multi-family-office-style wealth management -- investment management, financial planning, and adviser selection -- to high-net-worth individuals, families and charitable organizations across roughly 789 accounts and ~$1.7-2.0B in assets. It is a multi-family/RIA firm rather than a single-family office.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Goals-based, tax-aware investment management with a preference for equity exposure and outside-manager selection/oversight.</t>
+          <t>Client-tailored, diversified portfolio management for wealth preservation and growth across HNW households and institutions; discretionary management (769 of 789 accounts discretionary). Specific house investment philosophy not detailed publicly.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Favors exchange-traded equity exposure; discretionary portfolio management plus manager selection. No single-sector focus.</t>
+          <t>Diversified multi-asset wealth management (public equities, fixed income, funds); not sector-specialized. A partner sits on the board of fixed-income manager Breckinridge Capital Advisors.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>$857,939,726 regulatory AUM (260 accounts; $781.2M discretionary)</t>
+          <t>~$1.7B AUM across 789 accounts (Form ADV/adviserinfo, 2024-2025); third-party profiles cite ~$1.9-2.02B. As of the most recent Form ADV (2024 filing cycle).</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2310,17 +2318,17 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Andrew Harold Fabiano</t>
+          <t>George P. Beal</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Portfolio Manager (CFA); direct owner / principal</t>
+          <t>Co-Founder &amp; Managing Partner (Portfolio Manager)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/andrew-fabiano-2b4869ab</t>
+          <t>https://www.linkedin.com/in/george-beal-a6107a16/</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
@@ -2331,17 +2339,17 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>616-330-2270</t>
+          <t>617-624-0800</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Firm formerly named 'STILLWATER, LLC'; SEC registration effective 2025-04-02; TX notice filing 2025-08; FL notice filing 2026-07; 'RIMAR Development' became indirect owner 01/2026; PM Stephen Wilbur (CFP) departed May 2025; latest 13F reported $716.4M (261 positions) signed by Josh Gibbs</t>
+          <t>Filed Form ADV Part 2A/2B brochures in the 2024 filing cycle (Feb 2024); a partner (Beal) serves on the board of Breckinridge Capital Advisors. Firm moved offices to 20 Custom House St.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2025-04-02 (SEC reg); 2025-05 (Wilbur departure); 2025-08 (TX notice); 2026-01 (RIMAR indirect owner); 2026-04-21 &amp; 2026-02-20 (13F-HR filings); 2026-07-16 (ADV amendment)</t>
+          <t>2024-02-01 (ADV Part 2B brochure)</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2351,19 +2359,19 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>No single named CEO/CIO on the public site; ownership is a three-person partnership (Fabiano, Rausch, Gibbs) plus indirect owner RIMAR Development. Fabiano selected as principal on investment-lead + direct-owner basis; Rausch is a co-equal PM. 13F signatory (Josh Gibbs, Trust Advisor/CCO) differs from investment lead. Predecessor name 'Stillwater, LLC' explains 'established 2025' references despite larger AUM history.</t>
+          <t>Despite the 'family office' name, this is functionally a multi-family-office RIA / private wealth manager serving hundreds of client accounts, not a single family's office. Investment authority is distributed among ~8 managing directors, so Beal is one of several senior decision-makers (though the 13F signatory and co-founder). No official company LinkedIn URL confirmed. No individual email is published (the ZoomInfo masked pattern was deliberately not used).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UKCH-09580739</t>
+          <t>SEC13F-0002017744</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Blu Family Office Limited</t>
+          <t>Arrowroot Family Office, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2371,69 +2379,65 @@
           <t>MFO</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Originally Armbruester family (founder's wealth); now MFO serving multiple client families</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.blu-fo.com</t>
+          <t>https://arrowrootfamilyoffice.com/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/company/blu-family-office</t>
+          <t>https://www.linkedin.com/company/arrowroot-family-office</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>FCA-regulated multi-family office (Ltd inc. 2015; operations from 2010) in Richmond upon Thames, founded by Christian Armbruester post Credit Suisse. Offers hedge funds, crypto and alternatives; discretionary arm Blu Investment Management.</t>
+          <t>Arrowroot Family Office, LLC is a Marina del Rey, CA-based registered investment adviser and multi-family office, originally founded in 2013 as Vitreous Partners and rebranded in 2017. It provides multidisciplinary wealth management -- investment management, retirement, tax and estate planning -- to high-net-worth individuals, entrepreneurs, families and small institutions, with offices in Southern and Northern California, Virginia and Michigan. It is a multi-client RIA, not a single family's office.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Discretionary management not relying on forecasting; 'true diversification' and systematic rebalancing; passive in calm markets, opportunistic in adverse ones.</t>
+          <t>Team-based, fiduciary, goals-driven wealth management emphasizing comprehensive planning and diversified investment management for affluent households and business owners; open-architecture advice.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Hedge funds; crypto assets; alternatives; diversified multi-asset</t>
+          <t>Diversified multi-asset wealth management (public equities, funds/ETFs, fixed income, alternatives); not sector-specialized.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>£0.5bn-£1bn (third-party estimated range)</t>
+          <t>~$431M AUM as of Q2 2025 (third-party profiles); regulatory AUM per the 2025 Form ADV on the firm's site. A floor for total client assets under advisement.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Marina Del Rey</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Greater London</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Christian Armbruester</t>
+          <t>Rob (Roberto Francisco) Santos</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Founder &amp; Principal (largest shareholder ~40.8%)</t>
+          <t>Chief Executive Officer &amp; Principal Owner</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/christianarmbruesterblufamilyoffice</t>
+          <t>https://www.linkedin.com/in/rob-santos-afo/</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
@@ -2442,15 +2446,19 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>310.341.4774</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Founded 2010; Ltd inc. 2015; new director Vishesh Dawar appointed Dec 2025; investment arm rebranded Blu Investment Management; Marie Redron now CEO</t>
+          <t>Announced expansion of its private-wealth practice into Michigan via addition of The Athena Financial Group (offices now include Marina del Rey CA, Rochester Hills MI, Charlottesville VA, El Dorado Hills CA); filed updated Form ADV Part 2A/2B in April 2025.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2015-05-08; 2025-12-08</t>
+          <t>2022-09-05 (Michigan/Athena expansion press release); 2025-04 (Form ADV update)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2460,98 +2468,106 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Client-facing operations now run under 'Blu Investment Management' (blu-im.com), same address. Armbruester is founder/principal but not current CEO (Marie Redron is). AUM range is a third-party estimate. Only published contacts are a switchboard + generic mailbox.</t>
+          <t>Uses the 'family office' label but is a multi-client wealth-management RIA, not a single family's office. Possible name confusion with 'Arrowroot Capital Management' (a separate B2B enterprise-software private-equity firm) -- they are distinct; relationship not established here. No individual email published; RocketReach/broker data deliberately not used. Firm's most recent 13F filer registration is recent (CIK 0002017744).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UKCH-12233405</t>
+          <t>SEC13F-0001756485</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Schwarz Family Office Ltd</t>
+          <t>Independent Family Office, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Named after principal Andreas Schwarz (German); no wider family group evidenced beyond the surname</t>
+          <t>None (owner-operated MFO). Founded 2005 by W. Michael Reickert, who previously led the family-office practice at The Ayco Company. Serves multiple entrepreneurial client families; not a single-family vehicle.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://schwarzfamilyoffice.com/</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>https://ifollc.com/</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/independent-family-office-llc</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>London-based boutique investment/advisory firm branded as a family office, established 2019, led by Andreas Schwarz; provides capital raising, debt financing, wealth management and IR services.</t>
+          <t>Albany, New York-based multi-family office and SEC-registered investment adviser founded in 2005 by W. Michael Reickert. A bespoke family office serving a small number of high-net-worth families (average client tenure 10+ years) with investment advisory and asset allocation, estate-planning coordination, transaction/contract advisory and income-tax planning and compliance.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>'Be not afraid of growing slowly, be afraid only of standing still' — sustainable growth via established relationships and exclusive investor access. https://schwarzfamilyoffice.com/</t>
+          <t>Technical, unbiased, independent long-term stewardship of client families' financial lives; capital-allocator approach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Private equity; fintech; wealth management; venture capital; private debt; IPOs</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+          <t>Discretionary portfolio management and outside-manager selection for HNW families (largest reported 13F holding is the SPDR S&amp;P 500 ETF Trust); diversified, no single-sector focus disclosed.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>~$617.8 million discretionary AUM across ~34 clients (Form ADV, 2025-03-31); aggregators (FINTRX) report ~$760M</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>ALBANY</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Maida Vale</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Andreas Schwarz</t>
+          <t>W. Michael Reickert</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Founder / Director</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
-        </is>
-      </c>
+          <t>Managing Member / Managing Partner &amp; CEO (also Chief Compliance Officer); IRS Enrolled Agent, JD</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>(518) 452-8050</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Listed in Family Capital 'FamCap 50' (2024); second shareholder Syed Furqan Ahmed (490 shares)</t>
+          <t>Founded 2005; SEC-registered 2012; ex-Ayco family-office pedigree; very low client count (~34) with 10+ year average tenure</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2024-02 (FamCap 50)</t>
+          <t>2005 (founding); 2012 (SEC registration); AUM ~$617.8M as of 2025-03-31</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2561,53 +2577,69 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Presents as a family office but functions largely as a boutique capital-raising/advisory consultancy with two shareholders — fo_type left Undetermined. A Family Capital story linking Schwarz to a 'famous UK brand' is paywalled and the brand is NOT confirmed; not asserted. AUM undisclosed.</t>
+          <t>Firm marketing copy calls itself a 'bespoke family office' for 'select clients'; the ~34-client, multi-family reality plus Altss classification support MFO. 'dr@ifollc.com' is published but its initials do not match the principal, so it is treated as a shared/general mailbox, not the principal's individual email. No personal LinkedIn confirmed for W. Michael Reickert.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UKCH-14344019</t>
+          <t>UKCH-09580739</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hazell Family Office Ltd</t>
+          <t>Blu Family Office Limited</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hazell family of South Wales (haulage/waste/environmental-services wealth)</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
+          <t>Originally Armbruester family (founder's wealth); now MFO serving multiple client families</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://www.blu-fo.com</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/blu-family-office</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Active company (inc. 2022-09-08), SIC 70221 financial management; board is five members of the Hazell family. Structure strongly indicates a single-family office. No website/press footprint.</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
+          <t>FCA-regulated multi-family office (Ltd inc. 2015; operations from 2010) in Richmond upon Thames, founded by Christian Armbruester post Credit Suisse. Offers hedge funds, crypto and alternatives; discretionary arm Blu Investment Management.</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Discretionary management not relying on forecasting; 'true diversification' and systematic rebalancing; passive in calm markets, opportunistic in adverse ones.</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>70221 - Financial management</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+          <t>Hedge funds; crypto assets; alternatives; diversified multi-asset</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>£0.5bn-£1bn (third-party estimated range)</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Usk</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Monmouthshire, Wales</t>
+          <t>Greater London</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2617,15 +2649,19 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Mark David William Hazell</t>
+          <t>Christian Armbruester</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Director (family principal)</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr"/>
+          <t>Founder &amp; Principal (largest shareholder ~40.8%)</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/christianarmbruesterblufamilyoffice</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
@@ -2635,68 +2671,76 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Incorporated Sept 2022; five family directors appointed same day; principal is MD of family haulage/environmental companies</t>
+          <t>Founded 2010; Ltd inc. 2015; new director Vishesh Dawar appointed Dec 2025; investment arm rebranded Blu Investment Management; Marie Redron now CEO</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2015-05-08; 2025-12-08</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>SFO status inferred from shared surname + single family-farm address + Mark Hazell's operating-company directorships; no website/press confirms active investment operations. 'Mark = principal' is inference; control may be shared across the family.</t>
+          <t>Client-facing operations now run under 'Blu Investment Management' (blu-im.com), same address. Armbruester is founder/principal but not current CEO (Marie Redron is). AUM range is a third-party estimate. Only published contacts are a switchboard + generic mailbox.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UKCH-14442767</t>
+          <t>UKCH-12233405</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wedgwood Family Office Limited</t>
+          <t>Schwarz Family Office Ltd</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Undetermined</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Wedgwood (Paul Wedgwood family)</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
+          <t>Named after principal Andreas Schwarz (German); no wider family group evidenced beyond the surname</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://schwarzfamilyoffice.com/</t>
+        </is>
+      </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>UK private company (inc. 2022-10-25) under fund-management SIC, registered at a residential address in Keston. Appears to be the personal single-family investment vehicle of Paul Wedgwood.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
+          <t>London-based boutique investment/advisory firm branded as a family office, established 2019, led by Andreas Schwarz; provides capital raising, debt financing, wealth management and IR services.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>'Be not afraid of growing slowly, be afraid only of standing still' — sustainable growth via established relationships and exclusive investor access. https://schwarzfamilyoffice.com/</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>66300 - Fund management activities</t>
+          <t>Private equity; fintech; wealth management; venture capital; private debt; IPOs</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Keston</t>
+          <t>London</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Greater London (Bromley)</t>
+          <t>Maida Vale</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2706,15 +2750,19 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Paul Wedgwood</t>
+          <t>Andreas Schwarz</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
+          <t>Founder / Director</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
@@ -2724,34 +2772,34 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Co-director Christopher James Sharp resigned 2024-04-16; new secretary appointed 2026-01-06; accounts currently overdue</t>
+          <t>Listed in Family Capital 'FamCap 50' (2024); second shareholder Syed Furqan Ahmed (490 shares)</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2024-04-16; 2026-01-06</t>
+          <t>2024-02 (FamCap 50)</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Link between director 'Paul Wedgwood, b.1970' and the Splash Damage/Supernova entrepreneur is a strong inference (name + DOB + separate Wedgwood FIC directorship), NOT hard-confirmed. Zero public FO footprint (no website/LinkedIn/press/AUM); accounts overdue. Residential registered address.</t>
+          <t>Presents as a family office but functions largely as a boutique capital-raising/advisory consultancy with two shareholders — fo_type left Undetermined. A Family Capital story linking Schwarz to a 'famous UK brand' is paywalled and the brand is NOT confirmed; not asserted. AUM undisclosed.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SFO-dfo-management-dell</t>
+          <t>UKCH-14344019</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DFO Management (Dell Family Office)</t>
+          <t>Hazell Family Office Ltd</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2761,58 +2809,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Dell family (Michael Dell, founder/CEO of Dell Technologies)</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>https://www.dellfamilyoffice.com/</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/dfo-management</t>
-        </is>
-      </c>
+          <t>Hazell family of South Wales (haulage/waste/environmental-services wealth)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Private investment firm managing the assets of Michael Dell and family across public equities, private equity, real estate and other asset classes. Originally MSD Capital (1998); the multi-client business became BDT &amp; MSD Partners while the family's captive vehicle was rebranded DFO Management at end of 2022.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Multi-asset-class permanent capital: public equities, private equity/credit, real estate, opportunistic direct investments.</t>
-        </is>
-      </c>
+          <t>Active company (inc. 2022-09-08), SIC 70221 financial management; board is five members of the Hazell family. Structure strongly indicates a single-family office. No website/press footprint.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Diversified (consumer, real estate, financials, industrials)</t>
+          <t>70221 - Financial management</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Usk</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Monmouthshire, Wales</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Michael Dell</t>
+          <t>Mark David William Hazell</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Founder / Family Principal</t>
+          <t>Director (family principal)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -2825,12 +2861,12 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
-          <t>13F-HR filed 2026-05-15 (period ending 2026-03-31) disclosing U.S. equity holdings; rebrand from MSD Capital to DFO Management completed end of 2022.</t>
+          <t>Incorporated Sept 2022; five family directors appointed same day; principal is MD of family haulage/environmental companies</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2026-05-15; 2022-12</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2840,19 +2876,19 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>The 13F is filed in the name of the Michael &amp; Susan Dell Foundation with DFO Management as manager; the foundation and the family office are affiliated. AUM not disclosed. Michael Dell is a public figure; no personal LinkedIn tied specifically to DFO confirmed.</t>
+          <t>SFO status inferred from shared surname + single family-farm address + Mark Hazell's operating-company directorships; no website/press confirms active investment operations. 'Mark = principal' is inference; control may be shared across the family.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SFO-bayshore-global-brin</t>
+          <t>UKCH-14442767</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bayshore Global Management (Brin Family Office)</t>
+          <t>Wedgwood Family Office Limited</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2862,50 +2898,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Brin family (Sergey Brin, Google co-founder)</t>
+          <t>Wedgwood (Paul Wedgwood family)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Low-profile single-family office managing the wealth of Sergey Brin across public and private markets, real estate and philanthropy. Additional office in Singapore. Reported to have absorbed the Nexus NeuroTech brain-health VC fund in 2026.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Broad multi-asset allocation with notable venture/science-and-health direct investing.</t>
-        </is>
-      </c>
+          <t>UK private company (inc. 2022-10-25) under fund-management SIC, registered at a residential address in Keston. Appears to be the personal single-family investment vehicle of Paul Wedgwood.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Diversified; neuroscience/brain-health, deep tech, real estate</t>
+          <t>66300 - Fund management activities</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Keston</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Greater London (Bromley)</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Sergey Brin</t>
+          <t>Paul Wedgwood</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Family Principal</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -2918,12 +2950,12 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Absorbed Nexus NeuroTech brain-health VC fund (reported 2026-04-23, Bloomberg).</t>
+          <t>Co-director Christopher James Sharp resigned 2024-04-16; new secretary appointed 2026-01-06; accounts currently overdue</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2024-04-16; 2026-01-06</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2933,19 +2965,19 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>No public website confirmed. AUM figures are press estimates. CEO George Pavlov / CIO Marie Young named in Wikipedia and press but not verified against a primary filing.</t>
+          <t>Link between director 'Paul Wedgwood, b.1970' and the Splash Damage/Supernova entrepreneur is a strong inference (name + DOB + separate Wedgwood FIC directorship), NOT hard-confirmed. Zero public FO footprint (no website/LinkedIn/press/AUM); accounts overdue. Residential registered address.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SFO-hillspire-schmidt</t>
+          <t>SFO-dfo-management-dell</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hillspire (Eric Schmidt Family Office)</t>
+          <t>DFO Management (Dell Family Office)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2955,35 +2987,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Schmidt family (Eric &amp; Wendy Schmidt; Eric Schmidt is former Google/Alphabet CEO and chairman)</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+          <t>Dell family (Michael Dell, founder/CEO of Dell Technologies)</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://www.dellfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dfo-management</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Single-family office of Eric and Wendy Schmidt focused on deep technology: artificial intelligence, quantum computation, defense tech and biotech. Reported to have invested in 22+ private AI firms since 2019 (including Anthropic, SandboxAQ, Inworld AI) and topped CNBC's inaugural family-office dealmaking ranking for 2025.</t>
+          <t>Private investment firm managing the assets of Michael Dell and family across public equities, private equity, real estate and other asset classes. Originally MSD Capital (1998); the multi-client business became BDT &amp; MSD Partners while the family's captive vehicle was rebranded DFO Management at end of 2022.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Deep-tech direct investing concentrated in AI, quantum, defense technology and biotech.</t>
+          <t>Multi-asset-class permanent capital: public equities, private equity/credit, real estate, opportunistic direct investments.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>AI, quantum computing, defense tech, biotech</t>
+          <t>Diversified (consumer, real estate, financials, industrials)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2993,12 +3033,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Eric Schmidt</t>
+          <t>Michael Dell</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Family Principal / Founder</t>
+          <t>Founder / Family Principal</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -3011,12 +3051,12 @@
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Ranked #1 most active U.S. family office for dealmaking in 2025 (15 investments, mostly AI) per CNBC 2026-02-12; disclosed 22 private AI startup investments since 2019 (CNBC 2025-01-21).</t>
+          <t>13F-HR filed 2026-05-15 (period ending 2026-03-31) disclosing U.S. equity holdings; rebrand from MSD Capital to DFO Management completed end of 2022.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2026-02-12; 2025-01-21</t>
+          <t>2026-05-15; 2022-12</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3026,19 +3066,19 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>No public website confirmed (hillspire.com not verified). Does not file 13F (EDGAR full-text search returned no 13F-HR). AUM not disclosed. President Ken Goldman named in press, not verified against a primary filing.</t>
+          <t>The 13F is filed in the name of the Michael &amp; Susan Dell Foundation with DFO Management as manager; the foundation and the family office are affiliated. AUM not disclosed. Michael Dell is a public figure; no personal LinkedIn tied specifically to DFO confirmed.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SFO-blue-pool-capital-tsai</t>
+          <t>SFO-bayshore-global-brin</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Blue Pool Capital (Joe Tsai Family Office)</t>
+          <t>Bayshore Global Management (Brin Family Office)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3048,58 +3088,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tsai family (Joseph Tsai, Alibaba co-founder and chairman)</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://www.bluepoolcapital.com/</t>
-        </is>
-      </c>
+          <t>Brin family (Sergey Brin, Google co-founder)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hong Kong-based investment firm overseeing the Tsai family's wealth across hedge funds, private equity, private credit, venture and sports assets (Brooklyn Nets, LAFC). Raised ~$1bn for its first dedicated PE vehicle (Riverside Fund) reported 2026. Led by CEO Oliver Weisberg (ex-Goldman Sachs, ex-Citadel).</t>
+          <t>Low-profile single-family office managing the wealth of Sergey Brin across public and private markets, real estate and philanthropy. Additional office in Singapore. Reported to have absorbed the Nexus NeuroTech brain-health VC fund in 2026.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Multi-strategy long-term capital: public markets, PE, private credit, venture, and sports/real assets.</t>
+          <t>Broad multi-asset allocation with notable venture/science-and-health direct investing.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Diversified; technology (SpaceX, Epic Games, ByteDance), consumer/luxury (Golden Goose), sports, Japanese real estate</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>~$50 billion</t>
-        </is>
-      </c>
+          <t>Diversified; neuroscience/brain-health, deep tech, real estate</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Causeway Bay</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Hong Kong Island</t>
+          <t>California</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Joseph Tsai</t>
+          <t>Sergey Brin</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Family Principal / Founder</t>
+          <t>Family Principal</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -3112,12 +3144,12 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
-          <t>13F-HR filed 2026-05-15; sold ~83% of Blue Owl Capital stake (~$460m) reported 2024-03; joined consortium buying Burgundy vineyards 2024-09; raised ~$1bn first PE fund (Riverside) reported 2026-03-31.</t>
+          <t>Absorbed Nexus NeuroTech brain-health VC fund (reported 2026-04-23, Bloomberg).</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2026-05-15; 2024-03-03; 2024-09-19; 2026-03-31</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3127,19 +3159,19 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Some sources describe Blue Pool as a 'multi-family' vehicle co-backed by former Alibaba executives (and occasionally link Jack Ma); primary characterization is Joe Tsai's family office. Website confirmed to be minimal/uninformative per Crain Currency; bluepoolcapital.com domain asserted from press but not independently fetched.</t>
+          <t>No public website confirmed. AUM figures are press estimates. CEO George Pavlov / CIO Marie Young named in Wikipedia and press but not verified against a primary filing.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SFO-mousse-partners-wertheimer</t>
+          <t>SFO-hillspire-schmidt</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mousse Partners (Wertheimer Family Office)</t>
+          <t>Hillspire (Eric Schmidt Family Office)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3149,43 +3181,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Wertheimer family (Alain and Gerard Wertheimer, owners of Chanel)</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://moussepartners.com/</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/moussepartners</t>
-        </is>
-      </c>
+          <t>Schmidt family (Eric &amp; Wendy Schmidt; Eric Schmidt is former Google/Alphabet CEO and chairman)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Investment firm serving as the family office of the Wertheimer family. Manages a global diversified portfolio across public equities, fixed income, private equity, venture and real estate, with investment operations in New York and Asia (Beijing, Hong Kong).</t>
+          <t>Single-family office of Eric and Wendy Schmidt focused on deep technology: artificial intelligence, quantum computation, defense tech and biotech. Reported to have invested in 22+ private AI firms since 2019 (including Anthropic, SandboxAQ, Inworld AI) and topped CNBC's inaugural family-office dealmaking ranking for 2025.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Global multi-asset diversified investing with a notable consumer/brands tilt.</t>
+          <t>Deep-tech direct investing concentrated in AI, quantum, defense technology and biotech.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Diversified; consumer, luxury/brands, technology, real estate</t>
+          <t>AI, quantum computing, defense tech, biotech</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>California</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3195,12 +3219,12 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Charles Heilbronn</t>
+          <t>Eric Schmidt</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Founder / Chairman</t>
+          <t>Family Principal / Founder</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -3213,12 +3237,12 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Bloomberg feature (2024-2025) reporting the office reshaping its consumer/public-equity bets.</t>
+          <t>Ranked #1 most active U.S. family office for dealmaking in 2025 (15 investments, mostly AI) per CNBC 2026-02-12; disclosed 22 private AI startup investments since 2019 (CNBC 2025-01-21).</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2024/2025 (Bloomberg feature)</t>
+          <t>2026-02-12; 2025-01-21</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3228,19 +3252,19 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Does not appear as a 13F filer under 'Mousse Partners' (EDGAR full-text search returned 0); investment vehicle is domiciled offshore (Mousse Investments Limited, Bermuda) with a NYC office (9 W. 57th St). AUM figure is the family fortune, not disclosed firm AUM. Firm general phone reported as 212-303-5795 (not an individual principal line).</t>
+          <t>No public website confirmed (hillspire.com not verified). Does not file 13F (EDGAR full-text search returned no 13F-HR). AUM not disclosed. President Ken Goldman named in press, not verified against a primary filing.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SFO-kirkbi-kristiansen</t>
+          <t>SFO-blue-pool-capital-tsai</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>KIRKBI (Kirk Kristiansen Family Office)</t>
+          <t>Blue Pool Capital (Joe Tsai Family Office)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3250,62 +3274,58 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Kirk Kristiansen family (owners of the LEGO Group)</t>
+          <t>Tsai family (Joseph Tsai, Alibaba co-founder and chairman)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.kirkbi.com/</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/kirkbi</t>
-        </is>
-      </c>
+          <t>https://www.bluepoolcapital.com/</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Danish family-owned holding and investment company managing the wealth and legacy of the Kirk Kristiansen family. Holds the family's controlling stakes in LEGO Group and Merlin Entertainments and runs a long-term investment portfolio plus a dedicated climate/energy-transition program (KIRKBI Climate). Additional offices in Copenhagen and Baar, Switzerland.</t>
+          <t>Hong Kong-based investment firm overseeing the Tsai family's wealth across hedge funds, private equity, private credit, venture and sports assets (Brooklyn Nets, LAFC). Raised ~$1bn for its first dedicated PE vehicle (Riverside Fund) reported 2026. Led by CEO Oliver Weisberg (ex-Goldman Sachs, ex-Citadel).</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Protect and grow family wealth for future generations; long-term core holdings (LEGO, Merlin) plus diversified investments and thematic climate/energy investing.</t>
+          <t>Multi-strategy long-term capital: public markets, PE, private credit, venture, and sports/real assets.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Toys/entertainment (core), real estate, renewable energy/climate, diversified financial investments</t>
+          <t>Diversified; technology (SpaceX, Epic Games, ByteDance), consumer/luxury (Golden Goose), sports, Japanese real estate</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>~$16 billion (family wealth)</t>
+          <t>~$50 billion</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Billund</t>
+          <t>Causeway Bay</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Region of Southern Denmark</t>
+          <t>Hong Kong Island</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Soren Thorup Sorensen</t>
+          <t>Joseph Tsai</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Family Principal / Founder</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -3318,12 +3338,12 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
-          <t>KIRKBI Climate follow-on investment in Highview Power (Hunterston project) announced November 2025 (second investment after June 2024 Carrington); Adapture Renewables (KIRKBI-majority-owned) acquired 110MW Colorado solar-plus-storage project March 2025; generational handover of board chair to Thomas Kirk Kristiansen May 2023.</t>
+          <t>13F-HR filed 2026-05-15; sold ~83% of Blue Owl Capital stake (~$460m) reported 2024-03; joined consortium buying Burgundy vineyards 2024-09; raised ~$1bn first PE fund (Riverside) reported 2026-03-31.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2025-11; 2025-03; 2023-05</t>
+          <t>2026-05-15; 2024-03-03; 2024-09-19; 2026-03-31</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3333,19 +3353,19 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>KIRKBI is both the family holding company (owns LEGO) and the family investment office; some may classify it as a holding company rather than a pure family office. AUM figure is the family-wealth press figure, not full portfolio value.</t>
+          <t>Some sources describe Blue Pool as a 'multi-family' vehicle co-backed by former Alibaba executives (and occasionally link Jack Ma); primary characterization is Joe Tsai's family office. Website confirmed to be minimal/uninformative per Crain Currency; bluepoolcapital.com domain asserted from press but not independently fetched.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SFO-tethys-invest-bettencourt</t>
+          <t>SFO-mousse-partners-wertheimer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tethys / Tethys Invest (Bettencourt Meyers Family Office)</t>
+          <t>Mousse Partners (Wertheimer Family Office)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3355,62 +3375,58 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Bettencourt Meyers family (majority shareholder of L'Oreal; Francoise Bettencourt Meyers)</t>
+          <t>Wertheimer family (Alain and Gerard Wertheimer, owners of Chanel)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://tethys.fr/</t>
+          <t>https://moussepartners.com/</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/t%C3%A9thys</t>
+          <t>https://www.linkedin.com/company/moussepartners</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Paris-based single-family office of the Bettencourt Meyers family, holder of the family's ~34% L'Oreal stake. Its subsidiary Tethys Invest (&gt;EUR 3bn capital) makes long-term direct investments deliberately outside L'Oreal's competitive scope, with a healthcare emphasis (Elsan private hospitals, Sebia diagnostics).</t>
+          <t>Investment firm serving as the family office of the Wertheimer family. Manages a global diversified portfolio across public equities, fixed income, private equity, venture and real estate, with investment operations in New York and Asia (Beijing, Hong Kong).</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Preserve the L'Oreal core holding and deploy dividend income into long-term entrepreneurial direct investments, notably healthcare, that do not compete with L'Oreal.</t>
+          <t>Global multi-asset diversified investing with a notable consumer/brands tilt.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Healthcare (hospitals, diagnostics), consumer, technology, diversified</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>&gt; $90 billion (family assets)</t>
-        </is>
-      </c>
+          <t>Diversified; consumer, luxury/brands, technology, real estate</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Ile-de-France</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Alexandre Benais</t>
+          <t>Charles Heilbronn</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>CEO, Tethys Invest</t>
+          <t>Founder / Chairman</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -3423,12 +3439,12 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
-          <t>Named new head of family investment firm reported 2023-03-13 (The National); family succession moves (Jean-Victor Meyers to L'Oreal vice-chairman; Alexandre Benais to family L'Oreal board seat) reported 2025-02; co-invested (with Chanel/Wertheimer) in The Row reported 2024-09.</t>
+          <t>Bloomberg feature (2024-2025) reporting the office reshaping its consumer/public-equity bets.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2023-03-13; 2025-02-08; 2024-09</t>
+          <t>2024/2025 (Bloomberg feature)</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3438,19 +3454,19 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>'Tethys' (parent) vs 'Tethys Invest' (investment subsidiary) are distinct entities; leadership names span both. AUM is the family-asset press figure, not a disclosed managed-portfolio AUM.</t>
+          <t>Does not appear as a 13F filer under 'Mousse Partners' (EDGAR full-text search returned 0); investment vehicle is domiciled offshore (Mousse Investments Limited, Bermuda) with a NYC office (9 W. 57th St). AUM figure is the family fortune, not disclosed firm AUM. Firm general phone reported as 212-303-5795 (not an individual principal line).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SFO-cofra-holding-brenninkmeijer</t>
+          <t>SFO-kirkbi-kristiansen</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>COFRA Holding (Brenninkmeijer Family Office)</t>
+          <t>KIRKBI (Kirk Kristiansen Family Office)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3460,58 +3476,62 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Brenninkmeijer family (founders/owners of C&amp;A; ~500 family members)</t>
+          <t>Kirk Kristiansen family (owners of the LEGO Group)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.cofraholding.com/</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>https://www.kirkbi.com/</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kirkbi</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Zug-based family-owned holding coordinating the Brenninkmeijer family's global operations and ~EUR 35-38bn asset base across retail (C&amp;A), real estate (Redevco), private equity (Bregal Investments) and asset management (Anthos). In 2025 the family announced it would open its portfolio to outside investors, a shift from its historically secretive model.</t>
+          <t>Danish family-owned holding and investment company managing the wealth and legacy of the Kirk Kristiansen family. Holds the family's controlling stakes in LEGO Group and Merlin Entertainments and runs a long-term investment portfolio plus a dedicated climate/energy-transition program (KIRKBI Climate). Additional offices in Copenhagen and Baar, Switzerland.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Long-term stewardship of family capital across operating businesses, real estate, private equity and (increasingly) externally-opened investment platforms.</t>
+          <t>Protect and grow family wealth for future generations; long-term core holdings (LEGO, Merlin) plus diversified investments and thematic climate/energy investing.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Retail, real estate, private equity, asset management, climate/energy</t>
+          <t>Toys/entertainment (core), real estate, renewable energy/climate, diversified financial investments</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>EUR 35-38 billion</t>
+          <t>~$16 billion (family wealth)</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Zug</t>
+          <t>Billund</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Canton of Zug</t>
+          <t>Region of Southern Denmark</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Martijn Brenninkmeijer</t>
+          <t>Soren Thorup Sorensen</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Chairman of the Board, COFRA Holding AG</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -3524,12 +3544,12 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Announced opening of ~EUR 38bn portfolio to external investors (April 2025); Florian Brenninkmeyer appointed CFO effective 1 Jan 2025; Redevco closed landmark GBP 47.5m real-estate-debt loan (April 2025).</t>
+          <t>KIRKBI Climate follow-on investment in Highview Power (Hunterston project) announced November 2025 (second investment after June 2024 Carrington); Adapture Renewables (KIRKBI-majority-owned) acquired 110MW Colorado solar-plus-storage project March 2025; generational handover of board chair to Thomas Kirk Kristiansen May 2023.</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2025-04; 2025-01-01; 2025-04</t>
+          <t>2025-11; 2025-03; 2023-05</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3539,19 +3559,19 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>COFRA is primarily a family holding company; its asset-management arm Anthos is opening to third-party capital (2025), which blurs the pure single-family-office boundary. Classified SFO at the holding level but noted as trending toward external capital.</t>
+          <t>KIRKBI is both the family holding company (owns LEGO) and the family investment office; some may classify it as a holding company rather than a pure family office. AUM figure is the family-wealth press figure, not full portfolio value.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SFO-athos-strungmann</t>
+          <t>SFO-tethys-invest-bettencourt</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Athos (Strungmann Family Office)</t>
+          <t>Tethys / Tethys Invest (Bettencourt Meyers Family Office)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3561,50 +3581,62 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Strungmann family (Andreas and Thomas Strungmann, founders of Hexal)</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+          <t>Bettencourt Meyers family (majority shareholder of L'Oreal; Francoise Bettencourt Meyers)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://tethys.fr/</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/t%C3%A9thys</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Munich-based single-family office of the Strungmann twins, focused heavily on biotech and life sciences. Anchored and remains largest shareholder of BioNTech (~43.5%) and holds stakes in Formycon and Immatics; actively recycles BioNTech proceeds into new European biotech ventures.</t>
+          <t>Paris-based single-family office of the Bettencourt Meyers family, holder of the family's ~34% L'Oreal stake. Its subsidiary Tethys Invest (&gt;EUR 3bn capital) makes long-term direct investments deliberately outside L'Oreal's competitive scope, with a healthcare emphasis (Elsan private hospitals, Sebia diagnostics).</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Long-horizon anchor investing in biotech and life sciences, recycling returns from BioNTech into the next generation of European biotech.</t>
+          <t>Preserve the L'Oreal core holding and deploy dividend income into long-term entrepreneurial direct investments, notably healthcare, that do not compete with L'Oreal.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Biotech, life sciences, healthcare technology</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>Healthcare (hospitals, diagnostics), consumer, technology, diversified</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>&gt; $90 billion (family assets)</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Bavaria</t>
+          <t>Ile-de-France</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Andreas Strungmann</t>
+          <t>Alexandre Benais</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Family Principal / Co-Founder</t>
+          <t>CEO, Tethys Invest</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -3617,12 +3649,12 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Participated in AAVantgarde Bio's $141m Series B (Nov 2025); AMSilk EUR 52m round (Sep 2025); Antheia funding ($56m Jun 2025, $24m Jan 2026); admin services of Athos Service acquired by Bolder Group (May 2024).</t>
+          <t>Named new head of family investment firm reported 2023-03-13 (The National); family succession moves (Jean-Victor Meyers to L'Oreal vice-chairman; Alexandre Benais to family L'Oreal board seat) reported 2025-02; co-invested (with Chanel/Wertheimer) in The Row reported 2024-09.</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2025-11; 2025-09; 2025-06; 2026-01; 2024-05</t>
+          <t>2023-03-13; 2025-02-08; 2024-09</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3632,19 +3664,19 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>No public website confirmed. 'Athos Service GmbH' is the services entity; the investing vehicle is often cited as 'Athos KG'. Investment-round dates sourced from family-office trade press rather than primary filings. AUM not disclosed.</t>
+          <t>'Tethys' (parent) vs 'Tethys Invest' (investment subsidiary) are distinct entities; leadership names span both. AUM is the family-asset press figure, not a disclosed managed-portfolio AUM.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SFO-premji-invest</t>
+          <t>SFO-cofra-holding-brenninkmeijer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Premji Invest (Azim Premji Family Office)</t>
+          <t>COFRA Holding (Brenninkmeijer Family Office)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3654,62 +3686,58 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Premji family (Azim Premji, founder of Wipro)</t>
+          <t>Brenninkmeijer family (founders/owners of C&amp;A; ~500 family members)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.premjiinvest.com/</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/premjiinvest</t>
-        </is>
-      </c>
+          <t>https://www.cofraholding.com/</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bengaluru-based family office and investment firm managing the wealth of Azim Premji and family (and closely tied to the Azim Premji Foundation endowment). Invests across public equities, private equity and venture, backing technology, financial services, consumer, healthcare and industrials; crossed $10bn in managed assets.</t>
+          <t>Zug-based family-owned holding coordinating the Brenninkmeijer family's global operations and ~EUR 35-38bn asset base across retail (C&amp;A), real estate (Redevco), private equity (Bregal Investments) and asset management (Anthos). In 2025 the family announced it would open its portfolio to outside investors, a shift from its historically secretive model.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Long-horizon growth investing across public and private markets in emerging/disruptive technology and consumer/financial sectors.</t>
+          <t>Long-term stewardship of family capital across operating businesses, real estate, private equity and (increasingly) externally-opened investment platforms.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Technology, financial services, consumer, healthcare, industrials</t>
+          <t>Retail, real estate, private equity, asset management, climate/energy</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>&gt; $10 billion</t>
+          <t>EUR 35-38 billion</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Zug</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Canton of Zug</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>T.K. Kurien</t>
+          <t>Martijn Brenninkmeijer</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>CEO &amp; Managing Partner</t>
+          <t>Chairman of the Board, COFRA Holding AG</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -3722,12 +3750,12 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Acquisition of Anand Chemiceutics reported 2025-11-13; participated in Runway Series E (with General Atlantic, Nvidia) 2026-02-10; 19 funding rounds / 2 acquisitions in trailing 12 months (per Tracxn, Feb 2026).</t>
+          <t>Announced opening of ~EUR 38bn portfolio to external investors (April 2025); Florian Brenninkmeyer appointed CFO effective 1 Jan 2025; Redevco closed landmark GBP 47.5m real-estate-debt loan (April 2025).</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2025-11-13; 2026-02-10</t>
+          <t>2025-04; 2025-01-01; 2025-04</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3737,19 +3765,19 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Premji Invest also manages the Azim Premji Foundation's endowment, so it straddles family-office and foundation-endowment functions; consistently described as a family office, hence corroborated rather than strong-single-family-only.</t>
+          <t>COFRA is primarily a family holding company; its asset-management arm Anthos is opening to third-party capital (2025), which blurs the pure single-family-office boundary. Classified SFO at the holding level but noted as trending toward external capital.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SFO-catamaran-ventures-murthy</t>
+          <t>SFO-athos-strungmann</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Catamaran Ventures (N.R. Narayana Murthy Family Office)</t>
+          <t>Athos (Strungmann Family Office)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3759,58 +3787,50 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Murthy family (N.R. Narayana Murthy, co-founder of Infosys)</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>https://catamaran.in/</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/catamaran-ventures</t>
-        </is>
-      </c>
+          <t>Strungmann family (Andreas and Thomas Strungmann, founders of Hexal)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bengaluru-based single-family office of Infosys co-founder N.R. Narayana Murthy, investing permanent family capital (no external LPs). Focused on growth capital, notably Indian manufacturing and deep tech; has recently turned more cautious on Indian startup valuations.</t>
+          <t>Munich-based single-family office of the Strungmann twins, focused heavily on biotech and life sciences. Anchored and remains largest shareholder of BioNTech (~43.5%) and holds stakes in Formycon and Immatics; actively recycles BioNTech proceeds into new European biotech ventures.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Permanent-capital growth investing, with emphasis on Indian manufacturing and deep-tech, valuation-disciplined.</t>
+          <t>Long-horizon anchor investing in biotech and life sciences, recycling returns from BioNTech into the next generation of European biotech.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Manufacturing, deep tech, consumer, technology</t>
+          <t>Biotech, life sciences, healthcare technology</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>N.R. Narayana Murthy</t>
+          <t>Andreas Strungmann</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Founder / Chairman Emeritus (Family Principal)</t>
+          <t>Family Principal / Co-Founder</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -3823,12 +3843,12 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
-          <t>Bloomberg (2025-08-26) reporting Catamaran growing cautious on Indian startup valuations; recent deep-tech stake and follow-on investments (Akshayakalpa first-time, Innoviti follow-on) in 2025.</t>
+          <t>Participated in AAVantgarde Bio's $141m Series B (Nov 2025); AMSilk EUR 52m round (Sep 2025); Antheia funding ($56m Jun 2025, $24m Jan 2026); admin services of Athos Service acquired by Bolder Group (May 2024).</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2025-08-26; 2025</t>
+          <t>2025-11; 2025-09; 2025-06; 2026-01; 2024-05</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3838,19 +3858,19 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Investment pace slowed in 2025 (approximately one new investment) per Tracxn; AUM not disclosed.</t>
+          <t>No public website confirmed. 'Athos Service GmbH' is the services entity; the investing vehicle is often cited as 'Athos KG'. Investment-round dates sourced from family-office trade press rather than primary filings. AUM not disclosed.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>UKCH-10876208</t>
+          <t>SFO-premji-invest</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sha Family Office Ltd</t>
+          <t>Premji Invest (Azim Premji Family Office)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3860,32 +3880,64 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sha family (controlling PSCs: Mr Sharnpreet Singh Buttar)</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+          <t>Premji family (Azim Premji, founder of Wipro)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://www.premjiinvest.com/</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/premjiinvest</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Bengaluru-based family office and investment firm managing the wealth of Azim Premji and family (and closely tied to the Azim Premji Foundation endowment). Invests across public equities, private equity and venture, backing technology, financial services, consumer, healthcare and industrials; crossed $10bn in managed assets.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Long-horizon growth investing across public and private markets in emerging/disruptive technology and consumer/financial sectors.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>64205 - Activities of financial services holding companies; 64209 - Activities of other holding companies not elsewhere classified</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>Technology, financial services, consumer, healthcare, industrials</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>&gt; $10 billion</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>SIC codes - 64205</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>T.K. Kurien</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>CEO &amp; Managing Partner</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -3894,28 +3946,36 @@
         </is>
       </c>
       <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Acquisition of Anand Chemiceutics reported 2025-11-13; participated in Runway Series E (with General Atlantic, Nvidia) 2026-02-10; 19 funding rounds / 2 acquisitions in trailing 12 months (per Tracxn, Feb 2026).</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>2025-11-13; 2026-02-10</t>
+        </is>
+      </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>UK filing SIC: fo-relevant-sic. Active officers: BUTTAR, Sharnpreet Singh () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
+          <t>Premji Invest also manages the Azim Premji Foundation's endowment, so it straddles family-office and foundation-endowment functions; consistently described as a family office, hence corroborated rather than strong-single-family-only.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>UKCH-15240886</t>
+          <t>SFO-catamaran-ventures-murthy</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Freedman Family Office</t>
+          <t>Catamaran Ventures (N.R. Narayana Murthy Family Office)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3925,32 +3985,60 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Freedman family (controlling PSCs: Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman)</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+          <t>Murthy family (N.R. Narayana Murthy, co-founder of Infosys)</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://catamaran.in/</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/catamaran-ventures</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Bengaluru-based single-family office of Infosys co-founder N.R. Narayana Murthy, investing permanent family capital (no external LPs). Focused on growth capital, notably Indian manufacturing and deep tech; has recently turned more cautious on Indian startup valuations.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Permanent-capital growth investing, with emphasis on Indian manufacturing and deep-tech, valuation-disciplined.</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>64301 - Activities of investment trusts</t>
+          <t>Manufacturing, deep tech, consumer, technology</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>N.R. Narayana Murthy</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Founder / Chairman Emeritus (Family Principal)</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -3959,28 +4047,36 @@
         </is>
       </c>
       <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Bloomberg (2025-08-26) reporting Catamaran growing cautious on Indian startup valuations; recent deep-tech stake and follow-on investments (Akshayakalpa first-time, Innoviti follow-on) in 2025.</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>2025-08-26; 2025</t>
+        </is>
+      </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>UK filing SIC: fo-relevant-sic. Active officers: FREEDMAN, Elaine Wilson (), FREEDMAN, Laura-Leigh (), ZIMMERMAN, Samantha Jade () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
+          <t>Investment pace slowed in 2025 (approximately one new investment) per Tracxn; AUM not disclosed.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UKCH-11031775</t>
+          <t>UKCH-10876208</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ralph Family Office Limited</t>
+          <t>Sha Family Office Ltd</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3990,7 +4086,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ralph family (controlling PSCs: Melanie Lynette Ralph; Mr Jan De Ridder Ralph)</t>
+          <t>Sha family (controlling PSCs: Mr Sharnpreet Singh Buttar)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
@@ -3999,13 +4095,13 @@
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>64301 - Activities of investment trusts; 68209 - Other letting and operating of own or leased real estate</t>
+          <t>64205 - Activities of financial services holding companies; 64209 - Activities of other holding companies not elsewhere classified</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>SIC codes - 64301</t>
+          <t>SIC codes - 64205</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4032,6 +4128,136 @@
         </is>
       </c>
       <c r="W36" t="inlineStr">
+        <is>
+          <t>UK filing SIC: fo-relevant-sic. Active officers: BUTTAR, Sharnpreet Singh () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>UKCH-15240886</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Freedman Family Office</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Freedman family (controlling PSCs: Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>64301 - Activities of investment trusts</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>UK filing SIC: fo-relevant-sic. Active officers: FREEDMAN, Elaine Wilson (), FREEDMAN, Laura-Leigh (), ZIMMERMAN, Samantha Jade () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>UKCH-11031775</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Ralph Family Office Limited</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Ralph family (controlling PSCs: Melanie Lynette Ralph; Mr Jan De Ridder Ralph)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>64301 - Activities of investment trusts; 68209 - Other letting and operating of own or leased real estate</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>SIC codes - 64301</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
         <is>
           <t>UK filing SIC: fo-relevant-sic. Active officers: RALPH, Jan De Ridder (), RALPH, Melanie Lynette (), BETHELL, Karen (), BETHELL, Stuart (), YOULL, Gavin William () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
         </is>
@@ -4048,7 +4274,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4236,12 +4462,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEC13F-0001938970</t>
+          <t>SEC13F-0001802084</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Callan Family Office, LLC</t>
+          <t>CVA Family Office, LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4251,22 +4477,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001938970); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001802084); discovered via fts</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001938970&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001802084&amp;type=13F</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>A registered investment adviser and multi-family office that markets to and serves multiple ultra-high-net-worth families; accepts clients with $50M+ to invest (average client ~$100M) and reported &gt;$5B AUM by early 2024. Source: https://riabiz.com/a/2024/4/9/an-abbot-downing-breakaway-but-not-exactly-callan-family-office-hits-5-billion-of-aum-after-just-two-years-using-a-creative-callan-brand-deal-and-a-partnership-model</t>
+          <t>Boutique multi-family wealth-management firm serving multiple high-net-worth business owners/entrepreneurs; ~43 client accounts / ~24 client relationships, ~$222M regulatory AUM. Sources: https://wallmine.com/adviser/235356/cva-family-office-llc ; https://classvifamilyoffice.com/about/</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Self-describes as a family office; RIABiz and Forbes cover it as an MFO; files 13F under CIK 0001938970; published team/services pages. Source: https://callanfamilyoffice.com/team/ and https://www.forbes.com/companies/callan-family-office/</t>
+          <t>SEC-registered investment adviser (13F filer) established September 2016 as an RIA; branded and operated as a family office (now 'Class VI Family Office'). Sources: https://www.classvipartners.com/our-team/matt-blackburn/ ; https://classvifamilyoffice.com/about/</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -4276,12 +4502,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>https://riabiz.com/a/2024/4/9/an-abbot-downing-breakaway-but-not-exactly-callan-family-office-hits-5-billion-of-aum-after-just-two-years-using-a-creative-callan-brand-deal-and-a-partnership-model (March 2024)</t>
+          <t>Adviser/ADV aggregators. https://wallmine.com/adviser/235356/cva-family-office-llc</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Ginter is CEO and Founding Partner, leading firm strategy and business development; he is the current top principal and matches the 13F signatory 'John Ginter' (Jack = John). Verified on the firm's own team page. Source: https://callanfamilyoffice.com/team/jack-ginter/</t>
+          <t>Co-founder of the family office (est. Sept 2016 as CVA Family Office) who leads the wealth team and 'customiz[es] planning and investment management advice for Class VI clients' — the lead investment/advisory decision-maker. Co-founders Chris Younger (CEO, Class VI Partners) and David Tolson also sit above the group. https://www.classvipartners.com/our-team/matt-blackburn/ ; https://classvifamilyoffice.com/about/</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -4291,22 +4517,22 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://callanfamilyoffice.com/team/jack-ginter/</t>
+          <t>https://classvifamilyoffice.com/about/</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>The firm's own team/bio page for Jack Ginter publishes his individual professional email as jginter@callanfo.com (displayed on his profile page alongside his title 'Chief Executive Officer, Founding Partner'). Note the mail domain callanfo.com differs from the website domain.</t>
+          <t>The firm's own About/team page publishes individual emails including 'Matt@classvipartners.com' (and 'dalyce@classvipartners.com') alongside the general familyoffice@classvipartners.com. Published individual address; not independently provider-verified.</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1938970/000193897026000003/primary_doc.xml</t>
+          <t>https://cvafamilyoffice.com/ (main office line, 101 University Blvd, Denver; firm switchboard, not a personal line)</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>https://riabiz.com/a/2024/4/9/an-abbot-downing-breakaway-but-not-exactly-callan-family-office-hits-5-billion-of-aum-after-just-two-years-using-a-creative-callan-brand-deal-and-a-partnership-model ; https://www.diamond-consultants.com/building-a-business-with-intention-the-5b-callan-family-office-recipe-for-success/</t>
+          <t>https://www.classvipartners.com/our-team/matt-blackburn/ ; https://classvifamilyoffice.com/about/ ; https://www.getwarmer.com/firms/class-vi-family-office-llc</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -4318,12 +4544,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEC13F-0001596197</t>
+          <t>SEC13F-0001845066</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>INTREPID FAMILY OFFICE LLC</t>
+          <t>Collective Family Office LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4333,63 +4559,79 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001596197); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001845066); discovered via fts</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001596197&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001845066&amp;type=13F</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No SEC investment-adviser registration found in IAPD (searched 'INTREPID FAMILY OFFICE LLC'); files SEC Form 13F-HR (CIK 0001596197) reporting $123.64B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
+          <t>Self-branded multi-family office serving multiple Central Pennsylvania families ('serves multiple families rather than a single family's wealth'); Form ADV shows ~127 clients and ~$446M discretionary AUM. Broad multi-client RIA, not a single-family vehicle. Sources: https://www.collectivefamilyoffice.com/team-member-01 ; https://adviserinfo.sec.gov/firm/summary/301274 ; https://aum13f.com/firm/collective-family-office-llc</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No SEC investment-adviser registration found in IAPD (searched 'INTREPID FAMILY OFFICE LLC'); files SEC Form 13F-HR (CIK 0001596197) reporting $123.64B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
+          <t>SEC-registered investment adviser (CRD 301274, 13F filer) established 2019 and branded/operated as a family office; provides discretionary portfolio management and wealth-management services to HNW families. Sources: https://www.collectivefamilyoffice.com/ ; https://adviserinfo.sec.gov/firm/summary/301274</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Form ADV / adviser aggregators and 13F. https://adviserinfo.sec.gov/firm/summary/301274 ; https://aum13f.com/firm/collective-family-office-llc ; https://fintrx.com/firms/firm/collective-family-office-llc-301274 ; https://whalewisdom.com/filer/collective-family-office-llc</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Signed the firm's Form 13F-HR (03-31-2026) as Chief Financial Officer — verified associated person; investment-decision-maker status to be confirmed separately.</t>
+          <t>David Sivel founded Collective Family Office in 2019 and is Principal &amp; CEO with 30+ years of wealth-management experience (ex-BNY Mellon, Wilmington Trust); he is the firm's founder and lead decision-maker. Co-principal Brian Luster serves as Chief Investment Officer (investment lead) and Trevor Hoffman as COO. https://www.collectivefamilyoffice.com/team-member-01/david-sivel ; https://www.linkedin.com/in/david-s-sivel-cfp%C2%AE-ab078811/</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://www.collectivefamilyoffice.com/contact</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Firm's own Contact page publishes individual addresses for each principal, including 'David.Sivel@CollectiveFO.com' (also Brian.Luster@, Trevor.Hoffman@, Lisa.Fetrow@CollectiveFO.com) alongside the general Info@CollectiveFO.com. Published individual address; not independently provider-verified.</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
+          <t>https://www.collectivefamilyoffice.com/contact (direct line listed for David Sivel; main line 717-893-5057)</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>SEC EDGAR 13F-HR 0001013594-26-000589 (2026-05-15)</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
+          <t>https://adviserinfo.sec.gov/firm/summary/301274 ; https://www.collectivefamilyoffice.com/team-member-01 ; https://aum13f.com/firm/collective-family-office-llc</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEC13F-0001536411</t>
+          <t>SEC13F-0001938970</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Duquesne Family Office LLC</t>
+          <t>Callan Family Office, LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4399,22 +4641,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001536411); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001938970); discovered via fts</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001536411&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001938970&amp;type=13F</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Widely reported as the private investment office through which Stanley Druckenmiller manages his own family's capital after closing his hedge fund Duquesne Capital Management to outside investors in 2010. No external clients; it manages one family's money. Source: https://www.fool.com/investing/how-to-invest/famous-investors/duquesne-family-office and https://www.institutionalinvestor.com/article/stan-druckenmiller-overhauls-his-family-offices-us-stock-portfolio</t>
+          <t>A registered investment adviser and multi-family office that markets to and serves multiple ultra-high-net-worth families; accepts clients with $50M+ to invest (average client ~$100M) and reported &gt;$5B AUM by early 2024. Source: https://riabiz.com/a/2024/4/9/an-abbot-downing-breakaway-but-not-exactly-callan-family-office-hits-5-billion-of-aum-after-just-two-years-using-a-creative-callan-brand-deal-and-a-partnership-model</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Files SEC Form 13F as 'Duquesne Family Office LLC' (CIK 0001536411); press uniformly describes it as Druckenmiller's family office. Source: https://13f.info/manager/0001536411-duquesne-family-office-llc</t>
+          <t>Self-describes as a family office; RIABiz and Forbes cover it as an MFO; files 13F under CIK 0001938970; published team/services pages. Source: https://callanfamilyoffice.com/team/ and https://www.forbes.com/companies/callan-family-office/</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -4424,46 +4666,54 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13F value: https://13f.info/13f/000153641125000017-duquesne-family-office-llc-q3-2025 (as of 2025-09-30) and https://seekingalpha.com/article/4881297-tracking-stanley-druckenmillers-duquesne-family-office-portfolio-q4-2025-update ; net worth: https://www.forbes.com/profile/stanley-druckenmiller/</t>
+          <t>https://riabiz.com/a/2024/4/9/an-abbot-downing-breakaway-but-not-exactly-callan-family-office-hits-5-billion-of-aum-after-just-two-years-using-a-creative-callan-brand-deal-and-a-partnership-model (March 2024)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Druckenmiller is the founder and sole principal directing all investment decisions; he is named as portfolio manager on the firm's 13F activity in current (2025) press coverage. The 13F signatory Sue Meng is General Counsel (compliance), not the investment decision-maker. Source: https://www.institutionalinvestor.com/article/stan-druckenmiller-overhauls-his-family-offices-us-stock-portfolio and https://www.levelfields.ai/news/stanley-druckenmillers-duquesne-family-office-cuts-exposure-adds-new-tech-and-energy-stocks-in-q1-2025</t>
+          <t>Ginter is CEO and Founding Partner, leading firm strategy and business development; he is the current top principal and matches the 13F signatory 'John Ginter' (Jack = John). Verified on the firm's own team page. Source: https://callanfamilyoffice.com/team/jack-ginter/</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://callanfamilyoffice.com/team/jack-ginter/</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Tried: web searches for a Duquesne domain/team page (none exists); no firm website to host a team directory; no filing or press publishing an individual email. Refused to construct one from a name+domain pattern.</t>
+          <t>The firm's own team/bio page for Jack Ginter publishes his individual professional email as jginter@callanfo.com (displayed on his profile page alongside his title 'Chief Executive Officer, Founding Partner'). Note the mail domain callanfo.com differs from the website domain.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1536411/000153641126000004/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1938970/000193897026000003/primary_doc.xml</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>https://13f.info/13f/000153641125000017-duquesne-family-office-llc-q3-2025 ; https://seekingalpha.com/article/4881297-tracking-stanley-druckenmillers-duquesne-family-office-portfolio-q4-2025-update ; https://www.levelfields.ai/news/stanley-druckenmillers-duquesne-family-office-cuts-exposure-adds-new-tech-and-energy-stocks-in-q1-2025</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
+          <t>https://riabiz.com/a/2024/4/9/an-abbot-downing-breakaway-but-not-exactly-callan-family-office-hits-5-billion-of-aum-after-just-two-years-using-a-creative-callan-brand-deal-and-a-partnership-model ; https://www.diamond-consultants.com/building-a-business-with-intention-the-5b-callan-family-office-recipe-for-success/</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEC13F-0001683689</t>
+          <t>SEC13F-0002135110</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kopp Family Office, LLC</t>
+          <t>Pioneer Family Office, LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4473,63 +4723,79 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001683689); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0002135110); discovered via fts</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001683689&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002135110&amp;type=13F</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>No SEC investment-adviser registration found in IAPD (searched 'Kopp Family Office, LLC'); files SEC Form 13F-HR (CIK 0001683689) reporting $163.17B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
+          <t>Part of Pioneer Wealth Management Group (est. Israel 1986) serving international ultra-high-net-worth families across five continents plus institutions; acts as a capital allocator for individual/family and institutional clients. Multi-client, not single-family. Sources: https://www.piowealth.com/PFO/who-we-are ; https://www.piowealth.com/PFO/our-team ; https://fintrx.com/firms/firm/pioneer-family-office-llc-142856</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No SEC investment-adviser registration found in IAPD (searched 'Kopp Family Office, LLC'); files SEC Form 13F-HR (CIK 0001683689) reporting $163.17B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
+          <t>SEC-registered investment adviser (CRD 142856, 13F filer), SEC-registered in 2019; branded family office providing integrated wealth and investment management with no proprietary funds. Sources: https://adviserinfo.sec.gov/firm/summary/142856 ; https://www.piowealth.com/PFO/our-services</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Adviser aggregators. https://fintrx.com/firms/firm/pioneer-family-office-llc-142856 ; https://aum13f.com/firm/pioneer-family-office-llc</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Signed the firm's Form 13F-HR (06-30-2026) as Chief Financial Officer — verified associated person; investment-decision-maker status to be confirmed separately.</t>
+          <t>Aviram (Avi) Nahum is the US-based Managing Partner and Executive Director of the Pioneer Group who sits on the firm's Investment Committee and Steering Committee — the principal investment decision-maker for the North Miami Beach SEC entity. Firm co-founder Omer Galin (1986) leads the broader international organization from Israel. https://www.piowealth.com/PFO/our-team ; https://www.linkedin.com/in/aviram-nahum-450600243/</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://www.piowealth.com/PFO/our-team</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Firm's own team page publishes individual emails alongside each bio, including 'avin@piowealth.com' for Aviram Nahum (also omerg@piowealth.com for co-founder Omer Galin, ruthieb@, rafaelp@, santiagom@, iaell@piowealth.com). Published individual address; not independently provider-verified.</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1683689/000089271226000313/primary_doc.xml</t>
+          <t>https://www.piowealth.com/PFO/our-team (US office line listed with Aviram Nahum's bio; shared main line, not necessarily a dedicated direct line)</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>SEC EDGAR 13F-HR 0000892712-26-000313 (2026-07-09)</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
+          <t>https://www.piowealth.com/PFO/who-we-are ; https://www.piowealth.com/PFO/our-team ; https://fintrx.com/firms/firm/pioneer-family-office-llc-142856</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEC13F-0001889527</t>
+          <t>SEC13F-0001596197</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Louis-Dreyfus Family Office LLC</t>
+          <t>INTREPID FAMILY OFFICE LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4539,22 +4805,22 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001889527); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001596197); discovered via fts</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001889527&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001596197&amp;type=13F</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>A small, named single-family office (5 13F holdings, ~$64.7M, ~4 employees per business directories) serving the Louis-Dreyfus family; no evidence of external clients or a marketed multi-family service offering. Source: https://www.ctcompanydir.com/companies/louis-dreyfus-family-office-llc/ and https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
+          <t>No SEC investment-adviser registration found in IAPD (searched 'INTREPID FAMILY OFFICE LLC'); files SEC Form 13F-HR (CIK 0001596197) reporting $123.64B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Registered LLC named 'Louis-Dreyfus Family Office LLC' at 10 Westport Rd, Wilton CT (registered 2007 per directory); files SEC 13F under CIK 0001889527. Source: https://www.ctcompanydir.com/companies/louis-dreyfus-family-office-llc/</t>
+          <t>No SEC investment-adviser registration found in IAPD (searched 'INTREPID FAMILY OFFICE LLC'); files SEC Form 13F-HR (CIK 0001596197) reporting $123.64B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -4562,14 +4828,10 @@
           <t>corroborated</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc (latest filing Q3 2022, value ~$64,676K as of 2022-09-30); directory revenue estimate: https://www.manta.com/c/mm0v4v4/loius-dreyfus-family-office-llc</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Wingertzahn is the named 13F signatory and CFO; for an office this small he is likely the day-to-day operational and investment administrator. However, the TRUE family investment principal (a Louis-Dreyfus family member/heir) is not publicly identified. Source (signatory role provided in brief); firm identity: https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
+          <t>Signed the firm's Form 13F-HR (03-31-2026) as Chief Financial Officer — verified associated person; investment-decision-maker status to be confirmed separately.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -4578,19 +4840,15 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>Tried: searches for a firm website/team page (none), for Wingertzahn contact details, and for any filing/press publishing an individual email. None found published. Did not construct any address.</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1596197/000101359426000589/primary_doc.xml</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
+          <t>SEC EDGAR 13F-HR 0001013594-26-000589 (2026-05-15)</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -4598,37 +4856,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UKCH-12706913</t>
+          <t>SEC13F-0001536411</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Francis Family Office Limited</t>
+          <t>Duquesne Family Office LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Companies House 12706913 (Private limited company); inc. 30 June 2020</t>
+          <t>EDGAR 13F filer (CIK 0001536411); discovered via fts</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/12706913</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001536411&amp;type=13F</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Directors are three members of the Francis family (Benjamin David, Joseph John, Steven John Francis); vehicle holds Ben Francis's Gymshark stake. Source: https://find-and-update.company-information.service.gov.uk/company/12706913/officers ; https://www.netincome.co/p/the-boardroom-drama-behind-one-of</t>
+          <t>Widely reported as the private investment office through which Stanley Druckenmiller manages his own family's capital after closing his hedge fund Duquesne Capital Management to outside investors in 2010. No external clients; it manages one family's money. Source: https://www.fool.com/investing/how-to-invest/famous-investors/duquesne-family-office and https://www.institutionalinvestor.com/article/stan-druckenmiller-overhauls-his-family-offices-us-stock-portfolio</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Companies House shows firm renamed from 'BEN FRANCIS LIMITED' to 'FRANCIS FAMILY OFFICE LIMITED' on 2021-02-03; SIC 64209; registered at Gymshark HQ. Press: Ben Francis transferred half his Gymshark ownership into the vehicle, which he owns 100%. Sources: https://find-and-update.company-information.service.gov.uk/company/12706913 ; https://www.netincome.co/p/the-boardroom-drama-behind-one-of</t>
+          <t>Files SEC Form 13F as 'Duquesne Family Office LLC' (CIK 0001536411); press uniformly describes it as Druckenmiller's family office. Source: https://13f.info/manager/0001536411-duquesne-family-office-llc</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -4638,29 +4896,33 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Not disclosed. Ben Francis personal net worth ~$900m-1.3bn (Forbes) is personal wealth, not stated FO AUM. https://www.forbes.com/profile/ben-francis-1/</t>
+          <t>13F value: https://13f.info/13f/000153641125000017-duquesne-family-office-llc-q3-2025 (as of 2025-09-30) and https://seekingalpha.com/article/4881297-tracking-stanley-druckenmillers-duquesne-family-office-portfolio-q4-2025-update ; net worth: https://www.forbes.com/profile/stanley-druckenmiller/</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Named director since incorporation (2020-06-30), 100% owner and actual decision-maker. https://find-and-update.company-information.service.gov.uk/company/12706913/officers</t>
+          <t>Druckenmiller is the founder and sole principal directing all investment decisions; he is named as portfolio manager on the firm's 13F activity in current (2025) press coverage. The 13F signatory Sue Meng is General Counsel (compliance), not the investment decision-maker. Source: https://www.institutionalinvestor.com/article/stan-druckenmiller-overhauls-his-family-offices-us-stock-portfolio and https://www.levelfields.ai/news/stanley-druckenmillers-duquesne-family-office-cuts-exposure-adds-new-tech-and-energy-stocks-in-q1-2025</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>No individual email published; firm has no website. Checked Companies House filings and Gymshark press.</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>Tried: web searches for a Duquesne domain/team page (none exists); no firm website to host a team directory; no filing or press publishing an individual email. Refused to construct one from a name+domain pattern.</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1536411/000153641126000004/primary_doc.xml</t>
+        </is>
+      </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/12706913 ; https://www.forbes.com/sites/robertolsen-1/2026/07/04/britains-youngest-billionaire-wants-more-control-over-gymshark/</t>
+          <t>https://13f.info/13f/000153641125000017-duquesne-family-office-llc-q3-2025 ; https://seekingalpha.com/article/4881297-tracking-stanley-druckenmillers-duquesne-family-office-portfolio-q4-2025-update ; https://www.levelfields.ai/news/stanley-druckenmillers-duquesne-family-office-cuts-exposure-adds-new-tech-and-energy-stocks-in-q1-2025</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -4668,77 +4930,65 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UKCH-07931194</t>
+          <t>SEC13F-0001683689</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Wimmer Family Office Ltd</t>
+          <t>Kopp Family Office, LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Companies House 07931194 (Private limited company); inc. 1 February 2012</t>
+          <t>EDGAR 13F filer (CIK 0001683689); discovered via fts</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/07931194</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001683689&amp;type=13F</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Website: 'The Wimmer Family Office is based in Mayfair, London, and was established by Per Wimmer.' Built around a single principal. https://wfo.am/</t>
+          <t>No SEC investment-adviser registration found in IAPD (searched 'Kopp Family Office, LLC'); files SEC Form 13F-HR (CIK 0001683689) reporting $163.17B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Active FCA-authorised entity (FCA #665654), SIC 66190; live website branded as a family office with Mayfair address. https://wfo.am/ ; https://find-and-update.company-information.service.gov.uk/company/07931194</t>
+          <t>No SEC investment-adviser registration found in IAPD (searched 'Kopp Family Office, LLC'); files SEC Form 13F-HR (CIK 0001683689) reporting $163.17B in 13(f) holdings under a family-office name. Managing that scale without adviser registration is consistent with the single-family-office exemption (Advisers Act rule 202(a)(11)(G)-1).</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Not disclosed. Sectors are those of associated firm Wimmer Financial. https://wimmerfinancial.com/</t>
-        </is>
-      </c>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Founder/namesake; director from incorporation (2012) until resignation 2024-09-25; still presented as founder/CEO on website and LinkedIn. https://find-and-update.company-information.service.gov.uk/company/07931194/officers ; https://uk.linkedin.com/in/perwimmer</t>
+          <t>Signed the firm's Form 13F-HR (06-30-2026) as Chief Financial Officer — verified associated person; investment-decision-maker status to be confirmed separately.</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>https://wfo.am/</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Only a generic mailbox (info@WFO.am) is published (excluded). A per.wimmer@wimmerfinancial.com string appeared only in a URL parameter, not as a published contact — not shipped.</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>https://wfo.am/contact-us/ (firm switchboard, not a personal line)</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1683689/000089271226000313/primary_doc.xml</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/07931194/officers</t>
+          <t>SEC EDGAR 13F-HR 0000892712-26-000313 (2026-07-09)</t>
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
@@ -4746,12 +4996,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEC13F-0001802084</t>
+          <t>SEC13F-0001889527</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVA Family Office, LLC</t>
+          <t>Louis-Dreyfus Family Office LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4761,104 +5011,96 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001802084); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001889527); discovered via fts</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001802084&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001889527&amp;type=13F</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Boutique multi-family wealth-management firm serving multiple high-net-worth business owners/entrepreneurs; ~43 client accounts / ~24 client relationships, ~$222M regulatory AUM. Sources: https://wallmine.com/adviser/235356/cva-family-office-llc ; https://classvifamilyoffice.com/about/</t>
+          <t>A small, named single-family office (5 13F holdings, ~$64.7M, ~4 employees per business directories) serving the Louis-Dreyfus family; no evidence of external clients or a marketed multi-family service offering. Source: https://www.ctcompanydir.com/companies/louis-dreyfus-family-office-llc/ and https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (13F filer) established September 2016 as an RIA; branded and operated as a family office (now 'Class VI Family Office'). Sources: https://www.classvipartners.com/our-team/matt-blackburn/ ; https://classvifamilyoffice.com/about/</t>
+          <t>Registered LLC named 'Louis-Dreyfus Family Office LLC' at 10 Westport Rd, Wilton CT (registered 2007 per directory); files SEC 13F under CIK 0001889527. Source: https://www.ctcompanydir.com/companies/louis-dreyfus-family-office-llc/</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>corroborated</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Adviser/ADV aggregators. https://wallmine.com/adviser/235356/cva-family-office-llc</t>
+          <t>https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc (latest filing Q3 2022, value ~$64,676K as of 2022-09-30); directory revenue estimate: https://www.manta.com/c/mm0v4v4/loius-dreyfus-family-office-llc</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Co-founder of the family office (est. Sept 2016 as CVA Family Office) who leads the wealth team and 'customiz[es] planning and investment management advice for Class VI clients' — the lead investment/advisory decision-maker. Co-founders Chris Younger (CEO, Class VI Partners) and David Tolson also sit above the group. https://www.classvipartners.com/our-team/matt-blackburn/ ; https://classvifamilyoffice.com/about/</t>
+          <t>Wingertzahn is the named 13F signatory and CFO; for an office this small he is likely the day-to-day operational and investment administrator. However, the TRUE family investment principal (a Louis-Dreyfus family member/heir) is not publicly identified. Source (signatory role provided in brief); firm identity: https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>https://classvifamilyoffice.com/about/</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>The firm's own About/team page publishes individual emails including 'Matt@classvipartners.com' (and 'dalyce@classvipartners.com') alongside the general familyoffice@classvipartners.com. Published individual address; not independently provider-verified.</t>
+          <t>Tried: searches for a firm website/team page (none), for Wingertzahn contact details, and for any filing/press publishing an individual email. None found published. Did not construct any address.</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>https://cvafamilyoffice.com/ (main office line, 101 University Blvd, Denver; firm switchboard, not a personal line)</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1889527/000149315222031320/primary_doc.xml</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>https://www.classvipartners.com/our-team/matt-blackburn/ ; https://classvifamilyoffice.com/about/ ; https://www.getwarmer.com/firms/class-vi-family-office-llc</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
+          <t>https://13f.info/manager/0001889527-louis-dreyfus-family-office-llc</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEC13F-0001599603</t>
+          <t>UKCH-12706913</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tarbox Family Office, Inc.</t>
+          <t>Francis Family Office Limited</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>sec-13f</t>
+          <t>uk-companies-house</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001599603); discovered via fts</t>
+          <t>Companies House 12706913 (Private limited company); inc. 30 June 2020</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001599603&amp;type=13F</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/12706913</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>'The multi-family office ... with just 100+ client families and over $1 billion under management'; fee-only, $5M minimum, serving a select group of wealthy families/individuals. Sources: https://tarbox.com/who-we-are/ ; https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079</t>
+          <t>Directors are three members of the Francis family (Benjamin David, Joseph John, Steven John Francis); vehicle holds Ben Francis's Gymshark stake. Source: https://find-and-update.company-information.service.gov.uk/company/12706913/officers ; https://www.netincome.co/p/the-boardroom-drama-behind-one-of</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (13F filer) founded 1985 by Laura Tarbox; fee-only financial planning, tax preparation and investment advisory for HNW individuals, charities, businesses, trusts and estates. Sources: https://tarbox.com/history/ ; https://tarbox.com/who-we-are/</t>
+          <t>Companies House shows firm renamed from 'BEN FRANCIS LIMITED' to 'FRANCIS FAMILY OFFICE LIMITED' on 2021-02-03; SIC 64209; registered at Gymshark HQ. Press: Ben Francis transferred half his Gymshark ownership into the vehicle, which he owns 100%. Sources: https://find-and-update.company-information.service.gov.uk/company/12706913 ; https://www.netincome.co/p/the-boardroom-drama-behind-one-of</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -4868,136 +5110,120 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Firm-stated. https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079 ; https://tarbox.com/who-we-are/</t>
+          <t>Not disclosed. Ben Francis personal net worth ~$900m-1.3bn (Forbes) is personal wealth, not stated FO AUM. https://www.forbes.com/profile/ben-francis-1/</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Founder (1985), CEO and principal owner; CFP since 1984 with 40+ years' experience; sets firm vision and strategy and is the lead advisor/decision-maker. https://tarbox.com/team/laura-tarbox/ ; https://tarbox.com/history/</t>
+          <t>Named director since incorporation (2020-06-30), 100% owner and actual decision-maker. https://find-and-update.company-information.service.gov.uk/company/12706913/officers</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf</t>
-        </is>
-      </c>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Published on Laura Tarbox's own public presentation slide (title block reads 'Laura Tarbox, CFP(R) 949.721.2330 Laura@Tarbox.com'). Individual address on the firm's own domain; published, not independently provider-verified. Firm bio page itself shows only a phone and contact form. ZoomInfo listing (l***@tarboxgroup.com) is broker-masked and excluded.</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>https://tarbox.com/team/laura-tarbox/ (listed on Laura Tarbox's bio page; Newport Beach office line) and her presentation https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf</t>
-        </is>
-      </c>
+          <t>No individual email published; firm has no website. Checked Companies House filings and Gymshark press.</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>https://tarbox.com/history/ ; https://tarbox.com/who-we-are/ ; https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
+          <t>https://find-and-update.company-information.service.gov.uk/company/12706913 ; https://www.forbes.com/sites/robertolsen-1/2026/07/04/britains-youngest-billionaire-wants-more-control-over-gymshark/</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEC13F-0002056106</t>
+          <t>UKCH-07931194</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Stenger Family Office, LLC</t>
+          <t>Wimmer Family Office Ltd</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sec-13f</t>
+          <t>uk-companies-house</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0002056106); discovered via fts</t>
+          <t>Companies House 07931194 (Private limited company); inc. 1 February 2012</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002056106&amp;type=13F</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/07931194</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Self-described 'multi-family office'; the Stenger family has served 'over 1,200 families across the United States'. Serves many outside client families. Sources: https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
+          <t>Website: 'The Wimmer Family Office is based in Mayfair, London, and was established by Per Wimmer.' Built around a single principal. https://wfo.am/</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEC-registered investment adviser (13F filer); independent fiduciary wealth-management firm offering financial planning, investment management, tax and estate strategies under a family-office model; ~$731M AUM. Sources: https://www.stengerfamilyoffice.com/ </t>
+          <t>Active FCA-authorised entity (FCA #665654), SIC 66190; live website branded as a family office with Mayfair address. https://wfo.am/ ; https://find-and-update.company-information.service.gov.uk/company/07931194</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>corroborated</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Firm-stated. https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
+          <t>Not disclosed. Sectors are those of associated firm Wimmer Financial. https://wimmerfinancial.com/</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Founder and CEO / lead financial advisor; prior Senior Vice President financial advisor at Morgan Stanley Wealth Management, and roles at Invesco PowerShares and PwC; the firm's decision-maker and namesake. https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
+          <t>Founder/namesake; director from incorporation (2012) until resignation 2024-09-25; still presented as founder/CEO on website and LinkedIn. https://find-and-update.company-information.service.gov.uk/company/07931194/officers ; https://uk.linkedin.com/in/perwimmer</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://www.stengerfamilyoffice.com (published mailto/contact page)</t>
+          <t>https://wfo.am/</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>No individual email published on the firm site; contact is via a Calendly link (calendly.com/nicholasstenger/intro-meeting) rather than a published email address. No broker emails accepted.</t>
+          <t>Only a generic mailbox (info@WFO.am) is published (excluded). A per.wimmer@wimmerfinancial.com string appeared only in a URL parameter, not as a published contact — not shipped.</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
+          <t>https://wfo.am/contact-us/ (firm switchboard, not a personal line)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>https://www.stengerfamilyoffice.com/ ; https://www.stengerfamilyoffice.com/financialadvisornaperville ; https://podcasts.apple.com/us/podcast/the-nick-stenger-show/id1678810370</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
+          <t>https://find-and-update.company-information.service.gov.uk/company/07931194/officers</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEC13F-0001731123</t>
+          <t>SEC13F-0001599603</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Biltmore Family Office, LLC</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -5007,22 +5233,22 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001731123); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001599603); discovered via fts</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001731123&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001599603&amp;type=13F</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Independent SEC-registered adviser to investment-oriented multi-generational families plus institutional clients; ~951 accounts and ~$3.2-3.5B AUM (avg client ~$38M). A collaborative multi-family office, not a single-family vehicle. Sources: https://www.biltmorefamilyoffice.com/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
+          <t>'The multi-family office ... with just 100+ client families and over $1 billion under management'; fee-only, $5M minimum, serving a select group of wealthy families/individuals. Sources: https://tarbox.com/who-we-are/ ; https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (13F filer) founded 2008 (LLC organized 2013); positions itself as a hybrid family office and RIA. Sources: https://www.biltmorefamilyoffice.com/our-history/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
+          <t>SEC-registered investment adviser (13F filer) founded 1985 by Laura Tarbox; fee-only financial planning, tax preparation and investment advisory for HNW individuals, charities, businesses, trusts and estates. Sources: https://tarbox.com/history/ ; https://tarbox.com/who-we-are/</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -5032,46 +5258,54 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>AUM/ADV aggregators. https://fintrx.com/firms/firm/biltmore-family-office-llc-167174 ; https://advisor.guide/firms/biltmore-family-office ; https://whalewisdom.com/filer/biltmore-family-office-llc</t>
+          <t>Firm-stated. https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079 ; https://tarbox.com/who-we-are/</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Founder and President/CEO; 30 years' experience in investment management, asset allocation and investment-policy creation; prior Partner at GenSpring Family Offices, President at JPMorgan Private Bank, Managing Director at Brown Brothers Harriman. The firm's top decision-maker (Rael Gorelick is Partner &amp; Head of Investments / CIO-equivalent). https://www.biltmorefamilyoffice.com/who-we-are/chris-cecil/ ; https://www.linkedin.com/in/chris-cecil-9701b818/</t>
+          <t>Founder (1985), CEO and principal owner; CFP since 1984 with 40+ years' experience; sets firm vision and strategy and is the lead advisor/decision-maker. https://tarbox.com/team/laura-tarbox/ ; https://tarbox.com/history/</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>No individual email published on the firm site (biltmorefamilyoffice.com pages returned 403 during research; no person@ address found in accessible pages). RocketReach/ContactOut/Datanyze show only masked/pattern (first@biltmorefamilyoffice.com) broker data — excluded; not pattern-generated.</t>
+          <t>Published on Laura Tarbox's own public presentation slide (title block reads 'Laura Tarbox, CFP(R) 949.721.2330 Laura@Tarbox.com'). Individual address on the firm's own domain; published, not independently provider-verified. Firm bio page itself shows only a phone and contact form. ZoomInfo listing (l***@tarboxgroup.com) is broker-masked and excluded.</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Firm main line (6836 Morrison Blvd Suite 100, Charlotte); firm switchboard, not a personal line. https://www.biltmorefamilyoffice.com/</t>
+          <t>https://tarbox.com/team/laura-tarbox/ (listed on Laura Tarbox's bio page; Newport Beach office line) and her presentation https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>https://www.biltmorefamilyoffice.com/our-history/ ; https://businessnc.com/chris-cecil/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
+          <t>https://tarbox.com/history/ ; https://tarbox.com/who-we-are/ ; https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEC13F-0001039807</t>
+          <t>SEC13F-0002056106</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Boston Family Office LLC</t>
+          <t>Stenger Family Office, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5081,71 +5315,79 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001039807); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0002056106); discovered via fts</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001039807&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002056106&amp;type=13F</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (CRD #107141) serving many clients -- ~789 accounts across high-net-worth individuals, retail investors and charitable organizations; ~$1.7-2.0B AUM; 15 partners. This is a multi-family office / wealth-management RIA, not a single family's office. Source: https://adviserinfo.sec.gov/firm/summary/107141 and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
+          <t>Self-described 'multi-family office'; the Stenger family has served 'over 1,200 families across the United States'. Serves many outside client families. Sources: https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Operates as an RIA branded as a family office ('The Boston Family Office'), founded 1996; files 13F under CIK 0001039807. Source: https://www.bosfam.com/george-beal/</t>
+          <t xml:space="preserve">SEC-registered investment adviser (13F filer); independent fiduciary wealth-management firm offering financial planning, investment management, tax and estate strategies under a family-office model; ~$731M AUM. Sources: https://www.stengerfamilyoffice.com/ </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>corroborated</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/107141 (Form ADV, 2024-2025) and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
+          <t>Firm-stated. https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Beal co-founded the firm in 1996, is a Managing Partner and portfolio manager, and is the named 13F signatory -- an active, current investment decision-maker. Note the firm has 15 partners / ~8 active managing directors, so investment authority is shared. Source: https://www.bosfam.com/george-beal/</t>
+          <t>Founder and CEO / lead financial advisor; prior Senior Vice President financial advisor at Morgan Stanley Wealth Management, and roles at Invesco PowerShares and PwC; the firm's decision-maker and namesake. https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://www.stengerfamilyoffice.com (published mailto/contact page)</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Tried: fetched bosfam.com homepage and bosfam.com/george-beal/ team page -- only phone (617-624-0800) is published, no email. A ZoomInfo listing shows a masked pattern 'g***@bosfam.com' but that is a data-broker inference, NOT a published/attested individual address, so it is excluded. Did not construct an address.</t>
+          <t>No individual email published on the firm site; contact is via a Calendly link (calendly.com/nicholasstenger/intro-meeting) rather than a published email address. No broker emails accepted.</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>https://www.bosfam.com/wp-content/uploads/2024/02/2024-ADV-Part-2B-Brochure-Supplement_FINAL.pdf ; https://adviserinfo.sec.gov/firm/summary/107141</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
+          <t>https://www.stengerfamilyoffice.com/ ; https://www.stengerfamilyoffice.com/financialadvisornaperville ; https://podcasts.apple.com/us/podcast/the-nick-stenger-show/id1678810370</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEC13F-0002017744</t>
+          <t>SEC13F-0001908612</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC</t>
+          <t>Allie Family Office LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5155,22 +5397,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0002017744); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001908612); discovered via fts</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002017744&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001908612&amp;type=13F</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>A registered investment adviser and multi-family office that markets 'Multi Family Office Services' and serves many clients -- high-net-worth individuals, entrepreneurs, families and family offices -- with ~20 staff across multiple US offices. Source: https://arrowrootfamilyoffice.com/team/ and https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
+          <t>Self-described independent multi-family office with offices in Miami and Lima serving multiple Latin American (predominantly Peruvian) HNW families; press reports ~23 client families averaging ~$50M each. Clearly multi-client, not single-family. Sources: https://allie-intl.com/en/home/ ; https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami ; https://fintrx.com/firms/firm/allie-family-office-llc-307144</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SEC-registered RIA (Form ADV on file, SEC# 801-121878) branded 'Arrowroot Family Office'; files 13F under CIK 0002017744; multiple offices and a published team. Source: https://9at.com/Adviser/801-121878</t>
+          <t>SEC-registered investment adviser (CRD 307144, 13F filer) established September 2019; provides discretionary and limited-discretionary investment management, estate planning and cross-border tax coordination as an independent multi-family office. Sources: https://adviserinfo.sec.gov/firm/summary/307144 ; https://reports.adviserinfo.sec.gov/crs/crs_307144.pdf</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5180,12 +5422,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://fintrx.com/firms/firm/arrowroot-family-office-llc-168744 (~$431M, Q2 2025); Form ADV: https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf (2025)</t>
+          <t>Form ADV / adviser aggregators and press. https://fintrx.com/firms/firm/allie-family-office-llc-307144 ; https://aum13f.com/firm/allie-family-office-llc ; https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Santos is CEO and principal owner, leading the firm; he is the 13F signatory (Roberto Santos = Rob Santos) and a current decision-maker with 20+ years' experience. Source: https://arrowrootfamilyoffice.com/team/ and https://www.getwarmer.com/advisors/roberto-francisco-santos</t>
+          <t>Bruno Ghio founded Allié in 2019, owns 100% of the firm and is Founder &amp; CEO — the lead decision-maker — after serving as Managing Director / Regional Head of the Family Office at BCP and a senior private banker at JPMorgan. Jose Larrabure (CFA, CESGA) leads investment management. https://pe.linkedin.com/in/bruno-ghio-1264b616b ; https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -5196,17 +5438,17 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Tried: fetched the firm's team page (no email published, only phone 833-224-2249 and a contact form); searched for a published individual email; only data-broker (RocketReach) listings exist, which are not published/attested. Did not construct an address.</t>
+          <t>Firm publishes only a generic mailbox (info@allie-intl.com); the Team page lists members without individual emails or direct lines. RocketReach/aggregator listings for Bruno Ghio are broker-sourced and excluded per rules.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1908612/000190861226000002/primary_doc.xml</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>https://www.arrowrootfamilyoffice.com/press-releases/arrowroot-family-office-in-michigan/ ; https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
+          <t>https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami ; https://www.leadersleague.com/en/news/allie-family-office-adds-partner-in-peru ; https://www.bloomberg.com/news/articles/2024-03-18/family-office-head-sees-more-peruvian-clients-settling-in-miami</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
@@ -5214,12 +5456,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEC13F-0001950506</t>
+          <t>SEC13F-0001511137</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fortitude Family Office, LLC</t>
+          <t>Pathstone Family Office LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5229,22 +5471,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001950506); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001511137); discovered via fts</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001950506&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001511137&amp;type=13F</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Team page/site confirm it operates as a multi-family office serving 'high and ultra-high net worth families' with coordinated services; ~$1B regulatory AUM. Sources: https://fortitudefo.com/team/ ; https://fortitudefo.com/whoweserve/ ; https://fintrx.com/firms/firm/fortitude-family-office-317615</t>
+          <t>Large partner-owned multi-family office; named 'Best Multi-Family Office ($15B AUM/AUA and above)' at the 2025 Family Wealth Report Awards; serves UHNW families, single family offices, foundations and endowments.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (13F filer); fully-integrated advisory team providing investment/wealth management, tax, accounting, philanthropy and business-operations services to HNW/UHNW families; ~$1B AUM (~$2B assets under advisement claimed). Sources: https://fortitudefo.com/ ; https://www.prnewswire.com/news-releases/fortitude-family-office-founder-and-ceo-matt-walker-named-executive-of-the-year-by-business-intelligence-group-302117711.html</t>
+          <t>SEC-registered investment adviser (CRD 151736) and partner-owned MFO founded 2010; ~775+ employees; comprehensive investment management, tax, insurance, legacy and family-office services.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -5254,12 +5496,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>FINTRX (RAUM) and firm PR (AUA). https://fintrx.com/firms/firm/fortitude-family-office-317615 ; https://www.prnewswire.com/news-releases/fortitude-family-office-wins-2024-wealthmanagementcom-industry-award-for-private-lending-initiative-302253789.html</t>
+          <t>Family Wealth Report / Pathstone communications and Form ADV (03/31/2025) for the ~$125B firm figure; affiliate-inclusive totals per Preqin/press.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Founder and CEO; named InvestmentNews 2024 Excellence Awardee and Business Intelligence Group 'Executive of the Year' 2024; leads the integrated advisory team. https://fortitudefo.com/team/ ; https://www.linkedin.com/in/matt-walkercpa-cgma/</t>
+          <t>CEO and co-founder; sets the firm's strategic vision, on the Board of Managers and Executive Leadership Team; previously President of Pathstone and a Principal at Harris myCFO. Primary top decision-maker.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -5270,17 +5512,17 @@
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>No individual email published on the firm site; contact page shows only a Cloudflare-obfuscated generic mailbox and phone (602) 834-0089. No broker emails accepted.</t>
+          <t>No individual email is published on Fleissig's Pathstone bio page or elsewhere on pathstone.com; no qualifying published address found.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://fortitudefo.com/contact/ (firm main line, 7500 N Dobson Rd Suite 151, Scottsdale; not a personal line)</t>
+          <t>Englewood office line (201) 944-7284 appears on the firm's Form ADV cover (not a personal line).</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/fortitude-family-office-founder-and-ceo-matt-walker-named-executive-of-the-year-by-business-intelligence-group-302117711.html ; https://www.prnewswire.com/news-releases/matt-walker-fortitude-family-office-founder-and-ceo-honored-as-investmentnews-excellence-awardee-302175687.html ; https://www.prnewswire.com/news-releases/fortitude-family-office-wins-2024-wealthmanagementcom-industry-award-for-private-lending-initiative-302253789.html</t>
+          <t>https://pathstone.com/people/matthew-fleissig/ ; https://www.familywealthreport.com/article.php/Now-A-$100-Billion-MFO,-What%E2%80%99s-Next-For-Pathstone%3F-?id=202670</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
@@ -5288,12 +5530,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEC13F-0001802278</t>
+          <t>SEC13F-0001731123</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Stokes Family Office, LLC</t>
+          <t>Biltmore Family Office, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5303,22 +5545,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001802278); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001731123); discovered via fts</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001802278&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001731123&amp;type=13F</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Firm is '100% Family Owned' (owned by the Stokes family) but serves outside clients: 'individuals, families and institutions' with a billion-dollar advisory practice. Broad multi-client RIA, not a single-family vehicle. Sources: https://stokesfamilyoffice.com/about-us/ ; https://fintrx.com/firms/firm/stokes-family-office-llc-300899</t>
+          <t>Independent SEC-registered adviser to investment-oriented multi-generational families plus institutional clients; ~951 accounts and ~$3.2-3.5B AUM (avg client ~$38M). A collaborative multi-family office, not a single-family vehicle. Sources: https://www.biltmorefamilyoffice.com/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (13F filer) branded 'family office'; offers wealth management, retirement plan consulting and family-office services; ~$3.35B AUM. Sources: https://stokesfamilyoffice.com/about-us/ ; https://stokesfamilyoffice.com/insights/stokes-family-office-exceeds3b-aum/</t>
+          <t>SEC-registered investment adviser (13F filer) founded 2008 (LLC organized 2013); positions itself as a hybrid family office and RIA. Sources: https://www.biltmorefamilyoffice.com/our-history/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5328,12 +5570,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Firm press/AUM aggregators. https://stokesfamilyoffice.com/insights/stokes-family-office-exceeds3b-aum/ ; https://fintrx.com/firms/firm/stokes-family-office-llc-300899 ; https://aum13f.com/firm/stokes-family-office-llc</t>
+          <t>AUM/ADV aggregators. https://fintrx.com/firms/firm/biltmore-family-office-llc-167174 ; https://advisor.guide/firms/biltmore-family-office ; https://whalewisdom.com/filer/biltmore-family-office-llc</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Doug Stokes, CFA, is co-owner and Managing Partner who 'takes an active role in the firm's investment research process and investment committee decisions' — the investment decision-maker (co-managing partner Gregory Stokes, JD, runs business/innovation; founder David Stokes is Founder Emeritus). https://stokesfamilyoffice.com/about-us/ ; https://www.linkedin.com/in/doug-stokes-03716932/</t>
+          <t>Founder and President/CEO; 30 years' experience in investment management, asset allocation and investment-policy creation; prior Partner at GenSpring Family Offices, President at JPMorgan Private Bank, Managing Director at Brown Brothers Harriman. The firm's top decision-maker (Rael Gorelick is Partner &amp; Head of Investments / CIO-equivalent). https://www.biltmorefamilyoffice.com/who-we-are/chris-cecil/ ; https://www.linkedin.com/in/chris-cecil-9701b818/</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5344,17 +5586,17 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Only a generic mailbox published (info@stokesfamilyoffice.com on https://stokesfamilyoffice.com/contact-us/); no individual email on any firm bio/contact page. ZoomInfo/RocketReach/ContactOut listings (e.g., doug@... , dougstokes4@gmail.com) are broker-sourced/masked and excluded per rules.</t>
+          <t>No individual email published on the firm site (biltmorefamilyoffice.com pages returned 403 during research; no person@ address found in accessible pages). RocketReach/ContactOut/Datanyze show only masked/pattern (first@biltmorefamilyoffice.com) broker data — excluded; not pattern-generated.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://stokesfamilyoffice.com/contact-us/ (New Orleans office switchboard, 1100 Poydras St Suite 2775; not a personal line)</t>
+          <t>Firm main line (6836 Morrison Blvd Suite 100, Charlotte); firm switchboard, not a personal line. https://www.biltmorefamilyoffice.com/</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>https://www.prnewswire.com/news-releases/stokes-family-office-named-to-top-ria-list-by-forbesshook-research-301958395.html ; https://stokesfamilyoffice.com/contact-us/ ; https://stokesfamilyoffice.com/insights/stokes-family-office-exceeds3b-aum/</t>
+          <t>https://www.biltmorefamilyoffice.com/our-history/ ; https://businessnc.com/chris-cecil/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -5362,12 +5604,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEC13F-0002105684</t>
+          <t>SEC13F-0001039807</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cambient Family Office, LLC</t>
+          <t>Boston Family Office LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5377,22 +5619,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0002105684); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001039807); discovered via fts</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002105684&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001039807&amp;type=13F</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Self-described 'independent multi-family office serving affluent families, private foundations, and entrepreneurs'; Form ADV shows ~260 accounts and 172+ clients across categories. Sources: https://www.cambient.com/about-us ; Form ADV Part 1 (Item 5) https://reports.adviserinfo.sec.gov/reports/ADV/335128/PDF/335128.pdf</t>
+          <t>SEC-registered investment adviser (CRD #107141) serving many clients -- ~789 accounts across high-net-worth individuals, retail investors and charitable organizations; ~$1.7-2.0B AUM; 15 partners. This is a multi-family office / wealth-management RIA, not a single family's office. Source: https://adviserinfo.sec.gov/firm/summary/107141 and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (SEC file 801-132283, CRD 335128, 13F filer), registration effective 2025-04-02; ~$857.9M regulatory AUM, discretionary equity-oriented management. Sources: https://adviserinfo.sec.gov/firm/summary/335128 ; Form ADV https://reports.adviserinfo.sec.gov/reports/ADV/335128/PDF/335128.pdf</t>
+          <t>Operates as an RIA branded as a family office ('The Boston Family Office'), founded 1996; files 13F under CIK 0001039807. Source: https://www.bosfam.com/george-beal/</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5402,12 +5644,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Form ADV Part 1 Item 5.F (filed 2026-07-16). https://reports.adviserinfo.sec.gov/reports/ADV/335128/PDF/335128.pdf ; corroborated https://fintrx.com/firms/firm/cambient-family-office-llc-335128</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/107141 (Form ADV, 2024-2025) and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Listed as a direct owner/executive on Form ADV Schedule A and 'oversees investment strategy and portfolio construction' as a CFA charterholder — a lead investment decision-maker. Co-owner Daniel Rausch (CIMA) is a co-PM; co-owner Joshua Gibbs is Trust Advisor &amp; CCO and signed/filed the 13F. https://www.cambient.com/our-team ; Form ADV Schedule A https://reports.adviserinfo.sec.gov/reports/ADV/335128/PDF/335128.pdf ; https://www.linkedin.com/in/andrew-fabiano-2b4869ab</t>
+          <t>Beal co-founded the firm in 1996, is a Managing Partner and portfolio manager, and is the named 13F signatory -- an active, current investment decision-maker. Note the firm has 15 partners / ~8 active managing directors, so investment authority is shared. Source: https://www.bosfam.com/george-beal/</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5418,17 +5660,17 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Only generic mailbox published (info@cambient.com on cambient.com). No individual email on the firm site or in filings. Datanyze/ZoomInfo listings are broker-sourced and excluded.</t>
+          <t>Tried: fetched bosfam.com homepage and bosfam.com/george-beal/ team page -- only phone (617-624-0800) is published, no email. A ZoomInfo listing shows a masked pattern 'g***@bosfam.com' but that is a data-broker inference, NOT a published/attested individual address, so it is excluded. Did not construct an address.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Form ADV / 13F cover page (firm main line, Ada MI) https://reports.adviserinfo.sec.gov/reports/ADV/335128/PDF/335128.pdf</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>https://api.adviserinfo.sec.gov/search/firm/335128 ; https://reports.adviserinfo.sec.gov/reports/ADV/335128/PDF/335128.pdf ; https://reports.adviserinfo.sec.gov/reports/individual/individual_8098624.pdf</t>
+          <t>https://www.bosfam.com/wp-content/uploads/2024/02/2024-ADV-Part-2B-Brochure-Supplement_FINAL.pdf ; https://adviserinfo.sec.gov/firm/summary/107141</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -5436,37 +5678,37 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UKCH-09580739</t>
+          <t>SEC13F-0002017744</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Blu Family Office Limited</t>
+          <t>Arrowroot Family Office, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Companies House 09580739 (Private limited company); inc. 8 May 2015</t>
+          <t>EDGAR 13F filer (CIK 0002017744); discovered via fts</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/09580739</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002017744&amp;type=13F</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Founded 2010 by Christian Armbruester (ex-Credit Suisse) to manage his own family's wealth, then expanded to serve multiple families; repeatedly described as a multi-family office in press (Citywire, Private Banker International). FCA-regulated discretionary manager.</t>
+          <t>A registered investment adviser and multi-family office that markets 'Multi Family Office Services' and serves many clients -- high-net-worth individuals, entrepreneurs, families and family offices -- with ~20 staff across multiple US offices. Source: https://arrowrootfamilyoffice.com/team/ and https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Live FCA-regulated firm; active website; investment arm 'Blu Investment Management' (blu-im.com); corporate LinkedIn; named press profiles; defined team.</t>
+          <t>SEC-registered RIA (Form ADV on file, SEC# 801-121878) branded 'Arrowroot Family Office'; files 13F under CIK 0002017744; multiple offices and a published team. Source: https://9at.com/Adviser/801-121878</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,12 +5718,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Third-party estimate via industry data/press (Citywire wealth-manager profile); not officially disclosed.</t>
+          <t>https://fintrx.com/firms/firm/arrowroot-family-office-llc-168744 (~$431M, Q2 2025); Form ADV: https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf (2025)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Founder and principal investment decision-maker; single largest shareholder; individual, not nominee. Current day-to-day CEO is Marie Redron.</t>
+          <t>Santos is CEO and principal owner, leading the firm; he is the 13F signatory (Roberto Santos = Rob Santos) and a current decision-maker with 20+ years' experience. Source: https://arrowrootfamilyoffice.com/team/ and https://www.getwarmer.com/advisors/roberto-francisco-santos</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -5492,13 +5734,17 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Firm site publishes only a generic mailbox (info@blu-im.com). No individual/principal email published anywhere located. Nothing pattern-generated.</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>Tried: fetched the firm's team page (no email published, only phone 833-224-2249 and a contact form); searched for a published individual email; only data-broker (RocketReach) listings exist, which are not published/attested. Did not construct an address.</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/09580739/officers; https://citywire.com/wealth-manager/news/richmond-based-multi-family-boutique-names-new-ceo/a1109198</t>
+          <t>https://www.arrowrootfamilyoffice.com/press-releases/arrowroot-family-office-in-michigan/ ; https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -5506,69 +5752,73 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UKCH-12233405</t>
+          <t>SEC13F-0001756485</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Schwarz Family Office Ltd</t>
+          <t>Independent Family Office, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Companies House 12233405 (Private limited company); inc. 30 September 2019</t>
+          <t>EDGAR 13F filer (CIK 0001756485); discovered via fts</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/12233405</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001756485&amp;type=13F</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Website describes a 'boutique consultancy' providing debt financing, capital raising, IR and fund management for clients, with multiple partners — more advisory/MFO-style than a pure single-family office despite the name. Two shareholders. https://schwarzfamilyoffice.com/</t>
+          <t>Bespoke family office serving multiple 'select' high-net-worth client families across the country (~34 client relationships, ~$617.8M discretionary AUM); listed by Altss as a Multi Family Office. Multi-client, not single-family. Sources: https://ifollc.com/ ; https://altss.com/profile/independent-family-office-llc ; https://money.usnews.com/financial-advisors/firm/independent-family-office-llc-144811</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Active company, SIC 64304 + consultancy codes; own website; listed in Family Capital's 'FamCap 50'. https://schwarzfamilyoffice.com/ ; https://find-and-update.company-information.service.gov.uk/company/12233405</t>
+          <t>SEC-registered investment adviser (CRD 144811, 13F filer), SEC-registered since 2012 (founded 2005); acts as a capital allocator providing investment oversight, estate-planning support, tax and day-to-day financial administration for HNW families. Sources: https://adviserinfo.sec.gov/individual/summary/6993180 ; https://ifollc.com/blank-5/</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>corroborated</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Form ADV / adviser aggregators. https://money.usnews.com/financial-advisors/firm/independent-family-office-llc-144811 ; https://fintrx.com/firms/firm/independent-family-office-llc-144811 ; https://aum13f.com/firm/independent-family-office-llc</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Sole director since incorporation (2019) and majority shareholder (510/1000); ex Merrill Lynch and Bank of Singapore. https://find-and-update.company-information.service.gov.uk/company/12233405/officers ; https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
+          <t>William Michael Reickert established IFO in 2005 after leading The Ayco Company's family-office practice; he is Managing Member/CEO and the firm's lead investment and advisory decision-maker, described as a trusted advisor to Fortune 100 CEOs, fund managers and senior officials. https://ifollc.com/blank-5/ ; https://www.advisorcheck.com/advisor/1673416-william-michael-reickert-independent-family-office-llc-albany-new-york</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Only a generic mailbox (admin@schwarzfamilyoffice.com) is published (excluded). RocketReach result is a masked/broker source and excluded.</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>The only address published on the site (home + Reickert's bio page) is 'dr@ifollc.com'; the 'dr' initials do not match 'W. Michael Reickert', so it appears to be a shared/assistant or general mailbox rather than the principal's personal individual email — excluded as not clearly an individual address per rules. No other individual email found.</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>https://ifollc.com/blank-5/ and https://ifollc.com/ (main office line, 677 Broadway 7th Floor, Albany; not a personal line)</t>
+        </is>
+      </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>https://www.famcap.com/2024/02/the-famcap-50-the-worlds-top-family-capital-investment-specialists/</t>
+          <t>https://ifollc.com/blank-5/ ; https://altss.com/profile/independent-family-office-llc ; https://money.usnews.com/financial-advisors/firm/independent-family-office-llc-144811</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -5576,12 +5826,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UKCH-14344019</t>
+          <t>UKCH-09580739</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hazell Family Office Ltd</t>
+          <t>Blu Family Office Limited</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5591,50 +5841,54 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Companies House 14344019 (Private limited company); inc. 8 September 2022</t>
+          <t>Companies House 09580739 (Private limited company); inc. 8 May 2015</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14344019</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/09580739</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>All five directors share surname Hazell and one family address (Cefn Henllan Farm, Llanhennock, Usk); appointed same day 2022-09-08; DOB spread (1959-1994) indicates two parents + three adult children — a single-family board. SIC 70221 (financial management).</t>
+          <t>Founded 2010 by Christian Armbruester (ex-Credit Suisse) to manage his own family's wealth, then expanded to serve multiple families; repeatedly described as a multi-family office in press (Citywire, Private Banker International). FCA-regulated discretionary manager.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Family-only board, no external/nominee officers. Patriarch Mark Hazell is MD of the family's operating businesses (haulage / environmental services), a plausible wealth source. https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
+          <t>Live FCA-regulated firm; active website; investment arm 'Blu Investment Management' (blu-im.com); corporate LinkedIn; named press profiles; defined team.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Third-party estimate via industry data/press (Citywire wealth-manager profile); not officially disclosed.</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Patriarch (b.1959), MD of the family operating companies; most probable investment decision-maker; individual, not nominee.</t>
+          <t>Founder and principal investment decision-maker; single largest shareholder; individual, not nominee. Current day-to-day CEO is Marie Redron.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>No firm website; searches returned only company/director aggregators; no published individual email. Nothing pattern-generated.</t>
+          <t>Firm site publishes only a generic mailbox (info@blu-im.com). No individual/principal email published anywhere located. Nothing pattern-generated.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/09580739/officers; https://citywire.com/wealth-manager/news/richmond-based-multi-family-boutique-names-new-ceo/a1109198</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -5642,12 +5896,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UKCH-14442767</t>
+          <t>UKCH-12233405</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Wedgwood Family Office Limited</t>
+          <t>Schwarz Family Office Ltd</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5657,22 +5911,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Companies House 14442767 (Private limited company); inc. 25 October 2022</t>
+          <t>Companies House 12233405 (Private limited company); inc. 30 September 2019</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14442767</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/12233405</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>SIC 66300 (fund management), sole active director Paul Wedgwood at a single residential address; no external clients/multi-family structure. Principal separately holds 'Wedgwood FIC Limited' (a Family Investment Company), consistent with a single-family vehicle.</t>
+          <t>Website describes a 'boutique consultancy' providing debt financing, capital raising, IR and fund management for clients, with multiple partners — more advisory/MFO-style than a pure single-family office despite the name. Two shareholders. https://schwarzfamilyoffice.com/</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Active company (inc. 2022-10-25), SIC 66300, residential registered address. Director Paul Wedgwood (b. Jun 1970) very likely the video-game entrepreneur who sold Splash Damage (up to $150m, 2016) and co-founded Supernova Capital — a plausible wealth source. https://en.wikipedia.org/wiki/Paul_Wedgwood</t>
+          <t>Active company, SIC 64304 + consultancy codes; own website; listed in Family Capital's 'FamCap 50'. https://schwarzfamilyoffice.com/ ; https://find-and-update.company-information.service.gov.uk/company/12233405</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -5680,27 +5934,31 @@
           <t>corroborated</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sole active decision-making director since incorporation. Almost certainly the Splash Damage / Supernova Capital entrepreneur (DOB match; also director of Wedgwood FIC Limited).</t>
+          <t>Sole director since incorporation (2019) and majority shareholder (510/1000); ex Merrill Lynch and Bank of Singapore. https://find-and-update.company-information.service.gov.uk/company/12233405/officers ; https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>No firm website/press page; no individual email published. A uk.linkedin.com/in/paulwedgwood profile is labelled 'The Carbon Trust' and cannot be confirmed as the same person; nothing inferred.</t>
+          <t>Only a generic mailbox (admin@schwarzfamilyoffice.com) is published (excluded). RocketReach result is a masked/broker source and excluded.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14442767/officers</t>
+          <t>https://www.famcap.com/2024/02/the-famcap-50-the-worlds-top-family-capital-investment-specialists/</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -5708,52 +5966,48 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SFO-dfo-management-dell</t>
+          <t>UKCH-14344019</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DFO Management, LLC</t>
+          <t>Hazell Family Office Ltd</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>uk-companies-house</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (Michael Dell) -&gt; family office entity. Confirmed as Dell's single-family office by the firm's own site (dellfamilyoffice.com) and confirmed as an SEC 13F filer via EDGAR full-text search (13F-HR filed under Michael &amp; Susan Dell Foundation, managed by DFO Management, CIK 0001599858).</t>
+          <t>Companies House 14344019 (Private limited company); inc. 8 September 2022</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.dellfamilyoffice.com/about</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14344019</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Firm site states DFO is 'the private investment firm for Dell Technologies Founder &amp; CEO Michael Dell and his family'; launched 1998 as MSD Capital, restructured to DFO Management at end of 2022. Single-family (Dell) only.</t>
+          <t>All five directors share surname Hazell and one family address (Cefn Henllan Farm, Llanhennock, Usk); appointed same day 2022-09-08; DOB spread (1959-1994) indicates two parents + three adult children — a single-family board. SIC 70221 (financial management).</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SEC EDGAR 13F-HR filings (CIK 0001599858, period ending 2026-03-31, filed 2026-05-15) plus dedicated family-office website.</t>
+          <t>Family-only board, no external/nominee officers. Patriarch Mark Hazell is MD of the family's operating businesses (haulage / environmental services), a plausible wealth source. https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed; widely reported as tens of billions tied to Michael Dell's fortune.</t>
-        </is>
-      </c>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Beneficial owner and namesake; the family office exists to manage his and his family's capital.</t>
+          <t>Patriarch (b.1959), MD of the family operating companies; most probable investment decision-maker; individual, not nominee.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -5762,11 +6016,15 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No firm website; searches returned only company/director aggregators; no published individual email. Nothing pattern-generated.</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>https://efts.sec.gov/LATEST/search-index?q=%22DFO+Management%22&amp;forms=13F-HR</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -5774,52 +6032,48 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SFO-bayshore-global-brin</t>
+          <t>UKCH-14442767</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bayshore Global Management, LLC</t>
+          <t>Wedgwood Family Office Limited</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>uk-companies-house</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (Sergey Brin) -&gt; family office entity. Confirmed as Brin's single-family office by Bloomberg reporting (2026-04-23, 'Sergey Brin's Family Office Absorbs Nexus NeuroTech Brain-Health VC Fund') and Wikipedia.</t>
+          <t>Companies House 14442767 (Private limited company); inc. 25 October 2022</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-04-23/sergey-brin-s-family-office-takes-over-brain-focused-vc-fund</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14442767</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Described consistently as the single-family office of Google co-founder Sergey Brin; founded 2005; allocates across public/private markets, real estate and philanthropic vehicles.</t>
+          <t>SIC 66300 (fund management), sole active director Paul Wedgwood at a single residential address; no external clients/multi-family structure. Principal separately holds 'Wedgwood FIC Limited' (a Family Investment Company), consistent with a single-family vehicle.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Bloomberg news coverage naming it Sergey Brin's family office; Wikipedia entry; multiple family-office databases.</t>
+          <t>Active company (inc. 2022-10-25), SIC 66300, residential registered address. Director Paul Wedgwood (b. Jun 1970) very likely the video-game entrepreneur who sold Splash Damage (up to $150m, 2016) and co-founded Supernova Capital — a plausible wealth source. https://en.wikipedia.org/wiki/Paul_Wedgwood</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Press reports estimate over $100bn tied to Brin's Alphabet stake; not independently disclosed.</t>
-        </is>
-      </c>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Beneficial owner; office manages his assets. Day-to-day led by CEO George Pavlov and CIO Marie Young per press.</t>
+          <t>Sole active decision-making director since incorporation. Almost certainly the Splash Damage / Supernova Capital entrepreneur (DOB match; also director of Wedgwood FIC Limited).</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -5828,11 +6082,15 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No firm website/press page; no individual email published. A uk.linkedin.com/in/paulwedgwood profile is labelled 'The Carbon Trust' and cannot be confirmed as the same person; nothing inferred.</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-04-23/sergey-brin-s-family-office-takes-over-brain-focused-vc-fund</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14442767/officers</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -5840,12 +6098,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SFO-hillspire-schmidt</t>
+          <t>SFO-dfo-management-dell</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hillspire, LLC</t>
+          <t>DFO Management, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5855,22 +6113,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (Eric Schmidt) -&gt; family office entity. Confirmed as Schmidt's single-family office by CNBC reporting (CNBC 'Inside Wealth Family Office 15', 2026-02-12, and 2025-01-21 piece on 22 AI startup investments).</t>
+          <t>Identified via known UHNW individual (Michael Dell) -&gt; family office entity. Confirmed as Dell's single-family office by the firm's own site (dellfamilyoffice.com) and confirmed as an SEC 13F filer via EDGAR full-text search (13F-HR filed under Michael &amp; Susan Dell Foundation, managed by DFO Management, CIK 0001599858).</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/2025/01/21/eric-schmidts-family-office-invests-ai-startups.html</t>
+          <t>https://www.dellfamilyoffice.com/about</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Described by CNBC and family-office databases as the single-family office established by former Google CEO Eric Schmidt and his wife Wendy Schmidt (founded 2006).</t>
+          <t>Firm site states DFO is 'the private investment firm for Dell Technologies Founder &amp; CEO Michael Dell and his family'; launched 1998 as MSD Capital, restructured to DFO Management at end of 2022. Single-family (Dell) only.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CNBC news coverage naming Hillspire as Eric Schmidt's family office and ranking it the most active U.S. family office for 2025 dealmaking.</t>
+          <t>SEC EDGAR 13F-HR filings (CIK 0001599858, period ending 2026-03-31, filed 2026-05-15) plus dedicated family-office website.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -5880,12 +6138,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Not disclosed.</t>
+          <t>Not publicly disclosed; widely reported as tens of billions tied to Michael Dell's fortune.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Beneficial owner and namesake; office run day-to-day by President Ken Goldman per press.</t>
+          <t>Beneficial owner and namesake; the family office exists to manage his and his family's capital.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -5898,7 +6156,7 @@
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/2026/02/12/inside-wealth-family-office-15.html</t>
+          <t>https://efts.sec.gov/LATEST/search-index?q=%22DFO+Management%22&amp;forms=13F-HR</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -5906,12 +6164,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SFO-blue-pool-capital-tsai</t>
+          <t>SFO-bayshore-global-brin</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Blue Pool Capital Limited (13F filer: Blue Pool Management Ltd.)</t>
+          <t>Bayshore Global Management, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5921,22 +6179,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (Joseph Tsai, Alibaba co-founder) and via SEC 13F filer with a neutral name. Confirmed as an SEC 13F filer (Blue Pool Management Ltd., CIK 0001675855, HQ Causeway Bay Hong Kong) and confirmed as Tsai's family office by Crain Currency / Caproasia reporting.</t>
+          <t>Identified via known UHNW individual (Sergey Brin) -&gt; family office entity. Confirmed as Brin's single-family office by Bloomberg reporting (2026-04-23, 'Sergey Brin's Family Office Absorbs Nexus NeuroTech Brain-Health VC Fund') and Wikipedia.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.caproasia.com/2024/09/19/alibaba-co-founder-billionaire-joseph-tsai-joins-investor-consortium-to-buy-vineyards-in-france-burgundy-another-investor-in-group-is-oliver-weisberg-who-is-ceo-of-joseph-tsai-family-office-blue-po/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-04-23/sergey-brin-s-family-office-takes-over-brain-focused-vc-fund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Repeatedly described as the family office of Alibaba co-founder Joe Tsai; oversees the Tsai family's investments and operating assets (incl. Brooklyn Nets, LAFC).</t>
+          <t>Described consistently as the single-family office of Google co-founder Sergey Brin; founded 2005; allocates across public/private markets, real estate and philanthropic vehicles.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SEC EDGAR 13F-HR filings (Blue Pool Management Ltd., CIK 0001675855; latest 2026-05-15, HQ 25/F Hysan Place, 500 Hennessy Road, Causeway Bay) plus Crain Currency/Caproasia press naming it Joe Tsai's family office.</t>
+          <t>Bloomberg news coverage naming it Sergey Brin's family office; Wikipedia entry; multiple family-office databases.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -5946,12 +6204,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Press estimate (Caproasia/Crain Currency, 2022-2026); not an official disclosure.</t>
+          <t>Press reports estimate over $100bn tied to Brin's Alphabet stake; not independently disclosed.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Beneficial owner; founded the office in 2004/2015. Day-to-day CEO is Oliver Weisberg.</t>
+          <t>Beneficial owner; office manages his assets. Day-to-day led by CEO George Pavlov and CIO Marie Young per press.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -5964,7 +6222,7 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001675855.json</t>
+          <t>https://www.bloomberg.com/news/articles/2026-04-23/sergey-brin-s-family-office-takes-over-brain-focused-vc-fund</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -5972,12 +6230,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SFO-mousse-partners-wertheimer</t>
+          <t>SFO-hillspire-schmidt</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mousse Partners Limited (part of Mousse Investments Limited)</t>
+          <t>Hillspire, LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5987,22 +6245,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Identified via known UHNW family (Wertheimer, owners of Chanel) -&gt; family office entity. Confirmed as the Wertheimer family office by Bloomberg ('Family office for $90 billion fortune reshapes consumer bets') and Wikipedia.</t>
+          <t>Identified via known UHNW individual (Eric Schmidt) -&gt; family office entity. Confirmed as Schmidt's single-family office by CNBC reporting (CNBC 'Inside Wealth Family Office 15', 2026-02-12, and 2025-01-21 piece on 22 AI startup investments).</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/professional/insights/trading/family-office-for-90-billion-fortune-reshapes-consumer-bets/</t>
+          <t>https://www.cnbc.com/2025/01/21/eric-schmidts-family-office-invests-ai-startups.html</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Described as the family office managing the wealth of Alain and Gerard Wertheimer, owners of Chanel; founded 1991 by Charles Heilbronn (Chanel executive and half-brother of the Wertheimers).</t>
+          <t>Described by CNBC and family-office databases as the single-family office established by former Google CEO Eric Schmidt and his wife Wendy Schmidt (founded 2006).</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bloomberg feature and Wikipedia identify Mousse Partners as the Wertheimer family office; firm site describes it as the investment division of Mousse Investments Limited.</t>
+          <t>CNBC news coverage naming Hillspire as Eric Schmidt's family office and ranking it the most active U.S. family office for 2025 dealmaking.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -6012,12 +6270,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Press associates the family fortune at ~$90-100bn; this is the Wertheimer net worth, not a disclosed AUM figure for Mousse.</t>
+          <t>Not disclosed.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Founder and head of the office; Chanel executive and half-brother of owners Alain and Gerard Wertheimer.</t>
+          <t>Beneficial owner and namesake; office run day-to-day by President Ken Goldman per press.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -6030,7 +6288,7 @@
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/professional/insights/trading/family-office-for-90-billion-fortune-reshapes-consumer-bets/</t>
+          <t>https://www.cnbc.com/2026/02/12/inside-wealth-family-office-15.html</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -6038,12 +6296,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SFO-kirkbi-kristiansen</t>
+          <t>SFO-blue-pool-capital-tsai</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>KIRKBI A/S</t>
+          <t>Blue Pool Capital Limited (13F filer: Blue Pool Management Ltd.)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -6053,22 +6311,22 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Identified via known UHNW family (Kirk Kristiansen, owners of LEGO) -&gt; holding/family office. Confirmed as the Kristiansen single-family office by KIRKBI's own website and Wikipedia; a registered Danish company (A/S).</t>
+          <t>Identified via known UHNW individual (Joseph Tsai, Alibaba co-founder) and via SEC 13F filer with a neutral name. Confirmed as an SEC 13F filer (Blue Pool Management Ltd., CIK 0001675855, HQ Causeway Bay Hong Kong) and confirmed as Tsai's family office by Crain Currency / Caproasia reporting.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.kirkbi.com/about-us/family-ownership/</t>
+          <t>https://www.caproasia.com/2024/09/19/alibaba-co-founder-billionaire-joseph-tsai-joins-investor-consortium-to-buy-vineyards-in-france-burgundy-another-investor-in-group-is-oliver-weisberg-who-is-ceo-of-joseph-tsai-family-office-blue-po/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Established 1 April 1995 as the family office/holding for the Kirk Kristiansen family (owners of the LEGO Group); owns 75% of the LEGO Group and 47.5% of Merlin Entertainments. Single-family.</t>
+          <t>Repeatedly described as the family office of Alibaba co-founder Joe Tsai; oversees the Tsai family's investments and operating assets (incl. Brooklyn Nets, LAFC).</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>KIRKBI's own site (family-ownership page), Wikipedia, and Danish corporate registration as KIRKBI A/S.</t>
+          <t>SEC EDGAR 13F-HR filings (Blue Pool Management Ltd., CIK 0001675855; latest 2026-05-15, HQ 25/F Hysan Place, 500 Hennessy Road, Causeway Bay) plus Crain Currency/Caproasia press naming it Joe Tsai's family office.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -6078,12 +6336,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Press figure for the family's wealth controlled by KIRKBI; total company equity/portfolio larger and not fully disclosed here.</t>
+          <t>Press estimate (Caproasia/Crain Currency, 2022-2026); not an official disclosure.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>CEO and top investment decision-maker of KIRKBI; family chair is Thomas Kirk Kristiansen (assumed board chair May 2023); CIO is Thomas Lau Schleicher.</t>
+          <t>Beneficial owner; founded the office in 2004/2015. Day-to-day CEO is Oliver Weisberg.</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -6096,7 +6354,7 @@
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>https://www.kirkbi.com/press-releases/2025/kirkbi-climate-invests-in-highview/</t>
+          <t>https://data.sec.gov/submissions/CIK0001675855.json</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -6104,12 +6362,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SFO-tethys-invest-bettencourt</t>
+          <t>SFO-mousse-partners-wertheimer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tethys Invest SAS (Tethys SAS group)</t>
+          <t>Mousse Partners Limited (part of Mousse Investments Limited)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -6119,22 +6377,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Identified via known UHNW family (Bettencourt Meyers, largest shareholder of L'Oreal) -&gt; family office. Confirmed as the Bettencourt Meyers single-family office by The National and Caproasia reporting and the firm's own site (tethys.fr).</t>
+          <t>Identified via known UHNW family (Wertheimer, owners of Chanel) -&gt; family office entity. Confirmed as the Wertheimer family office by Bloomberg ('Family office for $90 billion fortune reshapes consumer bets') and Wikipedia.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.thenationalnews.com/business/money/2023/03/13/billionaires-loreal-heir-names-new-head-of-family-office/</t>
+          <t>https://www.bloomberg.com/professional/insights/trading/family-office-for-90-billion-fortune-reshapes-consumer-bets/</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Described as the single-family office managing the assets of the Bettencourt Meyers family, majority shareholder of L'Oreal; Tethys Invest is the entrepreneurial-investment subsidiary.</t>
+          <t>Described as the family office managing the wealth of Alain and Gerard Wertheimer, owners of Chanel; founded 1991 by Charles Heilbronn (Chanel executive and half-brother of the Wertheimers).</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>The National and Caproasia press naming Tethys as the Bettencourt family office; firm's own website.</t>
+          <t>Bloomberg feature and Wikipedia identify Mousse Partners as the Wertheimer family office; firm site describes it as the investment division of Mousse Investments Limited.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -6144,12 +6402,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Press figure for total family assets (dominated by the L'Oreal stake); Tethys Invest deploys &gt;EUR 3bn of direct-investment capital.</t>
+          <t>Press associates the family fortune at ~$90-100bn; this is the Wertheimer net worth, not a disclosed AUM figure for Mousse.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Head of the family's investment firm (Tethys Invest) and, per 2025 press, appointed to the L'Oreal board seat area of the family; family chair of Tethys is Francoise Bettencourt Meyers, CEO of Tethys is Jean-Pierre Meyers.</t>
+          <t>Founder and head of the office; Chanel executive and half-brother of owners Alain and Gerard Wertheimer.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -6162,7 +6420,7 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>https://www.caproasia.com/2025/02/08/loreal-heiress-france-billionaire-francoise-bettencourt-meyers-age-71-with-76-billion-fortune-starts-family-succession-with-retirement-from-loreal-board-as-vice-chairman-son-jean-victo/</t>
+          <t>https://www.bloomberg.com/professional/insights/trading/family-office-for-90-billion-fortune-reshapes-consumer-bets/</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -6170,12 +6428,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SFO-cofra-holding-brenninkmeijer</t>
+          <t>SFO-kirkbi-kristiansen</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>COFRA Holding AG</t>
+          <t>KIRKBI A/S</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -6185,37 +6443,37 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Identified via known UHNW family (Brenninkmeijer, owners of C&amp;A) -&gt; family holding/office. Confirmed by Crain Currency and the firm's own site as the Brenninkmeijer family's Zug-based holding; leadership verified on cofraholding.com.</t>
+          <t>Identified via known UHNW family (Kirk Kristiansen, owners of LEGO) -&gt; holding/family office. Confirmed as the Kristiansen single-family office by KIRKBI's own website and Wikipedia; a registered Danish company (A/S).</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.craincurrency.com/family-office-management/secretive-brenninkmeijer-family-behind-ca-opens-39-billion-retail-empire</t>
+          <t>https://www.kirkbi.com/about-us/family-ownership/</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Established 2001 in Zug to coordinate the Brenninkmeijer family's global businesses and investments; a single-family-owned holding with subsidiaries C&amp;A (retail), Redevco (real estate), Bregal (PE) and Anthos (asset management).</t>
+          <t>Established 1 April 1995 as the family office/holding for the Kirk Kristiansen family (owners of the LEGO Group); owns 75% of the LEGO Group and 47.5% of Merlin Entertainments. Single-family.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Crain Currency reporting on the family's ~$39bn empire; COFRA's own leadership/governance page listing the family-dominated board.</t>
+          <t>KIRKBI's own site (family-ownership page), Wikipedia, and Danish corporate registration as KIRKBI A/S.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>corroborated</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Reported total group asset base (Crain Currency and familyofficehub).</t>
+          <t>Press figure for the family's wealth controlled by KIRKBI; total company equity/portfolio larger and not fully disclosed here.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Family-member chairman since 2018 (former CEO of COFRA, C&amp;A Europe and Anthos); group CEO is Boudewijn Beerkens, CFO Florian Brenninkmeyer (from 2025).</t>
+          <t>CEO and top investment decision-maker of KIRKBI; family chair is Thomas Kirk Kristiansen (assumed board chair May 2023); CIO is Thomas Lau Schleicher.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -6228,7 +6486,7 @@
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>https://www.cofraholding.com/en/newsroom/latest-news/2025/redevco-closes-landmark-475m-loan-investment-for-new-real-estate-debt-platform/</t>
+          <t>https://www.kirkbi.com/press-releases/2025/kirkbi-climate-invests-in-highview/</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -6236,12 +6494,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SFO-athos-strungmann</t>
+          <t>SFO-tethys-invest-bettencourt</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Athos Service GmbH (family investment entity Athos KG)</t>
+          <t>Tethys Invest SAS (Tethys SAS group)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6251,22 +6509,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Identified via known UHNW family (Strungmann brothers, BioNTech's largest shareholders) -&gt; family office. Confirmed as their single-family office by Forbes and multiple family-office trade sources; recent dated direct investments corroborate activity.</t>
+          <t>Identified via known UHNW family (Bettencourt Meyers, largest shareholder of L'Oreal) -&gt; family office. Confirmed as the Bettencourt Meyers single-family office by The National and Caproasia reporting and the firm's own site (tethys.fr).</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.forbes.com/sites/paulwestall/2021/08/24/the-family-office-saving-lives-boosting-the-economy-and-making-billions/</t>
+          <t>https://www.thenationalnews.com/business/money/2023/03/13/billionaires-loreal-heir-names-new-head-of-family-office/</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Described as the single-family office of twins Andreas and Thomas Strungmann (who founded generics maker Hexal); anchor and largest shareholder of BioNTech (~43.5%).</t>
+          <t>Described as the single-family office managing the assets of the Bettencourt Meyers family, majority shareholder of L'Oreal; Tethys Invest is the entrepreneurial-investment subsidiary.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Forbes and biotech/family-office trade press naming Athos as the Strungmann single-family office; documented anchor investment in BioNTech.</t>
+          <t>The National and Caproasia press naming Tethys as the Bettencourt family office; firm's own website.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -6276,12 +6534,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Not disclosed; dominated by the BioNTech stake (~43.5%).</t>
+          <t>Press figure for total family assets (dominated by the L'Oreal stake); Tethys Invest deploys &gt;EUR 3bn of direct-investment capital.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Beneficial owner (with twin brother Thomas Strungmann) of the family office; jointly direct its investments.</t>
+          <t>Head of the family's investment firm (Tethys Invest) and, per 2025 press, appointed to the L'Oreal board seat area of the family; family chair of Tethys is Francoise Bettencourt Meyers, CEO of Tethys is Jean-Pierre Meyers.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -6294,7 +6552,7 @@
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>https://familyofficehub.io/blog/athos-family-office-invests-in-aavantgarde-bios-141m-series-b/</t>
+          <t>https://www.caproasia.com/2025/02/08/loreal-heiress-france-billionaire-francoise-bettencourt-meyers-age-71-with-76-billion-fortune-starts-family-succession-with-retirement-from-loreal-board-as-vice-chairman-son-jean-victo/</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -6302,12 +6560,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SFO-premji-invest</t>
+          <t>SFO-cofra-holding-brenninkmeijer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Premji Invest</t>
+          <t>COFRA Holding AG</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6317,22 +6575,22 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (Azim Premji, Wipro founder) -&gt; family office. Confirmed as his family office by The Arc and family-office databases; recent dated deals corroborate active investing.</t>
+          <t>Identified via known UHNW family (Brenninkmeijer, owners of C&amp;A) -&gt; family holding/office. Confirmed by Crain Currency and the firm's own site as the Brenninkmeijer family's Zug-based holding; leadership verified on cofraholding.com.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.thearcweb.com/article/wipro-azim-premji-invest-family-office-tk-kurien-0clyngtMEXrGHBNX</t>
+          <t>https://www.craincurrency.com/family-office-management/secretive-brenninkmeijer-family-behind-ca-opens-39-billion-retail-empire</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Described as the private investment office managing the portfolio of Wipro founder Azim Premji and family across public equities, PE and venture; founded 2006, offices in Bengaluru and Menlo Park.</t>
+          <t>Established 2001 in Zug to coordinate the Brenninkmeijer family's global businesses and investments; a single-family-owned holding with subsidiaries C&amp;A (retail), Redevco (real estate), Bregal (PE) and Anthos (asset management).</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>The Arc and multiple family-office databases identify Premji Invest as Azim Premji's family office; firm website.</t>
+          <t>Crain Currency reporting on the family's ~$39bn empire; COFRA's own leadership/governance page listing the family-dominated board.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -6342,12 +6600,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>The Arc reporting that the family office crossed $10bn in managed assets.</t>
+          <t>Reported total group asset base (Crain Currency and familyofficehub).</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Chief executive and top investment decision-maker of the office (former Wipro CEO); family principal is Azim Premji; U.S. office led by Sandesh Patnam.</t>
+          <t>Family-member chairman since 2018 (former CEO of COFRA, C&amp;A Europe and Anthos); group CEO is Boudewijn Beerkens, CFO Florian Brenninkmeyer (from 2025).</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -6360,7 +6618,7 @@
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>https://tracxn.com/d/private-equity/premjiinvest/__a9W9DN9hd7WxIGfm5z8PuA6IrDlu-VIas8-t59BU6xw</t>
+          <t>https://www.cofraholding.com/en/newsroom/latest-news/2025/redevco-closes-landmark-475m-loan-investment-for-new-real-estate-debt-platform/</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -6368,12 +6626,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SFO-catamaran-ventures-murthy</t>
+          <t>SFO-athos-strungmann</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Catamaran Management Services Pvt. Ltd. (Catamaran Ventures)</t>
+          <t>Athos Service GmbH (family investment entity Athos KG)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6383,22 +6641,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (N.R. Narayana Murthy, Infosys founder) -&gt; family office. Confirmed as his single-family office by Bloomberg and the firm's own site; described as investing permanent capital with no external LPs.</t>
+          <t>Identified via known UHNW family (Strungmann brothers, BioNTech's largest shareholders) -&gt; family office. Confirmed as their single-family office by Forbes and multiple family-office trade sources; recent dated direct investments corroborate activity.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2025-08-26/family-office-to-billionaire-murthy-warns-on-startup-valuations</t>
+          <t>https://www.forbes.com/sites/paulwestall/2021/08/24/the-family-office-saving-lives-boosting-the-economy-and-making-billions/</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Firm describes itself as a single-family office investing permanent capital with no external limited partners, managing the assets of Narayana Murthy and family.</t>
+          <t>Described as the single-family office of twins Andreas and Thomas Strungmann (who founded generics maker Hexal); anchor and largest shareholder of BioNTech (~43.5%).</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bloomberg reporting naming it the family office of billionaire Narayana Murthy; firm's own 'About' page stating single-family-office / permanent-capital structure.</t>
+          <t>Forbes and biotech/family-office trade press naming Athos as the Strungmann single-family office; documented anchor investment in BioNTech.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -6408,12 +6666,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Not disclosed.</t>
+          <t>Not disclosed; dominated by the BioNTech stake (~43.5%).</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Founder and ultimate principal; firm led operationally by Chairman M.D. Ranganath (ex-Infosys CFO) and President Deepak Padaki.</t>
+          <t>Beneficial owner (with twin brother Thomas Strungmann) of the family office; jointly direct its investments.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -6426,7 +6684,7 @@
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2025-08-26/family-office-to-billionaire-murthy-warns-on-startup-valuations</t>
+          <t>https://familyofficehub.io/blog/athos-family-office-invests-in-aavantgarde-bios-141m-series-b/</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -6434,37 +6692,37 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>UKCH-10876208</t>
+          <t>SFO-premji-invest</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SHA FAMILY OFFICE LTD</t>
+          <t>Premji Invest</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>press</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Companies House 10876208 (Private limited company); inc. 20 July 2017</t>
+          <t>Identified via known UHNW individual (Azim Premji, Wipro founder) -&gt; family office. Confirmed as his family office by The Arc and family-office databases; recent dated deals corroborate active investing.</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/10876208</t>
+          <t>https://www.thearcweb.com/article/wipro-azim-premji-invest-family-office-tk-kurien-0clyngtMEXrGHBNX</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Mr Sharnpreet Singh Buttar); firm carries a fund-management/investment SIC (64205 - Activities of financial services holding companies). Single-family control of an investment vehicle = single-family office.</t>
+          <t>Described as the private investment office managing the portfolio of Wipro founder Azim Premji and family across public equities, PE and venture; founded 2006, offices in Bengaluru and Menlo Park.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Mr Sharnpreet Singh Buttar); firm carries a fund-management/investment SIC (64205 - Activities of financial services holding companies). Single-family control of an investment vehicle = single-family office.</t>
+          <t>The Arc and multiple family-office databases identify Premji Invest as Azim Premji's family office; firm website.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -6472,8 +6730,16 @@
           <t>corroborated</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>The Arc reporting that the family office crossed $10bn in managed assets.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Chief executive and top investment decision-maker of the office (former Wipro CEO); family principal is Azim Premji; U.S. office led by Sandesh Patnam.</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
           <t>unresolved</t>
@@ -6482,52 +6748,64 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>https://tracxn.com/d/private-equity/premjiinvest/__a9W9DN9hd7WxIGfm5z8PuA6IrDlu-VIas8-t59BU6xw</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>UKCH-15240886</t>
+          <t>SFO-catamaran-ventures-murthy</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FREEDMAN FAMILY OFFICE</t>
+          <t>Catamaran Management Services Pvt. Ltd. (Catamaran Ventures)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>press</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Companies House 15240886 (Private unlimited company); inc. 27 October 2023</t>
+          <t>Identified via known UHNW individual (N.R. Narayana Murthy, Infosys founder) -&gt; family office. Confirmed as his single-family office by Bloomberg and the firm's own site; described as investing permanent capital with no external LPs.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/15240886</t>
+          <t>https://www.bloomberg.com/news/articles/2025-08-26/family-office-to-billionaire-murthy-warns-on-startup-valuations</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+          <t>Firm describes itself as a single-family office investing permanent capital with no external limited partners, managing the assets of Narayana Murthy and family.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+          <t>Bloomberg reporting naming it the family office of billionaire Narayana Murthy; firm's own 'About' page stating single-family-office / permanent-capital structure.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Not disclosed.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Founder and ultimate principal; firm led operationally by Chairman M.D. Ranganath (ex-Infosys CFO) and President Deepak Padaki.</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>unresolved</t>
@@ -6536,18 +6814,22 @@
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/articles/2025-08-26/family-office-to-billionaire-murthy-warns-on-startup-valuations</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UKCH-11031775</t>
+          <t>UKCH-10876208</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RALPH FAMILY OFFICE LIMITED</t>
+          <t>SHA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -6557,22 +6839,22 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Companies House 11031775 (Private limited company); inc. 25 October 2017</t>
+          <t>Companies House 10876208 (Private limited company); inc. 20 July 2017</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/11031775</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/10876208</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Melanie Lynette Ralph; Mr Jan De Ridder Ralph); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Mr Sharnpreet Singh Buttar); firm carries a fund-management/investment SIC (64205 - Activities of financial services holding companies). Single-family control of an investment vehicle = single-family office.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Melanie Lynette Ralph; Mr Jan De Ridder Ralph); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Mr Sharnpreet Singh Buttar); firm carries a fund-management/investment SIC (64205 - Activities of financial services holding companies). Single-family control of an investment vehicle = single-family office.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -6592,6 +6874,114 @@
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>UKCH-15240886</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FREEDMAN FAMILY OFFICE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>uk-companies-house</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Companies House 15240886 (Private unlimited company); inc. 27 October 2023</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/15240886</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>UKCH-11031775</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>RALPH FAMILY OFFICE LIMITED</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>uk-companies-house</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Companies House 11031775 (Private limited company); inc. 25 October 2017</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://find-and-update.company-information.service.gov.uk/company/11031775</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Melanie Lynette Ralph; Mr Jan De Ridder Ralph); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Melanie Lynette Ralph; Mr Jan De Ridder Ralph); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6604,7 +6994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E136"/>
+  <dimension ref="A1:E138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7937,7 +8327,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fortis Advisors, LLC</t>
+          <t>Family Office Research, LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -7948,7 +8338,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -7971,7 +8361,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -7983,7 +8373,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fortitude Family Office, LLC</t>
+          <t>Fortis Advisors, LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -7994,7 +8384,7 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8396,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GELLING FAMILY OFFICE LIMITED</t>
+          <t>Fortitude Family Office, LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8029,7 +8419,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GUNPUTH FAMILY OFFICE LIMITED</t>
+          <t>GELLING FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8052,7 +8442,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Geller Advisors LLC</t>
+          <t>GUNPUTH FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8086,7 +8476,7 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8488,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HALL LAURIE J TRUSTEE</t>
+          <t>Geller Advisors LLC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -8109,7 +8499,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8522,7 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -8144,7 +8534,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HBBA FAMILY OFFICE LIMITED</t>
+          <t>HALL LAURIE J TRUSTEE</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -8155,7 +8545,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -8167,7 +8557,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HILL FAMILY OFFICE LIMITED</t>
+          <t>HBBA FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -8190,7 +8580,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
+          <t>HILL FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -8224,7 +8614,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -8236,7 +8626,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>INTREPID FAMILY OFFICE LLC</t>
+          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8247,7 +8637,7 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8649,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ISHER CAPITAL FAMILY OFFICE LTD</t>
+          <t>INTREPID FAMILY OFFICE LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8282,7 +8672,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Independent Family Office, LLC</t>
+          <t>ISHER CAPITAL FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8305,7 +8695,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kopp Family Office, LLC</t>
+          <t>Independent Family Office, LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8328,7 +8718,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LELS CLARK FAMILY OFFICE LTD</t>
+          <t>Kopp Family Office, LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8351,7 +8741,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lido Advisors, LLC</t>
+          <t>LELS CLARK FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8385,7 +8775,7 @@
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -8397,7 +8787,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>MARCUARD FAMILY OFFICE LTD</t>
+          <t>Lido Advisors, LLC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8408,7 +8798,7 @@
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -8420,7 +8810,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MOBH UK FAMILY OFFICE LTD</t>
+          <t>MARCUARD FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8443,7 +8833,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NORTHBRIDGE FAMILY OFFICE LTD</t>
+          <t>MOBH UK FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -8466,7 +8856,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NOVA FAMILY OFFICE LTD</t>
+          <t>NORTHBRIDGE FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8489,7 +8879,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nilsson Family Office Ltd</t>
+          <t>NOVA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -8500,7 +8890,7 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -8627,7 +9017,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>OLD HOUSE FAMILY OFFICE LIMITED</t>
+          <t>Nilsson Family Office Ltd</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -8638,7 +9028,7 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -8650,7 +9040,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>OneAscent Family Office, LLC</t>
+          <t>OLD HOUSE FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -8673,7 +9063,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Orion Porfolio Solutions, LLC</t>
+          <t>OneAscent Family Office, LLC</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -8707,7 +9097,7 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -8719,7 +9109,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Orion Portfolio Solutions, LLC</t>
+          <t>Orion Porfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -8730,7 +9120,7 @@
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -8753,7 +9143,7 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -8765,7 +9155,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>PANDA FAMILY OFFICE LTD</t>
+          <t>Orion Portfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -8776,7 +9166,7 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -8788,7 +9178,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PANTHEON A FAMILY OFFICE LIMITED</t>
+          <t>PANDA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -8811,7 +9201,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PATHSTONE FAMILY OFFICE, LLC</t>
+          <t>PANTHEON A FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -8834,7 +9224,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PMG Family Office LLC</t>
+          <t>PATHSTONE FAMILY OFFICE, LLC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -8857,7 +9247,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PROSPERITY FAMILY OFFICE LIMITED</t>
+          <t>PMG Family Office LLC</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -8880,7 +9270,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Pathstone Holdings, LLC</t>
+          <t>PROSPERITY FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -8914,7 +9304,7 @@
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -8926,7 +9316,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Pioneer Family Office, LLC</t>
+          <t>Pathstone Holdings, LLC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -8937,7 +9327,7 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -8949,7 +9339,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>RALPH FAMILY OFFICE LIMITED</t>
+          <t>Pioneer Family Office, LLC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -8972,7 +9362,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SHA FAMILY OFFICE LTD</t>
+          <t>RALPH FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -8995,7 +9385,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SIGNATURE FAMILY OFFICE LTD</t>
+          <t>SHA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -9018,7 +9408,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SIMON FAMILY OFFICE INSURES LIMITED</t>
+          <t>SIGNATURE FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -9041,7 +9431,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SWAILES COMMERCIAL FAMILY OFFICE LTD</t>
+          <t>SIMON FAMILY OFFICE INSURES LIMITED</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -9064,7 +9454,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SWAILES TRADING GROUP FAMILY OFFICE LTD</t>
+          <t>SWAILES COMMERCIAL FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -9087,7 +9477,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Sageworth Trust Co</t>
+          <t>SWAILES TRADING GROUP FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -9121,7 +9511,7 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -9133,7 +9523,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Standard Family Office LLC</t>
+          <t>Sageworth Trust Co</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -9144,7 +9534,7 @@
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -9156,7 +9546,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Stenger Family Office, LLC</t>
+          <t>Standard Family Office LLC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -9179,7 +9569,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Stokes Family Office, LLC</t>
+          <t>Stenger Family Office, LLC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -9202,7 +9592,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>THE DIGITAL FAMILY OFFICE LIMITED</t>
+          <t>Stokes Family Office, LLC</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -9225,7 +9615,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>THE FAMILY OFFICE CHELTENHAM LIMITED</t>
+          <t>THE DIGITAL FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -9248,7 +9638,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>TIGRIS FAMILY OFFICE LIMITED</t>
+          <t>THE FAMILY OFFICE CHELTENHAM LIMITED</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -9271,7 +9661,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Tarbox Family Office, Inc.</t>
+          <t>TIGRIS FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -9299,17 +9689,13 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>principal_email</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>laura@tarbox.com</t>
-        </is>
-      </c>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>email not found at cited source on re-fetch (https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf); downgraded verified-&gt;unverified</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -9402,18 +9788,22 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Timonier Family Office, LTD.</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>firm-qualification</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
+          <t>principal_email</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>laura@tarbox.com</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>email not found at cited source on re-fetch (https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf); downgraded verified-&gt;unverified</t>
         </is>
       </c>
     </row>
@@ -9425,18 +9815,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>TrustBank</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>firm-qualification</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
+          <t>principal_email</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>laura@tarbox.com</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>email not found at cited source on re-fetch (https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf); downgraded verified-&gt;unverified</t>
         </is>
       </c>
     </row>
@@ -9448,7 +9842,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>TrustBank</t>
+          <t>Timonier Family Office, LTD.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -9459,7 +9853,7 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -9471,7 +9865,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>UNITA FAMILY OFFICE UK LIMITED</t>
+          <t>TrustBank</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -9494,7 +9888,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>UR FAMILY OFFICE MANAGEMENT SERVICES LTD</t>
+          <t>TrustBank</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -9505,7 +9899,7 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -9517,7 +9911,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>VASIL FAMILY OFFICE LLP</t>
+          <t>UNITA FAMILY OFFICE UK LIMITED</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -9540,7 +9934,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>VPR Management LLC</t>
+          <t>UR FAMILY OFFICE MANAGEMENT SERVICES LTD</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -9563,7 +9957,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>VPR Management LLC</t>
+          <t>VASIL FAMILY OFFICE LLP</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -9574,7 +9968,7 @@
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9980,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>VSTAR LONDON FAMILY OFFICE LTD</t>
+          <t>VPR Management LLC</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -9609,7 +10003,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Veritable, L.P.</t>
+          <t>VPR Management LLC</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -9620,7 +10014,7 @@
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -9632,7 +10026,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Veritable, L.P.</t>
+          <t>VSTAR LONDON FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -9643,7 +10037,7 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -9655,7 +10049,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Virtus Family Office LLC</t>
+          <t>Veritable, L.P.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -9678,7 +10072,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>WEYBRIDGE FAMILY OFFICE SERVICES LIMITED</t>
+          <t>Veritable, L.P.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -9689,7 +10083,7 @@
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -9701,7 +10095,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Wealthgate Family Office, LLC</t>
+          <t>Virtus Family Office LLC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9724,7 +10118,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Wilmington Savings Fund Society, FSB</t>
+          <t>WEYBRIDGE FAMILY OFFICE SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -9747,7 +10141,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Wilmington Savings Fund Society, FSB</t>
+          <t>Wealthgate Family Office, LLC</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9757,6 +10151,52 @@
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Wilmington Savings Fund Society, FSB</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Wilmington Savings Fund Society, FSB</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
         <is>
           <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
@@ -9805,11 +10245,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>46%</t>
         </is>
       </c>
     </row>
@@ -9824,7 +10264,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>24%</t>
         </is>
       </c>
     </row>
@@ -9839,7 +10279,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>30%</t>
         </is>
       </c>
     </row>
@@ -9851,7 +10291,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="C6" t="inlineStr"/>
     </row>
@@ -9862,7 +10302,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C7" t="inlineStr"/>
     </row>

--- a/data/final/family_office_dataset.xlsx
+++ b/data/final/family_office_dataset.xlsx
@@ -429,11 +429,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W38"/>
+  <dimension ref="A1:W51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
@@ -442,9 +442,9 @@
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="60" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="28" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
+    <col width="49" customWidth="1" min="11" max="11"/>
+    <col width="60" customWidth="1" min="12" max="12"/>
+    <col width="49" customWidth="1" min="13" max="13"/>
     <col width="32" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -1696,103 +1696,83 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEC13F-0001599603</t>
+          <t>UKCH-10957456</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tarbox Family Office, Inc.</t>
+          <t>Old House Family Office Limited</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>None as a single client family; founder-owned firm (Laura Tarbox founder, CEO and principal owner). Namesake is the founder, not a served family.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://tarbox.com/</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/tarboxfamilyoffice</t>
-        </is>
-      </c>
+          <t>Lewis family (Christopher David Lewis, director; Stella Ann Lewis, former director/ceased PSC with trust influence)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Newport Beach, CA-based multi-family office and SEC-registered investment adviser founded in 1985 by Laura Tarbox, CFP. Fee-only firm serving 100+ HNW/UHNW client families (also charities, businesses, trusts/estates) with comprehensive financial planning, tax preparation and individualized investment management; $5M minimum, over $1B AUM. Also has a Scottsdale, AZ office.</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Team-based, individualized asset allocation and investment management integrated with comprehensive financial and estate planning; fee-only fiduciary model.</t>
-        </is>
-      </c>
+          <t>UK private limited company incorporated 12 Sep 2017, presenting as the Lewis family's family-office / holding vehicle. Sits above / alongside Old Friend Capital Limited, a Bournemouth-based real-estate investment and development business run by Christopher (Chris) Lewis, whose track record includes UK leisure-residential and renewable-energy property projects (e.g. Wet N Wild Newcastle, Oasis Swindon). Accounts currently overdue as of research date.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Diversified asset-allocation / individualized investment management; no single-sector focus.</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Over $1 billion (100+ client families)</t>
-        </is>
-      </c>
+          <t>Real estate (buying/selling and management of own real estate); leisure-residential property development; renewable energy property (per principal's stated specialism on LinkedIn)</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>NEWPORT BEACH</t>
+          <t>Poole</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>Dorset, England</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Laura Tarbox</t>
+          <t>Christopher David Lewis</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Founder, CEO &amp; principal owner (CFP)</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>laura@tarbox.com</t>
-        </is>
-      </c>
+          <t>Director (Old House Family Office Limited); principal of Old Friend Capital</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chrislewismoirai/</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
-          <t>unverified</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>(949) 721-2330</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Founded 1985; CFP since 1984; 100+ client families and &gt;$1B AUM; $5M account minimum; second office in Scottsdale, AZ; Laura Tarbox a frequent WSJ/NYT/LA Times media source</t>
+          <t>Ceased PSC Stella Ann Lewis on 1 Jun 2024 (trust influence noted); director change May 2021 (Stella Lewis resigned, Christopher Lewis appointed). Accounts overdue as of 2026.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>1985 (founded); 1984 (Laura Tarbox CFP)</t>
+          <t>2017-09-12 (incorporated); 2021-05-14 (director change); 2024-06-01 (Stella Lewis ceased as PSC)</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1802,110 +1782,102 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Personal LinkedIn /in profile not located (only firm company page). Email captured from Laura Tarbox's public presentation PDF (matches firm domain) rather than the current bio page; treat as published-but-unverified.</t>
+          <t>No firm website or public FO branding beyond the company name; classification as an operating family office is inferred from the trust/PSC structure and the principal's real-estate activity rather than from any self-description as a family office. Accounts overdue. Registered office is Poole Stadium (a business address). 'Moirai' link is via principal's LinkedIn handle / prior Moirai Capital Investments Ltd, not confirmed as current firm branding.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEC13F-0002056106</t>
+          <t>SFO-grok-ventures-cannon-brookes</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stenger Family Office, LLC</t>
+          <t>Grok Ventures (Cannon-Brookes Family Office)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Stenger family (firm founded/led by Nick Stenger; the family has advised clients since 1981). The 'family' is the owner-operator, not a single client family.</t>
+          <t>Cannon-Brookes family (Mike Cannon-Brookes, co-founder of Atlassian)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.stengerfamilyoffice.com/</t>
+          <t>https://www.grok.ventures/</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/stenger-family-office</t>
+          <t>https://www.linkedin.com/company/grok-ventures</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Naperville, IL-based multi-family office / independent fiduciary RIA led by founder-CEO Nick Stenger, offering financial planning, investment management, and (via related companies) tax preparation, estate strategies and insurance. Also has a Spring, TX office. ~$731M AUM; named a Forbes Best-in-State Wealth Advisor 2026.</t>
+          <t>Sydney-based single-family office of Atlassian co-founder Mike Cannon-Brookes. One of Australia's most prominent family offices, it has increasingly concentrated on climate and clean-technology investing (backing SunCable's Australia-Asia Power Link, battery and decarbonisation ventures) alongside a diversified portfolio; in early 2026 it announced a climate-only investment focus.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Goals-based planning: assesses cash needs and upcoming goals, then builds customized portfolios.</t>
+          <t>Mission-driven investing to accelerate decarbonisation and net-zero, via venture and direct stakes in climate/clean-tech, energy and enabling technologies.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Core individual-stock portfolios and ETF-based asset-allocation portfolios; no single-sector focus.</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>~$731 million (as of 2026-06-30)</t>
-        </is>
-      </c>
+          <t>Climate tech, clean energy/renewables, batteries, decarbonisation, technology venture</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>NAPERVILLE</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>New South Wales</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Nicholas David Stenger</t>
+          <t>Mike Cannon-Brookes</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Founder &amp; Chief Executive Officer</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>nick.stenger@stengerfamilyoffice.com</t>
-        </is>
-      </c>
+          <t>Founder / Family Principal</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mikecannonbrookes</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>630-912-8295</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>$731M AUM (2026-06-30); Forbes Best-in-State Wealth Advisor 2026; hosts 'The Nick Stenger Show' podcast; opened Spring, TX office</t>
+          <t>Announced climate-only investment focus and appointment of CEO Tan Kueh (Jan 2026); latest investment Asterix Foods seed round (2025-10-08); portfolio exit of Cog (2025-03-03); long-running backing of SunCable.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-06-30 (AUM date); 2026 (Forbes Best-in-State)</t>
+          <t>2026-01; 2025-10-08; 2025-03-03</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1915,19 +1887,19 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Serves 1,200+ families 'of all net worth sizes' — a broad wealth-management RIA using family-office branding rather than a classic UHNW MFO; hence proof strength 'corroborated'. Personal LinkedIn /in profile not located (only company page and a Calendly slug for 'nicholasstenger'). No published individual email or direct phone line found.</t>
+          <t>principal_linkedin is the plausible public Mike Cannon-Brookes /in/ profile but not verified to explicitly list Grok Ventures (marked unconfirmed). Website domain (grok.ventures) asserted from press, not independently fetched. Mike and Annie Cannon-Brookes separated (2023); the office remains Mike's family office.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEC13F-0001908612</t>
+          <t>SEC13F-0001599603</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Allie Family Office LLC</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1937,47 +1909,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>None (owner-operated MFO). Founded 2019 and 100% owned by Bruno Ghio, formerly Regional Head of the Family Office / Managing Director at Banco de Credito del Peru (BCP) and a senior private banker at JPMorgan. Not tied to a single client family.</t>
+          <t>None as a single client family; founder-owned firm (Laura Tarbox founder, CEO and principal owner). Namesake is the founder, not a served family.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://allie-intl.com/en/home/</t>
+          <t>https://tarbox.com/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/alli%C3%A9-family-office</t>
+          <t>https://www.linkedin.com/company/tarboxfamilyoffice</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Miami-based (with a Lima, Peru office) independent multi-family office and SEC-registered investment adviser founded in 2019 by Bruno Ghio, serving Latin American — predominantly Peruvian — high-net-worth families. Provides discretionary and limited-discretionary portfolio management, wealth structuring, tax planning, single-family-office consulting and cross-border coordination via a global network of tax/legal/banking experts.</t>
+          <t>Newport Beach, CA-based multi-family office and SEC-registered investment adviser founded in 1985 by Laura Tarbox, CFP. Fee-only firm serving 100+ HNW/UHNW client families (also charities, businesses, trusts/estates) with comprehensive financial planning, tax preparation and individualized investment management; $5M minimum, over $1B AUM. Also has a Scottsdale, AZ office.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Cross-border wealth management and multi-generational governance for Latin American families relocating capital (and increasingly themselves) to the US; independent, conflict-free advisory.</t>
+          <t>Team-based, individualized asset allocation and investment management integrated with comprehensive financial and estate planning; fee-only fiduciary model.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Discretionary and limited-discretionary global portfolio management (largest reported 13F holding is the SPDR S&amp;P 500 ETF Trust; 95 equity positions); diversified across public markets, no single-sector focus disclosed.</t>
+          <t>Diversified asset-allocation / individualized investment management; no single-sector focus.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>~$1.15 billion AUM (as of 2024-12-31: ~$508.7M discretionary + ~$637.9M limited-discretionary); aggregators (FINTRX) report ~$1.3B; press (Bloomberg/Crain, 2024) cites ~$2B across the Peru/Miami practice</t>
+          <t>Over $1 billion (100+ client families)</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>NEWPORT BEACH</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1987,38 +1959,38 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Bruno Ghio</t>
+          <t>Laura Tarbox</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Founder &amp; Chief Executive Officer (CFA, CAIA, FRM); 100% owner</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>https://pe.linkedin.com/in/bruno-ghio-1264b616b</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr"/>
+          <t>Founder, CEO &amp; principal owner (CFP)</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>laura@tarbox.com</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>7866357162</t>
+          <t>(949) 721-2330</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Founded 2019; among Peru's top-3 independent multi-family offices; ~23 client families (avg ~$50M); Miami + Lima offices; growth from Peruvian clients relocating to Miami; added a partner in Peru</t>
+          <t>Founded 1985; CFP since 1984; 100+ client families and &gt;$1B AUM; $5M account minimum; second office in Scottsdale, AZ; Laura Tarbox a frequent WSJ/NYT/LA Times media source</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2019 (firm founding); 2024 (Bloomberg/Crain profile); AUM as of 2024-12-31</t>
+          <t>1985 (founded); 1984 (Laura Tarbox CFP)</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2028,19 +2000,19 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Legal 13F filer name is 'Allie Family Office LLC'; brand is 'Allié Family Office' (allie-intl.com). AUM figures vary by source (~$1.15B ADV vs ~$1.3B FINTRX vs ~$2B press including the broader Peru practice). No individual email or direct phone published; only generic info@ mailbox. Jose Larrabure is the investment lead; Bruno Ghio named principal as founder/CEO/100% owner.</t>
+          <t>Personal LinkedIn /in profile not located (only firm company page). Email captured from Laura Tarbox's public presentation PDF (matches firm domain) rather than the current bio page; treat as published-but-unverified.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEC13F-0001511137</t>
+          <t>SEC13F-0002056106</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pathstone Family Office, Llc</t>
+          <t>Stenger Family Office, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2050,47 +2022,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>No single family; one of the largest U.S. multi-family offices serving many UHNW families, SFOs and institutions.</t>
+          <t>Stenger family (firm founded/led by Nick Stenger; the family has advised clients since 1981). The 'family' is the owner-operator, not a single client family.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://pathstone.com</t>
+          <t>https://www.stengerfamilyoffice.com/</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/pathstone-family-office</t>
+          <t>https://www.linkedin.com/company/stenger-family-office</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Englewood, NJ headquartered partner-owned multi-family office and SEC-registered RIA founded in 2010 (co-founders Matthew Fleissig, Allan Zachariah, Steve Braverman). Provides integrated investment management, tax, insurance/risk, legacy planning and family-office services to UHNW families, family offices, foundations and endowments; ~$125B firm AUM (2025).</t>
+          <t>Naperville, IL-based multi-family office / independent fiduciary RIA led by founder-CEO Nick Stenger, offering financial planning, investment management, and (via related companies) tax preparation, estate strategies and insurance. Also has a Spring, TX office. ~$731M AUM; named a Forbes Best-in-State Wealth Advisor 2026.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Integrated, institutional-quality advice with a client-first culture; open-architecture investment management including private markets and alternatives; scale via organic growth and acquisitions (e.g., Crestone Capital).</t>
+          <t>Goals-based planning: assesses cash needs and upcoming goals, then builds customized portfolios.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Public equities (13F holdings), private markets/alternatives, fixed income, diversified multi-asset portfolios</t>
+          <t>Core individual-stock portfolios and ETF-based asset-allocation portfolios; no single-sector focus.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>~$125 billion (firm) as of 12/31/2025; ~$187 billion including affiliate firms (other sources cite $170B+ aggregate in 2025).</t>
+          <t>~$731 million (as of 2026-06-30)</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>ENGLEWOOD</t>
+          <t>NAPERVILLE</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2100,38 +2072,38 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Matthew Fleissig</t>
+          <t>Nicholas David Stenger</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Chief Executive Officer (co-founder)</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/fleissig/</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr"/>
+          <t>Founder &amp; Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>nick.stenger@stengerfamilyoffice.com</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>857-305-3070</t>
+          <t>630-912-8295</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Founded 2010; 15th anniversary in 2025; acquired Crestone Capital; ~775+ employees; co-founders Allan Zachariah and Steve Braverman serve as Co-Chairmen; multiple 2025 Family Wealth Report Awards.</t>
+          <t>$731M AUM (2026-06-30); Forbes Best-in-State Wealth Advisor 2026; hosts 'The Nick Stenger Show' podcast; opened Spring, TX office</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>Founded 2010; AUM as of 12/31/2025; ADV dated 03/31/2025.</t>
+          <t>2026-06-30 (AUM date); 2026 (Forbes Best-in-State)</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2141,19 +2113,19 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Very large firm; AUM figures vary by whether affiliate firms are included and by reporting date. No published individual email.</t>
+          <t>Serves 1,200+ families 'of all net worth sizes' — a broad wealth-management RIA using family-office branding rather than a classic UHNW MFO; hence proof strength 'corroborated'. Personal LinkedIn /in profile not located (only company page and a Calendly slug for 'nicholasstenger'). No published individual email or direct phone line found.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEC13F-0001731123</t>
+          <t>SEC13F-0001908612</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Biltmore Family Office, LLC</t>
+          <t>Allie Family Office LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2163,47 +2135,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Founder Chris Cecil is a great-grandson of George Vanderbilt (builder of the Biltmore Estate) and son of Asheville developer George Cecil; 'Biltmore' name derives from that Vanderbilt/Cecil family heritage. The firm serves many outside client families (MFO), not the Vanderbilt/Cecil family exclusively.</t>
+          <t>None (owner-operated MFO). Founded 2019 and 100% owned by Bruno Ghio, formerly Regional Head of the Family Office / Managing Director at Banco de Credito del Peru (BCP) and a senior private banker at JPMorgan. Not tied to a single client family.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.biltmorefamilyoffice.com/</t>
+          <t>https://allie-intl.com/en/home/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/biltmore-family-office-llc</t>
+          <t>https://www.linkedin.com/company/alli%C3%A9-family-office</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Charlotte, NC-based multi-family office and SEC-registered investment adviser founded in 2008 by Chris Cecil. A collaborative/independent RIA to investment-oriented multi-generational families and institutions, providing investment management, asset allocation, investment-policy design, multi-generational and succession planning. ~$3.2-3.5B AUM.</t>
+          <t>Miami-based (with a Lima, Peru office) independent multi-family office and SEC-registered investment adviser founded in 2019 by Bruno Ghio, serving Latin American — predominantly Peruvian — high-net-worth families. Provides discretionary and limited-discretionary portfolio management, wealth structuring, tax planning, single-family-office consulting and cross-border coordination via a global network of tax/legal/banking experts.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Collaborative, investment-policy-driven management for multi-generational HNW/UHNW families and institutions.</t>
+          <t>Cross-border wealth management and multi-generational governance for Latin American families relocating capital (and increasingly themselves) to the US; independent, conflict-free advisory.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Diversified public-equity/ETF portfolios; disclosed top 13F holdings include AAPL, IAU (gold), AVDX, ROBO, VV. No single-sector concentration.</t>
+          <t>Discretionary and limited-discretionary global portfolio management (largest reported 13F holding is the SPDR S&amp;P 500 ETF Trust; 95 equity positions); diversified across public markets, no single-sector focus disclosed.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>~$3.2-3.5 billion (reported ~$3.47B regulatory AUM across ~951 accounts)</t>
+          <t>~$1.15 billion AUM (as of 2024-12-31: ~$508.7M discretionary + ~$637.9M limited-discretionary); aggregators (FINTRX) report ~$1.3B; press (Bloomberg/Crain, 2024) cites ~$2B across the Peru/Miami practice</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>CHARLOTTE</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2213,17 +2185,17 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Chris Cecil</t>
+          <t>Bruno Ghio</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Founder, President &amp; CEO</t>
+          <t>Founder &amp; Chief Executive Officer (CFA, CAIA, FRM); 100% owner</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/chris-cecil-9701b818/</t>
+          <t>https://pe.linkedin.com/in/bruno-ghio-1264b616b</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
@@ -2234,17 +2206,17 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>+1 704-248-5230</t>
+          <t>7866357162</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Founded 2008 by Chris Cecil (LLC organized 2013); ~$3.2-3.5B AUM across ~951 accounts, avg client ~$38M; Cecil chairs TIGER 21 Charlotte / Family Office groups</t>
+          <t>Founded 2019; among Peru's top-3 independent multi-family offices; ~23 client families (avg ~$50M); Miami + Lima offices; growth from Peruvian clients relocating to Miami; added a partner in Peru</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2008 (founding); 2013 (LLC organized)</t>
+          <t>2019 (firm founding); 2024 (Bloomberg/Crain profile); AUM as of 2024-12-31</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2254,19 +2226,19 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Chris Cecil chosen as principal (founder/CEO); Rael Gorelick is Partner &amp; Head of Investments and would be the CIO-level investment lead. No published individual email located. AUM varies by source ($3.2B-$3.5B).</t>
+          <t>Legal 13F filer name is 'Allie Family Office LLC'; brand is 'Allié Family Office' (allie-intl.com). AUM figures vary by source (~$1.15B ADV vs ~$1.3B FINTRX vs ~$2B press including the broader Peru practice). No individual email or direct phone published; only generic info@ mailbox. Jose Larrabure is the investment lead; Bruno Ghio named principal as founder/CEO/100% owner.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEC13F-0001039807</t>
+          <t>SEC13F-0001511137</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Boston Family Office Llc</t>
+          <t>Pathstone Family Office, Llc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2274,41 +2246,49 @@
           <t>MFO</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>No single family; one of the largest U.S. multi-family offices serving many UHNW families, SFOs and institutions.</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.bosfam.com/</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>https://pathstone.com</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pathstone-family-office</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>The Boston Family Office LLC is an independent, employee-owned registered investment adviser founded in 1996 and based in Boston, MA. It provides multi-family-office-style wealth management -- investment management, financial planning, and adviser selection -- to high-net-worth individuals, families and charitable organizations across roughly 789 accounts and ~$1.7-2.0B in assets. It is a multi-family/RIA firm rather than a single-family office.</t>
+          <t>Englewood, NJ headquartered partner-owned multi-family office and SEC-registered RIA founded in 2010 (co-founders Matthew Fleissig, Allan Zachariah, Steve Braverman). Provides integrated investment management, tax, insurance/risk, legacy planning and family-office services to UHNW families, family offices, foundations and endowments; ~$125B firm AUM (2025).</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Client-tailored, diversified portfolio management for wealth preservation and growth across HNW households and institutions; discretionary management (769 of 789 accounts discretionary). Specific house investment philosophy not detailed publicly.</t>
+          <t>Integrated, institutional-quality advice with a client-first culture; open-architecture investment management including private markets and alternatives; scale via organic growth and acquisitions (e.g., Crestone Capital).</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Diversified multi-asset wealth management (public equities, fixed income, funds); not sector-specialized. A partner sits on the board of fixed-income manager Breckinridge Capital Advisors.</t>
+          <t>Public equities (13F holdings), private markets/alternatives, fixed income, diversified multi-asset portfolios</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>~$1.7B AUM across 789 accounts (Form ADV/adviserinfo, 2024-2025); third-party profiles cite ~$1.9-2.02B. As of the most recent Form ADV (2024 filing cycle).</t>
+          <t>~$125 billion (firm) as of 12/31/2025; ~$187 billion including affiliate firms (other sources cite $170B+ aggregate in 2025).</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>ENGLEWOOD</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2318,17 +2298,17 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>George P. Beal</t>
+          <t>Matthew Fleissig</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; Managing Partner (Portfolio Manager)</t>
+          <t>Chief Executive Officer (co-founder)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/george-beal-a6107a16/</t>
+          <t>https://www.linkedin.com/in/fleissig/</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
@@ -2339,17 +2319,17 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>617-624-0800</t>
+          <t>857-305-3070</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Filed Form ADV Part 2A/2B brochures in the 2024 filing cycle (Feb 2024); a partner (Beal) serves on the board of Breckinridge Capital Advisors. Firm moved offices to 20 Custom House St.</t>
+          <t>Founded 2010; 15th anniversary in 2025; acquired Crestone Capital; ~775+ employees; co-founders Allan Zachariah and Steve Braverman serve as Co-Chairmen; multiple 2025 Family Wealth Report Awards.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2024-02-01 (ADV Part 2B brochure)</t>
+          <t>Founded 2010; AUM as of 12/31/2025; ADV dated 03/31/2025.</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2359,19 +2339,19 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Despite the 'family office' name, this is functionally a multi-family-office RIA / private wealth manager serving hundreds of client accounts, not a single family's office. Investment authority is distributed among ~8 managing directors, so Beal is one of several senior decision-makers (though the 13F signatory and co-founder). No official company LinkedIn URL confirmed. No individual email is published (the ZoomInfo masked pattern was deliberately not used).</t>
+          <t>Very large firm; AUM figures vary by whether affiliate firms are included and by reporting date. No published individual email.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SEC13F-0002017744</t>
+          <t>SEC13F-0001731123</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC</t>
+          <t>Biltmore Family Office, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2379,45 +2359,49 @@
           <t>MFO</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Founder Chris Cecil is a great-grandson of George Vanderbilt (builder of the Biltmore Estate) and son of Asheville developer George Cecil; 'Biltmore' name derives from that Vanderbilt/Cecil family heritage. The firm serves many outside client families (MFO), not the Vanderbilt/Cecil family exclusively.</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://arrowrootfamilyoffice.com/</t>
+          <t>https://www.biltmorefamilyoffice.com/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/arrowroot-family-office</t>
+          <t>https://www.linkedin.com/company/biltmore-family-office-llc</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC is a Marina del Rey, CA-based registered investment adviser and multi-family office, originally founded in 2013 as Vitreous Partners and rebranded in 2017. It provides multidisciplinary wealth management -- investment management, retirement, tax and estate planning -- to high-net-worth individuals, entrepreneurs, families and small institutions, with offices in Southern and Northern California, Virginia and Michigan. It is a multi-client RIA, not a single family's office.</t>
+          <t>Charlotte, NC-based multi-family office and SEC-registered investment adviser founded in 2008 by Chris Cecil. A collaborative/independent RIA to investment-oriented multi-generational families and institutions, providing investment management, asset allocation, investment-policy design, multi-generational and succession planning. ~$3.2-3.5B AUM.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Team-based, fiduciary, goals-driven wealth management emphasizing comprehensive planning and diversified investment management for affluent households and business owners; open-architecture advice.</t>
+          <t>Collaborative, investment-policy-driven management for multi-generational HNW/UHNW families and institutions.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Diversified multi-asset wealth management (public equities, funds/ETFs, fixed income, alternatives); not sector-specialized.</t>
+          <t>Diversified public-equity/ETF portfolios; disclosed top 13F holdings include AAPL, IAU (gold), AVDX, ROBO, VV. No single-sector concentration.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>~$431M AUM as of Q2 2025 (third-party profiles); regulatory AUM per the 2025 Form ADV on the firm's site. A floor for total client assets under advisement.</t>
+          <t>~$3.2-3.5 billion (reported ~$3.47B regulatory AUM across ~951 accounts)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Marina Del Rey</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2427,17 +2411,17 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Rob (Roberto Francisco) Santos</t>
+          <t>Chris Cecil</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Chief Executive Officer &amp; Principal Owner</t>
+          <t>Founder, President &amp; CEO</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/rob-santos-afo/</t>
+          <t>https://www.linkedin.com/in/chris-cecil-9701b818/</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
@@ -2448,17 +2432,17 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>310.341.4774</t>
+          <t>+1 704-248-5230</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Announced expansion of its private-wealth practice into Michigan via addition of The Athena Financial Group (offices now include Marina del Rey CA, Rochester Hills MI, Charlottesville VA, El Dorado Hills CA); filed updated Form ADV Part 2A/2B in April 2025.</t>
+          <t>Founded 2008 by Chris Cecil (LLC organized 2013); ~$3.2-3.5B AUM across ~951 accounts, avg client ~$38M; Cecil chairs TIGER 21 Charlotte / Family Office groups</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2022-09-05 (Michigan/Athena expansion press release); 2025-04 (Form ADV update)</t>
+          <t>2008 (founding); 2013 (LLC organized)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2468,19 +2452,19 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Uses the 'family office' label but is a multi-client wealth-management RIA, not a single family's office. Possible name confusion with 'Arrowroot Capital Management' (a separate B2B enterprise-software private-equity firm) -- they are distinct; relationship not established here. No individual email published; RocketReach/broker data deliberately not used. Firm's most recent 13F filer registration is recent (CIK 0002017744).</t>
+          <t>Chris Cecil chosen as principal (founder/CEO); Rael Gorelick is Partner &amp; Head of Investments and would be the CIO-level investment lead. No published individual email located. AUM varies by source ($3.2B-$3.5B).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SEC13F-0001756485</t>
+          <t>SEC13F-0001039807</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Independent Family Office, LLC</t>
+          <t>Boston Family Office Llc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2488,49 +2472,41 @@
           <t>MFO</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>None (owner-operated MFO). Founded 2005 by W. Michael Reickert, who previously led the family-office practice at The Ayco Company. Serves multiple entrepreneurial client families; not a single-family vehicle.</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://ifollc.com/</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/independent-family-office-llc</t>
-        </is>
-      </c>
+          <t>https://www.bosfam.com/</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Albany, New York-based multi-family office and SEC-registered investment adviser founded in 2005 by W. Michael Reickert. A bespoke family office serving a small number of high-net-worth families (average client tenure 10+ years) with investment advisory and asset allocation, estate-planning coordination, transaction/contract advisory and income-tax planning and compliance.</t>
+          <t>The Boston Family Office LLC is an independent, employee-owned registered investment adviser founded in 1996 and based in Boston, MA. It provides multi-family-office-style wealth management -- investment management, financial planning, and adviser selection -- to high-net-worth individuals, families and charitable organizations across roughly 789 accounts and ~$1.7-2.0B in assets. It is a multi-family/RIA firm rather than a single-family office.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Technical, unbiased, independent long-term stewardship of client families' financial lives; capital-allocator approach.</t>
+          <t>Client-tailored, diversified portfolio management for wealth preservation and growth across HNW households and institutions; discretionary management (769 of 789 accounts discretionary). Specific house investment philosophy not detailed publicly.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Discretionary portfolio management and outside-manager selection for HNW families (largest reported 13F holding is the SPDR S&amp;P 500 ETF Trust); diversified, no single-sector focus disclosed.</t>
+          <t>Diversified multi-asset wealth management (public equities, fixed income, funds); not sector-specialized. A partner sits on the board of fixed-income manager Breckinridge Capital Advisors.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>~$617.8 million discretionary AUM across ~34 clients (Form ADV, 2025-03-31); aggregators (FINTRX) report ~$760M</t>
+          <t>~$1.7B AUM across 789 accounts (Form ADV/adviserinfo, 2024-2025); third-party profiles cite ~$1.9-2.02B. As of the most recent Form ADV (2024 filing cycle).</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>ALBANY</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2540,15 +2516,19 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>W. Michael Reickert</t>
+          <t>George P. Beal</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Managing Member / Managing Partner &amp; CEO (also Chief Compliance Officer); IRS Enrolled Agent, JD</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
+          <t>Co-Founder &amp; Managing Partner (Portfolio Manager)</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/george-beal-a6107a16/</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
@@ -2557,17 +2537,17 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>(518) 452-8050</t>
+          <t>617-624-0800</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Founded 2005; SEC-registered 2012; ex-Ayco family-office pedigree; very low client count (~34) with 10+ year average tenure</t>
+          <t>Filed Form ADV Part 2A/2B brochures in the 2024 filing cycle (Feb 2024); a partner (Beal) serves on the board of Breckinridge Capital Advisors. Firm moved offices to 20 Custom House St.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2005 (founding); 2012 (SEC registration); AUM ~$617.8M as of 2025-03-31</t>
+          <t>2024-02-01 (ADV Part 2B brochure)</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2577,19 +2557,19 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Firm marketing copy calls itself a 'bespoke family office' for 'select clients'; the ~34-client, multi-family reality plus Altss classification support MFO. 'dr@ifollc.com' is published but its initials do not match the principal, so it is treated as a shared/general mailbox, not the principal's individual email. No personal LinkedIn confirmed for W. Michael Reickert.</t>
+          <t>Despite the 'family office' name, this is functionally a multi-family-office RIA / private wealth manager serving hundreds of client accounts, not a single family's office. Investment authority is distributed among ~8 managing directors, so Beal is one of several senior decision-makers (though the 13F signatory and co-founder). No official company LinkedIn URL confirmed. No individual email is published (the ZoomInfo masked pattern was deliberately not used).</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UKCH-09580739</t>
+          <t>SEC13F-0002017744</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Blu Family Office Limited</t>
+          <t>Arrowroot Family Office, LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2597,69 +2577,65 @@
           <t>MFO</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Originally Armbruester family (founder's wealth); now MFO serving multiple client families</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.blu-fo.com</t>
+          <t>https://arrowrootfamilyoffice.com/</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/company/blu-family-office</t>
+          <t>https://www.linkedin.com/company/arrowroot-family-office</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FCA-regulated multi-family office (Ltd inc. 2015; operations from 2010) in Richmond upon Thames, founded by Christian Armbruester post Credit Suisse. Offers hedge funds, crypto and alternatives; discretionary arm Blu Investment Management.</t>
+          <t>Arrowroot Family Office, LLC is a Marina del Rey, CA-based registered investment adviser and multi-family office, originally founded in 2013 as Vitreous Partners and rebranded in 2017. It provides multidisciplinary wealth management -- investment management, retirement, tax and estate planning -- to high-net-worth individuals, entrepreneurs, families and small institutions, with offices in Southern and Northern California, Virginia and Michigan. It is a multi-client RIA, not a single family's office.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Discretionary management not relying on forecasting; 'true diversification' and systematic rebalancing; passive in calm markets, opportunistic in adverse ones.</t>
+          <t>Team-based, fiduciary, goals-driven wealth management emphasizing comprehensive planning and diversified investment management for affluent households and business owners; open-architecture advice.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Hedge funds; crypto assets; alternatives; diversified multi-asset</t>
+          <t>Diversified multi-asset wealth management (public equities, funds/ETFs, fixed income, alternatives); not sector-specialized.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>£0.5bn-£1bn (third-party estimated range)</t>
+          <t>~$431M AUM as of Q2 2025 (third-party profiles); regulatory AUM per the 2025 Form ADV on the firm's site. A floor for total client assets under advisement.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>Marina Del Rey</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Greater London</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Christian Armbruester</t>
+          <t>Rob (Roberto Francisco) Santos</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Founder &amp; Principal (largest shareholder ~40.8%)</t>
+          <t>Chief Executive Officer &amp; Principal Owner</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/christianarmbruesterblufamilyoffice</t>
+          <t>https://www.linkedin.com/in/rob-santos-afo/</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
@@ -2668,15 +2644,19 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>310.341.4774</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Founded 2010; Ltd inc. 2015; new director Vishesh Dawar appointed Dec 2025; investment arm rebranded Blu Investment Management; Marie Redron now CEO</t>
+          <t>Announced expansion of its private-wealth practice into Michigan via addition of The Athena Financial Group (offices now include Marina del Rey CA, Rochester Hills MI, Charlottesville VA, El Dorado Hills CA); filed updated Form ADV Part 2A/2B in April 2025.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2015-05-08; 2025-12-08</t>
+          <t>2022-09-05 (Michigan/Athena expansion press release); 2025-04 (Form ADV update)</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2686,98 +2666,106 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Client-facing operations now run under 'Blu Investment Management' (blu-im.com), same address. Armbruester is founder/principal but not current CEO (Marie Redron is). AUM range is a third-party estimate. Only published contacts are a switchboard + generic mailbox.</t>
+          <t>Uses the 'family office' label but is a multi-client wealth-management RIA, not a single family's office. Possible name confusion with 'Arrowroot Capital Management' (a separate B2B enterprise-software private-equity firm) -- they are distinct; relationship not established here. No individual email published; RocketReach/broker data deliberately not used. Firm's most recent 13F filer registration is recent (CIK 0002017744).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UKCH-12233405</t>
+          <t>SEC13F-0001756485</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Schwarz Family Office Ltd</t>
+          <t>Independent Family Office, LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Named after principal Andreas Schwarz (German); no wider family group evidenced beyond the surname</t>
+          <t>None (owner-operated MFO). Founded 2005 by W. Michael Reickert, who previously led the family-office practice at The Ayco Company. Serves multiple entrepreneurial client families; not a single-family vehicle.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://schwarzfamilyoffice.com/</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>https://ifollc.com/</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/independent-family-office-llc</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>London-based boutique investment/advisory firm branded as a family office, established 2019, led by Andreas Schwarz; provides capital raising, debt financing, wealth management and IR services.</t>
+          <t>Albany, New York-based multi-family office and SEC-registered investment adviser founded in 2005 by W. Michael Reickert. A bespoke family office serving a small number of high-net-worth families (average client tenure 10+ years) with investment advisory and asset allocation, estate-planning coordination, transaction/contract advisory and income-tax planning and compliance.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>'Be not afraid of growing slowly, be afraid only of standing still' — sustainable growth via established relationships and exclusive investor access. https://schwarzfamilyoffice.com/</t>
+          <t>Technical, unbiased, independent long-term stewardship of client families' financial lives; capital-allocator approach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Private equity; fintech; wealth management; venture capital; private debt; IPOs</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+          <t>Discretionary portfolio management and outside-manager selection for HNW families (largest reported 13F holding is the SPDR S&amp;P 500 ETF Trust); diversified, no single-sector focus disclosed.</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>~$617.8 million discretionary AUM across ~34 clients (Form ADV, 2025-03-31); aggregators (FINTRX) report ~$760M</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>ALBANY</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Maida Vale</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Andreas Schwarz</t>
+          <t>W. Michael Reickert</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Founder / Director</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
-        </is>
-      </c>
+          <t>Managing Member / Managing Partner &amp; CEO (also Chief Compliance Officer); IRS Enrolled Agent, JD</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>(518) 452-8050</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Listed in Family Capital 'FamCap 50' (2024); second shareholder Syed Furqan Ahmed (490 shares)</t>
+          <t>Founded 2005; SEC-registered 2012; ex-Ayco family-office pedigree; very low client count (~34) with 10+ year average tenure</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2024-02 (FamCap 50)</t>
+          <t>2005 (founding); 2012 (SEC registration); AUM ~$617.8M as of 2025-03-31</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2787,53 +2775,69 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Presents as a family office but functions largely as a boutique capital-raising/advisory consultancy with two shareholders — fo_type left Undetermined. A Family Capital story linking Schwarz to a 'famous UK brand' is paywalled and the brand is NOT confirmed; not asserted. AUM undisclosed.</t>
+          <t>Firm marketing copy calls itself a 'bespoke family office' for 'select clients'; the ~34-client, multi-family reality plus Altss classification support MFO. 'dr@ifollc.com' is published but its initials do not match the principal, so it is treated as a shared/general mailbox, not the principal's individual email. No personal LinkedIn confirmed for W. Michael Reickert.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UKCH-14344019</t>
+          <t>UKCH-09580739</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hazell Family Office Ltd</t>
+          <t>Blu Family Office Limited</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Hazell family of South Wales (haulage/waste/environmental-services wealth)</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
+          <t>Originally Armbruester family (founder's wealth); now MFO serving multiple client families</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://www.blu-fo.com</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/blu-family-office</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Active company (inc. 2022-09-08), SIC 70221 financial management; board is five members of the Hazell family. Structure strongly indicates a single-family office. No website/press footprint.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>FCA-regulated multi-family office (Ltd inc. 2015; operations from 2010) in Richmond upon Thames, founded by Christian Armbruester post Credit Suisse. Offers hedge funds, crypto and alternatives; discretionary arm Blu Investment Management.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Discretionary management not relying on forecasting; 'true diversification' and systematic rebalancing; passive in calm markets, opportunistic in adverse ones.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>70221 - Financial management</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>Hedge funds; crypto assets; alternatives; diversified multi-asset</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>£0.5bn-£1bn (third-party estimated range)</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Usk</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Monmouthshire, Wales</t>
+          <t>Greater London</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2843,15 +2847,19 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Mark David William Hazell</t>
+          <t>Christian Armbruester</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Director (family principal)</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr"/>
+          <t>Founder &amp; Principal (largest shareholder ~40.8%)</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/christianarmbruesterblufamilyoffice</t>
+        </is>
+      </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
@@ -2861,68 +2869,76 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Incorporated Sept 2022; five family directors appointed same day; principal is MD of family haulage/environmental companies</t>
+          <t>Founded 2010; Ltd inc. 2015; new director Vishesh Dawar appointed Dec 2025; investment arm rebranded Blu Investment Management; Marie Redron now CEO</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2015-05-08; 2025-12-08</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>SFO status inferred from shared surname + single family-farm address + Mark Hazell's operating-company directorships; no website/press confirms active investment operations. 'Mark = principal' is inference; control may be shared across the family.</t>
+          <t>Client-facing operations now run under 'Blu Investment Management' (blu-im.com), same address. Armbruester is founder/principal but not current CEO (Marie Redron is). AUM range is a third-party estimate. Only published contacts are a switchboard + generic mailbox.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UKCH-14442767</t>
+          <t>UKCH-12233405</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wedgwood Family Office Limited</t>
+          <t>Schwarz Family Office Ltd</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Undetermined</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Wedgwood (Paul Wedgwood family)</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
+          <t>Named after principal Andreas Schwarz (German); no wider family group evidenced beyond the surname</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://schwarzfamilyoffice.com/</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>UK private company (inc. 2022-10-25) under fund-management SIC, registered at a residential address in Keston. Appears to be the personal single-family investment vehicle of Paul Wedgwood.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>London-based boutique investment/advisory firm branded as a family office, established 2019, led by Andreas Schwarz; provides capital raising, debt financing, wealth management and IR services.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>'Be not afraid of growing slowly, be afraid only of standing still' — sustainable growth via established relationships and exclusive investor access. https://schwarzfamilyoffice.com/</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>66300 - Fund management activities</t>
+          <t>Private equity; fintech; wealth management; venture capital; private debt; IPOs</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Keston</t>
+          <t>London</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Greater London (Bromley)</t>
+          <t>Maida Vale</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2932,15 +2948,19 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Paul Wedgwood</t>
+          <t>Andreas Schwarz</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr"/>
+          <t>Founder / Director</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
@@ -2950,135 +2970,143 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Co-director Christopher James Sharp resigned 2024-04-16; new secretary appointed 2026-01-06; accounts currently overdue</t>
+          <t>Listed in Family Capital 'FamCap 50' (2024); second shareholder Syed Furqan Ahmed (490 shares)</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2024-04-16; 2026-01-06</t>
+          <t>2024-02 (FamCap 50)</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Link between director 'Paul Wedgwood, b.1970' and the Splash Damage/Supernova entrepreneur is a strong inference (name + DOB + separate Wedgwood FIC directorship), NOT hard-confirmed. Zero public FO footprint (no website/LinkedIn/press/AUM); accounts overdue. Residential registered address.</t>
+          <t>Presents as a family office but functions largely as a boutique capital-raising/advisory consultancy with two shareholders — fo_type left Undetermined. A Family Capital story linking Schwarz to a 'famous UK brand' is paywalled and the brand is NOT confirmed; not asserted. AUM undisclosed.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SFO-dfo-management-dell</t>
+          <t>APAC-farro-capital</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DFO Management (Dell Family Office)</t>
+          <t>Farro Capital</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Dell family (Michael Dell, founder/CEO of Dell Technologies)</t>
+          <t>Multi-family office — serves multiple UHNW families, billionaires and unicorn founders; not tied to a single family</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.dellfamilyoffice.com/</t>
+          <t>https://farrocapital.com/</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/dfo-management</t>
+          <t>https://sg.linkedin.com/company/farrocapital</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Private investment firm managing the assets of Michael Dell and family across public equities, private equity, real estate and other asset classes. Originally MSD Capital (1998); the multi-client business became BDT &amp; MSD Partners while the family's captive vehicle was rebranded DFO Management at end of 2022.</t>
+          <t>Independent multi-family office and wealth-management platform founded in October 2022 and headquartered in Singapore, with a regional headquarters established in the DIFC (Dubai). Founded by a team of former private and corporate bankers (Hemant Tucker, Manish Tibrewal, Mahesh Kumar, Rajiv Garg, Uthpal Rao) from institutions including Bank of Singapore, UBS, Barclays and Standard Chartered. Offers goal-based investing, risk management, credit solutions, cross-border structuring, next-generation planning and philanthropic stewardship.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Multi-asset-class permanent capital: public equities, private equity/credit, real estate, opportunistic direct investments.</t>
+          <t>Holistic, goal-based multi-asset wealth management and cross-border structuring for global UHNW families, with a philanthropy/impact emphasis.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Diversified (consumer, real estate, financials, industrials)</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+          <t>Multi-asset wealth management; Private markets; Public markets; Philanthropy/impact</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>~USD2-3 billion</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Michael Dell</t>
+          <t>Hemant Tucker</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Founder / Family Principal</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr"/>
+          <t>Co-Founder &amp; Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hemant-tucker-a97b49bb/</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
-          <t>13F-HR filed 2026-05-15 (period ending 2026-03-31) disclosing U.S. equity holdings; rebrand from MSD Capital to DFO Management completed end of 2022.</t>
+          <t>Oct 2022: founded / soft-launched in Singapore. 2023-2026: grew AUM from &gt;USD1bn to ~USD3bn across 12+ markets. Established a DIFC (Dubai) regional headquarters to drive global expansion.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2026-05-15; 2022-12</t>
+          <t>2022-10; 2026-04</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>The 13F is filed in the name of the Michael &amp; Susan Dell Foundation with DFO Management as manager; the foundation and the family office are affiliated. AUM not disclosed. Michael Dell is a public figure; no personal LinkedIn tied specifically to DFO confirmed.</t>
+          <t>Multi-family office (not a single-family office). Sister brand 'Farro &amp; Co' (international mobility advisory, 3 Philip Street, Singapore) is a distinct entity from Farro Capital. AUM figures are self-reported/press-reported. Principal LinkedIn confirmed; no published individual email.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SFO-bayshore-global-brin</t>
+          <t>UKCH-14344019</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bayshore Global Management (Brin Family Office)</t>
+          <t>Hazell Family Office Ltd</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3088,50 +3116,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Brin family (Sergey Brin, Google co-founder)</t>
+          <t>Hazell family of South Wales (haulage/waste/environmental-services wealth)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Low-profile single-family office managing the wealth of Sergey Brin across public and private markets, real estate and philanthropy. Additional office in Singapore. Reported to have absorbed the Nexus NeuroTech brain-health VC fund in 2026.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Broad multi-asset allocation with notable venture/science-and-health direct investing.</t>
-        </is>
-      </c>
+          <t>Active company (inc. 2022-09-08), SIC 70221 financial management; board is five members of the Hazell family. Structure strongly indicates a single-family office. No website/press footprint.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Diversified; neuroscience/brain-health, deep tech, real estate</t>
+          <t>70221 - Financial management</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Usk</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Monmouthshire, Wales</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Sergey Brin</t>
+          <t>Mark David William Hazell</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Family Principal</t>
+          <t>Director (family principal)</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -3144,12 +3168,12 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Absorbed Nexus NeuroTech brain-health VC fund (reported 2026-04-23, Bloomberg).</t>
+          <t>Incorporated Sept 2022; five family directors appointed same day; principal is MD of family haulage/environmental companies</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3159,19 +3183,19 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>No public website confirmed. AUM figures are press estimates. CEO George Pavlov / CIO Marie Young named in Wikipedia and press but not verified against a primary filing.</t>
+          <t>SFO status inferred from shared surname + single family-farm address + Mark Hazell's operating-company directorships; no website/press confirms active investment operations. 'Mark = principal' is inference; control may be shared across the family.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SFO-hillspire-schmidt</t>
+          <t>UKCH-14442767</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hillspire (Eric Schmidt Family Office)</t>
+          <t>Wedgwood Family Office Limited</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3181,50 +3205,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Schmidt family (Eric &amp; Wendy Schmidt; Eric Schmidt is former Google/Alphabet CEO and chairman)</t>
+          <t>Wedgwood (Paul Wedgwood family)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Single-family office of Eric and Wendy Schmidt focused on deep technology: artificial intelligence, quantum computation, defense tech and biotech. Reported to have invested in 22+ private AI firms since 2019 (including Anthropic, SandboxAQ, Inworld AI) and topped CNBC's inaugural family-office dealmaking ranking for 2025.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Deep-tech direct investing concentrated in AI, quantum, defense technology and biotech.</t>
-        </is>
-      </c>
+          <t>UK private company (inc. 2022-10-25) under fund-management SIC, registered at a residential address in Keston. Appears to be the personal single-family investment vehicle of Paul Wedgwood.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>AI, quantum computing, defense tech, biotech</t>
+          <t>66300 - Fund management activities</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Keston</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Greater London (Bromley)</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Eric Schmidt</t>
+          <t>Paul Wedgwood</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Family Principal / Founder</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -3237,12 +3257,12 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Ranked #1 most active U.S. family office for dealmaking in 2025 (15 investments, mostly AI) per CNBC 2026-02-12; disclosed 22 private AI startup investments since 2019 (CNBC 2025-01-21).</t>
+          <t>Co-director Christopher James Sharp resigned 2024-04-16; new secretary appointed 2026-01-06; accounts currently overdue</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2026-02-12; 2025-01-21</t>
+          <t>2024-04-16; 2026-01-06</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3252,19 +3272,19 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>No public website confirmed (hillspire.com not verified). Does not file 13F (EDGAR full-text search returned no 13F-HR). AUM not disclosed. President Ken Goldman named in press, not verified against a primary filing.</t>
+          <t>Link between director 'Paul Wedgwood, b.1970' and the Splash Damage/Supernova entrepreneur is a strong inference (name + DOB + separate Wedgwood FIC directorship), NOT hard-confirmed. Zero public FO footprint (no website/LinkedIn/press/AUM); accounts overdue. Residential registered address.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SFO-blue-pool-capital-tsai</t>
+          <t>UKCH-17062903</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Blue Pool Capital (Joe Tsai Family Office)</t>
+          <t>Frigus Family Office Ltd</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3274,58 +3294,54 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tsai family (Joseph Tsai, Alibaba co-founder and chairman)</t>
+          <t>Gudmundsson family (Lydur Gudmundsson, co-founder of Bakkavor; brother Agust Gudmundsson also linked to Frigus-branded entities)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.bluepoolcapital.com/</t>
+          <t>https://www.frigus.is/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hong Kong-based investment firm overseeing the Tsai family's wealth across hedge funds, private equity, private credit, venture and sports assets (Brooklyn Nets, LAFC). Raised ~$1bn for its first dedicated PE vehicle (Riverside Fund) reported 2026. Led by CEO Oliver Weisberg (ex-Goldman Sachs, ex-Citadel).</t>
+          <t>UK private limited company incorporated 2 Mar 2026 as the UK entity of Frigus, the Gudmundsson family's single family office (group HQ Kópavogur, Iceland, with a Luxembourg office). Frigus actively manages the family's assets, investments and real estate; its principal holding is a stake in LSE-listed Greencore Group, arising from the 2026 merger of the family business Bakkavor into Greencore. Registered at a London residential address (Fountain House, Park Street, Mayfair).</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Multi-strategy long-term capital: public markets, PE, private credit, venture, and sports/real assets.</t>
+          <t>Active management of family assets, investments and real estate (per frigus.is); large concentrated public-equity position in Greencore Group plus real estate.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Diversified; technology (SpaceX, Epic Games, ByteDance), consumer/luxury (Golden Goose), sports, Japanese real estate</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>~$50 billion</t>
-        </is>
-      </c>
+          <t>Listed equities (food manufacturing via Greencore Group stake), real estate, diversified investments</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Causeway Bay</t>
+          <t>London (UK entity); group HQ Kópavogur, Iceland</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Hong Kong Island</t>
+          <t>London, England (UK entity); Capital Region, Iceland (group)</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>United Kingdom (registered); Iceland (group HQ)</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Joseph Tsai</t>
+          <t>Lydur Gudmundsson</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Family Principal / Founder</t>
+          <t>Founder / controlling principal (PSC); co-founder of Bakkavor</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -3338,12 +3354,12 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
-          <t>13F-HR filed 2026-05-15; sold ~83% of Blue Owl Capital stake (~$460m) reported 2024-03; joined consortium buying Burgundy vineyards 2024-09; raised ~$1bn first PE fund (Riverside) reported 2026-03-31.</t>
+          <t>UK entity newly incorporated Mar 2026, following the 2026 Bakkavor-Greencore merger. Director Andrea Olsen (Icelandic, CEO/MD of Frigus ehf) appointed at incorporation. Historic Frigus-branded UK entities dissolved (Frigus Ltd dissolved 2022; Frigus Invest Ltd dissolved 2018).</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2026-05-15; 2024-03-03; 2024-09-19; 2026-03-31</t>
+          <t>2026-03-02 (UK incorporation); 2026 (Bakkavor/Greencore merger)</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3353,19 +3369,19 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Some sources describe Blue Pool as a 'multi-family' vehicle co-backed by former Alibaba executives (and occasionally link Jack Ma); primary characterization is Joe Tsai's family office. Website confirmed to be minimal/uninformative per Crain Currency; bluepoolcapital.com domain asserted from press but not independently fetched.</t>
+          <t>'Strong' proof applies to Frigus as a family office group (clear self-description + well-documented Gudmundsson/Bakkavor lineage); the specific UK entity 17062903 is brand-new (Mar 2026) with no filed accounts yet, so UK-level operations are unproven. Lydur Gudmundsson's nationality is shown as British on Companies House though he is the Icelandic Bakkavor co-founder. Switchboard/generic mailboxes belong to the Iceland/Luxembourg offices, not a UK-specific contact.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SFO-mousse-partners-wertheimer</t>
+          <t>SFO-dfo-management-dell</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mousse Partners (Wertheimer Family Office)</t>
+          <t>DFO Management (Dell Family Office)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3375,32 +3391,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Wertheimer family (Alain and Gerard Wertheimer, owners of Chanel)</t>
+          <t>Dell family (Michael Dell, founder/CEO of Dell Technologies)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://moussepartners.com/</t>
+          <t>https://www.dellfamilyoffice.com/</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/moussepartners</t>
+          <t>https://www.linkedin.com/company/dfo-management</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Investment firm serving as the family office of the Wertheimer family. Manages a global diversified portfolio across public equities, fixed income, private equity, venture and real estate, with investment operations in New York and Asia (Beijing, Hong Kong).</t>
+          <t>Private investment firm managing the assets of Michael Dell and family across public equities, private equity, real estate and other asset classes. Originally MSD Capital (1998); the multi-client business became BDT &amp; MSD Partners while the family's captive vehicle was rebranded DFO Management at end of 2022.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Global multi-asset diversified investing with a notable consumer/brands tilt.</t>
+          <t>Multi-asset-class permanent capital: public equities, private equity/credit, real estate, opportunistic direct investments.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Diversified; consumer, luxury/brands, technology, real estate</t>
+          <t>Diversified (consumer, real estate, financials, industrials)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -3421,12 +3437,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Charles Heilbronn</t>
+          <t>Michael Dell</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Founder / Chairman</t>
+          <t>Founder / Family Principal</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -3439,12 +3455,12 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
-          <t>Bloomberg feature (2024-2025) reporting the office reshaping its consumer/public-equity bets.</t>
+          <t>13F-HR filed 2026-05-15 (period ending 2026-03-31) disclosing U.S. equity holdings; rebrand from MSD Capital to DFO Management completed end of 2022.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2024/2025 (Bloomberg feature)</t>
+          <t>2026-05-15; 2022-12</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3454,19 +3470,19 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Does not appear as a 13F filer under 'Mousse Partners' (EDGAR full-text search returned 0); investment vehicle is domiciled offshore (Mousse Investments Limited, Bermuda) with a NYC office (9 W. 57th St). AUM figure is the family fortune, not disclosed firm AUM. Firm general phone reported as 212-303-5795 (not an individual principal line).</t>
+          <t>The 13F is filed in the name of the Michael &amp; Susan Dell Foundation with DFO Management as manager; the foundation and the family office are affiliated. AUM not disclosed. Michael Dell is a public figure; no personal LinkedIn tied specifically to DFO confirmed.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SFO-kirkbi-kristiansen</t>
+          <t>SFO-bayshore-global-brin</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KIRKBI (Kirk Kristiansen Family Office)</t>
+          <t>Bayshore Global Management (Brin Family Office)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3476,62 +3492,50 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Kirk Kristiansen family (owners of the LEGO Group)</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>https://www.kirkbi.com/</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/kirkbi</t>
-        </is>
-      </c>
+          <t>Brin family (Sergey Brin, Google co-founder)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Danish family-owned holding and investment company managing the wealth and legacy of the Kirk Kristiansen family. Holds the family's controlling stakes in LEGO Group and Merlin Entertainments and runs a long-term investment portfolio plus a dedicated climate/energy-transition program (KIRKBI Climate). Additional offices in Copenhagen and Baar, Switzerland.</t>
+          <t>Low-profile single-family office managing the wealth of Sergey Brin across public and private markets, real estate and philanthropy. Additional office in Singapore. Reported to have absorbed the Nexus NeuroTech brain-health VC fund in 2026.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Protect and grow family wealth for future generations; long-term core holdings (LEGO, Merlin) plus diversified investments and thematic climate/energy investing.</t>
+          <t>Broad multi-asset allocation with notable venture/science-and-health direct investing.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Toys/entertainment (core), real estate, renewable energy/climate, diversified financial investments</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>~$16 billion (family wealth)</t>
-        </is>
-      </c>
+          <t>Diversified; neuroscience/brain-health, deep tech, real estate</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Billund</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Region of Southern Denmark</t>
+          <t>California</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Soren Thorup Sorensen</t>
+          <t>Sergey Brin</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Family Principal</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -3544,12 +3548,12 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
-          <t>KIRKBI Climate follow-on investment in Highview Power (Hunterston project) announced November 2025 (second investment after June 2024 Carrington); Adapture Renewables (KIRKBI-majority-owned) acquired 110MW Colorado solar-plus-storage project March 2025; generational handover of board chair to Thomas Kirk Kristiansen May 2023.</t>
+          <t>Absorbed Nexus NeuroTech brain-health VC fund (reported 2026-04-23, Bloomberg).</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2025-11; 2025-03; 2023-05</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3559,19 +3563,19 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>KIRKBI is both the family holding company (owns LEGO) and the family investment office; some may classify it as a holding company rather than a pure family office. AUM figure is the family-wealth press figure, not full portfolio value.</t>
+          <t>No public website confirmed. AUM figures are press estimates. CEO George Pavlov / CIO Marie Young named in Wikipedia and press but not verified against a primary filing.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SFO-tethys-invest-bettencourt</t>
+          <t>SFO-hillspire-schmidt</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tethys / Tethys Invest (Bettencourt Meyers Family Office)</t>
+          <t>Hillspire (Eric Schmidt Family Office)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3581,62 +3585,50 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Bettencourt Meyers family (majority shareholder of L'Oreal; Francoise Bettencourt Meyers)</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>https://tethys.fr/</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/t%C3%A9thys</t>
-        </is>
-      </c>
+          <t>Schmidt family (Eric &amp; Wendy Schmidt; Eric Schmidt is former Google/Alphabet CEO and chairman)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Paris-based single-family office of the Bettencourt Meyers family, holder of the family's ~34% L'Oreal stake. Its subsidiary Tethys Invest (&gt;EUR 3bn capital) makes long-term direct investments deliberately outside L'Oreal's competitive scope, with a healthcare emphasis (Elsan private hospitals, Sebia diagnostics).</t>
+          <t>Single-family office of Eric and Wendy Schmidt focused on deep technology: artificial intelligence, quantum computation, defense tech and biotech. Reported to have invested in 22+ private AI firms since 2019 (including Anthropic, SandboxAQ, Inworld AI) and topped CNBC's inaugural family-office dealmaking ranking for 2025.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Preserve the L'Oreal core holding and deploy dividend income into long-term entrepreneurial direct investments, notably healthcare, that do not compete with L'Oreal.</t>
+          <t>Deep-tech direct investing concentrated in AI, quantum, defense technology and biotech.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Healthcare (hospitals, diagnostics), consumer, technology, diversified</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>&gt; $90 billion (family assets)</t>
-        </is>
-      </c>
+          <t>AI, quantum computing, defense tech, biotech</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Ile-de-France</t>
+          <t>California</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Alexandre Benais</t>
+          <t>Eric Schmidt</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>CEO, Tethys Invest</t>
+          <t>Family Principal / Founder</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -3649,12 +3641,12 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Named new head of family investment firm reported 2023-03-13 (The National); family succession moves (Jean-Victor Meyers to L'Oreal vice-chairman; Alexandre Benais to family L'Oreal board seat) reported 2025-02; co-invested (with Chanel/Wertheimer) in The Row reported 2024-09.</t>
+          <t>Ranked #1 most active U.S. family office for dealmaking in 2025 (15 investments, mostly AI) per CNBC 2026-02-12; disclosed 22 private AI startup investments since 2019 (CNBC 2025-01-21).</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2023-03-13; 2025-02-08; 2024-09</t>
+          <t>2026-02-12; 2025-01-21</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3664,19 +3656,19 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>'Tethys' (parent) vs 'Tethys Invest' (investment subsidiary) are distinct entities; leadership names span both. AUM is the family-asset press figure, not a disclosed managed-portfolio AUM.</t>
+          <t>No public website confirmed (hillspire.com not verified). Does not file 13F (EDGAR full-text search returned no 13F-HR). AUM not disclosed. President Ken Goldman named in press, not verified against a primary filing.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SFO-cofra-holding-brenninkmeijer</t>
+          <t>SFO-blue-pool-capital-tsai</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>COFRA Holding (Brenninkmeijer Family Office)</t>
+          <t>Blue Pool Capital (Joe Tsai Family Office)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3686,58 +3678,58 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Brenninkmeijer family (founders/owners of C&amp;A; ~500 family members)</t>
+          <t>Tsai family (Joseph Tsai, Alibaba co-founder and chairman)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.cofraholding.com/</t>
+          <t>https://www.bluepoolcapital.com/</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Zug-based family-owned holding coordinating the Brenninkmeijer family's global operations and ~EUR 35-38bn asset base across retail (C&amp;A), real estate (Redevco), private equity (Bregal Investments) and asset management (Anthos). In 2025 the family announced it would open its portfolio to outside investors, a shift from its historically secretive model.</t>
+          <t>Hong Kong-based investment firm overseeing the Tsai family's wealth across hedge funds, private equity, private credit, venture and sports assets (Brooklyn Nets, LAFC). Raised ~$1bn for its first dedicated PE vehicle (Riverside Fund) reported 2026. Led by CEO Oliver Weisberg (ex-Goldman Sachs, ex-Citadel).</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Long-term stewardship of family capital across operating businesses, real estate, private equity and (increasingly) externally-opened investment platforms.</t>
+          <t>Multi-strategy long-term capital: public markets, PE, private credit, venture, and sports/real assets.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Retail, real estate, private equity, asset management, climate/energy</t>
+          <t>Diversified; technology (SpaceX, Epic Games, ByteDance), consumer/luxury (Golden Goose), sports, Japanese real estate</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>EUR 35-38 billion</t>
+          <t>~$50 billion</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Zug</t>
+          <t>Causeway Bay</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Canton of Zug</t>
+          <t>Hong Kong Island</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Martijn Brenninkmeijer</t>
+          <t>Joseph Tsai</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Chairman of the Board, COFRA Holding AG</t>
+          <t>Family Principal / Founder</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -3750,12 +3742,12 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
-          <t>Announced opening of ~EUR 38bn portfolio to external investors (April 2025); Florian Brenninkmeyer appointed CFO effective 1 Jan 2025; Redevco closed landmark GBP 47.5m real-estate-debt loan (April 2025).</t>
+          <t>13F-HR filed 2026-05-15; sold ~83% of Blue Owl Capital stake (~$460m) reported 2024-03; joined consortium buying Burgundy vineyards 2024-09; raised ~$1bn first PE fund (Riverside) reported 2026-03-31.</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2025-04; 2025-01-01; 2025-04</t>
+          <t>2026-05-15; 2024-03-03; 2024-09-19; 2026-03-31</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3765,19 +3757,19 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>COFRA is primarily a family holding company; its asset-management arm Anthos is opening to third-party capital (2025), which blurs the pure single-family-office boundary. Classified SFO at the holding level but noted as trending toward external capital.</t>
+          <t>Some sources describe Blue Pool as a 'multi-family' vehicle co-backed by former Alibaba executives (and occasionally link Jack Ma); primary characterization is Joe Tsai's family office. Website confirmed to be minimal/uninformative per Crain Currency; bluepoolcapital.com domain asserted from press but not independently fetched.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SFO-athos-strungmann</t>
+          <t>SFO-mousse-partners-wertheimer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Athos (Strungmann Family Office)</t>
+          <t>Mousse Partners (Wertheimer Family Office)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3787,50 +3779,58 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Strungmann family (Andreas and Thomas Strungmann, founders of Hexal)</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
+          <t>Wertheimer family (Alain and Gerard Wertheimer, owners of Chanel)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://moussepartners.com/</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/moussepartners</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Munich-based single-family office of the Strungmann twins, focused heavily on biotech and life sciences. Anchored and remains largest shareholder of BioNTech (~43.5%) and holds stakes in Formycon and Immatics; actively recycles BioNTech proceeds into new European biotech ventures.</t>
+          <t>Investment firm serving as the family office of the Wertheimer family. Manages a global diversified portfolio across public equities, fixed income, private equity, venture and real estate, with investment operations in New York and Asia (Beijing, Hong Kong).</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Long-horizon anchor investing in biotech and life sciences, recycling returns from BioNTech into the next generation of European biotech.</t>
+          <t>Global multi-asset diversified investing with a notable consumer/brands tilt.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Biotech, life sciences, healthcare technology</t>
+          <t>Diversified; consumer, luxury/brands, technology, real estate</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Bavaria</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Andreas Strungmann</t>
+          <t>Charles Heilbronn</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Family Principal / Co-Founder</t>
+          <t>Founder / Chairman</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -3843,12 +3843,12 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
-          <t>Participated in AAVantgarde Bio's $141m Series B (Nov 2025); AMSilk EUR 52m round (Sep 2025); Antheia funding ($56m Jun 2025, $24m Jan 2026); admin services of Athos Service acquired by Bolder Group (May 2024).</t>
+          <t>Bloomberg feature (2024-2025) reporting the office reshaping its consumer/public-equity bets.</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2025-11; 2025-09; 2025-06; 2026-01; 2024-05</t>
+          <t>2024/2025 (Bloomberg feature)</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3858,19 +3858,19 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>No public website confirmed. 'Athos Service GmbH' is the services entity; the investing vehicle is often cited as 'Athos KG'. Investment-round dates sourced from family-office trade press rather than primary filings. AUM not disclosed.</t>
+          <t>Does not appear as a 13F filer under 'Mousse Partners' (EDGAR full-text search returned 0); investment vehicle is domiciled offshore (Mousse Investments Limited, Bermuda) with a NYC office (9 W. 57th St). AUM figure is the family fortune, not disclosed firm AUM. Firm general phone reported as 212-303-5795 (not an individual principal line).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SFO-premji-invest</t>
+          <t>SFO-kirkbi-kristiansen</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Premji Invest (Azim Premji Family Office)</t>
+          <t>KIRKBI (Kirk Kristiansen Family Office)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3880,62 +3880,62 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Premji family (Azim Premji, founder of Wipro)</t>
+          <t>Kirk Kristiansen family (owners of the LEGO Group)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.premjiinvest.com/</t>
+          <t>https://www.kirkbi.com/</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/premjiinvest</t>
+          <t>https://www.linkedin.com/company/kirkbi</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bengaluru-based family office and investment firm managing the wealth of Azim Premji and family (and closely tied to the Azim Premji Foundation endowment). Invests across public equities, private equity and venture, backing technology, financial services, consumer, healthcare and industrials; crossed $10bn in managed assets.</t>
+          <t>Danish family-owned holding and investment company managing the wealth and legacy of the Kirk Kristiansen family. Holds the family's controlling stakes in LEGO Group and Merlin Entertainments and runs a long-term investment portfolio plus a dedicated climate/energy-transition program (KIRKBI Climate). Additional offices in Copenhagen and Baar, Switzerland.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Long-horizon growth investing across public and private markets in emerging/disruptive technology and consumer/financial sectors.</t>
+          <t>Protect and grow family wealth for future generations; long-term core holdings (LEGO, Merlin) plus diversified investments and thematic climate/energy investing.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Technology, financial services, consumer, healthcare, industrials</t>
+          <t>Toys/entertainment (core), real estate, renewable energy/climate, diversified financial investments</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>&gt; $10 billion</t>
+          <t>~$16 billion (family wealth)</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Billund</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Region of Southern Denmark</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>T.K. Kurien</t>
+          <t>Soren Thorup Sorensen</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>CEO &amp; Managing Partner</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -3948,12 +3948,12 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
-          <t>Acquisition of Anand Chemiceutics reported 2025-11-13; participated in Runway Series E (with General Atlantic, Nvidia) 2026-02-10; 19 funding rounds / 2 acquisitions in trailing 12 months (per Tracxn, Feb 2026).</t>
+          <t>KIRKBI Climate follow-on investment in Highview Power (Hunterston project) announced November 2025 (second investment after June 2024 Carrington); Adapture Renewables (KIRKBI-majority-owned) acquired 110MW Colorado solar-plus-storage project March 2025; generational handover of board chair to Thomas Kirk Kristiansen May 2023.</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2025-11-13; 2026-02-10</t>
+          <t>2025-11; 2025-03; 2023-05</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3963,19 +3963,19 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>Premji Invest also manages the Azim Premji Foundation's endowment, so it straddles family-office and foundation-endowment functions; consistently described as a family office, hence corroborated rather than strong-single-family-only.</t>
+          <t>KIRKBI is both the family holding company (owns LEGO) and the family investment office; some may classify it as a holding company rather than a pure family office. AUM figure is the family-wealth press figure, not full portfolio value.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SFO-catamaran-ventures-murthy</t>
+          <t>SFO-tethys-invest-bettencourt</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Catamaran Ventures (N.R. Narayana Murthy Family Office)</t>
+          <t>Tethys / Tethys Invest (Bettencourt Meyers Family Office)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3985,58 +3985,62 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Murthy family (N.R. Narayana Murthy, co-founder of Infosys)</t>
+          <t>Bettencourt Meyers family (majority shareholder of L'Oreal; Francoise Bettencourt Meyers)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://catamaran.in/</t>
+          <t>https://tethys.fr/</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/catamaran-ventures</t>
+          <t>https://www.linkedin.com/company/t%C3%A9thys</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bengaluru-based single-family office of Infosys co-founder N.R. Narayana Murthy, investing permanent family capital (no external LPs). Focused on growth capital, notably Indian manufacturing and deep tech; has recently turned more cautious on Indian startup valuations.</t>
+          <t>Paris-based single-family office of the Bettencourt Meyers family, holder of the family's ~34% L'Oreal stake. Its subsidiary Tethys Invest (&gt;EUR 3bn capital) makes long-term direct investments deliberately outside L'Oreal's competitive scope, with a healthcare emphasis (Elsan private hospitals, Sebia diagnostics).</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Permanent-capital growth investing, with emphasis on Indian manufacturing and deep-tech, valuation-disciplined.</t>
+          <t>Preserve the L'Oreal core holding and deploy dividend income into long-term entrepreneurial direct investments, notably healthcare, that do not compete with L'Oreal.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Manufacturing, deep tech, consumer, technology</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>Healthcare (hospitals, diagnostics), consumer, technology, diversified</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>&gt; $90 billion (family assets)</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Ile-de-France</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>France</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>N.R. Narayana Murthy</t>
+          <t>Alexandre Benais</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Founder / Chairman Emeritus (Family Principal)</t>
+          <t>CEO, Tethys Invest</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
@@ -4049,12 +4053,12 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
-          <t>Bloomberg (2025-08-26) reporting Catamaran growing cautious on Indian startup valuations; recent deep-tech stake and follow-on investments (Akshayakalpa first-time, Innoviti follow-on) in 2025.</t>
+          <t>Named new head of family investment firm reported 2023-03-13 (The National); family succession moves (Jean-Victor Meyers to L'Oreal vice-chairman; Alexandre Benais to family L'Oreal board seat) reported 2025-02; co-invested (with Chanel/Wertheimer) in The Row reported 2024-09.</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2025-08-26; 2025</t>
+          <t>2023-03-13; 2025-02-08; 2024-09</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4064,19 +4068,19 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Investment pace slowed in 2025 (approximately one new investment) per Tracxn; AUM not disclosed.</t>
+          <t>'Tethys' (parent) vs 'Tethys Invest' (investment subsidiary) are distinct entities; leadership names span both. AUM is the family-asset press figure, not a disclosed managed-portfolio AUM.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UKCH-10876208</t>
+          <t>SFO-cofra-holding-brenninkmeijer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sha Family Office Ltd</t>
+          <t>COFRA Holding (Brenninkmeijer Family Office)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4086,32 +4090,60 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sha family (controlling PSCs: Mr Sharnpreet Singh Buttar)</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
+          <t>Brenninkmeijer family (founders/owners of C&amp;A; ~500 family members)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://www.cofraholding.com/</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Zug-based family-owned holding coordinating the Brenninkmeijer family's global operations and ~EUR 35-38bn asset base across retail (C&amp;A), real estate (Redevco), private equity (Bregal Investments) and asset management (Anthos). In 2025 the family announced it would open its portfolio to outside investors, a shift from its historically secretive model.</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Long-term stewardship of family capital across operating businesses, real estate, private equity and (increasingly) externally-opened investment platforms.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>64205 - Activities of financial services holding companies; 64209 - Activities of other holding companies not elsewhere classified</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+          <t>Retail, real estate, private equity, asset management, climate/energy</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>EUR 35-38 billion</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>SIC codes - 64205</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+          <t>Zug</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Canton of Zug</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Martijn Brenninkmeijer</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Chairman of the Board, COFRA Holding AG</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -4120,28 +4152,36 @@
         </is>
       </c>
       <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Announced opening of ~EUR 38bn portfolio to external investors (April 2025); Florian Brenninkmeyer appointed CFO effective 1 Jan 2025; Redevco closed landmark GBP 47.5m real-estate-debt loan (April 2025).</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>2025-04; 2025-01-01; 2025-04</t>
+        </is>
+      </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>UK filing SIC: fo-relevant-sic. Active officers: BUTTAR, Sharnpreet Singh () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
+          <t>COFRA is primarily a family holding company; its asset-management arm Anthos is opening to third-party capital (2025), which blurs the pure single-family-office boundary. Classified SFO at the holding level but noted as trending toward external capital.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>UKCH-15240886</t>
+          <t>SFO-athos-strungmann</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Freedman Family Office</t>
+          <t>Athos (Strungmann Family Office)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4151,32 +4191,52 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Freedman family (controlling PSCs: Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman)</t>
+          <t>Strungmann family (Andreas and Thomas Strungmann, founders of Hexal)</t>
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Munich-based single-family office of the Strungmann twins, focused heavily on biotech and life sciences. Anchored and remains largest shareholder of BioNTech (~43.5%) and holds stakes in Formycon and Immatics; actively recycles BioNTech proceeds into new European biotech ventures.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Long-horizon anchor investing in biotech and life sciences, recycling returns from BioNTech into the next generation of European biotech.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>64301 - Activities of investment trusts</t>
+          <t>Biotech, life sciences, healthcare technology</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>London</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
+          <t>Munich</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Bavaria</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Andreas Strungmann</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Family Principal / Co-Founder</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -4185,28 +4245,36 @@
         </is>
       </c>
       <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Participated in AAVantgarde Bio's $141m Series B (Nov 2025); AMSilk EUR 52m round (Sep 2025); Antheia funding ($56m Jun 2025, $24m Jan 2026); admin services of Athos Service acquired by Bolder Group (May 2024).</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>2025-11; 2025-09; 2025-06; 2026-01; 2024-05</t>
+        </is>
+      </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>UK filing SIC: fo-relevant-sic. Active officers: FREEDMAN, Elaine Wilson (), FREEDMAN, Laura-Leigh (), ZIMMERMAN, Samantha Jade () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
+          <t>No public website confirmed. 'Athos Service GmbH' is the services entity; the investing vehicle is often cited as 'Athos KG'. Investment-round dates sourced from family-office trade press rather than primary filings. AUM not disclosed.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>UKCH-11031775</t>
+          <t>SFO-premji-invest</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ralph Family Office Limited</t>
+          <t>Premji Invest (Azim Premji Family Office)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4216,32 +4284,64 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ralph family (controlling PSCs: Melanie Lynette Ralph; Mr Jan De Ridder Ralph)</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+          <t>Premji family (Azim Premji, founder of Wipro)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://www.premjiinvest.com/</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/premjiinvest</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Bengaluru-based family office and investment firm managing the wealth of Azim Premji and family (and closely tied to the Azim Premji Foundation endowment). Invests across public equities, private equity and venture, backing technology, financial services, consumer, healthcare and industrials; crossed $10bn in managed assets.</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Long-horizon growth investing across public and private markets in emerging/disruptive technology and consumer/financial sectors.</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>64301 - Activities of investment trusts; 68209 - Other letting and operating of own or leased real estate</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
+          <t>Technology, financial services, consumer, healthcare, industrials</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>&gt; $10 billion</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>SIC codes - 64301</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>T.K. Kurien</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>CEO &amp; Managing Partner</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
@@ -4250,16 +4350,1273 @@
         </is>
       </c>
       <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Acquisition of Anand Chemiceutics reported 2025-11-13; participated in Runway Series E (with General Atlantic, Nvidia) 2026-02-10; 19 funding rounds / 2 acquisitions in trailing 12 months (per Tracxn, Feb 2026).</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>2025-11-13; 2026-02-10</t>
+        </is>
+      </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>C+</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>UK filing SIC: fo-relevant-sic. Active officers: RALPH, Jan De Ridder (), RALPH, Melanie Lynette (), BETHELL, Karen (), BETHELL, Stuart (), YOULL, Gavin William () SFO corroborated via PSC surname match + investment SIC; principal and contact pending research pass.</t>
+          <t>Premji Invest also manages the Azim Premji Foundation's endowment, so it straddles family-office and foundation-endowment functions; consistently described as a family office, hence corroborated rather than strong-single-family-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SFO-catamaran-ventures-murthy</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Catamaran Ventures (N.R. Narayana Murthy Family Office)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Murthy family (N.R. Narayana Murthy, co-founder of Infosys)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://catamaran.in/</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/catamaran-ventures</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Bengaluru-based single-family office of Infosys co-founder N.R. Narayana Murthy, investing permanent family capital (no external LPs). Focused on growth capital, notably Indian manufacturing and deep tech; has recently turned more cautious on Indian startup valuations.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Permanent-capital growth investing, with emphasis on Indian manufacturing and deep-tech, valuation-disciplined.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Manufacturing, deep tech, consumer, technology</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Karnataka</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>N.R. Narayana Murthy</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Founder / Chairman Emeritus (Family Principal)</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Bloomberg (2025-08-26) reporting Catamaran growing cautious on Indian startup valuations; recent deep-tech stake and follow-on investments (Akshayakalpa first-time, Innoviti follow-on) in 2025.</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>2025-08-26; 2025</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Investment pace slowed in 2025 (approximately one new investment) per Tracxn; AUM not disclosed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>APAC-weybourne-holdings-dyson</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Weybourne (James Dyson Family Office)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Dyson family — Sir James Dyson (founder of Dyson Ltd) and family</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Single-family office managing the wealth of Sir James Dyson, founder of the Dyson appliance/engineering group. Founded 2013; a Singapore holding company (Weybourne Holdings Pte Ltd) now sits above the group, alongside a London office and a Singapore-based insurance unit. Investments span English farmland (the Dyson family is among England's largest private landowners), commercial and residential real estate, technology ventures and public markets.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Long-horizon preservation and growth of the Dyson family fortune across agricultural land, real estate, technology ventures and public markets.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Agricultural land/farmland; Real estate (commercial and residential); Technology ventures; Public equities</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>~USD17-21 billion (family fortune under management; not an officially disclosed AUM figure)</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>James Dyson</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Founder and family principal (Weybourne CEO since Feb 2025: Martin Bowen)</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Feb 2025: Martin Bowen (ex-Dyson Group PLC legal veteran) appointed Weybourne CEO, succeeding James Bucknall. 2025: transferred at least GBP624m (~USD834m) from a major UK entity to the Singapore holding company, reducing the UK unit's share capital to GBP1. Office reported at 70+ employees across London and Singapore.</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>2025-02; 2025</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Group is split between London and Singapore; this record treats the Singapore holding company (Weybourne Holdings Pte Ltd) as HQ per 2025 restructuring reporting. weybourne.com resolves to a parked GoDaddy page, so no confirmed public website/domain. AUM is an estimated family fortune, not a disclosed FO figure. Principal LinkedIn not verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>APAC-dalio-family-office-singapore</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Dalio Family Office (Ray Dalio) — Singapore</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Dalio family — Ray Dalio (founder of Bridgewater Associates) and family</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>The Singapore office of Ray Dalio's global single-family office. The Dalio Family Office invests across private equity, venture capital, real estate and credit and runs the family's philanthropy in Asia. Singapore was chosen as the Asia base given Dalio's long-standing ties to Singapore and China; the DFO also operates in Abu Dhabi. Globally the DFO is led by CEO Janine Racanelli (ex-JPMorgan) and COO Tom Waller; the Singapore office has been associated with Managing Director Tan Mae Shen.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Global multi-asset investing (PE, VC, real estate, credit) with a Singapore hub for Asian investments and philanthropy.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Private equity; Venture capital; Real estate; Credit</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Ray Dalio</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Founder and family principal (global DFO CEO: Janine Racanelli; Singapore MD: Tan Mae Shen)</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>2020: Dalio Family Office opened in Singapore; Dalio donated USD25m to Singapore's Wealth Management Institute. 2021: Tan Mae Shen joined as Singapore MD; Dalio bought two Club Street shophouses for ~SGD18.9m. Global CIO Mark Baumgartner departed Aug 2024.</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>2020; 2021; 2024-08</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>The Dalio Family Office's global headquarters is in Westport, Connecticut (USA), with offices in New York, Singapore and Abu Dhabi; this record covers the Singapore office as a Singapore-hubbed APAC operation, not the global HQ. No AUM or public website confirmed. Principal LinkedIn not verified.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>APAC-sunrise-capital-shu-ping</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sunrise Capital Management (Shu Ping / Haidilao Family Office)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Shu Ping — co-founder of Haidilao hotpot chain; spouse Zhang Yong (Haidilao co-founder), both naturalised Singapore citizens</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Single-family office established in Singapore (Shu Ping appointed sole shareholder and director in July 2019; publicly reported March 2020) to manage the wealth of Haidilao co-founder Shu Ping, reported at around USD7.7bn at the time. Shu Ping holds her Haidilao stake via the Rose Trust; her husband and Haidilao co-founder Zhang Yong holds his via the Apple Trust.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Preservation and diversification of the Shu Ping / Haidilao family fortune from Singapore.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Diversified/multi-asset (not publicly detailed)</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>~USD7.7 billion (reported family wealth at establishment, 2020)</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Shu Ping</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Founder, sole shareholder and director</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jul 2019: Shu Ping appointed sole shareholder/director of Sunrise Capital Management. Mar 2020: Bloomberg/SCMP/Caixin report the Singapore family office managing ~USD7.7bn. Couple purchased a ~SGD27m home near Singapore Botanic Gardens.</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>2019-07; 2020-03</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Entity legal-name suffix (Pte. Ltd.) inferred from Singapore incorporation norms; exact ACRA registration not independently verified in sources reviewed. AUM is a launch-era wealth estimate. Principal LinkedIn/email not available (private SFO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>APAC-tsao-family-office-tpc</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Tsao Family Office (IMC Group / TPC — Chavalit Tsao)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Tsao family — founders/controllers of IMC Group (Pan Asia maritime and industrial group); led by fourth-generation steward Chavalit Frederick Tsao</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://tsaopaochee.com/</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>The single-family office / strategic investment arm of Singapore's Tsao family, whose IMC Group traces its roots to 1906 and spans maritime, industrial and diversified businesses across 15+ countries. Organised today under TPC (Tsao Pao Chee) alongside the OCTAVE well-being ecosystem, the office pursues impact and ESG investing across environment, healthcare and education, reflecting Chavalit Tsao's 'well-being economy' philosophy.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Purpose-led, long-term impact/ESG investing (environment, healthcare, education) integrated with the family's maritime and industrial businesses under a 'well-being economy' model.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Impact/ESG; Healthcare; Education; Environment/sustainability; Maritime and industrial</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Chavalit Frederick Tsao</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Chairman, IMC Pan Asia Alliance Group / founder of OCTAVE; fourth-generation family steward</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>OCTAVE Well-being Economy Fund / OCTAVE investment platform active; TPC restructuring of the family enterprise into an integrated 'well-being business ecosystem' (IMC Industrial, OCTAVE and non-profits).</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>The family's structure spans several brands (TPC/Tsao Pao Chee, IMC Industrial, OCTAVE, Octave Capital); the precise legal entity of the family office is not cleanly disclosed. Dated recent signals were not pinned down in sources reviewed. No AUM, principal LinkedIn or individual email confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>APAC-wee-investments-uob</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Wee Investments (Wee family / UOB family office)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Wee family — Singapore's leading banking dynasty; founder Wee Cho Yaw (UOB; d. Feb 2024); next generation Wee Ee Cheong, Wee Ee Chao, Wee Ee Lim</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>The Wee family's single-family office, associated with the founders and controlling shareholders of United Overseas Bank (UOB), Singapore's third-largest bank. The family's wealth derives from stakes in UOB, property developers UOL Group and Kheng Leong Company, and Haw Par (maker of Tiger Balm). Allocations reportedly span public equities, direct real estate and private equity via SPVs.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Long-term stewardship of a banking-and-property dynasty's wealth: concentrated strategic stakes (UOB, UOL, Haw Par) plus direct real estate and private equity.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Banking/financial services; Real estate; Public equities; Private equity</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Wee Ee Cheong</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Family principal (Deputy Chairman &amp; CEO of UOB); son of founder Wee Cho Yaw</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>May 2024: family-controlled UOL Group made a top bid of ~SGD595m for a prime Singapore site (Forbes). Feb 2024: founder Wee Cho Yaw died, focusing attention on the next-generation family principals.</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2024-02; 2024-05</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Wee Investments Pte Ltd is private; several family vehicles exist (Wee Investments, Kheng Leong Company) with overlapping ownership, and the boundary between the 'family office' and family holding companies is not cleanly disclosed. Some structural detail relies on secondary FO directories (Altss/PipelineRoad) rather than primary filings. Principal LinkedIn/email not available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>APAC-ee-capital-saverin</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>EE Capital (Eduardo Saverin family office)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Saverin family — Eduardo Saverin (Facebook co-founder, Singapore citizen since 2011) and wife Elaine Andriejanssen</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Single-family office in Singapore managing the wealth of Facebook co-founder Eduardo Saverin, who relocated to Singapore in 2009 and became a citizen in 2011 and is repeatedly ranked Singapore's richest person by Forbes. EE Capital reportedly allocates proprietary capital across private equity, venture capital, hedge funds and public equities. Saverin separately co-founded the venture firm B Capital (a distinct, California-headquartered VC manager).</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Diversified proprietary investing of the Saverin family fortune across private equity, venture capital, hedge funds and public markets.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Private equity; Venture capital; Hedge funds; Public equities</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Eduardo Saverin</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Family principal (EE Capital Executive Chairman: Elaine Andriejanssen)</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Sep 2023 / 2024: Saverin ranked Singapore's richest person by Forbes (net worth reported &gt;USD30bn). Sep 2024: Eduardo and Elaine Saverin donated USD15.5m to Singapore American School.</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>2023-09; 2024-09</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>EE Capital is a private SFO; detail relies on Preqin/Citywire/Altss rather than primary filings, hence 'corroborated' not 'strong'. Do not conflate with B Capital, Saverin's separate VC firm headquartered in California. No website, principal LinkedIn or individual email confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>APAC-wuthelam-holdings-goh</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Wuthelam Holdings (Goh family office / Nippon Paint)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Goh family — founder Goh Cheng Liang (Nippon Paint fortune; d. Aug 2025); son and chairman Goh Hup Jin</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>The Goh family's private investment holding company and family office, founded by the late paint tycoon Goh Cheng Liang (long ranked Singapore's richest person) in 1974. Wuthelam Holdings consolidates the family's wealth and controls a ~58% stake in Tokyo-listed Nippon Paint Holdings, Asia's largest paint maker, built up after Wuthelam raised its stake from 39% to 58.7% in August 2020 in exchange for its Southeast Asian JV interests.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Long-term concentrated ownership of the family's core industrial asset (Nippon Paint) plus diversified private wealth management across generations.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Paints/chemicals (Nippon Paint); Public equities; Diversified private investments</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Goh Hup Jin</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Chairman of Nippon Paint Holdings; Wuthelam group executive director; family principal (son of founder)</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dec 2024: Wuthelam Holdings transferred Nippon Paint stakes to the founder's grandchildren, making six of them billionaires (each &gt;USD1bn). Aug 2025: founder Goh Cheng Liang died aged 98.</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>2024-12; 2025-08</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Wuthelam Holdings functions as both the family's operating holding company (Nippon Paint control) and its de facto family office; the two roles are not separately disclosed. No public website/domain, AUM, principal LinkedIn or individual email confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SFO-cascade-investment-gates</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cascade Investment (Bill Gates Family Office)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Gates family (Bill Gates, co-founder of Microsoft)</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Private investment firm managing the personal wealth of Bill Gates and, through the same manager Michael Larson, the Bill &amp; Melinda Gates Foundation Trust's investable assets. Holds large, often illiquid long-term stakes in mature businesses (Berkshire Hathaway, Canadian National Railway, Republic Services, Four Seasons, Deere) alongside a diversified public-equity portfolio.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Long-horizon, low-turnover allocation to high-quality mature businesses and diversified public equities; capital preservation and growth for the Gates family and foundation trust.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Diversified; industrials/rails, waste services, hospitality, financials, agriculture equipment</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Kirkland</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Bill Gates</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Family Principal / Beneficial Owner</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Q2 2025 13F-HR filed 2025-08-14 disclosing a significantly increased Berkshire Hathaway (BRK.B) stake (adding ~6.95m shares to ~24.12m); continued long-term holdings in Canadian National Railway, Republic Services, Deere and Four Seasons.</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>ENTITY CONFUSION WARNING: 'Cascade Investment, L.L.C.' (Bill Gates, CIK 0001052192, Kirkland WA) is distinct from 'Cascade Investment Advisors, Inc.' (a small Oregon RIA, CIK 0000919447) and 'Cascade Investment Group, Inc.' — do not merge. AUM not disclosed. Michael Larson is a private figure; no personal email/LinkedIn confirmed. No public website.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SFO-willett-advisors-bloomberg</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Willett Advisors (Michael Bloomberg Family Office)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Bloomberg family (Michael R. Bloomberg, founder of Bloomberg L.P.)</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>New York-based investment firm serving as Michael Bloomberg's family office, managing his personal wealth and the assets of Bloomberg Philanthropies across public markets, hedge funds, private equity and credit, real assets and direct investments. Chaired and led by former U.S. auto-industry adviser and Quadrangle co-founder Steven Rattner.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Multi-asset, alternatives-heavy allocation (private equity/credit, hedge funds, real assets) for combined personal and philanthropic capital.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Diversified; private equity/credit, hedge funds, real assets, public equities</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>~$25 billion</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Michael R. Bloomberg</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Family Principal / Beneficial Owner</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Ongoing management of Bloomberg's personal + Bloomberg Philanthropies assets under Chairman/CEO Steven Rattner (per Wikipedia/trade press, current).</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>2010 (founded); leadership current per 2026 profiles</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>SEC 13F filings (CIK 0001509379) CEASED after Q3 2014 (last filing 2014-11-04); Willett is NOT a current 13F filer because the bulk of assets are private/alternative. No public website confirmed. AUM is a press figure. Because assets include Bloomberg Philanthropies capital, it straddles family-office and philanthropic-endowment functions, but is consistently characterized as Bloomberg's family office.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SFO-soros-fund-management</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Soros Fund Management (Soros Family Office)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Soros family (George Soros, founder; Alexander 'Alex' Soros, chairman)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://www.soros.com/</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/soros</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>New York-based family office managing the Soros family's wealth and serving as the permanent capital base for the Open Society Foundations. Runs a large, actively traded multi-asset book (public equities, index put options, convertible notes, credit and private investments); recent 13F-reported U.S. equity portfolio ~$9bn.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Actively managed global macro / multi-asset investing, including sizeable hedging (index puts) and credit, supporting long-term family and Open Society capital.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Diversified; technology (Amazon, Nvidia, Alphabet, Apple, TSMC), consumer/media, credit, options/hedging</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>~$28 billion</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>George Soros</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Founder / Chairman (Family Principal)</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Q1 2026 13F (as of 2026-03-31) disclosing ~263 positions valued ~$9.12bn (~61% equities, ~20% index put options, ~19% convertibles); top holdings Amazon, Electronic Arts, Nvidia, TSMC, Alphabet, Apple. 2023 generational handover to Alex Soros.</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>2026-03-31 (13F period); 2023 (handover)</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Dawn Fitzpatrick is reported as CEO/CIO running day-to-day investing (not independently verified against a primary filing here). Manages Open Society Foundations capital as well as family wealth, so it straddles family-office and foundation-endowment functions; consistently characterized as the Soros family office. A related smaller entity, Soros Capital Management LLC (CIK), also files 13F — do not merge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SFO-bezos-expeditions</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Bezos Expeditions (Jeff Bezos Family Office)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Bezos family (Jeff Bezos, founder of Amazon)</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://www.bezosexpeditions.com/</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Personal investment and venture vehicle of Jeff Bezos, making early- and growth-stage direct investments across technology, biotech, fintech, cloud and healthcare (historically Google, Uber, Airbnb, Twitter, Workday, Business Insider, NotCo). Distinct from his aerospace company Blue Origin and from Nash Holdings (which owns The Washington Post).</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Founder-led venture and direct investing in disruptive technology and science, long horizon, concentrated conviction bets.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Technology, biotechnology, fintech, cloud computing, healthcare technology</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Mercer Island</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Jeff Bezos</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Family Principal / Founder</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Ongoing venture/direct investing (historically Airbnb, Uber, Twitter, Stack Overflow, Workday, NotCo). Note: recent dated deal specifics not verified against a primary source here.</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>2005 (founded)</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Does not file SEC 13F (a private venture/direct-investment vehicle). Legal-entity structure is opaque; the actual investing entity names (e.g., Zefram LLC) are asserted from trade press and not confirmed against a primary filing here. HQ commonly cited as Mercer Island / Seattle WA. AUM figures in trade press conflate the office with Bezos's net worth. Rated corroborated (not strong) pending a primary/legal-registry confirmation of the exact entity.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SFO-pritzker-organization</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>The Pritzker Organization (Tom Pritzker Family Office)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pritzker family (Tom Pritzker, executive chairman of Hyatt Hotels; descendants of Nicholas J. Pritzker)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://pritzkerorg.com/</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Chicago-based family office / merchant bank managing the assets of Tom Pritzker and the extended Pritzker family. Deploys permanent capital with a long-term 'buy to build' approach across private equity and growth equity; growth-stage positions have included Palantir, SpaceX, Uber, Dataminr, BlueVoyant and Nimble Robotics.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Permanent-capital, long-hold 'buy to build' investing across control private equity and later-stage growth equity (not a buy-to-sell PE fund).</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Diversified; technology/growth equity, industrials, consumer, private equity</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Thomas J. Pritzker</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Chairman &amp; CEO (Family Principal)</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Pritzker family office launched a venture-capital fund (Crain's Chicago Business report); ongoing growth-equity positions incl. Palantir, SpaceX, Uber, Dataminr.</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Reported by Crain's (date not independently confirmed here)</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>The Pritzker family runs SEVERAL distinct vehicles (The Pritzker Organization / Tom Pritzker; Pritzker Group / Tony &amp; J.B. Pritzker; Pritzker Private Capital / PPC; various family foundations) — do not merge them. Does not file 13F. AUM not disclosed. Signals date not verified.</t>
         </is>
       </c>
     </row>
@@ -4274,10 +5631,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P38"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
@@ -5218,176 +6575,144 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEC13F-0001599603</t>
+          <t>UKCH-10957456</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tarbox Family Office, Inc.</t>
+          <t>Old House Family Office Limited</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sec-13f</t>
+          <t>uk-companies-house</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001599603); discovered via fts</t>
+          <t>Companies House 10957456 (Private limited company); inc. 12 September 2017</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001599603&amp;type=13F</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/10957456</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>'The multi-family office ... with just 100+ client families and over $1 billion under management'; fee-only, $5M minimum, serving a select group of wealthy families/individuals. Sources: https://tarbox.com/who-we-are/ ; https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079</t>
+          <t>Controlled by a single family (Lewis). Ceased PSC Mrs Stella Ann Lewis held control 'as a member of a firm' plus 'influence over the trustees of a trust'; active corporate PSC is Old Friend Capital Limited (co. 10950444), a real-estate holding company also controlled by the Lewis family. Sole active director is Christopher David Lewis. No evidence of managing multiple unrelated families, so single-family. Source: https://find-and-update.company-information.service.gov.uk/company/10957456/persons-with-significant-control</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (13F filer) founded 1985 by Laura Tarbox; fee-only financial planning, tax preparation and investment advisory for HNW individuals, charities, businesses, trusts and estates. Sources: https://tarbox.com/history/ ; https://tarbox.com/who-we-are/</t>
+          <t>Named 'Family Office'; SIC 64999 (financial intermediation) + 68100/68320 (real estate). PSC chain resolves to the Lewis family via Old Friend Capital Ltd (real estate, SIC 68100/68209/68310/68320). Principal Chris Lewis is an active property/leisure developer (Old Friend Capital / Moirai Capital Investments) per LinkedIn. Consistent with a family investment/holding vehicle. Sources: https://find-and-update.company-information.service.gov.uk/company/10957456 ; https://find-and-update.company-information.service.gov.uk/company/10950444 ; https://www.linkedin.com/in/chrislewismoirai/</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Firm-stated. https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079 ; https://tarbox.com/who-we-are/</t>
-        </is>
-      </c>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Founder (1985), CEO and principal owner; CFP since 1984 with 40+ years' experience; sets firm vision and strategy and is the lead advisor/decision-maker. https://tarbox.com/team/laura-tarbox/ ; https://tarbox.com/history/</t>
+          <t>Sole active director and, via Old Friend Capital Limited (corporate PSC), the family principal / investment decision-maker. Active real-estate &amp; leisure developer. Not a nominee.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf</t>
-        </is>
-      </c>
+          <t>confirmed</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Published on Laura Tarbox's own public presentation slide (title block reads 'Laura Tarbox, CFP(R) 949.721.2330 Laura@Tarbox.com'). Individual address on the firm's own domain; published, not independently provider-verified. Firm bio page itself shows only a phone and contact form. ZoomInfo listing (l***@tarboxgroup.com) is broker-masked and excluded.</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>https://tarbox.com/team/laura-tarbox/ (listed on Laura Tarbox's bio page; Newport Beach office line) and her presentation https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf</t>
-        </is>
-      </c>
+          <t>No published individual email located. No firm website found for Old House Family Office or Old Friend Capital; searches of Companies House, LinkedIn and web returned no personal published email. Pattern-generation not permitted.</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>https://tarbox.com/history/ ; https://tarbox.com/who-we-are/ ; https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
+          <t>https://find-and-update.company-information.service.gov.uk/company/10957456/officers ; https://find-and-update.company-information.service.gov.uk/company/10957456/persons-with-significant-control</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEC13F-0002056106</t>
+          <t>SFO-grok-ventures-cannon-brookes</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Stenger Family Office, LLC</t>
+          <t>Grok Ventures Pty Ltd</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sec-13f</t>
+          <t>press</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0002056106); discovered via fts</t>
+          <t>Identified via known UHNW individual (Mike Cannon-Brookes, Atlassian co-founder) -&gt; family office. Confirmed as the Cannon-Brookes single-family office by Capital Brief, Startup Daily and family-office trade sources; distinctive recent climate-focus pivot corroborates active investing.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002056106&amp;type=13F</t>
+          <t>https://www.capitalbrief.com/article/mike-cannon-brookes-grok-ventures-leads-the-family-office-charge-into-climate-tech-8360daab-e12e-4d39-8909-f5fd17583168/</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Self-described 'multi-family office'; the Stenger family has served 'over 1,200 families across the United States'. Serves many outside client families. Sources: https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
+          <t>Founded 2016 by Mike Cannon-Brookes (co-founder/co-CEO of Atlassian) and his (then) wife Annie Cannon-Brookes as their single-family office; invests family capital, no external LPs.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEC-registered investment adviser (13F filer); independent fiduciary wealth-management firm offering financial planning, investment management, tax and estate strategies under a family-office model; ~$731M AUM. Sources: https://www.stengerfamilyoffice.com/ </t>
+          <t>Capital Brief and Startup Daily reporting naming Grok Ventures as the Cannon-Brookes family office; altss family-office profile.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>corroborated</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Firm-stated. https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
+          <t>Not disclosed; Grok has been described as backing Australia's first ~A$1bn climate-tech-focused family VC effort (press).</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Founder and CEO / lead financial advisor; prior Senior Vice President financial advisor at Morgan Stanley Wealth Management, and roles at Invesco PowerShares and PwC; the firm's decision-maker and namesake. https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
+          <t>Founder and beneficial owner; sets the office's climate mission. Day-to-day CEO is Tan Kueh (appointed to lead climate investing).</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>https://www.stengerfamilyoffice.com (published mailto/contact page)</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>No individual email published on the firm site; contact is via a Calendly link (calendly.com/nicholasstenger/intro-meeting) rather than a published email address. No broker emails accepted.</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
-        </is>
-      </c>
+          <t>unconfirmed</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>https://www.stengerfamilyoffice.com/ ; https://www.stengerfamilyoffice.com/financialadvisornaperville ; https://podcasts.apple.com/us/podcast/the-nick-stenger-show/id1678810370</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
+          <t>https://www.capitalbrief.com/article/mike-cannon-brookes-grok-ventures-leads-the-family-office-charge-into-climate-tech-8360daab-e12e-4d39-8909-f5fd17583168/</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEC13F-0001908612</t>
+          <t>SEC13F-0001599603</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Allie Family Office LLC</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5397,22 +6722,22 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001908612); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001599603); discovered via fts</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001908612&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001599603&amp;type=13F</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Self-described independent multi-family office with offices in Miami and Lima serving multiple Latin American (predominantly Peruvian) HNW families; press reports ~23 client families averaging ~$50M each. Clearly multi-client, not single-family. Sources: https://allie-intl.com/en/home/ ; https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami ; https://fintrx.com/firms/firm/allie-family-office-llc-307144</t>
+          <t>'The multi-family office ... with just 100+ client families and over $1 billion under management'; fee-only, $5M minimum, serving a select group of wealthy families/individuals. Sources: https://tarbox.com/who-we-are/ ; https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (CRD 307144, 13F filer) established September 2019; provides discretionary and limited-discretionary investment management, estate planning and cross-border tax coordination as an independent multi-family office. Sources: https://adviserinfo.sec.gov/firm/summary/307144 ; https://reports.adviserinfo.sec.gov/crs/crs_307144.pdf</t>
+          <t>SEC-registered investment adviser (13F filer) founded 1985 by Laura Tarbox; fee-only financial planning, tax preparation and investment advisory for HNW individuals, charities, businesses, trusts and estates. Sources: https://tarbox.com/history/ ; https://tarbox.com/who-we-are/</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -5422,46 +6747,54 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Form ADV / adviser aggregators and press. https://fintrx.com/firms/firm/allie-family-office-llc-307144 ; https://aum13f.com/firm/allie-family-office-llc ; https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami</t>
+          <t>Firm-stated. https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079 ; https://tarbox.com/who-we-are/</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Bruno Ghio founded Allié in 2019, owns 100% of the firm and is Founder &amp; CEO — the lead decision-maker — after serving as Managing Director / Regional Head of the Family Office at BCP and a senior private banker at JPMorgan. Jose Larrabure (CFA, CESGA) leads investment management. https://pe.linkedin.com/in/bruno-ghio-1264b616b ; https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami</t>
+          <t>Founder (1985), CEO and principal owner; CFP since 1984 with 40+ years' experience; sets firm vision and strategy and is the lead advisor/decision-maker. https://tarbox.com/team/laura-tarbox/ ; https://tarbox.com/history/</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Firm publishes only a generic mailbox (info@allie-intl.com); the Team page lists members without individual emails or direct lines. RocketReach/aggregator listings for Bruno Ghio are broker-sourced and excluded per rules.</t>
+          <t>Published on Laura Tarbox's own public presentation slide (title block reads 'Laura Tarbox, CFP(R) 949.721.2330 Laura@Tarbox.com'). Individual address on the firm's own domain; published, not independently provider-verified. Firm bio page itself shows only a phone and contact form. ZoomInfo listing (l***@tarboxgroup.com) is broker-masked and excluded.</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1908612/000190861226000002/primary_doc.xml</t>
+          <t>https://tarbox.com/team/laura-tarbox/ (listed on Laura Tarbox's bio page; Newport Beach office line) and her presentation https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami ; https://www.leadersleague.com/en/news/allie-family-office-adds-partner-in-peru ; https://www.bloomberg.com/news/articles/2024-03-18/family-office-head-sees-more-peruvian-clients-settling-in-miami</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
+          <t>https://tarbox.com/history/ ; https://tarbox.com/who-we-are/ ; https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEC13F-0001511137</t>
+          <t>SEC13F-0002056106</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pathstone Family Office LLC</t>
+          <t>Stenger Family Office, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -5471,71 +6804,79 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001511137); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0002056106); discovered via fts</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001511137&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002056106&amp;type=13F</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Large partner-owned multi-family office; named 'Best Multi-Family Office ($15B AUM/AUA and above)' at the 2025 Family Wealth Report Awards; serves UHNW families, single family offices, foundations and endowments.</t>
+          <t>Self-described 'multi-family office'; the Stenger family has served 'over 1,200 families across the United States'. Serves many outside client families. Sources: https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (CRD 151736) and partner-owned MFO founded 2010; ~775+ employees; comprehensive investment management, tax, insurance, legacy and family-office services.</t>
+          <t xml:space="preserve">SEC-registered investment adviser (13F filer); independent fiduciary wealth-management firm offering financial planning, investment management, tax and estate strategies under a family-office model; ~$731M AUM. Sources: https://www.stengerfamilyoffice.com/ </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>corroborated</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Family Wealth Report / Pathstone communications and Form ADV (03/31/2025) for the ~$125B firm figure; affiliate-inclusive totals per Preqin/press.</t>
+          <t>Firm-stated. https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>CEO and co-founder; sets the firm's strategic vision, on the Board of Managers and Executive Leadership Team; previously President of Pathstone and a Principal at Harris myCFO. Primary top decision-maker.</t>
+          <t>Founder and CEO / lead financial advisor; prior Senior Vice President financial advisor at Morgan Stanley Wealth Management, and roles at Invesco PowerShares and PwC; the firm's decision-maker and namesake. https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://www.stengerfamilyoffice.com (published mailto/contact page)</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>No individual email is published on Fleissig's Pathstone bio page or elsewhere on pathstone.com; no qualifying published address found.</t>
+          <t>No individual email published on the firm site; contact is via a Calendly link (calendly.com/nicholasstenger/intro-meeting) rather than a published email address. No broker emails accepted.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Englewood office line (201) 944-7284 appears on the firm's Form ADV cover (not a personal line).</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>https://pathstone.com/people/matthew-fleissig/ ; https://www.familywealthreport.com/article.php/Now-A-$100-Billion-MFO,-What%E2%80%99s-Next-For-Pathstone%3F-?id=202670</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
+          <t>https://www.stengerfamilyoffice.com/ ; https://www.stengerfamilyoffice.com/financialadvisornaperville ; https://podcasts.apple.com/us/podcast/the-nick-stenger-show/id1678810370</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEC13F-0001731123</t>
+          <t>SEC13F-0001908612</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Biltmore Family Office, LLC</t>
+          <t>Allie Family Office LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -5545,22 +6886,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001731123); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001908612); discovered via fts</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001731123&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001908612&amp;type=13F</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Independent SEC-registered adviser to investment-oriented multi-generational families plus institutional clients; ~951 accounts and ~$3.2-3.5B AUM (avg client ~$38M). A collaborative multi-family office, not a single-family vehicle. Sources: https://www.biltmorefamilyoffice.com/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
+          <t>Self-described independent multi-family office with offices in Miami and Lima serving multiple Latin American (predominantly Peruvian) HNW families; press reports ~23 client families averaging ~$50M each. Clearly multi-client, not single-family. Sources: https://allie-intl.com/en/home/ ; https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami ; https://fintrx.com/firms/firm/allie-family-office-llc-307144</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (13F filer) founded 2008 (LLC organized 2013); positions itself as a hybrid family office and RIA. Sources: https://www.biltmorefamilyoffice.com/our-history/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
+          <t>SEC-registered investment adviser (CRD 307144, 13F filer) established September 2019; provides discretionary and limited-discretionary investment management, estate planning and cross-border tax coordination as an independent multi-family office. Sources: https://adviserinfo.sec.gov/firm/summary/307144 ; https://reports.adviserinfo.sec.gov/crs/crs_307144.pdf</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -5570,12 +6911,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>AUM/ADV aggregators. https://fintrx.com/firms/firm/biltmore-family-office-llc-167174 ; https://advisor.guide/firms/biltmore-family-office ; https://whalewisdom.com/filer/biltmore-family-office-llc</t>
+          <t>Form ADV / adviser aggregators and press. https://fintrx.com/firms/firm/allie-family-office-llc-307144 ; https://aum13f.com/firm/allie-family-office-llc ; https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Founder and President/CEO; 30 years' experience in investment management, asset allocation and investment-policy creation; prior Partner at GenSpring Family Offices, President at JPMorgan Private Bank, Managing Director at Brown Brothers Harriman. The firm's top decision-maker (Rael Gorelick is Partner &amp; Head of Investments / CIO-equivalent). https://www.biltmorefamilyoffice.com/who-we-are/chris-cecil/ ; https://www.linkedin.com/in/chris-cecil-9701b818/</t>
+          <t>Bruno Ghio founded Allié in 2019, owns 100% of the firm and is Founder &amp; CEO — the lead decision-maker — after serving as Managing Director / Regional Head of the Family Office at BCP and a senior private banker at JPMorgan. Jose Larrabure (CFA, CESGA) leads investment management. https://pe.linkedin.com/in/bruno-ghio-1264b616b ; https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5586,17 +6927,17 @@
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>No individual email published on the firm site (biltmorefamilyoffice.com pages returned 403 during research; no person@ address found in accessible pages). RocketReach/ContactOut/Datanyze show only masked/pattern (first@biltmorefamilyoffice.com) broker data — excluded; not pattern-generated.</t>
+          <t>Firm publishes only a generic mailbox (info@allie-intl.com); the Team page lists members without individual emails or direct lines. RocketReach/aggregator listings for Bruno Ghio are broker-sourced and excluded per rules.</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Firm main line (6836 Morrison Blvd Suite 100, Charlotte); firm switchboard, not a personal line. https://www.biltmorefamilyoffice.com/</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1908612/000190861226000002/primary_doc.xml</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>https://www.biltmorefamilyoffice.com/our-history/ ; https://businessnc.com/chris-cecil/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
+          <t>https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami ; https://www.leadersleague.com/en/news/allie-family-office-adds-partner-in-peru ; https://www.bloomberg.com/news/articles/2024-03-18/family-office-head-sees-more-peruvian-clients-settling-in-miami</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -5604,12 +6945,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEC13F-0001039807</t>
+          <t>SEC13F-0001511137</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Boston Family Office LLC</t>
+          <t>Pathstone Family Office LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -5619,22 +6960,22 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001039807); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001511137); discovered via fts</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001039807&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001511137&amp;type=13F</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (CRD #107141) serving many clients -- ~789 accounts across high-net-worth individuals, retail investors and charitable organizations; ~$1.7-2.0B AUM; 15 partners. This is a multi-family office / wealth-management RIA, not a single family's office. Source: https://adviserinfo.sec.gov/firm/summary/107141 and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
+          <t>Large partner-owned multi-family office; named 'Best Multi-Family Office ($15B AUM/AUA and above)' at the 2025 Family Wealth Report Awards; serves UHNW families, single family offices, foundations and endowments.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Operates as an RIA branded as a family office ('The Boston Family Office'), founded 1996; files 13F under CIK 0001039807. Source: https://www.bosfam.com/george-beal/</t>
+          <t>SEC-registered investment adviser (CRD 151736) and partner-owned MFO founded 2010; ~775+ employees; comprehensive investment management, tax, insurance, legacy and family-office services.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5644,12 +6985,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/107141 (Form ADV, 2024-2025) and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
+          <t>Family Wealth Report / Pathstone communications and Form ADV (03/31/2025) for the ~$125B firm figure; affiliate-inclusive totals per Preqin/press.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Beal co-founded the firm in 1996, is a Managing Partner and portfolio manager, and is the named 13F signatory -- an active, current investment decision-maker. Note the firm has 15 partners / ~8 active managing directors, so investment authority is shared. Source: https://www.bosfam.com/george-beal/</t>
+          <t>CEO and co-founder; sets the firm's strategic vision, on the Board of Managers and Executive Leadership Team; previously President of Pathstone and a Principal at Harris myCFO. Primary top decision-maker.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -5660,17 +7001,17 @@
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Tried: fetched bosfam.com homepage and bosfam.com/george-beal/ team page -- only phone (617-624-0800) is published, no email. A ZoomInfo listing shows a masked pattern 'g***@bosfam.com' but that is a data-broker inference, NOT a published/attested individual address, so it is excluded. Did not construct an address.</t>
+          <t>No individual email is published on Fleissig's Pathstone bio page or elsewhere on pathstone.com; no qualifying published address found.</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
+          <t>Englewood office line (201) 944-7284 appears on the firm's Form ADV cover (not a personal line).</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>https://www.bosfam.com/wp-content/uploads/2024/02/2024-ADV-Part-2B-Brochure-Supplement_FINAL.pdf ; https://adviserinfo.sec.gov/firm/summary/107141</t>
+          <t>https://pathstone.com/people/matthew-fleissig/ ; https://www.familywealthreport.com/article.php/Now-A-$100-Billion-MFO,-What%E2%80%99s-Next-For-Pathstone%3F-?id=202670</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -5678,12 +7019,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SEC13F-0002017744</t>
+          <t>SEC13F-0001731123</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC</t>
+          <t>Biltmore Family Office, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5693,22 +7034,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0002017744); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001731123); discovered via fts</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002017744&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001731123&amp;type=13F</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>A registered investment adviser and multi-family office that markets 'Multi Family Office Services' and serves many clients -- high-net-worth individuals, entrepreneurs, families and family offices -- with ~20 staff across multiple US offices. Source: https://arrowrootfamilyoffice.com/team/ and https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
+          <t>Independent SEC-registered adviser to investment-oriented multi-generational families plus institutional clients; ~951 accounts and ~$3.2-3.5B AUM (avg client ~$38M). A collaborative multi-family office, not a single-family vehicle. Sources: https://www.biltmorefamilyoffice.com/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SEC-registered RIA (Form ADV on file, SEC# 801-121878) branded 'Arrowroot Family Office'; files 13F under CIK 0002017744; multiple offices and a published team. Source: https://9at.com/Adviser/801-121878</t>
+          <t>SEC-registered investment adviser (13F filer) founded 2008 (LLC organized 2013); positions itself as a hybrid family office and RIA. Sources: https://www.biltmorefamilyoffice.com/our-history/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5718,12 +7059,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://fintrx.com/firms/firm/arrowroot-family-office-llc-168744 (~$431M, Q2 2025); Form ADV: https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf (2025)</t>
+          <t>AUM/ADV aggregators. https://fintrx.com/firms/firm/biltmore-family-office-llc-167174 ; https://advisor.guide/firms/biltmore-family-office ; https://whalewisdom.com/filer/biltmore-family-office-llc</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Santos is CEO and principal owner, leading the firm; he is the 13F signatory (Roberto Santos = Rob Santos) and a current decision-maker with 20+ years' experience. Source: https://arrowrootfamilyoffice.com/team/ and https://www.getwarmer.com/advisors/roberto-francisco-santos</t>
+          <t>Founder and President/CEO; 30 years' experience in investment management, asset allocation and investment-policy creation; prior Partner at GenSpring Family Offices, President at JPMorgan Private Bank, Managing Director at Brown Brothers Harriman. The firm's top decision-maker (Rael Gorelick is Partner &amp; Head of Investments / CIO-equivalent). https://www.biltmorefamilyoffice.com/who-we-are/chris-cecil/ ; https://www.linkedin.com/in/chris-cecil-9701b818/</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -5734,17 +7075,17 @@
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Tried: fetched the firm's team page (no email published, only phone 833-224-2249 and a contact form); searched for a published individual email; only data-broker (RocketReach) listings exist, which are not published/attested. Did not construct an address.</t>
+          <t>No individual email published on the firm site (biltmorefamilyoffice.com pages returned 403 during research; no person@ address found in accessible pages). RocketReach/ContactOut/Datanyze show only masked/pattern (first@biltmorefamilyoffice.com) broker data — excluded; not pattern-generated.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
+          <t>Firm main line (6836 Morrison Blvd Suite 100, Charlotte); firm switchboard, not a personal line. https://www.biltmorefamilyoffice.com/</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>https://www.arrowrootfamilyoffice.com/press-releases/arrowroot-family-office-in-michigan/ ; https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
+          <t>https://www.biltmorefamilyoffice.com/our-history/ ; https://businessnc.com/chris-cecil/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
         </is>
       </c>
       <c r="P19" t="inlineStr"/>
@@ -5752,12 +7093,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SEC13F-0001756485</t>
+          <t>SEC13F-0001039807</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Independent Family Office, LLC</t>
+          <t>Boston Family Office LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5767,22 +7108,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001756485); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001039807); discovered via fts</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001756485&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001039807&amp;type=13F</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bespoke family office serving multiple 'select' high-net-worth client families across the country (~34 client relationships, ~$617.8M discretionary AUM); listed by Altss as a Multi Family Office. Multi-client, not single-family. Sources: https://ifollc.com/ ; https://altss.com/profile/independent-family-office-llc ; https://money.usnews.com/financial-advisors/firm/independent-family-office-llc-144811</t>
+          <t>SEC-registered investment adviser (CRD #107141) serving many clients -- ~789 accounts across high-net-worth individuals, retail investors and charitable organizations; ~$1.7-2.0B AUM; 15 partners. This is a multi-family office / wealth-management RIA, not a single family's office. Source: https://adviserinfo.sec.gov/firm/summary/107141 and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (CRD 144811, 13F filer), SEC-registered since 2012 (founded 2005); acts as a capital allocator providing investment oversight, estate-planning support, tax and day-to-day financial administration for HNW families. Sources: https://adviserinfo.sec.gov/individual/summary/6993180 ; https://ifollc.com/blank-5/</t>
+          <t>Operates as an RIA branded as a family office ('The Boston Family Office'), founded 1996; files 13F under CIK 0001039807. Source: https://www.bosfam.com/george-beal/</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -5792,33 +7133,33 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Form ADV / adviser aggregators. https://money.usnews.com/financial-advisors/firm/independent-family-office-llc-144811 ; https://fintrx.com/firms/firm/independent-family-office-llc-144811 ; https://aum13f.com/firm/independent-family-office-llc</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/107141 (Form ADV, 2024-2025) and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>William Michael Reickert established IFO in 2005 after leading The Ayco Company's family-office practice; he is Managing Member/CEO and the firm's lead investment and advisory decision-maker, described as a trusted advisor to Fortune 100 CEOs, fund managers and senior officials. https://ifollc.com/blank-5/ ; https://www.advisorcheck.com/advisor/1673416-william-michael-reickert-independent-family-office-llc-albany-new-york</t>
+          <t>Beal co-founded the firm in 1996, is a Managing Partner and portfolio manager, and is the named 13F signatory -- an active, current investment decision-maker. Note the firm has 15 partners / ~8 active managing directors, so investment authority is shared. Source: https://www.bosfam.com/george-beal/</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>The only address published on the site (home + Reickert's bio page) is 'dr@ifollc.com'; the 'dr' initials do not match 'W. Michael Reickert', so it appears to be a shared/assistant or general mailbox rather than the principal's personal individual email — excluded as not clearly an individual address per rules. No other individual email found.</t>
+          <t>Tried: fetched bosfam.com homepage and bosfam.com/george-beal/ team page -- only phone (617-624-0800) is published, no email. A ZoomInfo listing shows a masked pattern 'g***@bosfam.com' but that is a data-broker inference, NOT a published/attested individual address, so it is excluded. Did not construct an address.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>https://ifollc.com/blank-5/ and https://ifollc.com/ (main office line, 677 Broadway 7th Floor, Albany; not a personal line)</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>https://ifollc.com/blank-5/ ; https://altss.com/profile/independent-family-office-llc ; https://money.usnews.com/financial-advisors/firm/independent-family-office-llc-144811</t>
+          <t>https://www.bosfam.com/wp-content/uploads/2024/02/2024-ADV-Part-2B-Brochure-Supplement_FINAL.pdf ; https://adviserinfo.sec.gov/firm/summary/107141</t>
         </is>
       </c>
       <c r="P20" t="inlineStr"/>
@@ -5826,37 +7167,37 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UKCH-09580739</t>
+          <t>SEC13F-0002017744</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Blu Family Office Limited</t>
+          <t>Arrowroot Family Office, LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Companies House 09580739 (Private limited company); inc. 8 May 2015</t>
+          <t>EDGAR 13F filer (CIK 0002017744); discovered via fts</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/09580739</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002017744&amp;type=13F</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Founded 2010 by Christian Armbruester (ex-Credit Suisse) to manage his own family's wealth, then expanded to serve multiple families; repeatedly described as a multi-family office in press (Citywire, Private Banker International). FCA-regulated discretionary manager.</t>
+          <t>A registered investment adviser and multi-family office that markets 'Multi Family Office Services' and serves many clients -- high-net-worth individuals, entrepreneurs, families and family offices -- with ~20 staff across multiple US offices. Source: https://arrowrootfamilyoffice.com/team/ and https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Live FCA-regulated firm; active website; investment arm 'Blu Investment Management' (blu-im.com); corporate LinkedIn; named press profiles; defined team.</t>
+          <t>SEC-registered RIA (Form ADV on file, SEC# 801-121878) branded 'Arrowroot Family Office'; files 13F under CIK 0002017744; multiple offices and a published team. Source: https://9at.com/Adviser/801-121878</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -5866,12 +7207,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Third-party estimate via industry data/press (Citywire wealth-manager profile); not officially disclosed.</t>
+          <t>https://fintrx.com/firms/firm/arrowroot-family-office-llc-168744 (~$431M, Q2 2025); Form ADV: https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf (2025)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Founder and principal investment decision-maker; single largest shareholder; individual, not nominee. Current day-to-day CEO is Marie Redron.</t>
+          <t>Santos is CEO and principal owner, leading the firm; he is the 13F signatory (Roberto Santos = Rob Santos) and a current decision-maker with 20+ years' experience. Source: https://arrowrootfamilyoffice.com/team/ and https://www.getwarmer.com/advisors/roberto-francisco-santos</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -5882,13 +7223,17 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Firm site publishes only a generic mailbox (info@blu-im.com). No individual/principal email published anywhere located. Nothing pattern-generated.</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>Tried: fetched the firm's team page (no email published, only phone 833-224-2249 and a contact form); searched for a published individual email; only data-broker (RocketReach) listings exist, which are not published/attested. Did not construct an address.</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/09580739/officers; https://citywire.com/wealth-manager/news/richmond-based-multi-family-boutique-names-new-ceo/a1109198</t>
+          <t>https://www.arrowrootfamilyoffice.com/press-releases/arrowroot-family-office-in-michigan/ ; https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -5896,69 +7241,73 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UKCH-12233405</t>
+          <t>SEC13F-0001756485</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Schwarz Family Office Ltd</t>
+          <t>Independent Family Office, LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Companies House 12233405 (Private limited company); inc. 30 September 2019</t>
+          <t>EDGAR 13F filer (CIK 0001756485); discovered via fts</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/12233405</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001756485&amp;type=13F</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Website describes a 'boutique consultancy' providing debt financing, capital raising, IR and fund management for clients, with multiple partners — more advisory/MFO-style than a pure single-family office despite the name. Two shareholders. https://schwarzfamilyoffice.com/</t>
+          <t>Bespoke family office serving multiple 'select' high-net-worth client families across the country (~34 client relationships, ~$617.8M discretionary AUM); listed by Altss as a Multi Family Office. Multi-client, not single-family. Sources: https://ifollc.com/ ; https://altss.com/profile/independent-family-office-llc ; https://money.usnews.com/financial-advisors/firm/independent-family-office-llc-144811</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Active company, SIC 64304 + consultancy codes; own website; listed in Family Capital's 'FamCap 50'. https://schwarzfamilyoffice.com/ ; https://find-and-update.company-information.service.gov.uk/company/12233405</t>
+          <t>SEC-registered investment adviser (CRD 144811, 13F filer), SEC-registered since 2012 (founded 2005); acts as a capital allocator providing investment oversight, estate-planning support, tax and day-to-day financial administration for HNW families. Sources: https://adviserinfo.sec.gov/individual/summary/6993180 ; https://ifollc.com/blank-5/</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>corroborated</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>Form ADV / adviser aggregators. https://money.usnews.com/financial-advisors/firm/independent-family-office-llc-144811 ; https://fintrx.com/firms/firm/independent-family-office-llc-144811 ; https://aum13f.com/firm/independent-family-office-llc</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sole director since incorporation (2019) and majority shareholder (510/1000); ex Merrill Lynch and Bank of Singapore. https://find-and-update.company-information.service.gov.uk/company/12233405/officers ; https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
+          <t>William Michael Reickert established IFO in 2005 after leading The Ayco Company's family-office practice; he is Managing Member/CEO and the firm's lead investment and advisory decision-maker, described as a trusted advisor to Fortune 100 CEOs, fund managers and senior officials. https://ifollc.com/blank-5/ ; https://www.advisorcheck.com/advisor/1673416-william-michael-reickert-independent-family-office-llc-albany-new-york</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Only a generic mailbox (admin@schwarzfamilyoffice.com) is published (excluded). RocketReach result is a masked/broker source and excluded.</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>The only address published on the site (home + Reickert's bio page) is 'dr@ifollc.com'; the 'dr' initials do not match 'W. Michael Reickert', so it appears to be a shared/assistant or general mailbox rather than the principal's personal individual email — excluded as not clearly an individual address per rules. No other individual email found.</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>https://ifollc.com/blank-5/ and https://ifollc.com/ (main office line, 677 Broadway 7th Floor, Albany; not a personal line)</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>https://www.famcap.com/2024/02/the-famcap-50-the-worlds-top-family-capital-investment-specialists/</t>
+          <t>https://ifollc.com/blank-5/ ; https://altss.com/profile/independent-family-office-llc ; https://money.usnews.com/financial-advisors/firm/independent-family-office-llc-144811</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -5966,12 +7315,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UKCH-14344019</t>
+          <t>UKCH-09580739</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hazell Family Office Ltd</t>
+          <t>Blu Family Office Limited</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5981,50 +7330,54 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Companies House 14344019 (Private limited company); inc. 8 September 2022</t>
+          <t>Companies House 09580739 (Private limited company); inc. 8 May 2015</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14344019</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/09580739</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>All five directors share surname Hazell and one family address (Cefn Henllan Farm, Llanhennock, Usk); appointed same day 2022-09-08; DOB spread (1959-1994) indicates two parents + three adult children — a single-family board. SIC 70221 (financial management).</t>
+          <t>Founded 2010 by Christian Armbruester (ex-Credit Suisse) to manage his own family's wealth, then expanded to serve multiple families; repeatedly described as a multi-family office in press (Citywire, Private Banker International). FCA-regulated discretionary manager.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Family-only board, no external/nominee officers. Patriarch Mark Hazell is MD of the family's operating businesses (haulage / environmental services), a plausible wealth source. https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
+          <t>Live FCA-regulated firm; active website; investment arm 'Blu Investment Management' (blu-im.com); corporate LinkedIn; named press profiles; defined team.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Third-party estimate via industry data/press (Citywire wealth-manager profile); not officially disclosed.</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Patriarch (b.1959), MD of the family operating companies; most probable investment decision-maker; individual, not nominee.</t>
+          <t>Founder and principal investment decision-maker; single largest shareholder; individual, not nominee. Current day-to-day CEO is Marie Redron.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>No firm website; searches returned only company/director aggregators; no published individual email. Nothing pattern-generated.</t>
+          <t>Firm site publishes only a generic mailbox (info@blu-im.com). No individual/principal email published anywhere located. Nothing pattern-generated.</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/09580739/officers; https://citywire.com/wealth-manager/news/richmond-based-multi-family-boutique-names-new-ceo/a1109198</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -6032,12 +7385,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UKCH-14442767</t>
+          <t>UKCH-12233405</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Wedgwood Family Office Limited</t>
+          <t>Schwarz Family Office Ltd</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -6047,22 +7400,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Companies House 14442767 (Private limited company); inc. 25 October 2022</t>
+          <t>Companies House 12233405 (Private limited company); inc. 30 September 2019</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14442767</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/12233405</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>SIC 66300 (fund management), sole active director Paul Wedgwood at a single residential address; no external clients/multi-family structure. Principal separately holds 'Wedgwood FIC Limited' (a Family Investment Company), consistent with a single-family vehicle.</t>
+          <t>Website describes a 'boutique consultancy' providing debt financing, capital raising, IR and fund management for clients, with multiple partners — more advisory/MFO-style than a pure single-family office despite the name. Two shareholders. https://schwarzfamilyoffice.com/</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Active company (inc. 2022-10-25), SIC 66300, residential registered address. Director Paul Wedgwood (b. Jun 1970) very likely the video-game entrepreneur who sold Splash Damage (up to $150m, 2016) and co-founded Supernova Capital — a plausible wealth source. https://en.wikipedia.org/wiki/Paul_Wedgwood</t>
+          <t>Active company, SIC 64304 + consultancy codes; own website; listed in Family Capital's 'FamCap 50'. https://schwarzfamilyoffice.com/ ; https://find-and-update.company-information.service.gov.uk/company/12233405</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -6070,27 +7423,31 @@
           <t>corroborated</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Not disclosed</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Sole active decision-making director since incorporation. Almost certainly the Splash Damage / Supernova Capital entrepreneur (DOB match; also director of Wedgwood FIC Limited).</t>
+          <t>Sole director since incorporation (2019) and majority shareholder (510/1000); ex Merrill Lynch and Bank of Singapore. https://find-and-update.company-information.service.gov.uk/company/12233405/officers ; https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>No firm website/press page; no individual email published. A uk.linkedin.com/in/paulwedgwood profile is labelled 'The Carbon Trust' and cannot be confirmed as the same person; nothing inferred.</t>
+          <t>Only a generic mailbox (admin@schwarzfamilyoffice.com) is published (excluded). RocketReach result is a masked/broker source and excluded.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14442767/officers</t>
+          <t>https://www.famcap.com/2024/02/the-famcap-50-the-worlds-top-family-capital-investment-specialists/</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -6098,37 +7455,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SFO-dfo-management-dell</t>
+          <t>APAC-farro-capital</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DFO Management, LLC</t>
+          <t>Farro Capital Pte. Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>apac-eu-registry</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (Michael Dell) -&gt; family office entity. Confirmed as Dell's single-family office by the firm's own site (dellfamilyoffice.com) and confirmed as an SEC 13F filer via EDGAR full-text search (13F-HR filed under Michael &amp; Susan Dell Foundation, managed by DFO Management, CIK 0001599858).</t>
+          <t>Independent multi-family office headquartered in Singapore. Confirmed via Hubbis, Private Banker International and Fund Selector Asia coverage of its launch, plus DIFC's announcement of its Dubai regional HQ; leadership and AUM corroborated by Caproasia and the firm's own site.</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.dellfamilyoffice.com/about</t>
+          <t>https://hubbis.com/news/farro-capital-establishes-independent-multi-family-office-from-singapore</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Firm site states DFO is 'the private investment firm for Dell Technologies Founder &amp; CEO Michael Dell and his family'; launched 1998 as MSD Capital, restructured to DFO Management at end of 2022. Single-family (Dell) only.</t>
+          <t>Described by Hubbis, Private Banker International and Fund Selector Asia as an independent multi-family office established from Singapore, serving multiple UHNW families across 12+ markets.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SEC EDGAR 13F-HR filings (CIK 0001599858, period ending 2026-03-31, filed 2026-05-15) plus dedicated family-office website.</t>
+          <t>Multiple reputable trade outlets and the firm's own website confirm Farro Capital operates as a Singapore-headquartered multi-family office / wealth-management platform.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -6138,25 +7495,29 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Not publicly disclosed; widely reported as tens of billions tied to Michael Dell's fortune.</t>
+          <t>Caproasia (Apr 2026) reported AUM increased to ~USD3bn; the firm's Farro &amp; Co site references 'over USD2 billion' managed by sister brand Farro Capital.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Beneficial owner and namesake; the family office exists to manage his and his family's capital.</t>
+          <t>Hemant Tucker is the co-founder and current CEO and the firm's top decision-maker (former MD/Market Head for Global South Asia &amp; Middle East at Bank of Singapore).</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No individually published email located; only aggregator (RocketReach) listings, which are excluded per rules against broker/pattern-generated addresses.</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr">
         <is>
-          <t>https://efts.sec.gov/LATEST/search-index?q=%22DFO+Management%22&amp;forms=13F-HR</t>
+          <t>https://www.caproasia.com/2026/04/07/singapore-based-multi-family-office-farro-capital-aum-increased-to-3-billion-founded-in-2022-by-hemant-tucker-manish-tibrewal-mahesh-kumar-rajiv-garg-uthpal-rao-previous-financial-industry-p/</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -6164,52 +7525,48 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SFO-bayshore-global-brin</t>
+          <t>UKCH-14344019</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Bayshore Global Management, LLC</t>
+          <t>Hazell Family Office Ltd</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>uk-companies-house</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (Sergey Brin) -&gt; family office entity. Confirmed as Brin's single-family office by Bloomberg reporting (2026-04-23, 'Sergey Brin's Family Office Absorbs Nexus NeuroTech Brain-Health VC Fund') and Wikipedia.</t>
+          <t>Companies House 14344019 (Private limited company); inc. 8 September 2022</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-04-23/sergey-brin-s-family-office-takes-over-brain-focused-vc-fund</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14344019</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Described consistently as the single-family office of Google co-founder Sergey Brin; founded 2005; allocates across public/private markets, real estate and philanthropic vehicles.</t>
+          <t>All five directors share surname Hazell and one family address (Cefn Henllan Farm, Llanhennock, Usk); appointed same day 2022-09-08; DOB spread (1959-1994) indicates two parents + three adult children — a single-family board. SIC 70221 (financial management).</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bloomberg news coverage naming it Sergey Brin's family office; Wikipedia entry; multiple family-office databases.</t>
+          <t>Family-only board, no external/nominee officers. Patriarch Mark Hazell is MD of the family's operating businesses (haulage / environmental services), a plausible wealth source. https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Press reports estimate over $100bn tied to Brin's Alphabet stake; not independently disclosed.</t>
-        </is>
-      </c>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Beneficial owner; office manages his assets. Day-to-day led by CEO George Pavlov and CIO Marie Young per press.</t>
+          <t>Patriarch (b.1959), MD of the family operating companies; most probable investment decision-maker; individual, not nominee.</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -6218,11 +7575,15 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No firm website; searches returned only company/director aggregators; no published individual email. Nothing pattern-generated.</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-04-23/sergey-brin-s-family-office-takes-over-brain-focused-vc-fund</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -6230,52 +7591,48 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SFO-hillspire-schmidt</t>
+          <t>UKCH-14442767</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hillspire, LLC</t>
+          <t>Wedgwood Family Office Limited</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>uk-companies-house</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (Eric Schmidt) -&gt; family office entity. Confirmed as Schmidt's single-family office by CNBC reporting (CNBC 'Inside Wealth Family Office 15', 2026-02-12, and 2025-01-21 piece on 22 AI startup investments).</t>
+          <t>Companies House 14442767 (Private limited company); inc. 25 October 2022</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/2025/01/21/eric-schmidts-family-office-invests-ai-startups.html</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14442767</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Described by CNBC and family-office databases as the single-family office established by former Google CEO Eric Schmidt and his wife Wendy Schmidt (founded 2006).</t>
+          <t>SIC 66300 (fund management), sole active director Paul Wedgwood at a single residential address; no external clients/multi-family structure. Principal separately holds 'Wedgwood FIC Limited' (a Family Investment Company), consistent with a single-family vehicle.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CNBC news coverage naming Hillspire as Eric Schmidt's family office and ranking it the most active U.S. family office for 2025 dealmaking.</t>
+          <t>Active company (inc. 2022-10-25), SIC 66300, residential registered address. Director Paul Wedgwood (b. Jun 1970) very likely the video-game entrepreneur who sold Splash Damage (up to $150m, 2016) and co-founded Supernova Capital — a plausible wealth source. https://en.wikipedia.org/wiki/Paul_Wedgwood</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Not disclosed.</t>
-        </is>
-      </c>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Beneficial owner and namesake; office run day-to-day by President Ken Goldman per press.</t>
+          <t>Sole active decision-making director since incorporation. Almost certainly the Splash Damage / Supernova Capital entrepreneur (DOB match; also director of Wedgwood FIC Limited).</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -6284,11 +7641,15 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No firm website/press page; no individual email published. A uk.linkedin.com/in/paulwedgwood profile is labelled 'The Carbon Trust' and cannot be confirmed as the same person; nothing inferred.</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/2026/02/12/inside-wealth-family-office-15.html</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14442767/officers</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -6296,37 +7657,37 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SFO-blue-pool-capital-tsai</t>
+          <t>UKCH-17062903</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Blue Pool Capital Limited (13F filer: Blue Pool Management Ltd.)</t>
+          <t>Frigus Family Office Ltd</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>uk-companies-house</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (Joseph Tsai, Alibaba co-founder) and via SEC 13F filer with a neutral name. Confirmed as an SEC 13F filer (Blue Pool Management Ltd., CIK 0001675855, HQ Causeway Bay Hong Kong) and confirmed as Tsai's family office by Crain Currency / Caproasia reporting.</t>
+          <t>Companies House 17062903 (Private limited company); inc. 2 March 2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.caproasia.com/2024/09/19/alibaba-co-founder-billionaire-joseph-tsai-joins-investor-consortium-to-buy-vineyards-in-france-burgundy-another-investor-in-group-is-oliver-weisberg-who-is-ceo-of-joseph-tsai-family-office-blue-po/</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/17062903</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Repeatedly described as the family office of Alibaba co-founder Joe Tsai; oversees the Tsai family's investments and operating assets (incl. Brooklyn Nets, LAFC).</t>
+          <t>Frigus group self-describes as 'a single family office, specialising in the active management of assets, investments and real estate' (frigus.is). UK entity controlled by Lydur Gudmundsson (sole PSC, 'significant influence or control'); director Andrea Olsen is MD/CEO of the Icelandic parent Frigus ehf. Single family (Gudmundsson). Sources: https://www.frigus.is/ ; https://find-and-update.company-information.service.gov.uk/company/17062903/persons-with-significant-control</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SEC EDGAR 13F-HR filings (Blue Pool Management Ltd., CIK 0001675855; latest 2026-05-15, HQ 25/F Hysan Place, 500 Hennessy Road, Causeway Bay) plus Crain Currency/Caproasia press naming it Joe Tsai's family office.</t>
+          <t>Explicit self-description as a single family office on frigus.is. Principal Lydur Gudmundsson is co-founder of Bakkavor (now merged into Greencore, 2026); the family office's primary asset is described as a stake in Greencore Group. UK company incorporated 2 Mar 2026 as the UK arm. Sources: https://www.frigus.is/ ; https://find-and-update.company-information.service.gov.uk/company/17062903</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -6336,12 +7697,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Press estimate (Caproasia/Crain Currency, 2022-2026); not an official disclosure.</t>
+          <t>Not published as a figure. Primary asset described as a stake in Greencore Group (source: https://www.frigus.is/); no dollar/pound AUM disclosed.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Beneficial owner; founded the office in 2004/2015. Day-to-day CEO is Oliver Weisberg.</t>
+          <t>Sole PSC of the UK entity ('significant influence or control'); the family principal behind Frigus. British (per CH), DOB July 1967. Investment decision-maker / beneficial owner. (Professional executive Andrea Olsen is UK director and CEO/MD of Frigus ehf.)</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -6350,11 +7711,15 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Firm website publishes only generic mailboxes ('contact@frigus.is', 'contact@frigus.lu') and a switchboard (+354 550 9700) — no individual principal email. Generic mailboxes are excluded per rules; pattern-generation not permitted. Source checked: https://www.frigus.is/</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001675855.json</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/17062903 ; https://www.frigus.is/</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -6362,12 +7727,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SFO-mousse-partners-wertheimer</t>
+          <t>SFO-dfo-management-dell</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mousse Partners Limited (part of Mousse Investments Limited)</t>
+          <t>DFO Management, LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -6377,22 +7742,22 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Identified via known UHNW family (Wertheimer, owners of Chanel) -&gt; family office entity. Confirmed as the Wertheimer family office by Bloomberg ('Family office for $90 billion fortune reshapes consumer bets') and Wikipedia.</t>
+          <t>Identified via known UHNW individual (Michael Dell) -&gt; family office entity. Confirmed as Dell's single-family office by the firm's own site (dellfamilyoffice.com) and confirmed as an SEC 13F filer via EDGAR full-text search (13F-HR filed under Michael &amp; Susan Dell Foundation, managed by DFO Management, CIK 0001599858).</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/professional/insights/trading/family-office-for-90-billion-fortune-reshapes-consumer-bets/</t>
+          <t>https://www.dellfamilyoffice.com/about</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Described as the family office managing the wealth of Alain and Gerard Wertheimer, owners of Chanel; founded 1991 by Charles Heilbronn (Chanel executive and half-brother of the Wertheimers).</t>
+          <t>Firm site states DFO is 'the private investment firm for Dell Technologies Founder &amp; CEO Michael Dell and his family'; launched 1998 as MSD Capital, restructured to DFO Management at end of 2022. Single-family (Dell) only.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bloomberg feature and Wikipedia identify Mousse Partners as the Wertheimer family office; firm site describes it as the investment division of Mousse Investments Limited.</t>
+          <t>SEC EDGAR 13F-HR filings (CIK 0001599858, period ending 2026-03-31, filed 2026-05-15) plus dedicated family-office website.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -6402,12 +7767,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Press associates the family fortune at ~$90-100bn; this is the Wertheimer net worth, not a disclosed AUM figure for Mousse.</t>
+          <t>Not publicly disclosed; widely reported as tens of billions tied to Michael Dell's fortune.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Founder and head of the office; Chanel executive and half-brother of owners Alain and Gerard Wertheimer.</t>
+          <t>Beneficial owner and namesake; the family office exists to manage his and his family's capital.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -6420,7 +7785,7 @@
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/professional/insights/trading/family-office-for-90-billion-fortune-reshapes-consumer-bets/</t>
+          <t>https://efts.sec.gov/LATEST/search-index?q=%22DFO+Management%22&amp;forms=13F-HR</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -6428,12 +7793,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SFO-kirkbi-kristiansen</t>
+          <t>SFO-bayshore-global-brin</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KIRKBI A/S</t>
+          <t>Bayshore Global Management, LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -6443,22 +7808,22 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Identified via known UHNW family (Kirk Kristiansen, owners of LEGO) -&gt; holding/family office. Confirmed as the Kristiansen single-family office by KIRKBI's own website and Wikipedia; a registered Danish company (A/S).</t>
+          <t>Identified via known UHNW individual (Sergey Brin) -&gt; family office entity. Confirmed as Brin's single-family office by Bloomberg reporting (2026-04-23, 'Sergey Brin's Family Office Absorbs Nexus NeuroTech Brain-Health VC Fund') and Wikipedia.</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.kirkbi.com/about-us/family-ownership/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-04-23/sergey-brin-s-family-office-takes-over-brain-focused-vc-fund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Established 1 April 1995 as the family office/holding for the Kirk Kristiansen family (owners of the LEGO Group); owns 75% of the LEGO Group and 47.5% of Merlin Entertainments. Single-family.</t>
+          <t>Described consistently as the single-family office of Google co-founder Sergey Brin; founded 2005; allocates across public/private markets, real estate and philanthropic vehicles.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>KIRKBI's own site (family-ownership page), Wikipedia, and Danish corporate registration as KIRKBI A/S.</t>
+          <t>Bloomberg news coverage naming it Sergey Brin's family office; Wikipedia entry; multiple family-office databases.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -6468,12 +7833,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Press figure for the family's wealth controlled by KIRKBI; total company equity/portfolio larger and not fully disclosed here.</t>
+          <t>Press reports estimate over $100bn tied to Brin's Alphabet stake; not independently disclosed.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>CEO and top investment decision-maker of KIRKBI; family chair is Thomas Kirk Kristiansen (assumed board chair May 2023); CIO is Thomas Lau Schleicher.</t>
+          <t>Beneficial owner; office manages his assets. Day-to-day led by CEO George Pavlov and CIO Marie Young per press.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -6486,7 +7851,7 @@
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>https://www.kirkbi.com/press-releases/2025/kirkbi-climate-invests-in-highview/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-04-23/sergey-brin-s-family-office-takes-over-brain-focused-vc-fund</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -6494,12 +7859,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SFO-tethys-invest-bettencourt</t>
+          <t>SFO-hillspire-schmidt</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tethys Invest SAS (Tethys SAS group)</t>
+          <t>Hillspire, LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6509,22 +7874,22 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Identified via known UHNW family (Bettencourt Meyers, largest shareholder of L'Oreal) -&gt; family office. Confirmed as the Bettencourt Meyers single-family office by The National and Caproasia reporting and the firm's own site (tethys.fr).</t>
+          <t>Identified via known UHNW individual (Eric Schmidt) -&gt; family office entity. Confirmed as Schmidt's single-family office by CNBC reporting (CNBC 'Inside Wealth Family Office 15', 2026-02-12, and 2025-01-21 piece on 22 AI startup investments).</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.thenationalnews.com/business/money/2023/03/13/billionaires-loreal-heir-names-new-head-of-family-office/</t>
+          <t>https://www.cnbc.com/2025/01/21/eric-schmidts-family-office-invests-ai-startups.html</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Described as the single-family office managing the assets of the Bettencourt Meyers family, majority shareholder of L'Oreal; Tethys Invest is the entrepreneurial-investment subsidiary.</t>
+          <t>Described by CNBC and family-office databases as the single-family office established by former Google CEO Eric Schmidt and his wife Wendy Schmidt (founded 2006).</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>The National and Caproasia press naming Tethys as the Bettencourt family office; firm's own website.</t>
+          <t>CNBC news coverage naming Hillspire as Eric Schmidt's family office and ranking it the most active U.S. family office for 2025 dealmaking.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -6534,12 +7899,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Press figure for total family assets (dominated by the L'Oreal stake); Tethys Invest deploys &gt;EUR 3bn of direct-investment capital.</t>
+          <t>Not disclosed.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Head of the family's investment firm (Tethys Invest) and, per 2025 press, appointed to the L'Oreal board seat area of the family; family chair of Tethys is Francoise Bettencourt Meyers, CEO of Tethys is Jean-Pierre Meyers.</t>
+          <t>Beneficial owner and namesake; office run day-to-day by President Ken Goldman per press.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -6552,7 +7917,7 @@
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>https://www.caproasia.com/2025/02/08/loreal-heiress-france-billionaire-francoise-bettencourt-meyers-age-71-with-76-billion-fortune-starts-family-succession-with-retirement-from-loreal-board-as-vice-chairman-son-jean-victo/</t>
+          <t>https://www.cnbc.com/2026/02/12/inside-wealth-family-office-15.html</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -6560,12 +7925,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SFO-cofra-holding-brenninkmeijer</t>
+          <t>SFO-blue-pool-capital-tsai</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>COFRA Holding AG</t>
+          <t>Blue Pool Capital Limited (13F filer: Blue Pool Management Ltd.)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -6575,37 +7940,37 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Identified via known UHNW family (Brenninkmeijer, owners of C&amp;A) -&gt; family holding/office. Confirmed by Crain Currency and the firm's own site as the Brenninkmeijer family's Zug-based holding; leadership verified on cofraholding.com.</t>
+          <t>Identified via known UHNW individual (Joseph Tsai, Alibaba co-founder) and via SEC 13F filer with a neutral name. Confirmed as an SEC 13F filer (Blue Pool Management Ltd., CIK 0001675855, HQ Causeway Bay Hong Kong) and confirmed as Tsai's family office by Crain Currency / Caproasia reporting.</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.craincurrency.com/family-office-management/secretive-brenninkmeijer-family-behind-ca-opens-39-billion-retail-empire</t>
+          <t>https://www.caproasia.com/2024/09/19/alibaba-co-founder-billionaire-joseph-tsai-joins-investor-consortium-to-buy-vineyards-in-france-burgundy-another-investor-in-group-is-oliver-weisberg-who-is-ceo-of-joseph-tsai-family-office-blue-po/</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Established 2001 in Zug to coordinate the Brenninkmeijer family's global businesses and investments; a single-family-owned holding with subsidiaries C&amp;A (retail), Redevco (real estate), Bregal (PE) and Anthos (asset management).</t>
+          <t>Repeatedly described as the family office of Alibaba co-founder Joe Tsai; oversees the Tsai family's investments and operating assets (incl. Brooklyn Nets, LAFC).</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Crain Currency reporting on the family's ~$39bn empire; COFRA's own leadership/governance page listing the family-dominated board.</t>
+          <t>SEC EDGAR 13F-HR filings (Blue Pool Management Ltd., CIK 0001675855; latest 2026-05-15, HQ 25/F Hysan Place, 500 Hennessy Road, Causeway Bay) plus Crain Currency/Caproasia press naming it Joe Tsai's family office.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>corroborated</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Reported total group asset base (Crain Currency and familyofficehub).</t>
+          <t>Press estimate (Caproasia/Crain Currency, 2022-2026); not an official disclosure.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Family-member chairman since 2018 (former CEO of COFRA, C&amp;A Europe and Anthos); group CEO is Boudewijn Beerkens, CFO Florian Brenninkmeyer (from 2025).</t>
+          <t>Beneficial owner; founded the office in 2004/2015. Day-to-day CEO is Oliver Weisberg.</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -6618,7 +7983,7 @@
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>https://www.cofraholding.com/en/newsroom/latest-news/2025/redevco-closes-landmark-475m-loan-investment-for-new-real-estate-debt-platform/</t>
+          <t>https://data.sec.gov/submissions/CIK0001675855.json</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -6626,12 +7991,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SFO-athos-strungmann</t>
+          <t>SFO-mousse-partners-wertheimer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Athos Service GmbH (family investment entity Athos KG)</t>
+          <t>Mousse Partners Limited (part of Mousse Investments Limited)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -6641,22 +8006,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Identified via known UHNW family (Strungmann brothers, BioNTech's largest shareholders) -&gt; family office. Confirmed as their single-family office by Forbes and multiple family-office trade sources; recent dated direct investments corroborate activity.</t>
+          <t>Identified via known UHNW family (Wertheimer, owners of Chanel) -&gt; family office entity. Confirmed as the Wertheimer family office by Bloomberg ('Family office for $90 billion fortune reshapes consumer bets') and Wikipedia.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.forbes.com/sites/paulwestall/2021/08/24/the-family-office-saving-lives-boosting-the-economy-and-making-billions/</t>
+          <t>https://www.bloomberg.com/professional/insights/trading/family-office-for-90-billion-fortune-reshapes-consumer-bets/</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Described as the single-family office of twins Andreas and Thomas Strungmann (who founded generics maker Hexal); anchor and largest shareholder of BioNTech (~43.5%).</t>
+          <t>Described as the family office managing the wealth of Alain and Gerard Wertheimer, owners of Chanel; founded 1991 by Charles Heilbronn (Chanel executive and half-brother of the Wertheimers).</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Forbes and biotech/family-office trade press naming Athos as the Strungmann single-family office; documented anchor investment in BioNTech.</t>
+          <t>Bloomberg feature and Wikipedia identify Mousse Partners as the Wertheimer family office; firm site describes it as the investment division of Mousse Investments Limited.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -6666,12 +8031,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Not disclosed; dominated by the BioNTech stake (~43.5%).</t>
+          <t>Press associates the family fortune at ~$90-100bn; this is the Wertheimer net worth, not a disclosed AUM figure for Mousse.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Beneficial owner (with twin brother Thomas Strungmann) of the family office; jointly direct its investments.</t>
+          <t>Founder and head of the office; Chanel executive and half-brother of owners Alain and Gerard Wertheimer.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -6684,7 +8049,7 @@
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>https://familyofficehub.io/blog/athos-family-office-invests-in-aavantgarde-bios-141m-series-b/</t>
+          <t>https://www.bloomberg.com/professional/insights/trading/family-office-for-90-billion-fortune-reshapes-consumer-bets/</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -6692,12 +8057,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SFO-premji-invest</t>
+          <t>SFO-kirkbi-kristiansen</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Premji Invest</t>
+          <t>KIRKBI A/S</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -6707,37 +8072,37 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (Azim Premji, Wipro founder) -&gt; family office. Confirmed as his family office by The Arc and family-office databases; recent dated deals corroborate active investing.</t>
+          <t>Identified via known UHNW family (Kirk Kristiansen, owners of LEGO) -&gt; holding/family office. Confirmed as the Kristiansen single-family office by KIRKBI's own website and Wikipedia; a registered Danish company (A/S).</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.thearcweb.com/article/wipro-azim-premji-invest-family-office-tk-kurien-0clyngtMEXrGHBNX</t>
+          <t>https://www.kirkbi.com/about-us/family-ownership/</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Described as the private investment office managing the portfolio of Wipro founder Azim Premji and family across public equities, PE and venture; founded 2006, offices in Bengaluru and Menlo Park.</t>
+          <t>Established 1 April 1995 as the family office/holding for the Kirk Kristiansen family (owners of the LEGO Group); owns 75% of the LEGO Group and 47.5% of Merlin Entertainments. Single-family.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>The Arc and multiple family-office databases identify Premji Invest as Azim Premji's family office; firm website.</t>
+          <t>KIRKBI's own site (family-ownership page), Wikipedia, and Danish corporate registration as KIRKBI A/S.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>corroborated</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>The Arc reporting that the family office crossed $10bn in managed assets.</t>
+          <t>Press figure for the family's wealth controlled by KIRKBI; total company equity/portfolio larger and not fully disclosed here.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Chief executive and top investment decision-maker of the office (former Wipro CEO); family principal is Azim Premji; U.S. office led by Sandesh Patnam.</t>
+          <t>CEO and top investment decision-maker of KIRKBI; family chair is Thomas Kirk Kristiansen (assumed board chair May 2023); CIO is Thomas Lau Schleicher.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -6750,7 +8115,7 @@
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>https://tracxn.com/d/private-equity/premjiinvest/__a9W9DN9hd7WxIGfm5z8PuA6IrDlu-VIas8-t59BU6xw</t>
+          <t>https://www.kirkbi.com/press-releases/2025/kirkbi-climate-invests-in-highview/</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -6758,12 +8123,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SFO-catamaran-ventures-murthy</t>
+          <t>SFO-tethys-invest-bettencourt</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Catamaran Management Services Pvt. Ltd. (Catamaran Ventures)</t>
+          <t>Tethys Invest SAS (Tethys SAS group)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -6773,22 +8138,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (N.R. Narayana Murthy, Infosys founder) -&gt; family office. Confirmed as his single-family office by Bloomberg and the firm's own site; described as investing permanent capital with no external LPs.</t>
+          <t>Identified via known UHNW family (Bettencourt Meyers, largest shareholder of L'Oreal) -&gt; family office. Confirmed as the Bettencourt Meyers single-family office by The National and Caproasia reporting and the firm's own site (tethys.fr).</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2025-08-26/family-office-to-billionaire-murthy-warns-on-startup-valuations</t>
+          <t>https://www.thenationalnews.com/business/money/2023/03/13/billionaires-loreal-heir-names-new-head-of-family-office/</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Firm describes itself as a single-family office investing permanent capital with no external limited partners, managing the assets of Narayana Murthy and family.</t>
+          <t>Described as the single-family office managing the assets of the Bettencourt Meyers family, majority shareholder of L'Oreal; Tethys Invest is the entrepreneurial-investment subsidiary.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bloomberg reporting naming it the family office of billionaire Narayana Murthy; firm's own 'About' page stating single-family-office / permanent-capital structure.</t>
+          <t>The National and Caproasia press naming Tethys as the Bettencourt family office; firm's own website.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -6798,12 +8163,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Not disclosed.</t>
+          <t>Press figure for total family assets (dominated by the L'Oreal stake); Tethys Invest deploys &gt;EUR 3bn of direct-investment capital.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Founder and ultimate principal; firm led operationally by Chairman M.D. Ranganath (ex-Infosys CFO) and President Deepak Padaki.</t>
+          <t>Head of the family's investment firm (Tethys Invest) and, per 2025 press, appointed to the L'Oreal board seat area of the family; family chair of Tethys is Francoise Bettencourt Meyers, CEO of Tethys is Jean-Pierre Meyers.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -6816,7 +8181,7 @@
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2025-08-26/family-office-to-billionaire-murthy-warns-on-startup-valuations</t>
+          <t>https://www.caproasia.com/2025/02/08/loreal-heiress-france-billionaire-francoise-bettencourt-meyers-age-71-with-76-billion-fortune-starts-family-succession-with-retirement-from-loreal-board-as-vice-chairman-son-jean-victo/</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
@@ -6824,37 +8189,37 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UKCH-10876208</t>
+          <t>SFO-cofra-holding-brenninkmeijer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SHA FAMILY OFFICE LTD</t>
+          <t>COFRA Holding AG</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>press</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Companies House 10876208 (Private limited company); inc. 20 July 2017</t>
+          <t>Identified via known UHNW family (Brenninkmeijer, owners of C&amp;A) -&gt; family holding/office. Confirmed by Crain Currency and the firm's own site as the Brenninkmeijer family's Zug-based holding; leadership verified on cofraholding.com.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/10876208</t>
+          <t>https://www.craincurrency.com/family-office-management/secretive-brenninkmeijer-family-behind-ca-opens-39-billion-retail-empire</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Mr Sharnpreet Singh Buttar); firm carries a fund-management/investment SIC (64205 - Activities of financial services holding companies). Single-family control of an investment vehicle = single-family office.</t>
+          <t>Established 2001 in Zug to coordinate the Brenninkmeijer family's global businesses and investments; a single-family-owned holding with subsidiaries C&amp;A (retail), Redevco (real estate), Bregal (PE) and Anthos (asset management).</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Mr Sharnpreet Singh Buttar); firm carries a fund-management/investment SIC (64205 - Activities of financial services holding companies). Single-family control of an investment vehicle = single-family office.</t>
+          <t>Crain Currency reporting on the family's ~$39bn empire; COFRA's own leadership/governance page listing the family-dominated board.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -6862,8 +8227,16 @@
           <t>corroborated</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Reported total group asset base (Crain Currency and familyofficehub).</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Family-member chairman since 2018 (former CEO of COFRA, C&amp;A Europe and Anthos); group CEO is Boudewijn Beerkens, CFO Florian Brenninkmeyer (from 2025).</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr">
         <is>
           <t>unresolved</t>
@@ -6872,52 +8245,64 @@
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>https://www.cofraholding.com/en/newsroom/latest-news/2025/redevco-closes-landmark-475m-loan-investment-for-new-real-estate-debt-platform/</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>UKCH-15240886</t>
+          <t>SFO-athos-strungmann</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FREEDMAN FAMILY OFFICE</t>
+          <t>Athos Service GmbH (family investment entity Athos KG)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>press</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Companies House 15240886 (Private unlimited company); inc. 27 October 2023</t>
+          <t>Identified via known UHNW family (Strungmann brothers, BioNTech's largest shareholders) -&gt; family office. Confirmed as their single-family office by Forbes and multiple family-office trade sources; recent dated direct investments corroborate activity.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/15240886</t>
+          <t>https://www.forbes.com/sites/paulwestall/2021/08/24/the-family-office-saving-lives-boosting-the-economy-and-making-billions/</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+          <t>Described as the single-family office of twins Andreas and Thomas Strungmann (who founded generics maker Hexal); anchor and largest shareholder of BioNTech (~43.5%).</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Samantha Jade Zimmerman; Laura-Leigh Freedman; Mrs Elaine Wilson Freedman); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+          <t>Forbes and biotech/family-office trade press naming Athos as the Strungmann single-family office; documented anchor investment in BioNTech.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Not disclosed; dominated by the BioNTech stake (~43.5%).</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Beneficial owner (with twin brother Thomas Strungmann) of the family office; jointly direct its investments.</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
           <t>unresolved</t>
@@ -6926,43 +8311,47 @@
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>https://familyofficehub.io/blog/athos-family-office-invests-in-aavantgarde-bios-141m-series-b/</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>UKCH-11031775</t>
+          <t>SFO-premji-invest</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RALPH FAMILY OFFICE LIMITED</t>
+          <t>Premji Invest</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>press</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Companies House 11031775 (Private limited company); inc. 25 October 2017</t>
+          <t>Identified via known UHNW individual (Azim Premji, Wipro founder) -&gt; family office. Confirmed as his family office by The Arc and family-office databases; recent dated deals corroborate active investing.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/11031775</t>
+          <t>https://www.thearcweb.com/article/wipro-azim-premji-invest-family-office-tk-kurien-0clyngtMEXrGHBNX</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Melanie Lynette Ralph; Mr Jan De Ridder Ralph); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+          <t>Described as the private investment office managing the portfolio of Wipro founder Azim Premji and family across public equities, PE and venture; founded 2006, offices in Bengaluru and Menlo Park.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>UK Companies House PSC register lists individual controllers sharing the firm's family name (Melanie Lynette Ralph; Mr Jan De Ridder Ralph); firm carries a fund-management/investment SIC (64301 - Activities of investment trusts). Single-family control of an investment vehicle = single-family office.</t>
+          <t>The Arc and multiple family-office databases identify Premji Invest as Azim Premji's family office; firm website.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -6970,8 +8359,16 @@
           <t>corroborated</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>The Arc reporting that the family office crossed $10bn in managed assets.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Chief executive and top investment decision-maker of the office (former Wipro CEO); family principal is Azim Premji; U.S. office led by Sandesh Patnam.</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>unresolved</t>
@@ -6980,8 +8377,898 @@
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>https://tracxn.com/d/private-equity/premjiinvest/__a9W9DN9hd7WxIGfm5z8PuA6IrDlu-VIas8-t59BU6xw</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SFO-catamaran-ventures-murthy</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Catamaran Management Services Pvt. Ltd. (Catamaran Ventures)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Identified via known UHNW individual (N.R. Narayana Murthy, Infosys founder) -&gt; family office. Confirmed as his single-family office by Bloomberg and the firm's own site; described as investing permanent capital with no external LPs.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/articles/2025-08-26/family-office-to-billionaire-murthy-warns-on-startup-valuations</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Firm describes itself as a single-family office investing permanent capital with no external limited partners, managing the assets of Narayana Murthy and family.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Bloomberg reporting naming it the family office of billionaire Narayana Murthy; firm's own 'About' page stating single-family-office / permanent-capital structure.</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Not disclosed.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Founder and ultimate principal; firm led operationally by Chairman M.D. Ranganath (ex-Infosys CFO) and President Deepak Padaki.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/articles/2025-08-26/family-office-to-billionaire-murthy-warns-on-startup-valuations</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>APAC-weybourne-holdings-dyson</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Weybourne Holdings Pte. Ltd. (Singapore parent; UK operating entity Weybourne Holdings Limited)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>apac-eu-registry</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Known UHNW founder (Sir James Dyson). Confirmed via Crain Currency and Asia News Network reporting on Weybourne restructuring its family-office empire and transferring funds to its Singapore holding company; Weybourne is repeatedly named as Dyson's single-family office.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://www.craincurrency.com/family-office-management/james-dyson-reworks-weybourne-family-office-empire-17-billion-fortune</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Reported by Crain Currency, Bloomberg (via WealthBriefing) and Asia News Network as Sir James Dyson's single-family office managing the family's ~USD17-21bn fortune; not an external multi-client manager.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Multiple reputable outlets (Crain Currency, Bloomberg/WealthBriefing, Asia News Network) describe Weybourne as the Dyson family office; Weybourne Holdings Pte Ltd is the Singapore-based parent of the UK family office with an insurance unit and 70+ staff across London and Singapore.</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Estimated family fortune cited by Crain Currency (~USD17bn) and Asia News Network (~USD21bn); Weybourne does not publish an AUM figure.</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Sir James Dyson is the family principal whose wealth the office manages; day-to-day the office is run by CEO Martin Bowen (appointed February 2025, succeeding James Bucknall).</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Private single-family office; no individual email address published in any source reviewed.</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>https://www.craincurrency.com/family-office-management/james-dyson-reworks-weybourne-family-office-empire-17-billion-fortune</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>APAC-dalio-family-office-singapore</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Dalio Family Office (Singapore office of the Dalio Family Office / DFO)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>apac-eu-registry</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Known UHNW founder (Ray Dalio, Bridgewater Associates). Confirmed via South China Morning Post, The Edge Singapore and Bloomberg reporting that Dalio opened a Singapore family office to run Asian investments and philanthropy.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://www.scmp.com/news/asia/southeast-asia/article/3111745/us-billionaire-ray-dalio-latest-open-family-office</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Reported by SCMP, The Edge Singapore and Bloomberg as the single-family office of Bridgewater founder Ray Dalio, established in Singapore in 2020 to manage his regional investments and philanthropy.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Multiple reputable outlets confirm the Dalio Family Office (DFO) opened a Singapore office in 2020; Caproasia documents a Singapore Managing Director (Tan Mae Shen, joined 2021) and shophouse purchases in Singapore linked to Dalio.</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>No DFO AUM disclosed; Dalio's personal fortune is widely reported but not a family-office AUM figure.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Ray Dalio is the family principal. Janine Racanelli is global CEO of the Dalio Family Office; Tan Mae Shen (ex-JPMorgan/Credit Suisse) has been reported as Singapore Managing Director since 2021.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Private single-family office; no individual email address published in any source reviewed.</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>https://www.caproasia.com/2024/05/23/154-billion-bridgewater-associates-hedge-fund-founder-ray-dalio-bought-2-shophouses-in-singapore-club-street-in-2021-for-18-9-million-dalio-family-office-singapore-managing-director-tan-mae-shen-li/</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>APAC-sunrise-capital-shu-ping</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Sunrise Capital Management Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>apac-eu-registry</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Known UHNW founder (Shu Ping, Haidilao co-founder). Confirmed via Bloomberg, South China Morning Post and Caixin Global reporting that Shu Ping opened a Singapore family office (Sunrise Capital Management), of which she is sole shareholder and director, to manage her fortune.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://www.scmp.com/business/article/3065092/haidilao-hotpot-queen-opens-singapore-family-office-manage-us77-billion</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Bloomberg ('Hotpot Queen Opens Family Office in Singapore to Manage Wealth'), SCMP and Caixin all describe Sunrise Capital Management as the single-family office set up to manage Shu Ping's ~USD7.7bn fortune; she is sole shareholder and director.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Reputable press (Bloomberg, SCMP, Caixin Global) name the entity as Shu Ping's family office established in 2019/2020.</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Family wealth figure cited by SCMP/Bloomberg/Caixin at the office's launch (2020); not an audited FO AUM.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Shu Ping is the family principal and, per press, the sole shareholder and director of Sunrise Capital Management.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Private single-family office; no individual email address published in any source reviewed.</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>https://www.bloomberg.com/news/articles/2020-03-04/hotpot-queen-opens-family-office-in-singapore-to-manage-wealth</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>APAC-tsao-family-office-tpc</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Tsao Pao Chee (TPC) Group — Tsao Family Office (investment arm; OCTAVE brand)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>apac-eu-registry</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Known Singapore business family (Tsao family, IMC Group maritime dynasty). Confirmed via Preqin single-family-office profile and the family's own TPC/Tsao Pao Chee and OCTAVE websites describing the Tsao Family Office as the strategic investment arm of the group.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://www.preqin.com/data/profile/investor/tsao-family-office/246728</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Preqin classifies the Tsao Family Office as a single-family office based in Singapore; the family's TPC/OCTAVE sites describe it as the investment arm of the Tsao family (IMC Group), an integrated maritime and industrial group founded 1906.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Preqin single-family-office profile plus the family's own corporate sites (tsaopaochee.com, octaveinvestment.com) confirm a family-owned investment office.</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>No public AUM figure disclosed by the family office in sources reviewed.</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Chavalit Tsao is the current family principal and chairman leading the group and its investment/impact activities.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No individual published email located; group contact channels are via corporate websites only.</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>https://tsaopaochee.com/our-brands/octave/</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>APAC-wee-investments-uob</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Wee Investments Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>apac-eu-registry</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Known Singapore banking dynasty (Wee family, controllers of UOB). Confirmed via Forbes and VnExpress International reporting on the Wee family's investment vehicles, corroborated by family-office directories (Altss, PipelineRoad) identifying Wee Investments as the Wee Cho Yaw family office.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>https://www.forbes.com/profile/wee-1/</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Family-office directories (Altss, PipelineRoad) identify Wee Investments as the single-family office of the Wee family (founded by Wee Cho Yaw, builder of UOB); Forbes and VnExpress document the family's concentrated holdings in UOB, UOL, Haw Par and Kheng Leong managed through family vehicles.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Corroborating reputable coverage (Forbes, VnExpress) of the Wee family's wealth plus specialised FO directories naming Wee Investments as the family office.</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>No AUM disclosed; family fortune is multi-billion (Forbes) but the family office does not publish AUM.</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Following founder Wee Cho Yaw's death in February 2024, family principals Wee Ee Cheong, Wee Ee Chao and Wee Ee Lim oversee the family's allocations; Wee Ee Cheong leads UOB.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Private single-family office; no individual email published in any source reviewed.</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>https://www.forbes.com/sites/jonathanburgos/2024/05/14/billionaire-wee-familys-uol-offers-top-bid-of-595-million-for-prime-singapore-site/</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>APAC-ee-capital-saverin</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>EE Capital Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>apac-eu-registry</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Known UHNW resident (Eduardo Saverin, Facebook co-founder and Singapore's richest man). Identified as his single-family office via Preqin's SFO profile and Citywire Selector coverage of Singapore's family-office scene; corroborated by FO directory Altss.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://www.preqin.com/data/profile/investor/ee-capital/229861</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Preqin and Altss both classify EE Capital as a Singapore single-family office managing the assets of Eduardo Saverin; Saverin's wife Elaine Andriejanssen is described as Executive Chairman of EE Capital Pte Ltd.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Preqin single-family-office profile plus Citywire Selector and Altss identify EE Capital as Saverin's family office (private/public investments across sectors).</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>No FO AUM disclosed; Saverin's personal net worth is reported by Forbes (&gt;USD30bn) but is not an EE Capital AUM figure.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Eduardo Saverin is the family principal whose wealth EE Capital manages; his wife Elaine Andriejanssen is reported as Executive Chairman of EE Capital Pte Ltd.</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Private single-family office; no individual email address published in any source reviewed.</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>https://www.forbes.com/sites/naazneenkarmali/2023/09/06/singapores-50-richest-2023-facebook-cofounder-eduardo-saverin-is-new-no-1-as-combined-wealth-rises-8-to-177-billion/</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>APAC-wuthelam-holdings-goh</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Wuthelam Holdings Pte. Ltd.</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>apac-eu-registry</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Known Singapore business family (Goh family, controllers of Nippon Paint via Wuthelam). Confirmed via Nikkei Asia and Forbes reporting that Wuthelam Holdings is the Goh family's investment vehicle/family office; corroborated by The Independent/Mothership coverage of the 2024 inheritance transfer.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://asia.nikkei.com/business/business-deals/how-singapore-s-wuthelam-turned-the-tables-on-nippon-paint</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Described in reporting as the Singapore-based investment vehicle that combines all private wealth and investment activities of the late Goh Cheng Liang (Singapore's richest man) and his family, serving as the family's single-family office; controls a majority stake in Tokyo-listed Nippon Paint Holdings.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Reputable outlets (Nikkei Asia, Forbes, Bloomberg Billionaires Index) treat Wuthelam Holdings as the Goh family's private holding/family-office vehicle.</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>No FO AUM disclosed; the family's Nippon Paint stake and fortune are multi-billion (Forbes/Bloomberg) but not published as a family-office AUM.</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Following the founder's death in August 2025, Goh Hup Jin is the leading family principal, chairing Nippon Paint and serving as a Wuthelam group executive director.</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Private family holding company; no individual email published in any source reviewed.</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>https://mothership.sg/2025/09/goh-cheng-liang-grandchildren-billionaires/</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SFO-cascade-investment-gates</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Cascade Investment, L.L.C.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Identified via known UHNW individual (Bill Gates) -&gt; family office entity. Confirmed as Gates's private investment vehicle and an active SEC 13F filer (Cascade Investment, L.L.C., CIK 0001052192, Kirkland WA), with Michael Larson as Manager who also exercises investment discretion for the Gates Foundation Trust.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.danielscrivner.com/bill-gates-trades-and-holdings-q2-2025/</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Cascade Investment is the private investment vehicle managing the personal wealth of Microsoft co-founder Bill Gates (and, via the same manager Michael Larson, the assets of the Gates Foundation Trust). No external clients; single-family (Gates) capital.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>SEC EDGAR 13F-HR filings under CIK 0001052192 (Cascade Investment, L.L.C., 2365 Carillon Point, Kirkland WA), most recent Q2 2025 13F filed 2025-08-14; historical filings run 2002-present.</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Not officially disclosed; press estimates the combined Gates/Cascade portfolio in the tens of billions. 13F-reported U.S. equities are a subset of total assets.</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Beneficial owner; Cascade exists to manage his and the Gates Foundation Trust's assets. Day-to-day investment chief is Manager Michael Larson.</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>https://www.danielscrivner.com/bill-gates-trades-and-holdings-q2-2025/</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SFO-willett-advisors-bloomberg</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Willett Advisors LLC</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Identified via known UHNW individual (Michael Bloomberg) -&gt; family office entity. Confirmed as Bloomberg's family office by Wikipedia and multiple family-office trade sources; SEC EDGAR shows a registered 13F filer (CIK 0001509379) though filings ceased after 2014.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Willett_Advisors</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Described as the investment firm serving as the family office of Michael Bloomberg (founder of Bloomberg L.P., former NYC mayor); manages his personal assets and the assets of Bloomberg Philanthropies. Founded 2010.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Wikipedia and family-office trade press (familyofficehub, altss) name Willett Advisors as Michael Bloomberg's family office; SEC EDGAR registration as a 13F filer (CIK 0001509379).</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Widely reported managed-asset figure (Wikipedia/trade press) covering Bloomberg's personal and philanthropic assets; not an official disclosure.</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Beneficial owner; office manages his personal and philanthropic assets. Day-to-day Chairman and CEO is Steven Rattner.</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Willett_Advisors</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SFO-soros-fund-management</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Soros Fund Management LLC</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Identified via known UHNW individual (George/Alex Soros) -&gt; family office. Confirmed as the Soros family office (converted from hedge fund to family office after returning outside capital in 2011) by Wikipedia and Institutional Investor; active SEC 13F filer (CIK 0001029160).</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Soros_Fund_Management</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Founded 1970 by George Soros as a hedge fund; returned all outside investor capital in 2011 and has since operated as the Soros family office and the principal asset manager for the Open Society Foundations. No external LPs.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Wikipedia and Institutional Investor describe it as the Soros family office; active SEC EDGAR 13F-HR filings under CIK 0001029160 (latest reported Q1 2026, as of 2026-03-31).</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Widely reported total AUM (~$25-28bn) for the family office; 13F-reported U.S. equities (~$9bn, Q1 2026) are a subset.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Founder and beneficial principal; in 2023 handed control of the family's ~$25bn foundation to son Alex Soros, who chairs the Open Society Foundations and sits on the Soros Fund Management investment committee.</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>https://fintool.com/app/research/funds/family-offices/soros-fund-management-llc</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SFO-bezos-expeditions</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Bezos Expeditions (Zefram LLC / Nash Holdings affiliated vehicles)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Identified via known UHNW individual (Jeff Bezos) -&gt; family office. Confirmed as Bezos's personal investment vehicle by Wikipedia and multiple family-office trade sources; makes venture/direct investments rather than filing 13F.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Bezos_Expeditions</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Founded 2005 by Jeff Bezos to manage his personal venture and direct investments; described as the single-family office of the Amazon founder. Single-family (Bezos) capital, no external LPs.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Wikipedia entry and family-office trade press (familyofficehub, PipelineRoad) identify Bezos Expeditions as Jeff Bezos's family office/personal investment vehicle.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Not disclosed; trade-press figures conflate the vehicle with Bezos's total net worth and are unreliable.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Beneficial owner and founder; the vehicle exists to manage his personal investments.</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>https://en.wikipedia.org/wiki/Bezos_Expeditions</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SFO-pritzker-organization</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>The Pritzker Organization, L.L.C.</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>press</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Identified via known UHNW family (Pritzker) -&gt; family office. Confirmed by the firm's own website (pritzkerorg.com) and Crain's Chicago Business as the merchant-bank/family office managing the assets of Tom Pritzker and the extended Pritzker family.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>https://pritzkerorg.com/about-us/</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>The firm's own site traces its lineage to Pritzker &amp; Pritzker (1902), evolving into a merchant bank for the family's holdings and renamed The Pritzker Organization in the 1990s; described as the family office led by Tom Pritzker managing the extended Pritzker family's assets with permanent capital.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Firm website (pritzkerorg.com About page) plus Crain's Chicago Business reporting on the Pritzker family office launching a venture fund.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Not disclosed; the broader Pritzker family fortune is multi-billion but is split across several distinct Pritzker vehicles.</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Family principal and long-time head of the organization (40+ years); executive chairman of Hyatt Hotels Corporation.</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>https://www.chicagobusiness.com/finance-banking/pritzker-family-office-launches-venture-capital-fund</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6994,13 +9281,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="47" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -7223,7 +9510,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BANK OF MONTREAL /CAN/</t>
+          <t>Auxilium Family Office Limited</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -7234,7 +9521,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -7257,7 +9544,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -7269,7 +9556,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BRYN MAWR BANK CORP</t>
+          <t>BANK OF MONTREAL /CAN/</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -7280,7 +9567,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -7303,7 +9590,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -7315,7 +9602,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Biltmore Family Office, LLC</t>
+          <t>BRYN MAWR BANK CORP</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -7326,7 +9613,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -7338,7 +9625,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CAMBIENT FAMILY OFFICE, LLC</t>
+          <t>Biltmore Family Office, LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -7361,7 +9648,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CAROLINE BAKER FAMILY OFFICE LIMITED</t>
+          <t>CAMBIENT FAMILY OFFICE, LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -7384,7 +9671,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CK PROPERTIES AND FAMILY OFFICE LIMITED</t>
+          <t>CAROLINE BAKER FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -7407,7 +9694,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>COLLECTIVE FAMILY OFFICE LLC</t>
+          <t>CK PROPERTIES AND FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -7430,7 +9717,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CVA Family Office, LLC</t>
+          <t>COLLECTIVE FAMILY OFFICE LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -7453,7 +9740,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capitol Family Office, Inc.</t>
+          <t>CVA Family Office, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7476,7 +9763,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Crestone Asset Management LLC</t>
+          <t>Capitol Family Office, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -7510,7 +9797,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -7522,7 +9809,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Crew Family Office Limited</t>
+          <t>Crestone Asset Management LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -7533,7 +9820,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -7660,7 +9947,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DAO FAMILY OFFICE LP</t>
+          <t>Crew Family Office Limited</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -7671,7 +9958,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -7683,7 +9970,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DAVIDOFF FREY FAMILY OFFICE (UK) LTD</t>
+          <t>DAO FAMILY OFFICE LP</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -7706,7 +9993,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DE VILLIERS FAMILY OFFICE LIMITED</t>
+          <t>DAVIDOFF FREY FAMILY OFFICE (UK) LTD</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -7729,7 +10016,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DEUTSCHE BANK AG\</t>
+          <t>DE VILLIERS FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -7763,7 +10050,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -7775,7 +10062,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DONE FAMILY OFFICE LIMITED</t>
+          <t>DEUTSCHE BANK AG\</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -7786,7 +10073,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -7798,7 +10085,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DONNELLY FAMILY OFFICE</t>
+          <t>DONE FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -7821,7 +10108,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DSW FAMILY OFFICE LTD</t>
+          <t>DONNELLY FAMILY OFFICE</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -7844,7 +10131,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DUBAI FAMILY OFFICE LTD</t>
+          <t>DSW FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -7867,7 +10154,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Dorsey &amp; Whitney Trust CO LLC</t>
+          <t>DUBAI FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -7901,7 +10188,7 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -7913,7 +10200,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EMFO, LLC</t>
+          <t>Dorsey &amp; Whitney Trust CO LLC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -7924,7 +10211,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -7947,7 +10234,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -7959,7 +10246,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FAMILY OFFICE CONSULTING LIMITED</t>
+          <t>EMFO, LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -7970,7 +10257,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -7982,7 +10269,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FAMILY OFFICE EEB LTD</t>
+          <t>FAMILY OFFICE CONSULTING LIMITED</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -8005,7 +10292,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FIDUCIARY FAMILY OFFICE, LLC</t>
+          <t>FAMILY OFFICE EEB LTD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -8028,7 +10315,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FOOTPRINTS FAMILY OFFICE UK EUROPE LIMITED</t>
+          <t>FIDUCIARY FAMILY OFFICE, LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8051,7 +10338,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FREEDMAN FAMILY OFFICE</t>
+          <t>FOOTPRINTS FAMILY OFFICE UK EUROPE LIMITED</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -8074,7 +10361,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FRIGUS FAMILY OFFICE LTD</t>
+          <t>FREEDMAN FAMILY OFFICE</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -8097,7 +10384,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FRONTIER FAMILY OFFICE FORUM HOLDINGS LIMITED</t>
+          <t>FRIGUS FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -8120,7 +10407,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Family Investment Center, Inc.</t>
+          <t>FRONTIER FAMILY OFFICE FORUM HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -8154,7 +10441,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -8166,7 +10453,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Family Office DS Limited</t>
+          <t>Family Investment Center, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -8177,7 +10464,7 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -8304,7 +10591,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Family Office Research LLC</t>
+          <t>Family Office DS Limited</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -8315,7 +10602,7 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -8327,7 +10614,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Family Office Research, LLC</t>
+          <t>Family Office Research LLC</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -8338,7 +10625,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -8350,7 +10637,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fortis Advisors, LLC</t>
+          <t>Family Office Research, LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -8361,7 +10648,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -8384,7 +10671,7 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -8396,7 +10683,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Fortitude Family Office, LLC</t>
+          <t>Fortis Advisors, LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -8407,7 +10694,7 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -8419,7 +10706,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GELLING FAMILY OFFICE LIMITED</t>
+          <t>Fortitude Family Office, LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -8442,7 +10729,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GUNPUTH FAMILY OFFICE LIMITED</t>
+          <t>GELLING FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -8465,7 +10752,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Geller Advisors LLC</t>
+          <t>GUNPUTH FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -8499,7 +10786,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -8511,7 +10798,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>HALL LAURIE J TRUSTEE</t>
+          <t>Geller Advisors LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -8522,7 +10809,7 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -8545,7 +10832,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -8557,7 +10844,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>HBBA FAMILY OFFICE LIMITED</t>
+          <t>HALL LAURIE J TRUSTEE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -8568,7 +10855,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -8580,7 +10867,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HILL FAMILY OFFICE LIMITED</t>
+          <t>HBBA FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -8603,7 +10890,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
+          <t>HBBA Family Office Limited</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -8614,7 +10901,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -8626,7 +10913,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
+          <t>HILL FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -8637,7 +10924,7 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -8649,7 +10936,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>INTREPID FAMILY OFFICE LLC</t>
+          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -8672,7 +10959,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ISHER CAPITAL FAMILY OFFICE LTD</t>
+          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -8683,7 +10970,7 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -8695,7 +10982,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Independent Family Office, LLC</t>
+          <t>INTREPID FAMILY OFFICE LLC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -8718,7 +11005,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Kopp Family Office, LLC</t>
+          <t>ISHER CAPITAL FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -8741,7 +11028,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LELS CLARK FAMILY OFFICE LTD</t>
+          <t>Independent Family Office, LLC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -8764,7 +11051,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Lido Advisors, LLC</t>
+          <t>Kopp Family Office, LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -8787,7 +11074,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lido Advisors, LLC</t>
+          <t>LELS CLARK FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -8798,7 +11085,7 @@
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -8810,7 +11097,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>MARCUARD FAMILY OFFICE LTD</t>
+          <t>Lido Advisors, LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -8833,7 +11120,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>MOBH UK FAMILY OFFICE LTD</t>
+          <t>Lido Advisors, LLC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -8844,7 +11131,7 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -8856,7 +11143,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NORTHBRIDGE FAMILY OFFICE LTD</t>
+          <t>MARCUARD FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -8879,7 +11166,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NOVA FAMILY OFFICE LTD</t>
+          <t>MOBH UK FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -8902,7 +11189,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Nilsson Family Office Ltd</t>
+          <t>NORTHBRIDGE FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -8913,7 +11200,7 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -8925,7 +11212,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nilsson Family Office Ltd</t>
+          <t>NOVA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -8936,7 +11223,7 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -9040,7 +11327,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>OLD HOUSE FAMILY OFFICE LIMITED</t>
+          <t>Nilsson Family Office Ltd</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -9051,7 +11338,7 @@
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -9063,7 +11350,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>OneAscent Family Office, LLC</t>
+          <t>Nilsson Family Office Ltd</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -9074,7 +11361,7 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -9086,7 +11373,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Orion Porfolio Solutions, LLC</t>
+          <t>OLD HOUSE FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -9109,7 +11396,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Orion Porfolio Solutions, LLC</t>
+          <t>OneAscent Family Office, LLC</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -9120,7 +11407,7 @@
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -9132,7 +11419,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Orion Portfolio Solutions, LLC</t>
+          <t>Orion Porfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -9155,7 +11442,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Orion Portfolio Solutions, LLC</t>
+          <t>Orion Porfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -9178,7 +11465,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>PANDA FAMILY OFFICE LTD</t>
+          <t>Orion Portfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -9201,7 +11488,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PANTHEON A FAMILY OFFICE LIMITED</t>
+          <t>Orion Portfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -9212,7 +11499,7 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -9224,7 +11511,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PATHSTONE FAMILY OFFICE, LLC</t>
+          <t>PANDA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -9247,7 +11534,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PMG Family Office LLC</t>
+          <t>PANTHEON A FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -9270,7 +11557,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PROSPERITY FAMILY OFFICE LIMITED</t>
+          <t>PATHSTONE FAMILY OFFICE, LLC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -9293,7 +11580,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Pathstone Holdings, LLC</t>
+          <t>PMG Family Office LLC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -9316,7 +11603,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Pathstone Holdings, LLC</t>
+          <t>PROSPERITY FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -9327,7 +11614,7 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -9339,7 +11626,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Pioneer Family Office, LLC</t>
+          <t>Pathstone Holdings, LLC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -9362,7 +11649,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>RALPH FAMILY OFFICE LIMITED</t>
+          <t>Pathstone Holdings, LLC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -9373,7 +11660,7 @@
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -9385,7 +11672,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SHA FAMILY OFFICE LTD</t>
+          <t>Pioneer Family Office, LLC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -9408,7 +11695,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SIGNATURE FAMILY OFFICE LTD</t>
+          <t>RALPH FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -9431,7 +11718,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SIMON FAMILY OFFICE INSURES LIMITED</t>
+          <t>SHA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -9454,7 +11741,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SWAILES COMMERCIAL FAMILY OFFICE LTD</t>
+          <t>SIGNATURE FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -9477,7 +11764,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SWAILES TRADING GROUP FAMILY OFFICE LTD</t>
+          <t>SIMON FAMILY OFFICE INSURES LIMITED</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -9500,7 +11787,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Sageworth Trust Co</t>
+          <t>SWAILES COMMERCIAL FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -9523,7 +11810,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Sageworth Trust Co</t>
+          <t>SWAILES TRADING GROUP FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -9534,7 +11821,7 @@
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -9546,7 +11833,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Standard Family Office LLC</t>
+          <t>Sageworth Trust Co</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -9569,7 +11856,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Stenger Family Office, LLC</t>
+          <t>Sageworth Trust Co</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -9580,7 +11867,7 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -9592,7 +11879,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Stokes Family Office, LLC</t>
+          <t>Standard Family Office LLC</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -9615,7 +11902,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>THE DIGITAL FAMILY OFFICE LIMITED</t>
+          <t>Stenger Family Office, LLC</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -9638,7 +11925,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>THE FAMILY OFFICE CHELTENHAM LIMITED</t>
+          <t>Stokes Family Office, LLC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -9661,7 +11948,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>TIGRIS FAMILY OFFICE LIMITED</t>
+          <t>THE DIGITAL FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -9684,7 +11971,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Tarbox Family Office, Inc.</t>
+          <t>THE FAMILY OFFICE CHELTENHAM LIMITED</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -9707,22 +11994,18 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Tarbox Family Office, Inc.</t>
+          <t>TIGRIS FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>principal_email</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>laura@tarbox.com</t>
-        </is>
-      </c>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>email not found at cited source on re-fetch (https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf); downgraded verified-&gt;unverified</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -9739,17 +12022,13 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>principal_email</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>laura@tarbox.com</t>
-        </is>
-      </c>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>email not found at cited source on re-fetch (https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf); downgraded verified-&gt;unverified</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -9842,18 +12121,22 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Timonier Family Office, LTD.</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>firm-qualification</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
+          <t>principal_email</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>laura@tarbox.com</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>email not found at cited source on re-fetch (https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf); downgraded verified-&gt;unverified</t>
         </is>
       </c>
     </row>
@@ -9865,18 +12148,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TrustBank</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>firm-qualification</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
+          <t>principal_email</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>laura@tarbox.com</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>email not found at cited source on re-fetch (https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf); downgraded verified-&gt;unverified</t>
         </is>
       </c>
     </row>
@@ -9888,18 +12175,22 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>TrustBank</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>firm-qualification</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
+          <t>principal_email</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>laura@tarbox.com</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>email not found at cited source on re-fetch (https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf); downgraded verified-&gt;unverified</t>
         </is>
       </c>
     </row>
@@ -9911,7 +12202,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>UNITA FAMILY OFFICE UK LIMITED</t>
+          <t>The Family Office Cheltenham Limited</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -9922,7 +12213,7 @@
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -9934,7 +12225,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>UR FAMILY OFFICE MANAGEMENT SERVICES LTD</t>
+          <t>Timonier Family Office, LTD.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -9957,18 +12248,22 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>VASIL FAMILY OFFICE LLP</t>
+          <t>Timonier Family Office, LTD.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>firm-qualification</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>principal_email</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>timonier@timonier.com</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>firm-name mailbox wrongly matched (tim in timonier); removed - not an individual email</t>
         </is>
       </c>
     </row>
@@ -9980,7 +12275,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>VPR Management LLC</t>
+          <t>TrustBank</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -10003,7 +12298,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>VPR Management LLC</t>
+          <t>TrustBank</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -10026,7 +12321,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>VSTAR LONDON FAMILY OFFICE LTD</t>
+          <t>UNITA FAMILY OFFICE UK LIMITED</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -10049,7 +12344,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Veritable, L.P.</t>
+          <t>UR FAMILY OFFICE MANAGEMENT SERVICES LTD</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -10072,7 +12367,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Veritable, L.P.</t>
+          <t>VASIL FAMILY OFFICE LLP</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -10083,7 +12378,7 @@
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -10095,7 +12390,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Virtus Family Office LLC</t>
+          <t>VPR Management LLC</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -10118,7 +12413,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>WEYBRIDGE FAMILY OFFICE SERVICES LIMITED</t>
+          <t>VPR Management LLC</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -10129,7 +12424,7 @@
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -10141,7 +12436,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Wealthgate Family Office, LLC</t>
+          <t>VSTAR LONDON FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -10164,7 +12459,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Wilmington Savings Fund Society, FSB</t>
+          <t>Veritable, L.P.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -10187,7 +12482,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Wilmington Savings Fund Society, FSB</t>
+          <t>Veritable, L.P.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -10197,6 +12492,121 @@
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
+        <is>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Virtus Family Office LLC</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>WEYBRIDGE FAMILY OFFICE SERVICES LIMITED</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Wealthgate Family Office, LLC</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Wilmington Savings Fund Society, FSB</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Wilmington Savings Fund Society, FSB</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
         <is>
           <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
@@ -10213,7 +12623,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -10249,7 +12659,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>34%</t>
         </is>
       </c>
     </row>
@@ -10260,51 +12670,66 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>16%</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>apac-eu-registry</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>8</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>press</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>11</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Total qualified in store</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>50</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-    </row>
+      <c r="B5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Total qualified in store</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>71</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Selected into final</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>37</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="B8" t="n">
+        <v>50</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/final/family_office_dataset.xlsx
+++ b/data/final/family_office_dataset.xlsx
@@ -444,7 +444,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="49" customWidth="1" min="11" max="11"/>
     <col width="60" customWidth="1" min="12" max="12"/>
-    <col width="49" customWidth="1" min="13" max="13"/>
+    <col width="26" customWidth="1" min="13" max="13"/>
     <col width="32" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>United Kingdom (registered); Iceland (group HQ)</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -5182,7 +5182,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5279,7 +5279,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5384,7 +5384,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5578,7 +5578,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">

--- a/data/final/family_office_dataset.xlsx
+++ b/data/final/family_office_dataset.xlsx
@@ -1789,12 +1789,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SFO-grok-ventures-cannon-brookes</t>
+          <t>SFO-dfo-management-dell</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Grok Ventures (Cannon-Brookes Family Office)</t>
+          <t>DFO Management (Dell Family Office)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1804,53 +1804,53 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cannon-Brookes family (Mike Cannon-Brookes, co-founder of Atlassian)</t>
+          <t>Dell family (Michael Dell, founder/CEO of Dell Technologies)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.grok.ventures/</t>
+          <t>https://www.dellfamilyoffice.com/</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/grok-ventures</t>
+          <t>https://www.linkedin.com/company/dfo-management</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sydney-based single-family office of Atlassian co-founder Mike Cannon-Brookes. One of Australia's most prominent family offices, it has increasingly concentrated on climate and clean-technology investing (backing SunCable's Australia-Asia Power Link, battery and decarbonisation ventures) alongside a diversified portfolio; in early 2026 it announced a climate-only investment focus.</t>
+          <t>Private investment firm managing the assets of Michael Dell and family across public equities, private equity, real estate and other asset classes. Originally MSD Capital (1998); the multi-client business became BDT &amp; MSD Partners while the family's captive vehicle was rebranded DFO Management at end of 2022.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Mission-driven investing to accelerate decarbonisation and net-zero, via venture and direct stakes in climate/clean-tech, energy and enabling technologies.</t>
+          <t>Multi-asset-class permanent capital: public equities, private equity/credit, real estate, opportunistic direct investments.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Climate tech, clean energy/renewables, batteries, decarbonisation, technology venture</t>
+          <t>Diversified (consumer, real estate, financials, industrials)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Sydney</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>New South Wales</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Mike Cannon-Brookes</t>
+          <t>Michael Dell</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1858,26 +1858,26 @@
           <t>Founder / Family Principal</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/mikecannonbrookes</t>
-        </is>
-      </c>
+      <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>212-303-1668</t>
+        </is>
+      </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Announced climate-only investment focus and appointment of CEO Tan Kueh (Jan 2026); latest investment Asterix Foods seed round (2025-10-08); portfolio exit of Cog (2025-03-03); long-running backing of SunCable.</t>
+          <t>13F-HR filed 2026-05-15 (period ending 2026-03-31) disclosing U.S. equity holdings; rebrand from MSD Capital to DFO Management completed end of 2022.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-01; 2025-10-08; 2025-03-03</t>
+          <t>2026-05-15; 2022-12</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1887,110 +1887,102 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>principal_linkedin is the plausible public Mike Cannon-Brookes /in/ profile but not verified to explicitly list Grok Ventures (marked unconfirmed). Website domain (grok.ventures) asserted from press, not independently fetched. Mike and Annie Cannon-Brookes separated (2023); the office remains Mike's family office.</t>
+          <t>The 13F is filed in the name of the Michael &amp; Susan Dell Foundation with DFO Management as manager; the foundation and the family office are affiliated. AUM not disclosed. Michael Dell is a public figure; no personal LinkedIn tied specifically to DFO confirmed. 13F-HR (2026-05-15) signed by Marc R. Lisker (Treasurer, Michael &amp; Susan Dell Foundation) — a verified professional contact at the office in addition to the family principal.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEC13F-0001599603</t>
+          <t>SFO-blue-pool-capital-tsai</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tarbox Family Office, Inc.</t>
+          <t>Blue Pool Capital (Joe Tsai Family Office)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>None as a single client family; founder-owned firm (Laura Tarbox founder, CEO and principal owner). Namesake is the founder, not a served family.</t>
+          <t>Tsai family (Joseph Tsai, Alibaba co-founder and chairman)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://tarbox.com/</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/tarboxfamilyoffice</t>
-        </is>
-      </c>
+          <t>https://www.bluepoolcapital.com/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Newport Beach, CA-based multi-family office and SEC-registered investment adviser founded in 1985 by Laura Tarbox, CFP. Fee-only firm serving 100+ HNW/UHNW client families (also charities, businesses, trusts/estates) with comprehensive financial planning, tax preparation and individualized investment management; $5M minimum, over $1B AUM. Also has a Scottsdale, AZ office.</t>
+          <t>Hong Kong-based investment firm overseeing the Tsai family's wealth across hedge funds, private equity, private credit, venture and sports assets (Brooklyn Nets, LAFC). Raised ~$1bn for its first dedicated PE vehicle (Riverside Fund) reported 2026. Led by CEO Oliver Weisberg (ex-Goldman Sachs, ex-Citadel).</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Team-based, individualized asset allocation and investment management integrated with comprehensive financial and estate planning; fee-only fiduciary model.</t>
+          <t>Multi-strategy long-term capital: public markets, PE, private credit, venture, and sports/real assets.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Diversified asset-allocation / individualized investment management; no single-sector focus.</t>
+          <t>Diversified; technology (SpaceX, Epic Games, ByteDance), consumer/luxury (Golden Goose), sports, Japanese real estate</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Over $1 billion (100+ client families)</t>
+          <t>~$50 billion</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>NEWPORT BEACH</t>
+          <t>Causeway Bay</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>Hong Kong Island</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Laura Tarbox</t>
+          <t>Joseph Tsai</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Founder, CEO &amp; principal owner (CFP)</t>
+          <t>Family Principal / Founder</t>
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>laura@tarbox.com</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>(949) 721-2330</t>
+          <t>852-2825-9025</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Founded 1985; CFP since 1984; 100+ client families and &gt;$1B AUM; $5M account minimum; second office in Scottsdale, AZ; Laura Tarbox a frequent WSJ/NYT/LA Times media source</t>
+          <t>13F-HR filed 2026-05-15; sold ~83% of Blue Owl Capital stake (~$460m) reported 2024-03; joined consortium buying Burgundy vineyards 2024-09; raised ~$1bn first PE fund (Riverside) reported 2026-03-31.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>1985 (founded); 1984 (Laura Tarbox CFP)</t>
+          <t>2026-05-15; 2024-03-03; 2024-09-19; 2026-03-31</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -2000,69 +1992,61 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Personal LinkedIn /in profile not located (only firm company page). Email captured from Laura Tarbox's public presentation PDF (matches firm domain) rather than the current bio page; treat as published-but-unverified.</t>
+          <t>Some sources describe Blue Pool as a 'multi-family' vehicle co-backed by former Alibaba executives (and occasionally link Jack Ma); primary characterization is Joe Tsai's family office. Website confirmed to be minimal/uninformative per Crain Currency; bluepoolcapital.com domain asserted from press but not independently fetched. 13F-HR (2026-05-15) signed by Henry Li (Director) — a verified professional contact at the office in addition to the family principal.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEC13F-0002056106</t>
+          <t>SFO-willett-advisors-bloomberg</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stenger Family Office, LLC</t>
+          <t>Willett Advisors (Michael Bloomberg Family Office)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Stenger family (firm founded/led by Nick Stenger; the family has advised clients since 1981). The 'family' is the owner-operator, not a single client family.</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://www.stengerfamilyoffice.com/</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/stenger-family-office</t>
-        </is>
-      </c>
+          <t>Bloomberg family (Michael R. Bloomberg, founder of Bloomberg L.P.)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Naperville, IL-based multi-family office / independent fiduciary RIA led by founder-CEO Nick Stenger, offering financial planning, investment management, and (via related companies) tax preparation, estate strategies and insurance. Also has a Spring, TX office. ~$731M AUM; named a Forbes Best-in-State Wealth Advisor 2026.</t>
+          <t>New York-based investment firm serving as Michael Bloomberg's family office, managing his personal wealth and the assets of Bloomberg Philanthropies across public markets, hedge funds, private equity and credit, real assets and direct investments. Chaired and led by former U.S. auto-industry adviser and Quadrangle co-founder Steven Rattner.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Goals-based planning: assesses cash needs and upcoming goals, then builds customized portfolios.</t>
+          <t>Multi-asset, alternatives-heavy allocation (private equity/credit, hedge funds, real assets) for combined personal and philanthropic capital.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Core individual-stock portfolios and ETF-based asset-allocation portfolios; no single-sector focus.</t>
+          <t>Diversified; private equity/credit, hedge funds, real assets, public equities</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>~$731 million (as of 2026-06-30)</t>
+          <t>~$25 billion</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>NAPERVILLE</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2072,38 +2056,34 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Nicholas David Stenger</t>
+          <t>Michael R. Bloomberg</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Founder &amp; Chief Executive Officer</t>
+          <t>Family Principal / Beneficial Owner</t>
         </is>
       </c>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>nick.stenger@stengerfamilyoffice.com</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>630-912-8295</t>
+          <t>212-205-0100</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>$731M AUM (2026-06-30); Forbes Best-in-State Wealth Advisor 2026; hosts 'The Nick Stenger Show' podcast; opened Spring, TX office</t>
+          <t>Ongoing management of Bloomberg's personal + Bloomberg Philanthropies assets under Chairman/CEO Steven Rattner (per Wikipedia/trade press, current).</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2026-06-30 (AUM date); 2026 (Forbes Best-in-State)</t>
+          <t>2010 (founded); leadership current per 2026 profiles</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2113,69 +2093,69 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Serves 1,200+ families 'of all net worth sizes' — a broad wealth-management RIA using family-office branding rather than a classic UHNW MFO; hence proof strength 'corroborated'. Personal LinkedIn /in profile not located (only company page and a Calendly slug for 'nicholasstenger'). No published individual email or direct phone line found.</t>
+          <t>SEC 13F filings (CIK 0001509379) CEASED after Q3 2014 (last filing 2014-11-04); Willett is NOT a current 13F filer because the bulk of assets are private/alternative. No public website confirmed. AUM is a press figure. Because assets include Bloomberg Philanthropies capital, it straddles family-office and philanthropic-endowment functions, but is consistently characterized as Bloomberg's family office. 13F-HR (2014-11-04) signed by Alice Ruth (Chief Investment Officer) — a verified professional contact at the office in addition to the family principal.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEC13F-0001908612</t>
+          <t>SFO-soros-fund-management</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Allie Family Office LLC</t>
+          <t>Soros Fund Management (Soros Family Office)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>None (owner-operated MFO). Founded 2019 and 100% owned by Bruno Ghio, formerly Regional Head of the Family Office / Managing Director at Banco de Credito del Peru (BCP) and a senior private banker at JPMorgan. Not tied to a single client family.</t>
+          <t>Soros family (George Soros, founder; Alexander 'Alex' Soros, chairman)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://allie-intl.com/en/home/</t>
+          <t>https://www.soros.com/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/alli%C3%A9-family-office</t>
+          <t>https://www.linkedin.com/company/soros</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Miami-based (with a Lima, Peru office) independent multi-family office and SEC-registered investment adviser founded in 2019 by Bruno Ghio, serving Latin American — predominantly Peruvian — high-net-worth families. Provides discretionary and limited-discretionary portfolio management, wealth structuring, tax planning, single-family-office consulting and cross-border coordination via a global network of tax/legal/banking experts.</t>
+          <t>New York-based family office managing the Soros family's wealth and serving as the permanent capital base for the Open Society Foundations. Runs a large, actively traded multi-asset book (public equities, index put options, convertible notes, credit and private investments); recent 13F-reported U.S. equity portfolio ~$9bn.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Cross-border wealth management and multi-generational governance for Latin American families relocating capital (and increasingly themselves) to the US; independent, conflict-free advisory.</t>
+          <t>Actively managed global macro / multi-asset investing, including sizeable hedging (index puts) and credit, supporting long-term family and Open Society capital.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Discretionary and limited-discretionary global portfolio management (largest reported 13F holding is the SPDR S&amp;P 500 ETF Trust; 95 equity positions); diversified across public markets, no single-sector focus disclosed.</t>
+          <t>Diversified; technology (Amazon, Nvidia, Alphabet, Apple, TSMC), consumer/media, credit, options/hedging</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>~$1.15 billion AUM (as of 2024-12-31: ~$508.7M discretionary + ~$637.9M limited-discretionary); aggregators (FINTRX) report ~$1.3B; press (Bloomberg/Crain, 2024) cites ~$2B across the Peru/Miami practice</t>
+          <t>~$28 billion</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2185,19 +2165,15 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Bruno Ghio</t>
+          <t>George Soros</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Founder &amp; Chief Executive Officer (CFA, CAIA, FRM); 100% owner</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>https://pe.linkedin.com/in/bruno-ghio-1264b616b</t>
-        </is>
-      </c>
+          <t>Founder / Chairman (Family Principal)</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
@@ -2206,17 +2182,17 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>7866357162</t>
+          <t>212-320-5000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Founded 2019; among Peru's top-3 independent multi-family offices; ~23 client families (avg ~$50M); Miami + Lima offices; growth from Peruvian clients relocating to Miami; added a partner in Peru</t>
+          <t>Q1 2026 13F (as of 2026-03-31) disclosing ~263 positions valued ~$9.12bn (~61% equities, ~20% index put options, ~19% convertibles); top holdings Amazon, Electronic Arts, Nvidia, TSMC, Alphabet, Apple. 2023 generational handover to Alex Soros.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2019 (firm founding); 2024 (Bloomberg/Crain profile); AUM as of 2024-12-31</t>
+          <t>2026-03-31 (13F period); 2023 (handover)</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2226,89 +2202,85 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Legal 13F filer name is 'Allie Family Office LLC'; brand is 'Allié Family Office' (allie-intl.com). AUM figures vary by source (~$1.15B ADV vs ~$1.3B FINTRX vs ~$2B press including the broader Peru practice). No individual email or direct phone published; only generic info@ mailbox. Jose Larrabure is the investment lead; Bruno Ghio named principal as founder/CEO/100% owner.</t>
+          <t>Dawn Fitzpatrick is reported as CEO/CIO running day-to-day investing (not independently verified against a primary filing here). Manages Open Society Foundations capital as well as family wealth, so it straddles family-office and foundation-endowment functions; consistently characterized as the Soros family office. A related smaller entity, Soros Capital Management LLC (CIK), also files 13F — do not merge. 13F-HR (2026-05-15) signed by John DeSisto (Assistant General Counsel) — a verified professional contact at the office in addition to the family principal.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEC13F-0001511137</t>
+          <t>SFO-grok-ventures-cannon-brookes</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pathstone Family Office, Llc</t>
+          <t>Grok Ventures (Cannon-Brookes Family Office)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>No single family; one of the largest U.S. multi-family offices serving many UHNW families, SFOs and institutions.</t>
+          <t>Cannon-Brookes family (Mike Cannon-Brookes, co-founder of Atlassian)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://pathstone.com</t>
+          <t>https://www.grok.ventures/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/pathstone-family-office</t>
+          <t>https://www.linkedin.com/company/grok-ventures</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Englewood, NJ headquartered partner-owned multi-family office and SEC-registered RIA founded in 2010 (co-founders Matthew Fleissig, Allan Zachariah, Steve Braverman). Provides integrated investment management, tax, insurance/risk, legacy planning and family-office services to UHNW families, family offices, foundations and endowments; ~$125B firm AUM (2025).</t>
+          <t>Sydney-based single-family office of Atlassian co-founder Mike Cannon-Brookes. One of Australia's most prominent family offices, it has increasingly concentrated on climate and clean-technology investing (backing SunCable's Australia-Asia Power Link, battery and decarbonisation ventures) alongside a diversified portfolio; in early 2026 it announced a climate-only investment focus.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Integrated, institutional-quality advice with a client-first culture; open-architecture investment management including private markets and alternatives; scale via organic growth and acquisitions (e.g., Crestone Capital).</t>
+          <t>Mission-driven investing to accelerate decarbonisation and net-zero, via venture and direct stakes in climate/clean-tech, energy and enabling technologies.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Public equities (13F holdings), private markets/alternatives, fixed income, diversified multi-asset portfolios</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>~$125 billion (firm) as of 12/31/2025; ~$187 billion including affiliate firms (other sources cite $170B+ aggregate in 2025).</t>
-        </is>
-      </c>
+          <t>Climate tech, clean energy/renewables, batteries, decarbonisation, technology venture</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>ENGLEWOOD</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>New South Wales</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Matthew Fleissig</t>
+          <t>Mike Cannon-Brookes</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Chief Executive Officer (co-founder)</t>
+          <t>Founder / Family Principal</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/fleissig/</t>
+          <t>https://www.linkedin.com/in/mikecannonbrookes</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
@@ -2317,19 +2289,15 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>857-305-3070</t>
-        </is>
-      </c>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Founded 2010; 15th anniversary in 2025; acquired Crestone Capital; ~775+ employees; co-founders Allan Zachariah and Steve Braverman serve as Co-Chairmen; multiple 2025 Family Wealth Report Awards.</t>
+          <t>Announced climate-only investment focus and appointment of CEO Tan Kueh (Jan 2026); latest investment Asterix Foods seed round (2025-10-08); portfolio exit of Cog (2025-03-03); long-running backing of SunCable.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>Founded 2010; AUM as of 12/31/2025; ADV dated 03/31/2025.</t>
+          <t>2026-01; 2025-10-08; 2025-03-03</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2339,19 +2307,19 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Very large firm; AUM figures vary by whether affiliate firms are included and by reporting date. No published individual email.</t>
+          <t>principal_linkedin is the plausible public Mike Cannon-Brookes /in/ profile but not verified to explicitly list Grok Ventures (marked unconfirmed). Website domain (grok.ventures) asserted from press, not independently fetched. Mike and Annie Cannon-Brookes separated (2023); the office remains Mike's family office.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SEC13F-0001731123</t>
+          <t>SEC13F-0001599603</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Biltmore Family Office, LLC</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2361,47 +2329,47 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Founder Chris Cecil is a great-grandson of George Vanderbilt (builder of the Biltmore Estate) and son of Asheville developer George Cecil; 'Biltmore' name derives from that Vanderbilt/Cecil family heritage. The firm serves many outside client families (MFO), not the Vanderbilt/Cecil family exclusively.</t>
+          <t>None as a single client family; founder-owned firm (Laura Tarbox founder, CEO and principal owner). Namesake is the founder, not a served family.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.biltmorefamilyoffice.com/</t>
+          <t>https://tarbox.com/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/biltmore-family-office-llc</t>
+          <t>https://www.linkedin.com/company/tarboxfamilyoffice</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Charlotte, NC-based multi-family office and SEC-registered investment adviser founded in 2008 by Chris Cecil. A collaborative/independent RIA to investment-oriented multi-generational families and institutions, providing investment management, asset allocation, investment-policy design, multi-generational and succession planning. ~$3.2-3.5B AUM.</t>
+          <t>Newport Beach, CA-based multi-family office and SEC-registered investment adviser founded in 1985 by Laura Tarbox, CFP. Fee-only firm serving 100+ HNW/UHNW client families (also charities, businesses, trusts/estates) with comprehensive financial planning, tax preparation and individualized investment management; $5M minimum, over $1B AUM. Also has a Scottsdale, AZ office.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Collaborative, investment-policy-driven management for multi-generational HNW/UHNW families and institutions.</t>
+          <t>Team-based, individualized asset allocation and investment management integrated with comprehensive financial and estate planning; fee-only fiduciary model.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Diversified public-equity/ETF portfolios; disclosed top 13F holdings include AAPL, IAU (gold), AVDX, ROBO, VV. No single-sector concentration.</t>
+          <t>Diversified asset-allocation / individualized investment management; no single-sector focus.</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>~$3.2-3.5 billion (reported ~$3.47B regulatory AUM across ~951 accounts)</t>
+          <t>Over $1 billion (100+ client families)</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>CHARLOTTE</t>
+          <t>NEWPORT BEACH</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2411,38 +2379,38 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Chris Cecil</t>
+          <t>Laura Tarbox</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Founder, President &amp; CEO</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/chris-cecil-9701b818/</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr"/>
+          <t>Founder, CEO &amp; principal owner (CFP)</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>laura@tarbox.com</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>+1 704-248-5230</t>
+          <t>(949) 721-2330</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Founded 2008 by Chris Cecil (LLC organized 2013); ~$3.2-3.5B AUM across ~951 accounts, avg client ~$38M; Cecil chairs TIGER 21 Charlotte / Family Office groups</t>
+          <t>Founded 1985; CFP since 1984; 100+ client families and &gt;$1B AUM; $5M account minimum; second office in Scottsdale, AZ; Laura Tarbox a frequent WSJ/NYT/LA Times media source</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>2008 (founding); 2013 (LLC organized)</t>
+          <t>1985 (founded); 1984 (Laura Tarbox CFP)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2452,19 +2420,19 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Chris Cecil chosen as principal (founder/CEO); Rael Gorelick is Partner &amp; Head of Investments and would be the CIO-level investment lead. No published individual email located. AUM varies by source ($3.2B-$3.5B).</t>
+          <t>Personal LinkedIn /in profile not located (only firm company page). Email captured from Laura Tarbox's public presentation PDF (matches firm domain) rather than the current bio page; treat as published-but-unverified.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SEC13F-0001039807</t>
+          <t>SEC13F-0002056106</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Boston Family Office Llc</t>
+          <t>Stenger Family Office, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2472,41 +2440,49 @@
           <t>MFO</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Stenger family (firm founded/led by Nick Stenger; the family has advised clients since 1981). The 'family' is the owner-operator, not a single client family.</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.bosfam.com/</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>https://www.stengerfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/stenger-family-office</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>The Boston Family Office LLC is an independent, employee-owned registered investment adviser founded in 1996 and based in Boston, MA. It provides multi-family-office-style wealth management -- investment management, financial planning, and adviser selection -- to high-net-worth individuals, families and charitable organizations across roughly 789 accounts and ~$1.7-2.0B in assets. It is a multi-family/RIA firm rather than a single-family office.</t>
+          <t>Naperville, IL-based multi-family office / independent fiduciary RIA led by founder-CEO Nick Stenger, offering financial planning, investment management, and (via related companies) tax preparation, estate strategies and insurance. Also has a Spring, TX office. ~$731M AUM; named a Forbes Best-in-State Wealth Advisor 2026.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Client-tailored, diversified portfolio management for wealth preservation and growth across HNW households and institutions; discretionary management (769 of 789 accounts discretionary). Specific house investment philosophy not detailed publicly.</t>
+          <t>Goals-based planning: assesses cash needs and upcoming goals, then builds customized portfolios.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Diversified multi-asset wealth management (public equities, fixed income, funds); not sector-specialized. A partner sits on the board of fixed-income manager Breckinridge Capital Advisors.</t>
+          <t>Core individual-stock portfolios and ETF-based asset-allocation portfolios; no single-sector focus.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>~$1.7B AUM across 789 accounts (Form ADV/adviserinfo, 2024-2025); third-party profiles cite ~$1.9-2.02B. As of the most recent Form ADV (2024 filing cycle).</t>
+          <t>~$731 million (as of 2026-06-30)</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>NAPERVILLE</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2516,38 +2492,38 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>George P. Beal</t>
+          <t>Nicholas David Stenger</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; Managing Partner (Portfolio Manager)</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/george-beal-a6107a16/</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr"/>
+          <t>Founder &amp; Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>nick.stenger@stengerfamilyoffice.com</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>617-624-0800</t>
+          <t>630-912-8295</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>Filed Form ADV Part 2A/2B brochures in the 2024 filing cycle (Feb 2024); a partner (Beal) serves on the board of Breckinridge Capital Advisors. Firm moved offices to 20 Custom House St.</t>
+          <t>$731M AUM (2026-06-30); Forbes Best-in-State Wealth Advisor 2026; hosts 'The Nick Stenger Show' podcast; opened Spring, TX office</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2024-02-01 (ADV Part 2B brochure)</t>
+          <t>2026-06-30 (AUM date); 2026 (Forbes Best-in-State)</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2557,19 +2533,19 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Despite the 'family office' name, this is functionally a multi-family-office RIA / private wealth manager serving hundreds of client accounts, not a single family's office. Investment authority is distributed among ~8 managing directors, so Beal is one of several senior decision-makers (though the 13F signatory and co-founder). No official company LinkedIn URL confirmed. No individual email is published (the ZoomInfo masked pattern was deliberately not used).</t>
+          <t>Serves 1,200+ families 'of all net worth sizes' — a broad wealth-management RIA using family-office branding rather than a classic UHNW MFO; hence proof strength 'corroborated'. Personal LinkedIn /in profile not located (only company page and a Calendly slug for 'nicholasstenger'). No published individual email or direct phone line found.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEC13F-0002017744</t>
+          <t>SEC13F-0001908612</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC</t>
+          <t>Allie Family Office LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2577,45 +2553,49 @@
           <t>MFO</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>None (owner-operated MFO). Founded 2019 and 100% owned by Bruno Ghio, formerly Regional Head of the Family Office / Managing Director at Banco de Credito del Peru (BCP) and a senior private banker at JPMorgan. Not tied to a single client family.</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://arrowrootfamilyoffice.com/</t>
+          <t>https://allie-intl.com/en/home/</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/arrowroot-family-office</t>
+          <t>https://www.linkedin.com/company/alli%C3%A9-family-office</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC is a Marina del Rey, CA-based registered investment adviser and multi-family office, originally founded in 2013 as Vitreous Partners and rebranded in 2017. It provides multidisciplinary wealth management -- investment management, retirement, tax and estate planning -- to high-net-worth individuals, entrepreneurs, families and small institutions, with offices in Southern and Northern California, Virginia and Michigan. It is a multi-client RIA, not a single family's office.</t>
+          <t>Miami-based (with a Lima, Peru office) independent multi-family office and SEC-registered investment adviser founded in 2019 by Bruno Ghio, serving Latin American — predominantly Peruvian — high-net-worth families. Provides discretionary and limited-discretionary portfolio management, wealth structuring, tax planning, single-family-office consulting and cross-border coordination via a global network of tax/legal/banking experts.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Team-based, fiduciary, goals-driven wealth management emphasizing comprehensive planning and diversified investment management for affluent households and business owners; open-architecture advice.</t>
+          <t>Cross-border wealth management and multi-generational governance for Latin American families relocating capital (and increasingly themselves) to the US; independent, conflict-free advisory.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Diversified multi-asset wealth management (public equities, funds/ETFs, fixed income, alternatives); not sector-specialized.</t>
+          <t>Discretionary and limited-discretionary global portfolio management (largest reported 13F holding is the SPDR S&amp;P 500 ETF Trust; 95 equity positions); diversified across public markets, no single-sector focus disclosed.</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>~$431M AUM as of Q2 2025 (third-party profiles); regulatory AUM per the 2025 Form ADV on the firm's site. A floor for total client assets under advisement.</t>
+          <t>~$1.15 billion AUM (as of 2024-12-31: ~$508.7M discretionary + ~$637.9M limited-discretionary); aggregators (FINTRX) report ~$1.3B; press (Bloomberg/Crain, 2024) cites ~$2B across the Peru/Miami practice</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Marina Del Rey</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -2625,17 +2605,17 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Rob (Roberto Francisco) Santos</t>
+          <t>Bruno Ghio</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Chief Executive Officer &amp; Principal Owner</t>
+          <t>Founder &amp; Chief Executive Officer (CFA, CAIA, FRM); 100% owner</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/rob-santos-afo/</t>
+          <t>https://pe.linkedin.com/in/bruno-ghio-1264b616b</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
@@ -2646,17 +2626,17 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>310.341.4774</t>
+          <t>7866357162</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Announced expansion of its private-wealth practice into Michigan via addition of The Athena Financial Group (offices now include Marina del Rey CA, Rochester Hills MI, Charlottesville VA, El Dorado Hills CA); filed updated Form ADV Part 2A/2B in April 2025.</t>
+          <t>Founded 2019; among Peru's top-3 independent multi-family offices; ~23 client families (avg ~$50M); Miami + Lima offices; growth from Peruvian clients relocating to Miami; added a partner in Peru</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2022-09-05 (Michigan/Athena expansion press release); 2025-04 (Form ADV update)</t>
+          <t>2019 (firm founding); 2024 (Bloomberg/Crain profile); AUM as of 2024-12-31</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2666,19 +2646,19 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Uses the 'family office' label but is a multi-client wealth-management RIA, not a single family's office. Possible name confusion with 'Arrowroot Capital Management' (a separate B2B enterprise-software private-equity firm) -- they are distinct; relationship not established here. No individual email published; RocketReach/broker data deliberately not used. Firm's most recent 13F filer registration is recent (CIK 0002017744).</t>
+          <t>Legal 13F filer name is 'Allie Family Office LLC'; brand is 'Allié Family Office' (allie-intl.com). AUM figures vary by source (~$1.15B ADV vs ~$1.3B FINTRX vs ~$2B press including the broader Peru practice). No individual email or direct phone published; only generic info@ mailbox. Jose Larrabure is the investment lead; Bruno Ghio named principal as founder/CEO/100% owner.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SEC13F-0001756485</t>
+          <t>SEC13F-0001511137</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Independent Family Office, LLC</t>
+          <t>Pathstone Family Office, Llc</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2688,47 +2668,47 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>None (owner-operated MFO). Founded 2005 by W. Michael Reickert, who previously led the family-office practice at The Ayco Company. Serves multiple entrepreneurial client families; not a single-family vehicle.</t>
+          <t>No single family; one of the largest U.S. multi-family offices serving many UHNW families, SFOs and institutions.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://ifollc.com/</t>
+          <t>https://pathstone.com</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/independent-family-office-llc</t>
+          <t>https://www.linkedin.com/company/pathstone-family-office</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Albany, New York-based multi-family office and SEC-registered investment adviser founded in 2005 by W. Michael Reickert. A bespoke family office serving a small number of high-net-worth families (average client tenure 10+ years) with investment advisory and asset allocation, estate-planning coordination, transaction/contract advisory and income-tax planning and compliance.</t>
+          <t>Englewood, NJ headquartered partner-owned multi-family office and SEC-registered RIA founded in 2010 (co-founders Matthew Fleissig, Allan Zachariah, Steve Braverman). Provides integrated investment management, tax, insurance/risk, legacy planning and family-office services to UHNW families, family offices, foundations and endowments; ~$125B firm AUM (2025).</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Technical, unbiased, independent long-term stewardship of client families' financial lives; capital-allocator approach.</t>
+          <t>Integrated, institutional-quality advice with a client-first culture; open-architecture investment management including private markets and alternatives; scale via organic growth and acquisitions (e.g., Crestone Capital).</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Discretionary portfolio management and outside-manager selection for HNW families (largest reported 13F holding is the SPDR S&amp;P 500 ETF Trust); diversified, no single-sector focus disclosed.</t>
+          <t>Public equities (13F holdings), private markets/alternatives, fixed income, diversified multi-asset portfolios</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>~$617.8 million discretionary AUM across ~34 clients (Form ADV, 2025-03-31); aggregators (FINTRX) report ~$760M</t>
+          <t>~$125 billion (firm) as of 12/31/2025; ~$187 billion including affiliate firms (other sources cite $170B+ aggregate in 2025).</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>ALBANY</t>
+          <t>ENGLEWOOD</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2738,15 +2718,19 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>W. Michael Reickert</t>
+          <t>Matthew Fleissig</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Managing Member / Managing Partner &amp; CEO (also Chief Compliance Officer); IRS Enrolled Agent, JD</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr"/>
+          <t>Chief Executive Officer (co-founder)</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fleissig/</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
@@ -2755,17 +2739,17 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>(518) 452-8050</t>
+          <t>857-305-3070</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Founded 2005; SEC-registered 2012; ex-Ayco family-office pedigree; very low client count (~34) with 10+ year average tenure</t>
+          <t>Founded 2010; 15th anniversary in 2025; acquired Crestone Capital; ~775+ employees; co-founders Allan Zachariah and Steve Braverman serve as Co-Chairmen; multiple 2025 Family Wealth Report Awards.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>2005 (founding); 2012 (SEC registration); AUM ~$617.8M as of 2025-03-31</t>
+          <t>Founded 2010; AUM as of 12/31/2025; ADV dated 03/31/2025.</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2775,19 +2759,19 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Firm marketing copy calls itself a 'bespoke family office' for 'select clients'; the ~34-client, multi-family reality plus Altss classification support MFO. 'dr@ifollc.com' is published but its initials do not match the principal, so it is treated as a shared/general mailbox, not the principal's individual email. No personal LinkedIn confirmed for W. Michael Reickert.</t>
+          <t>Very large firm; AUM figures vary by whether affiliate firms are included and by reporting date. No published individual email.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UKCH-09580739</t>
+          <t>SEC13F-0001731123</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Blu Family Office Limited</t>
+          <t>Biltmore Family Office, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2797,67 +2781,67 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Originally Armbruester family (founder's wealth); now MFO serving multiple client families</t>
+          <t>Founder Chris Cecil is a great-grandson of George Vanderbilt (builder of the Biltmore Estate) and son of Asheville developer George Cecil; 'Biltmore' name derives from that Vanderbilt/Cecil family heritage. The firm serves many outside client families (MFO), not the Vanderbilt/Cecil family exclusively.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.blu-fo.com</t>
+          <t>https://www.biltmorefamilyoffice.com/</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/company/blu-family-office</t>
+          <t>https://www.linkedin.com/company/biltmore-family-office-llc</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>FCA-regulated multi-family office (Ltd inc. 2015; operations from 2010) in Richmond upon Thames, founded by Christian Armbruester post Credit Suisse. Offers hedge funds, crypto and alternatives; discretionary arm Blu Investment Management.</t>
+          <t>Charlotte, NC-based multi-family office and SEC-registered investment adviser founded in 2008 by Chris Cecil. A collaborative/independent RIA to investment-oriented multi-generational families and institutions, providing investment management, asset allocation, investment-policy design, multi-generational and succession planning. ~$3.2-3.5B AUM.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Discretionary management not relying on forecasting; 'true diversification' and systematic rebalancing; passive in calm markets, opportunistic in adverse ones.</t>
+          <t>Collaborative, investment-policy-driven management for multi-generational HNW/UHNW families and institutions.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Hedge funds; crypto assets; alternatives; diversified multi-asset</t>
+          <t>Diversified public-equity/ETF portfolios; disclosed top 13F holdings include AAPL, IAU (gold), AVDX, ROBO, VV. No single-sector concentration.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>£0.5bn-£1bn (third-party estimated range)</t>
+          <t>~$3.2-3.5 billion (reported ~$3.47B regulatory AUM across ~951 accounts)</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Greater London</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Christian Armbruester</t>
+          <t>Chris Cecil</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Founder &amp; Principal (largest shareholder ~40.8%)</t>
+          <t>Founder, President &amp; CEO</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/christianarmbruesterblufamilyoffice</t>
+          <t>https://www.linkedin.com/in/chris-cecil-9701b818/</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr"/>
@@ -2866,15 +2850,19 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>+1 704-248-5230</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Founded 2010; Ltd inc. 2015; new director Vishesh Dawar appointed Dec 2025; investment arm rebranded Blu Investment Management; Marie Redron now CEO</t>
+          <t>Founded 2008 by Chris Cecil (LLC organized 2013); ~$3.2-3.5B AUM across ~951 accounts, avg client ~$38M; Cecil chairs TIGER 21 Charlotte / Family Office groups</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2015-05-08; 2025-12-08</t>
+          <t>2008 (founding); 2013 (LLC organized)</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2884,81 +2872,81 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Client-facing operations now run under 'Blu Investment Management' (blu-im.com), same address. Armbruester is founder/principal but not current CEO (Marie Redron is). AUM range is a third-party estimate. Only published contacts are a switchboard + generic mailbox.</t>
+          <t>Chris Cecil chosen as principal (founder/CEO); Rael Gorelick is Partner &amp; Head of Investments and would be the CIO-level investment lead. No published individual email located. AUM varies by source ($3.2B-$3.5B).</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UKCH-12233405</t>
+          <t>SEC13F-0001039807</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Schwarz Family Office Ltd</t>
+          <t>Boston Family Office Llc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Undetermined</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Named after principal Andreas Schwarz (German); no wider family group evidenced beyond the surname</t>
-        </is>
-      </c>
+          <t>MFO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://schwarzfamilyoffice.com/</t>
+          <t>https://www.bosfam.com/</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>London-based boutique investment/advisory firm branded as a family office, established 2019, led by Andreas Schwarz; provides capital raising, debt financing, wealth management and IR services.</t>
+          <t>The Boston Family Office LLC is an independent, employee-owned registered investment adviser founded in 1996 and based in Boston, MA. It provides multi-family-office-style wealth management -- investment management, financial planning, and adviser selection -- to high-net-worth individuals, families and charitable organizations across roughly 789 accounts and ~$1.7-2.0B in assets. It is a multi-family/RIA firm rather than a single-family office.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>'Be not afraid of growing slowly, be afraid only of standing still' — sustainable growth via established relationships and exclusive investor access. https://schwarzfamilyoffice.com/</t>
+          <t>Client-tailored, diversified portfolio management for wealth preservation and growth across HNW households and institutions; discretionary management (769 of 789 accounts discretionary). Specific house investment philosophy not detailed publicly.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Private equity; fintech; wealth management; venture capital; private debt; IPOs</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+          <t>Diversified multi-asset wealth management (public equities, fixed income, funds); not sector-specialized. A partner sits on the board of fixed-income manager Breckinridge Capital Advisors.</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>~$1.7B AUM across 789 accounts (Form ADV/adviserinfo, 2024-2025); third-party profiles cite ~$1.9-2.02B. As of the most recent Form ADV (2024 filing cycle).</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Maida Vale</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Andreas Schwarz</t>
+          <t>George P. Beal</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Founder / Director</t>
+          <t>Co-Founder &amp; Managing Partner (Portfolio Manager)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
+          <t>https://www.linkedin.com/in/george-beal-a6107a16/</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr"/>
@@ -2967,15 +2955,19 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>617-624-0800</t>
+        </is>
+      </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Listed in Family Capital 'FamCap 50' (2024); second shareholder Syed Furqan Ahmed (490 shares)</t>
+          <t>Filed Form ADV Part 2A/2B brochures in the 2024 filing cycle (Feb 2024); a partner (Beal) serves on the board of Breckinridge Capital Advisors. Firm moved offices to 20 Custom House St.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2024-02 (FamCap 50)</t>
+          <t>2024-02-01 (ADV Part 2B brochure)</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2985,19 +2977,19 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Presents as a family office but functions largely as a boutique capital-raising/advisory consultancy with two shareholders — fo_type left Undetermined. A Family Capital story linking Schwarz to a 'famous UK brand' is paywalled and the brand is NOT confirmed; not asserted. AUM undisclosed.</t>
+          <t>Despite the 'family office' name, this is functionally a multi-family-office RIA / private wealth manager serving hundreds of client accounts, not a single family's office. Investment authority is distributed among ~8 managing directors, so Beal is one of several senior decision-makers (though the 13F signatory and co-founder). No official company LinkedIn URL confirmed. No individual email is published (the ZoomInfo masked pattern was deliberately not used).</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>APAC-farro-capital</t>
+          <t>SEC13F-0002017744</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Farro Capital</t>
+          <t>Arrowroot Family Office, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3005,86 +2997,86 @@
           <t>MFO</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Multi-family office — serves multiple UHNW families, billionaires and unicorn founders; not tied to a single family</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://farrocapital.com/</t>
+          <t>https://arrowrootfamilyoffice.com/</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://sg.linkedin.com/company/farrocapital</t>
+          <t>https://www.linkedin.com/company/arrowroot-family-office</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Independent multi-family office and wealth-management platform founded in October 2022 and headquartered in Singapore, with a regional headquarters established in the DIFC (Dubai). Founded by a team of former private and corporate bankers (Hemant Tucker, Manish Tibrewal, Mahesh Kumar, Rajiv Garg, Uthpal Rao) from institutions including Bank of Singapore, UBS, Barclays and Standard Chartered. Offers goal-based investing, risk management, credit solutions, cross-border structuring, next-generation planning and philanthropic stewardship.</t>
+          <t>Arrowroot Family Office, LLC is a Marina del Rey, CA-based registered investment adviser and multi-family office, originally founded in 2013 as Vitreous Partners and rebranded in 2017. It provides multidisciplinary wealth management -- investment management, retirement, tax and estate planning -- to high-net-worth individuals, entrepreneurs, families and small institutions, with offices in Southern and Northern California, Virginia and Michigan. It is a multi-client RIA, not a single family's office.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Holistic, goal-based multi-asset wealth management and cross-border structuring for global UHNW families, with a philanthropy/impact emphasis.</t>
+          <t>Team-based, fiduciary, goals-driven wealth management emphasizing comprehensive planning and diversified investment management for affluent households and business owners; open-architecture advice.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Multi-asset wealth management; Private markets; Public markets; Philanthropy/impact</t>
+          <t>Diversified multi-asset wealth management (public equities, funds/ETFs, fixed income, alternatives); not sector-specialized.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>~USD2-3 billion</t>
+          <t>~$431M AUM as of Q2 2025 (third-party profiles); regulatory AUM per the 2025 Form ADV on the firm's site. A floor for total client assets under advisement.</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Marina Del Rey</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Hemant Tucker</t>
+          <t>Rob (Roberto Francisco) Santos</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; Chief Executive Officer</t>
+          <t>Chief Executive Officer &amp; Principal Owner</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/hemant-tucker-a97b49bb/</t>
+          <t>https://www.linkedin.com/in/rob-santos-afo/</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>unverified</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr"/>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>310.341.4774</t>
+        </is>
+      </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Oct 2022: founded / soft-launched in Singapore. 2023-2026: grew AUM from &gt;USD1bn to ~USD3bn across 12+ markets. Established a DIFC (Dubai) regional headquarters to drive global expansion.</t>
+          <t>Announced expansion of its private-wealth practice into Michigan via addition of The Athena Financial Group (offices now include Marina del Rey CA, Rochester Hills MI, Charlottesville VA, El Dorado Hills CA); filed updated Form ADV Part 2A/2B in April 2025.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2022-10; 2026-04</t>
+          <t>2022-09-05 (Michigan/Athena expansion press release); 2025-04 (Form ADV update)</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
@@ -3094,68 +3086,84 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Multi-family office (not a single-family office). Sister brand 'Farro &amp; Co' (international mobility advisory, 3 Philip Street, Singapore) is a distinct entity from Farro Capital. AUM figures are self-reported/press-reported. Principal LinkedIn confirmed; no published individual email.</t>
+          <t>Uses the 'family office' label but is a multi-client wealth-management RIA, not a single family's office. Possible name confusion with 'Arrowroot Capital Management' (a separate B2B enterprise-software private-equity firm) -- they are distinct; relationship not established here. No individual email published; RocketReach/broker data deliberately not used. Firm's most recent 13F filer registration is recent (CIK 0002017744).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>UKCH-14344019</t>
+          <t>SEC13F-0001756485</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hazell Family Office Ltd</t>
+          <t>Independent Family Office, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Hazell family of South Wales (haulage/waste/environmental-services wealth)</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
+          <t>None (owner-operated MFO). Founded 2005 by W. Michael Reickert, who previously led the family-office practice at The Ayco Company. Serves multiple entrepreneurial client families; not a single-family vehicle.</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://ifollc.com/</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/independent-family-office-llc</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Active company (inc. 2022-09-08), SIC 70221 financial management; board is five members of the Hazell family. Structure strongly indicates a single-family office. No website/press footprint.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>Albany, New York-based multi-family office and SEC-registered investment adviser founded in 2005 by W. Michael Reickert. A bespoke family office serving a small number of high-net-worth families (average client tenure 10+ years) with investment advisory and asset allocation, estate-planning coordination, transaction/contract advisory and income-tax planning and compliance.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Technical, unbiased, independent long-term stewardship of client families' financial lives; capital-allocator approach.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>70221 - Financial management</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
+          <t>Discretionary portfolio management and outside-manager selection for HNW families (largest reported 13F holding is the SPDR S&amp;P 500 ETF Trust); diversified, no single-sector focus disclosed.</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>~$617.8 million discretionary AUM across ~34 clients (Form ADV, 2025-03-31); aggregators (FINTRX) report ~$760M</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Usk</t>
+          <t>ALBANY</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Monmouthshire, Wales</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Mark David William Hazell</t>
+          <t>W. Michael Reickert</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Director (family principal)</t>
+          <t>Managing Member / Managing Partner &amp; CEO (also Chief Compliance Officer); IRS Enrolled Agent, JD</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -3165,71 +3173,91 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>(518) 452-8050</t>
+        </is>
+      </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Incorporated Sept 2022; five family directors appointed same day; principal is MD of family haulage/environmental companies</t>
+          <t>Founded 2005; SEC-registered 2012; ex-Ayco family-office pedigree; very low client count (~34) with 10+ year average tenure</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>2005 (founding); 2012 (SEC registration); AUM ~$617.8M as of 2025-03-31</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>SFO status inferred from shared surname + single family-farm address + Mark Hazell's operating-company directorships; no website/press confirms active investment operations. 'Mark = principal' is inference; control may be shared across the family.</t>
+          <t>Firm marketing copy calls itself a 'bespoke family office' for 'select clients'; the ~34-client, multi-family reality plus Altss classification support MFO. 'dr@ifollc.com' is published but its initials do not match the principal, so it is treated as a shared/general mailbox, not the principal's individual email. No personal LinkedIn confirmed for W. Michael Reickert.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UKCH-14442767</t>
+          <t>UKCH-09580739</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wedgwood Family Office Limited</t>
+          <t>Blu Family Office Limited</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Wedgwood (Paul Wedgwood family)</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
+          <t>Originally Armbruester family (founder's wealth); now MFO serving multiple client families</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.blu-fo.com</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/blu-family-office</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>UK private company (inc. 2022-10-25) under fund-management SIC, registered at a residential address in Keston. Appears to be the personal single-family investment vehicle of Paul Wedgwood.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>FCA-regulated multi-family office (Ltd inc. 2015; operations from 2010) in Richmond upon Thames, founded by Christian Armbruester post Credit Suisse. Offers hedge funds, crypto and alternatives; discretionary arm Blu Investment Management.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Discretionary management not relying on forecasting; 'true diversification' and systematic rebalancing; passive in calm markets, opportunistic in adverse ones.</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>66300 - Fund management activities</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
+          <t>Hedge funds; crypto assets; alternatives; diversified multi-asset</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>£0.5bn-£1bn (third-party estimated range)</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Keston</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Greater London (Bromley)</t>
+          <t>Greater London</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3239,15 +3267,19 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Paul Wedgwood</t>
+          <t>Christian Armbruester</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr"/>
+          <t>Founder &amp; Principal (largest shareholder ~40.8%)</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/christianarmbruesterblufamilyoffice</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
         <is>
@@ -3257,76 +3289,76 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Co-director Christopher James Sharp resigned 2024-04-16; new secretary appointed 2026-01-06; accounts currently overdue</t>
+          <t>Founded 2010; Ltd inc. 2015; new director Vishesh Dawar appointed Dec 2025; investment arm rebranded Blu Investment Management; Marie Redron now CEO</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2024-04-16; 2026-01-06</t>
+          <t>2015-05-08; 2025-12-08</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Link between director 'Paul Wedgwood, b.1970' and the Splash Damage/Supernova entrepreneur is a strong inference (name + DOB + separate Wedgwood FIC directorship), NOT hard-confirmed. Zero public FO footprint (no website/LinkedIn/press/AUM); accounts overdue. Residential registered address.</t>
+          <t>Client-facing operations now run under 'Blu Investment Management' (blu-im.com), same address. Armbruester is founder/principal but not current CEO (Marie Redron is). AUM range is a third-party estimate. Only published contacts are a switchboard + generic mailbox.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UKCH-17062903</t>
+          <t>UKCH-12233405</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Frigus Family Office Ltd</t>
+          <t>Schwarz Family Office Ltd</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Undetermined</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Gudmundsson family (Lydur Gudmundsson, co-founder of Bakkavor; brother Agust Gudmundsson also linked to Frigus-branded entities)</t>
+          <t>Named after principal Andreas Schwarz (German); no wider family group evidenced beyond the surname</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.frigus.is/</t>
+          <t>https://schwarzfamilyoffice.com/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr">
         <is>
-          <t>UK private limited company incorporated 2 Mar 2026 as the UK entity of Frigus, the Gudmundsson family's single family office (group HQ Kópavogur, Iceland, with a Luxembourg office). Frigus actively manages the family's assets, investments and real estate; its principal holding is a stake in LSE-listed Greencore Group, arising from the 2026 merger of the family business Bakkavor into Greencore. Registered at a London residential address (Fountain House, Park Street, Mayfair).</t>
+          <t>London-based boutique investment/advisory firm branded as a family office, established 2019, led by Andreas Schwarz; provides capital raising, debt financing, wealth management and IR services.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Active management of family assets, investments and real estate (per frigus.is); large concentrated public-equity position in Greencore Group plus real estate.</t>
+          <t>'Be not afraid of growing slowly, be afraid only of standing still' — sustainable growth via established relationships and exclusive investor access. https://schwarzfamilyoffice.com/</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Listed equities (food manufacturing via Greencore Group stake), real estate, diversified investments</t>
+          <t>Private equity; fintech; wealth management; venture capital; private debt; IPOs</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>London (UK entity); group HQ Kópavogur, Iceland</t>
+          <t>London</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>London, England (UK entity); Capital Region, Iceland (group)</t>
+          <t>Maida Vale</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3336,15 +3368,19 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Lydur Gudmundsson</t>
+          <t>Andreas Schwarz</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Founder / controlling principal (PSC); co-founder of Bakkavor</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr"/>
+          <t>Founder / Director</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
         <is>
@@ -3354,135 +3390,143 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr">
         <is>
-          <t>UK entity newly incorporated Mar 2026, following the 2026 Bakkavor-Greencore merger. Director Andrea Olsen (Icelandic, CEO/MD of Frigus ehf) appointed at incorporation. Historic Frigus-branded UK entities dissolved (Frigus Ltd dissolved 2022; Frigus Invest Ltd dissolved 2018).</t>
+          <t>Listed in Family Capital 'FamCap 50' (2024); second shareholder Syed Furqan Ahmed (490 shares)</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2026-03-02 (UK incorporation); 2026 (Bakkavor/Greencore merger)</t>
+          <t>2024-02 (FamCap 50)</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>'Strong' proof applies to Frigus as a family office group (clear self-description + well-documented Gudmundsson/Bakkavor lineage); the specific UK entity 17062903 is brand-new (Mar 2026) with no filed accounts yet, so UK-level operations are unproven. Lydur Gudmundsson's nationality is shown as British on Companies House though he is the Icelandic Bakkavor co-founder. Switchboard/generic mailboxes belong to the Iceland/Luxembourg offices, not a UK-specific contact.</t>
+          <t>Presents as a family office but functions largely as a boutique capital-raising/advisory consultancy with two shareholders — fo_type left Undetermined. A Family Capital story linking Schwarz to a 'famous UK brand' is paywalled and the brand is NOT confirmed; not asserted. AUM undisclosed.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SFO-dfo-management-dell</t>
+          <t>APAC-farro-capital</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DFO Management (Dell Family Office)</t>
+          <t>Farro Capital</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Dell family (Michael Dell, founder/CEO of Dell Technologies)</t>
+          <t>Multi-family office — serves multiple UHNW families, billionaires and unicorn founders; not tied to a single family</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.dellfamilyoffice.com/</t>
+          <t>https://farrocapital.com/</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/dfo-management</t>
+          <t>https://sg.linkedin.com/company/farrocapital</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Private investment firm managing the assets of Michael Dell and family across public equities, private equity, real estate and other asset classes. Originally MSD Capital (1998); the multi-client business became BDT &amp; MSD Partners while the family's captive vehicle was rebranded DFO Management at end of 2022.</t>
+          <t>Independent multi-family office and wealth-management platform founded in October 2022 and headquartered in Singapore, with a regional headquarters established in the DIFC (Dubai). Founded by a team of former private and corporate bankers (Hemant Tucker, Manish Tibrewal, Mahesh Kumar, Rajiv Garg, Uthpal Rao) from institutions including Bank of Singapore, UBS, Barclays and Standard Chartered. Offers goal-based investing, risk management, credit solutions, cross-border structuring, next-generation planning and philanthropic stewardship.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Multi-asset-class permanent capital: public equities, private equity/credit, real estate, opportunistic direct investments.</t>
+          <t>Holistic, goal-based multi-asset wealth management and cross-border structuring for global UHNW families, with a philanthropy/impact emphasis.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Diversified (consumer, real estate, financials, industrials)</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
+          <t>Multi-asset wealth management; Private markets; Public markets; Philanthropy/impact</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>~USD2-3 billion</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Michael Dell</t>
+          <t>Hemant Tucker</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Founder / Family Principal</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr"/>
+          <t>Co-Founder &amp; Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/hemant-tucker-a97b49bb/</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
-          <t>13F-HR filed 2026-05-15 (period ending 2026-03-31) disclosing U.S. equity holdings; rebrand from MSD Capital to DFO Management completed end of 2022.</t>
+          <t>Oct 2022: founded / soft-launched in Singapore. 2023-2026: grew AUM from &gt;USD1bn to ~USD3bn across 12+ markets. Established a DIFC (Dubai) regional headquarters to drive global expansion.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2026-05-15; 2022-12</t>
+          <t>2022-10; 2026-04</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>The 13F is filed in the name of the Michael &amp; Susan Dell Foundation with DFO Management as manager; the foundation and the family office are affiliated. AUM not disclosed. Michael Dell is a public figure; no personal LinkedIn tied specifically to DFO confirmed.</t>
+          <t>Multi-family office (not a single-family office). Sister brand 'Farro &amp; Co' (international mobility advisory, 3 Philip Street, Singapore) is a distinct entity from Farro Capital. AUM figures are self-reported/press-reported. Principal LinkedIn confirmed; no published individual email.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SFO-bayshore-global-brin</t>
+          <t>UKCH-14344019</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bayshore Global Management (Brin Family Office)</t>
+          <t>Hazell Family Office Ltd</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3492,50 +3536,46 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Brin family (Sergey Brin, Google co-founder)</t>
+          <t>Hazell family of South Wales (haulage/waste/environmental-services wealth)</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Low-profile single-family office managing the wealth of Sergey Brin across public and private markets, real estate and philanthropy. Additional office in Singapore. Reported to have absorbed the Nexus NeuroTech brain-health VC fund in 2026.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Broad multi-asset allocation with notable venture/science-and-health direct investing.</t>
-        </is>
-      </c>
+          <t>Active company (inc. 2022-09-08), SIC 70221 financial management; board is five members of the Hazell family. Structure strongly indicates a single-family office. No website/press footprint.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Diversified; neuroscience/brain-health, deep tech, real estate</t>
+          <t>70221 - Financial management</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Usk</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Monmouthshire, Wales</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Sergey Brin</t>
+          <t>Mark David William Hazell</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Family Principal</t>
+          <t>Director (family principal)</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -3548,12 +3588,12 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Absorbed Nexus NeuroTech brain-health VC fund (reported 2026-04-23, Bloomberg).</t>
+          <t>Incorporated Sept 2022; five family directors appointed same day; principal is MD of family haulage/environmental companies</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2022-09-08</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
@@ -3563,19 +3603,19 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>No public website confirmed. AUM figures are press estimates. CEO George Pavlov / CIO Marie Young named in Wikipedia and press but not verified against a primary filing.</t>
+          <t>SFO status inferred from shared surname + single family-farm address + Mark Hazell's operating-company directorships; no website/press confirms active investment operations. 'Mark = principal' is inference; control may be shared across the family.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SFO-hillspire-schmidt</t>
+          <t>UKCH-14442767</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hillspire (Eric Schmidt Family Office)</t>
+          <t>Wedgwood Family Office Limited</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3585,50 +3625,46 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Schmidt family (Eric &amp; Wendy Schmidt; Eric Schmidt is former Google/Alphabet CEO and chairman)</t>
+          <t>Wedgwood (Paul Wedgwood family)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Single-family office of Eric and Wendy Schmidt focused on deep technology: artificial intelligence, quantum computation, defense tech and biotech. Reported to have invested in 22+ private AI firms since 2019 (including Anthropic, SandboxAQ, Inworld AI) and topped CNBC's inaugural family-office dealmaking ranking for 2025.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Deep-tech direct investing concentrated in AI, quantum, defense technology and biotech.</t>
-        </is>
-      </c>
+          <t>UK private company (inc. 2022-10-25) under fund-management SIC, registered at a residential address in Keston. Appears to be the personal single-family investment vehicle of Paul Wedgwood.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>AI, quantum computing, defense tech, biotech</t>
+          <t>66300 - Fund management activities</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Keston</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Greater London (Bromley)</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Eric Schmidt</t>
+          <t>Paul Wedgwood</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Family Principal / Founder</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -3641,12 +3677,12 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Ranked #1 most active U.S. family office for dealmaking in 2025 (15 investments, mostly AI) per CNBC 2026-02-12; disclosed 22 private AI startup investments since 2019 (CNBC 2025-01-21).</t>
+          <t>Co-director Christopher James Sharp resigned 2024-04-16; new secretary appointed 2026-01-06; accounts currently overdue</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2026-02-12; 2025-01-21</t>
+          <t>2024-04-16; 2026-01-06</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
@@ -3656,19 +3692,19 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>No public website confirmed (hillspire.com not verified). Does not file 13F (EDGAR full-text search returned no 13F-HR). AUM not disclosed. President Ken Goldman named in press, not verified against a primary filing.</t>
+          <t>Link between director 'Paul Wedgwood, b.1970' and the Splash Damage/Supernova entrepreneur is a strong inference (name + DOB + separate Wedgwood FIC directorship), NOT hard-confirmed. Zero public FO footprint (no website/LinkedIn/press/AUM); accounts overdue. Residential registered address.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SFO-blue-pool-capital-tsai</t>
+          <t>UKCH-17062903</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Blue Pool Capital (Joe Tsai Family Office)</t>
+          <t>Frigus Family Office Ltd</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3678,58 +3714,54 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tsai family (Joseph Tsai, Alibaba co-founder and chairman)</t>
+          <t>Gudmundsson family (Lydur Gudmundsson, co-founder of Bakkavor; brother Agust Gudmundsson also linked to Frigus-branded entities)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.bluepoolcapital.com/</t>
+          <t>https://www.frigus.is/</t>
         </is>
       </c>
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hong Kong-based investment firm overseeing the Tsai family's wealth across hedge funds, private equity, private credit, venture and sports assets (Brooklyn Nets, LAFC). Raised ~$1bn for its first dedicated PE vehicle (Riverside Fund) reported 2026. Led by CEO Oliver Weisberg (ex-Goldman Sachs, ex-Citadel).</t>
+          <t>UK private limited company incorporated 2 Mar 2026 as the UK entity of Frigus, the Gudmundsson family's single family office (group HQ Kópavogur, Iceland, with a Luxembourg office). Frigus actively manages the family's assets, investments and real estate; its principal holding is a stake in LSE-listed Greencore Group, arising from the 2026 merger of the family business Bakkavor into Greencore. Registered at a London residential address (Fountain House, Park Street, Mayfair).</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Multi-strategy long-term capital: public markets, PE, private credit, venture, and sports/real assets.</t>
+          <t>Active management of family assets, investments and real estate (per frigus.is); large concentrated public-equity position in Greencore Group plus real estate.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Diversified; technology (SpaceX, Epic Games, ByteDance), consumer/luxury (Golden Goose), sports, Japanese real estate</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>~$50 billion</t>
-        </is>
-      </c>
+          <t>Listed equities (food manufacturing via Greencore Group stake), real estate, diversified investments</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Causeway Bay</t>
+          <t>London (UK entity); group HQ Kópavogur, Iceland</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Hong Kong Island</t>
+          <t>London, England (UK entity); Capital Region, Iceland (group)</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Joseph Tsai</t>
+          <t>Lydur Gudmundsson</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Family Principal / Founder</t>
+          <t>Founder / controlling principal (PSC); co-founder of Bakkavor</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -3742,12 +3774,12 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
-          <t>13F-HR filed 2026-05-15; sold ~83% of Blue Owl Capital stake (~$460m) reported 2024-03; joined consortium buying Burgundy vineyards 2024-09; raised ~$1bn first PE fund (Riverside) reported 2026-03-31.</t>
+          <t>UK entity newly incorporated Mar 2026, following the 2026 Bakkavor-Greencore merger. Director Andrea Olsen (Icelandic, CEO/MD of Frigus ehf) appointed at incorporation. Historic Frigus-branded UK entities dissolved (Frigus Ltd dissolved 2022; Frigus Invest Ltd dissolved 2018).</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2026-05-15; 2024-03-03; 2024-09-19; 2026-03-31</t>
+          <t>2026-03-02 (UK incorporation); 2026 (Bakkavor/Greencore merger)</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
@@ -3757,19 +3789,19 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>Some sources describe Blue Pool as a 'multi-family' vehicle co-backed by former Alibaba executives (and occasionally link Jack Ma); primary characterization is Joe Tsai's family office. Website confirmed to be minimal/uninformative per Crain Currency; bluepoolcapital.com domain asserted from press but not independently fetched.</t>
+          <t>'Strong' proof applies to Frigus as a family office group (clear self-description + well-documented Gudmundsson/Bakkavor lineage); the specific UK entity 17062903 is brand-new (Mar 2026) with no filed accounts yet, so UK-level operations are unproven. Lydur Gudmundsson's nationality is shown as British on Companies House though he is the Icelandic Bakkavor co-founder. Switchboard/generic mailboxes belong to the Iceland/Luxembourg offices, not a UK-specific contact.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SFO-mousse-partners-wertheimer</t>
+          <t>SFO-bayshore-global-brin</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mousse Partners (Wertheimer Family Office)</t>
+          <t>Bayshore Global Management (Brin Family Office)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3779,43 +3811,35 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Wertheimer family (Alain and Gerard Wertheimer, owners of Chanel)</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>https://moussepartners.com/</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/moussepartners</t>
-        </is>
-      </c>
+          <t>Brin family (Sergey Brin, Google co-founder)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Investment firm serving as the family office of the Wertheimer family. Manages a global diversified portfolio across public equities, fixed income, private equity, venture and real estate, with investment operations in New York and Asia (Beijing, Hong Kong).</t>
+          <t>Low-profile single-family office managing the wealth of Sergey Brin across public and private markets, real estate and philanthropy. Additional office in Singapore. Reported to have absorbed the Nexus NeuroTech brain-health VC fund in 2026.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Global multi-asset diversified investing with a notable consumer/brands tilt.</t>
+          <t>Broad multi-asset allocation with notable venture/science-and-health direct investing.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Diversified; consumer, luxury/brands, technology, real estate</t>
+          <t>Diversified; neuroscience/brain-health, deep tech, real estate</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>California</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3825,12 +3849,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Charles Heilbronn</t>
+          <t>Sergey Brin</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Founder / Chairman</t>
+          <t>Family Principal</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -3843,12 +3867,12 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
-          <t>Bloomberg feature (2024-2025) reporting the office reshaping its consumer/public-equity bets.</t>
+          <t>Absorbed Nexus NeuroTech brain-health VC fund (reported 2026-04-23, Bloomberg).</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2024/2025 (Bloomberg feature)</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
@@ -3858,19 +3882,19 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>Does not appear as a 13F filer under 'Mousse Partners' (EDGAR full-text search returned 0); investment vehicle is domiciled offshore (Mousse Investments Limited, Bermuda) with a NYC office (9 W. 57th St). AUM figure is the family fortune, not disclosed firm AUM. Firm general phone reported as 212-303-5795 (not an individual principal line).</t>
+          <t>No public website confirmed. AUM figures are press estimates. CEO George Pavlov / CIO Marie Young named in Wikipedia and press but not verified against a primary filing.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SFO-kirkbi-kristiansen</t>
+          <t>SFO-hillspire-schmidt</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KIRKBI (Kirk Kristiansen Family Office)</t>
+          <t>Hillspire (Eric Schmidt Family Office)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3880,62 +3904,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Kirk Kristiansen family (owners of the LEGO Group)</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>https://www.kirkbi.com/</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/kirkbi</t>
-        </is>
-      </c>
+          <t>Schmidt family (Eric &amp; Wendy Schmidt; Eric Schmidt is former Google/Alphabet CEO and chairman)</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Danish family-owned holding and investment company managing the wealth and legacy of the Kirk Kristiansen family. Holds the family's controlling stakes in LEGO Group and Merlin Entertainments and runs a long-term investment portfolio plus a dedicated climate/energy-transition program (KIRKBI Climate). Additional offices in Copenhagen and Baar, Switzerland.</t>
+          <t>Single-family office of Eric and Wendy Schmidt focused on deep technology: artificial intelligence, quantum computation, defense tech and biotech. Reported to have invested in 22+ private AI firms since 2019 (including Anthropic, SandboxAQ, Inworld AI) and topped CNBC's inaugural family-office dealmaking ranking for 2025.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Protect and grow family wealth for future generations; long-term core holdings (LEGO, Merlin) plus diversified investments and thematic climate/energy investing.</t>
+          <t>Deep-tech direct investing concentrated in AI, quantum, defense technology and biotech.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Toys/entertainment (core), real estate, renewable energy/climate, diversified financial investments</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>~$16 billion (family wealth)</t>
-        </is>
-      </c>
+          <t>AI, quantum computing, defense tech, biotech</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Billund</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Region of Southern Denmark</t>
+          <t>California</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Soren Thorup Sorensen</t>
+          <t>Eric Schmidt</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>Family Principal / Founder</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -3948,12 +3960,12 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr">
         <is>
-          <t>KIRKBI Climate follow-on investment in Highview Power (Hunterston project) announced November 2025 (second investment after June 2024 Carrington); Adapture Renewables (KIRKBI-majority-owned) acquired 110MW Colorado solar-plus-storage project March 2025; generational handover of board chair to Thomas Kirk Kristiansen May 2023.</t>
+          <t>Ranked #1 most active U.S. family office for dealmaking in 2025 (15 investments, mostly AI) per CNBC 2026-02-12; disclosed 22 private AI startup investments since 2019 (CNBC 2025-01-21).</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2025-11; 2025-03; 2023-05</t>
+          <t>2026-02-12; 2025-01-21</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
@@ -3963,19 +3975,19 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>KIRKBI is both the family holding company (owns LEGO) and the family investment office; some may classify it as a holding company rather than a pure family office. AUM figure is the family-wealth press figure, not full portfolio value.</t>
+          <t>No public website confirmed (hillspire.com not verified). Does not file 13F (EDGAR full-text search returned no 13F-HR). AUM not disclosed. President Ken Goldman named in press, not verified against a primary filing.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SFO-tethys-invest-bettencourt</t>
+          <t>SFO-mousse-partners-wertheimer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tethys / Tethys Invest (Bettencourt Meyers Family Office)</t>
+          <t>Mousse Partners (Wertheimer Family Office)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3985,62 +3997,58 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Bettencourt Meyers family (majority shareholder of L'Oreal; Francoise Bettencourt Meyers)</t>
+          <t>Wertheimer family (Alain and Gerard Wertheimer, owners of Chanel)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://tethys.fr/</t>
+          <t>https://moussepartners.com/</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/t%C3%A9thys</t>
+          <t>https://www.linkedin.com/company/moussepartners</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Paris-based single-family office of the Bettencourt Meyers family, holder of the family's ~34% L'Oreal stake. Its subsidiary Tethys Invest (&gt;EUR 3bn capital) makes long-term direct investments deliberately outside L'Oreal's competitive scope, with a healthcare emphasis (Elsan private hospitals, Sebia diagnostics).</t>
+          <t>Investment firm serving as the family office of the Wertheimer family. Manages a global diversified portfolio across public equities, fixed income, private equity, venture and real estate, with investment operations in New York and Asia (Beijing, Hong Kong).</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Preserve the L'Oreal core holding and deploy dividend income into long-term entrepreneurial direct investments, notably healthcare, that do not compete with L'Oreal.</t>
+          <t>Global multi-asset diversified investing with a notable consumer/brands tilt.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Healthcare (hospitals, diagnostics), consumer, technology, diversified</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>&gt; $90 billion (family assets)</t>
-        </is>
-      </c>
+          <t>Diversified; consumer, luxury/brands, technology, real estate</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Ile-de-France</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Alexandre Benais</t>
+          <t>Charles Heilbronn</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>CEO, Tethys Invest</t>
+          <t>Founder / Chairman</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
@@ -4053,12 +4061,12 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr">
         <is>
-          <t>Named new head of family investment firm reported 2023-03-13 (The National); family succession moves (Jean-Victor Meyers to L'Oreal vice-chairman; Alexandre Benais to family L'Oreal board seat) reported 2025-02; co-invested (with Chanel/Wertheimer) in The Row reported 2024-09.</t>
+          <t>Bloomberg feature (2024-2025) reporting the office reshaping its consumer/public-equity bets.</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2023-03-13; 2025-02-08; 2024-09</t>
+          <t>2024/2025 (Bloomberg feature)</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
@@ -4068,19 +4076,19 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>'Tethys' (parent) vs 'Tethys Invest' (investment subsidiary) are distinct entities; leadership names span both. AUM is the family-asset press figure, not a disclosed managed-portfolio AUM.</t>
+          <t>Does not appear as a 13F filer under 'Mousse Partners' (EDGAR full-text search returned 0); investment vehicle is domiciled offshore (Mousse Investments Limited, Bermuda) with a NYC office (9 W. 57th St). AUM figure is the family fortune, not disclosed firm AUM. Firm general phone reported as 212-303-5795 (not an individual principal line).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SFO-cofra-holding-brenninkmeijer</t>
+          <t>SFO-kirkbi-kristiansen</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>COFRA Holding (Brenninkmeijer Family Office)</t>
+          <t>KIRKBI (Kirk Kristiansen Family Office)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -4090,58 +4098,62 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Brenninkmeijer family (founders/owners of C&amp;A; ~500 family members)</t>
+          <t>Kirk Kristiansen family (owners of the LEGO Group)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://www.cofraholding.com/</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>https://www.kirkbi.com/</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/kirkbi</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Zug-based family-owned holding coordinating the Brenninkmeijer family's global operations and ~EUR 35-38bn asset base across retail (C&amp;A), real estate (Redevco), private equity (Bregal Investments) and asset management (Anthos). In 2025 the family announced it would open its portfolio to outside investors, a shift from its historically secretive model.</t>
+          <t>Danish family-owned holding and investment company managing the wealth and legacy of the Kirk Kristiansen family. Holds the family's controlling stakes in LEGO Group and Merlin Entertainments and runs a long-term investment portfolio plus a dedicated climate/energy-transition program (KIRKBI Climate). Additional offices in Copenhagen and Baar, Switzerland.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Long-term stewardship of family capital across operating businesses, real estate, private equity and (increasingly) externally-opened investment platforms.</t>
+          <t>Protect and grow family wealth for future generations; long-term core holdings (LEGO, Merlin) plus diversified investments and thematic climate/energy investing.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Retail, real estate, private equity, asset management, climate/energy</t>
+          <t>Toys/entertainment (core), real estate, renewable energy/climate, diversified financial investments</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>EUR 35-38 billion</t>
+          <t>~$16 billion (family wealth)</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Zug</t>
+          <t>Billund</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Canton of Zug</t>
+          <t>Region of Southern Denmark</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Martijn Brenninkmeijer</t>
+          <t>Soren Thorup Sorensen</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Chairman of the Board, COFRA Holding AG</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -4154,12 +4166,12 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr">
         <is>
-          <t>Announced opening of ~EUR 38bn portfolio to external investors (April 2025); Florian Brenninkmeyer appointed CFO effective 1 Jan 2025; Redevco closed landmark GBP 47.5m real-estate-debt loan (April 2025).</t>
+          <t>KIRKBI Climate follow-on investment in Highview Power (Hunterston project) announced November 2025 (second investment after June 2024 Carrington); Adapture Renewables (KIRKBI-majority-owned) acquired 110MW Colorado solar-plus-storage project March 2025; generational handover of board chair to Thomas Kirk Kristiansen May 2023.</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2025-04; 2025-01-01; 2025-04</t>
+          <t>2025-11; 2025-03; 2023-05</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
@@ -4169,19 +4181,19 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>COFRA is primarily a family holding company; its asset-management arm Anthos is opening to third-party capital (2025), which blurs the pure single-family-office boundary. Classified SFO at the holding level but noted as trending toward external capital.</t>
+          <t>KIRKBI is both the family holding company (owns LEGO) and the family investment office; some may classify it as a holding company rather than a pure family office. AUM figure is the family-wealth press figure, not full portfolio value.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SFO-athos-strungmann</t>
+          <t>SFO-tethys-invest-bettencourt</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Athos (Strungmann Family Office)</t>
+          <t>Tethys / Tethys Invest (Bettencourt Meyers Family Office)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -4191,50 +4203,62 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Strungmann family (Andreas and Thomas Strungmann, founders of Hexal)</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Bettencourt Meyers family (majority shareholder of L'Oreal; Francoise Bettencourt Meyers)</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://tethys.fr/</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/t%C3%A9thys</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Munich-based single-family office of the Strungmann twins, focused heavily on biotech and life sciences. Anchored and remains largest shareholder of BioNTech (~43.5%) and holds stakes in Formycon and Immatics; actively recycles BioNTech proceeds into new European biotech ventures.</t>
+          <t>Paris-based single-family office of the Bettencourt Meyers family, holder of the family's ~34% L'Oreal stake. Its subsidiary Tethys Invest (&gt;EUR 3bn capital) makes long-term direct investments deliberately outside L'Oreal's competitive scope, with a healthcare emphasis (Elsan private hospitals, Sebia diagnostics).</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Long-horizon anchor investing in biotech and life sciences, recycling returns from BioNTech into the next generation of European biotech.</t>
+          <t>Preserve the L'Oreal core holding and deploy dividend income into long-term entrepreneurial direct investments, notably healthcare, that do not compete with L'Oreal.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Biotech, life sciences, healthcare technology</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
+          <t>Healthcare (hospitals, diagnostics), consumer, technology, diversified</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>&gt; $90 billion (family assets)</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Bavaria</t>
+          <t>Ile-de-France</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Andreas Strungmann</t>
+          <t>Alexandre Benais</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Family Principal / Co-Founder</t>
+          <t>CEO, Tethys Invest</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -4247,12 +4271,12 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr">
         <is>
-          <t>Participated in AAVantgarde Bio's $141m Series B (Nov 2025); AMSilk EUR 52m round (Sep 2025); Antheia funding ($56m Jun 2025, $24m Jan 2026); admin services of Athos Service acquired by Bolder Group (May 2024).</t>
+          <t>Named new head of family investment firm reported 2023-03-13 (The National); family succession moves (Jean-Victor Meyers to L'Oreal vice-chairman; Alexandre Benais to family L'Oreal board seat) reported 2025-02; co-invested (with Chanel/Wertheimer) in The Row reported 2024-09.</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2025-11; 2025-09; 2025-06; 2026-01; 2024-05</t>
+          <t>2023-03-13; 2025-02-08; 2024-09</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
@@ -4262,19 +4286,19 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>No public website confirmed. 'Athos Service GmbH' is the services entity; the investing vehicle is often cited as 'Athos KG'. Investment-round dates sourced from family-office trade press rather than primary filings. AUM not disclosed.</t>
+          <t>'Tethys' (parent) vs 'Tethys Invest' (investment subsidiary) are distinct entities; leadership names span both. AUM is the family-asset press figure, not a disclosed managed-portfolio AUM.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SFO-premji-invest</t>
+          <t>SFO-cofra-holding-brenninkmeijer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Premji Invest (Azim Premji Family Office)</t>
+          <t>COFRA Holding (Brenninkmeijer Family Office)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4284,62 +4308,58 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Premji family (Azim Premji, founder of Wipro)</t>
+          <t>Brenninkmeijer family (founders/owners of C&amp;A; ~500 family members)</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.premjiinvest.com/</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/premjiinvest</t>
-        </is>
-      </c>
+          <t>https://www.cofraholding.com/</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bengaluru-based family office and investment firm managing the wealth of Azim Premji and family (and closely tied to the Azim Premji Foundation endowment). Invests across public equities, private equity and venture, backing technology, financial services, consumer, healthcare and industrials; crossed $10bn in managed assets.</t>
+          <t>Zug-based family-owned holding coordinating the Brenninkmeijer family's global operations and ~EUR 35-38bn asset base across retail (C&amp;A), real estate (Redevco), private equity (Bregal Investments) and asset management (Anthos). In 2025 the family announced it would open its portfolio to outside investors, a shift from its historically secretive model.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Long-horizon growth investing across public and private markets in emerging/disruptive technology and consumer/financial sectors.</t>
+          <t>Long-term stewardship of family capital across operating businesses, real estate, private equity and (increasingly) externally-opened investment platforms.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Technology, financial services, consumer, healthcare, industrials</t>
+          <t>Retail, real estate, private equity, asset management, climate/energy</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>&gt; $10 billion</t>
+          <t>EUR 35-38 billion</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Zug</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Canton of Zug</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>T.K. Kurien</t>
+          <t>Martijn Brenninkmeijer</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>CEO &amp; Managing Partner</t>
+          <t>Chairman of the Board, COFRA Holding AG</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -4352,12 +4372,12 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Acquisition of Anand Chemiceutics reported 2025-11-13; participated in Runway Series E (with General Atlantic, Nvidia) 2026-02-10; 19 funding rounds / 2 acquisitions in trailing 12 months (per Tracxn, Feb 2026).</t>
+          <t>Announced opening of ~EUR 38bn portfolio to external investors (April 2025); Florian Brenninkmeyer appointed CFO effective 1 Jan 2025; Redevco closed landmark GBP 47.5m real-estate-debt loan (April 2025).</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2025-11-13; 2026-02-10</t>
+          <t>2025-04; 2025-01-01; 2025-04</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
@@ -4367,19 +4387,19 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>Premji Invest also manages the Azim Premji Foundation's endowment, so it straddles family-office and foundation-endowment functions; consistently described as a family office, hence corroborated rather than strong-single-family-only.</t>
+          <t>COFRA is primarily a family holding company; its asset-management arm Anthos is opening to third-party capital (2025), which blurs the pure single-family-office boundary. Classified SFO at the holding level but noted as trending toward external capital.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SFO-catamaran-ventures-murthy</t>
+          <t>SFO-athos-strungmann</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Catamaran Ventures (N.R. Narayana Murthy Family Office)</t>
+          <t>Athos (Strungmann Family Office)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4389,58 +4409,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Murthy family (N.R. Narayana Murthy, co-founder of Infosys)</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://catamaran.in/</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/catamaran-ventures</t>
-        </is>
-      </c>
+          <t>Strungmann family (Andreas and Thomas Strungmann, founders of Hexal)</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bengaluru-based single-family office of Infosys co-founder N.R. Narayana Murthy, investing permanent family capital (no external LPs). Focused on growth capital, notably Indian manufacturing and deep tech; has recently turned more cautious on Indian startup valuations.</t>
+          <t>Munich-based single-family office of the Strungmann twins, focused heavily on biotech and life sciences. Anchored and remains largest shareholder of BioNTech (~43.5%) and holds stakes in Formycon and Immatics; actively recycles BioNTech proceeds into new European biotech ventures.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Permanent-capital growth investing, with emphasis on Indian manufacturing and deep-tech, valuation-disciplined.</t>
+          <t>Long-horizon anchor investing in biotech and life sciences, recycling returns from BioNTech into the next generation of European biotech.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Manufacturing, deep tech, consumer, technology</t>
+          <t>Biotech, life sciences, healthcare technology</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Munich</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Bavaria</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>N.R. Narayana Murthy</t>
+          <t>Andreas Strungmann</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Founder / Chairman Emeritus (Family Principal)</t>
+          <t>Family Principal / Co-Founder</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -4453,12 +4465,12 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr">
         <is>
-          <t>Bloomberg (2025-08-26) reporting Catamaran growing cautious on Indian startup valuations; recent deep-tech stake and follow-on investments (Akshayakalpa first-time, Innoviti follow-on) in 2025.</t>
+          <t>Participated in AAVantgarde Bio's $141m Series B (Nov 2025); AMSilk EUR 52m round (Sep 2025); Antheia funding ($56m Jun 2025, $24m Jan 2026); admin services of Athos Service acquired by Bolder Group (May 2024).</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2025-08-26; 2025</t>
+          <t>2025-11; 2025-09; 2025-06; 2026-01; 2024-05</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
@@ -4468,19 +4480,19 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>Investment pace slowed in 2025 (approximately one new investment) per Tracxn; AUM not disclosed.</t>
+          <t>No public website confirmed. 'Athos Service GmbH' is the services entity; the investing vehicle is often cited as 'Athos KG'. Investment-round dates sourced from family-office trade press rather than primary filings. AUM not disclosed.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>APAC-weybourne-holdings-dyson</t>
+          <t>SFO-premji-invest</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Weybourne (James Dyson Family Office)</t>
+          <t>Premji Invest (Azim Premji Family Office)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4490,54 +4502,62 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Dyson family — Sir James Dyson (founder of Dyson Ltd) and family</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Premji family (Azim Premji, founder of Wipro)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://www.premjiinvest.com/</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/premjiinvest</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Single-family office managing the wealth of Sir James Dyson, founder of the Dyson appliance/engineering group. Founded 2013; a Singapore holding company (Weybourne Holdings Pte Ltd) now sits above the group, alongside a London office and a Singapore-based insurance unit. Investments span English farmland (the Dyson family is among England's largest private landowners), commercial and residential real estate, technology ventures and public markets.</t>
+          <t>Bengaluru-based family office and investment firm managing the wealth of Azim Premji and family (and closely tied to the Azim Premji Foundation endowment). Invests across public equities, private equity and venture, backing technology, financial services, consumer, healthcare and industrials; crossed $10bn in managed assets.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Long-horizon preservation and growth of the Dyson family fortune across agricultural land, real estate, technology ventures and public markets.</t>
+          <t>Long-horizon growth investing across public and private markets in emerging/disruptive technology and consumer/financial sectors.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Agricultural land/farmland; Real estate (commercial and residential); Technology ventures; Public equities</t>
+          <t>Technology, financial services, consumer, healthcare, industrials</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>~USD17-21 billion (family fortune under management; not an officially disclosed AUM figure)</t>
+          <t>&gt; $10 billion</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>India</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>James Dyson</t>
+          <t>T.K. Kurien</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Founder and family principal (Weybourne CEO since Feb 2025: Martin Bowen)</t>
+          <t>CEO &amp; Managing Partner</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
@@ -4550,12 +4570,12 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr">
         <is>
-          <t>Feb 2025: Martin Bowen (ex-Dyson Group PLC legal veteran) appointed Weybourne CEO, succeeding James Bucknall. 2025: transferred at least GBP624m (~USD834m) from a major UK entity to the Singapore holding company, reducing the UK unit's share capital to GBP1. Office reported at 70+ employees across London and Singapore.</t>
+          <t>Acquisition of Anand Chemiceutics reported 2025-11-13; participated in Runway Series E (with General Atlantic, Nvidia) 2026-02-10; 19 funding rounds / 2 acquisitions in trailing 12 months (per Tracxn, Feb 2026).</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2025-02; 2025</t>
+          <t>2025-11-13; 2026-02-10</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
@@ -4565,19 +4585,19 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Group is split between London and Singapore; this record treats the Singapore holding company (Weybourne Holdings Pte Ltd) as HQ per 2025 restructuring reporting. weybourne.com resolves to a parked GoDaddy page, so no confirmed public website/domain. AUM is an estimated family fortune, not a disclosed FO figure. Principal LinkedIn not verified.</t>
+          <t>Premji Invest also manages the Azim Premji Foundation's endowment, so it straddles family-office and foundation-endowment functions; consistently described as a family office, hence corroborated rather than strong-single-family-only.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>APAC-dalio-family-office-singapore</t>
+          <t>SFO-catamaran-ventures-murthy</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dalio Family Office (Ray Dalio) — Singapore</t>
+          <t>Catamaran Ventures (N.R. Narayana Murthy Family Office)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4587,50 +4607,58 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Dalio family — Ray Dalio (founder of Bridgewater Associates) and family</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
+          <t>Murthy family (N.R. Narayana Murthy, co-founder of Infosys)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://catamaran.in/</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/catamaran-ventures</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>The Singapore office of Ray Dalio's global single-family office. The Dalio Family Office invests across private equity, venture capital, real estate and credit and runs the family's philanthropy in Asia. Singapore was chosen as the Asia base given Dalio's long-standing ties to Singapore and China; the DFO also operates in Abu Dhabi. Globally the DFO is led by CEO Janine Racanelli (ex-JPMorgan) and COO Tom Waller; the Singapore office has been associated with Managing Director Tan Mae Shen.</t>
+          <t>Bengaluru-based single-family office of Infosys co-founder N.R. Narayana Murthy, investing permanent family capital (no external LPs). Focused on growth capital, notably Indian manufacturing and deep tech; has recently turned more cautious on Indian startup valuations.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Global multi-asset investing (PE, VC, real estate, credit) with a Singapore hub for Asian investments and philanthropy.</t>
+          <t>Permanent-capital growth investing, with emphasis on Indian manufacturing and deep-tech, valuation-disciplined.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Private equity; Venture capital; Real estate; Credit</t>
+          <t>Manufacturing, deep tech, consumer, technology</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>India</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Ray Dalio</t>
+          <t>N.R. Narayana Murthy</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Founder and family principal (global DFO CEO: Janine Racanelli; Singapore MD: Tan Mae Shen)</t>
+          <t>Founder / Chairman Emeritus (Family Principal)</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -4643,12 +4671,12 @@
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr">
         <is>
-          <t>2020: Dalio Family Office opened in Singapore; Dalio donated USD25m to Singapore's Wealth Management Institute. 2021: Tan Mae Shen joined as Singapore MD; Dalio bought two Club Street shophouses for ~SGD18.9m. Global CIO Mark Baumgartner departed Aug 2024.</t>
+          <t>Bloomberg (2025-08-26) reporting Catamaran growing cautious on Indian startup valuations; recent deep-tech stake and follow-on investments (Akshayakalpa first-time, Innoviti follow-on) in 2025.</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2020; 2021; 2024-08</t>
+          <t>2025-08-26; 2025</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
@@ -4658,19 +4686,19 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>The Dalio Family Office's global headquarters is in Westport, Connecticut (USA), with offices in New York, Singapore and Abu Dhabi; this record covers the Singapore office as a Singapore-hubbed APAC operation, not the global HQ. No AUM or public website confirmed. Principal LinkedIn not verified.</t>
+          <t>Investment pace slowed in 2025 (approximately one new investment) per Tracxn; AUM not disclosed.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>APAC-sunrise-capital-shu-ping</t>
+          <t>APAC-weybourne-holdings-dyson</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sunrise Capital Management (Shu Ping / Haidilao Family Office)</t>
+          <t>Weybourne (James Dyson Family Office)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4680,29 +4708,29 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Shu Ping — co-founder of Haidilao hotpot chain; spouse Zhang Yong (Haidilao co-founder), both naturalised Singapore citizens</t>
+          <t>Dyson family — Sir James Dyson (founder of Dyson Ltd) and family</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Single-family office established in Singapore (Shu Ping appointed sole shareholder and director in July 2019; publicly reported March 2020) to manage the wealth of Haidilao co-founder Shu Ping, reported at around USD7.7bn at the time. Shu Ping holds her Haidilao stake via the Rose Trust; her husband and Haidilao co-founder Zhang Yong holds his via the Apple Trust.</t>
+          <t>Single-family office managing the wealth of Sir James Dyson, founder of the Dyson appliance/engineering group. Founded 2013; a Singapore holding company (Weybourne Holdings Pte Ltd) now sits above the group, alongside a London office and a Singapore-based insurance unit. Investments span English farmland (the Dyson family is among England's largest private landowners), commercial and residential real estate, technology ventures and public markets.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Preservation and diversification of the Shu Ping / Haidilao family fortune from Singapore.</t>
+          <t>Long-horizon preservation and growth of the Dyson family fortune across agricultural land, real estate, technology ventures and public markets.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Diversified/multi-asset (not publicly detailed)</t>
+          <t>Agricultural land/farmland; Real estate (commercial and residential); Technology ventures; Public equities</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>~USD7.7 billion (reported family wealth at establishment, 2020)</t>
+          <t>~USD17-21 billion (family fortune under management; not an officially disclosed AUM figure)</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4722,12 +4750,12 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Shu Ping</t>
+          <t>James Dyson</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Founder, sole shareholder and director</t>
+          <t>Founder and family principal (Weybourne CEO since Feb 2025: Martin Bowen)</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -4740,12 +4768,12 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr">
         <is>
-          <t>Jul 2019: Shu Ping appointed sole shareholder/director of Sunrise Capital Management. Mar 2020: Bloomberg/SCMP/Caixin report the Singapore family office managing ~USD7.7bn. Couple purchased a ~SGD27m home near Singapore Botanic Gardens.</t>
+          <t>Feb 2025: Martin Bowen (ex-Dyson Group PLC legal veteran) appointed Weybourne CEO, succeeding James Bucknall. 2025: transferred at least GBP624m (~USD834m) from a major UK entity to the Singapore holding company, reducing the UK unit's share capital to GBP1. Office reported at 70+ employees across London and Singapore.</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2019-07; 2020-03</t>
+          <t>2025-02; 2025</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
@@ -4755,19 +4783,19 @@
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Entity legal-name suffix (Pte. Ltd.) inferred from Singapore incorporation norms; exact ACRA registration not independently verified in sources reviewed. AUM is a launch-era wealth estimate. Principal LinkedIn/email not available (private SFO).</t>
+          <t>Group is split between London and Singapore; this record treats the Singapore holding company (Weybourne Holdings Pte Ltd) as HQ per 2025 restructuring reporting. weybourne.com resolves to a parked GoDaddy page, so no confirmed public website/domain. AUM is an estimated family fortune, not a disclosed FO figure. Principal LinkedIn not verified.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>APAC-tsao-family-office-tpc</t>
+          <t>APAC-dalio-family-office-singapore</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tsao Family Office (IMC Group / TPC — Chavalit Tsao)</t>
+          <t>Dalio Family Office (Ray Dalio) — Singapore</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4777,28 +4805,24 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Tsao family — founders/controllers of IMC Group (Pan Asia maritime and industrial group); led by fourth-generation steward Chavalit Frederick Tsao</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>https://tsaopaochee.com/</t>
-        </is>
-      </c>
+          <t>Dalio family — Ray Dalio (founder of Bridgewater Associates) and family</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>The single-family office / strategic investment arm of Singapore's Tsao family, whose IMC Group traces its roots to 1906 and spans maritime, industrial and diversified businesses across 15+ countries. Organised today under TPC (Tsao Pao Chee) alongside the OCTAVE well-being ecosystem, the office pursues impact and ESG investing across environment, healthcare and education, reflecting Chavalit Tsao's 'well-being economy' philosophy.</t>
+          <t>The Singapore office of Ray Dalio's global single-family office. The Dalio Family Office invests across private equity, venture capital, real estate and credit and runs the family's philanthropy in Asia. Singapore was chosen as the Asia base given Dalio's long-standing ties to Singapore and China; the DFO also operates in Abu Dhabi. Globally the DFO is led by CEO Janine Racanelli (ex-JPMorgan) and COO Tom Waller; the Singapore office has been associated with Managing Director Tan Mae Shen.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Purpose-led, long-term impact/ESG investing (environment, healthcare, education) integrated with the family's maritime and industrial businesses under a 'well-being economy' model.</t>
+          <t>Global multi-asset investing (PE, VC, real estate, credit) with a Singapore hub for Asian investments and philanthropy.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Impact/ESG; Healthcare; Education; Environment/sustainability; Maritime and industrial</t>
+          <t>Private equity; Venture capital; Real estate; Credit</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -4819,28 +4843,32 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Chavalit Frederick Tsao</t>
+          <t>Ray Dalio</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Chairman, IMC Pan Asia Alliance Group / founder of OCTAVE; fourth-generation family steward</t>
+          <t>Founder and family principal (global DFO CEO: Janine Racanelli; Singapore MD: Tan Mae Shen)</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr">
         <is>
-          <t>OCTAVE Well-being Economy Fund / OCTAVE investment platform active; TPC restructuring of the family enterprise into an integrated 'well-being business ecosystem' (IMC Industrial, OCTAVE and non-profits).</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr"/>
+          <t>2020: Dalio Family Office opened in Singapore; Dalio donated USD25m to Singapore's Wealth Management Institute. 2021: Tan Mae Shen joined as Singapore MD; Dalio bought two Club Street shophouses for ~SGD18.9m. Global CIO Mark Baumgartner departed Aug 2024.</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>2020; 2021; 2024-08</t>
+        </is>
+      </c>
       <c r="V43" t="inlineStr">
         <is>
           <t>C+</t>
@@ -4848,19 +4876,19 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>The family's structure spans several brands (TPC/Tsao Pao Chee, IMC Industrial, OCTAVE, Octave Capital); the precise legal entity of the family office is not cleanly disclosed. Dated recent signals were not pinned down in sources reviewed. No AUM, principal LinkedIn or individual email confirmed.</t>
+          <t>The Dalio Family Office's global headquarters is in Westport, Connecticut (USA), with offices in New York, Singapore and Abu Dhabi; this record covers the Singapore office as a Singapore-hubbed APAC operation, not the global HQ. No AUM or public website confirmed. Principal LinkedIn not verified.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>APAC-wee-investments-uob</t>
+          <t>APAC-sunrise-capital-shu-ping</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wee Investments (Wee family / UOB family office)</t>
+          <t>Sunrise Capital Management (Shu Ping / Haidilao Family Office)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4870,27 +4898,31 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Wee family — Singapore's leading banking dynasty; founder Wee Cho Yaw (UOB; d. Feb 2024); next generation Wee Ee Cheong, Wee Ee Chao, Wee Ee Lim</t>
+          <t>Shu Ping — co-founder of Haidilao hotpot chain; spouse Zhang Yong (Haidilao co-founder), both naturalised Singapore citizens</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>The Wee family's single-family office, associated with the founders and controlling shareholders of United Overseas Bank (UOB), Singapore's third-largest bank. The family's wealth derives from stakes in UOB, property developers UOL Group and Kheng Leong Company, and Haw Par (maker of Tiger Balm). Allocations reportedly span public equities, direct real estate and private equity via SPVs.</t>
+          <t>Single-family office established in Singapore (Shu Ping appointed sole shareholder and director in July 2019; publicly reported March 2020) to manage the wealth of Haidilao co-founder Shu Ping, reported at around USD7.7bn at the time. Shu Ping holds her Haidilao stake via the Rose Trust; her husband and Haidilao co-founder Zhang Yong holds his via the Apple Trust.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Long-term stewardship of a banking-and-property dynasty's wealth: concentrated strategic stakes (UOB, UOL, Haw Par) plus direct real estate and private equity.</t>
+          <t>Preservation and diversification of the Shu Ping / Haidilao family fortune from Singapore.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Banking/financial services; Real estate; Public equities; Private equity</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>Diversified/multi-asset (not publicly detailed)</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>~USD7.7 billion (reported family wealth at establishment, 2020)</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr">
         <is>
           <t>Singapore</t>
@@ -4908,12 +4940,12 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Wee Ee Cheong</t>
+          <t>Shu Ping</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Family principal (Deputy Chairman &amp; CEO of UOB); son of founder Wee Cho Yaw</t>
+          <t>Founder, sole shareholder and director</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
@@ -4926,12 +4958,12 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr">
         <is>
-          <t>May 2024: family-controlled UOL Group made a top bid of ~SGD595m for a prime Singapore site (Forbes). Feb 2024: founder Wee Cho Yaw died, focusing attention on the next-generation family principals.</t>
+          <t>Jul 2019: Shu Ping appointed sole shareholder/director of Sunrise Capital Management. Mar 2020: Bloomberg/SCMP/Caixin report the Singapore family office managing ~USD7.7bn. Couple purchased a ~SGD27m home near Singapore Botanic Gardens.</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>2024-02; 2024-05</t>
+          <t>2019-07; 2020-03</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
@@ -4941,19 +4973,19 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>Wee Investments Pte Ltd is private; several family vehicles exist (Wee Investments, Kheng Leong Company) with overlapping ownership, and the boundary between the 'family office' and family holding companies is not cleanly disclosed. Some structural detail relies on secondary FO directories (Altss/PipelineRoad) rather than primary filings. Principal LinkedIn/email not available.</t>
+          <t>Entity legal-name suffix (Pte. Ltd.) inferred from Singapore incorporation norms; exact ACRA registration not independently verified in sources reviewed. AUM is a launch-era wealth estimate. Principal LinkedIn/email not available (private SFO).</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>APAC-ee-capital-saverin</t>
+          <t>APAC-tsao-family-office-tpc</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EE Capital (Eduardo Saverin family office)</t>
+          <t>Tsao Family Office (IMC Group / TPC — Chavalit Tsao)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4963,24 +4995,28 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Saverin family — Eduardo Saverin (Facebook co-founder, Singapore citizen since 2011) and wife Elaine Andriejanssen</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
+          <t>Tsao family — founders/controllers of IMC Group (Pan Asia maritime and industrial group); led by fourth-generation steward Chavalit Frederick Tsao</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://tsaopaochee.com/</t>
+        </is>
+      </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Single-family office in Singapore managing the wealth of Facebook co-founder Eduardo Saverin, who relocated to Singapore in 2009 and became a citizen in 2011 and is repeatedly ranked Singapore's richest person by Forbes. EE Capital reportedly allocates proprietary capital across private equity, venture capital, hedge funds and public equities. Saverin separately co-founded the venture firm B Capital (a distinct, California-headquartered VC manager).</t>
+          <t>The single-family office / strategic investment arm of Singapore's Tsao family, whose IMC Group traces its roots to 1906 and spans maritime, industrial and diversified businesses across 15+ countries. Organised today under TPC (Tsao Pao Chee) alongside the OCTAVE well-being ecosystem, the office pursues impact and ESG investing across environment, healthcare and education, reflecting Chavalit Tsao's 'well-being economy' philosophy.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Diversified proprietary investing of the Saverin family fortune across private equity, venture capital, hedge funds and public markets.</t>
+          <t>Purpose-led, long-term impact/ESG investing (environment, healthcare, education) integrated with the family's maritime and industrial businesses under a 'well-being economy' model.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Private equity; Venture capital; Hedge funds; Public equities</t>
+          <t>Impact/ESG; Healthcare; Education; Environment/sustainability; Maritime and industrial</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -5001,32 +5037,28 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Eduardo Saverin</t>
+          <t>Chavalit Frederick Tsao</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Family principal (EE Capital Executive Chairman: Elaine Andriejanssen)</t>
+          <t>Chairman, IMC Pan Asia Alliance Group / founder of OCTAVE; fourth-generation family steward</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>unverified</t>
         </is>
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr">
         <is>
-          <t>Sep 2023 / 2024: Saverin ranked Singapore's richest person by Forbes (net worth reported &gt;USD30bn). Sep 2024: Eduardo and Elaine Saverin donated USD15.5m to Singapore American School.</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>2023-09; 2024-09</t>
-        </is>
-      </c>
+          <t>OCTAVE Well-being Economy Fund / OCTAVE investment platform active; TPC restructuring of the family enterprise into an integrated 'well-being business ecosystem' (IMC Industrial, OCTAVE and non-profits).</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
       <c r="V45" t="inlineStr">
         <is>
           <t>C+</t>
@@ -5034,19 +5066,19 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>EE Capital is a private SFO; detail relies on Preqin/Citywire/Altss rather than primary filings, hence 'corroborated' not 'strong'. Do not conflate with B Capital, Saverin's separate VC firm headquartered in California. No website, principal LinkedIn or individual email confirmed.</t>
+          <t>The family's structure spans several brands (TPC/Tsao Pao Chee, IMC Industrial, OCTAVE, Octave Capital); the precise legal entity of the family office is not cleanly disclosed. Dated recent signals were not pinned down in sources reviewed. No AUM, principal LinkedIn or individual email confirmed.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>APAC-wuthelam-holdings-goh</t>
+          <t>APAC-wee-investments-uob</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wuthelam Holdings (Goh family office / Nippon Paint)</t>
+          <t>Wee Investments (Wee family / UOB family office)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5056,24 +5088,24 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Goh family — founder Goh Cheng Liang (Nippon Paint fortune; d. Aug 2025); son and chairman Goh Hup Jin</t>
+          <t>Wee family — Singapore's leading banking dynasty; founder Wee Cho Yaw (UOB; d. Feb 2024); next generation Wee Ee Cheong, Wee Ee Chao, Wee Ee Lim</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr">
         <is>
-          <t>The Goh family's private investment holding company and family office, founded by the late paint tycoon Goh Cheng Liang (long ranked Singapore's richest person) in 1974. Wuthelam Holdings consolidates the family's wealth and controls a ~58% stake in Tokyo-listed Nippon Paint Holdings, Asia's largest paint maker, built up after Wuthelam raised its stake from 39% to 58.7% in August 2020 in exchange for its Southeast Asian JV interests.</t>
+          <t>The Wee family's single-family office, associated with the founders and controlling shareholders of United Overseas Bank (UOB), Singapore's third-largest bank. The family's wealth derives from stakes in UOB, property developers UOL Group and Kheng Leong Company, and Haw Par (maker of Tiger Balm). Allocations reportedly span public equities, direct real estate and private equity via SPVs.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Long-term concentrated ownership of the family's core industrial asset (Nippon Paint) plus diversified private wealth management across generations.</t>
+          <t>Long-term stewardship of a banking-and-property dynasty's wealth: concentrated strategic stakes (UOB, UOL, Haw Par) plus direct real estate and private equity.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Paints/chemicals (Nippon Paint); Public equities; Diversified private investments</t>
+          <t>Banking/financial services; Real estate; Public equities; Private equity</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -5094,12 +5126,12 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Goh Hup Jin</t>
+          <t>Wee Ee Cheong</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Chairman of Nippon Paint Holdings; Wuthelam group executive director; family principal (son of founder)</t>
+          <t>Family principal (Deputy Chairman &amp; CEO of UOB); son of founder Wee Cho Yaw</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
@@ -5112,12 +5144,12 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr">
         <is>
-          <t>Dec 2024: Wuthelam Holdings transferred Nippon Paint stakes to the founder's grandchildren, making six of them billionaires (each &gt;USD1bn). Aug 2025: founder Goh Cheng Liang died aged 98.</t>
+          <t>May 2024: family-controlled UOL Group made a top bid of ~SGD595m for a prime Singapore site (Forbes). Feb 2024: founder Wee Cho Yaw died, focusing attention on the next-generation family principals.</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>2024-12; 2025-08</t>
+          <t>2024-02; 2024-05</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
@@ -5127,19 +5159,19 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Wuthelam Holdings functions as both the family's operating holding company (Nippon Paint control) and its de facto family office; the two roles are not separately disclosed. No public website/domain, AUM, principal LinkedIn or individual email confirmed.</t>
+          <t>Wee Investments Pte Ltd is private; several family vehicles exist (Wee Investments, Kheng Leong Company) with overlapping ownership, and the boundary between the 'family office' and family holding companies is not cleanly disclosed. Some structural detail relies on secondary FO directories (Altss/PipelineRoad) rather than primary filings. Principal LinkedIn/email not available.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SFO-cascade-investment-gates</t>
+          <t>APAC-ee-capital-saverin</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cascade Investment (Bill Gates Family Office)</t>
+          <t>EE Capital (Eduardo Saverin family office)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5149,50 +5181,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Gates family (Bill Gates, co-founder of Microsoft)</t>
+          <t>Saverin family — Eduardo Saverin (Facebook co-founder, Singapore citizen since 2011) and wife Elaine Andriejanssen</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Private investment firm managing the personal wealth of Bill Gates and, through the same manager Michael Larson, the Bill &amp; Melinda Gates Foundation Trust's investable assets. Holds large, often illiquid long-term stakes in mature businesses (Berkshire Hathaway, Canadian National Railway, Republic Services, Four Seasons, Deere) alongside a diversified public-equity portfolio.</t>
+          <t>Single-family office in Singapore managing the wealth of Facebook co-founder Eduardo Saverin, who relocated to Singapore in 2009 and became a citizen in 2011 and is repeatedly ranked Singapore's richest person by Forbes. EE Capital reportedly allocates proprietary capital across private equity, venture capital, hedge funds and public equities. Saverin separately co-founded the venture firm B Capital (a distinct, California-headquartered VC manager).</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Long-horizon, low-turnover allocation to high-quality mature businesses and diversified public equities; capital preservation and growth for the Gates family and foundation trust.</t>
+          <t>Diversified proprietary investing of the Saverin family fortune across private equity, venture capital, hedge funds and public markets.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Diversified; industrials/rails, waste services, hospitality, financials, agriculture equipment</t>
+          <t>Private equity; Venture capital; Hedge funds; Public equities</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Kirkland</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Bill Gates</t>
+          <t>Eduardo Saverin</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Family Principal / Beneficial Owner</t>
+          <t>Family principal (EE Capital Executive Chairman: Elaine Andriejanssen)</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -5205,12 +5237,12 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr">
         <is>
-          <t>Q2 2025 13F-HR filed 2025-08-14 disclosing a significantly increased Berkshire Hathaway (BRK.B) stake (adding ~6.95m shares to ~24.12m); continued long-term holdings in Canadian National Railway, Republic Services, Deere and Four Seasons.</t>
+          <t>Sep 2023 / 2024: Saverin ranked Singapore's richest person by Forbes (net worth reported &gt;USD30bn). Sep 2024: Eduardo and Elaine Saverin donated USD15.5m to Singapore American School.</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2023-09; 2024-09</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
@@ -5220,19 +5252,19 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>ENTITY CONFUSION WARNING: 'Cascade Investment, L.L.C.' (Bill Gates, CIK 0001052192, Kirkland WA) is distinct from 'Cascade Investment Advisors, Inc.' (a small Oregon RIA, CIK 0000919447) and 'Cascade Investment Group, Inc.' — do not merge. AUM not disclosed. Michael Larson is a private figure; no personal email/LinkedIn confirmed. No public website.</t>
+          <t>EE Capital is a private SFO; detail relies on Preqin/Citywire/Altss rather than primary filings, hence 'corroborated' not 'strong'. Do not conflate with B Capital, Saverin's separate VC firm headquartered in California. No website, principal LinkedIn or individual email confirmed.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SFO-willett-advisors-bloomberg</t>
+          <t>APAC-wuthelam-holdings-goh</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Willett Advisors (Michael Bloomberg Family Office)</t>
+          <t>Wuthelam Holdings (Goh family office / Nippon Paint)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5242,54 +5274,50 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Bloomberg family (Michael R. Bloomberg, founder of Bloomberg L.P.)</t>
+          <t>Goh family — founder Goh Cheng Liang (Nippon Paint fortune; d. Aug 2025); son and chairman Goh Hup Jin</t>
         </is>
       </c>
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr">
         <is>
-          <t>New York-based investment firm serving as Michael Bloomberg's family office, managing his personal wealth and the assets of Bloomberg Philanthropies across public markets, hedge funds, private equity and credit, real assets and direct investments. Chaired and led by former U.S. auto-industry adviser and Quadrangle co-founder Steven Rattner.</t>
+          <t>The Goh family's private investment holding company and family office, founded by the late paint tycoon Goh Cheng Liang (long ranked Singapore's richest person) in 1974. Wuthelam Holdings consolidates the family's wealth and controls a ~58% stake in Tokyo-listed Nippon Paint Holdings, Asia's largest paint maker, built up after Wuthelam raised its stake from 39% to 58.7% in August 2020 in exchange for its Southeast Asian JV interests.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Multi-asset, alternatives-heavy allocation (private equity/credit, hedge funds, real assets) for combined personal and philanthropic capital.</t>
+          <t>Long-term concentrated ownership of the family's core industrial asset (Nippon Paint) plus diversified private wealth management across generations.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Diversified; private equity/credit, hedge funds, real assets, public equities</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>~$25 billion</t>
-        </is>
-      </c>
+          <t>Paints/chemicals (Nippon Paint); Public equities; Diversified private investments</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Michael R. Bloomberg</t>
+          <t>Goh Hup Jin</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Family Principal / Beneficial Owner</t>
+          <t>Chairman of Nippon Paint Holdings; Wuthelam group executive director; family principal (son of founder)</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -5302,12 +5330,12 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr">
         <is>
-          <t>Ongoing management of Bloomberg's personal + Bloomberg Philanthropies assets under Chairman/CEO Steven Rattner (per Wikipedia/trade press, current).</t>
+          <t>Dec 2024: Wuthelam Holdings transferred Nippon Paint stakes to the founder's grandchildren, making six of them billionaires (each &gt;USD1bn). Aug 2025: founder Goh Cheng Liang died aged 98.</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>2010 (founded); leadership current per 2026 profiles</t>
+          <t>2024-12; 2025-08</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
@@ -5317,19 +5345,19 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>SEC 13F filings (CIK 0001509379) CEASED after Q3 2014 (last filing 2014-11-04); Willett is NOT a current 13F filer because the bulk of assets are private/alternative. No public website confirmed. AUM is a press figure. Because assets include Bloomberg Philanthropies capital, it straddles family-office and philanthropic-endowment functions, but is consistently characterized as Bloomberg's family office.</t>
+          <t>Wuthelam Holdings functions as both the family's operating holding company (Nippon Paint control) and its de facto family office; the two roles are not separately disclosed. No public website/domain, AUM, principal LinkedIn or individual email confirmed.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SFO-soros-fund-management</t>
+          <t>SFO-cascade-investment-gates</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Soros Fund Management (Soros Family Office)</t>
+          <t>Cascade Investment (Bill Gates Family Office)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5339,47 +5367,35 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Soros family (George Soros, founder; Alexander 'Alex' Soros, chairman)</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>https://www.soros.com/</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/soros</t>
-        </is>
-      </c>
+          <t>Gates family (Bill Gates, co-founder of Microsoft)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
-          <t>New York-based family office managing the Soros family's wealth and serving as the permanent capital base for the Open Society Foundations. Runs a large, actively traded multi-asset book (public equities, index put options, convertible notes, credit and private investments); recent 13F-reported U.S. equity portfolio ~$9bn.</t>
+          <t>Private investment firm managing the personal wealth of Bill Gates and, through the same manager Michael Larson, the Bill &amp; Melinda Gates Foundation Trust's investable assets. Holds large, often illiquid long-term stakes in mature businesses (Berkshire Hathaway, Canadian National Railway, Republic Services, Four Seasons, Deere) alongside a diversified public-equity portfolio.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Actively managed global macro / multi-asset investing, including sizeable hedging (index puts) and credit, supporting long-term family and Open Society capital.</t>
+          <t>Long-horizon, low-turnover allocation to high-quality mature businesses and diversified public equities; capital preservation and growth for the Gates family and foundation trust.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Diversified; technology (Amazon, Nvidia, Alphabet, Apple, TSMC), consumer/media, credit, options/hedging</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>~$28 billion</t>
-        </is>
-      </c>
+          <t>Diversified; industrials/rails, waste services, hospitality, financials, agriculture equipment</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Kirkland</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5389,12 +5405,12 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>George Soros</t>
+          <t>Bill Gates</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Founder / Chairman (Family Principal)</t>
+          <t>Family Principal / Beneficial Owner</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
@@ -5407,12 +5423,12 @@
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr">
         <is>
-          <t>Q1 2026 13F (as of 2026-03-31) disclosing ~263 positions valued ~$9.12bn (~61% equities, ~20% index put options, ~19% convertibles); top holdings Amazon, Electronic Arts, Nvidia, TSMC, Alphabet, Apple. 2023 generational handover to Alex Soros.</t>
+          <t>Q2 2025 13F-HR filed 2025-08-14 disclosing a significantly increased Berkshire Hathaway (BRK.B) stake (adding ~6.95m shares to ~24.12m); continued long-term holdings in Canadian National Railway, Republic Services, Deere and Four Seasons.</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>2026-03-31 (13F period); 2023 (handover)</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
@@ -5422,7 +5438,7 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>Dawn Fitzpatrick is reported as CEO/CIO running day-to-day investing (not independently verified against a primary filing here). Manages Open Society Foundations capital as well as family wealth, so it straddles family-office and foundation-endowment functions; consistently characterized as the Soros family office. A related smaller entity, Soros Capital Management LLC (CIK), also files 13F — do not merge.</t>
+          <t>ENTITY CONFUSION WARNING: 'Cascade Investment, L.L.C.' (Bill Gates, CIK 0001052192, Kirkland WA) is distinct from 'Cascade Investment Advisors, Inc.' (a small Oregon RIA, CIK 0000919447) and 'Cascade Investment Group, Inc.' — do not merge. AUM not disclosed. Michael Larson is a private figure; no personal email/LinkedIn confirmed. No public website.</t>
         </is>
       </c>
     </row>
@@ -6641,12 +6657,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SFO-grok-ventures-cannon-brookes</t>
+          <t>SFO-dfo-management-dell</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Grok Ventures Pty Ltd</t>
+          <t>DFO Management, LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -6656,22 +6672,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (Mike Cannon-Brookes, Atlassian co-founder) -&gt; family office. Confirmed as the Cannon-Brookes single-family office by Capital Brief, Startup Daily and family-office trade sources; distinctive recent climate-focus pivot corroborates active investing.</t>
+          <t>Identified via known UHNW individual (Michael Dell) -&gt; family office entity. Confirmed as Dell's single-family office by the firm's own site (dellfamilyoffice.com) and confirmed as an SEC 13F filer via EDGAR full-text search (13F-HR filed under Michael &amp; Susan Dell Foundation, managed by DFO Management, CIK 0001599858).</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.capitalbrief.com/article/mike-cannon-brookes-grok-ventures-leads-the-family-office-charge-into-climate-tech-8360daab-e12e-4d39-8909-f5fd17583168/</t>
+          <t>https://www.dellfamilyoffice.com/about</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Founded 2016 by Mike Cannon-Brookes (co-founder/co-CEO of Atlassian) and his (then) wife Annie Cannon-Brookes as their single-family office; invests family capital, no external LPs.</t>
+          <t>Firm site states DFO is 'the private investment firm for Dell Technologies Founder &amp; CEO Michael Dell and his family'; launched 1998 as MSD Capital, restructured to DFO Management at end of 2022. Single-family (Dell) only.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Capital Brief and Startup Daily reporting naming Grok Ventures as the Cannon-Brookes family office; altss family-office profile.</t>
+          <t>SEC EDGAR 13F-HR filings (CIK 0001599858, period ending 2026-03-31, filed 2026-05-15) plus dedicated family-office website.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -6681,25 +6697,29 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Not disclosed; Grok has been described as backing Australia's first ~A$1bn climate-tech-focused family VC effort (press).</t>
+          <t>Not publicly disclosed; widely reported as tens of billions tied to Michael Dell's fortune.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Founder and beneficial owner; sets the office's climate mission. Day-to-day CEO is Tan Kueh (appointed to lead climate investing).</t>
+          <t>Beneficial owner and namesake; the family office exists to manage his and his family's capital.</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>unconfirmed</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1599858/000110465926062560/primary_doc.xml</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>https://www.capitalbrief.com/article/mike-cannon-brookes-grok-ventures-leads-the-family-office-charge-into-climate-tech-8360daab-e12e-4d39-8909-f5fd17583168/</t>
+          <t>https://efts.sec.gov/LATEST/search-index?q=%22DFO+Management%22&amp;forms=13F-HR</t>
         </is>
       </c>
       <c r="P14" t="inlineStr"/>
@@ -6707,37 +6727,37 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEC13F-0001599603</t>
+          <t>SFO-blue-pool-capital-tsai</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tarbox Family Office, Inc.</t>
+          <t>Blue Pool Capital Limited (13F filer: Blue Pool Management Ltd.)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sec-13f</t>
+          <t>press</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001599603); discovered via fts</t>
+          <t>Identified via known UHNW individual (Joseph Tsai, Alibaba co-founder) and via SEC 13F filer with a neutral name. Confirmed as an SEC 13F filer (Blue Pool Management Ltd., CIK 0001675855, HQ Causeway Bay Hong Kong) and confirmed as Tsai's family office by Crain Currency / Caproasia reporting.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001599603&amp;type=13F</t>
+          <t>https://www.caproasia.com/2024/09/19/alibaba-co-founder-billionaire-joseph-tsai-joins-investor-consortium-to-buy-vineyards-in-france-burgundy-another-investor-in-group-is-oliver-weisberg-who-is-ceo-of-joseph-tsai-family-office-blue-po/</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>'The multi-family office ... with just 100+ client families and over $1 billion under management'; fee-only, $5M minimum, serving a select group of wealthy families/individuals. Sources: https://tarbox.com/who-we-are/ ; https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079</t>
+          <t>Repeatedly described as the family office of Alibaba co-founder Joe Tsai; oversees the Tsai family's investments and operating assets (incl. Brooklyn Nets, LAFC).</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (13F filer) founded 1985 by Laura Tarbox; fee-only financial planning, tax preparation and investment advisory for HNW individuals, charities, businesses, trusts and estates. Sources: https://tarbox.com/history/ ; https://tarbox.com/who-we-are/</t>
+          <t>SEC EDGAR 13F-HR filings (Blue Pool Management Ltd., CIK 0001675855; latest 2026-05-15, HQ 25/F Hysan Place, 500 Hennessy Road, Causeway Bay) plus Crain Currency/Caproasia press naming it Joe Tsai's family office.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -6747,12 +6767,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Firm-stated. https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079 ; https://tarbox.com/who-we-are/</t>
+          <t>Press estimate (Caproasia/Crain Currency, 2022-2026); not an official disclosure.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Founder (1985), CEO and principal owner; CFP since 1984 with 40+ years' experience; sets firm vision and strategy and is the lead advisor/decision-maker. https://tarbox.com/team/laura-tarbox/ ; https://tarbox.com/history/</t>
+          <t>Beneficial owner; founded the office in 2004/2015. Day-to-day CEO is Oliver Weisberg.</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6760,81 +6780,69 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Published on Laura Tarbox's own public presentation slide (title block reads 'Laura Tarbox, CFP(R) 949.721.2330 Laura@Tarbox.com'). Individual address on the firm's own domain; published, not independently provider-verified. Firm bio page itself shows only a phone and contact form. ZoomInfo listing (l***@tarboxgroup.com) is broker-masked and excluded.</t>
-        </is>
-      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://tarbox.com/team/laura-tarbox/ (listed on Laura Tarbox's bio page; Newport Beach office line) and her presentation https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1675855/000090514826002379/primary_doc.xml</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>https://tarbox.com/history/ ; https://tarbox.com/who-we-are/ ; https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
+          <t>https://data.sec.gov/submissions/CIK0001675855.json</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEC13F-0002056106</t>
+          <t>SFO-willett-advisors-bloomberg</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Stenger Family Office, LLC</t>
+          <t>Willett Advisors LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sec-13f</t>
+          <t>press</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0002056106); discovered via fts</t>
+          <t>Identified via known UHNW individual (Michael Bloomberg) -&gt; family office entity. Confirmed as Bloomberg's family office by Wikipedia and multiple family-office trade sources; SEC EDGAR shows a registered 13F filer (CIK 0001509379) though filings ceased after 2014.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002056106&amp;type=13F</t>
+          <t>https://en.wikipedia.org/wiki/Willett_Advisors</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Self-described 'multi-family office'; the Stenger family has served 'over 1,200 families across the United States'. Serves many outside client families. Sources: https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
+          <t>Described as the investment firm serving as the family office of Michael Bloomberg (founder of Bloomberg L.P., former NYC mayor); manages his personal assets and the assets of Bloomberg Philanthropies. Founded 2010.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEC-registered investment adviser (13F filer); independent fiduciary wealth-management firm offering financial planning, investment management, tax and estate strategies under a family-office model; ~$731M AUM. Sources: https://www.stengerfamilyoffice.com/ </t>
+          <t>Wikipedia and family-office trade press (familyofficehub, altss) name Willett Advisors as Michael Bloomberg's family office; SEC EDGAR registration as a 13F filer (CIK 0001509379).</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>corroborated</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Firm-stated. https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
+          <t>Widely reported managed-asset figure (Wikipedia/trade press) covering Bloomberg's personal and philanthropic assets; not an official disclosure.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Founder and CEO / lead financial advisor; prior Senior Vice President financial advisor at Morgan Stanley Wealth Management, and roles at Invesco PowerShares and PwC; the firm's decision-maker and namesake. https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
+          <t>Beneficial owner; office manages his personal and philanthropic assets. Day-to-day Chairman and CEO is Steven Rattner.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6842,66 +6850,54 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>https://www.stengerfamilyoffice.com (published mailto/contact page)</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>No individual email published on the firm site; contact is via a Calendly link (calendly.com/nicholasstenger/intro-meeting) rather than a published email address. No broker emails accepted.</t>
-        </is>
-      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1509379/000114036114040025/primary_doc.xml</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>https://www.stengerfamilyoffice.com/ ; https://www.stengerfamilyoffice.com/financialadvisornaperville ; https://podcasts.apple.com/us/podcast/the-nick-stenger-show/id1678810370</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
+          <t>https://en.wikipedia.org/wiki/Willett_Advisors</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEC13F-0001908612</t>
+          <t>SFO-soros-fund-management</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Allie Family Office LLC</t>
+          <t>Soros Fund Management LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>sec-13f</t>
+          <t>press</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001908612); discovered via fts</t>
+          <t>Identified via known UHNW individual (George/Alex Soros) -&gt; family office. Confirmed as the Soros family office (converted from hedge fund to family office after returning outside capital in 2011) by Wikipedia and Institutional Investor; active SEC 13F filer (CIK 0001029160).</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001908612&amp;type=13F</t>
+          <t>https://en.wikipedia.org/wiki/Soros_Fund_Management</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Self-described independent multi-family office with offices in Miami and Lima serving multiple Latin American (predominantly Peruvian) HNW families; press reports ~23 client families averaging ~$50M each. Clearly multi-client, not single-family. Sources: https://allie-intl.com/en/home/ ; https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami ; https://fintrx.com/firms/firm/allie-family-office-llc-307144</t>
+          <t>Founded 1970 by George Soros as a hedge fund; returned all outside investor capital in 2011 and has since operated as the Soros family office and the principal asset manager for the Open Society Foundations. No external LPs.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (CRD 307144, 13F filer) established September 2019; provides discretionary and limited-discretionary investment management, estate planning and cross-border tax coordination as an independent multi-family office. Sources: https://adviserinfo.sec.gov/firm/summary/307144 ; https://reports.adviserinfo.sec.gov/crs/crs_307144.pdf</t>
+          <t>Wikipedia and Institutional Investor describe it as the Soros family office; active SEC EDGAR 13F-HR filings under CIK 0001029160 (latest reported Q1 2026, as of 2026-03-31).</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -6911,33 +6907,29 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Form ADV / adviser aggregators and press. https://fintrx.com/firms/firm/allie-family-office-llc-307144 ; https://aum13f.com/firm/allie-family-office-llc ; https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami</t>
+          <t>Widely reported total AUM (~$25-28bn) for the family office; 13F-reported U.S. equities (~$9bn, Q1 2026) are a subset.</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Bruno Ghio founded Allié in 2019, owns 100% of the firm and is Founder &amp; CEO — the lead decision-maker — after serving as Managing Director / Regional Head of the Family Office at BCP and a senior private banker at JPMorgan. Jose Larrabure (CFA, CESGA) leads investment management. https://pe.linkedin.com/in/bruno-ghio-1264b616b ; https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami</t>
+          <t>Founder and beneficial principal; in 2023 handed control of the family's ~$25bn foundation to son Alex Soros, who chairs the Open Society Foundations and sits on the Soros Fund Management investment committee.</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Firm publishes only a generic mailbox (info@allie-intl.com); the Team page lists members without individual emails or direct lines. RocketReach/aggregator listings for Bruno Ghio are broker-sourced and excluded per rules.</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1908612/000190861226000002/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1029160/000090266426002529/primary_doc.xml</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami ; https://www.leadersleague.com/en/news/allie-family-office-adds-partner-in-peru ; https://www.bloomberg.com/news/articles/2024-03-18/family-office-head-sees-more-peruvian-clients-settling-in-miami</t>
+          <t>https://fintool.com/app/research/funds/family-offices/soros-fund-management-llc</t>
         </is>
       </c>
       <c r="P17" t="inlineStr"/>
@@ -6945,37 +6937,37 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEC13F-0001511137</t>
+          <t>SFO-grok-ventures-cannon-brookes</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Pathstone Family Office LLC</t>
+          <t>Grok Ventures Pty Ltd</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>sec-13f</t>
+          <t>press</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001511137); discovered via fts</t>
+          <t>Identified via known UHNW individual (Mike Cannon-Brookes, Atlassian co-founder) -&gt; family office. Confirmed as the Cannon-Brookes single-family office by Capital Brief, Startup Daily and family-office trade sources; distinctive recent climate-focus pivot corroborates active investing.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001511137&amp;type=13F</t>
+          <t>https://www.capitalbrief.com/article/mike-cannon-brookes-grok-ventures-leads-the-family-office-charge-into-climate-tech-8360daab-e12e-4d39-8909-f5fd17583168/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Large partner-owned multi-family office; named 'Best Multi-Family Office ($15B AUM/AUA and above)' at the 2025 Family Wealth Report Awards; serves UHNW families, single family offices, foundations and endowments.</t>
+          <t>Founded 2016 by Mike Cannon-Brookes (co-founder/co-CEO of Atlassian) and his (then) wife Annie Cannon-Brookes as their single-family office; invests family capital, no external LPs.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (CRD 151736) and partner-owned MFO founded 2010; ~775+ employees; comprehensive investment management, tax, insurance, legacy and family-office services.</t>
+          <t>Capital Brief and Startup Daily reporting naming Grok Ventures as the Cannon-Brookes family office; altss family-office profile.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -6985,33 +6977,25 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Family Wealth Report / Pathstone communications and Form ADV (03/31/2025) for the ~$125B firm figure; affiliate-inclusive totals per Preqin/press.</t>
+          <t>Not disclosed; Grok has been described as backing Australia's first ~A$1bn climate-tech-focused family VC effort (press).</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>CEO and co-founder; sets the firm's strategic vision, on the Board of Managers and Executive Leadership Team; previously President of Pathstone and a Principal at Harris myCFO. Primary top decision-maker.</t>
+          <t>Founder and beneficial owner; sets the office's climate mission. Day-to-day CEO is Tan Kueh (appointed to lead climate investing).</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>confirmed</t>
+          <t>unconfirmed</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>No individual email is published on Fleissig's Pathstone bio page or elsewhere on pathstone.com; no qualifying published address found.</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Englewood office line (201) 944-7284 appears on the firm's Form ADV cover (not a personal line).</t>
-        </is>
-      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>https://pathstone.com/people/matthew-fleissig/ ; https://www.familywealthreport.com/article.php/Now-A-$100-Billion-MFO,-What%E2%80%99s-Next-For-Pathstone%3F-?id=202670</t>
+          <t>https://www.capitalbrief.com/article/mike-cannon-brookes-grok-ventures-leads-the-family-office-charge-into-climate-tech-8360daab-e12e-4d39-8909-f5fd17583168/</t>
         </is>
       </c>
       <c r="P18" t="inlineStr"/>
@@ -7019,12 +7003,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SEC13F-0001731123</t>
+          <t>SEC13F-0001599603</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Biltmore Family Office, LLC</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -7034,22 +7018,22 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001731123); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001599603); discovered via fts</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001731123&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001599603&amp;type=13F</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Independent SEC-registered adviser to investment-oriented multi-generational families plus institutional clients; ~951 accounts and ~$3.2-3.5B AUM (avg client ~$38M). A collaborative multi-family office, not a single-family vehicle. Sources: https://www.biltmorefamilyoffice.com/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
+          <t>'The multi-family office ... with just 100+ client families and over $1 billion under management'; fee-only, $5M minimum, serving a select group of wealthy families/individuals. Sources: https://tarbox.com/who-we-are/ ; https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (13F filer) founded 2008 (LLC organized 2013); positions itself as a hybrid family office and RIA. Sources: https://www.biltmorefamilyoffice.com/our-history/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
+          <t>SEC-registered investment adviser (13F filer) founded 1985 by Laura Tarbox; fee-only financial planning, tax preparation and investment advisory for HNW individuals, charities, businesses, trusts and estates. Sources: https://tarbox.com/history/ ; https://tarbox.com/who-we-are/</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -7059,46 +7043,54 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>AUM/ADV aggregators. https://fintrx.com/firms/firm/biltmore-family-office-llc-167174 ; https://advisor.guide/firms/biltmore-family-office ; https://whalewisdom.com/filer/biltmore-family-office-llc</t>
+          <t>Firm-stated. https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079 ; https://tarbox.com/who-we-are/</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Founder and President/CEO; 30 years' experience in investment management, asset allocation and investment-policy creation; prior Partner at GenSpring Family Offices, President at JPMorgan Private Bank, Managing Director at Brown Brothers Harriman. The firm's top decision-maker (Rael Gorelick is Partner &amp; Head of Investments / CIO-equivalent). https://www.biltmorefamilyoffice.com/who-we-are/chris-cecil/ ; https://www.linkedin.com/in/chris-cecil-9701b818/</t>
+          <t>Founder (1985), CEO and principal owner; CFP since 1984 with 40+ years' experience; sets firm vision and strategy and is the lead advisor/decision-maker. https://tarbox.com/team/laura-tarbox/ ; https://tarbox.com/history/</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>No individual email published on the firm site (biltmorefamilyoffice.com pages returned 403 during research; no person@ address found in accessible pages). RocketReach/ContactOut/Datanyze show only masked/pattern (first@biltmorefamilyoffice.com) broker data — excluded; not pattern-generated.</t>
+          <t>Published on Laura Tarbox's own public presentation slide (title block reads 'Laura Tarbox, CFP(R) 949.721.2330 Laura@Tarbox.com'). Individual address on the firm's own domain; published, not independently provider-verified. Firm bio page itself shows only a phone and contact form. ZoomInfo listing (l***@tarboxgroup.com) is broker-masked and excluded.</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Firm main line (6836 Morrison Blvd Suite 100, Charlotte); firm switchboard, not a personal line. https://www.biltmorefamilyoffice.com/</t>
+          <t>https://tarbox.com/team/laura-tarbox/ (listed on Laura Tarbox's bio page; Newport Beach office line) and her presentation https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>https://www.biltmorefamilyoffice.com/our-history/ ; https://businessnc.com/chris-cecil/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
+          <t>https://tarbox.com/history/ ; https://tarbox.com/who-we-are/ ; https://www.unbiased.com/advisor-firm/newport-beach/tarbox-family-office-inc--106079</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SEC13F-0001039807</t>
+          <t>SEC13F-0002056106</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Boston Family Office LLC</t>
+          <t>Stenger Family Office, LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -7108,71 +7100,79 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001039807); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0002056106); discovered via fts</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001039807&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002056106&amp;type=13F</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (CRD #107141) serving many clients -- ~789 accounts across high-net-worth individuals, retail investors and charitable organizations; ~$1.7-2.0B AUM; 15 partners. This is a multi-family office / wealth-management RIA, not a single family's office. Source: https://adviserinfo.sec.gov/firm/summary/107141 and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
+          <t>Self-described 'multi-family office'; the Stenger family has served 'over 1,200 families across the United States'. Serves many outside client families. Sources: https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Operates as an RIA branded as a family office ('The Boston Family Office'), founded 1996; files 13F under CIK 0001039807. Source: https://www.bosfam.com/george-beal/</t>
+          <t xml:space="preserve">SEC-registered investment adviser (13F filer); independent fiduciary wealth-management firm offering financial planning, investment management, tax and estate strategies under a family-office model; ~$731M AUM. Sources: https://www.stengerfamilyoffice.com/ </t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>corroborated</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://adviserinfo.sec.gov/firm/summary/107141 (Form ADV, 2024-2025) and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
+          <t>Firm-stated. https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Beal co-founded the firm in 1996, is a Managing Partner and portfolio manager, and is the named 13F signatory -- an active, current investment decision-maker. Note the firm has 15 partners / ~8 active managing directors, so investment authority is shared. Source: https://www.bosfam.com/george-beal/</t>
+          <t>Founder and CEO / lead financial advisor; prior Senior Vice President financial advisor at Morgan Stanley Wealth Management, and roles at Invesco PowerShares and PwC; the firm's decision-maker and namesake. https://www.stengerfamilyoffice.com/ ; https://www.advisorcheck.com/advisor/6493900-stenger-family-office-llc-naperville-illinois</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://www.stengerfamilyoffice.com (published mailto/contact page)</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Tried: fetched bosfam.com homepage and bosfam.com/george-beal/ team page -- only phone (617-624-0800) is published, no email. A ZoomInfo listing shows a masked pattern 'g***@bosfam.com' but that is a data-broker inference, NOT a published/attested individual address, so it is excluded. Did not construct an address.</t>
+          <t>No individual email published on the firm site; contact is via a Calendly link (calendly.com/nicholasstenger/intro-meeting) rather than a published email address. No broker emails accepted.</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2056106/000208585326000698/primary_doc.xml</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>https://www.bosfam.com/wp-content/uploads/2024/02/2024-ADV-Part-2B-Brochure-Supplement_FINAL.pdf ; https://adviserinfo.sec.gov/firm/summary/107141</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
+          <t>https://www.stengerfamilyoffice.com/ ; https://www.stengerfamilyoffice.com/financialadvisornaperville ; https://podcasts.apple.com/us/podcast/the-nick-stenger-show/id1678810370</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEC13F-0002017744</t>
+          <t>SEC13F-0001908612</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC</t>
+          <t>Allie Family Office LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -7182,22 +7182,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0002017744); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001908612); discovered via fts</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002017744&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001908612&amp;type=13F</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>A registered investment adviser and multi-family office that markets 'Multi Family Office Services' and serves many clients -- high-net-worth individuals, entrepreneurs, families and family offices -- with ~20 staff across multiple US offices. Source: https://arrowrootfamilyoffice.com/team/ and https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
+          <t>Self-described independent multi-family office with offices in Miami and Lima serving multiple Latin American (predominantly Peruvian) HNW families; press reports ~23 client families averaging ~$50M each. Clearly multi-client, not single-family. Sources: https://allie-intl.com/en/home/ ; https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami ; https://fintrx.com/firms/firm/allie-family-office-llc-307144</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SEC-registered RIA (Form ADV on file, SEC# 801-121878) branded 'Arrowroot Family Office'; files 13F under CIK 0002017744; multiple offices and a published team. Source: https://9at.com/Adviser/801-121878</t>
+          <t>SEC-registered investment adviser (CRD 307144, 13F filer) established September 2019; provides discretionary and limited-discretionary investment management, estate planning and cross-border tax coordination as an independent multi-family office. Sources: https://adviserinfo.sec.gov/firm/summary/307144 ; https://reports.adviserinfo.sec.gov/crs/crs_307144.pdf</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://fintrx.com/firms/firm/arrowroot-family-office-llc-168744 (~$431M, Q2 2025); Form ADV: https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf (2025)</t>
+          <t>Form ADV / adviser aggregators and press. https://fintrx.com/firms/firm/allie-family-office-llc-307144 ; https://aum13f.com/firm/allie-family-office-llc ; https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Santos is CEO and principal owner, leading the firm; he is the 13F signatory (Roberto Santos = Rob Santos) and a current decision-maker with 20+ years' experience. Source: https://arrowrootfamilyoffice.com/team/ and https://www.getwarmer.com/advisors/roberto-francisco-santos</t>
+          <t>Bruno Ghio founded Allié in 2019, owns 100% of the firm and is Founder &amp; CEO — the lead decision-maker — after serving as Managing Director / Regional Head of the Family Office at BCP and a senior private banker at JPMorgan. Jose Larrabure (CFA, CESGA) leads investment management. https://pe.linkedin.com/in/bruno-ghio-1264b616b ; https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -7223,17 +7223,17 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Tried: fetched the firm's team page (no email published, only phone 833-224-2249 and a contact form); searched for a published individual email; only data-broker (RocketReach) listings exist, which are not published/attested. Did not construct an address.</t>
+          <t>Firm publishes only a generic mailbox (info@allie-intl.com); the Team page lists members without individual emails or direct lines. RocketReach/aggregator listings for Bruno Ghio are broker-sourced and excluded per rules.</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1908612/000190861226000002/primary_doc.xml</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>https://www.arrowrootfamilyoffice.com/press-releases/arrowroot-family-office-in-michigan/ ; https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
+          <t>https://www.craincurrency.com/family-office-management/family-office-head-bruno-ghio-sees-more-peruvian-clients-settling-miami ; https://www.leadersleague.com/en/news/allie-family-office-adds-partner-in-peru ; https://www.bloomberg.com/news/articles/2024-03-18/family-office-head-sees-more-peruvian-clients-settling-in-miami</t>
         </is>
       </c>
       <c r="P21" t="inlineStr"/>
@@ -7241,12 +7241,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SEC13F-0001756485</t>
+          <t>SEC13F-0001511137</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Independent Family Office, LLC</t>
+          <t>Pathstone Family Office LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -7256,22 +7256,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>EDGAR 13F filer (CIK 0001756485); discovered via fts</t>
+          <t>EDGAR 13F filer (CIK 0001511137); discovered via fts</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001756485&amp;type=13F</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001511137&amp;type=13F</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bespoke family office serving multiple 'select' high-net-worth client families across the country (~34 client relationships, ~$617.8M discretionary AUM); listed by Altss as a Multi Family Office. Multi-client, not single-family. Sources: https://ifollc.com/ ; https://altss.com/profile/independent-family-office-llc ; https://money.usnews.com/financial-advisors/firm/independent-family-office-llc-144811</t>
+          <t>Large partner-owned multi-family office; named 'Best Multi-Family Office ($15B AUM/AUA and above)' at the 2025 Family Wealth Report Awards; serves UHNW families, single family offices, foundations and endowments.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SEC-registered investment adviser (CRD 144811, 13F filer), SEC-registered since 2012 (founded 2005); acts as a capital allocator providing investment oversight, estate-planning support, tax and day-to-day financial administration for HNW families. Sources: https://adviserinfo.sec.gov/individual/summary/6993180 ; https://ifollc.com/blank-5/</t>
+          <t>SEC-registered investment adviser (CRD 151736) and partner-owned MFO founded 2010; ~775+ employees; comprehensive investment management, tax, insurance, legacy and family-office services.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -7281,33 +7281,33 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Form ADV / adviser aggregators. https://money.usnews.com/financial-advisors/firm/independent-family-office-llc-144811 ; https://fintrx.com/firms/firm/independent-family-office-llc-144811 ; https://aum13f.com/firm/independent-family-office-llc</t>
+          <t>Family Wealth Report / Pathstone communications and Form ADV (03/31/2025) for the ~$125B firm figure; affiliate-inclusive totals per Preqin/press.</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>William Michael Reickert established IFO in 2005 after leading The Ayco Company's family-office practice; he is Managing Member/CEO and the firm's lead investment and advisory decision-maker, described as a trusted advisor to Fortune 100 CEOs, fund managers and senior officials. https://ifollc.com/blank-5/ ; https://www.advisorcheck.com/advisor/1673416-william-michael-reickert-independent-family-office-llc-albany-new-york</t>
+          <t>CEO and co-founder; sets the firm's strategic vision, on the Board of Managers and Executive Leadership Team; previously President of Pathstone and a Principal at Harris myCFO. Primary top decision-maker.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>The only address published on the site (home + Reickert's bio page) is 'dr@ifollc.com'; the 'dr' initials do not match 'W. Michael Reickert', so it appears to be a shared/assistant or general mailbox rather than the principal's personal individual email — excluded as not clearly an individual address per rules. No other individual email found.</t>
+          <t>No individual email is published on Fleissig's Pathstone bio page or elsewhere on pathstone.com; no qualifying published address found.</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>https://ifollc.com/blank-5/ and https://ifollc.com/ (main office line, 677 Broadway 7th Floor, Albany; not a personal line)</t>
+          <t>Englewood office line (201) 944-7284 appears on the firm's Form ADV cover (not a personal line).</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>https://ifollc.com/blank-5/ ; https://altss.com/profile/independent-family-office-llc ; https://money.usnews.com/financial-advisors/firm/independent-family-office-llc-144811</t>
+          <t>https://pathstone.com/people/matthew-fleissig/ ; https://www.familywealthreport.com/article.php/Now-A-$100-Billion-MFO,-What%E2%80%99s-Next-For-Pathstone%3F-?id=202670</t>
         </is>
       </c>
       <c r="P22" t="inlineStr"/>
@@ -7315,37 +7315,37 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UKCH-09580739</t>
+          <t>SEC13F-0001731123</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Blu Family Office Limited</t>
+          <t>Biltmore Family Office, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Companies House 09580739 (Private limited company); inc. 8 May 2015</t>
+          <t>EDGAR 13F filer (CIK 0001731123); discovered via fts</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/09580739</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001731123&amp;type=13F</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Founded 2010 by Christian Armbruester (ex-Credit Suisse) to manage his own family's wealth, then expanded to serve multiple families; repeatedly described as a multi-family office in press (Citywire, Private Banker International). FCA-regulated discretionary manager.</t>
+          <t>Independent SEC-registered adviser to investment-oriented multi-generational families plus institutional clients; ~951 accounts and ~$3.2-3.5B AUM (avg client ~$38M). A collaborative multi-family office, not a single-family vehicle. Sources: https://www.biltmorefamilyoffice.com/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Live FCA-regulated firm; active website; investment arm 'Blu Investment Management' (blu-im.com); corporate LinkedIn; named press profiles; defined team.</t>
+          <t>SEC-registered investment adviser (13F filer) founded 2008 (LLC organized 2013); positions itself as a hybrid family office and RIA. Sources: https://www.biltmorefamilyoffice.com/our-history/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -7355,12 +7355,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Third-party estimate via industry data/press (Citywire wealth-manager profile); not officially disclosed.</t>
+          <t>AUM/ADV aggregators. https://fintrx.com/firms/firm/biltmore-family-office-llc-167174 ; https://advisor.guide/firms/biltmore-family-office ; https://whalewisdom.com/filer/biltmore-family-office-llc</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Founder and principal investment decision-maker; single largest shareholder; individual, not nominee. Current day-to-day CEO is Marie Redron.</t>
+          <t>Founder and President/CEO; 30 years' experience in investment management, asset allocation and investment-policy creation; prior Partner at GenSpring Family Offices, President at JPMorgan Private Bank, Managing Director at Brown Brothers Harriman. The firm's top decision-maker (Rael Gorelick is Partner &amp; Head of Investments / CIO-equivalent). https://www.biltmorefamilyoffice.com/who-we-are/chris-cecil/ ; https://www.linkedin.com/in/chris-cecil-9701b818/</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -7371,13 +7371,17 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Firm site publishes only a generic mailbox (info@blu-im.com). No individual/principal email published anywhere located. Nothing pattern-generated.</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>No individual email published on the firm site (biltmorefamilyoffice.com pages returned 403 during research; no person@ address found in accessible pages). RocketReach/ContactOut/Datanyze show only masked/pattern (first@biltmorefamilyoffice.com) broker data — excluded; not pattern-generated.</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Firm main line (6836 Morrison Blvd Suite 100, Charlotte); firm switchboard, not a personal line. https://www.biltmorefamilyoffice.com/</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/09580739/officers; https://citywire.com/wealth-manager/news/richmond-based-multi-family-boutique-names-new-ceo/a1109198</t>
+          <t>https://www.biltmorefamilyoffice.com/our-history/ ; https://businessnc.com/chris-cecil/ ; https://fintrx.com/firms/firm/biltmore-family-office-llc-167174</t>
         </is>
       </c>
       <c r="P23" t="inlineStr"/>
@@ -7385,52 +7389,52 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UKCH-12233405</t>
+          <t>SEC13F-0001039807</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Schwarz Family Office Ltd</t>
+          <t>Boston Family Office LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Companies House 12233405 (Private limited company); inc. 30 September 2019</t>
+          <t>EDGAR 13F filer (CIK 0001039807); discovered via fts</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/12233405</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001039807&amp;type=13F</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Website describes a 'boutique consultancy' providing debt financing, capital raising, IR and fund management for clients, with multiple partners — more advisory/MFO-style than a pure single-family office despite the name. Two shareholders. https://schwarzfamilyoffice.com/</t>
+          <t>SEC-registered investment adviser (CRD #107141) serving many clients -- ~789 accounts across high-net-worth individuals, retail investors and charitable organizations; ~$1.7-2.0B AUM; 15 partners. This is a multi-family office / wealth-management RIA, not a single family's office. Source: https://adviserinfo.sec.gov/firm/summary/107141 and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Active company, SIC 64304 + consultancy codes; own website; listed in Family Capital's 'FamCap 50'. https://schwarzfamilyoffice.com/ ; https://find-and-update.company-information.service.gov.uk/company/12233405</t>
+          <t>Operates as an RIA branded as a family office ('The Boston Family Office'), founded 1996; files 13F under CIK 0001039807. Source: https://www.bosfam.com/george-beal/</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>corroborated</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Not disclosed</t>
+          <t>https://adviserinfo.sec.gov/firm/summary/107141 (Form ADV, 2024-2025) and https://fintrx.com/firms/firm/boston-family-office-llc-107141</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Sole director since incorporation (2019) and majority shareholder (510/1000); ex Merrill Lynch and Bank of Singapore. https://find-and-update.company-information.service.gov.uk/company/12233405/officers ; https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
+          <t>Beal co-founded the firm in 1996, is a Managing Partner and portfolio manager, and is the named 13F signatory -- an active, current investment decision-maker. Note the firm has 15 partners / ~8 active managing directors, so investment authority is shared. Source: https://www.bosfam.com/george-beal/</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -7441,13 +7445,17 @@
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Only a generic mailbox (admin@schwarzfamilyoffice.com) is published (excluded). RocketReach result is a masked/broker source and excluded.</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>Tried: fetched bosfam.com homepage and bosfam.com/george-beal/ team page -- only phone (617-624-0800) is published, no email. A ZoomInfo listing shows a masked pattern 'g***@bosfam.com' but that is a data-broker inference, NOT a published/attested individual address, so it is excluded. Did not construct an address.</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/1039807/000103980726000004/primary_doc.xml</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>https://www.famcap.com/2024/02/the-famcap-50-the-worlds-top-family-capital-investment-specialists/</t>
+          <t>https://www.bosfam.com/wp-content/uploads/2024/02/2024-ADV-Part-2B-Brochure-Supplement_FINAL.pdf ; https://adviserinfo.sec.gov/firm/summary/107141</t>
         </is>
       </c>
       <c r="P24" t="inlineStr"/>
@@ -7455,37 +7463,37 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>APAC-farro-capital</t>
+          <t>SEC13F-0002017744</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Farro Capital Pte. Ltd.</t>
+          <t>Arrowroot Family Office, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>apac-eu-registry</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Independent multi-family office headquartered in Singapore. Confirmed via Hubbis, Private Banker International and Fund Selector Asia coverage of its launch, plus DIFC's announcement of its Dubai regional HQ; leadership and AUM corroborated by Caproasia and the firm's own site.</t>
+          <t>EDGAR 13F filer (CIK 0002017744); discovered via fts</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://hubbis.com/news/farro-capital-establishes-independent-multi-family-office-from-singapore</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0002017744&amp;type=13F</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Described by Hubbis, Private Banker International and Fund Selector Asia as an independent multi-family office established from Singapore, serving multiple UHNW families across 12+ markets.</t>
+          <t>A registered investment adviser and multi-family office that markets 'Multi Family Office Services' and serves many clients -- high-net-worth individuals, entrepreneurs, families and family offices -- with ~20 staff across multiple US offices. Source: https://arrowrootfamilyoffice.com/team/ and https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Multiple reputable trade outlets and the firm's own website confirm Farro Capital operates as a Singapore-headquartered multi-family office / wealth-management platform.</t>
+          <t>SEC-registered RIA (Form ADV on file, SEC# 801-121878) branded 'Arrowroot Family Office'; files 13F under CIK 0002017744; multiple offices and a published team. Source: https://9at.com/Adviser/801-121878</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7495,12 +7503,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Caproasia (Apr 2026) reported AUM increased to ~USD3bn; the firm's Farro &amp; Co site references 'over USD2 billion' managed by sister brand Farro Capital.</t>
+          <t>https://fintrx.com/firms/firm/arrowroot-family-office-llc-168744 (~$431M, Q2 2025); Form ADV: https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf (2025)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Hemant Tucker is the co-founder and current CEO and the firm's top decision-maker (former MD/Market Head for Global South Asia &amp; Middle East at Bank of Singapore).</t>
+          <t>Santos is CEO and principal owner, leading the firm; he is the 13F signatory (Roberto Santos = Rob Santos) and a current decision-maker with 20+ years' experience. Source: https://arrowrootfamilyoffice.com/team/ and https://www.getwarmer.com/advisors/roberto-francisco-santos</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -7511,13 +7519,17 @@
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>No individually published email located; only aggregator (RocketReach) listings, which are excluded per rules against broker/pattern-generated addresses.</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>Tried: fetched the firm's team page (no email published, only phone 833-224-2249 and a contact form); searched for a published individual email; only data-broker (RocketReach) listings exist, which are not published/attested. Did not construct an address.</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>SEC Form 13F-HR signature block, https://www.sec.gov/Archives/edgar/data/2017744/000142050626001082/primary_doc.xml</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>https://www.caproasia.com/2026/04/07/singapore-based-multi-family-office-farro-capital-aum-increased-to-3-billion-founded-in-2022-by-hemant-tucker-manish-tibrewal-mahesh-kumar-rajiv-garg-uthpal-rao-previous-financial-industry-p/</t>
+          <t>https://www.arrowrootfamilyoffice.com/press-releases/arrowroot-family-office-in-michigan/ ; https://arrowrootfamilyoffice.com/wp-content/uploads/2025/04/AFO-Form-ADV-Part-2A-Part-2B-Arrowroot-Family-Office-LLC-Final-2025.pdf</t>
         </is>
       </c>
       <c r="P25" t="inlineStr"/>
@@ -7525,48 +7537,52 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>UKCH-14344019</t>
+          <t>SEC13F-0001756485</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Hazell Family Office Ltd</t>
+          <t>Independent Family Office, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>uk-companies-house</t>
+          <t>sec-13f</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Companies House 14344019 (Private limited company); inc. 8 September 2022</t>
+          <t>EDGAR 13F filer (CIK 0001756485); discovered via fts</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14344019</t>
+          <t>https://www.sec.gov/cgi-bin/browse-edgar?action=getcompany&amp;CIK=0001756485&amp;type=13F</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>All five directors share surname Hazell and one family address (Cefn Henllan Farm, Llanhennock, Usk); appointed same day 2022-09-08; DOB spread (1959-1994) indicates two parents + three adult children — a single-family board. SIC 70221 (financial management).</t>
+          <t>Bespoke family office serving multiple 'select' high-net-worth client families across the country (~34 client relationships, ~$617.8M discretionary AUM); listed by Altss as a Multi Family Office. Multi-client, not single-family. Sources: https://ifollc.com/ ; https://altss.com/profile/independent-family-office-llc ; https://money.usnews.com/financial-advisors/firm/independent-family-office-llc-144811</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Family-only board, no external/nominee officers. Patriarch Mark Hazell is MD of the family's operating businesses (haulage / environmental services), a plausible wealth source. https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
+          <t>SEC-registered investment adviser (CRD 144811, 13F filer), SEC-registered since 2012 (founded 2005); acts as a capital allocator providing investment oversight, estate-planning support, tax and day-to-day financial administration for HNW families. Sources: https://adviserinfo.sec.gov/individual/summary/6993180 ; https://ifollc.com/blank-5/</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Form ADV / adviser aggregators. https://money.usnews.com/financial-advisors/firm/independent-family-office-llc-144811 ; https://fintrx.com/firms/firm/independent-family-office-llc-144811 ; https://aum13f.com/firm/independent-family-office-llc</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Patriarch (b.1959), MD of the family operating companies; most probable investment decision-maker; individual, not nominee.</t>
+          <t>William Michael Reickert established IFO in 2005 after leading The Ayco Company's family-office practice; he is Managing Member/CEO and the firm's lead investment and advisory decision-maker, described as a trusted advisor to Fortune 100 CEOs, fund managers and senior officials. https://ifollc.com/blank-5/ ; https://www.advisorcheck.com/advisor/1673416-william-michael-reickert-independent-family-office-llc-albany-new-york</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -7577,13 +7593,17 @@
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>No firm website; searches returned only company/director aggregators; no published individual email. Nothing pattern-generated.</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>The only address published on the site (home + Reickert's bio page) is 'dr@ifollc.com'; the 'dr' initials do not match 'W. Michael Reickert', so it appears to be a shared/assistant or general mailbox rather than the principal's personal individual email — excluded as not clearly an individual address per rules. No other individual email found.</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>https://ifollc.com/blank-5/ and https://ifollc.com/ (main office line, 677 Broadway 7th Floor, Albany; not a personal line)</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
+          <t>https://ifollc.com/blank-5/ ; https://altss.com/profile/independent-family-office-llc ; https://money.usnews.com/financial-advisors/firm/independent-family-office-llc-144811</t>
         </is>
       </c>
       <c r="P26" t="inlineStr"/>
@@ -7591,12 +7611,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UKCH-14442767</t>
+          <t>UKCH-09580739</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wedgwood Family Office Limited</t>
+          <t>Blu Family Office Limited</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -7606,50 +7626,54 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Companies House 14442767 (Private limited company); inc. 25 October 2022</t>
+          <t>Companies House 09580739 (Private limited company); inc. 8 May 2015</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14442767</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/09580739</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>SIC 66300 (fund management), sole active director Paul Wedgwood at a single residential address; no external clients/multi-family structure. Principal separately holds 'Wedgwood FIC Limited' (a Family Investment Company), consistent with a single-family vehicle.</t>
+          <t>Founded 2010 by Christian Armbruester (ex-Credit Suisse) to manage his own family's wealth, then expanded to serve multiple families; repeatedly described as a multi-family office in press (Citywire, Private Banker International). FCA-regulated discretionary manager.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Active company (inc. 2022-10-25), SIC 66300, residential registered address. Director Paul Wedgwood (b. Jun 1970) very likely the video-game entrepreneur who sold Splash Damage (up to $150m, 2016) and co-founded Supernova Capital — a plausible wealth source. https://en.wikipedia.org/wiki/Paul_Wedgwood</t>
+          <t>Live FCA-regulated firm; active website; investment arm 'Blu Investment Management' (blu-im.com); corporate LinkedIn; named press profiles; defined team.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>corroborated</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>strong</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Third-party estimate via industry data/press (Citywire wealth-manager profile); not officially disclosed.</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Sole active decision-making director since incorporation. Almost certainly the Splash Damage / Supernova Capital entrepreneur (DOB match; also director of Wedgwood FIC Limited).</t>
+          <t>Founder and principal investment decision-maker; single largest shareholder; individual, not nominee. Current day-to-day CEO is Marie Redron.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>No firm website/press page; no individual email published. A uk.linkedin.com/in/paulwedgwood profile is labelled 'The Carbon Trust' and cannot be confirmed as the same person; nothing inferred.</t>
+          <t>Firm site publishes only a generic mailbox (info@blu-im.com). No individual/principal email published anywhere located. Nothing pattern-generated.</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/14442767/officers</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/09580739/officers; https://citywire.com/wealth-manager/news/richmond-based-multi-family-boutique-names-new-ceo/a1109198</t>
         </is>
       </c>
       <c r="P27" t="inlineStr"/>
@@ -7657,12 +7681,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UKCH-17062903</t>
+          <t>UKCH-12233405</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Frigus Family Office Ltd</t>
+          <t>Schwarz Family Office Ltd</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -7672,54 +7696,54 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Companies House 17062903 (Private limited company); inc. 2 March 2026</t>
+          <t>Companies House 12233405 (Private limited company); inc. 30 September 2019</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/17062903</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/12233405</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Frigus group self-describes as 'a single family office, specialising in the active management of assets, investments and real estate' (frigus.is). UK entity controlled by Lydur Gudmundsson (sole PSC, 'significant influence or control'); director Andrea Olsen is MD/CEO of the Icelandic parent Frigus ehf. Single family (Gudmundsson). Sources: https://www.frigus.is/ ; https://find-and-update.company-information.service.gov.uk/company/17062903/persons-with-significant-control</t>
+          <t>Website describes a 'boutique consultancy' providing debt financing, capital raising, IR and fund management for clients, with multiple partners — more advisory/MFO-style than a pure single-family office despite the name. Two shareholders. https://schwarzfamilyoffice.com/</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Explicit self-description as a single family office on frigus.is. Principal Lydur Gudmundsson is co-founder of Bakkavor (now merged into Greencore, 2026); the family office's primary asset is described as a stake in Greencore Group. UK company incorporated 2 Mar 2026 as the UK arm. Sources: https://www.frigus.is/ ; https://find-and-update.company-information.service.gov.uk/company/17062903</t>
+          <t>Active company, SIC 64304 + consultancy codes; own website; listed in Family Capital's 'FamCap 50'. https://schwarzfamilyoffice.com/ ; https://find-and-update.company-information.service.gov.uk/company/12233405</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>corroborated</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Not published as a figure. Primary asset described as a stake in Greencore Group (source: https://www.frigus.is/); no dollar/pound AUM disclosed.</t>
+          <t>Not disclosed</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Sole PSC of the UK entity ('significant influence or control'); the family principal behind Frigus. British (per CH), DOB July 1967. Investment decision-maker / beneficial owner. (Professional executive Andrea Olsen is UK director and CEO/MD of Frigus ehf.)</t>
+          <t>Sole director since incorporation (2019) and majority shareholder (510/1000); ex Merrill Lynch and Bank of Singapore. https://find-and-update.company-information.service.gov.uk/company/12233405/officers ; https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Firm website publishes only generic mailboxes ('contact@frigus.is', 'contact@frigus.lu') and a switchboard (+354 550 9700) — no individual principal email. Generic mailboxes are excluded per rules; pattern-generation not permitted. Source checked: https://www.frigus.is/</t>
+          <t>Only a generic mailbox (admin@schwarzfamilyoffice.com) is published (excluded). RocketReach result is a masked/broker source and excluded.</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr">
         <is>
-          <t>https://find-and-update.company-information.service.gov.uk/company/17062903 ; https://www.frigus.is/</t>
+          <t>https://www.famcap.com/2024/02/the-famcap-50-the-worlds-top-family-capital-investment-specialists/</t>
         </is>
       </c>
       <c r="P28" t="inlineStr"/>
@@ -7727,37 +7751,37 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SFO-dfo-management-dell</t>
+          <t>APAC-farro-capital</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DFO Management, LLC</t>
+          <t>Farro Capital Pte. Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>apac-eu-registry</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (Michael Dell) -&gt; family office entity. Confirmed as Dell's single-family office by the firm's own site (dellfamilyoffice.com) and confirmed as an SEC 13F filer via EDGAR full-text search (13F-HR filed under Michael &amp; Susan Dell Foundation, managed by DFO Management, CIK 0001599858).</t>
+          <t>Independent multi-family office headquartered in Singapore. Confirmed via Hubbis, Private Banker International and Fund Selector Asia coverage of its launch, plus DIFC's announcement of its Dubai regional HQ; leadership and AUM corroborated by Caproasia and the firm's own site.</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.dellfamilyoffice.com/about</t>
+          <t>https://hubbis.com/news/farro-capital-establishes-independent-multi-family-office-from-singapore</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Firm site states DFO is 'the private investment firm for Dell Technologies Founder &amp; CEO Michael Dell and his family'; launched 1998 as MSD Capital, restructured to DFO Management at end of 2022. Single-family (Dell) only.</t>
+          <t>Described by Hubbis, Private Banker International and Fund Selector Asia as an independent multi-family office established from Singapore, serving multiple UHNW families across 12+ markets.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SEC EDGAR 13F-HR filings (CIK 0001599858, period ending 2026-03-31, filed 2026-05-15) plus dedicated family-office website.</t>
+          <t>Multiple reputable trade outlets and the firm's own website confirm Farro Capital operates as a Singapore-headquartered multi-family office / wealth-management platform.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -7767,25 +7791,29 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Not publicly disclosed; widely reported as tens of billions tied to Michael Dell's fortune.</t>
+          <t>Caproasia (Apr 2026) reported AUM increased to ~USD3bn; the firm's Farro &amp; Co site references 'over USD2 billion' managed by sister brand Farro Capital.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Beneficial owner and namesake; the family office exists to manage his and his family's capital.</t>
+          <t>Hemant Tucker is the co-founder and current CEO and the firm's top decision-maker (former MD/Market Head for Global South Asia &amp; Middle East at Bank of Singapore).</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No individually published email located; only aggregator (RocketReach) listings, which are excluded per rules against broker/pattern-generated addresses.</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr">
         <is>
-          <t>https://efts.sec.gov/LATEST/search-index?q=%22DFO+Management%22&amp;forms=13F-HR</t>
+          <t>https://www.caproasia.com/2026/04/07/singapore-based-multi-family-office-farro-capital-aum-increased-to-3-billion-founded-in-2022-by-hemant-tucker-manish-tibrewal-mahesh-kumar-rajiv-garg-uthpal-rao-previous-financial-industry-p/</t>
         </is>
       </c>
       <c r="P29" t="inlineStr"/>
@@ -7793,52 +7821,48 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SFO-bayshore-global-brin</t>
+          <t>UKCH-14344019</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bayshore Global Management, LLC</t>
+          <t>Hazell Family Office Ltd</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>uk-companies-house</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (Sergey Brin) -&gt; family office entity. Confirmed as Brin's single-family office by Bloomberg reporting (2026-04-23, 'Sergey Brin's Family Office Absorbs Nexus NeuroTech Brain-Health VC Fund') and Wikipedia.</t>
+          <t>Companies House 14344019 (Private limited company); inc. 8 September 2022</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-04-23/sergey-brin-s-family-office-takes-over-brain-focused-vc-fund</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14344019</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Described consistently as the single-family office of Google co-founder Sergey Brin; founded 2005; allocates across public/private markets, real estate and philanthropic vehicles.</t>
+          <t>All five directors share surname Hazell and one family address (Cefn Henllan Farm, Llanhennock, Usk); appointed same day 2022-09-08; DOB spread (1959-1994) indicates two parents + three adult children — a single-family board. SIC 70221 (financial management).</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bloomberg news coverage naming it Sergey Brin's family office; Wikipedia entry; multiple family-office databases.</t>
+          <t>Family-only board, no external/nominee officers. Patriarch Mark Hazell is MD of the family's operating businesses (haulage / environmental services), a plausible wealth source. https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Press reports estimate over $100bn tied to Brin's Alphabet stake; not independently disclosed.</t>
-        </is>
-      </c>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Beneficial owner; office manages his assets. Day-to-day led by CEO George Pavlov and CIO Marie Young per press.</t>
+          <t>Patriarch (b.1959), MD of the family operating companies; most probable investment decision-maker; individual, not nominee.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -7847,11 +7871,15 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No firm website; searches returned only company/director aggregators; no published individual email. Nothing pattern-generated.</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2026-04-23/sergey-brin-s-family-office-takes-over-brain-focused-vc-fund</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14344019/officers</t>
         </is>
       </c>
       <c r="P30" t="inlineStr"/>
@@ -7859,52 +7887,48 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SFO-hillspire-schmidt</t>
+          <t>UKCH-14442767</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hillspire, LLC</t>
+          <t>Wedgwood Family Office Limited</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>uk-companies-house</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (Eric Schmidt) -&gt; family office entity. Confirmed as Schmidt's single-family office by CNBC reporting (CNBC 'Inside Wealth Family Office 15', 2026-02-12, and 2025-01-21 piece on 22 AI startup investments).</t>
+          <t>Companies House 14442767 (Private limited company); inc. 25 October 2022</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/2025/01/21/eric-schmidts-family-office-invests-ai-startups.html</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14442767</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Described by CNBC and family-office databases as the single-family office established by former Google CEO Eric Schmidt and his wife Wendy Schmidt (founded 2006).</t>
+          <t>SIC 66300 (fund management), sole active director Paul Wedgwood at a single residential address; no external clients/multi-family structure. Principal separately holds 'Wedgwood FIC Limited' (a Family Investment Company), consistent with a single-family vehicle.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CNBC news coverage naming Hillspire as Eric Schmidt's family office and ranking it the most active U.S. family office for 2025 dealmaking.</t>
+          <t>Active company (inc. 2022-10-25), SIC 66300, residential registered address. Director Paul Wedgwood (b. Jun 1970) very likely the video-game entrepreneur who sold Splash Damage (up to $150m, 2016) and co-founded Supernova Capital — a plausible wealth source. https://en.wikipedia.org/wiki/Paul_Wedgwood</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>strong</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Not disclosed.</t>
-        </is>
-      </c>
+          <t>corroborated</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Beneficial owner and namesake; office run day-to-day by President Ken Goldman per press.</t>
+          <t>Sole active decision-making director since incorporation. Almost certainly the Splash Damage / Supernova Capital entrepreneur (DOB match; also director of Wedgwood FIC Limited).</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -7913,11 +7937,15 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No firm website/press page; no individual email published. A uk.linkedin.com/in/paulwedgwood profile is labelled 'The Carbon Trust' and cannot be confirmed as the same person; nothing inferred.</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr">
         <is>
-          <t>https://www.cnbc.com/2026/02/12/inside-wealth-family-office-15.html</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/14442767/officers</t>
         </is>
       </c>
       <c r="P31" t="inlineStr"/>
@@ -7925,37 +7953,37 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SFO-blue-pool-capital-tsai</t>
+          <t>UKCH-17062903</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Blue Pool Capital Limited (13F filer: Blue Pool Management Ltd.)</t>
+          <t>Frigus Family Office Ltd</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>uk-companies-house</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (Joseph Tsai, Alibaba co-founder) and via SEC 13F filer with a neutral name. Confirmed as an SEC 13F filer (Blue Pool Management Ltd., CIK 0001675855, HQ Causeway Bay Hong Kong) and confirmed as Tsai's family office by Crain Currency / Caproasia reporting.</t>
+          <t>Companies House 17062903 (Private limited company); inc. 2 March 2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.caproasia.com/2024/09/19/alibaba-co-founder-billionaire-joseph-tsai-joins-investor-consortium-to-buy-vineyards-in-france-burgundy-another-investor-in-group-is-oliver-weisberg-who-is-ceo-of-joseph-tsai-family-office-blue-po/</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/17062903</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Repeatedly described as the family office of Alibaba co-founder Joe Tsai; oversees the Tsai family's investments and operating assets (incl. Brooklyn Nets, LAFC).</t>
+          <t>Frigus group self-describes as 'a single family office, specialising in the active management of assets, investments and real estate' (frigus.is). UK entity controlled by Lydur Gudmundsson (sole PSC, 'significant influence or control'); director Andrea Olsen is MD/CEO of the Icelandic parent Frigus ehf. Single family (Gudmundsson). Sources: https://www.frigus.is/ ; https://find-and-update.company-information.service.gov.uk/company/17062903/persons-with-significant-control</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SEC EDGAR 13F-HR filings (Blue Pool Management Ltd., CIK 0001675855; latest 2026-05-15, HQ 25/F Hysan Place, 500 Hennessy Road, Causeway Bay) plus Crain Currency/Caproasia press naming it Joe Tsai's family office.</t>
+          <t>Explicit self-description as a single family office on frigus.is. Principal Lydur Gudmundsson is co-founder of Bakkavor (now merged into Greencore, 2026); the family office's primary asset is described as a stake in Greencore Group. UK company incorporated 2 Mar 2026 as the UK arm. Sources: https://www.frigus.is/ ; https://find-and-update.company-information.service.gov.uk/company/17062903</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -7965,12 +7993,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Press estimate (Caproasia/Crain Currency, 2022-2026); not an official disclosure.</t>
+          <t>Not published as a figure. Primary asset described as a stake in Greencore Group (source: https://www.frigus.is/); no dollar/pound AUM disclosed.</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Beneficial owner; founded the office in 2004/2015. Day-to-day CEO is Oliver Weisberg.</t>
+          <t>Sole PSC of the UK entity ('significant influence or control'); the family principal behind Frigus. British (per CH), DOB July 1967. Investment decision-maker / beneficial owner. (Professional executive Andrea Olsen is UK director and CEO/MD of Frigus ehf.)</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -7979,11 +8007,15 @@
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Firm website publishes only generic mailboxes ('contact@frigus.is', 'contact@frigus.lu') and a switchboard (+354 550 9700) — no individual principal email. Generic mailboxes are excluded per rules; pattern-generation not permitted. Source checked: https://www.frigus.is/</t>
+        </is>
+      </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr">
         <is>
-          <t>https://data.sec.gov/submissions/CIK0001675855.json</t>
+          <t>https://find-and-update.company-information.service.gov.uk/company/17062903 ; https://www.frigus.is/</t>
         </is>
       </c>
       <c r="P32" t="inlineStr"/>
@@ -7991,12 +8023,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SFO-mousse-partners-wertheimer</t>
+          <t>SFO-bayshore-global-brin</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mousse Partners Limited (part of Mousse Investments Limited)</t>
+          <t>Bayshore Global Management, LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -8006,22 +8038,22 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Identified via known UHNW family (Wertheimer, owners of Chanel) -&gt; family office entity. Confirmed as the Wertheimer family office by Bloomberg ('Family office for $90 billion fortune reshapes consumer bets') and Wikipedia.</t>
+          <t>Identified via known UHNW individual (Sergey Brin) -&gt; family office entity. Confirmed as Brin's single-family office by Bloomberg reporting (2026-04-23, 'Sergey Brin's Family Office Absorbs Nexus NeuroTech Brain-Health VC Fund') and Wikipedia.</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/professional/insights/trading/family-office-for-90-billion-fortune-reshapes-consumer-bets/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-04-23/sergey-brin-s-family-office-takes-over-brain-focused-vc-fund</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Described as the family office managing the wealth of Alain and Gerard Wertheimer, owners of Chanel; founded 1991 by Charles Heilbronn (Chanel executive and half-brother of the Wertheimers).</t>
+          <t>Described consistently as the single-family office of Google co-founder Sergey Brin; founded 2005; allocates across public/private markets, real estate and philanthropic vehicles.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bloomberg feature and Wikipedia identify Mousse Partners as the Wertheimer family office; firm site describes it as the investment division of Mousse Investments Limited.</t>
+          <t>Bloomberg news coverage naming it Sergey Brin's family office; Wikipedia entry; multiple family-office databases.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -8031,12 +8063,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Press associates the family fortune at ~$90-100bn; this is the Wertheimer net worth, not a disclosed AUM figure for Mousse.</t>
+          <t>Press reports estimate over $100bn tied to Brin's Alphabet stake; not independently disclosed.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Founder and head of the office; Chanel executive and half-brother of owners Alain and Gerard Wertheimer.</t>
+          <t>Beneficial owner; office manages his assets. Day-to-day led by CEO George Pavlov and CIO Marie Young per press.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -8049,7 +8081,7 @@
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/professional/insights/trading/family-office-for-90-billion-fortune-reshapes-consumer-bets/</t>
+          <t>https://www.bloomberg.com/news/articles/2026-04-23/sergey-brin-s-family-office-takes-over-brain-focused-vc-fund</t>
         </is>
       </c>
       <c r="P33" t="inlineStr"/>
@@ -8057,12 +8089,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SFO-kirkbi-kristiansen</t>
+          <t>SFO-hillspire-schmidt</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>KIRKBI A/S</t>
+          <t>Hillspire, LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8072,22 +8104,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Identified via known UHNW family (Kirk Kristiansen, owners of LEGO) -&gt; holding/family office. Confirmed as the Kristiansen single-family office by KIRKBI's own website and Wikipedia; a registered Danish company (A/S).</t>
+          <t>Identified via known UHNW individual (Eric Schmidt) -&gt; family office entity. Confirmed as Schmidt's single-family office by CNBC reporting (CNBC 'Inside Wealth Family Office 15', 2026-02-12, and 2025-01-21 piece on 22 AI startup investments).</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.kirkbi.com/about-us/family-ownership/</t>
+          <t>https://www.cnbc.com/2025/01/21/eric-schmidts-family-office-invests-ai-startups.html</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Established 1 April 1995 as the family office/holding for the Kirk Kristiansen family (owners of the LEGO Group); owns 75% of the LEGO Group and 47.5% of Merlin Entertainments. Single-family.</t>
+          <t>Described by CNBC and family-office databases as the single-family office established by former Google CEO Eric Schmidt and his wife Wendy Schmidt (founded 2006).</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>KIRKBI's own site (family-ownership page), Wikipedia, and Danish corporate registration as KIRKBI A/S.</t>
+          <t>CNBC news coverage naming Hillspire as Eric Schmidt's family office and ranking it the most active U.S. family office for 2025 dealmaking.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -8097,12 +8129,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Press figure for the family's wealth controlled by KIRKBI; total company equity/portfolio larger and not fully disclosed here.</t>
+          <t>Not disclosed.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>CEO and top investment decision-maker of KIRKBI; family chair is Thomas Kirk Kristiansen (assumed board chair May 2023); CIO is Thomas Lau Schleicher.</t>
+          <t>Beneficial owner and namesake; office run day-to-day by President Ken Goldman per press.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -8115,7 +8147,7 @@
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr">
         <is>
-          <t>https://www.kirkbi.com/press-releases/2025/kirkbi-climate-invests-in-highview/</t>
+          <t>https://www.cnbc.com/2026/02/12/inside-wealth-family-office-15.html</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
@@ -8123,12 +8155,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SFO-tethys-invest-bettencourt</t>
+          <t>SFO-mousse-partners-wertheimer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tethys Invest SAS (Tethys SAS group)</t>
+          <t>Mousse Partners Limited (part of Mousse Investments Limited)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8138,22 +8170,22 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Identified via known UHNW family (Bettencourt Meyers, largest shareholder of L'Oreal) -&gt; family office. Confirmed as the Bettencourt Meyers single-family office by The National and Caproasia reporting and the firm's own site (tethys.fr).</t>
+          <t>Identified via known UHNW family (Wertheimer, owners of Chanel) -&gt; family office entity. Confirmed as the Wertheimer family office by Bloomberg ('Family office for $90 billion fortune reshapes consumer bets') and Wikipedia.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://www.thenationalnews.com/business/money/2023/03/13/billionaires-loreal-heir-names-new-head-of-family-office/</t>
+          <t>https://www.bloomberg.com/professional/insights/trading/family-office-for-90-billion-fortune-reshapes-consumer-bets/</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Described as the single-family office managing the assets of the Bettencourt Meyers family, majority shareholder of L'Oreal; Tethys Invest is the entrepreneurial-investment subsidiary.</t>
+          <t>Described as the family office managing the wealth of Alain and Gerard Wertheimer, owners of Chanel; founded 1991 by Charles Heilbronn (Chanel executive and half-brother of the Wertheimers).</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>The National and Caproasia press naming Tethys as the Bettencourt family office; firm's own website.</t>
+          <t>Bloomberg feature and Wikipedia identify Mousse Partners as the Wertheimer family office; firm site describes it as the investment division of Mousse Investments Limited.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -8163,12 +8195,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Press figure for total family assets (dominated by the L'Oreal stake); Tethys Invest deploys &gt;EUR 3bn of direct-investment capital.</t>
+          <t>Press associates the family fortune at ~$90-100bn; this is the Wertheimer net worth, not a disclosed AUM figure for Mousse.</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Head of the family's investment firm (Tethys Invest) and, per 2025 press, appointed to the L'Oreal board seat area of the family; family chair of Tethys is Francoise Bettencourt Meyers, CEO of Tethys is Jean-Pierre Meyers.</t>
+          <t>Founder and head of the office; Chanel executive and half-brother of owners Alain and Gerard Wertheimer.</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -8181,7 +8213,7 @@
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr">
         <is>
-          <t>https://www.caproasia.com/2025/02/08/loreal-heiress-france-billionaire-francoise-bettencourt-meyers-age-71-with-76-billion-fortune-starts-family-succession-with-retirement-from-loreal-board-as-vice-chairman-son-jean-victo/</t>
+          <t>https://www.bloomberg.com/professional/insights/trading/family-office-for-90-billion-fortune-reshapes-consumer-bets/</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
@@ -8189,12 +8221,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SFO-cofra-holding-brenninkmeijer</t>
+          <t>SFO-kirkbi-kristiansen</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>COFRA Holding AG</t>
+          <t>KIRKBI A/S</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -8204,37 +8236,37 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Identified via known UHNW family (Brenninkmeijer, owners of C&amp;A) -&gt; family holding/office. Confirmed by Crain Currency and the firm's own site as the Brenninkmeijer family's Zug-based holding; leadership verified on cofraholding.com.</t>
+          <t>Identified via known UHNW family (Kirk Kristiansen, owners of LEGO) -&gt; holding/family office. Confirmed as the Kristiansen single-family office by KIRKBI's own website and Wikipedia; a registered Danish company (A/S).</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://www.craincurrency.com/family-office-management/secretive-brenninkmeijer-family-behind-ca-opens-39-billion-retail-empire</t>
+          <t>https://www.kirkbi.com/about-us/family-ownership/</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Established 2001 in Zug to coordinate the Brenninkmeijer family's global businesses and investments; a single-family-owned holding with subsidiaries C&amp;A (retail), Redevco (real estate), Bregal (PE) and Anthos (asset management).</t>
+          <t>Established 1 April 1995 as the family office/holding for the Kirk Kristiansen family (owners of the LEGO Group); owns 75% of the LEGO Group and 47.5% of Merlin Entertainments. Single-family.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Crain Currency reporting on the family's ~$39bn empire; COFRA's own leadership/governance page listing the family-dominated board.</t>
+          <t>KIRKBI's own site (family-ownership page), Wikipedia, and Danish corporate registration as KIRKBI A/S.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>corroborated</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Reported total group asset base (Crain Currency and familyofficehub).</t>
+          <t>Press figure for the family's wealth controlled by KIRKBI; total company equity/portfolio larger and not fully disclosed here.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Family-member chairman since 2018 (former CEO of COFRA, C&amp;A Europe and Anthos); group CEO is Boudewijn Beerkens, CFO Florian Brenninkmeyer (from 2025).</t>
+          <t>CEO and top investment decision-maker of KIRKBI; family chair is Thomas Kirk Kristiansen (assumed board chair May 2023); CIO is Thomas Lau Schleicher.</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -8247,7 +8279,7 @@
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr">
         <is>
-          <t>https://www.cofraholding.com/en/newsroom/latest-news/2025/redevco-closes-landmark-475m-loan-investment-for-new-real-estate-debt-platform/</t>
+          <t>https://www.kirkbi.com/press-releases/2025/kirkbi-climate-invests-in-highview/</t>
         </is>
       </c>
       <c r="P36" t="inlineStr"/>
@@ -8255,12 +8287,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SFO-athos-strungmann</t>
+          <t>SFO-tethys-invest-bettencourt</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Athos Service GmbH (family investment entity Athos KG)</t>
+          <t>Tethys Invest SAS (Tethys SAS group)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -8270,22 +8302,22 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Identified via known UHNW family (Strungmann brothers, BioNTech's largest shareholders) -&gt; family office. Confirmed as their single-family office by Forbes and multiple family-office trade sources; recent dated direct investments corroborate activity.</t>
+          <t>Identified via known UHNW family (Bettencourt Meyers, largest shareholder of L'Oreal) -&gt; family office. Confirmed as the Bettencourt Meyers single-family office by The National and Caproasia reporting and the firm's own site (tethys.fr).</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://www.forbes.com/sites/paulwestall/2021/08/24/the-family-office-saving-lives-boosting-the-economy-and-making-billions/</t>
+          <t>https://www.thenationalnews.com/business/money/2023/03/13/billionaires-loreal-heir-names-new-head-of-family-office/</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Described as the single-family office of twins Andreas and Thomas Strungmann (who founded generics maker Hexal); anchor and largest shareholder of BioNTech (~43.5%).</t>
+          <t>Described as the single-family office managing the assets of the Bettencourt Meyers family, majority shareholder of L'Oreal; Tethys Invest is the entrepreneurial-investment subsidiary.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Forbes and biotech/family-office trade press naming Athos as the Strungmann single-family office; documented anchor investment in BioNTech.</t>
+          <t>The National and Caproasia press naming Tethys as the Bettencourt family office; firm's own website.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -8295,12 +8327,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Not disclosed; dominated by the BioNTech stake (~43.5%).</t>
+          <t>Press figure for total family assets (dominated by the L'Oreal stake); Tethys Invest deploys &gt;EUR 3bn of direct-investment capital.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Beneficial owner (with twin brother Thomas Strungmann) of the family office; jointly direct its investments.</t>
+          <t>Head of the family's investment firm (Tethys Invest) and, per 2025 press, appointed to the L'Oreal board seat area of the family; family chair of Tethys is Francoise Bettencourt Meyers, CEO of Tethys is Jean-Pierre Meyers.</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -8313,7 +8345,7 @@
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr">
         <is>
-          <t>https://familyofficehub.io/blog/athos-family-office-invests-in-aavantgarde-bios-141m-series-b/</t>
+          <t>https://www.caproasia.com/2025/02/08/loreal-heiress-france-billionaire-francoise-bettencourt-meyers-age-71-with-76-billion-fortune-starts-family-succession-with-retirement-from-loreal-board-as-vice-chairman-son-jean-victo/</t>
         </is>
       </c>
       <c r="P37" t="inlineStr"/>
@@ -8321,12 +8353,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SFO-premji-invest</t>
+          <t>SFO-cofra-holding-brenninkmeijer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Premji Invest</t>
+          <t>COFRA Holding AG</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -8336,22 +8368,22 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (Azim Premji, Wipro founder) -&gt; family office. Confirmed as his family office by The Arc and family-office databases; recent dated deals corroborate active investing.</t>
+          <t>Identified via known UHNW family (Brenninkmeijer, owners of C&amp;A) -&gt; family holding/office. Confirmed by Crain Currency and the firm's own site as the Brenninkmeijer family's Zug-based holding; leadership verified on cofraholding.com.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.thearcweb.com/article/wipro-azim-premji-invest-family-office-tk-kurien-0clyngtMEXrGHBNX</t>
+          <t>https://www.craincurrency.com/family-office-management/secretive-brenninkmeijer-family-behind-ca-opens-39-billion-retail-empire</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Described as the private investment office managing the portfolio of Wipro founder Azim Premji and family across public equities, PE and venture; founded 2006, offices in Bengaluru and Menlo Park.</t>
+          <t>Established 2001 in Zug to coordinate the Brenninkmeijer family's global businesses and investments; a single-family-owned holding with subsidiaries C&amp;A (retail), Redevco (real estate), Bregal (PE) and Anthos (asset management).</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>The Arc and multiple family-office databases identify Premji Invest as Azim Premji's family office; firm website.</t>
+          <t>Crain Currency reporting on the family's ~$39bn empire; COFRA's own leadership/governance page listing the family-dominated board.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -8361,12 +8393,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>The Arc reporting that the family office crossed $10bn in managed assets.</t>
+          <t>Reported total group asset base (Crain Currency and familyofficehub).</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Chief executive and top investment decision-maker of the office (former Wipro CEO); family principal is Azim Premji; U.S. office led by Sandesh Patnam.</t>
+          <t>Family-member chairman since 2018 (former CEO of COFRA, C&amp;A Europe and Anthos); group CEO is Boudewijn Beerkens, CFO Florian Brenninkmeyer (from 2025).</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -8379,7 +8411,7 @@
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr">
         <is>
-          <t>https://tracxn.com/d/private-equity/premjiinvest/__a9W9DN9hd7WxIGfm5z8PuA6IrDlu-VIas8-t59BU6xw</t>
+          <t>https://www.cofraholding.com/en/newsroom/latest-news/2025/redevco-closes-landmark-475m-loan-investment-for-new-real-estate-debt-platform/</t>
         </is>
       </c>
       <c r="P38" t="inlineStr"/>
@@ -8387,12 +8419,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SFO-catamaran-ventures-murthy</t>
+          <t>SFO-athos-strungmann</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Catamaran Management Services Pvt. Ltd. (Catamaran Ventures)</t>
+          <t>Athos Service GmbH (family investment entity Athos KG)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -8402,22 +8434,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (N.R. Narayana Murthy, Infosys founder) -&gt; family office. Confirmed as his single-family office by Bloomberg and the firm's own site; described as investing permanent capital with no external LPs.</t>
+          <t>Identified via known UHNW family (Strungmann brothers, BioNTech's largest shareholders) -&gt; family office. Confirmed as their single-family office by Forbes and multiple family-office trade sources; recent dated direct investments corroborate activity.</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2025-08-26/family-office-to-billionaire-murthy-warns-on-startup-valuations</t>
+          <t>https://www.forbes.com/sites/paulwestall/2021/08/24/the-family-office-saving-lives-boosting-the-economy-and-making-billions/</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Firm describes itself as a single-family office investing permanent capital with no external limited partners, managing the assets of Narayana Murthy and family.</t>
+          <t>Described as the single-family office of twins Andreas and Thomas Strungmann (who founded generics maker Hexal); anchor and largest shareholder of BioNTech (~43.5%).</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bloomberg reporting naming it the family office of billionaire Narayana Murthy; firm's own 'About' page stating single-family-office / permanent-capital structure.</t>
+          <t>Forbes and biotech/family-office trade press naming Athos as the Strungmann single-family office; documented anchor investment in BioNTech.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -8427,12 +8459,12 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Not disclosed.</t>
+          <t>Not disclosed; dominated by the BioNTech stake (~43.5%).</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Founder and ultimate principal; firm led operationally by Chairman M.D. Ranganath (ex-Infosys CFO) and President Deepak Padaki.</t>
+          <t>Beneficial owner (with twin brother Thomas Strungmann) of the family office; jointly direct its investments.</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -8445,7 +8477,7 @@
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2025-08-26/family-office-to-billionaire-murthy-warns-on-startup-valuations</t>
+          <t>https://familyofficehub.io/blog/athos-family-office-invests-in-aavantgarde-bios-141m-series-b/</t>
         </is>
       </c>
       <c r="P39" t="inlineStr"/>
@@ -8453,52 +8485,52 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>APAC-weybourne-holdings-dyson</t>
+          <t>SFO-premji-invest</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Weybourne Holdings Pte. Ltd. (Singapore parent; UK operating entity Weybourne Holdings Limited)</t>
+          <t>Premji Invest</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>apac-eu-registry</t>
+          <t>press</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Known UHNW founder (Sir James Dyson). Confirmed via Crain Currency and Asia News Network reporting on Weybourne restructuring its family-office empire and transferring funds to its Singapore holding company; Weybourne is repeatedly named as Dyson's single-family office.</t>
+          <t>Identified via known UHNW individual (Azim Premji, Wipro founder) -&gt; family office. Confirmed as his family office by The Arc and family-office databases; recent dated deals corroborate active investing.</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://www.craincurrency.com/family-office-management/james-dyson-reworks-weybourne-family-office-empire-17-billion-fortune</t>
+          <t>https://www.thearcweb.com/article/wipro-azim-premji-invest-family-office-tk-kurien-0clyngtMEXrGHBNX</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Reported by Crain Currency, Bloomberg (via WealthBriefing) and Asia News Network as Sir James Dyson's single-family office managing the family's ~USD17-21bn fortune; not an external multi-client manager.</t>
+          <t>Described as the private investment office managing the portfolio of Wipro founder Azim Premji and family across public equities, PE and venture; founded 2006, offices in Bengaluru and Menlo Park.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Multiple reputable outlets (Crain Currency, Bloomberg/WealthBriefing, Asia News Network) describe Weybourne as the Dyson family office; Weybourne Holdings Pte Ltd is the Singapore-based parent of the UK family office with an insurance unit and 70+ staff across London and Singapore.</t>
+          <t>The Arc and multiple family-office databases identify Premji Invest as Azim Premji's family office; firm website.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>corroborated</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Estimated family fortune cited by Crain Currency (~USD17bn) and Asia News Network (~USD21bn); Weybourne does not publish an AUM figure.</t>
+          <t>The Arc reporting that the family office crossed $10bn in managed assets.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Sir James Dyson is the family principal whose wealth the office manages; day-to-day the office is run by CEO Martin Bowen (appointed February 2025, succeeding James Bucknall).</t>
+          <t>Chief executive and top investment decision-maker of the office (former Wipro CEO); family principal is Azim Premji; U.S. office led by Sandesh Patnam.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -8507,15 +8539,11 @@
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Private single-family office; no individual email address published in any source reviewed.</t>
-        </is>
-      </c>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr">
         <is>
-          <t>https://www.craincurrency.com/family-office-management/james-dyson-reworks-weybourne-family-office-empire-17-billion-fortune</t>
+          <t>https://tracxn.com/d/private-equity/premjiinvest/__a9W9DN9hd7WxIGfm5z8PuA6IrDlu-VIas8-t59BU6xw</t>
         </is>
       </c>
       <c r="P40" t="inlineStr"/>
@@ -8523,52 +8551,52 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>APAC-dalio-family-office-singapore</t>
+          <t>SFO-catamaran-ventures-murthy</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Dalio Family Office (Singapore office of the Dalio Family Office / DFO)</t>
+          <t>Catamaran Management Services Pvt. Ltd. (Catamaran Ventures)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>apac-eu-registry</t>
+          <t>press</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Known UHNW founder (Ray Dalio, Bridgewater Associates). Confirmed via South China Morning Post, The Edge Singapore and Bloomberg reporting that Dalio opened a Singapore family office to run Asian investments and philanthropy.</t>
+          <t>Identified via known UHNW individual (N.R. Narayana Murthy, Infosys founder) -&gt; family office. Confirmed as his single-family office by Bloomberg and the firm's own site; described as investing permanent capital with no external LPs.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/news/asia/southeast-asia/article/3111745/us-billionaire-ray-dalio-latest-open-family-office</t>
+          <t>https://www.bloomberg.com/news/articles/2025-08-26/family-office-to-billionaire-murthy-warns-on-startup-valuations</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Reported by SCMP, The Edge Singapore and Bloomberg as the single-family office of Bridgewater founder Ray Dalio, established in Singapore in 2020 to manage his regional investments and philanthropy.</t>
+          <t>Firm describes itself as a single-family office investing permanent capital with no external limited partners, managing the assets of Narayana Murthy and family.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Multiple reputable outlets confirm the Dalio Family Office (DFO) opened a Singapore office in 2020; Caproasia documents a Singapore Managing Director (Tan Mae Shen, joined 2021) and shophouse purchases in Singapore linked to Dalio.</t>
+          <t>Bloomberg reporting naming it the family office of billionaire Narayana Murthy; firm's own 'About' page stating single-family-office / permanent-capital structure.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>corroborated</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>No DFO AUM disclosed; Dalio's personal fortune is widely reported but not a family-office AUM figure.</t>
+          <t>Not disclosed.</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Ray Dalio is the family principal. Janine Racanelli is global CEO of the Dalio Family Office; Tan Mae Shen (ex-JPMorgan/Credit Suisse) has been reported as Singapore Managing Director since 2021.</t>
+          <t>Founder and ultimate principal; firm led operationally by Chairman M.D. Ranganath (ex-Infosys CFO) and President Deepak Padaki.</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -8577,15 +8605,11 @@
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Private single-family office; no individual email address published in any source reviewed.</t>
-        </is>
-      </c>
+      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr">
         <is>
-          <t>https://www.caproasia.com/2024/05/23/154-billion-bridgewater-associates-hedge-fund-founder-ray-dalio-bought-2-shophouses-in-singapore-club-street-in-2021-for-18-9-million-dalio-family-office-singapore-managing-director-tan-mae-shen-li/</t>
+          <t>https://www.bloomberg.com/news/articles/2025-08-26/family-office-to-billionaire-murthy-warns-on-startup-valuations</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -8593,12 +8617,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>APAC-sunrise-capital-shu-ping</t>
+          <t>APAC-weybourne-holdings-dyson</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Sunrise Capital Management Pte. Ltd.</t>
+          <t>Weybourne Holdings Pte. Ltd. (Singapore parent; UK operating entity Weybourne Holdings Limited)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -8608,22 +8632,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Known UHNW founder (Shu Ping, Haidilao co-founder). Confirmed via Bloomberg, South China Morning Post and Caixin Global reporting that Shu Ping opened a Singapore family office (Sunrise Capital Management), of which she is sole shareholder and director, to manage her fortune.</t>
+          <t>Known UHNW founder (Sir James Dyson). Confirmed via Crain Currency and Asia News Network reporting on Weybourne restructuring its family-office empire and transferring funds to its Singapore holding company; Weybourne is repeatedly named as Dyson's single-family office.</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://www.scmp.com/business/article/3065092/haidilao-hotpot-queen-opens-singapore-family-office-manage-us77-billion</t>
+          <t>https://www.craincurrency.com/family-office-management/james-dyson-reworks-weybourne-family-office-empire-17-billion-fortune</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bloomberg ('Hotpot Queen Opens Family Office in Singapore to Manage Wealth'), SCMP and Caixin all describe Sunrise Capital Management as the single-family office set up to manage Shu Ping's ~USD7.7bn fortune; she is sole shareholder and director.</t>
+          <t>Reported by Crain Currency, Bloomberg (via WealthBriefing) and Asia News Network as Sir James Dyson's single-family office managing the family's ~USD17-21bn fortune; not an external multi-client manager.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Reputable press (Bloomberg, SCMP, Caixin Global) name the entity as Shu Ping's family office established in 2019/2020.</t>
+          <t>Multiple reputable outlets (Crain Currency, Bloomberg/WealthBriefing, Asia News Network) describe Weybourne as the Dyson family office; Weybourne Holdings Pte Ltd is the Singapore-based parent of the UK family office with an insurance unit and 70+ staff across London and Singapore.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -8633,12 +8657,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Family wealth figure cited by SCMP/Bloomberg/Caixin at the office's launch (2020); not an audited FO AUM.</t>
+          <t>Estimated family fortune cited by Crain Currency (~USD17bn) and Asia News Network (~USD21bn); Weybourne does not publish an AUM figure.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Shu Ping is the family principal and, per press, the sole shareholder and director of Sunrise Capital Management.</t>
+          <t>Sir James Dyson is the family principal whose wealth the office manages; day-to-day the office is run by CEO Martin Bowen (appointed February 2025, succeeding James Bucknall).</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -8655,7 +8679,7 @@
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr">
         <is>
-          <t>https://www.bloomberg.com/news/articles/2020-03-04/hotpot-queen-opens-family-office-in-singapore-to-manage-wealth</t>
+          <t>https://www.craincurrency.com/family-office-management/james-dyson-reworks-weybourne-family-office-empire-17-billion-fortune</t>
         </is>
       </c>
       <c r="P42" t="inlineStr"/>
@@ -8663,12 +8687,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>APAC-tsao-family-office-tpc</t>
+          <t>APAC-dalio-family-office-singapore</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tsao Pao Chee (TPC) Group — Tsao Family Office (investment arm; OCTAVE brand)</t>
+          <t>Dalio Family Office (Singapore office of the Dalio Family Office / DFO)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -8678,37 +8702,37 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Known Singapore business family (Tsao family, IMC Group maritime dynasty). Confirmed via Preqin single-family-office profile and the family's own TPC/Tsao Pao Chee and OCTAVE websites describing the Tsao Family Office as the strategic investment arm of the group.</t>
+          <t>Known UHNW founder (Ray Dalio, Bridgewater Associates). Confirmed via South China Morning Post, The Edge Singapore and Bloomberg reporting that Dalio opened a Singapore family office to run Asian investments and philanthropy.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://www.preqin.com/data/profile/investor/tsao-family-office/246728</t>
+          <t>https://www.scmp.com/news/asia/southeast-asia/article/3111745/us-billionaire-ray-dalio-latest-open-family-office</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Preqin classifies the Tsao Family Office as a single-family office based in Singapore; the family's TPC/OCTAVE sites describe it as the investment arm of the Tsao family (IMC Group), an integrated maritime and industrial group founded 1906.</t>
+          <t>Reported by SCMP, The Edge Singapore and Bloomberg as the single-family office of Bridgewater founder Ray Dalio, established in Singapore in 2020 to manage his regional investments and philanthropy.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Preqin single-family-office profile plus the family's own corporate sites (tsaopaochee.com, octaveinvestment.com) confirm a family-owned investment office.</t>
+          <t>Multiple reputable outlets confirm the Dalio Family Office (DFO) opened a Singapore office in 2020; Caproasia documents a Singapore Managing Director (Tan Mae Shen, joined 2021) and shophouse purchases in Singapore linked to Dalio.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>corroborated</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>No public AUM figure disclosed by the family office in sources reviewed.</t>
+          <t>No DFO AUM disclosed; Dalio's personal fortune is widely reported but not a family-office AUM figure.</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Chavalit Tsao is the current family principal and chairman leading the group and its investment/impact activities.</t>
+          <t>Ray Dalio is the family principal. Janine Racanelli is global CEO of the Dalio Family Office; Tan Mae Shen (ex-JPMorgan/Credit Suisse) has been reported as Singapore Managing Director since 2021.</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -8719,13 +8743,13 @@
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>No individual published email located; group contact channels are via corporate websites only.</t>
+          <t>Private single-family office; no individual email address published in any source reviewed.</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
         <is>
-          <t>https://tsaopaochee.com/our-brands/octave/</t>
+          <t>https://www.caproasia.com/2024/05/23/154-billion-bridgewater-associates-hedge-fund-founder-ray-dalio-bought-2-shophouses-in-singapore-club-street-in-2021-for-18-9-million-dalio-family-office-singapore-managing-director-tan-mae-shen-li/</t>
         </is>
       </c>
       <c r="P43" t="inlineStr"/>
@@ -8733,12 +8757,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>APAC-wee-investments-uob</t>
+          <t>APAC-sunrise-capital-shu-ping</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wee Investments Pte. Ltd.</t>
+          <t>Sunrise Capital Management Pte. Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -8748,37 +8772,37 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Known Singapore banking dynasty (Wee family, controllers of UOB). Confirmed via Forbes and VnExpress International reporting on the Wee family's investment vehicles, corroborated by family-office directories (Altss, PipelineRoad) identifying Wee Investments as the Wee Cho Yaw family office.</t>
+          <t>Known UHNW founder (Shu Ping, Haidilao co-founder). Confirmed via Bloomberg, South China Morning Post and Caixin Global reporting that Shu Ping opened a Singapore family office (Sunrise Capital Management), of which she is sole shareholder and director, to manage her fortune.</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://www.forbes.com/profile/wee-1/</t>
+          <t>https://www.scmp.com/business/article/3065092/haidilao-hotpot-queen-opens-singapore-family-office-manage-us77-billion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Family-office directories (Altss, PipelineRoad) identify Wee Investments as the single-family office of the Wee family (founded by Wee Cho Yaw, builder of UOB); Forbes and VnExpress document the family's concentrated holdings in UOB, UOL, Haw Par and Kheng Leong managed through family vehicles.</t>
+          <t>Bloomberg ('Hotpot Queen Opens Family Office in Singapore to Manage Wealth'), SCMP and Caixin all describe Sunrise Capital Management as the single-family office set up to manage Shu Ping's ~USD7.7bn fortune; she is sole shareholder and director.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Corroborating reputable coverage (Forbes, VnExpress) of the Wee family's wealth plus specialised FO directories naming Wee Investments as the family office.</t>
+          <t>Reputable press (Bloomberg, SCMP, Caixin Global) name the entity as Shu Ping's family office established in 2019/2020.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>corroborated</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>No AUM disclosed; family fortune is multi-billion (Forbes) but the family office does not publish AUM.</t>
+          <t>Family wealth figure cited by SCMP/Bloomberg/Caixin at the office's launch (2020); not an audited FO AUM.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Following founder Wee Cho Yaw's death in February 2024, family principals Wee Ee Cheong, Wee Ee Chao and Wee Ee Lim oversee the family's allocations; Wee Ee Cheong leads UOB.</t>
+          <t>Shu Ping is the family principal and, per press, the sole shareholder and director of Sunrise Capital Management.</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -8789,13 +8813,13 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Private single-family office; no individual email published in any source reviewed.</t>
+          <t>Private single-family office; no individual email address published in any source reviewed.</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr">
         <is>
-          <t>https://www.forbes.com/sites/jonathanburgos/2024/05/14/billionaire-wee-familys-uol-offers-top-bid-of-595-million-for-prime-singapore-site/</t>
+          <t>https://www.bloomberg.com/news/articles/2020-03-04/hotpot-queen-opens-family-office-in-singapore-to-manage-wealth</t>
         </is>
       </c>
       <c r="P44" t="inlineStr"/>
@@ -8803,12 +8827,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>APAC-ee-capital-saverin</t>
+          <t>APAC-tsao-family-office-tpc</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EE Capital Pte. Ltd.</t>
+          <t>Tsao Pao Chee (TPC) Group — Tsao Family Office (investment arm; OCTAVE brand)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -8818,37 +8842,37 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Known UHNW resident (Eduardo Saverin, Facebook co-founder and Singapore's richest man). Identified as his single-family office via Preqin's SFO profile and Citywire Selector coverage of Singapore's family-office scene; corroborated by FO directory Altss.</t>
+          <t>Known Singapore business family (Tsao family, IMC Group maritime dynasty). Confirmed via Preqin single-family-office profile and the family's own TPC/Tsao Pao Chee and OCTAVE websites describing the Tsao Family Office as the strategic investment arm of the group.</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://www.preqin.com/data/profile/investor/ee-capital/229861</t>
+          <t>https://www.preqin.com/data/profile/investor/tsao-family-office/246728</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Preqin and Altss both classify EE Capital as a Singapore single-family office managing the assets of Eduardo Saverin; Saverin's wife Elaine Andriejanssen is described as Executive Chairman of EE Capital Pte Ltd.</t>
+          <t>Preqin classifies the Tsao Family Office as a single-family office based in Singapore; the family's TPC/OCTAVE sites describe it as the investment arm of the Tsao family (IMC Group), an integrated maritime and industrial group founded 1906.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Preqin single-family-office profile plus Citywire Selector and Altss identify EE Capital as Saverin's family office (private/public investments across sectors).</t>
+          <t>Preqin single-family-office profile plus the family's own corporate sites (tsaopaochee.com, octaveinvestment.com) confirm a family-owned investment office.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>corroborated</t>
+          <t>strong</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>No FO AUM disclosed; Saverin's personal net worth is reported by Forbes (&gt;USD30bn) but is not an EE Capital AUM figure.</t>
+          <t>No public AUM figure disclosed by the family office in sources reviewed.</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Eduardo Saverin is the family principal whose wealth EE Capital manages; his wife Elaine Andriejanssen is reported as Executive Chairman of EE Capital Pte Ltd.</t>
+          <t>Chavalit Tsao is the current family principal and chairman leading the group and its investment/impact activities.</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -8859,13 +8883,13 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Private single-family office; no individual email address published in any source reviewed.</t>
+          <t>No individual published email located; group contact channels are via corporate websites only.</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
         <is>
-          <t>https://www.forbes.com/sites/naazneenkarmali/2023/09/06/singapores-50-richest-2023-facebook-cofounder-eduardo-saverin-is-new-no-1-as-combined-wealth-rises-8-to-177-billion/</t>
+          <t>https://tsaopaochee.com/our-brands/octave/</t>
         </is>
       </c>
       <c r="P45" t="inlineStr"/>
@@ -8873,12 +8897,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>APAC-wuthelam-holdings-goh</t>
+          <t>APAC-wee-investments-uob</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wuthelam Holdings Pte. Ltd.</t>
+          <t>Wee Investments Pte. Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -8888,37 +8912,37 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Known Singapore business family (Goh family, controllers of Nippon Paint via Wuthelam). Confirmed via Nikkei Asia and Forbes reporting that Wuthelam Holdings is the Goh family's investment vehicle/family office; corroborated by The Independent/Mothership coverage of the 2024 inheritance transfer.</t>
+          <t>Known Singapore banking dynasty (Wee family, controllers of UOB). Confirmed via Forbes and VnExpress International reporting on the Wee family's investment vehicles, corroborated by family-office directories (Altss, PipelineRoad) identifying Wee Investments as the Wee Cho Yaw family office.</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://asia.nikkei.com/business/business-deals/how-singapore-s-wuthelam-turned-the-tables-on-nippon-paint</t>
+          <t>https://www.forbes.com/profile/wee-1/</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Described in reporting as the Singapore-based investment vehicle that combines all private wealth and investment activities of the late Goh Cheng Liang (Singapore's richest man) and his family, serving as the family's single-family office; controls a majority stake in Tokyo-listed Nippon Paint Holdings.</t>
+          <t>Family-office directories (Altss, PipelineRoad) identify Wee Investments as the single-family office of the Wee family (founded by Wee Cho Yaw, builder of UOB); Forbes and VnExpress document the family's concentrated holdings in UOB, UOL, Haw Par and Kheng Leong managed through family vehicles.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Reputable outlets (Nikkei Asia, Forbes, Bloomberg Billionaires Index) treat Wuthelam Holdings as the Goh family's private holding/family-office vehicle.</t>
+          <t>Corroborating reputable coverage (Forbes, VnExpress) of the Wee family's wealth plus specialised FO directories naming Wee Investments as the family office.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>corroborated</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>No FO AUM disclosed; the family's Nippon Paint stake and fortune are multi-billion (Forbes/Bloomberg) but not published as a family-office AUM.</t>
+          <t>No AUM disclosed; family fortune is multi-billion (Forbes) but the family office does not publish AUM.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Following the founder's death in August 2025, Goh Hup Jin is the leading family principal, chairing Nippon Paint and serving as a Wuthelam group executive director.</t>
+          <t>Following founder Wee Cho Yaw's death in February 2024, family principals Wee Ee Cheong, Wee Ee Chao and Wee Ee Lim oversee the family's allocations; Wee Ee Cheong leads UOB.</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -8929,13 +8953,13 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Private family holding company; no individual email published in any source reviewed.</t>
+          <t>Private single-family office; no individual email published in any source reviewed.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
         <is>
-          <t>https://mothership.sg/2025/09/goh-cheng-liang-grandchildren-billionaires/</t>
+          <t>https://www.forbes.com/sites/jonathanburgos/2024/05/14/billionaire-wee-familys-uol-offers-top-bid-of-595-million-for-prime-singapore-site/</t>
         </is>
       </c>
       <c r="P46" t="inlineStr"/>
@@ -8943,52 +8967,52 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SFO-cascade-investment-gates</t>
+          <t>APAC-ee-capital-saverin</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cascade Investment, L.L.C.</t>
+          <t>EE Capital Pte. Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>apac-eu-registry</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (Bill Gates) -&gt; family office entity. Confirmed as Gates's private investment vehicle and an active SEC 13F filer (Cascade Investment, L.L.C., CIK 0001052192, Kirkland WA), with Michael Larson as Manager who also exercises investment discretion for the Gates Foundation Trust.</t>
+          <t>Known UHNW resident (Eduardo Saverin, Facebook co-founder and Singapore's richest man). Identified as his single-family office via Preqin's SFO profile and Citywire Selector coverage of Singapore's family-office scene; corroborated by FO directory Altss.</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://www.danielscrivner.com/bill-gates-trades-and-holdings-q2-2025/</t>
+          <t>https://www.preqin.com/data/profile/investor/ee-capital/229861</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cascade Investment is the private investment vehicle managing the personal wealth of Microsoft co-founder Bill Gates (and, via the same manager Michael Larson, the assets of the Gates Foundation Trust). No external clients; single-family (Gates) capital.</t>
+          <t>Preqin and Altss both classify EE Capital as a Singapore single-family office managing the assets of Eduardo Saverin; Saverin's wife Elaine Andriejanssen is described as Executive Chairman of EE Capital Pte Ltd.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SEC EDGAR 13F-HR filings under CIK 0001052192 (Cascade Investment, L.L.C., 2365 Carillon Point, Kirkland WA), most recent Q2 2025 13F filed 2025-08-14; historical filings run 2002-present.</t>
+          <t>Preqin single-family-office profile plus Citywire Selector and Altss identify EE Capital as Saverin's family office (private/public investments across sectors).</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>strong</t>
+          <t>corroborated</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Not officially disclosed; press estimates the combined Gates/Cascade portfolio in the tens of billions. 13F-reported U.S. equities are a subset of total assets.</t>
+          <t>No FO AUM disclosed; Saverin's personal net worth is reported by Forbes (&gt;USD30bn) but is not an EE Capital AUM figure.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Beneficial owner; Cascade exists to manage his and the Gates Foundation Trust's assets. Day-to-day investment chief is Manager Michael Larson.</t>
+          <t>Eduardo Saverin is the family principal whose wealth EE Capital manages; his wife Elaine Andriejanssen is reported as Executive Chairman of EE Capital Pte Ltd.</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -8997,11 +9021,15 @@
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Private single-family office; no individual email address published in any source reviewed.</t>
+        </is>
+      </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
-          <t>https://www.danielscrivner.com/bill-gates-trades-and-holdings-q2-2025/</t>
+          <t>https://www.forbes.com/sites/naazneenkarmali/2023/09/06/singapores-50-richest-2023-facebook-cofounder-eduardo-saverin-is-new-no-1-as-combined-wealth-rises-8-to-177-billion/</t>
         </is>
       </c>
       <c r="P47" t="inlineStr"/>
@@ -9009,37 +9037,37 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SFO-willett-advisors-bloomberg</t>
+          <t>APAC-wuthelam-holdings-goh</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Willett Advisors LLC</t>
+          <t>Wuthelam Holdings Pte. Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>press</t>
+          <t>apac-eu-registry</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (Michael Bloomberg) -&gt; family office entity. Confirmed as Bloomberg's family office by Wikipedia and multiple family-office trade sources; SEC EDGAR shows a registered 13F filer (CIK 0001509379) though filings ceased after 2014.</t>
+          <t>Known Singapore business family (Goh family, controllers of Nippon Paint via Wuthelam). Confirmed via Nikkei Asia and Forbes reporting that Wuthelam Holdings is the Goh family's investment vehicle/family office; corroborated by The Independent/Mothership coverage of the 2024 inheritance transfer.</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Willett_Advisors</t>
+          <t>https://asia.nikkei.com/business/business-deals/how-singapore-s-wuthelam-turned-the-tables-on-nippon-paint</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Described as the investment firm serving as the family office of Michael Bloomberg (founder of Bloomberg L.P., former NYC mayor); manages his personal assets and the assets of Bloomberg Philanthropies. Founded 2010.</t>
+          <t>Described in reporting as the Singapore-based investment vehicle that combines all private wealth and investment activities of the late Goh Cheng Liang (Singapore's richest man) and his family, serving as the family's single-family office; controls a majority stake in Tokyo-listed Nippon Paint Holdings.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Wikipedia and family-office trade press (familyofficehub, altss) name Willett Advisors as Michael Bloomberg's family office; SEC EDGAR registration as a 13F filer (CIK 0001509379).</t>
+          <t>Reputable outlets (Nikkei Asia, Forbes, Bloomberg Billionaires Index) treat Wuthelam Holdings as the Goh family's private holding/family-office vehicle.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -9049,12 +9077,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Widely reported managed-asset figure (Wikipedia/trade press) covering Bloomberg's personal and philanthropic assets; not an official disclosure.</t>
+          <t>No FO AUM disclosed; the family's Nippon Paint stake and fortune are multi-billion (Forbes/Bloomberg) but not published as a family-office AUM.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Beneficial owner; office manages his personal and philanthropic assets. Day-to-day Chairman and CEO is Steven Rattner.</t>
+          <t>Following the founder's death in August 2025, Goh Hup Jin is the leading family principal, chairing Nippon Paint and serving as a Wuthelam group executive director.</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -9063,11 +9091,15 @@
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Private family holding company; no individual email published in any source reviewed.</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Willett_Advisors</t>
+          <t>https://mothership.sg/2025/09/goh-cheng-liang-grandchildren-billionaires/</t>
         </is>
       </c>
       <c r="P48" t="inlineStr"/>
@@ -9075,12 +9107,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SFO-soros-fund-management</t>
+          <t>SFO-cascade-investment-gates</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Soros Fund Management LLC</t>
+          <t>Cascade Investment, L.L.C.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -9090,22 +9122,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Identified via known UHNW individual (George/Alex Soros) -&gt; family office. Confirmed as the Soros family office (converted from hedge fund to family office after returning outside capital in 2011) by Wikipedia and Institutional Investor; active SEC 13F filer (CIK 0001029160).</t>
+          <t>Identified via known UHNW individual (Bill Gates) -&gt; family office entity. Confirmed as Gates's private investment vehicle and an active SEC 13F filer (Cascade Investment, L.L.C., CIK 0001052192, Kirkland WA), with Michael Larson as Manager who also exercises investment discretion for the Gates Foundation Trust.</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://en.wikipedia.org/wiki/Soros_Fund_Management</t>
+          <t>https://www.danielscrivner.com/bill-gates-trades-and-holdings-q2-2025/</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Founded 1970 by George Soros as a hedge fund; returned all outside investor capital in 2011 and has since operated as the Soros family office and the principal asset manager for the Open Society Foundations. No external LPs.</t>
+          <t>Cascade Investment is the private investment vehicle managing the personal wealth of Microsoft co-founder Bill Gates (and, via the same manager Michael Larson, the assets of the Gates Foundation Trust). No external clients; single-family (Gates) capital.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Wikipedia and Institutional Investor describe it as the Soros family office; active SEC EDGAR 13F-HR filings under CIK 0001029160 (latest reported Q1 2026, as of 2026-03-31).</t>
+          <t>SEC EDGAR 13F-HR filings under CIK 0001052192 (Cascade Investment, L.L.C., 2365 Carillon Point, Kirkland WA), most recent Q2 2025 13F filed 2025-08-14; historical filings run 2002-present.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -9115,12 +9147,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Widely reported total AUM (~$25-28bn) for the family office; 13F-reported U.S. equities (~$9bn, Q1 2026) are a subset.</t>
+          <t>Not officially disclosed; press estimates the combined Gates/Cascade portfolio in the tens of billions. 13F-reported U.S. equities are a subset of total assets.</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Founder and beneficial principal; in 2023 handed control of the family's ~$25bn foundation to son Alex Soros, who chairs the Open Society Foundations and sits on the Soros Fund Management investment committee.</t>
+          <t>Beneficial owner; Cascade exists to manage his and the Gates Foundation Trust's assets. Day-to-day investment chief is Manager Michael Larson.</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -9133,7 +9165,7 @@
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr">
         <is>
-          <t>https://fintool.com/app/research/funds/family-offices/soros-fund-management-llc</t>
+          <t>https://www.danielscrivner.com/bill-gates-trades-and-holdings-q2-2025/</t>
         </is>
       </c>
       <c r="P49" t="inlineStr"/>
@@ -9281,7 +9313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E143"/>
+  <dimension ref="A1:E145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -9786,18 +9818,18 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Crestone Asset Management LLC</t>
+          <t>Cascade Investment, L.L.C.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>firm-qualification</t>
+          <t>sfo-13f-phone</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>failed: HTTP Error 404: Not Found</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9852,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -9832,7 +9864,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Crew Family Office Limited</t>
+          <t>Crestone Asset Management LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -9843,7 +9875,7 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -9970,7 +10002,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DAO FAMILY OFFICE LP</t>
+          <t>Crew Family Office Limited</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -9981,7 +10013,7 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -9993,7 +10025,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DAVIDOFF FREY FAMILY OFFICE (UK) LTD</t>
+          <t>DAO FAMILY OFFICE LP</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -10016,7 +10048,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DE VILLIERS FAMILY OFFICE LIMITED</t>
+          <t>DAVIDOFF FREY FAMILY OFFICE (UK) LTD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -10039,7 +10071,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DEUTSCHE BANK AG\</t>
+          <t>DE VILLIERS FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -10073,7 +10105,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -10085,7 +10117,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DONE FAMILY OFFICE LIMITED</t>
+          <t>DEUTSCHE BANK AG\</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -10096,7 +10128,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -10108,7 +10140,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DONNELLY FAMILY OFFICE</t>
+          <t>DONE FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -10131,7 +10163,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DSW FAMILY OFFICE LTD</t>
+          <t>DONNELLY FAMILY OFFICE</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -10154,7 +10186,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DUBAI FAMILY OFFICE LTD</t>
+          <t>DSW FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -10177,7 +10209,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Dorsey &amp; Whitney Trust CO LLC</t>
+          <t>DUBAI FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -10211,7 +10243,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -10223,7 +10255,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EMFO, LLC</t>
+          <t>Dorsey &amp; Whitney Trust CO LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -10234,7 +10266,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -10257,7 +10289,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -10269,7 +10301,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FAMILY OFFICE CONSULTING LIMITED</t>
+          <t>EMFO, LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -10280,7 +10312,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -10292,7 +10324,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FAMILY OFFICE EEB LTD</t>
+          <t>FAMILY OFFICE CONSULTING LIMITED</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -10315,7 +10347,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FIDUCIARY FAMILY OFFICE, LLC</t>
+          <t>FAMILY OFFICE EEB LTD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -10338,7 +10370,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>FOOTPRINTS FAMILY OFFICE UK EUROPE LIMITED</t>
+          <t>FIDUCIARY FAMILY OFFICE, LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -10361,7 +10393,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FREEDMAN FAMILY OFFICE</t>
+          <t>FOOTPRINTS FAMILY OFFICE UK EUROPE LIMITED</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -10384,7 +10416,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FRIGUS FAMILY OFFICE LTD</t>
+          <t>FREEDMAN FAMILY OFFICE</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -10407,7 +10439,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FRONTIER FAMILY OFFICE FORUM HOLDINGS LIMITED</t>
+          <t>FRIGUS FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -10430,7 +10462,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Family Investment Center, Inc.</t>
+          <t>FRONTIER FAMILY OFFICE FORUM HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -10464,7 +10496,7 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -10476,7 +10508,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Family Office DS Limited</t>
+          <t>Family Investment Center, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -10487,7 +10519,7 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -10614,7 +10646,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Family Office Research LLC</t>
+          <t>Family Office DS Limited</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -10625,7 +10657,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -10637,7 +10669,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Family Office Research, LLC</t>
+          <t>Family Office Research LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -10648,7 +10680,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -10660,7 +10692,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Fortis Advisors, LLC</t>
+          <t>Family Office Research, LLC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -10671,7 +10703,7 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -10694,7 +10726,7 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -10706,7 +10738,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fortitude Family Office, LLC</t>
+          <t>Fortis Advisors, LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -10717,7 +10749,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -10729,7 +10761,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GELLING FAMILY OFFICE LIMITED</t>
+          <t>Fortitude Family Office, LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -10752,7 +10784,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GUNPUTH FAMILY OFFICE LIMITED</t>
+          <t>GELLING FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -10775,7 +10807,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Geller Advisors LLC</t>
+          <t>GUNPUTH FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -10809,7 +10841,7 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -10821,7 +10853,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HALL LAURIE J TRUSTEE</t>
+          <t>Geller Advisors LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -10832,7 +10864,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -10855,7 +10887,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -10867,7 +10899,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HBBA FAMILY OFFICE LIMITED</t>
+          <t>HALL LAURIE J TRUSTEE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -10878,7 +10910,7 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10922,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>HBBA Family Office Limited</t>
+          <t>HBBA FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -10901,7 +10933,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10945,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HILL FAMILY OFFICE LIMITED</t>
+          <t>HBBA Family Office Limited</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -10924,7 +10956,7 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -10936,7 +10968,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
+          <t>HILL FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -10970,7 +11002,7 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -10982,7 +11014,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>INTREPID FAMILY OFFICE LLC</t>
+          <t>INTREPID CAPITAL MANAGEMENT INC /DE/</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -10993,7 +11025,7 @@
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -11005,7 +11037,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ISHER CAPITAL FAMILY OFFICE LTD</t>
+          <t>INTREPID FAMILY OFFICE LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -11028,7 +11060,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Independent Family Office, LLC</t>
+          <t>ISHER CAPITAL FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -11051,7 +11083,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kopp Family Office, LLC</t>
+          <t>Independent Family Office, LLC</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -11074,7 +11106,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LELS CLARK FAMILY OFFICE LTD</t>
+          <t>Kopp Family Office, LLC</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -11097,7 +11129,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Lido Advisors, LLC</t>
+          <t>LELS CLARK FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -11131,7 +11163,7 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -11143,7 +11175,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MARCUARD FAMILY OFFICE LTD</t>
+          <t>Lido Advisors, LLC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -11154,7 +11186,7 @@
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -11166,7 +11198,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MOBH UK FAMILY OFFICE LTD</t>
+          <t>MARCUARD FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -11189,7 +11221,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NORTHBRIDGE FAMILY OFFICE LTD</t>
+          <t>MOBH UK FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -11212,7 +11244,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NOVA FAMILY OFFICE LTD</t>
+          <t>NORTHBRIDGE FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -11235,7 +11267,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nilsson Family Office Ltd</t>
+          <t>NOVA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -11246,7 +11278,7 @@
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -11373,7 +11405,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>OLD HOUSE FAMILY OFFICE LIMITED</t>
+          <t>Nilsson Family Office Ltd</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -11384,7 +11416,7 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -11396,7 +11428,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>OneAscent Family Office, LLC</t>
+          <t>OLD HOUSE FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -11419,7 +11451,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Orion Porfolio Solutions, LLC</t>
+          <t>OneAscent Family Office, LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -11453,7 +11485,7 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -11465,7 +11497,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Orion Portfolio Solutions, LLC</t>
+          <t>Orion Porfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -11476,7 +11508,7 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -11499,7 +11531,7 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -11511,7 +11543,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>PANDA FAMILY OFFICE LTD</t>
+          <t>Orion Portfolio Solutions, LLC</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -11522,7 +11554,7 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -11534,7 +11566,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>PANTHEON A FAMILY OFFICE LIMITED</t>
+          <t>PANDA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -11557,7 +11589,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>PATHSTONE FAMILY OFFICE, LLC</t>
+          <t>PANTHEON A FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -11580,7 +11612,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PMG Family Office LLC</t>
+          <t>PATHSTONE FAMILY OFFICE, LLC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -11603,7 +11635,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PROSPERITY FAMILY OFFICE LIMITED</t>
+          <t>PMG Family Office LLC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -11626,7 +11658,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Pathstone Holdings, LLC</t>
+          <t>PROSPERITY FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -11660,7 +11692,7 @@
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -11672,7 +11704,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Pioneer Family Office, LLC</t>
+          <t>Pathstone Holdings, LLC</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -11683,7 +11715,7 @@
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -11695,7 +11727,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>RALPH FAMILY OFFICE LIMITED</t>
+          <t>Pioneer Family Office, LLC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -11718,7 +11750,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SHA FAMILY OFFICE LTD</t>
+          <t>RALPH FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -11741,7 +11773,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SIGNATURE FAMILY OFFICE LTD</t>
+          <t>SHA FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -11764,7 +11796,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SIMON FAMILY OFFICE INSURES LIMITED</t>
+          <t>SIGNATURE FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -11787,7 +11819,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SWAILES COMMERCIAL FAMILY OFFICE LTD</t>
+          <t>SIMON FAMILY OFFICE INSURES LIMITED</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -11810,7 +11842,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SWAILES TRADING GROUP FAMILY OFFICE LTD</t>
+          <t>SWAILES COMMERCIAL FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -11833,7 +11865,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Sageworth Trust Co</t>
+          <t>SWAILES TRADING GROUP FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -11867,7 +11899,7 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -11879,7 +11911,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Standard Family Office LLC</t>
+          <t>Sageworth Trust Co</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -11890,7 +11922,7 @@
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11934,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Stenger Family Office, LLC</t>
+          <t>Standard Family Office LLC</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -11925,7 +11957,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Stokes Family Office, LLC</t>
+          <t>Stenger Family Office, LLC</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -11948,7 +11980,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>THE DIGITAL FAMILY OFFICE LIMITED</t>
+          <t>Stokes Family Office, LLC</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -11971,7 +12003,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>THE FAMILY OFFICE CHELTENHAM LIMITED</t>
+          <t>THE DIGITAL FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -11994,7 +12026,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>TIGRIS FAMILY OFFICE LIMITED</t>
+          <t>THE FAMILY OFFICE CHELTENHAM LIMITED</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -12017,7 +12049,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Tarbox Family Office, Inc.</t>
+          <t>TIGRIS FAMILY OFFICE LIMITED</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -12045,17 +12077,13 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>principal_email</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>laura@tarbox.com</t>
-        </is>
-      </c>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>email not found at cited source on re-fetch (https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf); downgraded verified-&gt;unverified</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -12202,18 +12230,22 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>The Family Office Cheltenham Limited</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>firm-qualification</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
+          <t>principal_email</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>laura@tarbox.com</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
+          <t>email not found at cited source on re-fetch (https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf); downgraded verified-&gt;unverified</t>
         </is>
       </c>
     </row>
@@ -12225,18 +12257,22 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Timonier Family Office, LTD.</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>firm-qualification</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
+          <t>principal_email</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>laura@tarbox.com</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>email not found at cited source on re-fetch (https://itsyourmoneyandestate.org/wp-content/uploads/2022/08/IYM-Presentation-Fall-2022-Laura-Tarbox.pdf); downgraded verified-&gt;unverified</t>
         </is>
       </c>
     </row>
@@ -12248,22 +12284,18 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Timonier Family Office, LTD.</t>
+          <t>The Family Office Cheltenham Limited</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>principal_email</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>timonier@timonier.com</t>
-        </is>
-      </c>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>firm-name mailbox wrongly matched (tim in timonier); removed - not an individual email</t>
+          <t>fo_proof_strength=insufficient (no affirmative FO evidence)</t>
         </is>
       </c>
     </row>
@@ -12275,7 +12307,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>TrustBank</t>
+          <t>Timonier Family Office, LTD.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -12298,18 +12330,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>TrustBank</t>
+          <t>Timonier Family Office, LTD.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>firm-qualification</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
+          <t>principal_email</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>timonier@timonier.com</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>firm-name mailbox wrongly matched (tim in timonier); removed - not an individual email</t>
         </is>
       </c>
     </row>
@@ -12321,7 +12357,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>UNITA FAMILY OFFICE UK LIMITED</t>
+          <t>TrustBank</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -12344,7 +12380,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>UR FAMILY OFFICE MANAGEMENT SERVICES LTD</t>
+          <t>TrustBank</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -12355,7 +12391,7 @@
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -12367,7 +12403,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>VASIL FAMILY OFFICE LLP</t>
+          <t>UNITA FAMILY OFFICE UK LIMITED</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -12390,7 +12426,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>VPR Management LLC</t>
+          <t>UR FAMILY OFFICE MANAGEMENT SERVICES LTD</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -12413,7 +12449,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>VPR Management LLC</t>
+          <t>VASIL FAMILY OFFICE LLP</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -12424,7 +12460,7 @@
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -12436,7 +12472,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>VSTAR LONDON FAMILY OFFICE LTD</t>
+          <t>VPR Management LLC</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -12459,7 +12495,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Veritable, L.P.</t>
+          <t>VPR Management LLC</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -12470,7 +12506,7 @@
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12518,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Veritable, L.P.</t>
+          <t>VSTAR LONDON FAMILY OFFICE LTD</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -12493,7 +12529,7 @@
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
+          <t>fo_proof_strength not established ('blank')</t>
         </is>
       </c>
     </row>
@@ -12505,7 +12541,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Virtus Family Office LLC</t>
+          <t>Veritable, L.P.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -12528,7 +12564,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>WEYBRIDGE FAMILY OFFICE SERVICES LIMITED</t>
+          <t>Veritable, L.P.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -12539,7 +12575,7 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>fo_proof_strength not established ('blank')</t>
+          <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>
       </c>
     </row>
@@ -12551,7 +12587,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Wealthgate Family Office, LLC</t>
+          <t>Virtus Family Office LLC</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -12574,7 +12610,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Wilmington Savings Fund Society, FSB</t>
+          <t>WEYBRIDGE FAMILY OFFICE SERVICES LIMITED</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -12597,7 +12633,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Wilmington Savings Fund Society, FSB</t>
+          <t>Wealthgate Family Office, LLC</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -12607,6 +12643,52 @@
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Wilmington Savings Fund Society, FSB</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>fo_proof_strength not established ('blank')</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Wilmington Savings Fund Society, FSB</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>firm-qualification</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
         <is>
           <t>13F matched "family office" only in holdings/filing text, not the firm name; not a family office (false positive)</t>
         </is>

--- a/data/final/family_office_dataset.xlsx
+++ b/data/final/family_office_dataset.xlsx
@@ -1179,7 +1179,11 @@
           <t>Chief Financial Officer</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/matt-dino-cpa-1577b225/</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
@@ -1276,12 +1280,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Stanley F. Druckenmiller</t>
+          <t>Stanley Druckenmiller</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Founder, Chairman &amp; CEO (Portfolio Manager)</t>
+          <t>Chairman, CEO &amp; Chief Investment Officer</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>
@@ -1313,7 +1317,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Total AUM is not officially disclosed; the 13F equity value is only US-listed long equity positions (a floor). The LinkedIn company page may not be firm-operated. No individual email is published anywhere; none provided. Sue Meng (13F signatory) is General Counsel, not the investment decision-maker.</t>
+          <t>Total AUM is not officially disclosed; the 13F equity value is only US-listed long equity positions (a floor). The LinkedIn company page may not be firm-operated. No individual email is published anywhere; none provided. Sue Meng (13F signatory) is General Counsel, not the investment decision-maker. Principal set to the reachable investment lead (Stanley Druckenmiller) per LinkedIn pass. Druckenmiller is himself the sole portfolio manager/CIO of Duquesne Family Office, which manages only his own capital and does not take outside money; he has no public personal LinkedIn (kept as principal rather than a delegate because he is the actual decision-maker, not a figurehead).</t>
         </is>
       </c>
     </row>
@@ -1502,12 +1506,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UKCH-12706913</t>
+          <t>UKCH-14442767</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Francis Family Office Limited</t>
+          <t>Wedgwood Family Office Limited</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1517,31 +1521,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Francis family (Ben Francis, founder/CEO of Gymshark)</t>
+          <t>Wedgwood (Paul Wedgwood family)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Personal family-office / holding vehicle of Ben Francis, billionaire founder and majority owner of fitness-apparel brand Gymshark; holds part of his Gymshark shareholding.</t>
+          <t>UK private company (inc. 2022-10-25) under fund-management SIC, registered at a residential address in Keston. Appears to be the personal single-family investment vehicle of Paul Wedgwood.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Holding company (concentrated Gymshark equity stake)</t>
+          <t>66300 - Fund management activities</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Solihull</t>
+          <t>Keston</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>West Midlands</t>
+          <t>Greater London (Bromley)</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1551,17 +1555,17 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Benjamin David Francis</t>
+          <t>Paul Wedgwood</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Director &amp; 100% owner; Founder &amp; CEO of Gymshark</t>
+          <t>Director</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/gymshark/</t>
+          <t>https://uk.linkedin.com/in/wedgwoodpaul</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
@@ -1573,12 +1577,12 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Renamed Ben Francis Ltd -&gt; Francis Family Office Ltd (2021); Ben Francis moved ~half his Gymshark stake into the vehicle; 2026 reporting he is seeking financing to buy back part of General Atlantic's Gymshark stake</t>
+          <t>Co-director Christopher James Sharp resigned 2024-04-16; new secretary appointed 2026-01-06; accounts currently overdue</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2021-02-03 (rename); 2026-07 (buyback reporting)</t>
+          <t>2024-04-16; 2026-01-06</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1588,19 +1592,19 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>No standalone website/LinkedIn/email for the FO itself — a private holding vehicle, not client-facing. Corporate secretary is a law-firm nominee, not the principal. Investment thesis/sectors not publicly disclosed.</t>
+          <t>Link between director 'Paul Wedgwood, b.1970' and the Splash Damage/Supernova entrepreneur is a strong inference (name + DOB + separate Wedgwood FIC directorship), NOT hard-confirmed. Zero public FO footprint (no website/LinkedIn/press/AUM); accounts overdue. Residential registered address.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UKCH-07931194</t>
+          <t>UKCH-12706913</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Wimmer Family Office Ltd</t>
+          <t>Francis Family Office Limited</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1610,35 +1614,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wimmer (Per Wimmer, Danish financier, founder of merchant bank Wimmer Financial)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://wfo.am/</t>
-        </is>
-      </c>
+          <t>Francis family (Ben Francis, founder/CEO of Gymshark)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>London (Mayfair) family office established by Per Wimmer, a Danish financier, entrepreneur and author; associated with his corporate-advisory firm Wimmer Financial.</t>
+          <t>Personal family-office / holding vehicle of Ben Francis, billionaire founder and majority owner of fitness-apparel brand Gymshark; holds part of his Gymshark shareholding.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Natural resources (mining, oil &amp; gas, green energy); real estate; infrastructure; aviation; shipping; space economy</t>
+          <t>Holding company (concentrated Gymshark equity stake)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Solihull</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Mayfair</t>
+          <t>West Midlands</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1648,17 +1648,17 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Per Thanning Wimmer</t>
+          <t>Benjamin David Francis</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO, Wimmer Family Office</t>
+          <t>Director &amp; 100% owner; Founder &amp; CEO of Gymshark</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/perwimmer</t>
+          <t>https://www.linkedin.com/in/gymshark/</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
@@ -1667,19 +1667,15 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>+44 207 432 7575</t>
-        </is>
-      </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
-          <t>Per Wimmer resigned as director 2024-09-25; two new directors appointed same day (Aida Feriz, Joppe Sikma); FCA-authorised (FCA #665654)</t>
+          <t>Renamed Ben Francis Ltd -&gt; Francis Family Office Ltd (2021); Ben Francis moved ~half his Gymshark stake into the vehicle; 2026 reporting he is seeking financing to buy back part of General Atlantic's Gymshark stake</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2024-09-25 (director change)</t>
+          <t>2021-02-03 (rename); 2026-07 (buyback reporting)</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1689,19 +1685,19 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Corrected task hint: principal is PER Wimmer, not 'Klaus Wimmer'. Per Wimmer resigned as registered director 2024-09-25 but remains named founder on the site; current directors appear operational/successor. Phone is switchboard. AUM/thesis not disclosed.</t>
+          <t>No standalone website/LinkedIn/email for the FO itself — a private holding vehicle, not client-facing. Corporate secretary is a law-firm nominee, not the principal. Investment thesis/sectors not publicly disclosed.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UKCH-10957456</t>
+          <t>UKCH-07931194</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Old House Family Office Limited</t>
+          <t>Wimmer Family Office Ltd</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1711,31 +1707,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lewis family (Christopher David Lewis, director; Stella Ann Lewis, former director/ceased PSC with trust influence)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>Wimmer (Per Wimmer, Danish financier, founder of merchant bank Wimmer Financial)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://wfo.am/</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>UK private limited company incorporated 12 Sep 2017, presenting as the Lewis family's family-office / holding vehicle. Sits above / alongside Old Friend Capital Limited, a Bournemouth-based real-estate investment and development business run by Christopher (Chris) Lewis, whose track record includes UK leisure-residential and renewable-energy property projects (e.g. Wet N Wild Newcastle, Oasis Swindon). Accounts currently overdue as of research date.</t>
+          <t>London (Mayfair) family office established by Per Wimmer, a Danish financier, entrepreneur and author; associated with his corporate-advisory firm Wimmer Financial.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Real estate (buying/selling and management of own real estate); leisure-residential property development; renewable energy property (per principal's stated specialism on LinkedIn)</t>
+          <t>Natural resources (mining, oil &amp; gas, green energy); real estate; infrastructure; aviation; shipping; space economy</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Poole</t>
+          <t>London</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Dorset, England</t>
+          <t>Mayfair</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1745,17 +1745,17 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Christopher David Lewis</t>
+          <t>Per Thanning Wimmer</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Director (Old House Family Office Limited); principal of Old Friend Capital</t>
+          <t>Founder &amp; CEO, Wimmer Family Office</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/chrislewismoirai/</t>
+          <t>https://uk.linkedin.com/in/perwimmer</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
@@ -1764,15 +1764,19 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>+44 207 432 7575</t>
+        </is>
+      </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>Ceased PSC Stella Ann Lewis on 1 Jun 2024 (trust influence noted); director change May 2021 (Stella Lewis resigned, Christopher Lewis appointed). Accounts overdue as of 2026.</t>
+          <t>Per Wimmer resigned as director 2024-09-25; two new directors appointed same day (Aida Feriz, Joppe Sikma); FCA-authorised (FCA #665654)</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2017-09-12 (incorporated); 2021-05-14 (director change); 2024-06-01 (Stella Lewis ceased as PSC)</t>
+          <t>2024-09-25 (director change)</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1782,19 +1786,19 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>No firm website or public FO branding beyond the company name; classification as an operating family office is inferred from the trust/PSC structure and the principal's real-estate activity rather than from any self-description as a family office. Accounts overdue. Registered office is Poole Stadium (a business address). 'Moirai' link is via principal's LinkedIn handle / prior Moirai Capital Investments Ltd, not confirmed as current firm branding.</t>
+          <t>Corrected task hint: principal is PER Wimmer, not 'Klaus Wimmer'. Per Wimmer resigned as registered director 2024-09-25 but remains named founder on the site; current directors appear operational/successor. Phone is switchboard. AUM/thesis not disclosed.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SFO-dfo-management-dell</t>
+          <t>UKCH-10957456</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DFO Management (Dell Family Office)</t>
+          <t>Old House Family Office Limited</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1804,80 +1808,68 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Dell family (Michael Dell, founder/CEO of Dell Technologies)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://www.dellfamilyoffice.com/</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/dfo-management</t>
-        </is>
-      </c>
+          <t>Lewis family (Christopher David Lewis, director; Stella Ann Lewis, former director/ceased PSC with trust influence)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Private investment firm managing the assets of Michael Dell and family across public equities, private equity, real estate and other asset classes. Originally MSD Capital (1998); the multi-client business became BDT &amp; MSD Partners while the family's captive vehicle was rebranded DFO Management at end of 2022.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Multi-asset-class permanent capital: public equities, private equity/credit, real estate, opportunistic direct investments.</t>
-        </is>
-      </c>
+          <t>UK private limited company incorporated 12 Sep 2017, presenting as the Lewis family's family-office / holding vehicle. Sits above / alongside Old Friend Capital Limited, a Bournemouth-based real-estate investment and development business run by Christopher (Chris) Lewis, whose track record includes UK leisure-residential and renewable-energy property projects (e.g. Wet N Wild Newcastle, Oasis Swindon). Accounts currently overdue as of research date.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Diversified (consumer, real estate, financials, industrials)</t>
+          <t>Real estate (buying/selling and management of own real estate); leisure-residential property development; renewable energy property (per principal's stated specialism on LinkedIn)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Poole</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Dorset, England</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Michael Dell</t>
+          <t>Christopher David Lewis</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Founder / Family Principal</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr"/>
+          <t>Director (Old House Family Office Limited); principal of Old Friend Capital</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chrislewismoirai/</t>
+        </is>
+      </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>212-303-1668</t>
-        </is>
-      </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>13F-HR filed 2026-05-15 (period ending 2026-03-31) disclosing U.S. equity holdings; rebrand from MSD Capital to DFO Management completed end of 2022.</t>
+          <t>Ceased PSC Stella Ann Lewis on 1 Jun 2024 (trust influence noted); director change May 2021 (Stella Lewis resigned, Christopher Lewis appointed). Accounts overdue as of 2026.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-05-15; 2022-12</t>
+          <t>2017-09-12 (incorporated); 2021-05-14 (director change); 2024-06-01 (Stella Lewis ceased as PSC)</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1887,19 +1879,19 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>The 13F is filed in the name of the Michael &amp; Susan Dell Foundation with DFO Management as manager; the foundation and the family office are affiliated. AUM not disclosed. Michael Dell is a public figure; no personal LinkedIn tied specifically to DFO confirmed. 13F-HR (2026-05-15) signed by Marc R. Lisker (Treasurer, Michael &amp; Susan Dell Foundation) — a verified professional contact at the office in addition to the family principal.</t>
+          <t>No firm website or public FO branding beyond the company name; classification as an operating family office is inferred from the trust/PSC structure and the principal's real-estate activity rather than from any self-description as a family office. Accounts overdue. Registered office is Poole Stadium (a business address). 'Moirai' link is via principal's LinkedIn handle / prior Moirai Capital Investments Ltd, not confirmed as current firm branding.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SFO-blue-pool-capital-tsai</t>
+          <t>SFO-dfo-management-dell</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Blue Pool Capital (Joe Tsai Family Office)</t>
+          <t>DFO Management (Dell Family Office)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1909,61 +1901,65 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tsai family (Joseph Tsai, Alibaba co-founder and chairman)</t>
+          <t>Dell family (Michael Dell, founder/CEO of Dell Technologies)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.bluepoolcapital.com/</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
+          <t>https://www.dellfamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/dfo-management</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hong Kong-based investment firm overseeing the Tsai family's wealth across hedge funds, private equity, private credit, venture and sports assets (Brooklyn Nets, LAFC). Raised ~$1bn for its first dedicated PE vehicle (Riverside Fund) reported 2026. Led by CEO Oliver Weisberg (ex-Goldman Sachs, ex-Citadel).</t>
+          <t>Private investment firm managing the assets of Michael Dell and family across public equities, private equity, real estate and other asset classes. Originally MSD Capital (1998); the multi-client business became BDT &amp; MSD Partners while the family's captive vehicle was rebranded DFO Management at end of 2022.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Multi-strategy long-term capital: public markets, PE, private credit, venture, and sports/real assets.</t>
+          <t>Multi-asset-class permanent capital: public equities, private equity/credit, real estate, opportunistic direct investments.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Diversified; technology (SpaceX, Epic Games, ByteDance), consumer/luxury (Golden Goose), sports, Japanese real estate</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>~$50 billion</t>
-        </is>
-      </c>
+          <t>Diversified (consumer, real estate, financials, industrials)</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Causeway Bay</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Hong Kong Island</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>Joseph Tsai</t>
+          <t>Gregg Lemkau</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Family Principal / Founder</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr"/>
+          <t>Chairman, DFO Management (Co-CEO, BDT &amp; MSD Partners)</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gregg-lemkau-b115b617/</t>
+        </is>
+      </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
@@ -1972,17 +1968,17 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>852-2825-9025</t>
+          <t>212-303-1668</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>13F-HR filed 2026-05-15; sold ~83% of Blue Owl Capital stake (~$460m) reported 2024-03; joined consortium buying Burgundy vineyards 2024-09; raised ~$1bn first PE fund (Riverside) reported 2026-03-31.</t>
+          <t>13F-HR filed 2026-05-15 (period ending 2026-03-31) disclosing U.S. equity holdings; rebrand from MSD Capital to DFO Management completed end of 2022.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-05-15; 2024-03-03; 2024-09-19; 2026-03-31</t>
+          <t>2026-05-15; 2022-12</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1992,19 +1988,19 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Some sources describe Blue Pool as a 'multi-family' vehicle co-backed by former Alibaba executives (and occasionally link Jack Ma); primary characterization is Joe Tsai's family office. Website confirmed to be minimal/uninformative per Crain Currency; bluepoolcapital.com domain asserted from press but not independently fetched. 13F-HR (2026-05-15) signed by Henry Li (Director) — a verified professional contact at the office in addition to the family principal.</t>
+          <t>The 13F is filed in the name of the Michael &amp; Susan Dell Foundation with DFO Management as manager; the foundation and the family office are affiliated. AUM not disclosed. Michael Dell is a public figure; no personal LinkedIn tied specifically to DFO confirmed. 13F-HR (2026-05-15) signed by Marc R. Lisker (Treasurer, Michael &amp; Susan Dell Foundation) — a verified professional contact at the office in addition to the family principal. Principal set to the reachable investment lead (Gregg Lemkau) per LinkedIn pass. Michael Dell is the figurehead; the reachable investment decision-maker is Gregg Lemkau, Chairman of DFO Management (Dell's family office) and Co-CEO of BDT &amp; MSD Partners, ex-Goldman IBD co-head. LinkedIn snippet confirms BDT &amp; MSD / DFO role.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SFO-willett-advisors-bloomberg</t>
+          <t>SFO-bayshore-global-brin</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Willett Advisors (Michael Bloomberg Family Office)</t>
+          <t>Bayshore Global Management (Brin Family Office)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2014,39 +2010,35 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bloomberg family (Michael R. Bloomberg, founder of Bloomberg L.P.)</t>
+          <t>Brin family (Sergey Brin, Google co-founder)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>New York-based investment firm serving as Michael Bloomberg's family office, managing his personal wealth and the assets of Bloomberg Philanthropies across public markets, hedge funds, private equity and credit, real assets and direct investments. Chaired and led by former U.S. auto-industry adviser and Quadrangle co-founder Steven Rattner.</t>
+          <t>Low-profile single-family office managing the wealth of Sergey Brin across public and private markets, real estate and philanthropy. Additional office in Singapore. Reported to have absorbed the Nexus NeuroTech brain-health VC fund in 2026.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Multi-asset, alternatives-heavy allocation (private equity/credit, hedge funds, real assets) for combined personal and philanthropic capital.</t>
+          <t>Broad multi-asset allocation with notable venture/science-and-health direct investing.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Diversified; private equity/credit, hedge funds, real assets, public equities</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>~$25 billion</t>
-        </is>
-      </c>
+          <t>Diversified; neuroscience/brain-health, deep tech, real estate</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>California</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -2056,34 +2048,34 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Michael R. Bloomberg</t>
+          <t>George Pavlov</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Family Principal / Beneficial Owner</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr"/>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/george-pavlov-b009503/</t>
+        </is>
+      </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>212-205-0100</t>
-        </is>
-      </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Ongoing management of Bloomberg's personal + Bloomberg Philanthropies assets under Chairman/CEO Steven Rattner (per Wikipedia/trade press, current).</t>
+          <t>Absorbed Nexus NeuroTech brain-health VC fund (reported 2026-04-23, Bloomberg).</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>2010 (founded); leadership current per 2026 profiles</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -2093,19 +2085,19 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>SEC 13F filings (CIK 0001509379) CEASED after Q3 2014 (last filing 2014-11-04); Willett is NOT a current 13F filer because the bulk of assets are private/alternative. No public website confirmed. AUM is a press figure. Because assets include Bloomberg Philanthropies capital, it straddles family-office and philanthropic-endowment functions, but is consistently characterized as Bloomberg's family office. 13F-HR (2014-11-04) signed by Alice Ruth (Chief Investment Officer) — a verified professional contact at the office in addition to the family principal.</t>
+          <t>No public website confirmed. AUM figures are press estimates. CEO George Pavlov / CIO Marie Young named in Wikipedia and press but not verified against a primary filing. Principal set to the reachable investment lead (George Pavlov) per LinkedIn pass. Sergey Brin is the figurehead; George Pavlov is CEO of Bayshore Global Management and runs the office (CIO is Marie Young, who has no public LinkedIn). The /in/george-pavlov-b009503 profile lists employer as 'Private Family Office' (classic Bayshore anonymity) but does not name the firm, so unconfirmed.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SFO-soros-fund-management</t>
+          <t>SFO-hillspire-schmidt</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Soros Fund Management (Soros Family Office)</t>
+          <t>Hillspire (Eric Schmidt Family Office)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -2115,47 +2107,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Soros family (George Soros, founder; Alexander 'Alex' Soros, chairman)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://www.soros.com/</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/soros</t>
-        </is>
-      </c>
+          <t>Schmidt family (Eric &amp; Wendy Schmidt; Eric Schmidt is former Google/Alphabet CEO and chairman)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>New York-based family office managing the Soros family's wealth and serving as the permanent capital base for the Open Society Foundations. Runs a large, actively traded multi-asset book (public equities, index put options, convertible notes, credit and private investments); recent 13F-reported U.S. equity portfolio ~$9bn.</t>
+          <t>Single-family office of Eric and Wendy Schmidt focused on deep technology: artificial intelligence, quantum computation, defense tech and biotech. Reported to have invested in 22+ private AI firms since 2019 (including Anthropic, SandboxAQ, Inworld AI) and topped CNBC's inaugural family-office dealmaking ranking for 2025.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Actively managed global macro / multi-asset investing, including sizeable hedging (index puts) and credit, supporting long-term family and Open Society capital.</t>
+          <t>Deep-tech direct investing concentrated in AI, quantum, defense technology and biotech.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Diversified; technology (Amazon, Nvidia, Alphabet, Apple, TSMC), consumer/media, credit, options/hedging</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>~$28 billion</t>
-        </is>
-      </c>
+          <t>AI, quantum computing, defense tech, biotech</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>California</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2165,34 +2145,34 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>George Soros</t>
+          <t>Kenneth Goldman</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Founder / Chairman (Family Principal)</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr"/>
+          <t>President, Hillspire</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ken-goldman-552a472</t>
+        </is>
+      </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>212-320-5000</t>
-        </is>
-      </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
-          <t>Q1 2026 13F (as of 2026-03-31) disclosing ~263 positions valued ~$9.12bn (~61% equities, ~20% index put options, ~19% convertibles); top holdings Amazon, Electronic Arts, Nvidia, TSMC, Alphabet, Apple. 2023 generational handover to Alex Soros.</t>
+          <t>Ranked #1 most active U.S. family office for dealmaking in 2025 (15 investments, mostly AI) per CNBC 2026-02-12; disclosed 22 private AI startup investments since 2019 (CNBC 2025-01-21).</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>2026-03-31 (13F period); 2023 (handover)</t>
+          <t>2026-02-12; 2025-01-21</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2202,19 +2182,19 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Dawn Fitzpatrick is reported as CEO/CIO running day-to-day investing (not independently verified against a primary filing here). Manages Open Society Foundations capital as well as family wealth, so it straddles family-office and foundation-endowment functions; consistently characterized as the Soros family office. A related smaller entity, Soros Capital Management LLC (CIK), also files 13F — do not merge. 13F-HR (2026-05-15) signed by John DeSisto (Assistant General Counsel) — a verified professional contact at the office in addition to the family principal.</t>
+          <t>No public website confirmed (hillspire.com not verified). Does not file 13F (EDGAR full-text search returned no 13F-HR). AUM not disclosed. President Ken Goldman named in press, not verified against a primary filing. Principal set to the reachable investment lead (Kenneth Goldman) per LinkedIn pass. Eric Schmidt is the figurehead; Ken Goldman (ex-Yahoo/Fortinet CFO) is President of Hillspire and the office's reachable head of investment/operations. Profile (Atherton, CA) is consistently cited across CNBC/Crunchbase/Bloomberg as his Hillspire presidency.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SFO-grok-ventures-cannon-brookes</t>
+          <t>SFO-blue-pool-capital-tsai</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Grok Ventures (Cannon-Brookes Family Office)</t>
+          <t>Blue Pool Capital (Joe Tsai Family Office)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2224,80 +2204,80 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cannon-Brookes family (Mike Cannon-Brookes, co-founder of Atlassian)</t>
+          <t>Tsai family (Joseph Tsai, Alibaba co-founder and chairman)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.grok.ventures/</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/grok-ventures</t>
-        </is>
-      </c>
+          <t>https://www.bluepoolcapital.com/</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sydney-based single-family office of Atlassian co-founder Mike Cannon-Brookes. One of Australia's most prominent family offices, it has increasingly concentrated on climate and clean-technology investing (backing SunCable's Australia-Asia Power Link, battery and decarbonisation ventures) alongside a diversified portfolio; in early 2026 it announced a climate-only investment focus.</t>
+          <t>Hong Kong-based investment firm overseeing the Tsai family's wealth across hedge funds, private equity, private credit, venture and sports assets (Brooklyn Nets, LAFC). Raised ~$1bn for its first dedicated PE vehicle (Riverside Fund) reported 2026. Led by CEO Oliver Weisberg (ex-Goldman Sachs, ex-Citadel).</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Mission-driven investing to accelerate decarbonisation and net-zero, via venture and direct stakes in climate/clean-tech, energy and enabling technologies.</t>
+          <t>Multi-strategy long-term capital: public markets, PE, private credit, venture, and sports/real assets.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Climate tech, clean energy/renewables, batteries, decarbonisation, technology venture</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
+          <t>Diversified; technology (SpaceX, Epic Games, ByteDance), consumer/luxury (Golden Goose), sports, Japanese real estate</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>~$50 billion</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Sydney</t>
+          <t>Causeway Bay</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>New South Wales</t>
+          <t>Hong Kong Island</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Mike Cannon-Brookes</t>
+          <t>Oliver Weisberg</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Founder / Family Principal</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/in/mikecannonbrookes</t>
-        </is>
-      </c>
+          <t>Chief Executive Officer, Blue Pool Capital</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>852-2825-9025</t>
+        </is>
+      </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>Announced climate-only investment focus and appointment of CEO Tan Kueh (Jan 2026); latest investment Asterix Foods seed round (2025-10-08); portfolio exit of Cog (2025-03-03); long-running backing of SunCable.</t>
+          <t>13F-HR filed 2026-05-15; sold ~83% of Blue Owl Capital stake (~$460m) reported 2024-03; joined consortium buying Burgundy vineyards 2024-09; raised ~$1bn first PE fund (Riverside) reported 2026-03-31.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>2026-01; 2025-10-08; 2025-03-03</t>
+          <t>2026-05-15; 2024-03-03; 2024-09-19; 2026-03-31</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2307,69 +2287,65 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>principal_linkedin is the plausible public Mike Cannon-Brookes /in/ profile but not verified to explicitly list Grok Ventures (marked unconfirmed). Website domain (grok.ventures) asserted from press, not independently fetched. Mike and Annie Cannon-Brookes separated (2023); the office remains Mike's family office.</t>
+          <t>Some sources describe Blue Pool as a 'multi-family' vehicle co-backed by former Alibaba executives (and occasionally link Jack Ma); primary characterization is Joe Tsai's family office. Website confirmed to be minimal/uninformative per Crain Currency; bluepoolcapital.com domain asserted from press but not independently fetched. 13F-HR (2026-05-15) signed by Henry Li (Director) — a verified professional contact at the office in addition to the family principal. Principal set to the reachable investment lead (Oliver Weisberg) per LinkedIn pass. Weisberg (ex-Goldman/Citadel) is CEO of Joe Tsai's HK family office and runs its investments; reachable decision-maker over figurehead Joseph Tsai. No personal /in/ profile located (low LinkedIn footprint).</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SEC13F-0001599603</t>
+          <t>SFO-mousse-partners-wertheimer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tarbox Family Office, Inc.</t>
+          <t>Mousse Partners (Wertheimer Family Office)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>None as a single client family; founder-owned firm (Laura Tarbox founder, CEO and principal owner). Namesake is the founder, not a served family.</t>
+          <t>Wertheimer family (Alain and Gerard Wertheimer, owners of Chanel)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://tarbox.com/</t>
+          <t>https://moussepartners.com/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/tarboxfamilyoffice</t>
+          <t>https://www.linkedin.com/company/moussepartners</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Newport Beach, CA-based multi-family office and SEC-registered investment adviser founded in 1985 by Laura Tarbox, CFP. Fee-only firm serving 100+ HNW/UHNW client families (also charities, businesses, trusts/estates) with comprehensive financial planning, tax preparation and individualized investment management; $5M minimum, over $1B AUM. Also has a Scottsdale, AZ office.</t>
+          <t>Investment firm serving as the family office of the Wertheimer family. Manages a global diversified portfolio across public equities, fixed income, private equity, venture and real estate, with investment operations in New York and Asia (Beijing, Hong Kong).</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Team-based, individualized asset allocation and investment management integrated with comprehensive financial and estate planning; fee-only fiduciary model.</t>
+          <t>Global multi-asset diversified investing with a notable consumer/brands tilt.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Diversified asset-allocation / individualized investment management; no single-sector focus.</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Over $1 billion (100+ client families)</t>
-        </is>
-      </c>
+          <t>Diversified; consumer, luxury/brands, technology, real estate</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>NEWPORT BEACH</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2379,38 +2355,34 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Laura Tarbox</t>
+          <t>Charles Heilbronn</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Founder, CEO &amp; principal owner (CFP)</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>laura@tarbox.com</t>
-        </is>
-      </c>
+          <t>Founder / Chairman</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/charles-heilbronn-27984515b/</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
-          <t>unverified</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>(949) 721-2330</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
-          <t>Founded 1985; CFP since 1984; 100+ client families and &gt;$1B AUM; $5M account minimum; second office in Scottsdale, AZ; Laura Tarbox a frequent WSJ/NYT/LA Times media source</t>
+          <t>Bloomberg feature (2024-2025) reporting the office reshaping its consumer/public-equity bets.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1985 (founded); 1984 (Laura Tarbox CFP)</t>
+          <t>2024/2025 (Bloomberg feature)</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2420,110 +2392,106 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Personal LinkedIn /in profile not located (only firm company page). Email captured from Laura Tarbox's public presentation PDF (matches firm domain) rather than the current bio page; treat as published-but-unverified.</t>
+          <t>Does not appear as a 13F filer under 'Mousse Partners' (EDGAR full-text search returned 0); investment vehicle is domiciled offshore (Mousse Investments Limited, Bermuda) with a NYC office (9 W. 57th St). AUM figure is the family fortune, not disclosed firm AUM. Firm general phone reported as 212-303-5795 (not an individual principal line).</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SEC13F-0002056106</t>
+          <t>SFO-kirkbi-kristiansen</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Stenger Family Office, LLC</t>
+          <t>KIRKBI (Kirk Kristiansen Family Office)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stenger family (firm founded/led by Nick Stenger; the family has advised clients since 1981). The 'family' is the owner-operator, not a single client family.</t>
+          <t>Kirk Kristiansen family (owners of the LEGO Group)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.stengerfamilyoffice.com/</t>
+          <t>https://www.kirkbi.com/</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/stenger-family-office</t>
+          <t>https://www.linkedin.com/company/kirkbi</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Naperville, IL-based multi-family office / independent fiduciary RIA led by founder-CEO Nick Stenger, offering financial planning, investment management, and (via related companies) tax preparation, estate strategies and insurance. Also has a Spring, TX office. ~$731M AUM; named a Forbes Best-in-State Wealth Advisor 2026.</t>
+          <t>Danish family-owned holding and investment company managing the wealth and legacy of the Kirk Kristiansen family. Holds the family's controlling stakes in LEGO Group and Merlin Entertainments and runs a long-term investment portfolio plus a dedicated climate/energy-transition program (KIRKBI Climate). Additional offices in Copenhagen and Baar, Switzerland.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Goals-based planning: assesses cash needs and upcoming goals, then builds customized portfolios.</t>
+          <t>Protect and grow family wealth for future generations; long-term core holdings (LEGO, Merlin) plus diversified investments and thematic climate/energy investing.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Core individual-stock portfolios and ETF-based asset-allocation portfolios; no single-sector focus.</t>
+          <t>Toys/entertainment (core), real estate, renewable energy/climate, diversified financial investments</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>~$731 million (as of 2026-06-30)</t>
+          <t>~$16 billion (family wealth)</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>NAPERVILLE</t>
+          <t>Billund</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>Region of Southern Denmark</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Nicholas David Stenger</t>
+          <t>Soren Thorup Sorensen</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Founder &amp; Chief Executive Officer</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>nick.stenger@stengerfamilyoffice.com</t>
-        </is>
-      </c>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>https://dk.linkedin.com/in/sosorensen</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>630-912-8295</t>
-        </is>
-      </c>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
-          <t>$731M AUM (2026-06-30); Forbes Best-in-State Wealth Advisor 2026; hosts 'The Nick Stenger Show' podcast; opened Spring, TX office</t>
+          <t>KIRKBI Climate follow-on investment in Highview Power (Hunterston project) announced November 2025 (second investment after June 2024 Carrington); Adapture Renewables (KIRKBI-majority-owned) acquired 110MW Colorado solar-plus-storage project March 2025; generational handover of board chair to Thomas Kirk Kristiansen May 2023.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>2026-06-30 (AUM date); 2026 (Forbes Best-in-State)</t>
+          <t>2025-11; 2025-03; 2023-05</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2533,89 +2501,85 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Serves 1,200+ families 'of all net worth sizes' — a broad wealth-management RIA using family-office branding rather than a classic UHNW MFO; hence proof strength 'corroborated'. Personal LinkedIn /in profile not located (only company page and a Calendly slug for 'nicholasstenger'). No published individual email or direct phone line found.</t>
+          <t>KIRKBI is both the family holding company (owns LEGO) and the family investment office; some may classify it as a holding company rather than a pure family office. AUM figure is the family-wealth press figure, not full portfolio value.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEC13F-0001908612</t>
+          <t>SFO-cofra-holding-brenninkmeijer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Allie Family Office LLC</t>
+          <t>COFRA Holding (Brenninkmeijer Family Office)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>None (owner-operated MFO). Founded 2019 and 100% owned by Bruno Ghio, formerly Regional Head of the Family Office / Managing Director at Banco de Credito del Peru (BCP) and a senior private banker at JPMorgan. Not tied to a single client family.</t>
+          <t>Brenninkmeijer family (founders/owners of C&amp;A; ~500 family members)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://allie-intl.com/en/home/</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/alli%C3%A9-family-office</t>
-        </is>
-      </c>
+          <t>https://www.cofraholding.com/</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Miami-based (with a Lima, Peru office) independent multi-family office and SEC-registered investment adviser founded in 2019 by Bruno Ghio, serving Latin American — predominantly Peruvian — high-net-worth families. Provides discretionary and limited-discretionary portfolio management, wealth structuring, tax planning, single-family-office consulting and cross-border coordination via a global network of tax/legal/banking experts.</t>
+          <t>Zug-based family-owned holding coordinating the Brenninkmeijer family's global operations and ~EUR 35-38bn asset base across retail (C&amp;A), real estate (Redevco), private equity (Bregal Investments) and asset management (Anthos). In 2025 the family announced it would open its portfolio to outside investors, a shift from its historically secretive model.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Cross-border wealth management and multi-generational governance for Latin American families relocating capital (and increasingly themselves) to the US; independent, conflict-free advisory.</t>
+          <t>Long-term stewardship of family capital across operating businesses, real estate, private equity and (increasingly) externally-opened investment platforms.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Discretionary and limited-discretionary global portfolio management (largest reported 13F holding is the SPDR S&amp;P 500 ETF Trust; 95 equity positions); diversified across public markets, no single-sector focus disclosed.</t>
+          <t>Retail, real estate, private equity, asset management, climate/energy</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>~$1.15 billion AUM (as of 2024-12-31: ~$508.7M discretionary + ~$637.9M limited-discretionary); aggregators (FINTRX) report ~$1.3B; press (Bloomberg/Crain, 2024) cites ~$2B across the Peru/Miami practice</t>
+          <t>EUR 35-38 billion</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>MIAMI</t>
+          <t>Zug</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>Canton of Zug</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Bruno Ghio</t>
+          <t>Jacco Maters</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Founder &amp; Chief Executive Officer (CFA, CAIA, FRM); 100% owner</t>
+          <t>CEO, Anthos Fund &amp; Asset Management (COFRA/Brenninkmeijer family asset manager)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://pe.linkedin.com/in/bruno-ghio-1264b616b</t>
+          <t>https://www.linkedin.com/in/jacco-maters-74a8364/</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr"/>
@@ -2624,19 +2588,15 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>7866357162</t>
-        </is>
-      </c>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
         <is>
-          <t>Founded 2019; among Peru's top-3 independent multi-family offices; ~23 client families (avg ~$50M); Miami + Lima offices; growth from Peruvian clients relocating to Miami; added a partner in Peru</t>
+          <t>Announced opening of ~EUR 38bn portfolio to external investors (April 2025); Florian Brenninkmeyer appointed CFO effective 1 Jan 2025; Redevco closed landmark GBP 47.5m real-estate-debt loan (April 2025).</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>2019 (firm founding); 2024 (Bloomberg/Crain profile); AUM as of 2024-12-31</t>
+          <t>2025-04; 2025-01-01; 2025-04</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2646,89 +2606,89 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Legal 13F filer name is 'Allie Family Office LLC'; brand is 'Allié Family Office' (allie-intl.com). AUM figures vary by source (~$1.15B ADV vs ~$1.3B FINTRX vs ~$2B press including the broader Peru practice). No individual email or direct phone published; only generic info@ mailbox. Jose Larrabure is the investment lead; Bruno Ghio named principal as founder/CEO/100% owner.</t>
+          <t>COFRA is primarily a family holding company; its asset-management arm Anthos is opening to third-party capital (2025), which blurs the pure single-family-office boundary. Classified SFO at the holding level but noted as trending toward external capital. Principal set to the reachable investment lead (Jacco Maters) per LinkedIn pass. Investments run through Anthos, COFRA's dedicated asset manager; Maters (CFA, ex-Delta Lloyd Group CIO) is its CEO and the party a fund manager would contact. COFRA Holding group CEO is Boudewijn Beerkens; figurehead is Martijn Brenninkmeijer.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SEC13F-0001511137</t>
+          <t>SFO-premji-invest</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pathstone Family Office, Llc</t>
+          <t>Premji Invest (Azim Premji Family Office)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>No single family; one of the largest U.S. multi-family offices serving many UHNW families, SFOs and institutions.</t>
+          <t>Premji family (Azim Premji, founder of Wipro)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://pathstone.com</t>
+          <t>https://www.premjiinvest.com/</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/pathstone-family-office</t>
+          <t>https://www.linkedin.com/company/premjiinvest</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Englewood, NJ headquartered partner-owned multi-family office and SEC-registered RIA founded in 2010 (co-founders Matthew Fleissig, Allan Zachariah, Steve Braverman). Provides integrated investment management, tax, insurance/risk, legacy planning and family-office services to UHNW families, family offices, foundations and endowments; ~$125B firm AUM (2025).</t>
+          <t>Bengaluru-based family office and investment firm managing the wealth of Azim Premji and family (and closely tied to the Azim Premji Foundation endowment). Invests across public equities, private equity and venture, backing technology, financial services, consumer, healthcare and industrials; crossed $10bn in managed assets.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Integrated, institutional-quality advice with a client-first culture; open-architecture investment management including private markets and alternatives; scale via organic growth and acquisitions (e.g., Crestone Capital).</t>
+          <t>Long-horizon growth investing across public and private markets in emerging/disruptive technology and consumer/financial sectors.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Public equities (13F holdings), private markets/alternatives, fixed income, diversified multi-asset portfolios</t>
+          <t>Technology, financial services, consumer, healthcare, industrials</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>~$125 billion (firm) as of 12/31/2025; ~$187 billion including affiliate firms (other sources cite $170B+ aggregate in 2025).</t>
+          <t>&gt; $10 billion</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>ENGLEWOOD</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>India</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Matthew Fleissig</t>
+          <t>T.K. Kurien</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Chief Executive Officer (co-founder)</t>
+          <t>CEO &amp; Managing Partner</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/fleissig/</t>
+          <t>https://in.linkedin.com/in/tk-kurien-2b456a5</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr"/>
@@ -2737,19 +2697,15 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>857-305-3070</t>
-        </is>
-      </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
-          <t>Founded 2010; 15th anniversary in 2025; acquired Crestone Capital; ~775+ employees; co-founders Allan Zachariah and Steve Braverman serve as Co-Chairmen; multiple 2025 Family Wealth Report Awards.</t>
+          <t>Acquisition of Anand Chemiceutics reported 2025-11-13; participated in Runway Series E (with General Atlantic, Nvidia) 2026-02-10; 19 funding rounds / 2 acquisitions in trailing 12 months (per Tracxn, Feb 2026).</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>Founded 2010; AUM as of 12/31/2025; ADV dated 03/31/2025.</t>
+          <t>2025-11-13; 2026-02-10</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2759,89 +2715,85 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Very large firm; AUM figures vary by whether affiliate firms are included and by reporting date. No published individual email.</t>
+          <t>Premji Invest also manages the Azim Premji Foundation's endowment, so it straddles family-office and foundation-endowment functions; consistently described as a family office, hence corroborated rather than strong-single-family-only.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SEC13F-0001731123</t>
+          <t>SFO-catamaran-ventures-murthy</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Biltmore Family Office, LLC</t>
+          <t>Catamaran Ventures (N.R. Narayana Murthy Family Office)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Founder Chris Cecil is a great-grandson of George Vanderbilt (builder of the Biltmore Estate) and son of Asheville developer George Cecil; 'Biltmore' name derives from that Vanderbilt/Cecil family heritage. The firm serves many outside client families (MFO), not the Vanderbilt/Cecil family exclusively.</t>
+          <t>Murthy family (N.R. Narayana Murthy, co-founder of Infosys)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.biltmorefamilyoffice.com/</t>
+          <t>https://catamaran.in/</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/biltmore-family-office-llc</t>
+          <t>https://www.linkedin.com/company/catamaran-ventures</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Charlotte, NC-based multi-family office and SEC-registered investment adviser founded in 2008 by Chris Cecil. A collaborative/independent RIA to investment-oriented multi-generational families and institutions, providing investment management, asset allocation, investment-policy design, multi-generational and succession planning. ~$3.2-3.5B AUM.</t>
+          <t>Bengaluru-based single-family office of Infosys co-founder N.R. Narayana Murthy, investing permanent family capital (no external LPs). Focused on growth capital, notably Indian manufacturing and deep tech; has recently turned more cautious on Indian startup valuations.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Collaborative, investment-policy-driven management for multi-generational HNW/UHNW families and institutions.</t>
+          <t>Permanent-capital growth investing, with emphasis on Indian manufacturing and deep-tech, valuation-disciplined.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Diversified public-equity/ETF portfolios; disclosed top 13F holdings include AAPL, IAU (gold), AVDX, ROBO, VV. No single-sector concentration.</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>~$3.2-3.5 billion (reported ~$3.47B regulatory AUM across ~951 accounts)</t>
-        </is>
-      </c>
+          <t>Manufacturing, deep tech, consumer, technology</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>CHARLOTTE</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>India</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Chris Cecil</t>
+          <t>Deepak Padaki</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Founder, President &amp; CEO</t>
+          <t>President, Catamaran</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/chris-cecil-9701b818/</t>
+          <t>https://in.linkedin.com/in/deepakpadaki</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr"/>
@@ -2850,19 +2802,15 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>+1 704-248-5230</t>
-        </is>
-      </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
-          <t>Founded 2008 by Chris Cecil (LLC organized 2013); ~$3.2-3.5B AUM across ~951 accounts, avg client ~$38M; Cecil chairs TIGER 21 Charlotte / Family Office groups</t>
+          <t>Bloomberg (2025-08-26) reporting Catamaran growing cautious on Indian startup valuations; recent deep-tech stake and follow-on investments (Akshayakalpa first-time, Innoviti follow-on) in 2025.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>2008 (founding); 2013 (LLC organized)</t>
+          <t>2025-08-26; 2025</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -2872,81 +2820,77 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>Chris Cecil chosen as principal (founder/CEO); Rael Gorelick is Partner &amp; Head of Investments and would be the CIO-level investment lead. No published individual email located. AUM varies by source ($3.2B-$3.5B).</t>
+          <t>Investment pace slowed in 2025 (approximately one new investment) per Tracxn; AUM not disclosed. Principal set to the reachable investment lead (Deepak Padaki) per LinkedIn pass. Padaki (ex-Infosys Group Head of Strategy/Chief Risk Officer) is President of Catamaran and sets investment strategy/asset allocation; reachable decision-maker over founder-figurehead N.R. Narayana Murthy. LinkedIn snippet matches name + President, Catamaran.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SEC13F-0001039807</t>
+          <t>APAC-dalio-family-office-singapore</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Boston Family Office Llc</t>
+          <t>Dalio Family Office (Ray Dalio) — Singapore</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MFO</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>https://www.bosfam.com/</t>
-        </is>
-      </c>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Dalio family — Ray Dalio (founder of Bridgewater Associates) and family</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>The Boston Family Office LLC is an independent, employee-owned registered investment adviser founded in 1996 and based in Boston, MA. It provides multi-family-office-style wealth management -- investment management, financial planning, and adviser selection -- to high-net-worth individuals, families and charitable organizations across roughly 789 accounts and ~$1.7-2.0B in assets. It is a multi-family/RIA firm rather than a single-family office.</t>
+          <t>The Singapore office of Ray Dalio's global single-family office. The Dalio Family Office invests across private equity, venture capital, real estate and credit and runs the family's philanthropy in Asia. Singapore was chosen as the Asia base given Dalio's long-standing ties to Singapore and China; the DFO also operates in Abu Dhabi. Globally the DFO is led by CEO Janine Racanelli (ex-JPMorgan) and COO Tom Waller; the Singapore office has been associated with Managing Director Tan Mae Shen.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Client-tailored, diversified portfolio management for wealth preservation and growth across HNW households and institutions; discretionary management (769 of 789 accounts discretionary). Specific house investment philosophy not detailed publicly.</t>
+          <t>Global multi-asset investing (PE, VC, real estate, credit) with a Singapore hub for Asian investments and philanthropy.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Diversified multi-asset wealth management (public equities, fixed income, funds); not sector-specialized. A partner sits on the board of fixed-income manager Breckinridge Capital Advisors.</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>~$1.7B AUM across 789 accounts (Form ADV/adviserinfo, 2024-2025); third-party profiles cite ~$1.9-2.02B. As of the most recent Form ADV (2024 filing cycle).</t>
-        </is>
-      </c>
+          <t>Private equity; Venture capital; Real estate; Credit</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>George P. Beal</t>
+          <t>Tan Mae Shen</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; Managing Partner (Portfolio Manager)</t>
+          <t>Managing Director, Dalio Family Office (Singapore)</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/george-beal-a6107a16/</t>
+          <t>https://sg.linkedin.com/in/mae-shen-tan</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr"/>
@@ -2955,19 +2899,15 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>617-624-0800</t>
-        </is>
-      </c>
+      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
-          <t>Filed Form ADV Part 2A/2B brochures in the 2024 filing cycle (Feb 2024); a partner (Beal) serves on the board of Breckinridge Capital Advisors. Firm moved offices to 20 Custom House St.</t>
+          <t>2020: Dalio Family Office opened in Singapore; Dalio donated USD25m to Singapore's Wealth Management Institute. 2021: Tan Mae Shen joined as Singapore MD; Dalio bought two Club Street shophouses for ~SGD18.9m. Global CIO Mark Baumgartner departed Aug 2024.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2024-02-01 (ADV Part 2B brochure)</t>
+          <t>2020; 2021; 2024-08</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
@@ -2977,108 +2917,96 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>Despite the 'family office' name, this is functionally a multi-family-office RIA / private wealth manager serving hundreds of client accounts, not a single family's office. Investment authority is distributed among ~8 managing directors, so Beal is one of several senior decision-makers (though the 13F signatory and co-founder). No official company LinkedIn URL confirmed. No individual email is published (the ZoomInfo masked pattern was deliberately not used).</t>
+          <t>The Dalio Family Office's global headquarters is in Westport, Connecticut (USA), with offices in New York, Singapore and Abu Dhabi; this record covers the Singapore office as a Singapore-hubbed APAC operation, not the global HQ. No AUM or public website confirmed. Principal LinkedIn not verified. Principal set to the reachable investment lead (Tan Mae Shen) per LinkedIn pass. Tan (ex-JPMorgan/Credit Suisse, 14 yrs) is MD of the Dalio Family Office Singapore and its local head; reachable over figurehead Ray Dalio. LinkedIn profile (Mae Shen Tan, Singapore) matches and posted Dalio Family Office Singapore hiring.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SEC13F-0002017744</t>
+          <t>APAC-tsao-family-office-tpc</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC</t>
+          <t>Tsao Family Office (IMC Group / TPC — Chavalit Tsao)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>MFO</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>SFO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Tsao family — founders/controllers of IMC Group (Pan Asia maritime and industrial group); led by fourth-generation steward Chavalit Frederick Tsao</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://arrowrootfamilyoffice.com/</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/arrowroot-family-office</t>
-        </is>
-      </c>
+          <t>https://tsaopaochee.com/</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Arrowroot Family Office, LLC is a Marina del Rey, CA-based registered investment adviser and multi-family office, originally founded in 2013 as Vitreous Partners and rebranded in 2017. It provides multidisciplinary wealth management -- investment management, retirement, tax and estate planning -- to high-net-worth individuals, entrepreneurs, families and small institutions, with offices in Southern and Northern California, Virginia and Michigan. It is a multi-client RIA, not a single family's office.</t>
+          <t>The single-family office / strategic investment arm of Singapore's Tsao family, whose IMC Group traces its roots to 1906 and spans maritime, industrial and diversified businesses across 15+ countries. Organised today under TPC (Tsao Pao Chee) alongside the OCTAVE well-being ecosystem, the office pursues impact and ESG investing across environment, healthcare and education, reflecting Chavalit Tsao's 'well-being economy' philosophy.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Team-based, fiduciary, goals-driven wealth management emphasizing comprehensive planning and diversified investment management for affluent households and business owners; open-architecture advice.</t>
+          <t>Purpose-led, long-term impact/ESG investing (environment, healthcare, education) integrated with the family's maritime and industrial businesses under a 'well-being economy' model.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Diversified multi-asset wealth management (public equities, funds/ETFs, fixed income, alternatives); not sector-specialized.</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>~$431M AUM as of Q2 2025 (third-party profiles); regulatory AUM per the 2025 Form ADV on the firm's site. A floor for total client assets under advisement.</t>
-        </is>
-      </c>
+          <t>Impact/ESG; Healthcare; Education; Environment/sustainability; Maritime and industrial</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Marina Del Rey</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Rob (Roberto Francisco) Santos</t>
+          <t>Bryan Goh</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Chief Executive Officer &amp; Principal Owner</t>
+          <t>CEO &amp; Chief Investment Officer, Tsao Family Office (TPC)</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/rob-santos-afo/</t>
+          <t>https://sg.linkedin.com/in/convexity</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>310.341.4774</t>
-        </is>
-      </c>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr">
         <is>
-          <t>Announced expansion of its private-wealth practice into Michigan via addition of The Athena Financial Group (offices now include Marina del Rey CA, Rochester Hills MI, Charlottesville VA, El Dorado Hills CA); filed updated Form ADV Part 2A/2B in April 2025.</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>2022-09-05 (Michigan/Athena expansion press release); 2025-04 (Form ADV update)</t>
-        </is>
-      </c>
+          <t>OCTAVE Well-being Economy Fund / OCTAVE investment platform active; TPC restructuring of the family enterprise into an integrated 'well-being business ecosystem' (IMC Industrial, OCTAVE and non-profits).</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr">
         <is>
           <t>B+</t>
@@ -3086,106 +3014,94 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>Uses the 'family office' label but is a multi-client wealth-management RIA, not a single family's office. Possible name confusion with 'Arrowroot Capital Management' (a separate B2B enterprise-software private-equity firm) -- they are distinct; relationship not established here. No individual email published; RocketReach/broker data deliberately not used. Firm's most recent 13F filer registration is recent (CIK 0002017744).</t>
+          <t>The family's structure spans several brands (TPC/Tsao Pao Chee, IMC Industrial, OCTAVE, Octave Capital); the precise legal entity of the family office is not cleanly disclosed. Dated recent signals were not pinned down in sources reviewed. No AUM, principal LinkedIn or individual email confirmed. Principal set to the reachable investment lead (Bryan Goh) per LinkedIn pass. Goh (ex-Bordier CIO, DBS) is CEO &amp; CIO of the Tsao/TPC family office and runs investments; reachable over figurehead Chavalit Frederick Tsao. /in/convexity snippet reads 'Bryan Goh - CEO, Tsao Family Office' (note: /in/bryangoh1 is a different Bryan Goh at Treehouse Finance).</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SEC13F-0001756485</t>
+          <t>APAC-ee-capital-saverin</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Independent Family Office, LLC</t>
+          <t>EE Capital (Eduardo Saverin family office)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>None (owner-operated MFO). Founded 2005 by W. Michael Reickert, who previously led the family-office practice at The Ayco Company. Serves multiple entrepreneurial client families; not a single-family vehicle.</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://ifollc.com/</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/independent-family-office-llc</t>
-        </is>
-      </c>
+          <t>Saverin family — Eduardo Saverin (Facebook co-founder, Singapore citizen since 2011) and wife Elaine Andriejanssen</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Albany, New York-based multi-family office and SEC-registered investment adviser founded in 2005 by W. Michael Reickert. A bespoke family office serving a small number of high-net-worth families (average client tenure 10+ years) with investment advisory and asset allocation, estate-planning coordination, transaction/contract advisory and income-tax planning and compliance.</t>
+          <t>Single-family office in Singapore managing the wealth of Facebook co-founder Eduardo Saverin, who relocated to Singapore in 2009 and became a citizen in 2011 and is repeatedly ranked Singapore's richest person by Forbes. EE Capital reportedly allocates proprietary capital across private equity, venture capital, hedge funds and public equities. Saverin separately co-founded the venture firm B Capital (a distinct, California-headquartered VC manager).</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Technical, unbiased, independent long-term stewardship of client families' financial lives; capital-allocator approach.</t>
+          <t>Diversified proprietary investing of the Saverin family fortune across private equity, venture capital, hedge funds and public markets.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Discretionary portfolio management and outside-manager selection for HNW families (largest reported 13F holding is the SPDR S&amp;P 500 ETF Trust); diversified, no single-sector focus disclosed.</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>~$617.8 million discretionary AUM across ~34 clients (Form ADV, 2025-03-31); aggregators (FINTRX) report ~$760M</t>
-        </is>
-      </c>
+          <t>Private equity; Venture capital; Hedge funds; Public equities</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>ALBANY</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>W. Michael Reickert</t>
+          <t>Eduardo Saverin</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Managing Member / Managing Partner &amp; CEO (also Chief Compliance Officer); IRS Enrolled Agent, JD</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr"/>
+          <t>Family principal (EE Capital Executive Chairman: Elaine Andriejanssen)</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>https://sg.linkedin.com/in/saverin</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>(518) 452-8050</t>
-        </is>
-      </c>
+      <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr">
         <is>
-          <t>Founded 2005; SEC-registered 2012; ex-Ayco family-office pedigree; very low client count (~34) with 10+ year average tenure</t>
+          <t>Sep 2023 / 2024: Saverin ranked Singapore's richest person by Forbes (net worth reported &gt;USD30bn). Sep 2024: Eduardo and Elaine Saverin donated USD15.5m to Singapore American School.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>2005 (founding); 2012 (SEC registration); AUM ~$617.8M as of 2025-03-31</t>
+          <t>2023-09; 2024-09</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
@@ -3195,89 +3111,81 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Firm marketing copy calls itself a 'bespoke family office' for 'select clients'; the ~34-client, multi-family reality plus Altss classification support MFO. 'dr@ifollc.com' is published but its initials do not match the principal, so it is treated as a shared/general mailbox, not the principal's individual email. No personal LinkedIn confirmed for W. Michael Reickert.</t>
+          <t>EE Capital is a private SFO; detail relies on Preqin/Citywire/Altss rather than primary filings, hence 'corroborated' not 'strong'. Do not conflate with B Capital, Saverin's separate VC firm headquartered in California. No website, principal LinkedIn or individual email confirmed.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UKCH-09580739</t>
+          <t>SFO-willett-advisors-bloomberg</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Blu Family Office Limited</t>
+          <t>Willett Advisors (Michael Bloomberg Family Office)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Originally Armbruester family (founder's wealth); now MFO serving multiple client families</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://www.blu-fo.com</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>https://uk.linkedin.com/company/blu-family-office</t>
-        </is>
-      </c>
+          <t>Bloomberg family (Michael R. Bloomberg, founder of Bloomberg L.P.)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>FCA-regulated multi-family office (Ltd inc. 2015; operations from 2010) in Richmond upon Thames, founded by Christian Armbruester post Credit Suisse. Offers hedge funds, crypto and alternatives; discretionary arm Blu Investment Management.</t>
+          <t>New York-based investment firm serving as Michael Bloomberg's family office, managing his personal wealth and the assets of Bloomberg Philanthropies across public markets, hedge funds, private equity and credit, real assets and direct investments. Chaired and led by former U.S. auto-industry adviser and Quadrangle co-founder Steven Rattner.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Discretionary management not relying on forecasting; 'true diversification' and systematic rebalancing; passive in calm markets, opportunistic in adverse ones.</t>
+          <t>Multi-asset, alternatives-heavy allocation (private equity/credit, hedge funds, real assets) for combined personal and philanthropic capital.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Hedge funds; crypto assets; alternatives; diversified multi-asset</t>
+          <t>Diversified; private equity/credit, hedge funds, real assets, public equities</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>£0.5bn-£1bn (third-party estimated range)</t>
+          <t>~$25 billion</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Richmond</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Greater London</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Christian Armbruester</t>
+          <t>Steven Rattner</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Founder &amp; Principal (largest shareholder ~40.8%)</t>
+          <t>Chairman &amp; CEO, Willett Advisors</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/christianarmbruesterblufamilyoffice</t>
+          <t>https://www.linkedin.com/in/srattner/</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr"/>
@@ -3286,15 +3194,19 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr"/>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>212-205-0100</t>
+        </is>
+      </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Founded 2010; Ltd inc. 2015; new director Vishesh Dawar appointed Dec 2025; investment arm rebranded Blu Investment Management; Marie Redron now CEO</t>
+          <t>Ongoing management of Bloomberg's personal + Bloomberg Philanthropies assets under Chairman/CEO Steven Rattner (per Wikipedia/trade press, current).</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>2015-05-08; 2025-12-08</t>
+          <t>2010 (founded); leadership current per 2026 profiles</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
@@ -3304,81 +3216,89 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Client-facing operations now run under 'Blu Investment Management' (blu-im.com), same address. Armbruester is founder/principal but not current CEO (Marie Redron is). AUM range is a third-party estimate. Only published contacts are a switchboard + generic mailbox.</t>
+          <t>SEC 13F filings (CIK 0001509379) CEASED after Q3 2014 (last filing 2014-11-04); Willett is NOT a current 13F filer because the bulk of assets are private/alternative. No public website confirmed. AUM is a press figure. Because assets include Bloomberg Philanthropies capital, it straddles family-office and philanthropic-endowment functions, but is consistently characterized as Bloomberg's family office. 13F-HR (2014-11-04) signed by Alice Ruth (Chief Investment Officer) — a verified professional contact at the office in addition to the family principal. Principal set to the reachable investment lead (Steven Rattner) per LinkedIn pass. Michael Bloomberg is the figurehead; Steven Rattner is Chairman &amp; CEO of Willett Advisors (Bloomberg's personal/philanthropic investment arm; CIO is Andrew Mulderry). LinkedIn snippet explicitly confirms 'Chairman and CEO at Willett Advisors LLC'.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UKCH-12233405</t>
+          <t>SFO-soros-fund-management</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Schwarz Family Office Ltd</t>
+          <t>Soros Fund Management (Soros Family Office)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Undetermined</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Named after principal Andreas Schwarz (German); no wider family group evidenced beyond the surname</t>
+          <t>Soros family (George Soros, founder; Alexander 'Alex' Soros, chairman)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://schwarzfamilyoffice.com/</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>https://www.soros.com/</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/soros</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>London-based boutique investment/advisory firm branded as a family office, established 2019, led by Andreas Schwarz; provides capital raising, debt financing, wealth management and IR services.</t>
+          <t>New York-based family office managing the Soros family's wealth and serving as the permanent capital base for the Open Society Foundations. Runs a large, actively traded multi-asset book (public equities, index put options, convertible notes, credit and private investments); recent 13F-reported U.S. equity portfolio ~$9bn.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>'Be not afraid of growing slowly, be afraid only of standing still' — sustainable growth via established relationships and exclusive investor access. https://schwarzfamilyoffice.com/</t>
+          <t>Actively managed global macro / multi-asset investing, including sizeable hedging (index puts) and credit, supporting long-term family and Open Society capital.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Private equity; fintech; wealth management; venture capital; private debt; IPOs</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+          <t>Diversified; technology (Amazon, Nvidia, Alphabet, Apple, TSMC), consumer/media, credit, options/hedging</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>~$28 billion</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Maida Vale</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Andreas Schwarz</t>
+          <t>Dawn Fitzpatrick</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Founder / Director</t>
+          <t>Chief Executive Officer &amp; Chief Investment Officer</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
+          <t>https://www.linkedin.com/in/dawnfitzpatrick/</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr"/>
@@ -3387,15 +3307,19 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>212-320-5000</t>
+        </is>
+      </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>Listed in Family Capital 'FamCap 50' (2024); second shareholder Syed Furqan Ahmed (490 shares)</t>
+          <t>Q1 2026 13F (as of 2026-03-31) disclosing ~263 positions valued ~$9.12bn (~61% equities, ~20% index put options, ~19% convertibles); top holdings Amazon, Electronic Arts, Nvidia, TSMC, Alphabet, Apple. 2023 generational handover to Alex Soros.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>2024-02 (FamCap 50)</t>
+          <t>2026-03-31 (13F period); 2023 (handover)</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
@@ -3405,106 +3329,98 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>Presents as a family office but functions largely as a boutique capital-raising/advisory consultancy with two shareholders — fo_type left Undetermined. A Family Capital story linking Schwarz to a 'famous UK brand' is paywalled and the brand is NOT confirmed; not asserted. AUM undisclosed.</t>
+          <t>Dawn Fitzpatrick is reported as CEO/CIO running day-to-day investing (not independently verified against a primary filing here). Manages Open Society Foundations capital as well as family wealth, so it straddles family-office and foundation-endowment functions; consistently characterized as the Soros family office. A related smaller entity, Soros Capital Management LLC (CIK), also files 13F — do not merge. 13F-HR (2026-05-15) signed by John DeSisto (Assistant General Counsel) — a verified professional contact at the office in addition to the family principal. Principal set to the reachable investment lead (Dawn Fitzpatrick) per LinkedIn pass. George Soros is the figurehead; Dawn Fitzpatrick is CEO/CIO of Soros Fund Management and the actual investment decision-maker. Profile (Danbury, CT) is widely and consistently cited as her Soros CEO/CIO presence.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>APAC-farro-capital</t>
+          <t>SFO-bezos-expeditions</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Farro Capital</t>
+          <t>Bezos Expeditions (Jeff Bezos Family Office)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MFO</t>
+          <t>SFO</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Multi-family office — serves multiple UHNW families, billionaires and unicorn founders; not tied to a single family</t>
+          <t>Bezos family (Jeff Bezos, founder of Amazon)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://farrocapital.com/</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>https://sg.linkedin.com/company/farrocapital</t>
-        </is>
-      </c>
+          <t>https://www.bezosexpeditions.com/</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Independent multi-family office and wealth-management platform founded in October 2022 and headquartered in Singapore, with a regional headquarters established in the DIFC (Dubai). Founded by a team of former private and corporate bankers (Hemant Tucker, Manish Tibrewal, Mahesh Kumar, Rajiv Garg, Uthpal Rao) from institutions including Bank of Singapore, UBS, Barclays and Standard Chartered. Offers goal-based investing, risk management, credit solutions, cross-border structuring, next-generation planning and philanthropic stewardship.</t>
+          <t>Personal investment and venture vehicle of Jeff Bezos, making early- and growth-stage direct investments across technology, biotech, fintech, cloud and healthcare (historically Google, Uber, Airbnb, Twitter, Workday, Business Insider, NotCo). Distinct from his aerospace company Blue Origin and from Nash Holdings (which owns The Washington Post).</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Holistic, goal-based multi-asset wealth management and cross-border structuring for global UHNW families, with a philanthropy/impact emphasis.</t>
+          <t>Founder-led venture and direct investing in disruptive technology and science, long horizon, concentrated conviction bets.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Multi-asset wealth management; Private markets; Public markets; Philanthropy/impact</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>~USD2-3 billion</t>
-        </is>
-      </c>
+          <t>Technology, biotechnology, fintech, cloud computing, healthcare technology</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Mercer Island</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Hemant Tucker</t>
+          <t>Melinda Lewison</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Co-Founder &amp; Chief Executive Officer</t>
+          <t>Managing Director</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/in/hemant-tucker-a97b49bb/</t>
+          <t>https://www.linkedin.com/in/melindalewison/</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
         <is>
-          <t>unverified</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr">
         <is>
-          <t>Oct 2022: founded / soft-launched in Singapore. 2023-2026: grew AUM from &gt;USD1bn to ~USD3bn across 12+ markets. Established a DIFC (Dubai) regional headquarters to drive global expansion.</t>
+          <t>Ongoing venture/direct investing (historically Airbnb, Uber, Twitter, Stack Overflow, Workday, NotCo). Note: recent dated deal specifics not verified against a primary source here.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>2022-10; 2026-04</t>
+          <t>2005 (founded)</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
@@ -3514,19 +3430,19 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>Multi-family office (not a single-family office). Sister brand 'Farro &amp; Co' (international mobility advisory, 3 Philip Street, Singapore) is a distinct entity from Farro Capital. AUM figures are self-reported/press-reported. Principal LinkedIn confirmed; no published individual email.</t>
+          <t>Does not file SEC 13F (a private venture/direct-investment vehicle). Legal-entity structure is opaque; the actual investing entity names (e.g., Zefram LLC) are asserted from trade press and not confirmed against a primary filing here. HQ commonly cited as Mercer Island / Seattle WA. AUM figures in trade press conflate the office with Bezos's net worth. Rated corroborated (not strong) pending a primary/legal-registry confirmation of the exact entity. Principal set to the reachable investment lead (Melinda Lewison) per LinkedIn pass. Jeff Bezos is the figurehead; Melinda Lewison is Managing Director of Bezos Expeditions and its day-to-day investment lead (ex-Lehman/Rustic Canyon). The /in/melindalewison profile (Seattle - matches office location) does not name Bezos Expeditions in the snippet, so unconfirmed.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UKCH-14344019</t>
+          <t>SFO-pritzker-organization</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hazell Family Office Ltd</t>
+          <t>The Pritzker Organization (Tom Pritzker Family Office)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3536,49 +3452,61 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Hazell family of South Wales (haulage/waste/environmental-services wealth)</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
+          <t>Pritzker family (Tom Pritzker, executive chairman of Hyatt Hotels; descendants of Nicholas J. Pritzker)</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>https://pritzkerorg.com/</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Active company (inc. 2022-09-08), SIC 70221 financial management; board is five members of the Hazell family. Structure strongly indicates a single-family office. No website/press footprint.</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Chicago-based family office / merchant bank managing the assets of Tom Pritzker and the extended Pritzker family. Deploys permanent capital with a long-term 'buy to build' approach across private equity and growth equity; growth-stage positions have included Palantir, SpaceX, Uber, Dataminr, BlueVoyant and Nimble Robotics.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Permanent-capital, long-hold 'buy to build' investing across control private equity and later-stage growth equity (not a buy-to-sell PE fund).</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>70221 - Financial management</t>
+          <t>Diversified; technology/growth equity, industrials, consumer, private equity</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Usk</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Monmouthshire, Wales</t>
+          <t>Illinois</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Mark David William Hazell</t>
+          <t>Joseph Gleberman</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Director (family principal)</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr"/>
+          <t>Chief Executive Officer, The Pritzker Organization</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/joseph-gleberman-74630258/</t>
+        </is>
+      </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
         <is>
@@ -3588,34 +3516,34 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr">
         <is>
-          <t>Incorporated Sept 2022; five family directors appointed same day; principal is MD of family haulage/environmental companies</t>
+          <t>Pritzker family office launched a venture-capital fund (Crain's Chicago Business report); ongoing growth-equity positions incl. Palantir, SpaceX, Uber, Dataminr.</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2022-09-08</t>
+          <t>Reported by Crain's (date not independently confirmed here)</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>SFO status inferred from shared surname + single family-farm address + Mark Hazell's operating-company directorships; no website/press confirms active investment operations. 'Mark = principal' is inference; control may be shared across the family.</t>
+          <t>The Pritzker family runs SEVERAL distinct vehicles (The Pritzker Organization / Tom Pritzker; Pritzker Group / Tony &amp; J.B. Pritzker; Pritzker Private Capital / PPC; various family foundations) — do not merge them. Does not file 13F. AUM not disclosed. Signals date not verified. Principal set to the reachable investment lead (Joseph Gleberman) per LinkedIn pass. Tom Pritzker is Executive Chairman/figurehead; Joseph Gleberman (ex-Goldman Sachs merchant banking) is CEO of The Pritzker Organization and the reachable investment decision-maker. LinkedIn snippet confirms 'The Pritzker Organization'.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>UKCH-14442767</t>
+          <t>SFO-hartono-family-office</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wedgwood Family Office Limited</t>
+          <t>Hartono Family Office / GDP Venture (Hartono Family)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3625,49 +3553,65 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Wedgwood (Paul Wedgwood family)</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
+          <t>Hartono family (Robert Budi Hartono and the late Michael Bambang Hartono; owners of Djarum and largest shareholders of Bank Central Asia)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>https://www.gdpventure.com/</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gdp-venture</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>UK private company (inc. 2022-10-25) under fund-management SIC, registered at a residential address in Keston. Appears to be the personal single-family investment vehicle of Paul Wedgwood.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Jakarta-based single-family office managing the multi-generational wealth of Indonesia's richest family. Capital base is the family's controlling interests in Bank Central Asia (BCA), Djarum (tobacco), Polytron (electronics) and Grand Indonesia (property). Allocations span public equities, private equity, real estate and venture, with technology venture investing run through GDP Venture (Blibli, Kaskus, Gojek-era bets).</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Preserve and grow the family's core BCA/Djarum wealth while building Indonesian digital-economy and consumer businesses via GDP Venture.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>66300 - Fund management activities</t>
+          <t>Financial services (BCA), consumer/tobacco, consumer electronics, real estate, technology/venture (e-commerce, digital media)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Keston</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Greater London (Bromley)</t>
+          <t>Jakarta</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Paul Wedgwood</t>
+          <t>Martin Basuki Hartono</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr"/>
+          <t>Chief Executive Officer, GDP Venture</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tarm1n/</t>
+        </is>
+      </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
@@ -3677,34 +3621,34 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr">
         <is>
-          <t>Co-director Christopher James Sharp resigned 2024-04-16; new secretary appointed 2026-01-06; accounts currently overdue</t>
+          <t>Michael Bambang Hartono died March 2026 (age 86) in Singapore; November 2025 reporting of a 6-month travel ban on Victor Hartono amid an Indonesian tax investigation; ongoing GDP Venture digital-economy investing.</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2024-04-16; 2026-01-06</t>
+          <t>2026-03-21; 2025-11-24</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>Link between director 'Paul Wedgwood, b.1970' and the Splash Damage/Supernova entrepreneur is a strong inference (name + DOB + separate Wedgwood FIC directorship), NOT hard-confirmed. Zero public FO footprint (no website/LinkedIn/press/AUM); accounts overdue. Residential registered address.</t>
+          <t>The 'Hartono Family Office' as a single named legal entity is asserted mainly from family-office databases (altss, cbinsights); the family's investing is publicly visible chiefly through GDP Venture and their operating holdings (Djarum, BCA). GDP Venture is the venture arm, not the whole office. Rated corroborated. A 2025 corruption/tax investigation touching Victor Hartono is an ongoing reputational caveat (allegations, not adjudicated). Principal set to the reachable investment lead (Martin Basuki Hartono) per LinkedIn pass. Martin Hartono (son of patriarch R. Budi Hartono) is CEO of GDP Venture, the family's venture/investment arm; reachable decision-maker over figurehead Robert Budi Hartono. LinkedIn snippet matches name + CEO at GDP Venture.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>UKCH-17062903</t>
+          <t>SFO-grok-ventures-cannon-brookes</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Frigus Family Office Ltd</t>
+          <t>Grok Ventures (Cannon-Brookes Family Office)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3714,57 +3658,65 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Gudmundsson family (Lydur Gudmundsson, co-founder of Bakkavor; brother Agust Gudmundsson also linked to Frigus-branded entities)</t>
+          <t>Cannon-Brookes family (Mike Cannon-Brookes, co-founder of Atlassian)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.frigus.is/</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>https://www.grok.ventures/</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/grok-ventures</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>UK private limited company incorporated 2 Mar 2026 as the UK entity of Frigus, the Gudmundsson family's single family office (group HQ Kópavogur, Iceland, with a Luxembourg office). Frigus actively manages the family's assets, investments and real estate; its principal holding is a stake in LSE-listed Greencore Group, arising from the 2026 merger of the family business Bakkavor into Greencore. Registered at a London residential address (Fountain House, Park Street, Mayfair).</t>
+          <t>Sydney-based single-family office of Atlassian co-founder Mike Cannon-Brookes. One of Australia's most prominent family offices, it has increasingly concentrated on climate and clean-technology investing (backing SunCable's Australia-Asia Power Link, battery and decarbonisation ventures) alongside a diversified portfolio; in early 2026 it announced a climate-only investment focus.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Active management of family assets, investments and real estate (per frigus.is); large concentrated public-equity position in Greencore Group plus real estate.</t>
+          <t>Mission-driven investing to accelerate decarbonisation and net-zero, via venture and direct stakes in climate/clean-tech, energy and enabling technologies.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Listed equities (food manufacturing via Greencore Group stake), real estate, diversified investments</t>
+          <t>Climate tech, clean energy/renewables, batteries, decarbonisation, technology venture</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>London (UK entity); group HQ Kópavogur, Iceland</t>
+          <t>Sydney</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>London, England (UK entity); Capital Region, Iceland (group)</t>
+          <t>New South Wales</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Lydur Gudmundsson</t>
+          <t>Mike Cannon-Brookes</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Founder / controlling principal (PSC); co-founder of Bakkavor</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr"/>
+          <t>Founder / Family Principal</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mikecannonbrookes</t>
+        </is>
+      </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
         <is>
@@ -3774,34 +3726,34 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr">
         <is>
-          <t>UK entity newly incorporated Mar 2026, following the 2026 Bakkavor-Greencore merger. Director Andrea Olsen (Icelandic, CEO/MD of Frigus ehf) appointed at incorporation. Historic Frigus-branded UK entities dissolved (Frigus Ltd dissolved 2022; Frigus Invest Ltd dissolved 2018).</t>
+          <t>Announced climate-only investment focus and appointment of CEO Tan Kueh (Jan 2026); latest investment Asterix Foods seed round (2025-10-08); portfolio exit of Cog (2025-03-03); long-running backing of SunCable.</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>2026-03-02 (UK incorporation); 2026 (Bakkavor/Greencore merger)</t>
+          <t>2026-01; 2025-10-08; 2025-03-03</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>'Strong' proof applies to Frigus as a family office group (clear self-description + well-documented Gudmundsson/Bakkavor lineage); the specific UK entity 17062903 is brand-new (Mar 2026) with no filed accounts yet, so UK-level operations are unproven. Lydur Gudmundsson's nationality is shown as British on Companies House though he is the Icelandic Bakkavor co-founder. Switchboard/generic mailboxes belong to the Iceland/Luxembourg offices, not a UK-specific contact.</t>
+          <t>principal_linkedin is the plausible public Mike Cannon-Brookes /in/ profile but not verified to explicitly list Grok Ventures (marked unconfirmed). Website domain (grok.ventures) asserted from press, not independently fetched. Mike and Annie Cannon-Brookes separated (2023); the office remains Mike's family office.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SFO-bayshore-global-brin</t>
+          <t>SFO-woodbridge-company-thomson</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bayshore Global Management (Brin Family Office)</t>
+          <t>The Woodbridge Company (Thomson Family Office)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3811,53 +3763,61 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Brin family (Sergey Brin, Google co-founder)</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
+          <t>Thomson family (descendants of Roy Thomson; chaired by David Thomson, 3rd Baron Thomson of Fleet)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://www.woodbridge.ca/</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Low-profile single-family office managing the wealth of Sergey Brin across public and private markets, real estate and philanthropy. Additional office in Singapore. Reported to have absorbed the Nexus NeuroTech brain-health VC fund in 2026.</t>
+          <t>Toronto-based private holding company and family office of the Thomson family, Canada's wealthiest. Controls the family's ~68% stake in Thomson Reuters and owns The Globe and Mail, alongside a diversified portfolio spanning real estate, private equity, public equities, art and other alternatives.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Broad multi-asset allocation with notable venture/science-and-health direct investing.</t>
+          <t>Long-term stewardship of multi-generational family wealth; retain control of the Thomson Reuters core holding and diversify across private equity, real estate and alternatives.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Diversified; neuroscience/brain-health, deep tech, real estate</t>
+          <t>Information/media (core, via Thomson Reuters), real estate, private equity, public equities, art/alternatives</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Toronto</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>Ontario</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>United States of America</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Sergey Brin</t>
+          <t>Jay Forbes</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Family Principal</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr"/>
+          <t>President &amp; CEO, The Woodbridge Company</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>https://ca.linkedin.com/in/jay-forbes-fcpa-fca-51b8924</t>
+        </is>
+      </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
@@ -3867,72 +3827,84 @@
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr">
         <is>
-          <t>Absorbed Nexus NeuroTech brain-health VC fund (reported 2026-04-23, Bloomberg).</t>
+          <t>Jay Forbes became president &amp; CEO of Woodbridge in September 2024; continues as controlling (~68%) shareholder of Thomson Reuters.</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2024-09</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>No public website confirmed. AUM figures are press estimates. CEO George Pavlov / CIO Marie Young named in Wikipedia and press but not verified against a primary filing.</t>
+          <t>Primarily a controlling HOLDING company for Thomson Reuters rather than a liquid-portfolio family office; classified SFO at the holding/family-office level (precedent: KIRKBI, COFRA). Does not file U.S. 13F for its own account (appears in Thomson Reuters ownership 13D/G filings). AUM not disclosed. Website domain (woodbridge.ca) asserted, not independently fetched. Principal set to the reachable investment lead (Jay Forbes) per LinkedIn pass. Forbes (ex-CEO Element Fleet) became President &amp; CEO of Woodbridge, the Thomson family investment company, in Sept 2024; reachable over figurehead David Thomson. /in/ profile is the correct individual (Jay Forbes, FCPA FCA) but still lists his prior Element Fleet role, not Woodbridge, hence unconfirmed.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SFO-hillspire-schmidt</t>
+          <t>SEC13F-0001599603</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hillspire (Eric Schmidt Family Office)</t>
+          <t>Tarbox Family Office, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Schmidt family (Eric &amp; Wendy Schmidt; Eric Schmidt is former Google/Alphabet CEO and chairman)</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
+          <t>None as a single client family; founder-owned firm (Laura Tarbox founder, CEO and principal owner). Namesake is the founder, not a served family.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://tarbox.com/</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/tarboxfamilyoffice</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Single-family office of Eric and Wendy Schmidt focused on deep technology: artificial intelligence, quantum computation, defense tech and biotech. Reported to have invested in 22+ private AI firms since 2019 (including Anthropic, SandboxAQ, Inworld AI) and topped CNBC's inaugural family-office dealmaking ranking for 2025.</t>
+          <t>Newport Beach, CA-based multi-family office and SEC-registered investment adviser founded in 1985 by Laura Tarbox, CFP. Fee-only firm serving 100+ HNW/UHNW client families (also charities, businesses, trusts/estates) with comprehensive financial planning, tax preparation and individualized investment management; $5M minimum, over $1B AUM. Also has a Scottsdale, AZ office.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Deep-tech direct investing concentrated in AI, quantum, defense technology and biotech.</t>
+          <t>Team-based, individualized asset allocation and investment management integrated with comprehensive financial and estate planning; fee-only fiduciary model.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>AI, quantum computing, defense tech, biotech</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+          <t>Diversified asset-allocation / individualized investment management; no single-sector focus.</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Over $1 billion (100+ client families)</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>NEWPORT BEACH</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3942,98 +3914,110 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Eric Schmidt</t>
+          <t>Laura Tarbox</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Family Principal / Founder</t>
+          <t>Founder, CEO &amp; principal owner (CFP)</t>
         </is>
       </c>
       <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>laura@tarbox.com</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr"/>
+          <t>unverified</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>(949) 721-2330</t>
+        </is>
+      </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>Ranked #1 most active U.S. family office for dealmaking in 2025 (15 investments, mostly AI) per CNBC 2026-02-12; disclosed 22 private AI startup investments since 2019 (CNBC 2025-01-21).</t>
+          <t>Founded 1985; CFP since 1984; 100+ client families and &gt;$1B AUM; $5M account minimum; second office in Scottsdale, AZ; Laura Tarbox a frequent WSJ/NYT/LA Times media source</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>2026-02-12; 2025-01-21</t>
+          <t>1985 (founded); 1984 (Laura Tarbox CFP)</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>No public website confirmed (hillspire.com not verified). Does not file 13F (EDGAR full-text search returned no 13F-HR). AUM not disclosed. President Ken Goldman named in press, not verified against a primary filing.</t>
+          <t>Personal LinkedIn /in profile not located (only firm company page). Email captured from Laura Tarbox's public presentation PDF (matches firm domain) rather than the current bio page; treat as published-but-unverified.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SFO-mousse-partners-wertheimer</t>
+          <t>SEC13F-0002056106</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mousse Partners (Wertheimer Family Office)</t>
+          <t>Stenger Family Office, LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Wertheimer family (Alain and Gerard Wertheimer, owners of Chanel)</t>
+          <t>Stenger family (firm founded/led by Nick Stenger; the family has advised clients since 1981). The 'family' is the owner-operator, not a single client family.</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://moussepartners.com/</t>
+          <t>https://www.stengerfamilyoffice.com/</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/moussepartners</t>
+          <t>https://www.linkedin.com/company/stenger-family-office</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Investment firm serving as the family office of the Wertheimer family. Manages a global diversified portfolio across public equities, fixed income, private equity, venture and real estate, with investment operations in New York and Asia (Beijing, Hong Kong).</t>
+          <t>Naperville, IL-based multi-family office / independent fiduciary RIA led by founder-CEO Nick Stenger, offering financial planning, investment management, and (via related companies) tax preparation, estate strategies and insurance. Also has a Spring, TX office. ~$731M AUM; named a Forbes Best-in-State Wealth Advisor 2026.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Global multi-asset diversified investing with a notable consumer/brands tilt.</t>
+          <t>Goals-based planning: assesses cash needs and upcoming goals, then builds customized portfolios.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Diversified; consumer, luxury/brands, technology, real estate</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
+          <t>Core individual-stock portfolios and ETF-based asset-allocation portfolios; no single-sector focus.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>~$731 million (as of 2026-06-30)</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>NAPERVILLE</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4043,622 +4027,678 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Charles Heilbronn</t>
+          <t>Nicholas David Stenger</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Founder / Chairman</t>
+          <t>Founder &amp; Chief Executive Officer</t>
         </is>
       </c>
       <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>nick.stenger@stengerfamilyoffice.com</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>630-912-8295</t>
+        </is>
+      </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>Bloomberg feature (2024-2025) reporting the office reshaping its consumer/public-equity bets.</t>
+          <t>$731M AUM (2026-06-30); Forbes Best-in-State Wealth Advisor 2026; hosts 'The Nick Stenger Show' podcast; opened Spring, TX office</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2024/2025 (Bloomberg feature)</t>
+          <t>2026-06-30 (AUM date); 2026 (Forbes Best-in-State)</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>Does not appear as a 13F filer under 'Mousse Partners' (EDGAR full-text search returned 0); investment vehicle is domiciled offshore (Mousse Investments Limited, Bermuda) with a NYC office (9 W. 57th St). AUM figure is the family fortune, not disclosed firm AUM. Firm general phone reported as 212-303-5795 (not an individual principal line).</t>
+          <t>Serves 1,200+ families 'of all net worth sizes' — a broad wealth-management RIA using family-office branding rather than a classic UHNW MFO; hence proof strength 'corroborated'. Personal LinkedIn /in profile not located (only company page and a Calendly slug for 'nicholasstenger'). No published individual email or direct phone line found.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SFO-kirkbi-kristiansen</t>
+          <t>SEC13F-0001908612</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>KIRKBI (Kirk Kristiansen Family Office)</t>
+          <t>Allie Family Office LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Kirk Kristiansen family (owners of the LEGO Group)</t>
+          <t>None (owner-operated MFO). Founded 2019 and 100% owned by Bruno Ghio, formerly Regional Head of the Family Office / Managing Director at Banco de Credito del Peru (BCP) and a senior private banker at JPMorgan. Not tied to a single client family.</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://www.kirkbi.com/</t>
+          <t>https://allie-intl.com/en/home/</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/kirkbi</t>
+          <t>https://www.linkedin.com/company/alli%C3%A9-family-office</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Danish family-owned holding and investment company managing the wealth and legacy of the Kirk Kristiansen family. Holds the family's controlling stakes in LEGO Group and Merlin Entertainments and runs a long-term investment portfolio plus a dedicated climate/energy-transition program (KIRKBI Climate). Additional offices in Copenhagen and Baar, Switzerland.</t>
+          <t>Miami-based (with a Lima, Peru office) independent multi-family office and SEC-registered investment adviser founded in 2019 by Bruno Ghio, serving Latin American — predominantly Peruvian — high-net-worth families. Provides discretionary and limited-discretionary portfolio management, wealth structuring, tax planning, single-family-office consulting and cross-border coordination via a global network of tax/legal/banking experts.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Protect and grow family wealth for future generations; long-term core holdings (LEGO, Merlin) plus diversified investments and thematic climate/energy investing.</t>
+          <t>Cross-border wealth management and multi-generational governance for Latin American families relocating capital (and increasingly themselves) to the US; independent, conflict-free advisory.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Toys/entertainment (core), real estate, renewable energy/climate, diversified financial investments</t>
+          <t>Discretionary and limited-discretionary global portfolio management (largest reported 13F holding is the SPDR S&amp;P 500 ETF Trust; 95 equity positions); diversified across public markets, no single-sector focus disclosed.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>~$16 billion (family wealth)</t>
+          <t>~$1.15 billion AUM (as of 2024-12-31: ~$508.7M discretionary + ~$637.9M limited-discretionary); aggregators (FINTRX) report ~$1.3B; press (Bloomberg/Crain, 2024) cites ~$2B across the Peru/Miami practice</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Billund</t>
+          <t>MIAMI</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Region of Southern Denmark</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Soren Thorup Sorensen</t>
+          <t>Bruno Ghio</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr"/>
+          <t>Founder &amp; Chief Executive Officer (CFA, CAIA, FRM); 100% owner</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>https://pe.linkedin.com/in/bruno-ghio-1264b616b</t>
+        </is>
+      </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr"/>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>7866357162</t>
+        </is>
+      </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>KIRKBI Climate follow-on investment in Highview Power (Hunterston project) announced November 2025 (second investment after June 2024 Carrington); Adapture Renewables (KIRKBI-majority-owned) acquired 110MW Colorado solar-plus-storage project March 2025; generational handover of board chair to Thomas Kirk Kristiansen May 2023.</t>
+          <t>Founded 2019; among Peru's top-3 independent multi-family offices; ~23 client families (avg ~$50M); Miami + Lima offices; growth from Peruvian clients relocating to Miami; added a partner in Peru</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>2025-11; 2025-03; 2023-05</t>
+          <t>2019 (firm founding); 2024 (Bloomberg/Crain profile); AUM as of 2024-12-31</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>KIRKBI is both the family holding company (owns LEGO) and the family investment office; some may classify it as a holding company rather than a pure family office. AUM figure is the family-wealth press figure, not full portfolio value.</t>
+          <t>Legal 13F filer name is 'Allie Family Office LLC'; brand is 'Allié Family Office' (allie-intl.com). AUM figures vary by source (~$1.15B ADV vs ~$1.3B FINTRX vs ~$2B press including the broader Peru practice). No individual email or direct phone published; only generic info@ mailbox. Jose Larrabure is the investment lead; Bruno Ghio named principal as founder/CEO/100% owner.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SFO-tethys-invest-bettencourt</t>
+          <t>SEC13F-0001511137</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tethys / Tethys Invest (Bettencourt Meyers Family Office)</t>
+          <t>Pathstone Family Office, Llc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Bettencourt Meyers family (majority shareholder of L'Oreal; Francoise Bettencourt Meyers)</t>
+          <t>No single family; one of the largest U.S. multi-family offices serving many UHNW families, SFOs and institutions.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://tethys.fr/</t>
+          <t>https://pathstone.com</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/t%C3%A9thys</t>
+          <t>https://www.linkedin.com/company/pathstone-family-office</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Paris-based single-family office of the Bettencourt Meyers family, holder of the family's ~34% L'Oreal stake. Its subsidiary Tethys Invest (&gt;EUR 3bn capital) makes long-term direct investments deliberately outside L'Oreal's competitive scope, with a healthcare emphasis (Elsan private hospitals, Sebia diagnostics).</t>
+          <t>Englewood, NJ headquartered partner-owned multi-family office and SEC-registered RIA founded in 2010 (co-founders Matthew Fleissig, Allan Zachariah, Steve Braverman). Provides integrated investment management, tax, insurance/risk, legacy planning and family-office services to UHNW families, family offices, foundations and endowments; ~$125B firm AUM (2025).</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Preserve the L'Oreal core holding and deploy dividend income into long-term entrepreneurial direct investments, notably healthcare, that do not compete with L'Oreal.</t>
+          <t>Integrated, institutional-quality advice with a client-first culture; open-architecture investment management including private markets and alternatives; scale via organic growth and acquisitions (e.g., Crestone Capital).</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Healthcare (hospitals, diagnostics), consumer, technology, diversified</t>
+          <t>Public equities (13F holdings), private markets/alternatives, fixed income, diversified multi-asset portfolios</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>&gt; $90 billion (family assets)</t>
+          <t>~$125 billion (firm) as of 12/31/2025; ~$187 billion including affiliate firms (other sources cite $170B+ aggregate in 2025).</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>ENGLEWOOD</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Ile-de-France</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Alexandre Benais</t>
+          <t>Matthew Fleissig</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>CEO, Tethys Invest</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr"/>
+          <t>Chief Executive Officer (co-founder)</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/fleissig/</t>
+        </is>
+      </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>857-305-3070</t>
+        </is>
+      </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>Named new head of family investment firm reported 2023-03-13 (The National); family succession moves (Jean-Victor Meyers to L'Oreal vice-chairman; Alexandre Benais to family L'Oreal board seat) reported 2025-02; co-invested (with Chanel/Wertheimer) in The Row reported 2024-09.</t>
+          <t>Founded 2010; 15th anniversary in 2025; acquired Crestone Capital; ~775+ employees; co-founders Allan Zachariah and Steve Braverman serve as Co-Chairmen; multiple 2025 Family Wealth Report Awards.</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>2023-03-13; 2025-02-08; 2024-09</t>
+          <t>Founded 2010; AUM as of 12/31/2025; ADV dated 03/31/2025.</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>'Tethys' (parent) vs 'Tethys Invest' (investment subsidiary) are distinct entities; leadership names span both. AUM is the family-asset press figure, not a disclosed managed-portfolio AUM.</t>
+          <t>Very large firm; AUM figures vary by whether affiliate firms are included and by reporting date. No published individual email.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SFO-cofra-holding-brenninkmeijer</t>
+          <t>SEC13F-0001731123</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>COFRA Holding (Brenninkmeijer Family Office)</t>
+          <t>Biltmore Family Office, LLC</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Brenninkmeijer family (founders/owners of C&amp;A; ~500 family members)</t>
+          <t>Founder Chris Cecil is a great-grandson of George Vanderbilt (builder of the Biltmore Estate) and son of Asheville developer George Cecil; 'Biltmore' name derives from that Vanderbilt/Cecil family heritage. The firm serves many outside client families (MFO), not the Vanderbilt/Cecil family exclusively.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.cofraholding.com/</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>https://www.biltmorefamilyoffice.com/</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/biltmore-family-office-llc</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Zug-based family-owned holding coordinating the Brenninkmeijer family's global operations and ~EUR 35-38bn asset base across retail (C&amp;A), real estate (Redevco), private equity (Bregal Investments) and asset management (Anthos). In 2025 the family announced it would open its portfolio to outside investors, a shift from its historically secretive model.</t>
+          <t>Charlotte, NC-based multi-family office and SEC-registered investment adviser founded in 2008 by Chris Cecil. A collaborative/independent RIA to investment-oriented multi-generational families and institutions, providing investment management, asset allocation, investment-policy design, multi-generational and succession planning. ~$3.2-3.5B AUM.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Long-term stewardship of family capital across operating businesses, real estate, private equity and (increasingly) externally-opened investment platforms.</t>
+          <t>Collaborative, investment-policy-driven management for multi-generational HNW/UHNW families and institutions.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Retail, real estate, private equity, asset management, climate/energy</t>
+          <t>Diversified public-equity/ETF portfolios; disclosed top 13F holdings include AAPL, IAU (gold), AVDX, ROBO, VV. No single-sector concentration.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>EUR 35-38 billion</t>
+          <t>~$3.2-3.5 billion (reported ~$3.47B regulatory AUM across ~951 accounts)</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Zug</t>
+          <t>CHARLOTTE</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Canton of Zug</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Martijn Brenninkmeijer</t>
+          <t>Chris Cecil</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Chairman of the Board, COFRA Holding AG</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr"/>
+          <t>Founder, President &amp; CEO</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/chris-cecil-9701b818/</t>
+        </is>
+      </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>+1 704-248-5230</t>
+        </is>
+      </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>Announced opening of ~EUR 38bn portfolio to external investors (April 2025); Florian Brenninkmeyer appointed CFO effective 1 Jan 2025; Redevco closed landmark GBP 47.5m real-estate-debt loan (April 2025).</t>
+          <t>Founded 2008 by Chris Cecil (LLC organized 2013); ~$3.2-3.5B AUM across ~951 accounts, avg client ~$38M; Cecil chairs TIGER 21 Charlotte / Family Office groups</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>2025-04; 2025-01-01; 2025-04</t>
+          <t>2008 (founding); 2013 (LLC organized)</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>COFRA is primarily a family holding company; its asset-management arm Anthos is opening to third-party capital (2025), which blurs the pure single-family-office boundary. Classified SFO at the holding level but noted as trending toward external capital.</t>
+          <t>Chris Cecil chosen as principal (founder/CEO); Rael Gorelick is Partner &amp; Head of Investments and would be the CIO-level investment lead. No published individual email located. AUM varies by source ($3.2B-$3.5B).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SFO-athos-strungmann</t>
+          <t>SEC13F-0001039807</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Athos (Strungmann Family Office)</t>
+          <t>Boston Family Office Llc</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SFO</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Strungmann family (Andreas and Thomas Strungmann, founders of Hexal)</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
+          <t>MFO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://www.bosfam.com/</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Munich-based single-family office of the Strungmann twins, focused heavily on biotech and life sciences. Anchored and remains largest shareholder of BioNTech (~43.5%) and holds stakes in Formycon and Immatics; actively recycles BioNTech proceeds into new European biotech ventures.</t>
+          <t>The Boston Family Office LLC is an independent, employee-owned registered investment adviser founded in 1996 and based in Boston, MA. It provides multi-family-office-style wealth management -- investment management, financial planning, and adviser selection -- to high-net-worth individuals, families and charitable organizations across roughly 789 accounts and ~$1.7-2.0B in assets. It is a multi-family/RIA firm rather than a single-family office.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Long-horizon anchor investing in biotech and life sciences, recycling returns from BioNTech into the next generation of European biotech.</t>
+          <t>Client-tailored, diversified portfolio management for wealth preservation and growth across HNW households and institutions; discretionary management (769 of 789 accounts discretionary). Specific house investment philosophy not detailed publicly.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Biotech, life sciences, healthcare technology</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
+          <t>Diversified multi-asset wealth management (public equities, fixed income, funds); not sector-specialized. A partner sits on the board of fixed-income manager Breckinridge Capital Advisors.</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>~$1.7B AUM across 789 accounts (Form ADV/adviserinfo, 2024-2025); third-party profiles cite ~$1.9-2.02B. As of the most recent Form ADV (2024 filing cycle).</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Munich</t>
+          <t>Boston</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Bavaria</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Andreas Strungmann</t>
+          <t>George P. Beal</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Family Principal / Co-Founder</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr"/>
+          <t>Co-Founder &amp; Managing Partner (Portfolio Manager)</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/george-beal-a6107a16/</t>
+        </is>
+      </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>617-624-0800</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>Participated in AAVantgarde Bio's $141m Series B (Nov 2025); AMSilk EUR 52m round (Sep 2025); Antheia funding ($56m Jun 2025, $24m Jan 2026); admin services of Athos Service acquired by Bolder Group (May 2024).</t>
+          <t>Filed Form ADV Part 2A/2B brochures in the 2024 filing cycle (Feb 2024); a partner (Beal) serves on the board of Breckinridge Capital Advisors. Firm moved offices to 20 Custom House St.</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>2025-11; 2025-09; 2025-06; 2026-01; 2024-05</t>
+          <t>2024-02-01 (ADV Part 2B brochure)</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>No public website confirmed. 'Athos Service GmbH' is the services entity; the investing vehicle is often cited as 'Athos KG'. Investment-round dates sourced from family-office trade press rather than primary filings. AUM not disclosed.</t>
+          <t>Despite the 'family office' name, this is functionally a multi-family-office RIA / private wealth manager serving hundreds of client accounts, not a single family's office. Investment authority is distributed among ~8 managing directors, so Beal is one of several senior decision-makers (though the 13F signatory and co-founder). No official company LinkedIn URL confirmed. No individual email is published (the ZoomInfo masked pattern was deliberately not used).</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SFO-premji-invest</t>
+          <t>SEC13F-0002017744</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Premji Invest (Azim Premji Family Office)</t>
+          <t>Arrowroot Family Office, LLC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SFO</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Premji family (Azim Premji, founder of Wipro)</t>
-        </is>
-      </c>
+          <t>MFO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://www.premjiinvest.com/</t>
+          <t>https://arrowrootfamilyoffice.com/</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/premjiinvest</t>
+          <t>https://www.linkedin.com/company/arrowroot-family-office</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bengaluru-based family office and investment firm managing the wealth of Azim Premji and family (and closely tied to the Azim Premji Foundation endowment). Invests across public equities, private equity and venture, backing technology, financial services, consumer, healthcare and industrials; crossed $10bn in managed assets.</t>
+          <t>Arrowroot Family Office, LLC is a Marina del Rey, CA-based registered investment adviser and multi-family office, originally founded in 2013 as Vitreous Partners and rebranded in 2017. It provides multidisciplinary wealth management -- investment management, retirement, tax and estate planning -- to high-net-worth individuals, entrepreneurs, families and small institutions, with offices in Southern and Northern California, Virginia and Michigan. It is a multi-client RIA, not a single family's office.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Long-horizon growth investing across public and private markets in emerging/disruptive technology and consumer/financial sectors.</t>
+          <t>Team-based, fiduciary, goals-driven wealth management emphasizing comprehensive planning and diversified investment management for affluent households and business owners; open-architecture advice.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Technology, financial services, consumer, healthcare, industrials</t>
+          <t>Diversified multi-asset wealth management (public equities, funds/ETFs, fixed income, alternatives); not sector-specialized.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>&gt; $10 billion</t>
+          <t>~$431M AUM as of Q2 2025 (third-party profiles); regulatory AUM per the 2025 Form ADV on the firm's site. A floor for total client assets under advisement.</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Marina Del Rey</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>T.K. Kurien</t>
+          <t>Rob (Roberto Francisco) Santos</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>CEO &amp; Managing Partner</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr"/>
+          <t>Chief Executive Officer &amp; Principal Owner</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rob-santos-afo/</t>
+        </is>
+      </c>
       <c r="Q40" t="inlineStr"/>
       <c r="R40" t="inlineStr">
         <is>
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr"/>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>310.341.4774</t>
+        </is>
+      </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>Acquisition of Anand Chemiceutics reported 2025-11-13; participated in Runway Series E (with General Atlantic, Nvidia) 2026-02-10; 19 funding rounds / 2 acquisitions in trailing 12 months (per Tracxn, Feb 2026).</t>
+          <t>Announced expansion of its private-wealth practice into Michigan via addition of The Athena Financial Group (offices now include Marina del Rey CA, Rochester Hills MI, Charlottesville VA, El Dorado Hills CA); filed updated Form ADV Part 2A/2B in April 2025.</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2025-11-13; 2026-02-10</t>
+          <t>2022-09-05 (Michigan/Athena expansion press release); 2025-04 (Form ADV update)</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>Premji Invest also manages the Azim Premji Foundation's endowment, so it straddles family-office and foundation-endowment functions; consistently described as a family office, hence corroborated rather than strong-single-family-only.</t>
+          <t>Uses the 'family office' label but is a multi-client wealth-management RIA, not a single family's office. Possible name confusion with 'Arrowroot Capital Management' (a separate B2B enterprise-software private-equity firm) -- they are distinct; relationship not established here. No individual email published; RocketReach/broker data deliberately not used. Firm's most recent 13F filer registration is recent (CIK 0002017744).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SFO-catamaran-ventures-murthy</t>
+          <t>SEC13F-0001756485</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Catamaran Ventures (N.R. Narayana Murthy Family Office)</t>
+          <t>Independent Family Office, LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Murthy family (N.R. Narayana Murthy, co-founder of Infosys)</t>
+          <t>None (owner-operated MFO). Founded 2005 by W. Michael Reickert, who previously led the family-office practice at The Ayco Company. Serves multiple entrepreneurial client families; not a single-family vehicle.</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://catamaran.in/</t>
+          <t>https://ifollc.com/</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/catamaran-ventures</t>
+          <t>https://www.linkedin.com/company/independent-family-office-llc</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bengaluru-based single-family office of Infosys co-founder N.R. Narayana Murthy, investing permanent family capital (no external LPs). Focused on growth capital, notably Indian manufacturing and deep tech; has recently turned more cautious on Indian startup valuations.</t>
+          <t>Albany, New York-based multi-family office and SEC-registered investment adviser founded in 2005 by W. Michael Reickert. A bespoke family office serving a small number of high-net-worth families (average client tenure 10+ years) with investment advisory and asset allocation, estate-planning coordination, transaction/contract advisory and income-tax planning and compliance.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Permanent-capital growth investing, with emphasis on Indian manufacturing and deep-tech, valuation-disciplined.</t>
+          <t>Technical, unbiased, independent long-term stewardship of client families' financial lives; capital-allocator approach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Manufacturing, deep tech, consumer, technology</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
+          <t>Discretionary portfolio management and outside-manager selection for HNW families (largest reported 13F holding is the SPDR S&amp;P 500 ETF Trust); diversified, no single-sector focus disclosed.</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>~$617.8 million discretionary AUM across ~34 clients (Form ADV, 2025-03-31); aggregators (FINTRX) report ~$760M</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>ALBANY</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United States of America</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>N.R. Narayana Murthy</t>
+          <t>W. Michael Reickert</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Founder / Chairman Emeritus (Family Principal)</t>
+          <t>Managing Member / Managing Partner &amp; CEO (also Chief Compliance Officer); IRS Enrolled Agent, JD</t>
         </is>
       </c>
       <c r="P41" t="inlineStr"/>
@@ -4668,97 +4708,113 @@
           <t>unresolved</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr"/>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>(518) 452-8050</t>
+        </is>
+      </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>Bloomberg (2025-08-26) reporting Catamaran growing cautious on Indian startup valuations; recent deep-tech stake and follow-on investments (Akshayakalpa first-time, Innoviti follow-on) in 2025.</t>
+          <t>Founded 2005; SEC-registered 2012; ex-Ayco family-office pedigree; very low client count (~34) with 10+ year average tenure</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>2025-08-26; 2025</t>
+          <t>2005 (founding); 2012 (SEC registration); AUM ~$617.8M as of 2025-03-31</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>Investment pace slowed in 2025 (approximately one new investment) per Tracxn; AUM not disclosed.</t>
+          <t>Firm marketing copy calls itself a 'bespoke family office' for 'select clients'; the ~34-client, multi-family reality plus Altss classification support MFO. 'dr@ifollc.com' is published but its initials do not match the principal, so it is treated as a shared/general mailbox, not the principal's individual email. No personal LinkedIn confirmed for W. Michael Reickert.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>APAC-weybourne-holdings-dyson</t>
+          <t>UKCH-09580739</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Weybourne (James Dyson Family Office)</t>
+          <t>Blu Family Office Limited</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Dyson family — Sir James Dyson (founder of Dyson Ltd) and family</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
+          <t>Originally Armbruester family (founder's wealth); now MFO serving multiple client families</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>https://www.blu-fo.com</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/company/blu-family-office</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Single-family office managing the wealth of Sir James Dyson, founder of the Dyson appliance/engineering group. Founded 2013; a Singapore holding company (Weybourne Holdings Pte Ltd) now sits above the group, alongside a London office and a Singapore-based insurance unit. Investments span English farmland (the Dyson family is among England's largest private landowners), commercial and residential real estate, technology ventures and public markets.</t>
+          <t>FCA-regulated multi-family office (Ltd inc. 2015; operations from 2010) in Richmond upon Thames, founded by Christian Armbruester post Credit Suisse. Offers hedge funds, crypto and alternatives; discretionary arm Blu Investment Management.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Long-horizon preservation and growth of the Dyson family fortune across agricultural land, real estate, technology ventures and public markets.</t>
+          <t>Discretionary management not relying on forecasting; 'true diversification' and systematic rebalancing; passive in calm markets, opportunistic in adverse ones.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Agricultural land/farmland; Real estate (commercial and residential); Technology ventures; Public equities</t>
+          <t>Hedge funds; crypto assets; alternatives; diversified multi-asset</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>~USD17-21 billion (family fortune under management; not an officially disclosed AUM figure)</t>
+          <t>£0.5bn-£1bn (third-party estimated range)</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Richmond</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Greater London</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>James Dyson</t>
+          <t>Christian Armbruester</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Founder and family principal (Weybourne CEO since Feb 2025: Martin Bowen)</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr"/>
+          <t>Founder &amp; Principal (largest shareholder ~40.8%)</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/christianarmbruesterblufamilyoffice</t>
+        </is>
+      </c>
       <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
         <is>
@@ -4768,90 +4824,98 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr">
         <is>
-          <t>Feb 2025: Martin Bowen (ex-Dyson Group PLC legal veteran) appointed Weybourne CEO, succeeding James Bucknall. 2025: transferred at least GBP624m (~USD834m) from a major UK entity to the Singapore holding company, reducing the UK unit's share capital to GBP1. Office reported at 70+ employees across London and Singapore.</t>
+          <t>Founded 2010; Ltd inc. 2015; new director Vishesh Dawar appointed Dec 2025; investment arm rebranded Blu Investment Management; Marie Redron now CEO</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2025-02; 2025</t>
+          <t>2015-05-08; 2025-12-08</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>Group is split between London and Singapore; this record treats the Singapore holding company (Weybourne Holdings Pte Ltd) as HQ per 2025 restructuring reporting. weybourne.com resolves to a parked GoDaddy page, so no confirmed public website/domain. AUM is an estimated family fortune, not a disclosed FO figure. Principal LinkedIn not verified.</t>
+          <t>Client-facing operations now run under 'Blu Investment Management' (blu-im.com), same address. Armbruester is founder/principal but not current CEO (Marie Redron is). AUM range is a third-party estimate. Only published contacts are a switchboard + generic mailbox.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>APAC-dalio-family-office-singapore</t>
+          <t>UKCH-12233405</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Dalio Family Office (Ray Dalio) — Singapore</t>
+          <t>Schwarz Family Office Ltd</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>Undetermined</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Dalio family — Ray Dalio (founder of Bridgewater Associates) and family</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
+          <t>Named after principal Andreas Schwarz (German); no wider family group evidenced beyond the surname</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://schwarzfamilyoffice.com/</t>
+        </is>
+      </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
-          <t>The Singapore office of Ray Dalio's global single-family office. The Dalio Family Office invests across private equity, venture capital, real estate and credit and runs the family's philanthropy in Asia. Singapore was chosen as the Asia base given Dalio's long-standing ties to Singapore and China; the DFO also operates in Abu Dhabi. Globally the DFO is led by CEO Janine Racanelli (ex-JPMorgan) and COO Tom Waller; the Singapore office has been associated with Managing Director Tan Mae Shen.</t>
+          <t>London-based boutique investment/advisory firm branded as a family office, established 2019, led by Andreas Schwarz; provides capital raising, debt financing, wealth management and IR services.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Global multi-asset investing (PE, VC, real estate, credit) with a Singapore hub for Asian investments and philanthropy.</t>
+          <t>'Be not afraid of growing slowly, be afraid only of standing still' — sustainable growth via established relationships and exclusive investor access. https://schwarzfamilyoffice.com/</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Private equity; Venture capital; Real estate; Credit</t>
+          <t>Private equity; fintech; wealth management; venture capital; private debt; IPOs</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>London</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Maida Vale</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Ray Dalio</t>
+          <t>Andreas Schwarz</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Founder and family principal (global DFO CEO: Janine Racanelli; Singapore MD: Tan Mae Shen)</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr"/>
+          <t>Founder / Director</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>https://uk.linkedin.com/in/andreas-schwarz-63437064</t>
+        </is>
+      </c>
       <c r="Q43" t="inlineStr"/>
       <c r="R43" t="inlineStr">
         <is>
@@ -4861,66 +4925,74 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr">
         <is>
-          <t>2020: Dalio Family Office opened in Singapore; Dalio donated USD25m to Singapore's Wealth Management Institute. 2021: Tan Mae Shen joined as Singapore MD; Dalio bought two Club Street shophouses for ~SGD18.9m. Global CIO Mark Baumgartner departed Aug 2024.</t>
+          <t>Listed in Family Capital 'FamCap 50' (2024); second shareholder Syed Furqan Ahmed (490 shares)</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>2020; 2021; 2024-08</t>
+          <t>2024-02 (FamCap 50)</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>C+</t>
+          <t>B+</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>The Dalio Family Office's global headquarters is in Westport, Connecticut (USA), with offices in New York, Singapore and Abu Dhabi; this record covers the Singapore office as a Singapore-hubbed APAC operation, not the global HQ. No AUM or public website confirmed. Principal LinkedIn not verified.</t>
+          <t>Presents as a family office but functions largely as a boutique capital-raising/advisory consultancy with two shareholders — fo_type left Undetermined. A Family Capital story linking Schwarz to a 'famous UK brand' is paywalled and the brand is NOT confirmed; not asserted. AUM undisclosed.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>APAC-sunrise-capital-shu-ping</t>
+          <t>APAC-farro-capital</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Sunrise Capital Management (Shu Ping / Haidilao Family Office)</t>
+          <t>Farro Capital</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SFO</t>
+          <t>MFO</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Shu Ping — co-founder of Haidilao hotpot chain; spouse Zhang Yong (Haidilao co-founder), both naturalised Singapore citizens</t>
-        </is>